--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -12,9 +12,9 @@
     <sheet name="Prefill_8K" sheetId="3" r:id="rId3"/>
     <sheet name="Decode_1M" sheetId="4" r:id="rId4"/>
     <sheet name="Memory" sheetId="5" r:id="rId5"/>
-    <sheet name="Summary" sheetId="6" r:id="rId6"/>
-    <sheet name="Comparison" sheetId="7" r:id="rId7"/>
-    <sheet name="Methodology" sheetId="8" r:id="rId8"/>
+    <sheet name="Comparison" sheetId="6" r:id="rId6"/>
+    <sheet name="Methodology" sheetId="7" r:id="rId7"/>
+    <sheet name="Summary" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Layer_Config!$A$3:$F$67</definedName>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="600">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1675,7 +1675,7 @@
     <t>按 MaxContext 预分配，KV 在每个 TP Rank 复制。</t>
   </si>
   <si>
-    <t>逐 Rank 设备驻留容量（默认均匀分片）</t>
+    <t>单 Rank 设备驻留容量（默认均匀分片）</t>
   </si>
   <si>
     <t>配置</t>
@@ -1711,34 +1711,172 @@
     <t>TP1</t>
   </si>
   <si>
+    <t>任一 Rank</t>
+  </si>
+  <si>
+    <t>1 个 Rank 均相同</t>
+  </si>
+  <si>
     <t>TP8</t>
   </si>
   <si>
-    <t>每 Rank 推理硬件资源汇总</t>
-  </si>
-  <si>
-    <t>面向 TP1 / TP8 硬件选型：计算量、HBM 流量、参数量、参数容量与 KV Cache。</t>
+    <t>8 个 Rank 均相同</t>
+  </si>
+  <si>
+    <t>TP1 / TP8 推理资源对比图</t>
+  </si>
+  <si>
+    <t>所有图表使用线性坐标与固定 M/G/T 单位，不显示科学计数法。</t>
+  </si>
+  <si>
+    <t>Prefill TP1 TFLOPs</t>
+  </si>
+  <si>
+    <t>Prefill TP8 TFLOPs</t>
+  </si>
+  <si>
+    <t>Decode TP1 GFLOPs</t>
+  </si>
+  <si>
+    <t>Decode TP8 GFLOPs</t>
+  </si>
+  <si>
+    <t>Prefill TP1 GB</t>
+  </si>
+  <si>
+    <t>Prefill TP8 GB</t>
+  </si>
+  <si>
+    <t>Decode TP1 GB</t>
+  </si>
+  <si>
+    <t>Decode TP8 GB</t>
+  </si>
+  <si>
+    <t>TP1 参数 GB/rank</t>
+  </si>
+  <si>
+    <t>TP8 参数 GB/rank</t>
+  </si>
+  <si>
+    <t>容量项</t>
+  </si>
+  <si>
+    <t>TP1 GB/rank</t>
+  </si>
+  <si>
+    <t>TP8 GB/rank</t>
+  </si>
+  <si>
+    <t>参数</t>
+  </si>
+  <si>
+    <t>Decode KV+State</t>
+  </si>
+  <si>
+    <t>方法与统计边界</t>
+  </si>
+  <si>
+    <t>主题</t>
+  </si>
+  <si>
+    <t>定义</t>
+  </si>
+  <si>
+    <t>统计范围</t>
+  </si>
+  <si>
+    <t>仅统计 43 层主推理路径；不含 MTP、反向传播、梯度、优化器状态和训练激活。Layer_Config 最多可维护 64 层。</t>
+  </si>
+  <si>
+    <t>计算量</t>
+  </si>
+  <si>
+    <t>矩阵乘加按 2 FLOPs 计。Attention 与 MoE 主要 GEMM 使用显式公式；HC 与逐元素运算为近似估计。</t>
+  </si>
+  <si>
+    <t>Prefill Attention</t>
+  </si>
+  <si>
+    <t>使用因果候选对数量，不直接使用 S×S；Raw Window、Compressed KV 和 Indexer 扫描分别统计。</t>
+  </si>
+  <si>
+    <t>Decode Attention</t>
+  </si>
+  <si>
+    <t>每个 DecodeTokens 在 DecodeContext 下建模；ratio-4 主 Attention 取 Top-K，但 Indexer 需要扫描全部已完成压缩项。</t>
+  </si>
+  <si>
+    <t>每 Token 执行 Top-K Routed Experts 和 Shared Experts。HBM 参数读取按专家至少被命中一次的概率估计。</t>
+  </si>
+  <si>
+    <t>HBM 流量</t>
+  </si>
+  <si>
+    <t>统计本地逻辑参数、激活和 KV 的读取与写入；不模拟 L2 命中、算子融合、分块、Allocator 或厂商 Kernel 内部复用。</t>
+  </si>
+  <si>
+    <t>参数容量</t>
+  </si>
+  <si>
+    <t>按推理运行 dtype 估算：Routed Expert FP4、多数投影 FP8、Wo_a BF16、Compressor FP32、LM Head FP32，并计入量化 Scale。</t>
+  </si>
+  <si>
+    <t>KV Cache</t>
+  </si>
+  <si>
+    <t>有效容量表示已填充项；预分配容量使用 MaxContext。当前实现的 KV 和 Compressor State 在每个 TP Rank 上完整复制。</t>
+  </si>
+  <si>
+    <t>TP 分片</t>
+  </si>
+  <si>
+    <t>Wq_a、Wkv、Compressor、Router、HC、Shared Expert 复制；Q/O 部分投影、Routed Experts、Embedding 和 LM Head 按 TP 分片。</t>
+  </si>
+  <si>
+    <t>卡间通信</t>
+  </si>
+  <si>
+    <t>Ring 公式给出每 Rank 发送加接收的数据量。TP1 为 0；该数值是传输量，不是实测 GB/s 或时延。</t>
+  </si>
+  <si>
+    <t>硬件下界</t>
+  </si>
+  <si>
+    <t>计算/HBM/互连下界使用 Parameters 中可编辑硬件峰值并假设互不重叠；真实运行时间必须通过 Profiling 验证。</t>
+  </si>
+  <si>
+    <t>FLOPs 使用 M/G/T/P 十进制单位；容量与流量使用 KB/MB/GB/TB，1 GB=10^9 Bytes；Memory 明细保留原始公式。</t>
+  </si>
+  <si>
+    <t>公式维护</t>
+  </si>
+  <si>
+    <t>蓝色单元格为输入；结果由 Excel 公式计算并在打开时完整重算。隐藏列保留原始未缩放值，便于审计。</t>
+  </si>
+  <si>
+    <t>单 Rank 推理硬件资源汇总</t>
+  </si>
+  <si>
+    <t>TP1 与 TP8 分区独立展示；所有值均为单个 Rank，不进行跨 Rank 或跨 TP 求和。</t>
+  </si>
+  <si>
+    <t>TP1（配置值=1）单 Rank 资源</t>
   </si>
   <si>
     <t>资源项目</t>
   </si>
   <si>
-    <t>Prefill TP1</t>
-  </si>
-  <si>
-    <t>Prefill TP8/rank</t>
-  </si>
-  <si>
-    <t>Decode TP1</t>
-  </si>
-  <si>
-    <t>Decode TP8/rank</t>
+    <t>Prefill/rank</t>
+  </si>
+  <si>
+    <t>Decode/rank</t>
   </si>
   <si>
     <t>Attention 计算量</t>
   </si>
   <si>
-    <t>单次 Prefill 或 Decode step 的每 Rank 逻辑 FLOPs。</t>
+    <t>单次推理调用的单 Rank 计算量。</t>
   </si>
   <si>
     <t>MoE 计算量</t>
@@ -1753,7 +1891,7 @@
     <t>Attention HBM 流量</t>
   </si>
   <si>
-    <t>本地逻辑 HBM 读写量，不含缓存复用和算子融合。</t>
+    <t>本地逻辑 HBM 读写量，不含缓存复用。</t>
   </si>
   <si>
     <t>MoE HBM 流量</t>
@@ -1768,7 +1906,7 @@
     <t>Attention 所需 HBM 带宽</t>
   </si>
   <si>
-    <t>按 Parameters 中目标时延换算；是静态需求值，不是实测带宽。</t>
+    <t>按 Parameters 中目标时延换算。</t>
   </si>
   <si>
     <t>MoE 所需 HBM 带宽</t>
@@ -1780,13 +1918,13 @@
     <t>目标时延所需计算性能</t>
   </si>
   <si>
-    <t>按目标时延折算的每 Rank 最低计算吞吐需求。</t>
+    <t>单 Rank 最低计算吞吐需求。</t>
   </si>
   <si>
     <t>卡间互连传输量</t>
   </si>
   <si>
-    <t>Ring 集合通信每 Rank 发送加接收；TP1 为 0。</t>
+    <t>Ring 集合通信单 Rank 发送加接收；TP1 为 0。</t>
   </si>
   <si>
     <t>目标时延所需互连带宽</t>
@@ -1798,7 +1936,7 @@
     <t>Attention 逻辑参数量</t>
   </si>
   <si>
-    <t>Attention 投影、Compressor、Indexer。</t>
+    <t>投影、Compressor、Indexer。</t>
   </si>
   <si>
     <t>MoE 逻辑参数量</t>
@@ -1810,43 +1948,40 @@
     <t>Other 逻辑参数量</t>
   </si>
   <si>
-    <t>Embedding、LM Head、HC 与 Norm。</t>
+    <t>Embedding、LM Head、HC、Norm。</t>
   </si>
   <si>
     <t>总逻辑参数量</t>
   </si>
   <si>
-    <t>不包含 MTP。</t>
+    <t>不含 MTP。</t>
   </si>
   <si>
     <t>Attention 参数容量</t>
   </si>
   <si>
-    <t>按推理 dtype 与量化 scale 计算。</t>
+    <t>按推理 dtype 与 Scale 计算。</t>
   </si>
   <si>
     <t>MoE 参数容量</t>
   </si>
   <si>
-    <t>Routed FP4、Shared FP8、Router 复制。</t>
+    <t>Routed FP4，Shared FP8。</t>
   </si>
   <si>
     <t>Other 参数容量</t>
   </si>
   <si>
-    <t>Embedding/LM Head/HC/Norm。</t>
-  </si>
-  <si>
     <t>总参数容量</t>
   </si>
   <si>
-    <t>每 Rank 静态参数驻留。</t>
+    <t>单 Rank 静态参数驻留。</t>
   </si>
   <si>
     <t>有效主 KV Cache</t>
   </si>
   <si>
-    <t>当前实现中 KV 与 Compressor State 在 TP Rank 间复制。</t>
+    <t>KV/State 在当前实现中每个 TP Rank 复制。</t>
   </si>
   <si>
     <t>有效 Indexer KV Cache</t>
@@ -1861,139 +1996,10 @@
     <t>总驻留容量</t>
   </si>
   <si>
-    <t>参数 + 按 MaxContext 预分配的 KV/State；不含临时 workspace。</t>
-  </si>
-  <si>
-    <t>TP1 / TP8 推理资源对比图</t>
-  </si>
-  <si>
-    <t>所有图表使用线性坐标与固定 M/G/T 单位，不显示科学计数法。</t>
-  </si>
-  <si>
-    <t>Prefill TP1 TFLOPs</t>
-  </si>
-  <si>
-    <t>Prefill TP8 TFLOPs</t>
-  </si>
-  <si>
-    <t>Decode TP1 GFLOPs</t>
-  </si>
-  <si>
-    <t>Decode TP8 GFLOPs</t>
-  </si>
-  <si>
-    <t>Prefill TP1 GB</t>
-  </si>
-  <si>
-    <t>Prefill TP8 GB</t>
-  </si>
-  <si>
-    <t>Decode TP1 GB</t>
-  </si>
-  <si>
-    <t>Decode TP8 GB</t>
-  </si>
-  <si>
-    <t>TP1 参数 GB/rank</t>
-  </si>
-  <si>
-    <t>TP8 参数 GB/rank</t>
-  </si>
-  <si>
-    <t>容量项</t>
-  </si>
-  <si>
-    <t>TP1 GB/rank</t>
-  </si>
-  <si>
-    <t>TP8 GB/rank</t>
-  </si>
-  <si>
-    <t>参数</t>
-  </si>
-  <si>
-    <t>Decode KV+State</t>
-  </si>
-  <si>
-    <t>方法与统计边界</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>定义</t>
-  </si>
-  <si>
-    <t>统计范围</t>
-  </si>
-  <si>
-    <t>仅统计 43 层主推理路径；不含 MTP、反向传播、梯度、优化器状态和训练激活。Layer_Config 最多可维护 64 层。</t>
-  </si>
-  <si>
-    <t>计算量</t>
-  </si>
-  <si>
-    <t>矩阵乘加按 2 FLOPs 计。Attention 与 MoE 主要 GEMM 使用显式公式；HC 与逐元素运算为近似估计。</t>
-  </si>
-  <si>
-    <t>Prefill Attention</t>
-  </si>
-  <si>
-    <t>使用因果候选对数量，不直接使用 S×S；Raw Window、Compressed KV 和 Indexer 扫描分别统计。</t>
-  </si>
-  <si>
-    <t>Decode Attention</t>
-  </si>
-  <si>
-    <t>每个 DecodeTokens 在 DecodeContext 下建模；ratio-4 主 Attention 取 Top-K，但 Indexer 需要扫描全部已完成压缩项。</t>
-  </si>
-  <si>
-    <t>每 Token 执行 Top-K Routed Experts 和 Shared Experts。HBM 参数读取按专家至少被命中一次的概率估计。</t>
-  </si>
-  <si>
-    <t>HBM 流量</t>
-  </si>
-  <si>
-    <t>统计本地逻辑参数、激活和 KV 的读取与写入；不模拟 L2 命中、算子融合、分块、Allocator 或厂商 Kernel 内部复用。</t>
-  </si>
-  <si>
-    <t>参数容量</t>
-  </si>
-  <si>
-    <t>按推理运行 dtype 估算：Routed Expert FP4、多数投影 FP8、Wo_a BF16、Compressor FP32、LM Head FP32，并计入量化 Scale。</t>
-  </si>
-  <si>
-    <t>KV Cache</t>
-  </si>
-  <si>
-    <t>有效容量表示已填充项；预分配容量使用 MaxContext。当前实现的 KV 和 Compressor State 在每个 TP Rank 上完整复制。</t>
-  </si>
-  <si>
-    <t>TP 分片</t>
-  </si>
-  <si>
-    <t>Wq_a、Wkv、Compressor、Router、HC、Shared Expert 复制；Q/O 部分投影、Routed Experts、Embedding 和 LM Head 按 TP 分片。</t>
-  </si>
-  <si>
-    <t>卡间通信</t>
-  </si>
-  <si>
-    <t>Ring 公式给出每 Rank 发送加接收的数据量。TP1 为 0；该数值是传输量，不是实测 GB/s 或时延。</t>
-  </si>
-  <si>
-    <t>硬件下界</t>
-  </si>
-  <si>
-    <t>计算/HBM/互连下界使用 Parameters 中可编辑硬件峰值并假设互不重叠；真实运行时间必须通过 Profiling 验证。</t>
-  </si>
-  <si>
-    <t>FLOPs 使用 M/G/T/P 十进制单位；容量与流量使用 KB/MB/GB/TB，1 GB=10^9 Bytes；Memory 明细保留原始公式。</t>
-  </si>
-  <si>
-    <t>公式维护</t>
-  </si>
-  <si>
-    <t>蓝色单元格为输入；结果由 Excel 公式计算并在打开时完整重算。隐藏列保留原始未缩放值，便于审计。</t>
+    <t>参数 + 预分配 KV/State；不含临时 workspace。</t>
+  </si>
+  <si>
+    <t>TP8（配置值=8）单 Rank 资源</t>
   </si>
 </sst>
 </file>
@@ -3532,8 +3538,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Per_Rank_Inference_Memory" displayName="Per_Rank_Inference_Memory" ref="A37:J165" totalsRowShown="0">
-  <autoFilter ref="A37:J165"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Per_Rank_Inference_Memory" displayName="Per_Rank_Inference_Memory" ref="A37:J39" totalsRowShown="0">
+  <autoFilter ref="A37:J39"/>
   <tableColumns count="10">
     <tableColumn id="1" name="配置"/>
     <tableColumn id="2" name="Rank"/>
@@ -10746,7 +10752,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U165"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -12323,5120 +12329,78 @@
       <c r="A38" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B38" s="9">
-        <v>0</v>
+      <c r="B38" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="C38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
+        <f>'Memory'!$R$18/1E9</f>
         <v>7.45138496</v>
       </c>
       <c r="D38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
+        <f>'Memory'!$R$19/1E9</f>
         <v>148.351461888</v>
       </c>
       <c r="E38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
+        <f>'Memory'!$R$20/1E9</f>
         <v>3.314423644</v>
       </c>
       <c r="F38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
+        <f>'Memory'!$R$21/1E9</f>
         <v>159.117270492</v>
       </c>
       <c r="G38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
+        <f>'Memory'!$P$33/1E9</f>
         <v>7.232045056</v>
       </c>
       <c r="H38" s="13">
-        <f>IF(B38&lt;TP1Size,F38+G38,"")</f>
+        <f>F38+G38</f>
         <v>166.349315548</v>
       </c>
       <c r="I38" s="13">
-        <f>IF(B38&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
+        <f>'Memory'!$P$21/1E9</f>
         <v>284.334567511</v>
       </c>
-      <c r="J38" s="4" t="str">
-        <f>IF(B38&lt;TP1Size,"YES","")</f>
-        <v>YES</v>
+      <c r="J38" s="4" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B39" s="9">
-        <v>1</v>
+        <v>505</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="C39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
+        <f>'Memory'!$S$18/1E9</f>
+        <v>2.23750496</v>
       </c>
       <c r="D39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
+        <f>'Memory'!$S$19/1E9</f>
+        <v>19.57794048</v>
       </c>
       <c r="E39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
+        <f>'Memory'!$S$20/1E9</f>
+        <v>0.534376892</v>
       </c>
       <c r="F39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
+        <f>'Memory'!$S$21/1E9</f>
+        <v>22.349822332</v>
       </c>
       <c r="G39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
+        <f>'Memory'!$Q$33/1E9</f>
+        <v>7.232045056</v>
       </c>
       <c r="H39" s="13">
-        <f>IF(B39&lt;TP1Size,F39+G39,"")</f>
-        <v/>
+        <f>F39+G39</f>
+        <v>29.581867388</v>
       </c>
       <c r="I39" s="13">
-        <f>IF(B39&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="4">
-        <f>IF(B39&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B40" s="9">
-        <v>2</v>
-      </c>
-      <c r="C40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="13">
-        <f>IF(B40&lt;TP1Size,F40+G40,"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="13">
-        <f>IF(B40&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="4">
-        <f>IF(B40&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B41" s="9">
-        <v>3</v>
-      </c>
-      <c r="C41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="13">
-        <f>IF(B41&lt;TP1Size,F41+G41,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="13">
-        <f>IF(B41&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="4">
-        <f>IF(B41&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="A42" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B42" s="9">
-        <v>4</v>
-      </c>
-      <c r="C42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="13">
-        <f>IF(B42&lt;TP1Size,F42+G42,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="13">
-        <f>IF(B42&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="4">
-        <f>IF(B42&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:17">
-      <c r="A43" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B43" s="9">
-        <v>5</v>
-      </c>
-      <c r="C43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="13">
-        <f>IF(B43&lt;TP1Size,F43+G43,"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="13">
-        <f>IF(B43&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="4">
-        <f>IF(B43&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B44" s="9">
-        <v>6</v>
-      </c>
-      <c r="C44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="13">
-        <f>IF(B44&lt;TP1Size,F44+G44,"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="13">
-        <f>IF(B44&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="4">
-        <f>IF(B44&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:17">
-      <c r="A45" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B45" s="9">
-        <v>7</v>
-      </c>
-      <c r="C45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="13">
-        <f>IF(B45&lt;TP1Size,F45+G45,"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="13">
-        <f>IF(B45&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="4">
-        <f>IF(B45&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B46" s="9">
-        <v>8</v>
-      </c>
-      <c r="C46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="13">
-        <f>IF(B46&lt;TP1Size,F46+G46,"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="13">
-        <f>IF(B46&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="4">
-        <f>IF(B46&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
-      <c r="A47" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B47" s="9">
-        <v>9</v>
-      </c>
-      <c r="C47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="13">
-        <f>IF(B47&lt;TP1Size,F47+G47,"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="13">
-        <f>IF(B47&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="4">
-        <f>IF(B47&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B48" s="9">
-        <v>10</v>
-      </c>
-      <c r="C48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="13">
-        <f>IF(B48&lt;TP1Size,F48+G48,"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="13">
-        <f>IF(B48&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="4">
-        <f>IF(B48&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B49" s="9">
-        <v>11</v>
-      </c>
-      <c r="C49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="13">
-        <f>IF(B49&lt;TP1Size,F49+G49,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="13">
-        <f>IF(B49&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="4">
-        <f>IF(B49&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B50" s="9">
-        <v>12</v>
-      </c>
-      <c r="C50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="13">
-        <f>IF(B50&lt;TP1Size,F50+G50,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="13">
-        <f>IF(B50&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="4">
-        <f>IF(B50&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B51" s="9">
-        <v>13</v>
-      </c>
-      <c r="C51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="13">
-        <f>IF(B51&lt;TP1Size,F51+G51,"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="13">
-        <f>IF(B51&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="4">
-        <f>IF(B51&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B52" s="9">
-        <v>14</v>
-      </c>
-      <c r="C52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="13">
-        <f>IF(B52&lt;TP1Size,F52+G52,"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="13">
-        <f>IF(B52&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="4">
-        <f>IF(B52&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B53" s="9">
-        <v>15</v>
-      </c>
-      <c r="C53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="13">
-        <f>IF(B53&lt;TP1Size,F53+G53,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="13">
-        <f>IF(B53&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="4">
-        <f>IF(B53&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B54" s="9">
-        <v>16</v>
-      </c>
-      <c r="C54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="13">
-        <f>IF(B54&lt;TP1Size,F54+G54,"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="13">
-        <f>IF(B54&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="4">
-        <f>IF(B54&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B55" s="9">
-        <v>17</v>
-      </c>
-      <c r="C55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="13">
-        <f>IF(B55&lt;TP1Size,F55+G55,"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="13">
-        <f>IF(B55&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="4">
-        <f>IF(B55&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B56" s="9">
-        <v>18</v>
-      </c>
-      <c r="C56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="13">
-        <f>IF(B56&lt;TP1Size,F56+G56,"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="13">
-        <f>IF(B56&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="4">
-        <f>IF(B56&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B57" s="9">
-        <v>19</v>
-      </c>
-      <c r="C57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="13">
-        <f>IF(B57&lt;TP1Size,F57+G57,"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="13">
-        <f>IF(B57&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="4">
-        <f>IF(B57&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B58" s="9">
-        <v>20</v>
-      </c>
-      <c r="C58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="13">
-        <f>IF(B58&lt;TP1Size,F58+G58,"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="13">
-        <f>IF(B58&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="4">
-        <f>IF(B58&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B59" s="9">
-        <v>21</v>
-      </c>
-      <c r="C59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="13">
-        <f>IF(B59&lt;TP1Size,F59+G59,"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="13">
-        <f>IF(B59&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="4">
-        <f>IF(B59&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B60" s="9">
-        <v>22</v>
-      </c>
-      <c r="C60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="13">
-        <f>IF(B60&lt;TP1Size,F60+G60,"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="13">
-        <f>IF(B60&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="4">
-        <f>IF(B60&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B61" s="9">
-        <v>23</v>
-      </c>
-      <c r="C61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="13">
-        <f>IF(B61&lt;TP1Size,F61+G61,"")</f>
-        <v/>
-      </c>
-      <c r="I61" s="13">
-        <f>IF(B61&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J61" s="4">
-        <f>IF(B61&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B62" s="9">
-        <v>24</v>
-      </c>
-      <c r="C62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="13">
-        <f>IF(B62&lt;TP1Size,F62+G62,"")</f>
-        <v/>
-      </c>
-      <c r="I62" s="13">
-        <f>IF(B62&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J62" s="4">
-        <f>IF(B62&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B63" s="9">
-        <v>25</v>
-      </c>
-      <c r="C63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="13">
-        <f>IF(B63&lt;TP1Size,F63+G63,"")</f>
-        <v/>
-      </c>
-      <c r="I63" s="13">
-        <f>IF(B63&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="4">
-        <f>IF(B63&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B64" s="9">
-        <v>26</v>
-      </c>
-      <c r="C64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="13">
-        <f>IF(B64&lt;TP1Size,F64+G64,"")</f>
-        <v/>
-      </c>
-      <c r="I64" s="13">
-        <f>IF(B64&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J64" s="4">
-        <f>IF(B64&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B65" s="9">
-        <v>27</v>
-      </c>
-      <c r="C65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="13">
-        <f>IF(B65&lt;TP1Size,F65+G65,"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="13">
-        <f>IF(B65&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="4">
-        <f>IF(B65&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B66" s="9">
-        <v>28</v>
-      </c>
-      <c r="C66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="13">
-        <f>IF(B66&lt;TP1Size,F66+G66,"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="13">
-        <f>IF(B66&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="4">
-        <f>IF(B66&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B67" s="9">
-        <v>29</v>
-      </c>
-      <c r="C67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="13">
-        <f>IF(B67&lt;TP1Size,F67+G67,"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="13">
-        <f>IF(B67&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="4">
-        <f>IF(B67&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B68" s="9">
-        <v>30</v>
-      </c>
-      <c r="C68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="13">
-        <f>IF(B68&lt;TP1Size,F68+G68,"")</f>
-        <v/>
-      </c>
-      <c r="I68" s="13">
-        <f>IF(B68&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="4">
-        <f>IF(B68&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B69" s="9">
-        <v>31</v>
-      </c>
-      <c r="C69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="13">
-        <f>IF(B69&lt;TP1Size,F69+G69,"")</f>
-        <v/>
-      </c>
-      <c r="I69" s="13">
-        <f>IF(B69&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J69" s="4">
-        <f>IF(B69&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B70" s="9">
-        <v>32</v>
-      </c>
-      <c r="C70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="13">
-        <f>IF(B70&lt;TP1Size,F70+G70,"")</f>
-        <v/>
-      </c>
-      <c r="I70" s="13">
-        <f>IF(B70&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J70" s="4">
-        <f>IF(B70&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B71" s="9">
-        <v>33</v>
-      </c>
-      <c r="C71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="13">
-        <f>IF(B71&lt;TP1Size,F71+G71,"")</f>
-        <v/>
-      </c>
-      <c r="I71" s="13">
-        <f>IF(B71&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="4">
-        <f>IF(B71&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B72" s="9">
-        <v>34</v>
-      </c>
-      <c r="C72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H72" s="13">
-        <f>IF(B72&lt;TP1Size,F72+G72,"")</f>
-        <v/>
-      </c>
-      <c r="I72" s="13">
-        <f>IF(B72&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J72" s="4">
-        <f>IF(B72&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B73" s="9">
-        <v>35</v>
-      </c>
-      <c r="C73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H73" s="13">
-        <f>IF(B73&lt;TP1Size,F73+G73,"")</f>
-        <v/>
-      </c>
-      <c r="I73" s="13">
-        <f>IF(B73&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="4">
-        <f>IF(B73&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B74" s="9">
-        <v>36</v>
-      </c>
-      <c r="C74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H74" s="13">
-        <f>IF(B74&lt;TP1Size,F74+G74,"")</f>
-        <v/>
-      </c>
-      <c r="I74" s="13">
-        <f>IF(B74&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="4">
-        <f>IF(B74&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B75" s="9">
-        <v>37</v>
-      </c>
-      <c r="C75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H75" s="13">
-        <f>IF(B75&lt;TP1Size,F75+G75,"")</f>
-        <v/>
-      </c>
-      <c r="I75" s="13">
-        <f>IF(B75&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="4">
-        <f>IF(B75&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B76" s="9">
-        <v>38</v>
-      </c>
-      <c r="C76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H76" s="13">
-        <f>IF(B76&lt;TP1Size,F76+G76,"")</f>
-        <v/>
-      </c>
-      <c r="I76" s="13">
-        <f>IF(B76&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J76" s="4">
-        <f>IF(B76&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B77" s="9">
-        <v>39</v>
-      </c>
-      <c r="C77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H77" s="13">
-        <f>IF(B77&lt;TP1Size,F77+G77,"")</f>
-        <v/>
-      </c>
-      <c r="I77" s="13">
-        <f>IF(B77&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="4">
-        <f>IF(B77&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B78" s="9">
-        <v>40</v>
-      </c>
-      <c r="C78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H78" s="13">
-        <f>IF(B78&lt;TP1Size,F78+G78,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="13">
-        <f>IF(B78&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="4">
-        <f>IF(B78&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B79" s="9">
-        <v>41</v>
-      </c>
-      <c r="C79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H79" s="13">
-        <f>IF(B79&lt;TP1Size,F79+G79,"")</f>
-        <v/>
-      </c>
-      <c r="I79" s="13">
-        <f>IF(B79&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="4">
-        <f>IF(B79&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B80" s="9">
-        <v>42</v>
-      </c>
-      <c r="C80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H80" s="13">
-        <f>IF(B80&lt;TP1Size,F80+G80,"")</f>
-        <v/>
-      </c>
-      <c r="I80" s="13">
-        <f>IF(B80&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J80" s="4">
-        <f>IF(B80&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B81" s="9">
-        <v>43</v>
-      </c>
-      <c r="C81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H81" s="13">
-        <f>IF(B81&lt;TP1Size,F81+G81,"")</f>
-        <v/>
-      </c>
-      <c r="I81" s="13">
-        <f>IF(B81&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="4">
-        <f>IF(B81&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B82" s="9">
-        <v>44</v>
-      </c>
-      <c r="C82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H82" s="13">
-        <f>IF(B82&lt;TP1Size,F82+G82,"")</f>
-        <v/>
-      </c>
-      <c r="I82" s="13">
-        <f>IF(B82&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J82" s="4">
-        <f>IF(B82&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B83" s="9">
-        <v>45</v>
-      </c>
-      <c r="C83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H83" s="13">
-        <f>IF(B83&lt;TP1Size,F83+G83,"")</f>
-        <v/>
-      </c>
-      <c r="I83" s="13">
-        <f>IF(B83&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="4">
-        <f>IF(B83&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B84" s="9">
-        <v>46</v>
-      </c>
-      <c r="C84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H84" s="13">
-        <f>IF(B84&lt;TP1Size,F84+G84,"")</f>
-        <v/>
-      </c>
-      <c r="I84" s="13">
-        <f>IF(B84&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J84" s="4">
-        <f>IF(B84&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B85" s="9">
-        <v>47</v>
-      </c>
-      <c r="C85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H85" s="13">
-        <f>IF(B85&lt;TP1Size,F85+G85,"")</f>
-        <v/>
-      </c>
-      <c r="I85" s="13">
-        <f>IF(B85&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J85" s="4">
-        <f>IF(B85&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B86" s="9">
-        <v>48</v>
-      </c>
-      <c r="C86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H86" s="13">
-        <f>IF(B86&lt;TP1Size,F86+G86,"")</f>
-        <v/>
-      </c>
-      <c r="I86" s="13">
-        <f>IF(B86&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J86" s="4">
-        <f>IF(B86&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B87" s="9">
-        <v>49</v>
-      </c>
-      <c r="C87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H87" s="13">
-        <f>IF(B87&lt;TP1Size,F87+G87,"")</f>
-        <v/>
-      </c>
-      <c r="I87" s="13">
-        <f>IF(B87&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J87" s="4">
-        <f>IF(B87&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="A88" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B88" s="9">
-        <v>50</v>
-      </c>
-      <c r="C88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H88" s="13">
-        <f>IF(B88&lt;TP1Size,F88+G88,"")</f>
-        <v/>
-      </c>
-      <c r="I88" s="13">
-        <f>IF(B88&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J88" s="4">
-        <f>IF(B88&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B89" s="9">
-        <v>51</v>
-      </c>
-      <c r="C89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H89" s="13">
-        <f>IF(B89&lt;TP1Size,F89+G89,"")</f>
-        <v/>
-      </c>
-      <c r="I89" s="13">
-        <f>IF(B89&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J89" s="4">
-        <f>IF(B89&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B90" s="9">
-        <v>52</v>
-      </c>
-      <c r="C90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H90" s="13">
-        <f>IF(B90&lt;TP1Size,F90+G90,"")</f>
-        <v/>
-      </c>
-      <c r="I90" s="13">
-        <f>IF(B90&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J90" s="4">
-        <f>IF(B90&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B91" s="9">
-        <v>53</v>
-      </c>
-      <c r="C91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H91" s="13">
-        <f>IF(B91&lt;TP1Size,F91+G91,"")</f>
-        <v/>
-      </c>
-      <c r="I91" s="13">
-        <f>IF(B91&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J91" s="4">
-        <f>IF(B91&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B92" s="9">
-        <v>54</v>
-      </c>
-      <c r="C92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H92" s="13">
-        <f>IF(B92&lt;TP1Size,F92+G92,"")</f>
-        <v/>
-      </c>
-      <c r="I92" s="13">
-        <f>IF(B92&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J92" s="4">
-        <f>IF(B92&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B93" s="9">
-        <v>55</v>
-      </c>
-      <c r="C93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H93" s="13">
-        <f>IF(B93&lt;TP1Size,F93+G93,"")</f>
-        <v/>
-      </c>
-      <c r="I93" s="13">
-        <f>IF(B93&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J93" s="4">
-        <f>IF(B93&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B94" s="9">
-        <v>56</v>
-      </c>
-      <c r="C94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H94" s="13">
-        <f>IF(B94&lt;TP1Size,F94+G94,"")</f>
-        <v/>
-      </c>
-      <c r="I94" s="13">
-        <f>IF(B94&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J94" s="4">
-        <f>IF(B94&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B95" s="9">
-        <v>57</v>
-      </c>
-      <c r="C95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H95" s="13">
-        <f>IF(B95&lt;TP1Size,F95+G95,"")</f>
-        <v/>
-      </c>
-      <c r="I95" s="13">
-        <f>IF(B95&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J95" s="4">
-        <f>IF(B95&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B96" s="9">
-        <v>58</v>
-      </c>
-      <c r="C96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H96" s="13">
-        <f>IF(B96&lt;TP1Size,F96+G96,"")</f>
-        <v/>
-      </c>
-      <c r="I96" s="13">
-        <f>IF(B96&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J96" s="4">
-        <f>IF(B96&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
-      <c r="A97" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B97" s="9">
-        <v>59</v>
-      </c>
-      <c r="C97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H97" s="13">
-        <f>IF(B97&lt;TP1Size,F97+G97,"")</f>
-        <v/>
-      </c>
-      <c r="I97" s="13">
-        <f>IF(B97&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J97" s="4">
-        <f>IF(B97&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B98" s="9">
-        <v>60</v>
-      </c>
-      <c r="C98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H98" s="13">
-        <f>IF(B98&lt;TP1Size,F98+G98,"")</f>
-        <v/>
-      </c>
-      <c r="I98" s="13">
-        <f>IF(B98&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J98" s="4">
-        <f>IF(B98&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B99" s="9">
-        <v>61</v>
-      </c>
-      <c r="C99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H99" s="13">
-        <f>IF(B99&lt;TP1Size,F99+G99,"")</f>
-        <v/>
-      </c>
-      <c r="I99" s="13">
-        <f>IF(B99&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J99" s="4">
-        <f>IF(B99&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B100" s="9">
-        <v>62</v>
-      </c>
-      <c r="C100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H100" s="13">
-        <f>IF(B100&lt;TP1Size,F100+G100,"")</f>
-        <v/>
-      </c>
-      <c r="I100" s="13">
-        <f>IF(B100&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J100" s="4">
-        <f>IF(B100&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B101" s="9">
-        <v>63</v>
-      </c>
-      <c r="C101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$R$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$R$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$R$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$R$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$P$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H101" s="13">
-        <f>IF(B101&lt;TP1Size,F101+G101,"")</f>
-        <v/>
-      </c>
-      <c r="I101" s="13">
-        <f>IF(B101&lt;TP1Size,'Memory'!$P$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J101" s="4">
-        <f>IF(B101&lt;TP1Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B102" s="9">
-        <v>0</v>
-      </c>
-      <c r="C102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H102" s="13">
-        <f>IF(B102&lt;TP8Size,F102+G102,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I102" s="13">
-        <f>IF(B102&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
+        <f>'Memory'!$Q$21/1E9</f>
         <v>37.064255215</v>
       </c>
-      <c r="J102" s="4" t="str">
-        <f>IF(B102&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B103" s="9">
-        <v>1</v>
-      </c>
-      <c r="C103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H103" s="13">
-        <f>IF(B103&lt;TP8Size,F103+G103,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I103" s="13">
-        <f>IF(B103&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J103" s="4" t="str">
-        <f>IF(B103&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B104" s="9">
-        <v>2</v>
-      </c>
-      <c r="C104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H104" s="13">
-        <f>IF(B104&lt;TP8Size,F104+G104,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I104" s="13">
-        <f>IF(B104&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J104" s="4" t="str">
-        <f>IF(B104&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B105" s="9">
-        <v>3</v>
-      </c>
-      <c r="C105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H105" s="13">
-        <f>IF(B105&lt;TP8Size,F105+G105,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I105" s="13">
-        <f>IF(B105&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J105" s="4" t="str">
-        <f>IF(B105&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B106" s="9">
-        <v>4</v>
-      </c>
-      <c r="C106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H106" s="13">
-        <f>IF(B106&lt;TP8Size,F106+G106,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I106" s="13">
-        <f>IF(B106&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J106" s="4" t="str">
-        <f>IF(B106&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B107" s="9">
-        <v>5</v>
-      </c>
-      <c r="C107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H107" s="13">
-        <f>IF(B107&lt;TP8Size,F107+G107,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I107" s="13">
-        <f>IF(B107&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J107" s="4" t="str">
-        <f>IF(B107&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B108" s="9">
-        <v>6</v>
-      </c>
-      <c r="C108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H108" s="13">
-        <f>IF(B108&lt;TP8Size,F108+G108,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I108" s="13">
-        <f>IF(B108&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J108" s="4" t="str">
-        <f>IF(B108&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B109" s="9">
-        <v>7</v>
-      </c>
-      <c r="C109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="D109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v>0.534376892</v>
-      </c>
-      <c r="F109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="G109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="H109" s="13">
-        <f>IF(B109&lt;TP8Size,F109+G109,"")</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I109" s="13">
-        <f>IF(B109&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="J109" s="4" t="str">
-        <f>IF(B109&lt;TP8Size,"YES","")</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B110" s="9">
-        <v>8</v>
-      </c>
-      <c r="C110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H110" s="13">
-        <f>IF(B110&lt;TP8Size,F110+G110,"")</f>
-        <v/>
-      </c>
-      <c r="I110" s="13">
-        <f>IF(B110&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J110" s="4">
-        <f>IF(B110&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B111" s="9">
-        <v>9</v>
-      </c>
-      <c r="C111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H111" s="13">
-        <f>IF(B111&lt;TP8Size,F111+G111,"")</f>
-        <v/>
-      </c>
-      <c r="I111" s="13">
-        <f>IF(B111&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J111" s="4">
-        <f>IF(B111&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B112" s="9">
-        <v>10</v>
-      </c>
-      <c r="C112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="13">
-        <f>IF(B112&lt;TP8Size,F112+G112,"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="13">
-        <f>IF(B112&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="4">
-        <f>IF(B112&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B113" s="9">
-        <v>11</v>
-      </c>
-      <c r="C113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H113" s="13">
-        <f>IF(B113&lt;TP8Size,F113+G113,"")</f>
-        <v/>
-      </c>
-      <c r="I113" s="13">
-        <f>IF(B113&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J113" s="4">
-        <f>IF(B113&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B114" s="9">
-        <v>12</v>
-      </c>
-      <c r="C114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H114" s="13">
-        <f>IF(B114&lt;TP8Size,F114+G114,"")</f>
-        <v/>
-      </c>
-      <c r="I114" s="13">
-        <f>IF(B114&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J114" s="4">
-        <f>IF(B114&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B115" s="9">
-        <v>13</v>
-      </c>
-      <c r="C115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H115" s="13">
-        <f>IF(B115&lt;TP8Size,F115+G115,"")</f>
-        <v/>
-      </c>
-      <c r="I115" s="13">
-        <f>IF(B115&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J115" s="4">
-        <f>IF(B115&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B116" s="9">
-        <v>14</v>
-      </c>
-      <c r="C116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="13">
-        <f>IF(B116&lt;TP8Size,F116+G116,"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="13">
-        <f>IF(B116&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="4">
-        <f>IF(B116&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B117" s="9">
-        <v>15</v>
-      </c>
-      <c r="C117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H117" s="13">
-        <f>IF(B117&lt;TP8Size,F117+G117,"")</f>
-        <v/>
-      </c>
-      <c r="I117" s="13">
-        <f>IF(B117&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J117" s="4">
-        <f>IF(B117&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B118" s="9">
-        <v>16</v>
-      </c>
-      <c r="C118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H118" s="13">
-        <f>IF(B118&lt;TP8Size,F118+G118,"")</f>
-        <v/>
-      </c>
-      <c r="I118" s="13">
-        <f>IF(B118&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J118" s="4">
-        <f>IF(B118&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B119" s="9">
-        <v>17</v>
-      </c>
-      <c r="C119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H119" s="13">
-        <f>IF(B119&lt;TP8Size,F119+G119,"")</f>
-        <v/>
-      </c>
-      <c r="I119" s="13">
-        <f>IF(B119&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J119" s="4">
-        <f>IF(B119&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B120" s="9">
-        <v>18</v>
-      </c>
-      <c r="C120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H120" s="13">
-        <f>IF(B120&lt;TP8Size,F120+G120,"")</f>
-        <v/>
-      </c>
-      <c r="I120" s="13">
-        <f>IF(B120&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J120" s="4">
-        <f>IF(B120&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B121" s="9">
-        <v>19</v>
-      </c>
-      <c r="C121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H121" s="13">
-        <f>IF(B121&lt;TP8Size,F121+G121,"")</f>
-        <v/>
-      </c>
-      <c r="I121" s="13">
-        <f>IF(B121&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J121" s="4">
-        <f>IF(B121&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B122" s="9">
-        <v>20</v>
-      </c>
-      <c r="C122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H122" s="13">
-        <f>IF(B122&lt;TP8Size,F122+G122,"")</f>
-        <v/>
-      </c>
-      <c r="I122" s="13">
-        <f>IF(B122&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J122" s="4">
-        <f>IF(B122&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B123" s="9">
-        <v>21</v>
-      </c>
-      <c r="C123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H123" s="13">
-        <f>IF(B123&lt;TP8Size,F123+G123,"")</f>
-        <v/>
-      </c>
-      <c r="I123" s="13">
-        <f>IF(B123&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J123" s="4">
-        <f>IF(B123&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B124" s="9">
-        <v>22</v>
-      </c>
-      <c r="C124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H124" s="13">
-        <f>IF(B124&lt;TP8Size,F124+G124,"")</f>
-        <v/>
-      </c>
-      <c r="I124" s="13">
-        <f>IF(B124&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J124" s="4">
-        <f>IF(B124&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B125" s="9">
-        <v>23</v>
-      </c>
-      <c r="C125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H125" s="13">
-        <f>IF(B125&lt;TP8Size,F125+G125,"")</f>
-        <v/>
-      </c>
-      <c r="I125" s="13">
-        <f>IF(B125&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J125" s="4">
-        <f>IF(B125&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B126" s="9">
-        <v>24</v>
-      </c>
-      <c r="C126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H126" s="13">
-        <f>IF(B126&lt;TP8Size,F126+G126,"")</f>
-        <v/>
-      </c>
-      <c r="I126" s="13">
-        <f>IF(B126&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J126" s="4">
-        <f>IF(B126&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
-      <c r="A127" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B127" s="9">
-        <v>25</v>
-      </c>
-      <c r="C127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H127" s="13">
-        <f>IF(B127&lt;TP8Size,F127+G127,"")</f>
-        <v/>
-      </c>
-      <c r="I127" s="13">
-        <f>IF(B127&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J127" s="4">
-        <f>IF(B127&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
-      <c r="A128" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B128" s="9">
-        <v>26</v>
-      </c>
-      <c r="C128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H128" s="13">
-        <f>IF(B128&lt;TP8Size,F128+G128,"")</f>
-        <v/>
-      </c>
-      <c r="I128" s="13">
-        <f>IF(B128&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J128" s="4">
-        <f>IF(B128&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
-      <c r="A129" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B129" s="9">
-        <v>27</v>
-      </c>
-      <c r="C129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H129" s="13">
-        <f>IF(B129&lt;TP8Size,F129+G129,"")</f>
-        <v/>
-      </c>
-      <c r="I129" s="13">
-        <f>IF(B129&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J129" s="4">
-        <f>IF(B129&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
-      <c r="A130" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B130" s="9">
-        <v>28</v>
-      </c>
-      <c r="C130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H130" s="13">
-        <f>IF(B130&lt;TP8Size,F130+G130,"")</f>
-        <v/>
-      </c>
-      <c r="I130" s="13">
-        <f>IF(B130&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J130" s="4">
-        <f>IF(B130&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:10">
-      <c r="A131" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B131" s="9">
-        <v>29</v>
-      </c>
-      <c r="C131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H131" s="13">
-        <f>IF(B131&lt;TP8Size,F131+G131,"")</f>
-        <v/>
-      </c>
-      <c r="I131" s="13">
-        <f>IF(B131&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J131" s="4">
-        <f>IF(B131&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:10">
-      <c r="A132" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B132" s="9">
-        <v>30</v>
-      </c>
-      <c r="C132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H132" s="13">
-        <f>IF(B132&lt;TP8Size,F132+G132,"")</f>
-        <v/>
-      </c>
-      <c r="I132" s="13">
-        <f>IF(B132&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J132" s="4">
-        <f>IF(B132&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:10">
-      <c r="A133" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B133" s="9">
-        <v>31</v>
-      </c>
-      <c r="C133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H133" s="13">
-        <f>IF(B133&lt;TP8Size,F133+G133,"")</f>
-        <v/>
-      </c>
-      <c r="I133" s="13">
-        <f>IF(B133&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J133" s="4">
-        <f>IF(B133&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
-      <c r="A134" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B134" s="9">
-        <v>32</v>
-      </c>
-      <c r="C134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H134" s="13">
-        <f>IF(B134&lt;TP8Size,F134+G134,"")</f>
-        <v/>
-      </c>
-      <c r="I134" s="13">
-        <f>IF(B134&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J134" s="4">
-        <f>IF(B134&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
-      <c r="A135" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B135" s="9">
-        <v>33</v>
-      </c>
-      <c r="C135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H135" s="13">
-        <f>IF(B135&lt;TP8Size,F135+G135,"")</f>
-        <v/>
-      </c>
-      <c r="I135" s="13">
-        <f>IF(B135&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J135" s="4">
-        <f>IF(B135&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
-      <c r="A136" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B136" s="9">
-        <v>34</v>
-      </c>
-      <c r="C136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H136" s="13">
-        <f>IF(B136&lt;TP8Size,F136+G136,"")</f>
-        <v/>
-      </c>
-      <c r="I136" s="13">
-        <f>IF(B136&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J136" s="4">
-        <f>IF(B136&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:10">
-      <c r="A137" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B137" s="9">
-        <v>35</v>
-      </c>
-      <c r="C137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H137" s="13">
-        <f>IF(B137&lt;TP8Size,F137+G137,"")</f>
-        <v/>
-      </c>
-      <c r="I137" s="13">
-        <f>IF(B137&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J137" s="4">
-        <f>IF(B137&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:10">
-      <c r="A138" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B138" s="9">
-        <v>36</v>
-      </c>
-      <c r="C138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H138" s="13">
-        <f>IF(B138&lt;TP8Size,F138+G138,"")</f>
-        <v/>
-      </c>
-      <c r="I138" s="13">
-        <f>IF(B138&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J138" s="4">
-        <f>IF(B138&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
-      <c r="A139" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B139" s="9">
-        <v>37</v>
-      </c>
-      <c r="C139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H139" s="13">
-        <f>IF(B139&lt;TP8Size,F139+G139,"")</f>
-        <v/>
-      </c>
-      <c r="I139" s="13">
-        <f>IF(B139&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J139" s="4">
-        <f>IF(B139&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
-      <c r="A140" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B140" s="9">
-        <v>38</v>
-      </c>
-      <c r="C140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H140" s="13">
-        <f>IF(B140&lt;TP8Size,F140+G140,"")</f>
-        <v/>
-      </c>
-      <c r="I140" s="13">
-        <f>IF(B140&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J140" s="4">
-        <f>IF(B140&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
-      <c r="A141" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B141" s="9">
-        <v>39</v>
-      </c>
-      <c r="C141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H141" s="13">
-        <f>IF(B141&lt;TP8Size,F141+G141,"")</f>
-        <v/>
-      </c>
-      <c r="I141" s="13">
-        <f>IF(B141&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J141" s="4">
-        <f>IF(B141&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
-      <c r="A142" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B142" s="9">
-        <v>40</v>
-      </c>
-      <c r="C142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H142" s="13">
-        <f>IF(B142&lt;TP8Size,F142+G142,"")</f>
-        <v/>
-      </c>
-      <c r="I142" s="13">
-        <f>IF(B142&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J142" s="4">
-        <f>IF(B142&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
-      <c r="A143" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B143" s="9">
-        <v>41</v>
-      </c>
-      <c r="C143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H143" s="13">
-        <f>IF(B143&lt;TP8Size,F143+G143,"")</f>
-        <v/>
-      </c>
-      <c r="I143" s="13">
-        <f>IF(B143&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J143" s="4">
-        <f>IF(B143&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
-      <c r="A144" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B144" s="9">
-        <v>42</v>
-      </c>
-      <c r="C144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H144" s="13">
-        <f>IF(B144&lt;TP8Size,F144+G144,"")</f>
-        <v/>
-      </c>
-      <c r="I144" s="13">
-        <f>IF(B144&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J144" s="4">
-        <f>IF(B144&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
-      <c r="A145" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B145" s="9">
-        <v>43</v>
-      </c>
-      <c r="C145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H145" s="13">
-        <f>IF(B145&lt;TP8Size,F145+G145,"")</f>
-        <v/>
-      </c>
-      <c r="I145" s="13">
-        <f>IF(B145&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J145" s="4">
-        <f>IF(B145&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
-      <c r="A146" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B146" s="9">
-        <v>44</v>
-      </c>
-      <c r="C146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H146" s="13">
-        <f>IF(B146&lt;TP8Size,F146+G146,"")</f>
-        <v/>
-      </c>
-      <c r="I146" s="13">
-        <f>IF(B146&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J146" s="4">
-        <f>IF(B146&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
-      <c r="A147" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B147" s="9">
-        <v>45</v>
-      </c>
-      <c r="C147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H147" s="13">
-        <f>IF(B147&lt;TP8Size,F147+G147,"")</f>
-        <v/>
-      </c>
-      <c r="I147" s="13">
-        <f>IF(B147&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J147" s="4">
-        <f>IF(B147&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
-      <c r="A148" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B148" s="9">
-        <v>46</v>
-      </c>
-      <c r="C148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H148" s="13">
-        <f>IF(B148&lt;TP8Size,F148+G148,"")</f>
-        <v/>
-      </c>
-      <c r="I148" s="13">
-        <f>IF(B148&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J148" s="4">
-        <f>IF(B148&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
-      <c r="A149" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B149" s="9">
-        <v>47</v>
-      </c>
-      <c r="C149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H149" s="13">
-        <f>IF(B149&lt;TP8Size,F149+G149,"")</f>
-        <v/>
-      </c>
-      <c r="I149" s="13">
-        <f>IF(B149&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J149" s="4">
-        <f>IF(B149&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
-      <c r="A150" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B150" s="9">
-        <v>48</v>
-      </c>
-      <c r="C150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H150" s="13">
-        <f>IF(B150&lt;TP8Size,F150+G150,"")</f>
-        <v/>
-      </c>
-      <c r="I150" s="13">
-        <f>IF(B150&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J150" s="4">
-        <f>IF(B150&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
-      <c r="A151" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B151" s="9">
-        <v>49</v>
-      </c>
-      <c r="C151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H151" s="13">
-        <f>IF(B151&lt;TP8Size,F151+G151,"")</f>
-        <v/>
-      </c>
-      <c r="I151" s="13">
-        <f>IF(B151&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J151" s="4">
-        <f>IF(B151&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B152" s="9">
-        <v>50</v>
-      </c>
-      <c r="C152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H152" s="13">
-        <f>IF(B152&lt;TP8Size,F152+G152,"")</f>
-        <v/>
-      </c>
-      <c r="I152" s="13">
-        <f>IF(B152&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J152" s="4">
-        <f>IF(B152&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B153" s="9">
-        <v>51</v>
-      </c>
-      <c r="C153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H153" s="13">
-        <f>IF(B153&lt;TP8Size,F153+G153,"")</f>
-        <v/>
-      </c>
-      <c r="I153" s="13">
-        <f>IF(B153&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J153" s="4">
-        <f>IF(B153&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B154" s="9">
-        <v>52</v>
-      </c>
-      <c r="C154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H154" s="13">
-        <f>IF(B154&lt;TP8Size,F154+G154,"")</f>
-        <v/>
-      </c>
-      <c r="I154" s="13">
-        <f>IF(B154&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J154" s="4">
-        <f>IF(B154&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
-      <c r="A155" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B155" s="9">
-        <v>53</v>
-      </c>
-      <c r="C155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H155" s="13">
-        <f>IF(B155&lt;TP8Size,F155+G155,"")</f>
-        <v/>
-      </c>
-      <c r="I155" s="13">
-        <f>IF(B155&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J155" s="4">
-        <f>IF(B155&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
-      <c r="A156" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B156" s="9">
-        <v>54</v>
-      </c>
-      <c r="C156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H156" s="13">
-        <f>IF(B156&lt;TP8Size,F156+G156,"")</f>
-        <v/>
-      </c>
-      <c r="I156" s="13">
-        <f>IF(B156&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J156" s="4">
-        <f>IF(B156&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
-      <c r="A157" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B157" s="9">
-        <v>55</v>
-      </c>
-      <c r="C157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H157" s="13">
-        <f>IF(B157&lt;TP8Size,F157+G157,"")</f>
-        <v/>
-      </c>
-      <c r="I157" s="13">
-        <f>IF(B157&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J157" s="4">
-        <f>IF(B157&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
-      <c r="A158" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B158" s="9">
-        <v>56</v>
-      </c>
-      <c r="C158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H158" s="13">
-        <f>IF(B158&lt;TP8Size,F158+G158,"")</f>
-        <v/>
-      </c>
-      <c r="I158" s="13">
-        <f>IF(B158&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J158" s="4">
-        <f>IF(B158&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
-      <c r="A159" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B159" s="9">
-        <v>57</v>
-      </c>
-      <c r="C159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H159" s="13">
-        <f>IF(B159&lt;TP8Size,F159+G159,"")</f>
-        <v/>
-      </c>
-      <c r="I159" s="13">
-        <f>IF(B159&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J159" s="4">
-        <f>IF(B159&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
-      <c r="A160" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B160" s="9">
-        <v>58</v>
-      </c>
-      <c r="C160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H160" s="13">
-        <f>IF(B160&lt;TP8Size,F160+G160,"")</f>
-        <v/>
-      </c>
-      <c r="I160" s="13">
-        <f>IF(B160&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J160" s="4">
-        <f>IF(B160&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:10">
-      <c r="A161" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B161" s="9">
-        <v>59</v>
-      </c>
-      <c r="C161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H161" s="13">
-        <f>IF(B161&lt;TP8Size,F161+G161,"")</f>
-        <v/>
-      </c>
-      <c r="I161" s="13">
-        <f>IF(B161&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J161" s="4">
-        <f>IF(B161&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
-      <c r="A162" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B162" s="9">
-        <v>60</v>
-      </c>
-      <c r="C162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H162" s="13">
-        <f>IF(B162&lt;TP8Size,F162+G162,"")</f>
-        <v/>
-      </c>
-      <c r="I162" s="13">
-        <f>IF(B162&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J162" s="4">
-        <f>IF(B162&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
-      <c r="A163" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B163" s="9">
-        <v>61</v>
-      </c>
-      <c r="C163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H163" s="13">
-        <f>IF(B163&lt;TP8Size,F163+G163,"")</f>
-        <v/>
-      </c>
-      <c r="I163" s="13">
-        <f>IF(B163&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J163" s="4">
-        <f>IF(B163&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
-      <c r="A164" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B164" s="9">
-        <v>62</v>
-      </c>
-      <c r="C164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H164" s="13">
-        <f>IF(B164&lt;TP8Size,F164+G164,"")</f>
-        <v/>
-      </c>
-      <c r="I164" s="13">
-        <f>IF(B164&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J164" s="4">
-        <f>IF(B164&lt;TP8Size,"YES","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
-      <c r="A165" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B165" s="9">
-        <v>63</v>
-      </c>
-      <c r="C165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$S$18/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="D165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$S$19/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="E165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$S$20/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="F165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$S$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="G165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$Q$33/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="H165" s="13">
-        <f>IF(B165&lt;TP8Size,F165+G165,"")</f>
-        <v/>
-      </c>
-      <c r="I165" s="13">
-        <f>IF(B165&lt;TP8Size,'Memory'!$Q$21/1E9,"")</f>
-        <v/>
-      </c>
-      <c r="J165" s="4">
-        <f>IF(B165&lt;TP8Size,"YES","")</f>
-        <v/>
+      <c r="J39" s="4" t="s">
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -17455,1556 +12419,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
-    <col min="2" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="62.7109375" customWidth="1"/>
-    <col min="11" max="14" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B5" s="12">
-        <f>IF(ABS(K5)&gt;=1E15,K5/1E15,IF(ABS(K5)&gt;=1E12,K5/1E12,IF(ABS(K5)&gt;=1E9,K5/1E9,IF(ABS(K5)&gt;=1E6,K5/1E6,K5))))</f>
-        <v>102.836037746688</v>
-      </c>
-      <c r="C5" s="11" t="str">
-        <f>IF(ABS(K5)&gt;=1E15,"PFLOPs",IF(ABS(K5)&gt;=1E12,"TFLOPs",IF(ABS(K5)&gt;=1E9,"GFLOPs",IF(ABS(K5)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="D5" s="12">
-        <f>IF(ABS(L5)&gt;=1E15,L5/1E15,IF(ABS(L5)&gt;=1E12,L5/1E12,IF(ABS(L5)&gt;=1E9,L5/1E9,IF(ABS(L5)&gt;=1E6,L5/1E6,L5))))</f>
-        <v>23.172382457856</v>
-      </c>
-      <c r="E5" s="11" t="str">
-        <f>IF(ABS(L5)&gt;=1E15,"PFLOPs",IF(ABS(L5)&gt;=1E12,"TFLOPs",IF(ABS(L5)&gt;=1E9,"GFLOPs",IF(ABS(L5)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="F5" s="12">
-        <f>IF(ABS(M5)&gt;=1E15,M5/1E15,IF(ABS(M5)&gt;=1E12,M5/1E12,IF(ABS(M5)&gt;=1E9,M5/1E9,IF(ABS(M5)&gt;=1E6,M5/1E6,M5))))</f>
-        <v>123.969470464</v>
-      </c>
-      <c r="G5" s="11" t="str">
-        <f>IF(ABS(M5)&gt;=1E15,"PFLOPs",IF(ABS(M5)&gt;=1E12,"TFLOPs",IF(ABS(M5)&gt;=1E9,"GFLOPs",IF(ABS(M5)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="H5" s="12">
-        <f>IF(ABS(N5)&gt;=1E15,N5/1E15,IF(ABS(N5)&gt;=1E12,N5/1E12,IF(ABS(N5)&gt;=1E9,N5/1E9,IF(ABS(N5)&gt;=1E6,N5/1E6,N5))))</f>
-        <v>19.452461056</v>
-      </c>
-      <c r="I5" s="11" t="str">
-        <f>IF(ABS(N5)&gt;=1E15,"PFLOPs",IF(ABS(N5)&gt;=1E12,"TFLOPs",IF(ABS(N5)&gt;=1E9,"GFLOPs",IF(ABS(N5)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="K5" s="13">
-        <f>'Prefill_8K'!$AE$13</f>
-        <v>102836037746688.0</v>
-      </c>
-      <c r="L5" s="13">
-        <f>'Prefill_8K'!$AF$13</f>
-        <v>23172382457856.0</v>
-      </c>
-      <c r="M5" s="13">
-        <f>'Decode_1M'!$AE$13</f>
-        <v>123969470464.0</v>
-      </c>
-      <c r="N5" s="13">
-        <f>'Decode_1M'!$AF$13</f>
-        <v>19452461056.0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="B6" s="12">
-        <f>IF(ABS(K6)&gt;=1E15,K6/1E15,IF(ABS(K6)&gt;=1E12,K6/1E12,IF(ABS(K6)&gt;=1E9,K6/1E9,IF(ABS(K6)&gt;=1E6,K6/1E6,K6))))</f>
-        <v>124.846109360128</v>
-      </c>
-      <c r="C6" s="11" t="str">
-        <f>IF(ABS(K6)&gt;=1E15,"PFLOPs",IF(ABS(K6)&gt;=1E12,"TFLOPs",IF(ABS(K6)&gt;=1E9,"GFLOPs",IF(ABS(K6)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="D6" s="12">
-        <f>IF(ABS(L6)&gt;=1E15,L6/1E15,IF(ABS(L6)&gt;=1E12,L6/1E12,IF(ABS(L6)&gt;=1E9,L6/1E9,IF(ABS(L6)&gt;=1E6,L6/1E6,L6))))</f>
-        <v>31.765578121216</v>
-      </c>
-      <c r="E6" s="11" t="str">
-        <f>IF(ABS(L6)&gt;=1E15,"PFLOPs",IF(ABS(L6)&gt;=1E12,"TFLOPs",IF(ABS(L6)&gt;=1E9,"GFLOPs",IF(ABS(L6)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="F6" s="12">
-        <f>IF(ABS(M6)&gt;=1E15,M6/1E15,IF(ABS(M6)&gt;=1E12,M6/1E12,IF(ABS(M6)&gt;=1E9,M6/1E9,IF(ABS(M6)&gt;=1E6,M6/1E6,M6))))</f>
-        <v>15.240003584</v>
-      </c>
-      <c r="G6" s="11" t="str">
-        <f>IF(ABS(M6)&gt;=1E15,"PFLOPs",IF(ABS(M6)&gt;=1E12,"TFLOPs",IF(ABS(M6)&gt;=1E9,"GFLOPs",IF(ABS(M6)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="H6" s="12">
-        <f>IF(ABS(N6)&gt;=1E15,N6/1E15,IF(ABS(N6)&gt;=1E12,N6/1E12,IF(ABS(N6)&gt;=1E9,N6/1E9,IF(ABS(N6)&gt;=1E6,N6/1E6,N6))))</f>
-        <v>3.877634048</v>
-      </c>
-      <c r="I6" s="11" t="str">
-        <f>IF(ABS(N6)&gt;=1E15,"PFLOPs",IF(ABS(N6)&gt;=1E12,"TFLOPs",IF(ABS(N6)&gt;=1E9,"GFLOPs",IF(ABS(N6)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="K6" s="13">
-        <f>'Prefill_8K'!$AE$14</f>
-        <v>124846109360128.0</v>
-      </c>
-      <c r="L6" s="13">
-        <f>'Prefill_8K'!$AF$14</f>
-        <v>31765578121216.0</v>
-      </c>
-      <c r="M6" s="13">
-        <f>'Decode_1M'!$AE$14</f>
-        <v>15240003584.0</v>
-      </c>
-      <c r="N6" s="13">
-        <f>'Decode_1M'!$AF$14</f>
-        <v>3877634048.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="B7" s="12">
-        <f>IF(ABS(K7)&gt;=1E15,K7/1E15,IF(ABS(K7)&gt;=1E12,K7/1E12,IF(ABS(K7)&gt;=1E9,K7/1E9,IF(ABS(K7)&gt;=1E6,K7/1E6,K7))))</f>
-        <v>702.280286208</v>
-      </c>
-      <c r="C7" s="11" t="str">
-        <f>IF(ABS(K7)&gt;=1E15,"PFLOPs",IF(ABS(K7)&gt;=1E12,"TFLOPs",IF(ABS(K7)&gt;=1E9,"GFLOPs",IF(ABS(K7)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="D7" s="12">
-        <f>IF(ABS(L7)&gt;=1E15,L7/1E15,IF(ABS(L7)&gt;=1E12,L7/1E12,IF(ABS(L7)&gt;=1E9,L7/1E9,IF(ABS(L7)&gt;=1E6,L7/1E6,L7))))</f>
-        <v>701.353607168</v>
-      </c>
-      <c r="E7" s="11" t="str">
-        <f>IF(ABS(L7)&gt;=1E15,"PFLOPs",IF(ABS(L7)&gt;=1E12,"TFLOPs",IF(ABS(L7)&gt;=1E9,"GFLOPs",IF(ABS(L7)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="F7" s="12">
-        <f>IF(ABS(M7)&gt;=1E15,M7/1E15,IF(ABS(M7)&gt;=1E12,M7/1E12,IF(ABS(M7)&gt;=1E9,M7/1E9,IF(ABS(M7)&gt;=1E6,M7/1E6,M7))))</f>
-        <v>1.144660054</v>
-      </c>
-      <c r="G7" s="11" t="str">
-        <f>IF(ABS(M7)&gt;=1E15,"PFLOPs",IF(ABS(M7)&gt;=1E12,"TFLOPs",IF(ABS(M7)&gt;=1E9,"GFLOPs",IF(ABS(M7)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="H7" s="12">
-        <f>IF(ABS(N7)&gt;=1E15,N7/1E15,IF(ABS(N7)&gt;=1E12,N7/1E12,IF(ABS(N7)&gt;=1E9,N7/1E9,IF(ABS(N7)&gt;=1E6,N7/1E6,N7))))</f>
-        <v>217.981014</v>
-      </c>
-      <c r="I7" s="11" t="str">
-        <f>IF(ABS(N7)&gt;=1E15,"PFLOPs",IF(ABS(N7)&gt;=1E12,"TFLOPs",IF(ABS(N7)&gt;=1E9,"GFLOPs",IF(ABS(N7)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>MFLOPs</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="K7" s="13">
-        <f>'Prefill_8K'!$AE$15</f>
-        <v>702280286208.0</v>
-      </c>
-      <c r="L7" s="13">
-        <f>'Prefill_8K'!$AF$15</f>
-        <v>701353607168.0</v>
-      </c>
-      <c r="M7" s="13">
-        <f>'Decode_1M'!$AE$15</f>
-        <v>1144660054.0</v>
-      </c>
-      <c r="N7" s="13">
-        <f>'Decode_1M'!$AF$15</f>
-        <v>217981014.0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="B8" s="14">
-        <f>IF(ABS(K8)&gt;=1E15,K8/1E15,IF(ABS(K8)&gt;=1E12,K8/1E12,IF(ABS(K8)&gt;=1E9,K8/1E9,IF(ABS(K8)&gt;=1E6,K8/1E6,K8))))</f>
-        <v>228.384427393024</v>
-      </c>
-      <c r="C8" s="11" t="str">
-        <f>IF(ABS(K8)&gt;=1E15,"PFLOPs",IF(ABS(K8)&gt;=1E12,"TFLOPs",IF(ABS(K8)&gt;=1E9,"GFLOPs",IF(ABS(K8)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="D8" s="14">
-        <f>IF(ABS(L8)&gt;=1E15,L8/1E15,IF(ABS(L8)&gt;=1E12,L8/1E12,IF(ABS(L8)&gt;=1E9,L8/1E9,IF(ABS(L8)&gt;=1E6,L8/1E6,L8))))</f>
-        <v>55.63931418624</v>
-      </c>
-      <c r="E8" s="11" t="str">
-        <f>IF(ABS(L8)&gt;=1E15,"PFLOPs",IF(ABS(L8)&gt;=1E12,"TFLOPs",IF(ABS(L8)&gt;=1E9,"GFLOPs",IF(ABS(L8)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>TFLOPs</v>
-      </c>
-      <c r="F8" s="14">
-        <f>IF(ABS(M8)&gt;=1E15,M8/1E15,IF(ABS(M8)&gt;=1E12,M8/1E12,IF(ABS(M8)&gt;=1E9,M8/1E9,IF(ABS(M8)&gt;=1E6,M8/1E6,M8))))</f>
-        <v>140.354134102</v>
-      </c>
-      <c r="G8" s="11" t="str">
-        <f>IF(ABS(M8)&gt;=1E15,"PFLOPs",IF(ABS(M8)&gt;=1E12,"TFLOPs",IF(ABS(M8)&gt;=1E9,"GFLOPs",IF(ABS(M8)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="H8" s="14">
-        <f>IF(ABS(N8)&gt;=1E15,N8/1E15,IF(ABS(N8)&gt;=1E12,N8/1E12,IF(ABS(N8)&gt;=1E9,N8/1E9,IF(ABS(N8)&gt;=1E6,N8/1E6,N8))))</f>
-        <v>23.548076118</v>
-      </c>
-      <c r="I8" s="11" t="str">
-        <f>IF(ABS(N8)&gt;=1E15,"PFLOPs",IF(ABS(N8)&gt;=1E12,"TFLOPs",IF(ABS(N8)&gt;=1E9,"GFLOPs",IF(ABS(N8)&gt;=1E6,"MFLOPs","flops"))))</f>
-        <v>GFLOPs</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="K8" s="13">
-        <f>'Prefill_8K'!$AE$16</f>
-        <v>228384427393024.0</v>
-      </c>
-      <c r="L8" s="13">
-        <f>'Prefill_8K'!$AF$16</f>
-        <v>55639314186240.0</v>
-      </c>
-      <c r="M8" s="13">
-        <f>'Decode_1M'!$AE$16</f>
-        <v>140354134102.0</v>
-      </c>
-      <c r="N8" s="13">
-        <f>'Decode_1M'!$AF$16</f>
-        <v>23548076118.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="B9" s="12">
-        <f>IF(ABS(K9)&gt;=1E12,K9/1E12,IF(ABS(K9)&gt;=1E9,K9/1E9,IF(ABS(K9)&gt;=1E6,K9/1E6,IF(ABS(K9)&gt;=1E3,K9/1E3,K9))))</f>
-        <v>358.0378144</v>
-      </c>
-      <c r="C9" s="11" t="str">
-        <f>IF(ABS(K9)&gt;=1E12,"TB",IF(ABS(K9)&gt;=1E9,"GB",IF(ABS(K9)&gt;=1E6,"MB",IF(ABS(K9)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D9" s="12">
-        <f>IF(ABS(L9)&gt;=1E12,L9/1E12,IF(ABS(L9)&gt;=1E9,L9/1E9,IF(ABS(L9)&gt;=1E6,L9/1E6,IF(ABS(L9)&gt;=1E3,L9/1E3,L9))))</f>
-        <v>231.531806144</v>
-      </c>
-      <c r="E9" s="11" t="str">
-        <f>IF(ABS(L9)&gt;=1E12,"TB",IF(ABS(L9)&gt;=1E9,"GB",IF(ABS(L9)&gt;=1E6,"MB",IF(ABS(L9)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F9" s="12">
-        <f>IF(ABS(M9)&gt;=1E12,M9/1E12,IF(ABS(M9)&gt;=1E9,M9/1E9,IF(ABS(M9)&gt;=1E6,M9/1E6,IF(ABS(M9)&gt;=1E3,M9/1E3,M9))))</f>
-        <v>10.492228352</v>
-      </c>
-      <c r="G9" s="11" t="str">
-        <f>IF(ABS(M9)&gt;=1E12,"TB",IF(ABS(M9)&gt;=1E9,"GB",IF(ABS(M9)&gt;=1E6,"MB",IF(ABS(M9)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H9" s="12">
-        <f>IF(ABS(N9)&gt;=1E12,N9/1E12,IF(ABS(N9)&gt;=1E9,N9/1E9,IF(ABS(N9)&gt;=1E6,N9/1E6,IF(ABS(N9)&gt;=1E3,N9/1E3,N9))))</f>
-        <v>4.035232528</v>
-      </c>
-      <c r="I9" s="11" t="str">
-        <f>IF(ABS(N9)&gt;=1E12,"TB",IF(ABS(N9)&gt;=1E9,"GB",IF(ABS(N9)&gt;=1E6,"MB",IF(ABS(N9)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="K9" s="13">
-        <f>'Prefill_8K'!$AE$17</f>
-        <v>358037814400.0</v>
-      </c>
-      <c r="L9" s="13">
-        <f>'Prefill_8K'!$AF$17</f>
-        <v>231531806144.0</v>
-      </c>
-      <c r="M9" s="13">
-        <f>'Decode_1M'!$AE$17</f>
-        <v>10492228352.0</v>
-      </c>
-      <c r="N9" s="13">
-        <f>'Decode_1M'!$AF$17</f>
-        <v>4035232528.0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B10" s="12">
-        <f>IF(ABS(K10)&gt;=1E12,K10/1E12,IF(ABS(K10)&gt;=1E9,K10/1E9,IF(ABS(K10)&gt;=1E6,K10/1E6,IF(ABS(K10)&gt;=1E3,K10/1E3,K10))))</f>
-        <v>191.988670976</v>
-      </c>
-      <c r="C10" s="11" t="str">
-        <f>IF(ABS(K10)&gt;=1E12,"TB",IF(ABS(K10)&gt;=1E9,"GB",IF(ABS(K10)&gt;=1E6,"MB",IF(ABS(K10)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D10" s="12">
-        <f>IF(ABS(L10)&gt;=1E12,L10/1E12,IF(ABS(L10)&gt;=1E9,L10/1E9,IF(ABS(L10)&gt;=1E6,L10/1E6,IF(ABS(L10)&gt;=1E3,L10/1E3,L10))))</f>
-        <v>32.915497472</v>
-      </c>
-      <c r="E10" s="11" t="str">
-        <f>IF(ABS(L10)&gt;=1E12,"TB",IF(ABS(L10)&gt;=1E9,"GB",IF(ABS(L10)&gt;=1E6,"MB",IF(ABS(L10)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F10" s="12">
-        <f>IF(ABS(M10)&gt;=1E12,M10/1E12,IF(ABS(M10)&gt;=1E9,M10/1E9,IF(ABS(M10)&gt;=1E6,M10/1E6,IF(ABS(M10)&gt;=1E3,M10/1E3,M10))))</f>
-        <v>4.627033672</v>
-      </c>
-      <c r="G10" s="11" t="str">
-        <f>IF(ABS(M10)&gt;=1E12,"TB",IF(ABS(M10)&gt;=1E9,"GB",IF(ABS(M10)&gt;=1E6,"MB",IF(ABS(M10)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H10" s="12">
-        <f>IF(ABS(N10)&gt;=1E12,N10/1E12,IF(ABS(N10)&gt;=1E9,N10/1E9,IF(ABS(N10)&gt;=1E6,N10/1E6,IF(ABS(N10)&gt;=1E3,N10/1E3,N10))))</f>
-        <v>1.605205576</v>
-      </c>
-      <c r="I10" s="11" t="str">
-        <f>IF(ABS(N10)&gt;=1E12,"TB",IF(ABS(N10)&gt;=1E9,"GB",IF(ABS(N10)&gt;=1E6,"MB",IF(ABS(N10)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="K10" s="13">
-        <f>'Prefill_8K'!$AE$18</f>
-        <v>191988670976.0</v>
-      </c>
-      <c r="L10" s="13">
-        <f>'Prefill_8K'!$AF$18</f>
-        <v>32915497472.0</v>
-      </c>
-      <c r="M10" s="13">
-        <f>'Decode_1M'!$AE$18</f>
-        <v>4627033672.0</v>
-      </c>
-      <c r="N10" s="13">
-        <f>'Decode_1M'!$AF$18</f>
-        <v>1605205576.0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="B11" s="12">
-        <f>IF(ABS(K11)&gt;=1E12,K11/1E12,IF(ABS(K11)&gt;=1E9,K11/1E9,IF(ABS(K11)&gt;=1E6,K11/1E6,IF(ABS(K11)&gt;=1E3,K11/1E3,K11))))</f>
-        <v>94.59572948</v>
-      </c>
-      <c r="C11" s="11" t="str">
-        <f>IF(ABS(K11)&gt;=1E12,"TB",IF(ABS(K11)&gt;=1E9,"GB",IF(ABS(K11)&gt;=1E6,"MB",IF(ABS(K11)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D11" s="12">
-        <f>IF(ABS(L11)&gt;=1E12,L11/1E12,IF(ABS(L11)&gt;=1E9,L11/1E9,IF(ABS(L11)&gt;=1E6,L11/1E6,IF(ABS(L11)&gt;=1E3,L11/1E3,L11))))</f>
-        <v>92.74191892</v>
-      </c>
-      <c r="E11" s="11" t="str">
-        <f>IF(ABS(L11)&gt;=1E12,"TB",IF(ABS(L11)&gt;=1E9,"GB",IF(ABS(L11)&gt;=1E6,"MB",IF(ABS(L11)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F11" s="12">
-        <f>IF(ABS(M11)&gt;=1E12,M11/1E12,IF(ABS(M11)&gt;=1E9,M11/1E9,IF(ABS(M11)&gt;=1E6,M11/1E6,IF(ABS(M11)&gt;=1E3,M11/1E3,M11))))</f>
-        <v>2.265204808</v>
-      </c>
-      <c r="G11" s="11" t="str">
-        <f>IF(ABS(M11)&gt;=1E12,"TB",IF(ABS(M11)&gt;=1E9,"GB",IF(ABS(M11)&gt;=1E6,"MB",IF(ABS(M11)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H11" s="12">
-        <f>IF(ABS(N11)&gt;=1E12,N11/1E12,IF(ABS(N11)&gt;=1E9,N11/1E9,IF(ABS(N11)&gt;=1E6,N11/1E6,IF(ABS(N11)&gt;=1E3,N11/1E3,N11))))</f>
-        <v>411.394248</v>
-      </c>
-      <c r="I11" s="11" t="str">
-        <f>IF(ABS(N11)&gt;=1E12,"TB",IF(ABS(N11)&gt;=1E9,"GB",IF(ABS(N11)&gt;=1E6,"MB",IF(ABS(N11)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" s="13">
-        <f>'Prefill_8K'!$AE$19</f>
-        <v>94595729480.0</v>
-      </c>
-      <c r="L11" s="13">
-        <f>'Prefill_8K'!$AF$19</f>
-        <v>92741918920.0</v>
-      </c>
-      <c r="M11" s="13">
-        <f>'Decode_1M'!$AE$19</f>
-        <v>2265204808.0</v>
-      </c>
-      <c r="N11" s="13">
-        <f>'Decode_1M'!$AF$19</f>
-        <v>411394248.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="B12" s="14">
-        <f>IF(ABS(K12)&gt;=1E12,K12/1E12,IF(ABS(K12)&gt;=1E9,K12/1E9,IF(ABS(K12)&gt;=1E6,K12/1E6,IF(ABS(K12)&gt;=1E3,K12/1E3,K12))))</f>
-        <v>644.622214856</v>
-      </c>
-      <c r="C12" s="11" t="str">
-        <f>IF(ABS(K12)&gt;=1E12,"TB",IF(ABS(K12)&gt;=1E9,"GB",IF(ABS(K12)&gt;=1E6,"MB",IF(ABS(K12)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D12" s="14">
-        <f>IF(ABS(L12)&gt;=1E12,L12/1E12,IF(ABS(L12)&gt;=1E9,L12/1E9,IF(ABS(L12)&gt;=1E6,L12/1E6,IF(ABS(L12)&gt;=1E3,L12/1E3,L12))))</f>
-        <v>357.189222536</v>
-      </c>
-      <c r="E12" s="11" t="str">
-        <f>IF(ABS(L12)&gt;=1E12,"TB",IF(ABS(L12)&gt;=1E9,"GB",IF(ABS(L12)&gt;=1E6,"MB",IF(ABS(L12)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F12" s="14">
-        <f>IF(ABS(M12)&gt;=1E12,M12/1E12,IF(ABS(M12)&gt;=1E9,M12/1E9,IF(ABS(M12)&gt;=1E6,M12/1E6,IF(ABS(M12)&gt;=1E3,M12/1E3,M12))))</f>
-        <v>17.384466832</v>
-      </c>
-      <c r="G12" s="11" t="str">
-        <f>IF(ABS(M12)&gt;=1E12,"TB",IF(ABS(M12)&gt;=1E9,"GB",IF(ABS(M12)&gt;=1E6,"MB",IF(ABS(M12)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H12" s="14">
-        <f>IF(ABS(N12)&gt;=1E12,N12/1E12,IF(ABS(N12)&gt;=1E9,N12/1E9,IF(ABS(N12)&gt;=1E6,N12/1E6,IF(ABS(N12)&gt;=1E3,N12/1E3,N12))))</f>
-        <v>6.051832352</v>
-      </c>
-      <c r="I12" s="11" t="str">
-        <f>IF(ABS(N12)&gt;=1E12,"TB",IF(ABS(N12)&gt;=1E9,"GB",IF(ABS(N12)&gt;=1E6,"MB",IF(ABS(N12)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="K12" s="13">
-        <f>'Prefill_8K'!$AE$20</f>
-        <v>644622214856.0</v>
-      </c>
-      <c r="L12" s="13">
-        <f>'Prefill_8K'!$AF$20</f>
-        <v>357189222536.0</v>
-      </c>
-      <c r="M12" s="13">
-        <f>'Decode_1M'!$AE$20</f>
-        <v>17384466832.0</v>
-      </c>
-      <c r="N12" s="13">
-        <f>'Decode_1M'!$AF$20</f>
-        <v>6051832352.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B13" s="12">
-        <f>K13</f>
-        <v>358.0378144</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" s="12">
-        <f>L13</f>
-        <v>231.531806144</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="12">
-        <f>M13</f>
-        <v>1049.2228352</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="12">
-        <f>N13</f>
-        <v>403.5232528</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="K13" s="13">
-        <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
-        <v>358.0378144</v>
-      </c>
-      <c r="L13" s="13">
-        <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
-        <v>231.531806144</v>
-      </c>
-      <c r="M13" s="13">
-        <f>'Decode_1M'!$AE$17/(DecodeTargetMs/1000)/1E9</f>
-        <v>1049.2228352</v>
-      </c>
-      <c r="N13" s="13">
-        <f>'Decode_1M'!$AF$17/(DecodeTargetMs/1000)/1E9</f>
-        <v>403.5232528</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="B14" s="12">
-        <f>K14</f>
-        <v>191.988670976</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="12">
-        <f>L14</f>
-        <v>32.915497472</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="12">
-        <f>M14</f>
-        <v>462.7033672</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H14" s="12">
-        <f>N14</f>
-        <v>160.5205576</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="K14" s="13">
-        <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
-        <v>191.988670976</v>
-      </c>
-      <c r="L14" s="13">
-        <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
-        <v>32.915497472</v>
-      </c>
-      <c r="M14" s="13">
-        <f>'Decode_1M'!$AE$18/(DecodeTargetMs/1000)/1E9</f>
-        <v>462.7033672</v>
-      </c>
-      <c r="N14" s="13">
-        <f>'Decode_1M'!$AF$18/(DecodeTargetMs/1000)/1E9</f>
-        <v>160.5205576</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="B15" s="12">
-        <f>K15</f>
-        <v>94.59572948</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" s="12">
-        <f>L15</f>
-        <v>92.74191892</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="12">
-        <f>M15</f>
-        <v>226.5204808</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H15" s="12">
-        <f>N15</f>
-        <v>41.1394248</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="K15" s="13">
-        <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
-        <v>94.59572948</v>
-      </c>
-      <c r="L15" s="13">
-        <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
-        <v>92.74191892</v>
-      </c>
-      <c r="M15" s="13">
-        <f>'Decode_1M'!$AE$19/(DecodeTargetMs/1000)/1E9</f>
-        <v>226.5204808</v>
-      </c>
-      <c r="N15" s="13">
-        <f>'Decode_1M'!$AF$19/(DecodeTargetMs/1000)/1E9</f>
-        <v>41.1394248</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="B16" s="12">
-        <f>K16</f>
-        <v>228.384427393024</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="12">
-        <f>L16</f>
-        <v>55.63931418624</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" s="12">
-        <f>M16</f>
-        <v>14.0354134102</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="12">
-        <f>N16</f>
-        <v>2.3548076118</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="K16" s="13">
-        <f>'Prefill_8K'!$AE$23</f>
-        <v>228.384427393024</v>
-      </c>
-      <c r="L16" s="13">
-        <f>'Prefill_8K'!$AF$23</f>
-        <v>55.63931418624</v>
-      </c>
-      <c r="M16" s="13">
-        <f>'Decode_1M'!$AE$23</f>
-        <v>14.0354134102</v>
-      </c>
-      <c r="N16" s="13">
-        <f>'Decode_1M'!$AF$23</f>
-        <v>2.3548076118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="B17" s="12">
-        <f>IF(ABS(K17)&gt;=1E12,K17/1E12,IF(ABS(K17)&gt;=1E9,K17/1E9,IF(ABS(K17)&gt;=1E6,K17/1E6,IF(ABS(K17)&gt;=1E3,K17/1E3,K17))))</f>
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="11" t="str">
-        <f>IF(ABS(K17)&gt;=1E12,"TB",IF(ABS(K17)&gt;=1E9,"GB",IF(ABS(K17)&gt;=1E6,"MB",IF(ABS(K17)&gt;=1E3,"KB","bytes"))))</f>
-        <v>B</v>
-      </c>
-      <c r="D17" s="12">
-        <f>IF(ABS(L17)&gt;=1E12,L17/1E12,IF(ABS(L17)&gt;=1E9,L17/1E9,IF(ABS(L17)&gt;=1E6,L17/1E6,IF(ABS(L17)&gt;=1E3,L17/1E3,L17))))</f>
-        <v>40.635322112</v>
-      </c>
-      <c r="E17" s="11" t="str">
-        <f>IF(ABS(L17)&gt;=1E12,"TB",IF(ABS(L17)&gt;=1E9,"GB",IF(ABS(L17)&gt;=1E6,"MB",IF(ABS(L17)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F17" s="12">
-        <f>IF(ABS(M17)&gt;=1E12,M17/1E12,IF(ABS(M17)&gt;=1E9,M17/1E9,IF(ABS(M17)&gt;=1E6,M17/1E6,IF(ABS(M17)&gt;=1E3,M17/1E3,M17))))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="11" t="str">
-        <f>IF(ABS(M17)&gt;=1E12,"TB",IF(ABS(M17)&gt;=1E9,"GB",IF(ABS(M17)&gt;=1E6,"MB",IF(ABS(M17)&gt;=1E3,"KB","bytes"))))</f>
-        <v>B</v>
-      </c>
-      <c r="H17" s="12">
-        <f>IF(ABS(N17)&gt;=1E12,N17/1E12,IF(ABS(N17)&gt;=1E9,N17/1E9,IF(ABS(N17)&gt;=1E6,N17/1E6,IF(ABS(N17)&gt;=1E3,N17/1E3,N17))))</f>
-        <v>5.865216</v>
-      </c>
-      <c r="I17" s="11" t="str">
-        <f>IF(ABS(N17)&gt;=1E12,"TB",IF(ABS(N17)&gt;=1E9,"GB",IF(ABS(N17)&gt;=1E6,"MB",IF(ABS(N17)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="K17" s="13">
-        <f>'Prefill_8K'!$AE$21</f>
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="13">
-        <f>'Prefill_8K'!$AF$21</f>
-        <v>40635322112.0</v>
-      </c>
-      <c r="M17" s="13">
-        <f>'Decode_1M'!$AE$21</f>
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="13">
-        <f>'Decode_1M'!$AF$21</f>
-        <v>5865216.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B18" s="12">
-        <f>K18</f>
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" s="12">
-        <f>L18</f>
-        <v>40.635322112</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="12">
-        <f>M18</f>
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="12">
-        <f>N18</f>
-        <v>0.5865216</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="K18" s="13">
-        <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="13">
-        <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
-        <v>40.635322112</v>
-      </c>
-      <c r="M18" s="13">
-        <f>'Decode_1M'!$AE$21/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="13">
-        <f>'Decode_1M'!$AF$21/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.5865216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="B19" s="12">
-        <f>IF(ABS(K19)&gt;=1E12,K19/1E12,IF(ABS(K19)&gt;=1E9,K19/1E9,IF(ABS(K19)&gt;=1E6,K19/1E6,IF(ABS(K19)&gt;=1E3,K19/1E3,K19))))</f>
-        <v>5.086249088</v>
-      </c>
-      <c r="C19" s="11" t="str">
-        <f>IF(ABS(K19)&gt;=1E12,"T params",IF(ABS(K19)&gt;=1E9,"G params",IF(ABS(K19)&gt;=1E6,"M params",IF(ABS(K19)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="D19" s="12">
-        <f>IF(ABS(L19)&gt;=1E12,L19/1E12,IF(ABS(L19)&gt;=1E9,L19/1E9,IF(ABS(L19)&gt;=1E6,L19/1E6,IF(ABS(L19)&gt;=1E3,L19/1E3,L19))))</f>
-        <v>1.139835008</v>
-      </c>
-      <c r="E19" s="11" t="str">
-        <f>IF(ABS(L19)&gt;=1E12,"T params",IF(ABS(L19)&gt;=1E9,"G params",IF(ABS(L19)&gt;=1E6,"M params",IF(ABS(L19)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="F19" s="12">
-        <f>IF(ABS(M19)&gt;=1E12,M19/1E12,IF(ABS(M19)&gt;=1E9,M19/1E9,IF(ABS(M19)&gt;=1E6,M19/1E6,IF(ABS(M19)&gt;=1E3,M19/1E3,M19))))</f>
-        <v>5.086249088</v>
-      </c>
-      <c r="G19" s="11" t="str">
-        <f>IF(ABS(M19)&gt;=1E12,"T params",IF(ABS(M19)&gt;=1E9,"G params",IF(ABS(M19)&gt;=1E6,"M params",IF(ABS(M19)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="H19" s="12">
-        <f>IF(ABS(N19)&gt;=1E12,N19/1E12,IF(ABS(N19)&gt;=1E9,N19/1E9,IF(ABS(N19)&gt;=1E6,N19/1E6,IF(ABS(N19)&gt;=1E3,N19/1E3,N19))))</f>
-        <v>1.139835008</v>
-      </c>
-      <c r="I19" s="11" t="str">
-        <f>IF(ABS(N19)&gt;=1E12,"T params",IF(ABS(N19)&gt;=1E9,"G params",IF(ABS(N19)&gt;=1E6,"M params",IF(ABS(N19)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="K19" s="13">
-        <f>'Memory'!$P$18</f>
-        <v>5086249088.0</v>
-      </c>
-      <c r="L19" s="13">
-        <f>'Memory'!$Q$18</f>
-        <v>1139835008.0</v>
-      </c>
-      <c r="M19" s="13">
-        <f>'Memory'!$P$18</f>
-        <v>5086249088.0</v>
-      </c>
-      <c r="N19" s="13">
-        <f>'Memory'!$Q$18</f>
-        <v>1139835008.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="B20" s="12">
-        <f>IF(ABS(K20)&gt;=1E12,K20/1E12,IF(ABS(K20)&gt;=1E9,K20/1E9,IF(ABS(K20)&gt;=1E6,K20/1E6,IF(ABS(K20)&gt;=1E3,K20/1E3,K20))))</f>
-        <v>278.154947072</v>
-      </c>
-      <c r="C20" s="11" t="str">
-        <f>IF(ABS(K20)&gt;=1E12,"T params",IF(ABS(K20)&gt;=1E9,"G params",IF(ABS(K20)&gt;=1E6,"M params",IF(ABS(K20)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="D20" s="12">
-        <f>IF(ABS(L20)&gt;=1E12,L20/1E12,IF(ABS(L20)&gt;=1E9,L20/1E9,IF(ABS(L20)&gt;=1E6,L20/1E6,IF(ABS(L20)&gt;=1E3,L20/1E3,L20))))</f>
-        <v>35.757730304</v>
-      </c>
-      <c r="E20" s="11" t="str">
-        <f>IF(ABS(L20)&gt;=1E12,"T params",IF(ABS(L20)&gt;=1E9,"G params",IF(ABS(L20)&gt;=1E6,"M params",IF(ABS(L20)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="F20" s="12">
-        <f>IF(ABS(M20)&gt;=1E12,M20/1E12,IF(ABS(M20)&gt;=1E9,M20/1E9,IF(ABS(M20)&gt;=1E6,M20/1E6,IF(ABS(M20)&gt;=1E3,M20/1E3,M20))))</f>
-        <v>278.154947072</v>
-      </c>
-      <c r="G20" s="11" t="str">
-        <f>IF(ABS(M20)&gt;=1E12,"T params",IF(ABS(M20)&gt;=1E9,"G params",IF(ABS(M20)&gt;=1E6,"M params",IF(ABS(M20)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="H20" s="12">
-        <f>IF(ABS(N20)&gt;=1E12,N20/1E12,IF(ABS(N20)&gt;=1E9,N20/1E9,IF(ABS(N20)&gt;=1E6,N20/1E6,IF(ABS(N20)&gt;=1E3,N20/1E3,N20))))</f>
-        <v>35.757730304</v>
-      </c>
-      <c r="I20" s="11" t="str">
-        <f>IF(ABS(N20)&gt;=1E12,"T params",IF(ABS(N20)&gt;=1E9,"G params",IF(ABS(N20)&gt;=1E6,"M params",IF(ABS(N20)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="K20" s="13">
-        <f>'Memory'!$P$19</f>
-        <v>278154947072.0</v>
-      </c>
-      <c r="L20" s="13">
-        <f>'Memory'!$Q$19</f>
-        <v>35757730304.0</v>
-      </c>
-      <c r="M20" s="13">
-        <f>'Memory'!$P$19</f>
-        <v>278154947072.0</v>
-      </c>
-      <c r="N20" s="13">
-        <f>'Memory'!$Q$19</f>
-        <v>35757730304.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="B21" s="12">
-        <f>IF(ABS(K21)&gt;=1E12,K21/1E12,IF(ABS(K21)&gt;=1E9,K21/1E9,IF(ABS(K21)&gt;=1E6,K21/1E6,IF(ABS(K21)&gt;=1E3,K21/1E3,K21))))</f>
-        <v>1.093371351</v>
-      </c>
-      <c r="C21" s="11" t="str">
-        <f>IF(ABS(K21)&gt;=1E12,"T params",IF(ABS(K21)&gt;=1E9,"G params",IF(ABS(K21)&gt;=1E6,"M params",IF(ABS(K21)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="D21" s="12">
-        <f>IF(ABS(L21)&gt;=1E12,L21/1E12,IF(ABS(L21)&gt;=1E9,L21/1E9,IF(ABS(L21)&gt;=1E6,L21/1E6,IF(ABS(L21)&gt;=1E3,L21/1E3,L21))))</f>
-        <v>166.689903</v>
-      </c>
-      <c r="E21" s="11" t="str">
-        <f>IF(ABS(L21)&gt;=1E12,"T params",IF(ABS(L21)&gt;=1E9,"G params",IF(ABS(L21)&gt;=1E6,"M params",IF(ABS(L21)&gt;=1E3,"K params","params"))))</f>
-        <v>M params</v>
-      </c>
-      <c r="F21" s="12">
-        <f>IF(ABS(M21)&gt;=1E12,M21/1E12,IF(ABS(M21)&gt;=1E9,M21/1E9,IF(ABS(M21)&gt;=1E6,M21/1E6,IF(ABS(M21)&gt;=1E3,M21/1E3,M21))))</f>
-        <v>1.093371351</v>
-      </c>
-      <c r="G21" s="11" t="str">
-        <f>IF(ABS(M21)&gt;=1E12,"T params",IF(ABS(M21)&gt;=1E9,"G params",IF(ABS(M21)&gt;=1E6,"M params",IF(ABS(M21)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="H21" s="12">
-        <f>IF(ABS(N21)&gt;=1E12,N21/1E12,IF(ABS(N21)&gt;=1E9,N21/1E9,IF(ABS(N21)&gt;=1E6,N21/1E6,IF(ABS(N21)&gt;=1E3,N21/1E3,N21))))</f>
-        <v>166.689903</v>
-      </c>
-      <c r="I21" s="11" t="str">
-        <f>IF(ABS(N21)&gt;=1E12,"T params",IF(ABS(N21)&gt;=1E9,"G params",IF(ABS(N21)&gt;=1E6,"M params",IF(ABS(N21)&gt;=1E3,"K params","params"))))</f>
-        <v>M params</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="K21" s="13">
-        <f>'Memory'!$P$20</f>
-        <v>1093371351.0</v>
-      </c>
-      <c r="L21" s="13">
-        <f>'Memory'!$Q$20</f>
-        <v>166689903.0</v>
-      </c>
-      <c r="M21" s="13">
-        <f>'Memory'!$P$20</f>
-        <v>1093371351.0</v>
-      </c>
-      <c r="N21" s="13">
-        <f>'Memory'!$Q$20</f>
-        <v>166689903.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="B22" s="14">
-        <f>IF(ABS(K22)&gt;=1E12,K22/1E12,IF(ABS(K22)&gt;=1E9,K22/1E9,IF(ABS(K22)&gt;=1E6,K22/1E6,IF(ABS(K22)&gt;=1E3,K22/1E3,K22))))</f>
-        <v>284.334567511</v>
-      </c>
-      <c r="C22" s="11" t="str">
-        <f>IF(ABS(K22)&gt;=1E12,"T params",IF(ABS(K22)&gt;=1E9,"G params",IF(ABS(K22)&gt;=1E6,"M params",IF(ABS(K22)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="D22" s="14">
-        <f>IF(ABS(L22)&gt;=1E12,L22/1E12,IF(ABS(L22)&gt;=1E9,L22/1E9,IF(ABS(L22)&gt;=1E6,L22/1E6,IF(ABS(L22)&gt;=1E3,L22/1E3,L22))))</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="E22" s="11" t="str">
-        <f>IF(ABS(L22)&gt;=1E12,"T params",IF(ABS(L22)&gt;=1E9,"G params",IF(ABS(L22)&gt;=1E6,"M params",IF(ABS(L22)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="F22" s="14">
-        <f>IF(ABS(M22)&gt;=1E12,M22/1E12,IF(ABS(M22)&gt;=1E9,M22/1E9,IF(ABS(M22)&gt;=1E6,M22/1E6,IF(ABS(M22)&gt;=1E3,M22/1E3,M22))))</f>
-        <v>284.334567511</v>
-      </c>
-      <c r="G22" s="11" t="str">
-        <f>IF(ABS(M22)&gt;=1E12,"T params",IF(ABS(M22)&gt;=1E9,"G params",IF(ABS(M22)&gt;=1E6,"M params",IF(ABS(M22)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="H22" s="14">
-        <f>IF(ABS(N22)&gt;=1E12,N22/1E12,IF(ABS(N22)&gt;=1E9,N22/1E9,IF(ABS(N22)&gt;=1E6,N22/1E6,IF(ABS(N22)&gt;=1E3,N22/1E3,N22))))</f>
-        <v>37.064255215</v>
-      </c>
-      <c r="I22" s="11" t="str">
-        <f>IF(ABS(N22)&gt;=1E12,"T params",IF(ABS(N22)&gt;=1E9,"G params",IF(ABS(N22)&gt;=1E6,"M params",IF(ABS(N22)&gt;=1E3,"K params","params"))))</f>
-        <v>G params</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="K22" s="13">
-        <f>'Memory'!$P$21</f>
-        <v>284334567511.0</v>
-      </c>
-      <c r="L22" s="13">
-        <f>'Memory'!$Q$21</f>
-        <v>37064255215.0</v>
-      </c>
-      <c r="M22" s="13">
-        <f>'Memory'!$P$21</f>
-        <v>284334567511.0</v>
-      </c>
-      <c r="N22" s="13">
-        <f>'Memory'!$Q$21</f>
-        <v>37064255215.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="B23" s="12">
-        <f>IF(ABS(K23)&gt;=1E12,K23/1E12,IF(ABS(K23)&gt;=1E9,K23/1E9,IF(ABS(K23)&gt;=1E6,K23/1E6,IF(ABS(K23)&gt;=1E3,K23/1E3,K23))))</f>
-        <v>7.45138496</v>
-      </c>
-      <c r="C23" s="11" t="str">
-        <f>IF(ABS(K23)&gt;=1E12,"TB",IF(ABS(K23)&gt;=1E9,"GB",IF(ABS(K23)&gt;=1E6,"MB",IF(ABS(K23)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D23" s="12">
-        <f>IF(ABS(L23)&gt;=1E12,L23/1E12,IF(ABS(L23)&gt;=1E9,L23/1E9,IF(ABS(L23)&gt;=1E6,L23/1E6,IF(ABS(L23)&gt;=1E3,L23/1E3,L23))))</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="E23" s="11" t="str">
-        <f>IF(ABS(L23)&gt;=1E12,"TB",IF(ABS(L23)&gt;=1E9,"GB",IF(ABS(L23)&gt;=1E6,"MB",IF(ABS(L23)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F23" s="12">
-        <f>IF(ABS(M23)&gt;=1E12,M23/1E12,IF(ABS(M23)&gt;=1E9,M23/1E9,IF(ABS(M23)&gt;=1E6,M23/1E6,IF(ABS(M23)&gt;=1E3,M23/1E3,M23))))</f>
-        <v>7.45138496</v>
-      </c>
-      <c r="G23" s="11" t="str">
-        <f>IF(ABS(M23)&gt;=1E12,"TB",IF(ABS(M23)&gt;=1E9,"GB",IF(ABS(M23)&gt;=1E6,"MB",IF(ABS(M23)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H23" s="12">
-        <f>IF(ABS(N23)&gt;=1E12,N23/1E12,IF(ABS(N23)&gt;=1E9,N23/1E9,IF(ABS(N23)&gt;=1E6,N23/1E6,IF(ABS(N23)&gt;=1E3,N23/1E3,N23))))</f>
-        <v>2.23750496</v>
-      </c>
-      <c r="I23" s="11" t="str">
-        <f>IF(ABS(N23)&gt;=1E12,"TB",IF(ABS(N23)&gt;=1E9,"GB",IF(ABS(N23)&gt;=1E6,"MB",IF(ABS(N23)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="K23" s="13">
-        <f>'Memory'!$R$18</f>
-        <v>7451384960</v>
-      </c>
-      <c r="L23" s="13">
-        <f>'Memory'!$S$18</f>
-        <v>2237504960</v>
-      </c>
-      <c r="M23" s="13">
-        <f>'Memory'!$R$18</f>
-        <v>7451384960</v>
-      </c>
-      <c r="N23" s="13">
-        <f>'Memory'!$S$18</f>
-        <v>2237504960</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="B24" s="12">
-        <f>IF(ABS(K24)&gt;=1E12,K24/1E12,IF(ABS(K24)&gt;=1E9,K24/1E9,IF(ABS(K24)&gt;=1E6,K24/1E6,IF(ABS(K24)&gt;=1E3,K24/1E3,K24))))</f>
-        <v>148.351461888</v>
-      </c>
-      <c r="C24" s="11" t="str">
-        <f>IF(ABS(K24)&gt;=1E12,"TB",IF(ABS(K24)&gt;=1E9,"GB",IF(ABS(K24)&gt;=1E6,"MB",IF(ABS(K24)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D24" s="12">
-        <f>IF(ABS(L24)&gt;=1E12,L24/1E12,IF(ABS(L24)&gt;=1E9,L24/1E9,IF(ABS(L24)&gt;=1E6,L24/1E6,IF(ABS(L24)&gt;=1E3,L24/1E3,L24))))</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="E24" s="11" t="str">
-        <f>IF(ABS(L24)&gt;=1E12,"TB",IF(ABS(L24)&gt;=1E9,"GB",IF(ABS(L24)&gt;=1E6,"MB",IF(ABS(L24)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F24" s="12">
-        <f>IF(ABS(M24)&gt;=1E12,M24/1E12,IF(ABS(M24)&gt;=1E9,M24/1E9,IF(ABS(M24)&gt;=1E6,M24/1E6,IF(ABS(M24)&gt;=1E3,M24/1E3,M24))))</f>
-        <v>148.351461888</v>
-      </c>
-      <c r="G24" s="11" t="str">
-        <f>IF(ABS(M24)&gt;=1E12,"TB",IF(ABS(M24)&gt;=1E9,"GB",IF(ABS(M24)&gt;=1E6,"MB",IF(ABS(M24)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H24" s="12">
-        <f>IF(ABS(N24)&gt;=1E12,N24/1E12,IF(ABS(N24)&gt;=1E9,N24/1E9,IF(ABS(N24)&gt;=1E6,N24/1E6,IF(ABS(N24)&gt;=1E3,N24/1E3,N24))))</f>
-        <v>19.57794048</v>
-      </c>
-      <c r="I24" s="11" t="str">
-        <f>IF(ABS(N24)&gt;=1E12,"TB",IF(ABS(N24)&gt;=1E9,"GB",IF(ABS(N24)&gt;=1E6,"MB",IF(ABS(N24)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="K24" s="13">
-        <f>'Memory'!$R$19</f>
-        <v>148351461888.0</v>
-      </c>
-      <c r="L24" s="13">
-        <f>'Memory'!$S$19</f>
-        <v>19577940480.0</v>
-      </c>
-      <c r="M24" s="13">
-        <f>'Memory'!$R$19</f>
-        <v>148351461888.0</v>
-      </c>
-      <c r="N24" s="13">
-        <f>'Memory'!$S$19</f>
-        <v>19577940480.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="B25" s="12">
-        <f>IF(ABS(K25)&gt;=1E12,K25/1E12,IF(ABS(K25)&gt;=1E9,K25/1E9,IF(ABS(K25)&gt;=1E6,K25/1E6,IF(ABS(K25)&gt;=1E3,K25/1E3,K25))))</f>
-        <v>3.314423644</v>
-      </c>
-      <c r="C25" s="11" t="str">
-        <f>IF(ABS(K25)&gt;=1E12,"TB",IF(ABS(K25)&gt;=1E9,"GB",IF(ABS(K25)&gt;=1E6,"MB",IF(ABS(K25)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D25" s="12">
-        <f>IF(ABS(L25)&gt;=1E12,L25/1E12,IF(ABS(L25)&gt;=1E9,L25/1E9,IF(ABS(L25)&gt;=1E6,L25/1E6,IF(ABS(L25)&gt;=1E3,L25/1E3,L25))))</f>
-        <v>534.376892</v>
-      </c>
-      <c r="E25" s="11" t="str">
-        <f>IF(ABS(L25)&gt;=1E12,"TB",IF(ABS(L25)&gt;=1E9,"GB",IF(ABS(L25)&gt;=1E6,"MB",IF(ABS(L25)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="F25" s="12">
-        <f>IF(ABS(M25)&gt;=1E12,M25/1E12,IF(ABS(M25)&gt;=1E9,M25/1E9,IF(ABS(M25)&gt;=1E6,M25/1E6,IF(ABS(M25)&gt;=1E3,M25/1E3,M25))))</f>
-        <v>3.314423644</v>
-      </c>
-      <c r="G25" s="11" t="str">
-        <f>IF(ABS(M25)&gt;=1E12,"TB",IF(ABS(M25)&gt;=1E9,"GB",IF(ABS(M25)&gt;=1E6,"MB",IF(ABS(M25)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H25" s="12">
-        <f>IF(ABS(N25)&gt;=1E12,N25/1E12,IF(ABS(N25)&gt;=1E9,N25/1E9,IF(ABS(N25)&gt;=1E6,N25/1E6,IF(ABS(N25)&gt;=1E3,N25/1E3,N25))))</f>
-        <v>534.376892</v>
-      </c>
-      <c r="I25" s="11" t="str">
-        <f>IF(ABS(N25)&gt;=1E12,"TB",IF(ABS(N25)&gt;=1E9,"GB",IF(ABS(N25)&gt;=1E6,"MB",IF(ABS(N25)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="K25" s="13">
-        <f>'Memory'!$R$20</f>
-        <v>3314423644.0</v>
-      </c>
-      <c r="L25" s="13">
-        <f>'Memory'!$S$20</f>
-        <v>534376892.0</v>
-      </c>
-      <c r="M25" s="13">
-        <f>'Memory'!$R$20</f>
-        <v>3314423644.0</v>
-      </c>
-      <c r="N25" s="13">
-        <f>'Memory'!$S$20</f>
-        <v>534376892.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="B26" s="14">
-        <f>IF(ABS(K26)&gt;=1E12,K26/1E12,IF(ABS(K26)&gt;=1E9,K26/1E9,IF(ABS(K26)&gt;=1E6,K26/1E6,IF(ABS(K26)&gt;=1E3,K26/1E3,K26))))</f>
-        <v>159.117270492</v>
-      </c>
-      <c r="C26" s="11" t="str">
-        <f>IF(ABS(K26)&gt;=1E12,"TB",IF(ABS(K26)&gt;=1E9,"GB",IF(ABS(K26)&gt;=1E6,"MB",IF(ABS(K26)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D26" s="14">
-        <f>IF(ABS(L26)&gt;=1E12,L26/1E12,IF(ABS(L26)&gt;=1E9,L26/1E9,IF(ABS(L26)&gt;=1E6,L26/1E6,IF(ABS(L26)&gt;=1E3,L26/1E3,L26))))</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="E26" s="11" t="str">
-        <f>IF(ABS(L26)&gt;=1E12,"TB",IF(ABS(L26)&gt;=1E9,"GB",IF(ABS(L26)&gt;=1E6,"MB",IF(ABS(L26)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F26" s="14">
-        <f>IF(ABS(M26)&gt;=1E12,M26/1E12,IF(ABS(M26)&gt;=1E9,M26/1E9,IF(ABS(M26)&gt;=1E6,M26/1E6,IF(ABS(M26)&gt;=1E3,M26/1E3,M26))))</f>
-        <v>159.117270492</v>
-      </c>
-      <c r="G26" s="11" t="str">
-        <f>IF(ABS(M26)&gt;=1E12,"TB",IF(ABS(M26)&gt;=1E9,"GB",IF(ABS(M26)&gt;=1E6,"MB",IF(ABS(M26)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H26" s="14">
-        <f>IF(ABS(N26)&gt;=1E12,N26/1E12,IF(ABS(N26)&gt;=1E9,N26/1E9,IF(ABS(N26)&gt;=1E6,N26/1E6,IF(ABS(N26)&gt;=1E3,N26/1E3,N26))))</f>
-        <v>22.349822332</v>
-      </c>
-      <c r="I26" s="11" t="str">
-        <f>IF(ABS(N26)&gt;=1E12,"TB",IF(ABS(N26)&gt;=1E9,"GB",IF(ABS(N26)&gt;=1E6,"MB",IF(ABS(N26)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="K26" s="13">
-        <f>'Memory'!$R$21</f>
-        <v>159117270492.0</v>
-      </c>
-      <c r="L26" s="13">
-        <f>'Memory'!$S$21</f>
-        <v>22349822332.0</v>
-      </c>
-      <c r="M26" s="13">
-        <f>'Memory'!$R$21</f>
-        <v>159117270492.0</v>
-      </c>
-      <c r="N26" s="13">
-        <f>'Memory'!$S$21</f>
-        <v>22349822332.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="B27" s="12">
-        <f>IF(ABS(K27)&gt;=1E12,K27/1E12,IF(ABS(K27)&gt;=1E9,K27/1E9,IF(ABS(K27)&gt;=1E6,K27/1E6,IF(ABS(K27)&gt;=1E3,K27/1E3,K27))))</f>
-        <v>50.987008</v>
-      </c>
-      <c r="C27" s="11" t="str">
-        <f>IF(ABS(K27)&gt;=1E12,"TB",IF(ABS(K27)&gt;=1E9,"GB",IF(ABS(K27)&gt;=1E6,"MB",IF(ABS(K27)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="D27" s="12">
-        <f>IF(ABS(L27)&gt;=1E12,L27/1E12,IF(ABS(L27)&gt;=1E9,L27/1E9,IF(ABS(L27)&gt;=1E6,L27/1E6,IF(ABS(L27)&gt;=1E3,L27/1E3,L27))))</f>
-        <v>50.987008</v>
-      </c>
-      <c r="E27" s="11" t="str">
-        <f>IF(ABS(L27)&gt;=1E12,"TB",IF(ABS(L27)&gt;=1E9,"GB",IF(ABS(L27)&gt;=1E6,"MB",IF(ABS(L27)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="F27" s="12">
-        <f>IF(ABS(M27)&gt;=1E12,M27/1E12,IF(ABS(M27)&gt;=1E9,M27/1E9,IF(ABS(M27)&gt;=1E6,M27/1E6,IF(ABS(M27)&gt;=1E3,M27/1E3,M27))))</f>
-        <v>5.810552832</v>
-      </c>
-      <c r="G27" s="11" t="str">
-        <f>IF(ABS(M27)&gt;=1E12,"TB",IF(ABS(M27)&gt;=1E9,"GB",IF(ABS(M27)&gt;=1E6,"MB",IF(ABS(M27)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H27" s="12">
-        <f>IF(ABS(N27)&gt;=1E12,N27/1E12,IF(ABS(N27)&gt;=1E9,N27/1E9,IF(ABS(N27)&gt;=1E6,N27/1E6,IF(ABS(N27)&gt;=1E3,N27/1E3,N27))))</f>
-        <v>5.810552832</v>
-      </c>
-      <c r="I27" s="11" t="str">
-        <f>IF(ABS(N27)&gt;=1E12,"TB",IF(ABS(N27)&gt;=1E9,"GB",IF(ABS(N27)&gt;=1E6,"MB",IF(ABS(N27)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="K27" s="13">
-        <f>'Memory'!$P$26</f>
-        <v>50987008</v>
-      </c>
-      <c r="L27" s="13">
-        <f>'Memory'!$Q$26</f>
-        <v>50987008</v>
-      </c>
-      <c r="M27" s="13">
-        <f>'Memory'!$P$30</f>
-        <v>5810552832</v>
-      </c>
-      <c r="N27" s="13">
-        <f>'Memory'!$Q$30</f>
-        <v>5810552832</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="B28" s="12">
-        <f>IF(ABS(K28)&gt;=1E12,K28/1E12,IF(ABS(K28)&gt;=1E9,K28/1E9,IF(ABS(K28)&gt;=1E6,K28/1E6,IF(ABS(K28)&gt;=1E3,K28/1E3,K28))))</f>
-        <v>11.010048</v>
-      </c>
-      <c r="C28" s="11" t="str">
-        <f>IF(ABS(K28)&gt;=1E12,"TB",IF(ABS(K28)&gt;=1E9,"GB",IF(ABS(K28)&gt;=1E6,"MB",IF(ABS(K28)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="D28" s="12">
-        <f>IF(ABS(L28)&gt;=1E12,L28/1E12,IF(ABS(L28)&gt;=1E9,L28/1E9,IF(ABS(L28)&gt;=1E6,L28/1E6,IF(ABS(L28)&gt;=1E3,L28/1E3,L28))))</f>
-        <v>11.010048</v>
-      </c>
-      <c r="E28" s="11" t="str">
-        <f>IF(ABS(L28)&gt;=1E12,"TB",IF(ABS(L28)&gt;=1E9,"GB",IF(ABS(L28)&gt;=1E6,"MB",IF(ABS(L28)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="F28" s="12">
-        <f>IF(ABS(M28)&gt;=1E12,M28/1E12,IF(ABS(M28)&gt;=1E9,M28/1E9,IF(ABS(M28)&gt;=1E6,M28/1E6,IF(ABS(M28)&gt;=1E3,M28/1E3,M28))))</f>
-        <v>1.409286144</v>
-      </c>
-      <c r="G28" s="11" t="str">
-        <f>IF(ABS(M28)&gt;=1E12,"TB",IF(ABS(M28)&gt;=1E9,"GB",IF(ABS(M28)&gt;=1E6,"MB",IF(ABS(M28)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H28" s="12">
-        <f>IF(ABS(N28)&gt;=1E12,N28/1E12,IF(ABS(N28)&gt;=1E9,N28/1E9,IF(ABS(N28)&gt;=1E6,N28/1E6,IF(ABS(N28)&gt;=1E3,N28/1E3,N28))))</f>
-        <v>1.409286144</v>
-      </c>
-      <c r="I28" s="11" t="str">
-        <f>IF(ABS(N28)&gt;=1E12,"TB",IF(ABS(N28)&gt;=1E9,"GB",IF(ABS(N28)&gt;=1E6,"MB",IF(ABS(N28)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="K28" s="13">
-        <f>'Memory'!$P$27</f>
-        <v>11010048</v>
-      </c>
-      <c r="L28" s="13">
-        <f>'Memory'!$Q$27</f>
-        <v>11010048</v>
-      </c>
-      <c r="M28" s="13">
-        <f>'Memory'!$P$31</f>
-        <v>1409286144</v>
-      </c>
-      <c r="N28" s="13">
-        <f>'Memory'!$Q$31</f>
-        <v>1409286144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="B29" s="12">
-        <f>IF(ABS(K29)&gt;=1E12,K29/1E12,IF(ABS(K29)&gt;=1E9,K29/1E9,IF(ABS(K29)&gt;=1E6,K29/1E6,IF(ABS(K29)&gt;=1E3,K29/1E3,K29))))</f>
-        <v>12.20608</v>
-      </c>
-      <c r="C29" s="11" t="str">
-        <f>IF(ABS(K29)&gt;=1E12,"TB",IF(ABS(K29)&gt;=1E9,"GB",IF(ABS(K29)&gt;=1E6,"MB",IF(ABS(K29)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="D29" s="12">
-        <f>IF(ABS(L29)&gt;=1E12,L29/1E12,IF(ABS(L29)&gt;=1E9,L29/1E9,IF(ABS(L29)&gt;=1E6,L29/1E6,IF(ABS(L29)&gt;=1E3,L29/1E3,L29))))</f>
-        <v>12.20608</v>
-      </c>
-      <c r="E29" s="11" t="str">
-        <f>IF(ABS(L29)&gt;=1E12,"TB",IF(ABS(L29)&gt;=1E9,"GB",IF(ABS(L29)&gt;=1E6,"MB",IF(ABS(L29)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="F29" s="12">
-        <f>IF(ABS(M29)&gt;=1E12,M29/1E12,IF(ABS(M29)&gt;=1E9,M29/1E9,IF(ABS(M29)&gt;=1E6,M29/1E6,IF(ABS(M29)&gt;=1E3,M29/1E3,M29))))</f>
-        <v>12.20608</v>
-      </c>
-      <c r="G29" s="11" t="str">
-        <f>IF(ABS(M29)&gt;=1E12,"TB",IF(ABS(M29)&gt;=1E9,"GB",IF(ABS(M29)&gt;=1E6,"MB",IF(ABS(M29)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="H29" s="12">
-        <f>IF(ABS(N29)&gt;=1E12,N29/1E12,IF(ABS(N29)&gt;=1E9,N29/1E9,IF(ABS(N29)&gt;=1E6,N29/1E6,IF(ABS(N29)&gt;=1E3,N29/1E3,N29))))</f>
-        <v>12.20608</v>
-      </c>
-      <c r="I29" s="11" t="str">
-        <f>IF(ABS(N29)&gt;=1E12,"TB",IF(ABS(N29)&gt;=1E9,"GB",IF(ABS(N29)&gt;=1E6,"MB",IF(ABS(N29)&gt;=1E3,"KB","bytes"))))</f>
-        <v>MB</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="K29" s="13">
-        <f>'Memory'!$P$28</f>
-        <v>12206080</v>
-      </c>
-      <c r="L29" s="13">
-        <f>'Memory'!$Q$28</f>
-        <v>12206080</v>
-      </c>
-      <c r="M29" s="13">
-        <f>'Memory'!$P$32</f>
-        <v>12206080</v>
-      </c>
-      <c r="N29" s="13">
-        <f>'Memory'!$Q$32</f>
-        <v>12206080</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="B30" s="12">
-        <f>IF(ABS(K30)&gt;=1E12,K30/1E12,IF(ABS(K30)&gt;=1E9,K30/1E9,IF(ABS(K30)&gt;=1E6,K30/1E6,IF(ABS(K30)&gt;=1E3,K30/1E3,K30))))</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="C30" s="11" t="str">
-        <f>IF(ABS(K30)&gt;=1E12,"TB",IF(ABS(K30)&gt;=1E9,"GB",IF(ABS(K30)&gt;=1E6,"MB",IF(ABS(K30)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D30" s="12">
-        <f>IF(ABS(L30)&gt;=1E12,L30/1E12,IF(ABS(L30)&gt;=1E9,L30/1E9,IF(ABS(L30)&gt;=1E6,L30/1E6,IF(ABS(L30)&gt;=1E3,L30/1E3,L30))))</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="E30" s="11" t="str">
-        <f>IF(ABS(L30)&gt;=1E12,"TB",IF(ABS(L30)&gt;=1E9,"GB",IF(ABS(L30)&gt;=1E6,"MB",IF(ABS(L30)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F30" s="12">
-        <f>IF(ABS(M30)&gt;=1E12,M30/1E12,IF(ABS(M30)&gt;=1E9,M30/1E9,IF(ABS(M30)&gt;=1E6,M30/1E6,IF(ABS(M30)&gt;=1E3,M30/1E3,M30))))</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="G30" s="11" t="str">
-        <f>IF(ABS(M30)&gt;=1E12,"TB",IF(ABS(M30)&gt;=1E9,"GB",IF(ABS(M30)&gt;=1E6,"MB",IF(ABS(M30)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H30" s="12">
-        <f>IF(ABS(N30)&gt;=1E12,N30/1E12,IF(ABS(N30)&gt;=1E9,N30/1E9,IF(ABS(N30)&gt;=1E6,N30/1E6,IF(ABS(N30)&gt;=1E3,N30/1E3,N30))))</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="I30" s="11" t="str">
-        <f>IF(ABS(N30)&gt;=1E12,"TB",IF(ABS(N30)&gt;=1E9,"GB",IF(ABS(N30)&gt;=1E6,"MB",IF(ABS(N30)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="K30" s="13">
-        <f>'Memory'!$P$29</f>
-        <v>7232045056</v>
-      </c>
-      <c r="L30" s="13">
-        <f>'Memory'!$Q$29</f>
-        <v>7232045056</v>
-      </c>
-      <c r="M30" s="13">
-        <f>'Memory'!$P$33</f>
-        <v>7232045056</v>
-      </c>
-      <c r="N30" s="13">
-        <f>'Memory'!$Q$33</f>
-        <v>7232045056</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="B31" s="14">
-        <f>IF(ABS(K31)&gt;=1E12,K31/1E12,IF(ABS(K31)&gt;=1E9,K31/1E9,IF(ABS(K31)&gt;=1E6,K31/1E6,IF(ABS(K31)&gt;=1E3,K31/1E3,K31))))</f>
-        <v>166.349315548</v>
-      </c>
-      <c r="C31" s="11" t="str">
-        <f>IF(ABS(K31)&gt;=1E12,"TB",IF(ABS(K31)&gt;=1E9,"GB",IF(ABS(K31)&gt;=1E6,"MB",IF(ABS(K31)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="D31" s="14">
-        <f>IF(ABS(L31)&gt;=1E12,L31/1E12,IF(ABS(L31)&gt;=1E9,L31/1E9,IF(ABS(L31)&gt;=1E6,L31/1E6,IF(ABS(L31)&gt;=1E3,L31/1E3,L31))))</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="E31" s="11" t="str">
-        <f>IF(ABS(L31)&gt;=1E12,"TB",IF(ABS(L31)&gt;=1E9,"GB",IF(ABS(L31)&gt;=1E6,"MB",IF(ABS(L31)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="F31" s="14">
-        <f>IF(ABS(M31)&gt;=1E12,M31/1E12,IF(ABS(M31)&gt;=1E9,M31/1E9,IF(ABS(M31)&gt;=1E6,M31/1E6,IF(ABS(M31)&gt;=1E3,M31/1E3,M31))))</f>
-        <v>166.349315548</v>
-      </c>
-      <c r="G31" s="11" t="str">
-        <f>IF(ABS(M31)&gt;=1E12,"TB",IF(ABS(M31)&gt;=1E9,"GB",IF(ABS(M31)&gt;=1E6,"MB",IF(ABS(M31)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="H31" s="14">
-        <f>IF(ABS(N31)&gt;=1E12,N31/1E12,IF(ABS(N31)&gt;=1E9,N31/1E9,IF(ABS(N31)&gt;=1E6,N31/1E6,IF(ABS(N31)&gt;=1E3,N31/1E3,N31))))</f>
-        <v>29.581867388</v>
-      </c>
-      <c r="I31" s="11" t="str">
-        <f>IF(ABS(N31)&gt;=1E12,"TB",IF(ABS(N31)&gt;=1E9,"GB",IF(ABS(N31)&gt;=1E6,"MB",IF(ABS(N31)&gt;=1E3,"KB","bytes"))))</f>
-        <v>GB</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="K31" s="13">
-        <f>'Memory'!$R$21+'Memory'!$P$29</f>
-        <v>166349315548.0</v>
-      </c>
-      <c r="L31" s="13">
-        <f>'Memory'!$S$21+'Memory'!$Q$29</f>
-        <v>29581867388.0</v>
-      </c>
-      <c r="M31" s="13">
-        <f>'Memory'!$R$21+'Memory'!$P$33</f>
-        <v>166349315548.0</v>
-      </c>
-      <c r="N31" s="13">
-        <f>'Memory'!$S$21+'Memory'!$Q$33</f>
-        <v>29581867388.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -19014,12 +12428,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>554</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>555</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -19027,16 +12441,16 @@
         <v>404</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>556</v>
+        <v>509</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>557</v>
+        <v>510</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>558</v>
+        <v>511</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>559</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -19107,16 +12521,16 @@
         <v>404</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>560</v>
+        <v>513</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>561</v>
+        <v>514</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>562</v>
+        <v>515</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>563</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -19187,10 +12601,10 @@
         <v>404</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>565</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -19234,18 +12648,18 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>566</v>
+        <v>519</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>569</v>
+        <v>522</v>
       </c>
       <c r="B23" s="13">
         <f>'Memory'!$R$21/1E9</f>
@@ -19258,7 +12672,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="B24" s="13">
         <f>'Memory'!$P$33/1E9</f>
@@ -19275,7 +12689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19286,47 +12700,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>573</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>574</v>
+        <v>527</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>575</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>576</v>
+        <v>529</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>577</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>578</v>
+        <v>531</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>579</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>580</v>
+        <v>533</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>581</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -19334,55 +12748,55 @@
         <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>582</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>583</v>
+        <v>536</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>584</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>585</v>
+        <v>538</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>586</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>587</v>
+        <v>540</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>588</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>589</v>
+        <v>542</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>590</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>591</v>
+        <v>544</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>592</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>593</v>
+        <v>546</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>594</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -19390,18 +12804,1816 @@
         <v>460</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>595</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>596</v>
+        <v>549</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>597</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="62.7109375" customWidth="1"/>
+    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" s="12">
+        <f>IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6))))</f>
+        <v>102.836037746688</v>
+      </c>
+      <c r="C6" s="11" t="str">
+        <f>IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D6" s="12">
+        <f>IF(ABS(H6)&gt;=1E15,H6/1E15,IF(ABS(H6)&gt;=1E12,H6/1E12,IF(ABS(H6)&gt;=1E9,H6/1E9,IF(ABS(H6)&gt;=1E6,H6/1E6,H6))))</f>
+        <v>123.969470464</v>
+      </c>
+      <c r="E6" s="11" t="str">
+        <f>IF(ABS(H6)&gt;=1E15,"PFLOPs",IF(ABS(H6)&gt;=1E12,"TFLOPs",IF(ABS(H6)&gt;=1E9,"GFLOPs",IF(ABS(H6)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G6" s="13">
+        <f>'Prefill_8K'!$AE$13</f>
+        <v>102836037746688.0</v>
+      </c>
+      <c r="H6" s="13">
+        <f>'Decode_1M'!$AE$13</f>
+        <v>123969470464.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B7" s="12">
+        <f>IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7))))</f>
+        <v>124.846109360128</v>
+      </c>
+      <c r="C7" s="11" t="str">
+        <f>IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D7" s="12">
+        <f>IF(ABS(H7)&gt;=1E15,H7/1E15,IF(ABS(H7)&gt;=1E12,H7/1E12,IF(ABS(H7)&gt;=1E9,H7/1E9,IF(ABS(H7)&gt;=1E6,H7/1E6,H7))))</f>
+        <v>15.240003584</v>
+      </c>
+      <c r="E7" s="11" t="str">
+        <f>IF(ABS(H7)&gt;=1E15,"PFLOPs",IF(ABS(H7)&gt;=1E12,"TFLOPs",IF(ABS(H7)&gt;=1E9,"GFLOPs",IF(ABS(H7)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G7" s="13">
+        <f>'Prefill_8K'!$AE$14</f>
+        <v>124846109360128.0</v>
+      </c>
+      <c r="H7" s="13">
+        <f>'Decode_1M'!$AE$14</f>
+        <v>15240003584.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B8" s="12">
+        <f>IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8))))</f>
+        <v>702.280286208</v>
+      </c>
+      <c r="C8" s="11" t="str">
+        <f>IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="D8" s="12">
+        <f>IF(ABS(H8)&gt;=1E15,H8/1E15,IF(ABS(H8)&gt;=1E12,H8/1E12,IF(ABS(H8)&gt;=1E9,H8/1E9,IF(ABS(H8)&gt;=1E6,H8/1E6,H8))))</f>
+        <v>1.144660054</v>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f>IF(ABS(H8)&gt;=1E15,"PFLOPs",IF(ABS(H8)&gt;=1E12,"TFLOPs",IF(ABS(H8)&gt;=1E9,"GFLOPs",IF(ABS(H8)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G8" s="13">
+        <f>'Prefill_8K'!$AE$15</f>
+        <v>702280286208.0</v>
+      </c>
+      <c r="H8" s="13">
+        <f>'Decode_1M'!$AE$15</f>
+        <v>1144660054.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="B9" s="14">
+        <f>IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9))))</f>
+        <v>228.384427393024</v>
+      </c>
+      <c r="C9" s="11" t="str">
+        <f>IF(ABS(G9)&gt;=1E15,"PFLOPs",IF(ABS(G9)&gt;=1E12,"TFLOPs",IF(ABS(G9)&gt;=1E9,"GFLOPs",IF(ABS(G9)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D9" s="14">
+        <f>IF(ABS(H9)&gt;=1E15,H9/1E15,IF(ABS(H9)&gt;=1E12,H9/1E12,IF(ABS(H9)&gt;=1E9,H9/1E9,IF(ABS(H9)&gt;=1E6,H9/1E6,H9))))</f>
+        <v>140.354134102</v>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f>IF(ABS(H9)&gt;=1E15,"PFLOPs",IF(ABS(H9)&gt;=1E12,"TFLOPs",IF(ABS(H9)&gt;=1E9,"GFLOPs",IF(ABS(H9)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G9" s="13">
+        <f>'Prefill_8K'!$AE$16</f>
+        <v>228384427393024.0</v>
+      </c>
+      <c r="H9" s="13">
+        <f>'Decode_1M'!$AE$16</f>
+        <v>140354134102.0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B10" s="12">
+        <f>IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10))))</f>
+        <v>358.0378144</v>
+      </c>
+      <c r="C10" s="11" t="str">
+        <f>IF(ABS(G10)&gt;=1E12,"TB",IF(ABS(G10)&gt;=1E9,"GB",IF(ABS(G10)&gt;=1E6,"MB",IF(ABS(G10)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D10" s="12">
+        <f>IF(ABS(H10)&gt;=1E12,H10/1E12,IF(ABS(H10)&gt;=1E9,H10/1E9,IF(ABS(H10)&gt;=1E6,H10/1E6,IF(ABS(H10)&gt;=1E3,H10/1E3,H10))))</f>
+        <v>10.492228352</v>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f>IF(ABS(H10)&gt;=1E12,"TB",IF(ABS(H10)&gt;=1E9,"GB",IF(ABS(H10)&gt;=1E6,"MB",IF(ABS(H10)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G10" s="13">
+        <f>'Prefill_8K'!$AE$17</f>
+        <v>358037814400.0</v>
+      </c>
+      <c r="H10" s="13">
+        <f>'Decode_1M'!$AE$17</f>
+        <v>10492228352.0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B11" s="12">
+        <f>IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11))))</f>
+        <v>191.988670976</v>
+      </c>
+      <c r="C11" s="11" t="str">
+        <f>IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D11" s="12">
+        <f>IF(ABS(H11)&gt;=1E12,H11/1E12,IF(ABS(H11)&gt;=1E9,H11/1E9,IF(ABS(H11)&gt;=1E6,H11/1E6,IF(ABS(H11)&gt;=1E3,H11/1E3,H11))))</f>
+        <v>4.627033672</v>
+      </c>
+      <c r="E11" s="11" t="str">
+        <f>IF(ABS(H11)&gt;=1E12,"TB",IF(ABS(H11)&gt;=1E9,"GB",IF(ABS(H11)&gt;=1E6,"MB",IF(ABS(H11)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G11" s="13">
+        <f>'Prefill_8K'!$AE$18</f>
+        <v>191988670976.0</v>
+      </c>
+      <c r="H11" s="13">
+        <f>'Decode_1M'!$AE$18</f>
+        <v>4627033672.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B12" s="12">
+        <f>IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12))))</f>
+        <v>94.59572948</v>
+      </c>
+      <c r="C12" s="11" t="str">
+        <f>IF(ABS(G12)&gt;=1E12,"TB",IF(ABS(G12)&gt;=1E9,"GB",IF(ABS(G12)&gt;=1E6,"MB",IF(ABS(G12)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D12" s="12">
+        <f>IF(ABS(H12)&gt;=1E12,H12/1E12,IF(ABS(H12)&gt;=1E9,H12/1E9,IF(ABS(H12)&gt;=1E6,H12/1E6,IF(ABS(H12)&gt;=1E3,H12/1E3,H12))))</f>
+        <v>2.265204808</v>
+      </c>
+      <c r="E12" s="11" t="str">
+        <f>IF(ABS(H12)&gt;=1E12,"TB",IF(ABS(H12)&gt;=1E9,"GB",IF(ABS(H12)&gt;=1E6,"MB",IF(ABS(H12)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G12" s="13">
+        <f>'Prefill_8K'!$AE$19</f>
+        <v>94595729480.0</v>
+      </c>
+      <c r="H12" s="13">
+        <f>'Decode_1M'!$AE$19</f>
+        <v>2265204808.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="B13" s="14">
+        <f>IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13))))</f>
+        <v>644.622214856</v>
+      </c>
+      <c r="C13" s="11" t="str">
+        <f>IF(ABS(G13)&gt;=1E12,"TB",IF(ABS(G13)&gt;=1E9,"GB",IF(ABS(G13)&gt;=1E6,"MB",IF(ABS(G13)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D13" s="14">
+        <f>IF(ABS(H13)&gt;=1E12,H13/1E12,IF(ABS(H13)&gt;=1E9,H13/1E9,IF(ABS(H13)&gt;=1E6,H13/1E6,IF(ABS(H13)&gt;=1E3,H13/1E3,H13))))</f>
+        <v>17.384466832</v>
+      </c>
+      <c r="E13" s="11" t="str">
+        <f>IF(ABS(H13)&gt;=1E12,"TB",IF(ABS(H13)&gt;=1E9,"GB",IF(ABS(H13)&gt;=1E6,"MB",IF(ABS(H13)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G13" s="13">
+        <f>'Prefill_8K'!$AE$20</f>
+        <v>644622214856.0</v>
+      </c>
+      <c r="H13" s="13">
+        <f>'Decode_1M'!$AE$20</f>
+        <v>17384466832.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B14" s="12">
+        <f>G14</f>
+        <v>358.0378144</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="12">
+        <f>H14</f>
+        <v>1049.2228352</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G14" s="13">
+        <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
+        <v>358.0378144</v>
+      </c>
+      <c r="H14" s="13">
+        <f>'Decode_1M'!$AE$17/(DecodeTargetMs/1000)/1E9</f>
+        <v>1049.2228352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B15" s="12">
+        <f>G15</f>
+        <v>191.988670976</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="12">
+        <f>H15</f>
+        <v>462.7033672</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G15" s="13">
+        <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
+        <v>191.988670976</v>
+      </c>
+      <c r="H15" s="13">
+        <f>'Decode_1M'!$AE$18/(DecodeTargetMs/1000)/1E9</f>
+        <v>462.7033672</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B16" s="12">
+        <f>G16</f>
+        <v>94.59572948</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="12">
+        <f>H16</f>
+        <v>226.5204808</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G16" s="13">
+        <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
+        <v>94.59572948</v>
+      </c>
+      <c r="H16" s="13">
+        <f>'Decode_1M'!$AE$19/(DecodeTargetMs/1000)/1E9</f>
+        <v>226.5204808</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B17" s="12">
+        <f>G17</f>
+        <v>228.384427393024</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="12">
+        <f>H17</f>
+        <v>14.0354134102</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="G17" s="13">
+        <f>'Prefill_8K'!$AE$23</f>
+        <v>228.384427393024</v>
+      </c>
+      <c r="H17" s="13">
+        <f>'Decode_1M'!$AE$23</f>
+        <v>14.0354134102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B18" s="12">
+        <f>IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18))))</f>
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <f>IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes"))))</f>
+        <v>B</v>
+      </c>
+      <c r="D18" s="12">
+        <f>IF(ABS(H18)&gt;=1E12,H18/1E12,IF(ABS(H18)&gt;=1E9,H18/1E9,IF(ABS(H18)&gt;=1E6,H18/1E6,IF(ABS(H18)&gt;=1E3,H18/1E3,H18))))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="11" t="str">
+        <f>IF(ABS(H18)&gt;=1E12,"TB",IF(ABS(H18)&gt;=1E9,"GB",IF(ABS(H18)&gt;=1E6,"MB",IF(ABS(H18)&gt;=1E3,"KB","bytes"))))</f>
+        <v>B</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G18" s="13">
+        <f>'Prefill_8K'!$AE$21</f>
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="13">
+        <f>'Decode_1M'!$AE$21</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B19" s="12">
+        <f>G19</f>
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="12">
+        <f>H19</f>
+        <v>0.0</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G19" s="13">
+        <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="13">
+        <f>'Decode_1M'!$AE$21/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B20" s="12">
+        <f>IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20))))</f>
+        <v>5.086249088</v>
+      </c>
+      <c r="C20" s="11" t="str">
+        <f>IF(ABS(G20)&gt;=1E12,"T params",IF(ABS(G20)&gt;=1E9,"G params",IF(ABS(G20)&gt;=1E6,"M params",IF(ABS(G20)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D20" s="12">
+        <f>IF(ABS(H20)&gt;=1E12,H20/1E12,IF(ABS(H20)&gt;=1E9,H20/1E9,IF(ABS(H20)&gt;=1E6,H20/1E6,IF(ABS(H20)&gt;=1E3,H20/1E3,H20))))</f>
+        <v>5.086249088</v>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f>IF(ABS(H20)&gt;=1E12,"T params",IF(ABS(H20)&gt;=1E9,"G params",IF(ABS(H20)&gt;=1E6,"M params",IF(ABS(H20)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G20" s="13">
+        <f>'Memory'!$P$18</f>
+        <v>5086249088.0</v>
+      </c>
+      <c r="H20" s="13">
+        <f>'Memory'!$P$18</f>
+        <v>5086249088.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B21" s="12">
+        <f>IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21))))</f>
+        <v>278.154947072</v>
+      </c>
+      <c r="C21" s="11" t="str">
+        <f>IF(ABS(G21)&gt;=1E12,"T params",IF(ABS(G21)&gt;=1E9,"G params",IF(ABS(G21)&gt;=1E6,"M params",IF(ABS(G21)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D21" s="12">
+        <f>IF(ABS(H21)&gt;=1E12,H21/1E12,IF(ABS(H21)&gt;=1E9,H21/1E9,IF(ABS(H21)&gt;=1E6,H21/1E6,IF(ABS(H21)&gt;=1E3,H21/1E3,H21))))</f>
+        <v>278.154947072</v>
+      </c>
+      <c r="E21" s="11" t="str">
+        <f>IF(ABS(H21)&gt;=1E12,"T params",IF(ABS(H21)&gt;=1E9,"G params",IF(ABS(H21)&gt;=1E6,"M params",IF(ABS(H21)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G21" s="13">
+        <f>'Memory'!$P$19</f>
+        <v>278154947072.0</v>
+      </c>
+      <c r="H21" s="13">
+        <f>'Memory'!$P$19</f>
+        <v>278154947072.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B22" s="12">
+        <f>IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22))))</f>
+        <v>1.093371351</v>
+      </c>
+      <c r="C22" s="11" t="str">
+        <f>IF(ABS(G22)&gt;=1E12,"T params",IF(ABS(G22)&gt;=1E9,"G params",IF(ABS(G22)&gt;=1E6,"M params",IF(ABS(G22)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D22" s="12">
+        <f>IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22))))</f>
+        <v>1.093371351</v>
+      </c>
+      <c r="E22" s="11" t="str">
+        <f>IF(ABS(H22)&gt;=1E12,"T params",IF(ABS(H22)&gt;=1E9,"G params",IF(ABS(H22)&gt;=1E6,"M params",IF(ABS(H22)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G22" s="13">
+        <f>'Memory'!$P$20</f>
+        <v>1093371351.0</v>
+      </c>
+      <c r="H22" s="13">
+        <f>'Memory'!$P$20</f>
+        <v>1093371351.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="B23" s="14">
+        <f>IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23))))</f>
+        <v>284.334567511</v>
+      </c>
+      <c r="C23" s="11" t="str">
+        <f>IF(ABS(G23)&gt;=1E12,"T params",IF(ABS(G23)&gt;=1E9,"G params",IF(ABS(G23)&gt;=1E6,"M params",IF(ABS(G23)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D23" s="14">
+        <f>IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,IF(ABS(H23)&gt;=1E3,H23/1E3,H23))))</f>
+        <v>284.334567511</v>
+      </c>
+      <c r="E23" s="11" t="str">
+        <f>IF(ABS(H23)&gt;=1E12,"T params",IF(ABS(H23)&gt;=1E9,"G params",IF(ABS(H23)&gt;=1E6,"M params",IF(ABS(H23)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="G23" s="13">
+        <f>'Memory'!$P$21</f>
+        <v>284334567511.0</v>
+      </c>
+      <c r="H23" s="13">
+        <f>'Memory'!$P$21</f>
+        <v>284334567511.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B24" s="12">
+        <f>IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24))))</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="C24" s="11" t="str">
+        <f>IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D24" s="12">
+        <f>IF(ABS(H24)&gt;=1E12,H24/1E12,IF(ABS(H24)&gt;=1E9,H24/1E9,IF(ABS(H24)&gt;=1E6,H24/1E6,IF(ABS(H24)&gt;=1E3,H24/1E3,H24))))</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="E24" s="11" t="str">
+        <f>IF(ABS(H24)&gt;=1E12,"TB",IF(ABS(H24)&gt;=1E9,"GB",IF(ABS(H24)&gt;=1E6,"MB",IF(ABS(H24)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G24" s="13">
+        <f>'Memory'!$R$18</f>
+        <v>7451384960</v>
+      </c>
+      <c r="H24" s="13">
+        <f>'Memory'!$R$18</f>
+        <v>7451384960</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B25" s="12">
+        <f>IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25))))</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="C25" s="11" t="str">
+        <f>IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D25" s="12">
+        <f>IF(ABS(H25)&gt;=1E12,H25/1E12,IF(ABS(H25)&gt;=1E9,H25/1E9,IF(ABS(H25)&gt;=1E6,H25/1E6,IF(ABS(H25)&gt;=1E3,H25/1E3,H25))))</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f>IF(ABS(H25)&gt;=1E12,"TB",IF(ABS(H25)&gt;=1E9,"GB",IF(ABS(H25)&gt;=1E6,"MB",IF(ABS(H25)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="G25" s="13">
+        <f>'Memory'!$R$19</f>
+        <v>148351461888.0</v>
+      </c>
+      <c r="H25" s="13">
+        <f>'Memory'!$R$19</f>
+        <v>148351461888.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B26" s="12">
+        <f>IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26))))</f>
+        <v>3.314423644</v>
+      </c>
+      <c r="C26" s="11" t="str">
+        <f>IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D26" s="12">
+        <f>IF(ABS(H26)&gt;=1E12,H26/1E12,IF(ABS(H26)&gt;=1E9,H26/1E9,IF(ABS(H26)&gt;=1E6,H26/1E6,IF(ABS(H26)&gt;=1E3,H26/1E3,H26))))</f>
+        <v>3.314423644</v>
+      </c>
+      <c r="E26" s="11" t="str">
+        <f>IF(ABS(H26)&gt;=1E12,"TB",IF(ABS(H26)&gt;=1E9,"GB",IF(ABS(H26)&gt;=1E6,"MB",IF(ABS(H26)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G26" s="13">
+        <f>'Memory'!$R$20</f>
+        <v>3314423644.0</v>
+      </c>
+      <c r="H26" s="13">
+        <f>'Memory'!$R$20</f>
+        <v>3314423644.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="B27" s="14">
+        <f>IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27))))</f>
+        <v>159.117270492</v>
+      </c>
+      <c r="C27" s="11" t="str">
+        <f>IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D27" s="14">
+        <f>IF(ABS(H27)&gt;=1E12,H27/1E12,IF(ABS(H27)&gt;=1E9,H27/1E9,IF(ABS(H27)&gt;=1E6,H27/1E6,IF(ABS(H27)&gt;=1E3,H27/1E3,H27))))</f>
+        <v>159.117270492</v>
+      </c>
+      <c r="E27" s="11" t="str">
+        <f>IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="G27" s="13">
+        <f>'Memory'!$R$21</f>
+        <v>159117270492.0</v>
+      </c>
+      <c r="H27" s="13">
+        <f>'Memory'!$R$21</f>
+        <v>159117270492.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B28" s="12">
+        <f>IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28))))</f>
+        <v>50.987008</v>
+      </c>
+      <c r="C28" s="11" t="str">
+        <f>IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D28" s="12">
+        <f>IF(ABS(H28)&gt;=1E12,H28/1E12,IF(ABS(H28)&gt;=1E9,H28/1E9,IF(ABS(H28)&gt;=1E6,H28/1E6,IF(ABS(H28)&gt;=1E3,H28/1E3,H28))))</f>
+        <v>5.810552832</v>
+      </c>
+      <c r="E28" s="11" t="str">
+        <f>IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G28" s="13">
+        <f>'Memory'!$P$26</f>
+        <v>50987008</v>
+      </c>
+      <c r="H28" s="13">
+        <f>'Memory'!$P$30</f>
+        <v>5810552832</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B29" s="12">
+        <f>IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29))))</f>
+        <v>11.010048</v>
+      </c>
+      <c r="C29" s="11" t="str">
+        <f>IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D29" s="12">
+        <f>IF(ABS(H29)&gt;=1E12,H29/1E12,IF(ABS(H29)&gt;=1E9,H29/1E9,IF(ABS(H29)&gt;=1E6,H29/1E6,IF(ABS(H29)&gt;=1E3,H29/1E3,H29))))</f>
+        <v>1.409286144</v>
+      </c>
+      <c r="E29" s="11" t="str">
+        <f>IF(ABS(H29)&gt;=1E12,"TB",IF(ABS(H29)&gt;=1E9,"GB",IF(ABS(H29)&gt;=1E6,"MB",IF(ABS(H29)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G29" s="13">
+        <f>'Memory'!$P$27</f>
+        <v>11010048</v>
+      </c>
+      <c r="H29" s="13">
+        <f>'Memory'!$P$31</f>
+        <v>1409286144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B30" s="12">
+        <f>IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30))))</f>
+        <v>12.20608</v>
+      </c>
+      <c r="C30" s="11" t="str">
+        <f>IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D30" s="12">
+        <f>IF(ABS(H30)&gt;=1E12,H30/1E12,IF(ABS(H30)&gt;=1E9,H30/1E9,IF(ABS(H30)&gt;=1E6,H30/1E6,IF(ABS(H30)&gt;=1E3,H30/1E3,H30))))</f>
+        <v>12.20608</v>
+      </c>
+      <c r="E30" s="11" t="str">
+        <f>IF(ABS(H30)&gt;=1E12,"TB",IF(ABS(H30)&gt;=1E9,"GB",IF(ABS(H30)&gt;=1E6,"MB",IF(ABS(H30)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G30" s="13">
+        <f>'Memory'!$P$28</f>
+        <v>12206080</v>
+      </c>
+      <c r="H30" s="13">
+        <f>'Memory'!$P$32</f>
+        <v>12206080</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B31" s="12">
+        <f>IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31))))</f>
+        <v>7.232045056</v>
+      </c>
+      <c r="C31" s="11" t="str">
+        <f>IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D31" s="12">
+        <f>IF(ABS(H31)&gt;=1E12,H31/1E12,IF(ABS(H31)&gt;=1E9,H31/1E9,IF(ABS(H31)&gt;=1E6,H31/1E6,IF(ABS(H31)&gt;=1E3,H31/1E3,H31))))</f>
+        <v>7.232045056</v>
+      </c>
+      <c r="E31" s="11" t="str">
+        <f>IF(ABS(H31)&gt;=1E12,"TB",IF(ABS(H31)&gt;=1E9,"GB",IF(ABS(H31)&gt;=1E6,"MB",IF(ABS(H31)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G31" s="13">
+        <f>'Memory'!$P$29</f>
+        <v>7232045056</v>
+      </c>
+      <c r="H31" s="13">
+        <f>'Memory'!$P$33</f>
+        <v>7232045056</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="B32" s="14">
+        <f>IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32))))</f>
+        <v>166.349315548</v>
+      </c>
+      <c r="C32" s="11" t="str">
+        <f>IF(ABS(G32)&gt;=1E12,"TB",IF(ABS(G32)&gt;=1E9,"GB",IF(ABS(G32)&gt;=1E6,"MB",IF(ABS(G32)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D32" s="14">
+        <f>IF(ABS(H32)&gt;=1E12,H32/1E12,IF(ABS(H32)&gt;=1E9,H32/1E9,IF(ABS(H32)&gt;=1E6,H32/1E6,IF(ABS(H32)&gt;=1E3,H32/1E3,H32))))</f>
+        <v>166.349315548</v>
+      </c>
+      <c r="E32" s="11" t="str">
+        <f>IF(ABS(H32)&gt;=1E12,"TB",IF(ABS(H32)&gt;=1E9,"GB",IF(ABS(H32)&gt;=1E6,"MB",IF(ABS(H32)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G32" s="13">
+        <f>'Memory'!$R$21+'Memory'!$P$29</f>
+        <v>166349315548.0</v>
+      </c>
+      <c r="H32" s="13">
+        <f>'Memory'!$R$21+'Memory'!$P$33</f>
+        <v>166349315548.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B36" s="12">
+        <f>IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36))))</f>
+        <v>23.172382457856</v>
+      </c>
+      <c r="C36" s="11" t="str">
+        <f>IF(ABS(G36)&gt;=1E15,"PFLOPs",IF(ABS(G36)&gt;=1E12,"TFLOPs",IF(ABS(G36)&gt;=1E9,"GFLOPs",IF(ABS(G36)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D36" s="12">
+        <f>IF(ABS(H36)&gt;=1E15,H36/1E15,IF(ABS(H36)&gt;=1E12,H36/1E12,IF(ABS(H36)&gt;=1E9,H36/1E9,IF(ABS(H36)&gt;=1E6,H36/1E6,H36))))</f>
+        <v>19.452461056</v>
+      </c>
+      <c r="E36" s="11" t="str">
+        <f>IF(ABS(H36)&gt;=1E15,"PFLOPs",IF(ABS(H36)&gt;=1E12,"TFLOPs",IF(ABS(H36)&gt;=1E9,"GFLOPs",IF(ABS(H36)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G36" s="13">
+        <f>'Prefill_8K'!$AF$13</f>
+        <v>23172382457856.0</v>
+      </c>
+      <c r="H36" s="13">
+        <f>'Decode_1M'!$AF$13</f>
+        <v>19452461056.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B37" s="12">
+        <f>IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37))))</f>
+        <v>31.765578121216</v>
+      </c>
+      <c r="C37" s="11" t="str">
+        <f>IF(ABS(G37)&gt;=1E15,"PFLOPs",IF(ABS(G37)&gt;=1E12,"TFLOPs",IF(ABS(G37)&gt;=1E9,"GFLOPs",IF(ABS(G37)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D37" s="12">
+        <f>IF(ABS(H37)&gt;=1E15,H37/1E15,IF(ABS(H37)&gt;=1E12,H37/1E12,IF(ABS(H37)&gt;=1E9,H37/1E9,IF(ABS(H37)&gt;=1E6,H37/1E6,H37))))</f>
+        <v>3.877634048</v>
+      </c>
+      <c r="E37" s="11" t="str">
+        <f>IF(ABS(H37)&gt;=1E15,"PFLOPs",IF(ABS(H37)&gt;=1E12,"TFLOPs",IF(ABS(H37)&gt;=1E9,"GFLOPs",IF(ABS(H37)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G37" s="13">
+        <f>'Prefill_8K'!$AF$14</f>
+        <v>31765578121216.0</v>
+      </c>
+      <c r="H37" s="13">
+        <f>'Decode_1M'!$AF$14</f>
+        <v>3877634048.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B38" s="12">
+        <f>IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38))))</f>
+        <v>701.353607168</v>
+      </c>
+      <c r="C38" s="11" t="str">
+        <f>IF(ABS(G38)&gt;=1E15,"PFLOPs",IF(ABS(G38)&gt;=1E12,"TFLOPs",IF(ABS(G38)&gt;=1E9,"GFLOPs",IF(ABS(G38)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="D38" s="12">
+        <f>IF(ABS(H38)&gt;=1E15,H38/1E15,IF(ABS(H38)&gt;=1E12,H38/1E12,IF(ABS(H38)&gt;=1E9,H38/1E9,IF(ABS(H38)&gt;=1E6,H38/1E6,H38))))</f>
+        <v>217.981014</v>
+      </c>
+      <c r="E38" s="11" t="str">
+        <f>IF(ABS(H38)&gt;=1E15,"PFLOPs",IF(ABS(H38)&gt;=1E12,"TFLOPs",IF(ABS(H38)&gt;=1E9,"GFLOPs",IF(ABS(H38)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>MFLOPs</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G38" s="13">
+        <f>'Prefill_8K'!$AF$15</f>
+        <v>701353607168.0</v>
+      </c>
+      <c r="H38" s="13">
+        <f>'Decode_1M'!$AF$15</f>
+        <v>217981014.0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="B39" s="14">
+        <f>IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39))))</f>
+        <v>55.63931418624</v>
+      </c>
+      <c r="C39" s="11" t="str">
+        <f>IF(ABS(G39)&gt;=1E15,"PFLOPs",IF(ABS(G39)&gt;=1E12,"TFLOPs",IF(ABS(G39)&gt;=1E9,"GFLOPs",IF(ABS(G39)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>TFLOPs</v>
+      </c>
+      <c r="D39" s="14">
+        <f>IF(ABS(H39)&gt;=1E15,H39/1E15,IF(ABS(H39)&gt;=1E12,H39/1E12,IF(ABS(H39)&gt;=1E9,H39/1E9,IF(ABS(H39)&gt;=1E6,H39/1E6,H39))))</f>
+        <v>23.548076118</v>
+      </c>
+      <c r="E39" s="11" t="str">
+        <f>IF(ABS(H39)&gt;=1E15,"PFLOPs",IF(ABS(H39)&gt;=1E12,"TFLOPs",IF(ABS(H39)&gt;=1E9,"GFLOPs",IF(ABS(H39)&gt;=1E6,"MFLOPs","flops"))))</f>
+        <v>GFLOPs</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G39" s="13">
+        <f>'Prefill_8K'!$AF$16</f>
+        <v>55639314186240.0</v>
+      </c>
+      <c r="H39" s="13">
+        <f>'Decode_1M'!$AF$16</f>
+        <v>23548076118.0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B40" s="12">
+        <f>IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40))))</f>
+        <v>231.531806144</v>
+      </c>
+      <c r="C40" s="11" t="str">
+        <f>IF(ABS(G40)&gt;=1E12,"TB",IF(ABS(G40)&gt;=1E9,"GB",IF(ABS(G40)&gt;=1E6,"MB",IF(ABS(G40)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D40" s="12">
+        <f>IF(ABS(H40)&gt;=1E12,H40/1E12,IF(ABS(H40)&gt;=1E9,H40/1E9,IF(ABS(H40)&gt;=1E6,H40/1E6,IF(ABS(H40)&gt;=1E3,H40/1E3,H40))))</f>
+        <v>4.035232528</v>
+      </c>
+      <c r="E40" s="11" t="str">
+        <f>IF(ABS(H40)&gt;=1E12,"TB",IF(ABS(H40)&gt;=1E9,"GB",IF(ABS(H40)&gt;=1E6,"MB",IF(ABS(H40)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G40" s="13">
+        <f>'Prefill_8K'!$AF$17</f>
+        <v>231531806144.0</v>
+      </c>
+      <c r="H40" s="13">
+        <f>'Decode_1M'!$AF$17</f>
+        <v>4035232528.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B41" s="12">
+        <f>IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41))))</f>
+        <v>32.915497472</v>
+      </c>
+      <c r="C41" s="11" t="str">
+        <f>IF(ABS(G41)&gt;=1E12,"TB",IF(ABS(G41)&gt;=1E9,"GB",IF(ABS(G41)&gt;=1E6,"MB",IF(ABS(G41)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D41" s="12">
+        <f>IF(ABS(H41)&gt;=1E12,H41/1E12,IF(ABS(H41)&gt;=1E9,H41/1E9,IF(ABS(H41)&gt;=1E6,H41/1E6,IF(ABS(H41)&gt;=1E3,H41/1E3,H41))))</f>
+        <v>1.605205576</v>
+      </c>
+      <c r="E41" s="11" t="str">
+        <f>IF(ABS(H41)&gt;=1E12,"TB",IF(ABS(H41)&gt;=1E9,"GB",IF(ABS(H41)&gt;=1E6,"MB",IF(ABS(H41)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G41" s="13">
+        <f>'Prefill_8K'!$AF$18</f>
+        <v>32915497472.0</v>
+      </c>
+      <c r="H41" s="13">
+        <f>'Decode_1M'!$AF$18</f>
+        <v>1605205576.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B42" s="12">
+        <f>IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42))))</f>
+        <v>92.74191892</v>
+      </c>
+      <c r="C42" s="11" t="str">
+        <f>IF(ABS(G42)&gt;=1E12,"TB",IF(ABS(G42)&gt;=1E9,"GB",IF(ABS(G42)&gt;=1E6,"MB",IF(ABS(G42)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D42" s="12">
+        <f>IF(ABS(H42)&gt;=1E12,H42/1E12,IF(ABS(H42)&gt;=1E9,H42/1E9,IF(ABS(H42)&gt;=1E6,H42/1E6,IF(ABS(H42)&gt;=1E3,H42/1E3,H42))))</f>
+        <v>411.394248</v>
+      </c>
+      <c r="E42" s="11" t="str">
+        <f>IF(ABS(H42)&gt;=1E12,"TB",IF(ABS(H42)&gt;=1E9,"GB",IF(ABS(H42)&gt;=1E6,"MB",IF(ABS(H42)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G42" s="13">
+        <f>'Prefill_8K'!$AF$19</f>
+        <v>92741918920.0</v>
+      </c>
+      <c r="H42" s="13">
+        <f>'Decode_1M'!$AF$19</f>
+        <v>411394248.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="B43" s="14">
+        <f>IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43))))</f>
+        <v>357.189222536</v>
+      </c>
+      <c r="C43" s="11" t="str">
+        <f>IF(ABS(G43)&gt;=1E12,"TB",IF(ABS(G43)&gt;=1E9,"GB",IF(ABS(G43)&gt;=1E6,"MB",IF(ABS(G43)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D43" s="14">
+        <f>IF(ABS(H43)&gt;=1E12,H43/1E12,IF(ABS(H43)&gt;=1E9,H43/1E9,IF(ABS(H43)&gt;=1E6,H43/1E6,IF(ABS(H43)&gt;=1E3,H43/1E3,H43))))</f>
+        <v>6.051832352</v>
+      </c>
+      <c r="E43" s="11" t="str">
+        <f>IF(ABS(H43)&gt;=1E12,"TB",IF(ABS(H43)&gt;=1E9,"GB",IF(ABS(H43)&gt;=1E6,"MB",IF(ABS(H43)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G43" s="13">
+        <f>'Prefill_8K'!$AF$20</f>
+        <v>357189222536.0</v>
+      </c>
+      <c r="H43" s="13">
+        <f>'Decode_1M'!$AF$20</f>
+        <v>6051832352.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B44" s="12">
+        <f>G44</f>
+        <v>231.531806144</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="12">
+        <f>H44</f>
+        <v>403.5232528</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G44" s="13">
+        <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
+        <v>231.531806144</v>
+      </c>
+      <c r="H44" s="13">
+        <f>'Decode_1M'!$AF$17/(DecodeTargetMs/1000)/1E9</f>
+        <v>403.5232528</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B45" s="12">
+        <f>G45</f>
+        <v>32.915497472</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="12">
+        <f>H45</f>
+        <v>160.5205576</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G45" s="13">
+        <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
+        <v>32.915497472</v>
+      </c>
+      <c r="H45" s="13">
+        <f>'Decode_1M'!$AF$18/(DecodeTargetMs/1000)/1E9</f>
+        <v>160.5205576</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B46" s="12">
+        <f>G46</f>
+        <v>92.74191892</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="12">
+        <f>H46</f>
+        <v>41.1394248</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G46" s="13">
+        <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
+        <v>92.74191892</v>
+      </c>
+      <c r="H46" s="13">
+        <f>'Decode_1M'!$AF$19/(DecodeTargetMs/1000)/1E9</f>
+        <v>41.1394248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B47" s="12">
+        <f>G47</f>
+        <v>55.63931418624</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" s="12">
+        <f>H47</f>
+        <v>2.3548076118</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="G47" s="13">
+        <f>'Prefill_8K'!$AF$23</f>
+        <v>55.63931418624</v>
+      </c>
+      <c r="H47" s="13">
+        <f>'Decode_1M'!$AF$23</f>
+        <v>2.3548076118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B48" s="12">
+        <f>IF(ABS(G48)&gt;=1E12,G48/1E12,IF(ABS(G48)&gt;=1E9,G48/1E9,IF(ABS(G48)&gt;=1E6,G48/1E6,IF(ABS(G48)&gt;=1E3,G48/1E3,G48))))</f>
+        <v>40.635322112</v>
+      </c>
+      <c r="C48" s="11" t="str">
+        <f>IF(ABS(G48)&gt;=1E12,"TB",IF(ABS(G48)&gt;=1E9,"GB",IF(ABS(G48)&gt;=1E6,"MB",IF(ABS(G48)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D48" s="12">
+        <f>IF(ABS(H48)&gt;=1E12,H48/1E12,IF(ABS(H48)&gt;=1E9,H48/1E9,IF(ABS(H48)&gt;=1E6,H48/1E6,IF(ABS(H48)&gt;=1E3,H48/1E3,H48))))</f>
+        <v>5.865216</v>
+      </c>
+      <c r="E48" s="11" t="str">
+        <f>IF(ABS(H48)&gt;=1E12,"TB",IF(ABS(H48)&gt;=1E9,"GB",IF(ABS(H48)&gt;=1E6,"MB",IF(ABS(H48)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G48" s="13">
+        <f>'Prefill_8K'!$AF$21</f>
+        <v>40635322112.0</v>
+      </c>
+      <c r="H48" s="13">
+        <f>'Decode_1M'!$AF$21</f>
+        <v>5865216.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B49" s="12">
+        <f>G49</f>
+        <v>40.635322112</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="12">
+        <f>H49</f>
+        <v>0.5865216</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G49" s="13">
+        <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
+        <v>40.635322112</v>
+      </c>
+      <c r="H49" s="13">
+        <f>'Decode_1M'!$AF$21/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.5865216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B50" s="12">
+        <f>IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50))))</f>
+        <v>1.139835008</v>
+      </c>
+      <c r="C50" s="11" t="str">
+        <f>IF(ABS(G50)&gt;=1E12,"T params",IF(ABS(G50)&gt;=1E9,"G params",IF(ABS(G50)&gt;=1E6,"M params",IF(ABS(G50)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D50" s="12">
+        <f>IF(ABS(H50)&gt;=1E12,H50/1E12,IF(ABS(H50)&gt;=1E9,H50/1E9,IF(ABS(H50)&gt;=1E6,H50/1E6,IF(ABS(H50)&gt;=1E3,H50/1E3,H50))))</f>
+        <v>1.139835008</v>
+      </c>
+      <c r="E50" s="11" t="str">
+        <f>IF(ABS(H50)&gt;=1E12,"T params",IF(ABS(H50)&gt;=1E9,"G params",IF(ABS(H50)&gt;=1E6,"M params",IF(ABS(H50)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G50" s="13">
+        <f>'Memory'!$Q$18</f>
+        <v>1139835008.0</v>
+      </c>
+      <c r="H50" s="13">
+        <f>'Memory'!$Q$18</f>
+        <v>1139835008.0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B51" s="12">
+        <f>IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51))))</f>
+        <v>35.757730304</v>
+      </c>
+      <c r="C51" s="11" t="str">
+        <f>IF(ABS(G51)&gt;=1E12,"T params",IF(ABS(G51)&gt;=1E9,"G params",IF(ABS(G51)&gt;=1E6,"M params",IF(ABS(G51)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D51" s="12">
+        <f>IF(ABS(H51)&gt;=1E12,H51/1E12,IF(ABS(H51)&gt;=1E9,H51/1E9,IF(ABS(H51)&gt;=1E6,H51/1E6,IF(ABS(H51)&gt;=1E3,H51/1E3,H51))))</f>
+        <v>35.757730304</v>
+      </c>
+      <c r="E51" s="11" t="str">
+        <f>IF(ABS(H51)&gt;=1E12,"T params",IF(ABS(H51)&gt;=1E9,"G params",IF(ABS(H51)&gt;=1E6,"M params",IF(ABS(H51)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G51" s="13">
+        <f>'Memory'!$Q$19</f>
+        <v>35757730304.0</v>
+      </c>
+      <c r="H51" s="13">
+        <f>'Memory'!$Q$19</f>
+        <v>35757730304.0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B52" s="12">
+        <f>IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52))))</f>
+        <v>166.689903</v>
+      </c>
+      <c r="C52" s="11" t="str">
+        <f>IF(ABS(G52)&gt;=1E12,"T params",IF(ABS(G52)&gt;=1E9,"G params",IF(ABS(G52)&gt;=1E6,"M params",IF(ABS(G52)&gt;=1E3,"K params","params"))))</f>
+        <v>M params</v>
+      </c>
+      <c r="D52" s="12">
+        <f>IF(ABS(H52)&gt;=1E12,H52/1E12,IF(ABS(H52)&gt;=1E9,H52/1E9,IF(ABS(H52)&gt;=1E6,H52/1E6,IF(ABS(H52)&gt;=1E3,H52/1E3,H52))))</f>
+        <v>166.689903</v>
+      </c>
+      <c r="E52" s="11" t="str">
+        <f>IF(ABS(H52)&gt;=1E12,"T params",IF(ABS(H52)&gt;=1E9,"G params",IF(ABS(H52)&gt;=1E6,"M params",IF(ABS(H52)&gt;=1E3,"K params","params"))))</f>
+        <v>M params</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G52" s="13">
+        <f>'Memory'!$Q$20</f>
+        <v>166689903.0</v>
+      </c>
+      <c r="H52" s="13">
+        <f>'Memory'!$Q$20</f>
+        <v>166689903.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="B53" s="14">
+        <f>IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53))))</f>
+        <v>37.064255215</v>
+      </c>
+      <c r="C53" s="11" t="str">
+        <f>IF(ABS(G53)&gt;=1E12,"T params",IF(ABS(G53)&gt;=1E9,"G params",IF(ABS(G53)&gt;=1E6,"M params",IF(ABS(G53)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="D53" s="14">
+        <f>IF(ABS(H53)&gt;=1E12,H53/1E12,IF(ABS(H53)&gt;=1E9,H53/1E9,IF(ABS(H53)&gt;=1E6,H53/1E6,IF(ABS(H53)&gt;=1E3,H53/1E3,H53))))</f>
+        <v>37.064255215</v>
+      </c>
+      <c r="E53" s="11" t="str">
+        <f>IF(ABS(H53)&gt;=1E12,"T params",IF(ABS(H53)&gt;=1E9,"G params",IF(ABS(H53)&gt;=1E6,"M params",IF(ABS(H53)&gt;=1E3,"K params","params"))))</f>
+        <v>G params</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="G53" s="13">
+        <f>'Memory'!$Q$21</f>
+        <v>37064255215.0</v>
+      </c>
+      <c r="H53" s="13">
+        <f>'Memory'!$Q$21</f>
+        <v>37064255215.0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B54" s="12">
+        <f>IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54))))</f>
+        <v>2.23750496</v>
+      </c>
+      <c r="C54" s="11" t="str">
+        <f>IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D54" s="12">
+        <f>IF(ABS(H54)&gt;=1E12,H54/1E12,IF(ABS(H54)&gt;=1E9,H54/1E9,IF(ABS(H54)&gt;=1E6,H54/1E6,IF(ABS(H54)&gt;=1E3,H54/1E3,H54))))</f>
+        <v>2.23750496</v>
+      </c>
+      <c r="E54" s="11" t="str">
+        <f>IF(ABS(H54)&gt;=1E12,"TB",IF(ABS(H54)&gt;=1E9,"GB",IF(ABS(H54)&gt;=1E6,"MB",IF(ABS(H54)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G54" s="13">
+        <f>'Memory'!$S$18</f>
+        <v>2237504960</v>
+      </c>
+      <c r="H54" s="13">
+        <f>'Memory'!$S$18</f>
+        <v>2237504960</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B55" s="12">
+        <f>IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55))))</f>
+        <v>19.57794048</v>
+      </c>
+      <c r="C55" s="11" t="str">
+        <f>IF(ABS(G55)&gt;=1E12,"TB",IF(ABS(G55)&gt;=1E9,"GB",IF(ABS(G55)&gt;=1E6,"MB",IF(ABS(G55)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D55" s="12">
+        <f>IF(ABS(H55)&gt;=1E12,H55/1E12,IF(ABS(H55)&gt;=1E9,H55/1E9,IF(ABS(H55)&gt;=1E6,H55/1E6,IF(ABS(H55)&gt;=1E3,H55/1E3,H55))))</f>
+        <v>19.57794048</v>
+      </c>
+      <c r="E55" s="11" t="str">
+        <f>IF(ABS(H55)&gt;=1E12,"TB",IF(ABS(H55)&gt;=1E9,"GB",IF(ABS(H55)&gt;=1E6,"MB",IF(ABS(H55)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="G55" s="13">
+        <f>'Memory'!$S$19</f>
+        <v>19577940480.0</v>
+      </c>
+      <c r="H55" s="13">
+        <f>'Memory'!$S$19</f>
+        <v>19577940480.0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B56" s="12">
+        <f>IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56))))</f>
+        <v>534.376892</v>
+      </c>
+      <c r="C56" s="11" t="str">
+        <f>IF(ABS(G56)&gt;=1E12,"TB",IF(ABS(G56)&gt;=1E9,"GB",IF(ABS(G56)&gt;=1E6,"MB",IF(ABS(G56)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D56" s="12">
+        <f>IF(ABS(H56)&gt;=1E12,H56/1E12,IF(ABS(H56)&gt;=1E9,H56/1E9,IF(ABS(H56)&gt;=1E6,H56/1E6,IF(ABS(H56)&gt;=1E3,H56/1E3,H56))))</f>
+        <v>534.376892</v>
+      </c>
+      <c r="E56" s="11" t="str">
+        <f>IF(ABS(H56)&gt;=1E12,"TB",IF(ABS(H56)&gt;=1E9,"GB",IF(ABS(H56)&gt;=1E6,"MB",IF(ABS(H56)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G56" s="13">
+        <f>'Memory'!$S$20</f>
+        <v>534376892.0</v>
+      </c>
+      <c r="H56" s="13">
+        <f>'Memory'!$S$20</f>
+        <v>534376892.0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="B57" s="14">
+        <f>IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57))))</f>
+        <v>22.349822332</v>
+      </c>
+      <c r="C57" s="11" t="str">
+        <f>IF(ABS(G57)&gt;=1E12,"TB",IF(ABS(G57)&gt;=1E9,"GB",IF(ABS(G57)&gt;=1E6,"MB",IF(ABS(G57)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D57" s="14">
+        <f>IF(ABS(H57)&gt;=1E12,H57/1E12,IF(ABS(H57)&gt;=1E9,H57/1E9,IF(ABS(H57)&gt;=1E6,H57/1E6,IF(ABS(H57)&gt;=1E3,H57/1E3,H57))))</f>
+        <v>22.349822332</v>
+      </c>
+      <c r="E57" s="11" t="str">
+        <f>IF(ABS(H57)&gt;=1E12,"TB",IF(ABS(H57)&gt;=1E9,"GB",IF(ABS(H57)&gt;=1E6,"MB",IF(ABS(H57)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="G57" s="13">
+        <f>'Memory'!$S$21</f>
+        <v>22349822332.0</v>
+      </c>
+      <c r="H57" s="13">
+        <f>'Memory'!$S$21</f>
+        <v>22349822332.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B58" s="12">
+        <f>IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58))))</f>
+        <v>50.987008</v>
+      </c>
+      <c r="C58" s="11" t="str">
+        <f>IF(ABS(G58)&gt;=1E12,"TB",IF(ABS(G58)&gt;=1E9,"GB",IF(ABS(G58)&gt;=1E6,"MB",IF(ABS(G58)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D58" s="12">
+        <f>IF(ABS(H58)&gt;=1E12,H58/1E12,IF(ABS(H58)&gt;=1E9,H58/1E9,IF(ABS(H58)&gt;=1E6,H58/1E6,IF(ABS(H58)&gt;=1E3,H58/1E3,H58))))</f>
+        <v>5.810552832</v>
+      </c>
+      <c r="E58" s="11" t="str">
+        <f>IF(ABS(H58)&gt;=1E12,"TB",IF(ABS(H58)&gt;=1E9,"GB",IF(ABS(H58)&gt;=1E6,"MB",IF(ABS(H58)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G58" s="13">
+        <f>'Memory'!$Q$26</f>
+        <v>50987008</v>
+      </c>
+      <c r="H58" s="13">
+        <f>'Memory'!$Q$30</f>
+        <v>5810552832</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B59" s="12">
+        <f>IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59))))</f>
+        <v>11.010048</v>
+      </c>
+      <c r="C59" s="11" t="str">
+        <f>IF(ABS(G59)&gt;=1E12,"TB",IF(ABS(G59)&gt;=1E9,"GB",IF(ABS(G59)&gt;=1E6,"MB",IF(ABS(G59)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D59" s="12">
+        <f>IF(ABS(H59)&gt;=1E12,H59/1E12,IF(ABS(H59)&gt;=1E9,H59/1E9,IF(ABS(H59)&gt;=1E6,H59/1E6,IF(ABS(H59)&gt;=1E3,H59/1E3,H59))))</f>
+        <v>1.409286144</v>
+      </c>
+      <c r="E59" s="11" t="str">
+        <f>IF(ABS(H59)&gt;=1E12,"TB",IF(ABS(H59)&gt;=1E9,"GB",IF(ABS(H59)&gt;=1E6,"MB",IF(ABS(H59)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G59" s="13">
+        <f>'Memory'!$Q$27</f>
+        <v>11010048</v>
+      </c>
+      <c r="H59" s="13">
+        <f>'Memory'!$Q$31</f>
+        <v>1409286144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B60" s="12">
+        <f>IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60))))</f>
+        <v>12.20608</v>
+      </c>
+      <c r="C60" s="11" t="str">
+        <f>IF(ABS(G60)&gt;=1E12,"TB",IF(ABS(G60)&gt;=1E9,"GB",IF(ABS(G60)&gt;=1E6,"MB",IF(ABS(G60)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="D60" s="12">
+        <f>IF(ABS(H60)&gt;=1E12,H60/1E12,IF(ABS(H60)&gt;=1E9,H60/1E9,IF(ABS(H60)&gt;=1E6,H60/1E6,IF(ABS(H60)&gt;=1E3,H60/1E3,H60))))</f>
+        <v>12.20608</v>
+      </c>
+      <c r="E60" s="11" t="str">
+        <f>IF(ABS(H60)&gt;=1E12,"TB",IF(ABS(H60)&gt;=1E9,"GB",IF(ABS(H60)&gt;=1E6,"MB",IF(ABS(H60)&gt;=1E3,"KB","bytes"))))</f>
+        <v>MB</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G60" s="13">
+        <f>'Memory'!$Q$28</f>
+        <v>12206080</v>
+      </c>
+      <c r="H60" s="13">
+        <f>'Memory'!$Q$32</f>
+        <v>12206080</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B61" s="12">
+        <f>IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61))))</f>
+        <v>7.232045056</v>
+      </c>
+      <c r="C61" s="11" t="str">
+        <f>IF(ABS(G61)&gt;=1E12,"TB",IF(ABS(G61)&gt;=1E9,"GB",IF(ABS(G61)&gt;=1E6,"MB",IF(ABS(G61)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D61" s="12">
+        <f>IF(ABS(H61)&gt;=1E12,H61/1E12,IF(ABS(H61)&gt;=1E9,H61/1E9,IF(ABS(H61)&gt;=1E6,H61/1E6,IF(ABS(H61)&gt;=1E3,H61/1E3,H61))))</f>
+        <v>7.232045056</v>
+      </c>
+      <c r="E61" s="11" t="str">
+        <f>IF(ABS(H61)&gt;=1E12,"TB",IF(ABS(H61)&gt;=1E9,"GB",IF(ABS(H61)&gt;=1E6,"MB",IF(ABS(H61)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G61" s="13">
+        <f>'Memory'!$Q$29</f>
+        <v>7232045056</v>
+      </c>
+      <c r="H61" s="13">
+        <f>'Memory'!$Q$33</f>
+        <v>7232045056</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="B62" s="14">
+        <f>IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62))))</f>
+        <v>29.581867388</v>
+      </c>
+      <c r="C62" s="11" t="str">
+        <f>IF(ABS(G62)&gt;=1E12,"TB",IF(ABS(G62)&gt;=1E9,"GB",IF(ABS(G62)&gt;=1E6,"MB",IF(ABS(G62)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="D62" s="14">
+        <f>IF(ABS(H62)&gt;=1E12,H62/1E12,IF(ABS(H62)&gt;=1E9,H62/1E9,IF(ABS(H62)&gt;=1E6,H62/1E6,IF(ABS(H62)&gt;=1E3,H62/1E3,H62))))</f>
+        <v>29.581867388</v>
+      </c>
+      <c r="E62" s="11" t="str">
+        <f>IF(ABS(H62)&gt;=1E12,"TB",IF(ABS(H62)&gt;=1E9,"GB",IF(ABS(H62)&gt;=1E6,"MB",IF(ABS(H62)&gt;=1E3,"KB","bytes"))))</f>
+        <v>GB</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G62" s="13">
+        <f>'Memory'!$S$21+'Memory'!$Q$29</f>
+        <v>29581867388.0</v>
+      </c>
+      <c r="H62" s="13">
+        <f>'Memory'!$S$21+'Memory'!$Q$33</f>
+        <v>29581867388.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="603">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1753,25 +1753,34 @@
     <t>Decode TP8 GB</t>
   </si>
   <si>
-    <t>TP1 参数 GB/rank</t>
-  </si>
-  <si>
-    <t>TP8 参数 GB/rank</t>
-  </si>
-  <si>
-    <t>容量项</t>
-  </si>
-  <si>
-    <t>TP1 GB/rank</t>
-  </si>
-  <si>
-    <t>TP8 GB/rank</t>
-  </si>
-  <si>
-    <t>参数</t>
-  </si>
-  <si>
-    <t>Decode KV+State</t>
+    <t>静态参数大类（Prefill/Decode 共用）</t>
+  </si>
+  <si>
+    <t>TP1 单 Rank GB</t>
+  </si>
+  <si>
+    <t>TP8 单 Rank GB</t>
+  </si>
+  <si>
+    <t>说明：参数容量只由模型结构、dtype 和 TP 分片决定，与 Prefill/Decode 场景无关；两列分别是单 Rank 值，不相加。</t>
+  </si>
+  <si>
+    <t>推理场景容量项</t>
+  </si>
+  <si>
+    <t>静态参数（场景共用）</t>
+  </si>
+  <si>
+    <t>Prefill 预分配 KV+State</t>
+  </si>
+  <si>
+    <t>Prefill 总驻留（参数+KV）</t>
+  </si>
+  <si>
+    <t>Decode 预分配 KV+State</t>
+  </si>
+  <si>
+    <t>Decode 总驻留（参数+KV）</t>
   </si>
   <si>
     <t>方法与统计边界</t>
@@ -2936,7 +2945,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>每 Rank 参数容量</a:t>
+              <a:t>静态参数容量/单 Rank（Prefill/Decode 共用）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2952,7 +2961,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>TP1</c:v>
+            <c:v>TP1 单 Rank</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0" sourceLinked="0"/>
@@ -2998,7 +3007,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>TP8</c:v>
+            <c:v>TP8 单 Rank</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0" sourceLinked="0"/>
@@ -3118,7 +3127,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Decode 每 Rank 驻留容量</a:t>
+              <a:t>Prefill / Decode 单 Rank 容量（TP 配置独立）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3134,7 +3143,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>TP1</c:v>
+            <c:v>TP1 单 Rank</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0" sourceLinked="0"/>
@@ -3142,29 +3151,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$A$23:$A$24</c:f>
+              <c:f>Comparison!$A$23:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>参数</c:v>
+                  <c:v>静态参数（场景共用）</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Decode KV+State</c:v>
+                  <c:v>Prefill 预分配 KV+State</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Prefill 总驻留（参数+KV）</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Decode 预分配 KV+State</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Decode 总驻留（参数+KV）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$23:$B$24</c:f>
+              <c:f>Comparison!$B$23:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>159.117270492</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>7.232045056</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166.349315548</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.232045056</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>166.349315548</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3174,7 +3201,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>TP8</c:v>
+            <c:v>TP8 单 Rank</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0" sourceLinked="0"/>
@@ -3182,29 +3209,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$A$23:$A$24</c:f>
+              <c:f>Comparison!$A$23:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>参数</c:v>
+                  <c:v>静态参数（场景共用）</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Decode KV+State</c:v>
+                  <c:v>Prefill 预分配 KV+State</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Prefill 总驻留（参数+KV）</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Decode 预分配 KV+State</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Decode 总驻留（参数+KV）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$C$23:$C$24</c:f>
+              <c:f>Comparison!$C$23:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>22.349822332</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>7.232045056</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.581867388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.232045056</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.581867388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12419,7 +12464,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -12598,13 +12643,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -12646,15 +12691,20 @@
         <v>0.534376892</v>
       </c>
     </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -12675,12 +12725,51 @@
         <v>523</v>
       </c>
       <c r="B24" s="13">
+        <f>'Memory'!$P$29/1E9</f>
+        <v>7.232045056</v>
+      </c>
+      <c r="C24" s="13">
+        <f>'Memory'!$Q$29/1E9</f>
+        <v>7.232045056</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B25" s="13">
+        <f>'Memory'!$R$21+'Memory'!$P$29/1E9</f>
+        <v>166.349315548</v>
+      </c>
+      <c r="C25" s="13">
+        <f>'Memory'!$S$21+'Memory'!$Q$29/1E9</f>
+        <v>29.581867388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B26" s="13">
         <f>'Memory'!$P$33/1E9</f>
         <v>7.232045056</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C26" s="13">
         <f>'Memory'!$Q$33/1E9</f>
         <v>7.232045056</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B27" s="13">
+        <f>'Memory'!$R$21+'Memory'!$P$33/1E9</f>
+        <v>166.349315548</v>
+      </c>
+      <c r="C27" s="13">
+        <f>'Memory'!$S$21+'Memory'!$Q$33/1E9</f>
+        <v>29.581867388</v>
       </c>
     </row>
   </sheetData>
@@ -12700,47 +12789,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -12748,55 +12837,55 @@
         <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -12804,15 +12893,15 @@
         <v>460</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -12833,17 +12922,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -12853,16 +12942,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>460</v>
@@ -12873,7 +12962,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B6" s="12">
         <f>IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6))))</f>
@@ -12892,7 +12981,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G6" s="13">
         <f>'Prefill_8K'!$AE$13</f>
@@ -12905,7 +12994,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B7" s="12">
         <f>IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7))))</f>
@@ -12924,7 +13013,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G7" s="13">
         <f>'Prefill_8K'!$AE$14</f>
@@ -12937,7 +13026,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B8" s="12">
         <f>IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8))))</f>
@@ -12956,7 +13045,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G8" s="13">
         <f>'Prefill_8K'!$AE$15</f>
@@ -12969,7 +13058,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B9" s="14">
         <f>IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9))))</f>
@@ -12988,7 +13077,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G9" s="13">
         <f>'Prefill_8K'!$AE$16</f>
@@ -13001,7 +13090,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B10" s="12">
         <f>IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10))))</f>
@@ -13020,7 +13109,7 @@
         <v>GB</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G10" s="13">
         <f>'Prefill_8K'!$AE$17</f>
@@ -13033,7 +13122,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B11" s="12">
         <f>IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11))))</f>
@@ -13052,7 +13141,7 @@
         <v>GB</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G11" s="13">
         <f>'Prefill_8K'!$AE$18</f>
@@ -13065,7 +13154,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B12" s="12">
         <f>IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12))))</f>
@@ -13084,7 +13173,7 @@
         <v>GB</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G12" s="13">
         <f>'Prefill_8K'!$AE$19</f>
@@ -13097,7 +13186,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B13" s="14">
         <f>IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13))))</f>
@@ -13116,7 +13205,7 @@
         <v>GB</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G13" s="13">
         <f>'Prefill_8K'!$AE$20</f>
@@ -13129,7 +13218,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B14" s="12">
         <f>G14</f>
@@ -13146,7 +13235,7 @@
         <v>159</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G14" s="13">
         <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
@@ -13159,7 +13248,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B15" s="12">
         <f>G15</f>
@@ -13176,7 +13265,7 @@
         <v>159</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G15" s="13">
         <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
@@ -13189,7 +13278,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B16" s="12">
         <f>G16</f>
@@ -13206,7 +13295,7 @@
         <v>159</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G16" s="13">
         <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
@@ -13219,7 +13308,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B17" s="12">
         <f>G17</f>
@@ -13236,7 +13325,7 @@
         <v>155</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="G17" s="13">
         <f>'Prefill_8K'!$AE$23</f>
@@ -13249,7 +13338,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B18" s="12">
         <f>IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18))))</f>
@@ -13268,7 +13357,7 @@
         <v>B</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="G18" s="13">
         <f>'Prefill_8K'!$AE$21</f>
@@ -13281,7 +13370,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B19" s="12">
         <f>G19</f>
@@ -13298,7 +13387,7 @@
         <v>159</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G19" s="13">
         <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
@@ -13311,7 +13400,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B20" s="12">
         <f>IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20))))</f>
@@ -13330,7 +13419,7 @@
         <v>G params</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G20" s="13">
         <f>'Memory'!$P$18</f>
@@ -13343,7 +13432,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B21" s="12">
         <f>IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21))))</f>
@@ -13362,7 +13451,7 @@
         <v>G params</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G21" s="13">
         <f>'Memory'!$P$19</f>
@@ -13375,7 +13464,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B22" s="12">
         <f>IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22))))</f>
@@ -13394,7 +13483,7 @@
         <v>G params</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G22" s="13">
         <f>'Memory'!$P$20</f>
@@ -13407,7 +13496,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="14" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B23" s="14">
         <f>IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23))))</f>
@@ -13426,7 +13515,7 @@
         <v>G params</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G23" s="13">
         <f>'Memory'!$P$21</f>
@@ -13439,7 +13528,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B24" s="12">
         <f>IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24))))</f>
@@ -13458,7 +13547,7 @@
         <v>GB</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G24" s="13">
         <f>'Memory'!$R$18</f>
@@ -13471,7 +13560,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B25" s="12">
         <f>IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25))))</f>
@@ -13490,7 +13579,7 @@
         <v>GB</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G25" s="13">
         <f>'Memory'!$R$19</f>
@@ -13503,7 +13592,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B26" s="12">
         <f>IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26))))</f>
@@ -13522,7 +13611,7 @@
         <v>GB</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G26" s="13">
         <f>'Memory'!$R$20</f>
@@ -13535,7 +13624,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="14" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B27" s="14">
         <f>IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27))))</f>
@@ -13554,7 +13643,7 @@
         <v>GB</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G27" s="13">
         <f>'Memory'!$R$21</f>
@@ -13567,7 +13656,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B28" s="12">
         <f>IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28))))</f>
@@ -13586,7 +13675,7 @@
         <v>GB</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G28" s="13">
         <f>'Memory'!$P$26</f>
@@ -13599,7 +13688,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B29" s="12">
         <f>IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29))))</f>
@@ -13618,7 +13707,7 @@
         <v>GB</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G29" s="13">
         <f>'Memory'!$P$27</f>
@@ -13631,7 +13720,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B30" s="12">
         <f>IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30))))</f>
@@ -13650,7 +13739,7 @@
         <v>MB</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G30" s="13">
         <f>'Memory'!$P$28</f>
@@ -13663,7 +13752,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B31" s="12">
         <f>IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31))))</f>
@@ -13682,7 +13771,7 @@
         <v>GB</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G31" s="13">
         <f>'Memory'!$P$29</f>
@@ -13695,7 +13784,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="14" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B32" s="14">
         <f>IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32))))</f>
@@ -13714,7 +13803,7 @@
         <v>GB</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G32" s="13">
         <f>'Memory'!$R$21+'Memory'!$P$29</f>
@@ -13727,7 +13816,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="7" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -13737,16 +13826,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>460</v>
@@ -13757,7 +13846,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B36" s="12">
         <f>IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36))))</f>
@@ -13776,7 +13865,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G36" s="13">
         <f>'Prefill_8K'!$AF$13</f>
@@ -13789,7 +13878,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B37" s="12">
         <f>IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37))))</f>
@@ -13808,7 +13897,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G37" s="13">
         <f>'Prefill_8K'!$AF$14</f>
@@ -13821,7 +13910,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B38" s="12">
         <f>IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38))))</f>
@@ -13840,7 +13929,7 @@
         <v>MFLOPs</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G38" s="13">
         <f>'Prefill_8K'!$AF$15</f>
@@ -13853,7 +13942,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="14" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B39" s="14">
         <f>IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39))))</f>
@@ -13872,7 +13961,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G39" s="13">
         <f>'Prefill_8K'!$AF$16</f>
@@ -13885,7 +13974,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B40" s="12">
         <f>IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40))))</f>
@@ -13904,7 +13993,7 @@
         <v>GB</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G40" s="13">
         <f>'Prefill_8K'!$AF$17</f>
@@ -13917,7 +14006,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B41" s="12">
         <f>IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41))))</f>
@@ -13936,7 +14025,7 @@
         <v>GB</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G41" s="13">
         <f>'Prefill_8K'!$AF$18</f>
@@ -13949,7 +14038,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B42" s="12">
         <f>IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42))))</f>
@@ -13968,7 +14057,7 @@
         <v>MB</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G42" s="13">
         <f>'Prefill_8K'!$AF$19</f>
@@ -13981,7 +14070,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="14" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B43" s="14">
         <f>IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43))))</f>
@@ -14000,7 +14089,7 @@
         <v>GB</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G43" s="13">
         <f>'Prefill_8K'!$AF$20</f>
@@ -14013,7 +14102,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B44" s="12">
         <f>G44</f>
@@ -14030,7 +14119,7 @@
         <v>159</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G44" s="13">
         <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
@@ -14043,7 +14132,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B45" s="12">
         <f>G45</f>
@@ -14060,7 +14149,7 @@
         <v>159</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G45" s="13">
         <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
@@ -14073,7 +14162,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B46" s="12">
         <f>G46</f>
@@ -14090,7 +14179,7 @@
         <v>159</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G46" s="13">
         <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
@@ -14103,7 +14192,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B47" s="12">
         <f>G47</f>
@@ -14120,7 +14209,7 @@
         <v>155</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="G47" s="13">
         <f>'Prefill_8K'!$AF$23</f>
@@ -14133,7 +14222,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B48" s="12">
         <f>IF(ABS(G48)&gt;=1E12,G48/1E12,IF(ABS(G48)&gt;=1E9,G48/1E9,IF(ABS(G48)&gt;=1E6,G48/1E6,IF(ABS(G48)&gt;=1E3,G48/1E3,G48))))</f>
@@ -14152,7 +14241,7 @@
         <v>MB</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="G48" s="13">
         <f>'Prefill_8K'!$AF$21</f>
@@ -14165,7 +14254,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B49" s="12">
         <f>G49</f>
@@ -14182,7 +14271,7 @@
         <v>159</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G49" s="13">
         <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
@@ -14195,7 +14284,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B50" s="12">
         <f>IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50))))</f>
@@ -14214,7 +14303,7 @@
         <v>G params</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G50" s="13">
         <f>'Memory'!$Q$18</f>
@@ -14227,7 +14316,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B51" s="12">
         <f>IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51))))</f>
@@ -14246,7 +14335,7 @@
         <v>G params</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G51" s="13">
         <f>'Memory'!$Q$19</f>
@@ -14259,7 +14348,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B52" s="12">
         <f>IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52))))</f>
@@ -14278,7 +14367,7 @@
         <v>M params</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G52" s="13">
         <f>'Memory'!$Q$20</f>
@@ -14291,7 +14380,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="14" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B53" s="14">
         <f>IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53))))</f>
@@ -14310,7 +14399,7 @@
         <v>G params</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G53" s="13">
         <f>'Memory'!$Q$21</f>
@@ -14323,7 +14412,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B54" s="12">
         <f>IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54))))</f>
@@ -14342,7 +14431,7 @@
         <v>GB</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G54" s="13">
         <f>'Memory'!$S$18</f>
@@ -14355,7 +14444,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B55" s="12">
         <f>IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55))))</f>
@@ -14374,7 +14463,7 @@
         <v>GB</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G55" s="13">
         <f>'Memory'!$S$19</f>
@@ -14387,7 +14476,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B56" s="12">
         <f>IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56))))</f>
@@ -14406,7 +14495,7 @@
         <v>MB</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G56" s="13">
         <f>'Memory'!$S$20</f>
@@ -14419,7 +14508,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="14" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B57" s="14">
         <f>IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57))))</f>
@@ -14438,7 +14527,7 @@
         <v>GB</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G57" s="13">
         <f>'Memory'!$S$21</f>
@@ -14451,7 +14540,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B58" s="12">
         <f>IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58))))</f>
@@ -14470,7 +14559,7 @@
         <v>GB</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G58" s="13">
         <f>'Memory'!$Q$26</f>
@@ -14483,7 +14572,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B59" s="12">
         <f>IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59))))</f>
@@ -14502,7 +14591,7 @@
         <v>GB</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G59" s="13">
         <f>'Memory'!$Q$27</f>
@@ -14515,7 +14604,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B60" s="12">
         <f>IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60))))</f>
@@ -14534,7 +14623,7 @@
         <v>MB</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G60" s="13">
         <f>'Memory'!$Q$28</f>
@@ -14547,7 +14636,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B61" s="12">
         <f>IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61))))</f>
@@ -14566,7 +14655,7 @@
         <v>GB</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G61" s="13">
         <f>'Memory'!$Q$29</f>
@@ -14579,7 +14668,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="14" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B62" s="14">
         <f>IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62))))</f>
@@ -14598,7 +14687,7 @@
         <v>GB</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G62" s="13">
         <f>'Memory'!$S$21+'Memory'!$Q$29</f>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="609">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1781,6 +1781,24 @@
   </si>
   <si>
     <t>Decode 总驻留（参数+KV）</t>
+  </si>
+  <si>
+    <t>算力需求场景</t>
+  </si>
+  <si>
+    <t>所需 TFLOP/s</t>
+  </si>
+  <si>
+    <t>Prefill TP1/rank</t>
+  </si>
+  <si>
+    <t>Prefill TP8/rank</t>
+  </si>
+  <si>
+    <t>Decode TP1/rank</t>
+  </si>
+  <si>
+    <t>Decode TP8/rank</t>
   </si>
   <si>
     <t>方法与统计边界</t>
@@ -2217,6 +2235,148 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>目标时延所需总算力/单 Rank</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>所需 TFLOP/s</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$31:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Prefill TP1/rank</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prefill TP8/rank</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Decode TP1/rank</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Decode TP8/rank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$B$31:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>228.384427393024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55.63931418624</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.0354134102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3548076118</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>TFLOP/s</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Prefill 每 Rank 计算量</a:t>
             </a:r>
           </a:p>
@@ -2321,24 +2481,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50010001"/>
-        <c:axId val="50010002"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50010001"/>
+        <c:axId val="50020001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50010002"/>
+        <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50010002"/>
+        <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2364,7 +2524,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50010001"/>
+        <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2383,7 +2543,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:style val="10"/>
@@ -2503,24 +2663,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50020001"/>
-        <c:axId val="50020002"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50020001"/>
+        <c:axId val="50030001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50020002"/>
+        <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50020002"/>
+        <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2546,7 +2706,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50020001"/>
+        <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2565,7 +2725,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:style val="10"/>
@@ -2685,24 +2845,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50030001"/>
-        <c:axId val="50030002"/>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50030001"/>
+        <c:axId val="50040001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50030002"/>
+        <c:crossAx val="50040002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50030002"/>
+        <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2728,7 +2888,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50030001"/>
+        <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2747,7 +2907,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:style val="10"/>
@@ -2867,24 +3027,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50040001"/>
-        <c:axId val="50040002"/>
+        <c:axId val="50050001"/>
+        <c:axId val="50050002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50040001"/>
+        <c:axId val="50050001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50040002"/>
+        <c:crossAx val="50050002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50040002"/>
+        <c:axId val="50050002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2910,7 +3070,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50040001"/>
+        <c:crossAx val="50050001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2929,7 +3089,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:style val="10"/>
@@ -3049,24 +3209,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50050001"/>
-        <c:axId val="50050002"/>
+        <c:axId val="50060001"/>
+        <c:axId val="50060002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50050001"/>
+        <c:axId val="50060001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50050002"/>
+        <c:crossAx val="50060002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50050002"/>
+        <c:axId val="50060002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3092,7 +3252,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50050001"/>
+        <c:crossAx val="50060001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3111,7 +3271,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:style val="10"/>
@@ -3255,24 +3415,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50060001"/>
-        <c:axId val="50060002"/>
+        <c:axId val="50070001"/>
+        <c:axId val="50070002"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50060001"/>
+        <c:axId val="50070001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="50060002"/>
+        <c:crossAx val="50070002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50060002"/>
+        <c:axId val="50070002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3298,7 +3458,7 @@
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50060001"/>
+        <c:crossAx val="50070001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3321,15 +3481,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3351,15 +3511,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3381,15 +3541,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3411,15 +3571,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3441,15 +3601,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3471,15 +3631,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3494,6 +3654,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -12464,7 +12654,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -12712,11 +12902,11 @@
         <v>522</v>
       </c>
       <c r="B23" s="13">
-        <f>'Memory'!$R$21/1E9</f>
+        <f>('Memory'!$R$21)/1E9</f>
         <v>159.117270492</v>
       </c>
       <c r="C23" s="13">
-        <f>'Memory'!$S$21/1E9</f>
+        <f>('Memory'!$S$21)/1E9</f>
         <v>22.349822332</v>
       </c>
     </row>
@@ -12725,11 +12915,11 @@
         <v>523</v>
       </c>
       <c r="B24" s="13">
-        <f>'Memory'!$P$29/1E9</f>
+        <f>('Memory'!$P$29)/1E9</f>
         <v>7.232045056</v>
       </c>
       <c r="C24" s="13">
-        <f>'Memory'!$Q$29/1E9</f>
+        <f>('Memory'!$Q$29)/1E9</f>
         <v>7.232045056</v>
       </c>
     </row>
@@ -12738,11 +12928,11 @@
         <v>524</v>
       </c>
       <c r="B25" s="13">
-        <f>'Memory'!$R$21+'Memory'!$P$29/1E9</f>
+        <f>('Memory'!$R$21+'Memory'!$P$29)/1E9</f>
         <v>166.349315548</v>
       </c>
       <c r="C25" s="13">
-        <f>'Memory'!$S$21+'Memory'!$Q$29/1E9</f>
+        <f>('Memory'!$S$21+'Memory'!$Q$29)/1E9</f>
         <v>29.581867388</v>
       </c>
     </row>
@@ -12751,11 +12941,11 @@
         <v>525</v>
       </c>
       <c r="B26" s="13">
-        <f>'Memory'!$P$33/1E9</f>
+        <f>('Memory'!$P$33)/1E9</f>
         <v>7.232045056</v>
       </c>
       <c r="C26" s="13">
-        <f>'Memory'!$Q$33/1E9</f>
+        <f>('Memory'!$Q$33)/1E9</f>
         <v>7.232045056</v>
       </c>
     </row>
@@ -12764,12 +12954,56 @@
         <v>526</v>
       </c>
       <c r="B27" s="13">
-        <f>'Memory'!$R$21+'Memory'!$P$33/1E9</f>
+        <f>('Memory'!$R$21+'Memory'!$P$33)/1E9</f>
         <v>166.349315548</v>
       </c>
       <c r="C27" s="13">
-        <f>'Memory'!$S$21+'Memory'!$Q$33/1E9</f>
+        <f>('Memory'!$S$21+'Memory'!$Q$33)/1E9</f>
         <v>29.581867388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B31" s="13">
+        <f>'Prefill_8K'!$AE$23</f>
+        <v>228.384427393024</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B32" s="13">
+        <f>'Prefill_8K'!$AF$23</f>
+        <v>55.63931418624</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B33" s="13">
+        <f>'Decode_1M'!$AE$23</f>
+        <v>14.0354134102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B34" s="13">
+        <f>'Decode_1M'!$AF$23</f>
+        <v>2.3548076118</v>
       </c>
     </row>
   </sheetData>
@@ -12789,47 +13023,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -12837,55 +13071,55 @@
         <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -12893,15 +13127,15 @@
         <v>460</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -12922,17 +13156,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -12942,16 +13176,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>460</v>
@@ -12962,7 +13196,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B6" s="12">
         <f>IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6))))</f>
@@ -12981,7 +13215,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G6" s="13">
         <f>'Prefill_8K'!$AE$13</f>
@@ -12994,7 +13228,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B7" s="12">
         <f>IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7))))</f>
@@ -13013,7 +13247,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G7" s="13">
         <f>'Prefill_8K'!$AE$14</f>
@@ -13026,7 +13260,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B8" s="12">
         <f>IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8))))</f>
@@ -13045,7 +13279,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G8" s="13">
         <f>'Prefill_8K'!$AE$15</f>
@@ -13058,7 +13292,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B9" s="14">
         <f>IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9))))</f>
@@ -13077,7 +13311,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G9" s="13">
         <f>'Prefill_8K'!$AE$16</f>
@@ -13090,7 +13324,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B10" s="12">
         <f>IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10))))</f>
@@ -13109,7 +13343,7 @@
         <v>GB</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G10" s="13">
         <f>'Prefill_8K'!$AE$17</f>
@@ -13122,7 +13356,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B11" s="12">
         <f>IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11))))</f>
@@ -13141,7 +13375,7 @@
         <v>GB</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G11" s="13">
         <f>'Prefill_8K'!$AE$18</f>
@@ -13154,7 +13388,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B12" s="12">
         <f>IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12))))</f>
@@ -13173,7 +13407,7 @@
         <v>GB</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G12" s="13">
         <f>'Prefill_8K'!$AE$19</f>
@@ -13186,7 +13420,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B13" s="14">
         <f>IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13))))</f>
@@ -13205,7 +13439,7 @@
         <v>GB</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G13" s="13">
         <f>'Prefill_8K'!$AE$20</f>
@@ -13218,7 +13452,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B14" s="12">
         <f>G14</f>
@@ -13235,7 +13469,7 @@
         <v>159</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G14" s="13">
         <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
@@ -13248,7 +13482,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B15" s="12">
         <f>G15</f>
@@ -13265,7 +13499,7 @@
         <v>159</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G15" s="13">
         <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
@@ -13278,7 +13512,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B16" s="12">
         <f>G16</f>
@@ -13295,7 +13529,7 @@
         <v>159</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G16" s="13">
         <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
@@ -13308,7 +13542,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B17" s="12">
         <f>G17</f>
@@ -13325,7 +13559,7 @@
         <v>155</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="G17" s="13">
         <f>'Prefill_8K'!$AE$23</f>
@@ -13338,7 +13572,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B18" s="12">
         <f>IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18))))</f>
@@ -13357,7 +13591,7 @@
         <v>B</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G18" s="13">
         <f>'Prefill_8K'!$AE$21</f>
@@ -13370,7 +13604,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B19" s="12">
         <f>G19</f>
@@ -13387,7 +13621,7 @@
         <v>159</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G19" s="13">
         <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
@@ -13400,7 +13634,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B20" s="12">
         <f>IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20))))</f>
@@ -13419,7 +13653,7 @@
         <v>G params</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="G20" s="13">
         <f>'Memory'!$P$18</f>
@@ -13432,7 +13666,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B21" s="12">
         <f>IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21))))</f>
@@ -13451,7 +13685,7 @@
         <v>G params</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="G21" s="13">
         <f>'Memory'!$P$19</f>
@@ -13464,7 +13698,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B22" s="12">
         <f>IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22))))</f>
@@ -13483,7 +13717,7 @@
         <v>G params</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G22" s="13">
         <f>'Memory'!$P$20</f>
@@ -13496,7 +13730,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="14" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B23" s="14">
         <f>IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23))))</f>
@@ -13515,7 +13749,7 @@
         <v>G params</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="G23" s="13">
         <f>'Memory'!$P$21</f>
@@ -13528,7 +13762,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B24" s="12">
         <f>IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24))))</f>
@@ -13547,7 +13781,7 @@
         <v>GB</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="G24" s="13">
         <f>'Memory'!$R$18</f>
@@ -13560,7 +13794,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B25" s="12">
         <f>IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25))))</f>
@@ -13579,7 +13813,7 @@
         <v>GB</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="G25" s="13">
         <f>'Memory'!$R$19</f>
@@ -13592,7 +13826,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B26" s="12">
         <f>IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26))))</f>
@@ -13611,7 +13845,7 @@
         <v>GB</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G26" s="13">
         <f>'Memory'!$R$20</f>
@@ -13624,7 +13858,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="14" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B27" s="14">
         <f>IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27))))</f>
@@ -13643,7 +13877,7 @@
         <v>GB</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G27" s="13">
         <f>'Memory'!$R$21</f>
@@ -13656,7 +13890,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B28" s="12">
         <f>IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28))))</f>
@@ -13675,7 +13909,7 @@
         <v>GB</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G28" s="13">
         <f>'Memory'!$P$26</f>
@@ -13688,7 +13922,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B29" s="12">
         <f>IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29))))</f>
@@ -13707,7 +13941,7 @@
         <v>GB</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G29" s="13">
         <f>'Memory'!$P$27</f>
@@ -13720,7 +13954,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B30" s="12">
         <f>IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30))))</f>
@@ -13739,7 +13973,7 @@
         <v>MB</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G30" s="13">
         <f>'Memory'!$P$28</f>
@@ -13752,7 +13986,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B31" s="12">
         <f>IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31))))</f>
@@ -13771,7 +14005,7 @@
         <v>GB</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G31" s="13">
         <f>'Memory'!$P$29</f>
@@ -13784,7 +14018,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="14" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B32" s="14">
         <f>IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32))))</f>
@@ -13803,7 +14037,7 @@
         <v>GB</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="G32" s="13">
         <f>'Memory'!$R$21+'Memory'!$P$29</f>
@@ -13816,7 +14050,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="7" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -13826,16 +14060,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>460</v>
@@ -13846,7 +14080,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B36" s="12">
         <f>IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36))))</f>
@@ -13865,7 +14099,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G36" s="13">
         <f>'Prefill_8K'!$AF$13</f>
@@ -13878,7 +14112,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B37" s="12">
         <f>IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37))))</f>
@@ -13897,7 +14131,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G37" s="13">
         <f>'Prefill_8K'!$AF$14</f>
@@ -13910,7 +14144,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B38" s="12">
         <f>IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38))))</f>
@@ -13929,7 +14163,7 @@
         <v>MFLOPs</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G38" s="13">
         <f>'Prefill_8K'!$AF$15</f>
@@ -13942,7 +14176,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="14" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B39" s="14">
         <f>IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39))))</f>
@@ -13961,7 +14195,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G39" s="13">
         <f>'Prefill_8K'!$AF$16</f>
@@ -13974,7 +14208,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B40" s="12">
         <f>IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40))))</f>
@@ -13993,7 +14227,7 @@
         <v>GB</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G40" s="13">
         <f>'Prefill_8K'!$AF$17</f>
@@ -14006,7 +14240,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B41" s="12">
         <f>IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41))))</f>
@@ -14025,7 +14259,7 @@
         <v>GB</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G41" s="13">
         <f>'Prefill_8K'!$AF$18</f>
@@ -14038,7 +14272,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B42" s="12">
         <f>IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42))))</f>
@@ -14057,7 +14291,7 @@
         <v>MB</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G42" s="13">
         <f>'Prefill_8K'!$AF$19</f>
@@ -14070,7 +14304,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="14" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B43" s="14">
         <f>IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43))))</f>
@@ -14089,7 +14323,7 @@
         <v>GB</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G43" s="13">
         <f>'Prefill_8K'!$AF$20</f>
@@ -14102,7 +14336,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B44" s="12">
         <f>G44</f>
@@ -14119,7 +14353,7 @@
         <v>159</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G44" s="13">
         <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
@@ -14132,7 +14366,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B45" s="12">
         <f>G45</f>
@@ -14149,7 +14383,7 @@
         <v>159</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G45" s="13">
         <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
@@ -14162,7 +14396,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B46" s="12">
         <f>G46</f>
@@ -14179,7 +14413,7 @@
         <v>159</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G46" s="13">
         <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
@@ -14192,7 +14426,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B47" s="12">
         <f>G47</f>
@@ -14209,7 +14443,7 @@
         <v>155</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="G47" s="13">
         <f>'Prefill_8K'!$AF$23</f>
@@ -14222,7 +14456,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B48" s="12">
         <f>IF(ABS(G48)&gt;=1E12,G48/1E12,IF(ABS(G48)&gt;=1E9,G48/1E9,IF(ABS(G48)&gt;=1E6,G48/1E6,IF(ABS(G48)&gt;=1E3,G48/1E3,G48))))</f>
@@ -14241,7 +14475,7 @@
         <v>MB</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G48" s="13">
         <f>'Prefill_8K'!$AF$21</f>
@@ -14254,7 +14488,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B49" s="12">
         <f>G49</f>
@@ -14271,7 +14505,7 @@
         <v>159</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G49" s="13">
         <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
@@ -14284,7 +14518,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B50" s="12">
         <f>IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50))))</f>
@@ -14303,7 +14537,7 @@
         <v>G params</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="G50" s="13">
         <f>'Memory'!$Q$18</f>
@@ -14316,7 +14550,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B51" s="12">
         <f>IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51))))</f>
@@ -14335,7 +14569,7 @@
         <v>G params</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="G51" s="13">
         <f>'Memory'!$Q$19</f>
@@ -14348,7 +14582,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B52" s="12">
         <f>IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52))))</f>
@@ -14367,7 +14601,7 @@
         <v>M params</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G52" s="13">
         <f>'Memory'!$Q$20</f>
@@ -14380,7 +14614,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="14" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B53" s="14">
         <f>IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53))))</f>
@@ -14399,7 +14633,7 @@
         <v>G params</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="G53" s="13">
         <f>'Memory'!$Q$21</f>
@@ -14412,7 +14646,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B54" s="12">
         <f>IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54))))</f>
@@ -14431,7 +14665,7 @@
         <v>GB</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="G54" s="13">
         <f>'Memory'!$S$18</f>
@@ -14444,7 +14678,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B55" s="12">
         <f>IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55))))</f>
@@ -14463,7 +14697,7 @@
         <v>GB</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="G55" s="13">
         <f>'Memory'!$S$19</f>
@@ -14476,7 +14710,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B56" s="12">
         <f>IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56))))</f>
@@ -14495,7 +14729,7 @@
         <v>MB</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G56" s="13">
         <f>'Memory'!$S$20</f>
@@ -14508,7 +14742,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="14" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B57" s="14">
         <f>IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57))))</f>
@@ -14527,7 +14761,7 @@
         <v>GB</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G57" s="13">
         <f>'Memory'!$S$21</f>
@@ -14540,7 +14774,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B58" s="12">
         <f>IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58))))</f>
@@ -14559,7 +14793,7 @@
         <v>GB</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G58" s="13">
         <f>'Memory'!$Q$26</f>
@@ -14572,7 +14806,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B59" s="12">
         <f>IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59))))</f>
@@ -14591,7 +14825,7 @@
         <v>GB</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G59" s="13">
         <f>'Memory'!$Q$27</f>
@@ -14604,7 +14838,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B60" s="12">
         <f>IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60))))</f>
@@ -14623,7 +14857,7 @@
         <v>MB</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G60" s="13">
         <f>'Memory'!$Q$28</f>
@@ -14636,7 +14870,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B61" s="12">
         <f>IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61))))</f>
@@ -14655,7 +14889,7 @@
         <v>GB</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G61" s="13">
         <f>'Memory'!$Q$29</f>
@@ -14668,7 +14902,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="14" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B62" s="14">
         <f>IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62))))</f>
@@ -14687,7 +14921,7 @@
         <v>GB</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="G62" s="13">
         <f>'Memory'!$S$21+'Memory'!$Q$29</f>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="607">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1765,22 +1765,16 @@
     <t>说明：参数容量只由模型结构、dtype 和 TP 分片决定，与 Prefill/Decode 场景无关；两列分别是单 Rank 值，不相加。</t>
   </si>
   <si>
-    <t>推理场景容量项</t>
+    <t>单 Rank 容量项</t>
   </si>
   <si>
     <t>静态参数（场景共用）</t>
   </si>
   <si>
-    <t>Prefill 预分配 KV+State</t>
-  </si>
-  <si>
-    <t>Prefill 总驻留（参数+KV）</t>
-  </si>
-  <si>
-    <t>Decode 预分配 KV+State</t>
-  </si>
-  <si>
-    <t>Decode 总驻留（参数+KV）</t>
+    <t>预分配 KV+State（Prefill/Decode 当前相同）</t>
+  </si>
+  <si>
+    <t>总驻留（静态参数+KV+State）</t>
   </si>
   <si>
     <t>算力需求场景</t>
@@ -3287,7 +3281,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Prefill / Decode 单 Rank 容量（TP 配置独立）</a:t>
+              <a:t>TP1 vs TP8：单 Rank 推理驻留容量</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3311,33 +3305,27 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$A$23:$A$27</c:f>
+              <c:f>Comparison!$A$23:$A$25</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>静态参数（场景共用）</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Prefill 预分配 KV+State</c:v>
+                  <c:v>预分配 KV+State（Prefill/Decode 当前相同）</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Prefill 总驻留（参数+KV）</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Decode 预分配 KV+State</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Decode 总驻留（参数+KV）</c:v>
+                  <c:v>总驻留（静态参数+KV+State）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$23:$B$27</c:f>
+              <c:f>Comparison!$B$23:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>159.117270492</c:v>
                 </c:pt>
@@ -3345,12 +3333,6 @@
                   <c:v>7.232045056</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>166.349315548</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.232045056</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>166.349315548</c:v>
                 </c:pt>
               </c:numCache>
@@ -3369,33 +3351,27 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$A$23:$A$27</c:f>
+              <c:f>Comparison!$A$23:$A$25</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>静态参数（场景共用）</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Prefill 预分配 KV+State</c:v>
+                  <c:v>预分配 KV+State（Prefill/Decode 当前相同）</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Prefill 总驻留（参数+KV）</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Decode 预分配 KV+State</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Decode 总驻留（参数+KV）</c:v>
+                  <c:v>总驻留（静态参数+KV+State）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$C$23:$C$27</c:f>
+              <c:f>Comparison!$C$23:$C$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>22.349822332</c:v>
                 </c:pt>
@@ -3403,12 +3379,6 @@
                   <c:v>7.232045056</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29.581867388</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.232045056</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>29.581867388</c:v>
                 </c:pt>
               </c:numCache>
@@ -12936,43 +12906,17 @@
         <v>29.581867388</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="B26" s="13">
-        <f>('Memory'!$P$33)/1E9</f>
-        <v>7.232045056</v>
-      </c>
-      <c r="C26" s="13">
-        <f>('Memory'!$Q$33)/1E9</f>
-        <v>7.232045056</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="B27" s="13">
-        <f>('Memory'!$R$21+'Memory'!$P$33)/1E9</f>
-        <v>166.349315548</v>
-      </c>
-      <c r="C27" s="13">
-        <f>('Memory'!$S$21+'Memory'!$Q$33)/1E9</f>
-        <v>29.581867388</v>
-      </c>
-    </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B31" s="13">
         <f>'Prefill_8K'!$AE$23</f>
@@ -12981,7 +12925,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B32" s="13">
         <f>'Prefill_8K'!$AF$23</f>
@@ -12990,7 +12934,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B33" s="13">
         <f>'Decode_1M'!$AE$23</f>
@@ -12999,7 +12943,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B34" s="13">
         <f>'Decode_1M'!$AF$23</f>
@@ -13023,47 +12967,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -13071,55 +13015,55 @@
         <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -13127,15 +13071,15 @@
         <v>460</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -13156,17 +13100,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -13176,16 +13120,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>460</v>
@@ -13196,7 +13140,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B6" s="12">
         <f>IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6))))</f>
@@ -13215,7 +13159,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G6" s="13">
         <f>'Prefill_8K'!$AE$13</f>
@@ -13228,7 +13172,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B7" s="12">
         <f>IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7))))</f>
@@ -13247,7 +13191,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G7" s="13">
         <f>'Prefill_8K'!$AE$14</f>
@@ -13260,7 +13204,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B8" s="12">
         <f>IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8))))</f>
@@ -13279,7 +13223,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G8" s="13">
         <f>'Prefill_8K'!$AE$15</f>
@@ -13292,7 +13236,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B9" s="14">
         <f>IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9))))</f>
@@ -13311,7 +13255,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G9" s="13">
         <f>'Prefill_8K'!$AE$16</f>
@@ -13324,7 +13268,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B10" s="12">
         <f>IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10))))</f>
@@ -13343,7 +13287,7 @@
         <v>GB</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G10" s="13">
         <f>'Prefill_8K'!$AE$17</f>
@@ -13356,7 +13300,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B11" s="12">
         <f>IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11))))</f>
@@ -13375,7 +13319,7 @@
         <v>GB</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G11" s="13">
         <f>'Prefill_8K'!$AE$18</f>
@@ -13388,7 +13332,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B12" s="12">
         <f>IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12))))</f>
@@ -13407,7 +13351,7 @@
         <v>GB</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G12" s="13">
         <f>'Prefill_8K'!$AE$19</f>
@@ -13420,7 +13364,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B13" s="14">
         <f>IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13))))</f>
@@ -13439,7 +13383,7 @@
         <v>GB</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G13" s="13">
         <f>'Prefill_8K'!$AE$20</f>
@@ -13452,7 +13396,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B14" s="12">
         <f>G14</f>
@@ -13469,7 +13413,7 @@
         <v>159</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G14" s="13">
         <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
@@ -13482,7 +13426,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B15" s="12">
         <f>G15</f>
@@ -13499,7 +13443,7 @@
         <v>159</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G15" s="13">
         <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
@@ -13512,7 +13456,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B16" s="12">
         <f>G16</f>
@@ -13529,7 +13473,7 @@
         <v>159</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G16" s="13">
         <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
@@ -13542,7 +13486,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B17" s="12">
         <f>G17</f>
@@ -13559,7 +13503,7 @@
         <v>155</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G17" s="13">
         <f>'Prefill_8K'!$AE$23</f>
@@ -13572,7 +13516,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B18" s="12">
         <f>IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18))))</f>
@@ -13591,7 +13535,7 @@
         <v>B</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G18" s="13">
         <f>'Prefill_8K'!$AE$21</f>
@@ -13604,7 +13548,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B19" s="12">
         <f>G19</f>
@@ -13621,7 +13565,7 @@
         <v>159</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G19" s="13">
         <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
@@ -13634,7 +13578,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B20" s="12">
         <f>IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20))))</f>
@@ -13653,7 +13597,7 @@
         <v>G params</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G20" s="13">
         <f>'Memory'!$P$18</f>
@@ -13666,7 +13610,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B21" s="12">
         <f>IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21))))</f>
@@ -13685,7 +13629,7 @@
         <v>G params</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G21" s="13">
         <f>'Memory'!$P$19</f>
@@ -13698,7 +13642,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B22" s="12">
         <f>IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22))))</f>
@@ -13717,7 +13661,7 @@
         <v>G params</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G22" s="13">
         <f>'Memory'!$P$20</f>
@@ -13730,7 +13674,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="14" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B23" s="14">
         <f>IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23))))</f>
@@ -13749,7 +13693,7 @@
         <v>G params</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G23" s="13">
         <f>'Memory'!$P$21</f>
@@ -13762,7 +13706,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B24" s="12">
         <f>IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24))))</f>
@@ -13781,7 +13725,7 @@
         <v>GB</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G24" s="13">
         <f>'Memory'!$R$18</f>
@@ -13794,7 +13738,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B25" s="12">
         <f>IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25))))</f>
@@ -13813,7 +13757,7 @@
         <v>GB</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G25" s="13">
         <f>'Memory'!$R$19</f>
@@ -13826,7 +13770,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B26" s="12">
         <f>IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26))))</f>
@@ -13845,7 +13789,7 @@
         <v>GB</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G26" s="13">
         <f>'Memory'!$R$20</f>
@@ -13858,7 +13802,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="14" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B27" s="14">
         <f>IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27))))</f>
@@ -13877,7 +13821,7 @@
         <v>GB</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G27" s="13">
         <f>'Memory'!$R$21</f>
@@ -13890,7 +13834,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B28" s="12">
         <f>IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28))))</f>
@@ -13909,7 +13853,7 @@
         <v>GB</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G28" s="13">
         <f>'Memory'!$P$26</f>
@@ -13922,7 +13866,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B29" s="12">
         <f>IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29))))</f>
@@ -13941,7 +13885,7 @@
         <v>GB</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G29" s="13">
         <f>'Memory'!$P$27</f>
@@ -13954,7 +13898,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B30" s="12">
         <f>IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30))))</f>
@@ -13973,7 +13917,7 @@
         <v>MB</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G30" s="13">
         <f>'Memory'!$P$28</f>
@@ -13986,7 +13930,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B31" s="12">
         <f>IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31))))</f>
@@ -14005,7 +13949,7 @@
         <v>GB</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G31" s="13">
         <f>'Memory'!$P$29</f>
@@ -14018,7 +13962,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B32" s="14">
         <f>IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32))))</f>
@@ -14037,7 +13981,7 @@
         <v>GB</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G32" s="13">
         <f>'Memory'!$R$21+'Memory'!$P$29</f>
@@ -14050,7 +13994,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="7" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -14060,16 +14004,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>460</v>
@@ -14080,7 +14024,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B36" s="12">
         <f>IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36))))</f>
@@ -14099,7 +14043,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G36" s="13">
         <f>'Prefill_8K'!$AF$13</f>
@@ -14112,7 +14056,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B37" s="12">
         <f>IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37))))</f>
@@ -14131,7 +14075,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G37" s="13">
         <f>'Prefill_8K'!$AF$14</f>
@@ -14144,7 +14088,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B38" s="12">
         <f>IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38))))</f>
@@ -14163,7 +14107,7 @@
         <v>MFLOPs</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G38" s="13">
         <f>'Prefill_8K'!$AF$15</f>
@@ -14176,7 +14120,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B39" s="14">
         <f>IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39))))</f>
@@ -14195,7 +14139,7 @@
         <v>GFLOPs</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G39" s="13">
         <f>'Prefill_8K'!$AF$16</f>
@@ -14208,7 +14152,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B40" s="12">
         <f>IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40))))</f>
@@ -14227,7 +14171,7 @@
         <v>GB</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G40" s="13">
         <f>'Prefill_8K'!$AF$17</f>
@@ -14240,7 +14184,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B41" s="12">
         <f>IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41))))</f>
@@ -14259,7 +14203,7 @@
         <v>GB</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G41" s="13">
         <f>'Prefill_8K'!$AF$18</f>
@@ -14272,7 +14216,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B42" s="12">
         <f>IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42))))</f>
@@ -14291,7 +14235,7 @@
         <v>MB</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G42" s="13">
         <f>'Prefill_8K'!$AF$19</f>
@@ -14304,7 +14248,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B43" s="14">
         <f>IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43))))</f>
@@ -14323,7 +14267,7 @@
         <v>GB</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G43" s="13">
         <f>'Prefill_8K'!$AF$20</f>
@@ -14336,7 +14280,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B44" s="12">
         <f>G44</f>
@@ -14353,7 +14297,7 @@
         <v>159</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G44" s="13">
         <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
@@ -14366,7 +14310,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B45" s="12">
         <f>G45</f>
@@ -14383,7 +14327,7 @@
         <v>159</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G45" s="13">
         <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
@@ -14396,7 +14340,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B46" s="12">
         <f>G46</f>
@@ -14413,7 +14357,7 @@
         <v>159</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G46" s="13">
         <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
@@ -14426,7 +14370,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B47" s="12">
         <f>G47</f>
@@ -14443,7 +14387,7 @@
         <v>155</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G47" s="13">
         <f>'Prefill_8K'!$AF$23</f>
@@ -14456,7 +14400,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B48" s="12">
         <f>IF(ABS(G48)&gt;=1E12,G48/1E12,IF(ABS(G48)&gt;=1E9,G48/1E9,IF(ABS(G48)&gt;=1E6,G48/1E6,IF(ABS(G48)&gt;=1E3,G48/1E3,G48))))</f>
@@ -14475,7 +14419,7 @@
         <v>MB</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G48" s="13">
         <f>'Prefill_8K'!$AF$21</f>
@@ -14488,7 +14432,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B49" s="12">
         <f>G49</f>
@@ -14505,7 +14449,7 @@
         <v>159</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G49" s="13">
         <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
@@ -14518,7 +14462,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B50" s="12">
         <f>IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50))))</f>
@@ -14537,7 +14481,7 @@
         <v>G params</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G50" s="13">
         <f>'Memory'!$Q$18</f>
@@ -14550,7 +14494,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B51" s="12">
         <f>IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51))))</f>
@@ -14569,7 +14513,7 @@
         <v>G params</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G51" s="13">
         <f>'Memory'!$Q$19</f>
@@ -14582,7 +14526,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B52" s="12">
         <f>IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52))))</f>
@@ -14601,7 +14545,7 @@
         <v>M params</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G52" s="13">
         <f>'Memory'!$Q$20</f>
@@ -14614,7 +14558,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="14" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B53" s="14">
         <f>IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53))))</f>
@@ -14633,7 +14577,7 @@
         <v>G params</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G53" s="13">
         <f>'Memory'!$Q$21</f>
@@ -14646,7 +14590,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B54" s="12">
         <f>IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54))))</f>
@@ -14665,7 +14609,7 @@
         <v>GB</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G54" s="13">
         <f>'Memory'!$S$18</f>
@@ -14678,7 +14622,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B55" s="12">
         <f>IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55))))</f>
@@ -14697,7 +14641,7 @@
         <v>GB</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G55" s="13">
         <f>'Memory'!$S$19</f>
@@ -14710,7 +14654,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B56" s="12">
         <f>IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56))))</f>
@@ -14729,7 +14673,7 @@
         <v>MB</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G56" s="13">
         <f>'Memory'!$S$20</f>
@@ -14742,7 +14686,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="14" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B57" s="14">
         <f>IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57))))</f>
@@ -14761,7 +14705,7 @@
         <v>GB</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G57" s="13">
         <f>'Memory'!$S$21</f>
@@ -14774,7 +14718,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B58" s="12">
         <f>IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58))))</f>
@@ -14793,7 +14737,7 @@
         <v>GB</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G58" s="13">
         <f>'Memory'!$Q$26</f>
@@ -14806,7 +14750,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B59" s="12">
         <f>IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59))))</f>
@@ -14825,7 +14769,7 @@
         <v>GB</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G59" s="13">
         <f>'Memory'!$Q$27</f>
@@ -14838,7 +14782,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B60" s="12">
         <f>IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60))))</f>
@@ -14857,7 +14801,7 @@
         <v>MB</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G60" s="13">
         <f>'Memory'!$Q$28</f>
@@ -14870,7 +14814,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B61" s="12">
         <f>IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61))))</f>
@@ -14889,7 +14833,7 @@
         <v>GB</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G61" s="13">
         <f>'Memory'!$Q$29</f>
@@ -14902,7 +14846,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B62" s="14">
         <f>IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62))))</f>
@@ -14921,7 +14865,7 @@
         <v>GB</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G62" s="13">
         <f>'Memory'!$S$21+'Memory'!$Q$29</f>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,33 +98,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="547">
-  <si>
-    <t>DeepSeek V4 Flash - 可编辑架构参数</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="542">
+  <si>
+    <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
   <si>
     <t>蓝色单元格为可编辑输入，绿色单元格为 Excel 派生公式。</t>
   </si>
   <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>参数</t>
-  </si>
-  <si>
-    <t>Excel 名称</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>并行</t>
-  </si>
-  <si>
-    <t>TP1 对比规模</t>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Excel name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Parallel</t>
+  </si>
+  <si>
+    <t>TP1 comparison size</t>
   </si>
   <si>
     <t>TP1Size</t>
@@ -133,7 +133,7 @@
     <t>第一组张量并行配置。</t>
   </si>
   <si>
-    <t>TP8 对比规模</t>
+    <t>TP8 comparison size</t>
   </si>
   <si>
     <t>TP8Size</t>
@@ -142,10 +142,10 @@
     <t>第二组张量并行配置，可编辑。</t>
   </si>
   <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>预填充批大小</t>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Prefill batch size</t>
   </si>
   <si>
     <t>PrefillBatch</t>
@@ -154,7 +154,7 @@
     <t>可编辑的预填充批大小。</t>
   </si>
   <si>
-    <t>预填充序列长度</t>
+    <t>Prefill sequence length</t>
   </si>
   <si>
     <t>PrefillSequence</t>
@@ -163,7 +163,7 @@
     <t>一次预填充处理的提示词令牌数。</t>
   </si>
   <si>
-    <t>解码批大小</t>
+    <t>Decode batch size</t>
   </si>
   <si>
     <t>DecodeBatch</t>
@@ -172,7 +172,7 @@
     <t>可编辑的解码批大小。</t>
   </si>
   <si>
-    <t>每个解码步骤的令牌数</t>
+    <t>Decode tokens per step</t>
   </si>
   <si>
     <t>DecodeTokens</t>
@@ -181,7 +181,7 @@
     <t>通常为 1；公式按解码上下文长度建模每个令牌。</t>
   </si>
   <si>
-    <t>解码上下文长度</t>
+    <t>Decode context</t>
   </si>
   <si>
     <t>DecodeContext</t>
@@ -190,7 +190,7 @@
     <t>解码阶段可见的有效上下文长度。</t>
   </si>
   <si>
-    <t>最大预分配上下文长度</t>
+    <t>Maximum allocated context</t>
   </si>
   <si>
     <t>MaxContext</t>
@@ -199,10 +199,10 @@
     <t>KV 缓存的预分配容量。</t>
   </si>
   <si>
-    <t>模型</t>
-  </si>
-  <si>
-    <t>隐藏维度</t>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Hidden size</t>
   </si>
   <si>
     <t>HiddenSize</t>
@@ -211,7 +211,7 @@
     <t>Transformer 残差宽度。</t>
   </si>
   <si>
-    <t>词表大小</t>
+    <t>Vocabulary size</t>
   </si>
   <si>
     <t>VocabSize</t>
@@ -220,10 +220,10 @@
     <t>Embedding 与 LM Head 使用的词表大小。</t>
   </si>
   <si>
-    <t>注意力</t>
-  </si>
-  <si>
-    <t>查询头数</t>
+    <t>Attention</t>
+  </si>
+  <si>
+    <t>Query heads</t>
   </si>
   <si>
     <t>NumHeads</t>
@@ -232,7 +232,7 @@
     <t>全局 Query 头数量。</t>
   </si>
   <si>
-    <t>头维度</t>
+    <t>Head dimension</t>
   </si>
   <si>
     <t>HeadDim</t>
@@ -241,7 +241,7 @@
     <t>共享潜在 KV 宽度及每个 Query 头的宽度。</t>
   </si>
   <si>
-    <t>RoPE 维度</t>
+    <t>RoPE dimension</t>
   </si>
   <si>
     <t>RopeDim</t>
@@ -250,7 +250,7 @@
     <t>HeadDim 中用于旋转位置编码的维度。</t>
   </si>
   <si>
-    <t>Q LoRA 秩</t>
+    <t>Q LoRA rank</t>
   </si>
   <si>
     <t>QLoraRank</t>
@@ -259,7 +259,7 @@
     <t>Q 投影的低秩中间宽度。</t>
   </si>
   <si>
-    <t>输出分组数</t>
+    <t>Output groups</t>
   </si>
   <si>
     <t>OGroups</t>
@@ -268,7 +268,7 @@
     <t>分组低秩输出投影的分组数量。</t>
   </si>
   <si>
-    <t>输出 LoRA 秩</t>
+    <t>Output LoRA rank</t>
   </si>
   <si>
     <t>OLoraRank</t>
@@ -277,10 +277,10 @@
     <t>每个输出分组的低秩宽度。</t>
   </si>
   <si>
-    <t>混合专家</t>
-  </si>
-  <si>
-    <t>路由专家数</t>
+    <t>MoE</t>
+  </si>
+  <si>
+    <t>Routed experts</t>
   </si>
   <si>
     <t>RoutedExperts</t>
@@ -289,7 +289,7 @@
     <t>每个专家块的全局路由专家数量。</t>
   </si>
   <si>
-    <t>激活专家数</t>
+    <t>Activated experts</t>
   </si>
   <si>
     <t>ActivatedExperts</t>
@@ -298,7 +298,7 @@
     <t>每个令牌选取的 Top-K 路由专家数量。</t>
   </si>
   <si>
-    <t>共享专家数</t>
+    <t>Shared experts</t>
   </si>
   <si>
     <t>SharedExperts</t>
@@ -307,7 +307,7 @@
     <t>每个专家块复制的共享专家数量。</t>
   </si>
   <si>
-    <t>专家中间维度</t>
+    <t>Expert intermediate size</t>
   </si>
   <si>
     <t>ExpertInter</t>
@@ -316,10 +316,10 @@
     <t>SwiGLU 专家的中间维度。</t>
   </si>
   <si>
-    <t>缓存</t>
-  </si>
-  <si>
-    <t>原始滑动窗口</t>
+    <t>Cache</t>
+  </si>
+  <si>
+    <t>Raw sliding window</t>
   </si>
   <si>
     <t>WindowSize</t>
@@ -328,7 +328,7 @@
     <t>每层保留的原始 KV 位置数量。</t>
   </si>
   <si>
-    <t>短压缩比例</t>
+    <t>Short compression ratio</t>
   </si>
   <si>
     <t>ShortRatio</t>
@@ -337,7 +337,7 @@
     <t>默认的 ratio-4 模式。</t>
   </si>
   <si>
-    <t>长压缩比例</t>
+    <t>Long compression ratio</t>
   </si>
   <si>
     <t>LongRatio</t>
@@ -346,10 +346,10 @@
     <t>默认的 ratio-128 模式。</t>
   </si>
   <si>
-    <t>索引器</t>
-  </si>
-  <si>
-    <t>索引头数</t>
+    <t>Indexer</t>
+  </si>
+  <si>
+    <t>Indexer heads</t>
   </si>
   <si>
     <t>IndexHeads</t>
@@ -358,7 +358,7 @@
     <t>全局 ratio-4 Indexer 头数量。</t>
   </si>
   <si>
-    <t>索引头维度</t>
+    <t>Indexer head dimension</t>
   </si>
   <si>
     <t>IndexHeadDim</t>
@@ -379,7 +379,7 @@
     <t>HC</t>
   </si>
   <si>
-    <t>HC 槽位数</t>
+    <t>HC slots</t>
   </si>
   <si>
     <t>HCSlots</t>
@@ -388,7 +388,7 @@
     <t>Hyper-Connection 残差流数量。</t>
   </si>
   <si>
-    <t>Sinkhorn 迭代次数</t>
+    <t>Sinkhorn iterations</t>
   </si>
   <si>
     <t>HCIters</t>
@@ -397,10 +397,10 @@
     <t>HC 组合归一化的迭代次数。</t>
   </si>
   <si>
-    <t>路由</t>
-  </si>
-  <si>
-    <t>哈希路由层数</t>
+    <t>Routing</t>
+  </si>
+  <si>
+    <t>Hash-routed layers</t>
   </si>
   <si>
     <t>HashLayers</t>
@@ -409,10 +409,10 @@
     <t>使用令牌编号到专家编号的路由起始层数量。</t>
   </si>
   <si>
-    <t>数据类型</t>
-  </si>
-  <si>
-    <t>BF16 字节数</t>
+    <t>DType</t>
+  </si>
+  <si>
+    <t>BF16 bytes</t>
   </si>
   <si>
     <t>BF16Bytes</t>
@@ -421,7 +421,7 @@
     <t>每个 BF16 元素占用的存储字节数。</t>
   </si>
   <si>
-    <t>FP32 字节数</t>
+    <t>FP32 bytes</t>
   </si>
   <si>
     <t>FP32Bytes</t>
@@ -430,7 +430,7 @@
     <t>每个 FP32 元素占用的存储字节数。</t>
   </si>
   <si>
-    <t>FP8 字节数</t>
+    <t>FP8 bytes</t>
   </si>
   <si>
     <t>FP8Bytes</t>
@@ -439,7 +439,7 @@
     <t>每个 FP8 元素占用的存储字节数。</t>
   </si>
   <si>
-    <t>FP4 字节数</t>
+    <t>FP4 bytes</t>
   </si>
   <si>
     <t>FP4Bytes</t>
@@ -448,7 +448,7 @@
     <t>每个 FP4 元素的逻辑打包字节数。</t>
   </si>
   <si>
-    <t>Scale 字节数</t>
+    <t>Scale bytes</t>
   </si>
   <si>
     <t>ScaleBytes</t>
@@ -457,7 +457,7 @@
     <t>E8M0 Scale 的存储字节数。</t>
   </si>
   <si>
-    <t>INT32 字节数</t>
+    <t>INT32 bytes</t>
   </si>
   <si>
     <t>INT32Bytes</t>
@@ -466,7 +466,7 @@
     <t>每个 INT32 元素占用的存储字节数。</t>
   </si>
   <si>
-    <t>INT64 字节数</t>
+    <t>INT64 bytes</t>
   </si>
   <si>
     <t>INT64Bytes</t>
@@ -475,10 +475,10 @@
     <t>每个 INT64 元素占用的存储字节数。</t>
   </si>
   <si>
-    <t>量化</t>
-  </si>
-  <si>
-    <t>FP8 Scale 分块大小</t>
+    <t>Quantization</t>
+  </si>
+  <si>
+    <t>FP8 scale block</t>
   </si>
   <si>
     <t>FP8Block</t>
@@ -487,7 +487,7 @@
     <t>二维 FP8 权重 Scale 的分块大小。</t>
   </si>
   <si>
-    <t>FP4 Scale 分块大小</t>
+    <t>FP4 scale block</t>
   </si>
   <si>
     <t>FP4Block</t>
@@ -496,10 +496,10 @@
     <t>沿 K 维度的 FP4 专家 Scale 分块大小。</t>
   </si>
   <si>
-    <t>内核</t>
-  </si>
-  <si>
-    <t>稀疏注意力最小头数</t>
+    <t>Kernel</t>
+  </si>
+  <si>
+    <t>Minimum sparse-attention heads</t>
   </si>
   <si>
     <t>KernelMinHeads</t>
@@ -508,10 +508,10 @@
     <t>当本地头数不足时，内核补齐到该头数。</t>
   </si>
   <si>
-    <t>硬件</t>
-  </si>
-  <si>
-    <t>峰值算力</t>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Peak compute</t>
   </si>
   <si>
     <t>PeakTFLOPs</t>
@@ -520,7 +520,7 @@
     <t>可编辑的示例硬件峰值算力。</t>
   </si>
   <si>
-    <t>HBM 带宽</t>
+    <t>HBM bandwidth</t>
   </si>
   <si>
     <t>HBMBandwidthGBps</t>
@@ -529,7 +529,7 @@
     <t>可编辑的持续/目标 HBM 带宽。</t>
   </si>
   <si>
-    <t>卡间互连带宽</t>
+    <t>Interconnect bandwidth</t>
   </si>
   <si>
     <t>InterconnectGBps</t>
@@ -538,7 +538,7 @@
     <t>可编辑的有效双向互连带宽。</t>
   </si>
   <si>
-    <t>预填充目标延迟</t>
+    <t>Prefill target latency</t>
   </si>
   <si>
     <t>PrefillTargetMs</t>
@@ -547,16 +547,16 @@
     <t>仅用于推导所需 HBM 带宽和卡间互连带宽。</t>
   </si>
   <si>
-    <t>解码目标延迟</t>
+    <t>Decode target latency</t>
   </si>
   <si>
     <t>DecodeTargetMs</t>
   </si>
   <si>
-    <t>派生</t>
-  </si>
-  <si>
-    <t>有效层数</t>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>Active layers</t>
   </si>
   <si>
     <t>TotalLayers</t>
@@ -565,7 +565,7 @@
     <t>Layer_Config 中启用的层数。</t>
   </si>
   <si>
-    <t>仅窗口层数</t>
+    <t>Window-only layers</t>
   </si>
   <si>
     <t>WindowLayers</t>
@@ -574,7 +574,7 @@
     <t>启用的窗口模式层数。</t>
   </si>
   <si>
-    <t>短压缩层数</t>
+    <t>Short-compression layers</t>
   </si>
   <si>
     <t>ShortLayers</t>
@@ -583,7 +583,7 @@
     <t>启用的 ratio-4/短压缩层数。</t>
   </si>
   <si>
-    <t>长压缩层数</t>
+    <t>Long-compression layers</t>
   </si>
   <si>
     <t>LongLayers</t>
@@ -592,7 +592,7 @@
     <t>启用的 ratio-128/长压缩层数。</t>
   </si>
   <si>
-    <t>有效哈希层数</t>
+    <t>Active hash layers</t>
   </si>
   <si>
     <t>ActiveHashLayers</t>
@@ -601,7 +601,7 @@
     <t>层 ID 小于 HashLayers 且已启用的层数。</t>
   </si>
   <si>
-    <t>TP1 本地 Q 头数</t>
+    <t>TP1 local Q heads</t>
   </si>
   <si>
     <t>TP1LocalHeads</t>
@@ -610,7 +610,7 @@
     <t>单个 TP1 Rank 上的 Q 头数。</t>
   </si>
   <si>
-    <t>TP1 内核本地头数</t>
+    <t>TP1 kernel local heads</t>
   </si>
   <si>
     <t>TP1KernelLocalHeads</t>
@@ -619,7 +619,7 @@
     <t>补齐后的稀疏内核本地头数。</t>
   </si>
   <si>
-    <t>TP1 本地索引头数</t>
+    <t>TP1 local index heads</t>
   </si>
   <si>
     <t>TP1LocalIndexHeads</t>
@@ -628,7 +628,7 @@
     <t>单个 TP1 Rank 上的 Indexer 头数。</t>
   </si>
   <si>
-    <t>TP1 本地专家数</t>
+    <t>TP1 local experts</t>
   </si>
   <si>
     <t>TP1LocalExperts</t>
@@ -637,7 +637,7 @@
     <t>单个 TP1 Rank 上的路由专家数。</t>
   </si>
   <si>
-    <t>TP1 本地输出分组数</t>
+    <t>TP1 local output groups</t>
   </si>
   <si>
     <t>TP1LocalOGroups</t>
@@ -646,7 +646,7 @@
     <t>单个 TP1 Rank 上的输出分组数。</t>
   </si>
   <si>
-    <t>TP1 本地词表大小</t>
+    <t>TP1 local vocabulary</t>
   </si>
   <si>
     <t>TP1LocalVocab</t>
@@ -655,7 +655,7 @@
     <t>单个 TP1 Rank 上的词表行数。</t>
   </si>
   <si>
-    <t>TP8 本地 Q 头数</t>
+    <t>TP8 local Q heads</t>
   </si>
   <si>
     <t>TP8LocalHeads</t>
@@ -664,13 +664,13 @@
     <t>单个 TP8 Rank 上的 Q 头数。</t>
   </si>
   <si>
-    <t>TP8 内核本地头数</t>
+    <t>TP8 kernel local heads</t>
   </si>
   <si>
     <t>TP8KernelLocalHeads</t>
   </si>
   <si>
-    <t>TP8 本地索引头数</t>
+    <t>TP8 local index heads</t>
   </si>
   <si>
     <t>TP8LocalIndexHeads</t>
@@ -679,7 +679,7 @@
     <t>单个 TP8 Rank 上的 Indexer 头数。</t>
   </si>
   <si>
-    <t>TP8 本地专家数</t>
+    <t>TP8 local experts</t>
   </si>
   <si>
     <t>TP8LocalExperts</t>
@@ -688,7 +688,7 @@
     <t>单个 TP8 Rank 上的路由专家数。</t>
   </si>
   <si>
-    <t>TP8 本地输出分组数</t>
+    <t>TP8 local output groups</t>
   </si>
   <si>
     <t>TP8LocalOGroups</t>
@@ -697,7 +697,7 @@
     <t>单个 TP8 Rank 上的输出分组数。</t>
   </si>
   <si>
-    <t>TP8 本地词表大小</t>
+    <t>TP8 local vocabulary</t>
   </si>
   <si>
     <t>TP8LocalVocab</t>
@@ -706,70 +706,70 @@
     <t>单个 TP8 Rank 上的词表行数。</t>
   </si>
   <si>
-    <t>8K 预填充 - TP1 与 TP8 推理对比</t>
+    <t>8K Prefill - TP1 vs TP8 inference comparison</t>
   </si>
   <si>
     <t>仅推理：不包含反向传播、梯度、优化器或训练状态内存。第 3 行以下可滚动查看。</t>
   </si>
   <si>
-    <t>辅助指标</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>令牌行数</t>
-  </si>
-  <si>
-    <t>令牌行</t>
+    <t>Helper metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Token rows</t>
+  </si>
+  <si>
+    <t>token rows</t>
   </si>
   <si>
     <t>当前场景需要处理的令牌总数；预填充为批大小乘序列长度，解码为批大小乘每步令牌数。</t>
   </si>
   <si>
-    <t>因果原始窗口对数</t>
-  </si>
-  <si>
-    <t>对数/序列</t>
+    <t>Causal raw-window pairs</t>
+  </si>
+  <si>
+    <t>pairs/sequence</t>
   </si>
   <si>
     <t>因果原始窗口路径中可参与注意力计算的令牌对数量，按每个序列统计。</t>
   </si>
   <si>
-    <t>封顶短压缩对数</t>
+    <t>Capped short-compressed pairs</t>
   </si>
   <si>
     <t>短压缩路径的候选令牌对数量；按短压缩比例折叠，并受 Top-K 候选上限约束。</t>
   </si>
   <si>
-    <t>长压缩对数</t>
+    <t>Long-compressed pairs</t>
   </si>
   <si>
     <t>长压缩路径按长压缩比例折叠后的候选令牌对数量。</t>
   </si>
   <si>
-    <t>Indexer 扫描对数</t>
+    <t>Indexer scan pairs</t>
   </si>
   <si>
     <t>ratio-4 Indexer 评分时需要扫描的压缩条目数量，作为索引器计算量输入。</t>
   </si>
   <si>
-    <t>专家激活概率</t>
-  </si>
-  <si>
-    <t>概率</t>
+    <t>Expert activation probability</t>
+  </si>
+  <si>
+    <t>probability</t>
   </si>
   <si>
     <t>在当前场景令牌数下，单个路由专家至少被激活一次的概率，用于估算路由专家参数读取量。</t>
   </si>
   <si>
-    <t>推理计算明细</t>
-  </si>
-  <si>
-    <t>算子/项目</t>
-  </si>
-  <si>
-    <t>层范围</t>
+    <t>Inference calculation detail</t>
+  </si>
+  <si>
+    <t>Operator/item</t>
+  </si>
+  <si>
+    <t>Layer scope</t>
   </si>
   <si>
     <t>TP1 FLOPs</t>
@@ -784,91 +784,91 @@
     <t>TP8 HBM/rank</t>
   </si>
   <si>
-    <t>TP1 卡间互连</t>
-  </si>
-  <si>
-    <t>TP8 卡间互连/rank</t>
-  </si>
-  <si>
-    <t>统计类型</t>
-  </si>
-  <si>
-    <t>Q/K/O 投影</t>
-  </si>
-  <si>
-    <t>所有启用层</t>
-  </si>
-  <si>
-    <t>主要</t>
+    <t>TP1 Interconnect</t>
+  </si>
+  <si>
+    <t>TP8 Interconnect/rank</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Q/K/O projections</t>
+  </si>
+  <si>
+    <t>All active layers</t>
+  </si>
+  <si>
+    <t>Major</t>
   </si>
   <si>
     <t>Wq_a 和 Wkv 在每个 TP Rank 上复制；Wq_b/Wo_a/Wo_b 按 TP 分片。</t>
   </si>
   <si>
-    <t>稀疏注意力 QK + AV</t>
-  </si>
-  <si>
-    <t>窗口/短压缩/长压缩层组合</t>
+    <t>Sparse attention QK + AV</t>
+  </si>
+  <si>
+    <t>Window/short/long layer mix</t>
   </si>
   <si>
     <t>KV 在各头之间共享；每个 Rank 的内核头数包含最小头数补齐。</t>
   </si>
   <si>
-    <t>ratio-4 Indexer 投影</t>
-  </si>
-  <si>
-    <t>短压缩层</t>
+    <t>Ratio-4 Indexer projections</t>
   </si>
   <si>
     <t>Indexer Q 和令牌权重投影；仅 ratio-4 层使用。</t>
   </si>
   <si>
-    <t>ratio-4 Indexer 评分扫描</t>
+    <t>Ratio-4 Indexer score scan</t>
   </si>
   <si>
     <t>在选取 Top-K 前扫描所有已完成的 ratio-4 索引条目。</t>
   </si>
   <si>
-    <t>主 KV Compressor 投影</t>
-  </si>
-  <si>
-    <t>所有压缩 KV 层</t>
+    <t>Main KV compressor projections</t>
+  </si>
+  <si>
+    <t>All compressed-KV layers</t>
   </si>
   <si>
     <t>每个 TP Rank 都复制；ratio-4 使用重叠的 2 倍投影。</t>
   </si>
   <si>
-    <t>Indexer Compressor 投影</t>
+    <t>Indexer compressor projections</t>
   </si>
   <si>
     <t>复制的辅助 Compressor，用于构建 Indexer 缓存。</t>
   </si>
   <si>
-    <t>Router 评分投影</t>
+    <t>Router score projection</t>
   </si>
   <si>
     <t>即使是哈希路由层，源码仍会计算 Gate 分数。</t>
   </si>
   <si>
-    <t>Top-K 路由专家</t>
+    <t>Top-K routed experts</t>
   </si>
   <si>
     <t>每个 Rank 的均衡期望分配；参数读取使用专家至少被触发一次的概率。</t>
   </si>
   <si>
-    <t>共享专家</t>
+    <t>Shared expert</t>
   </si>
   <si>
     <t>共享专家在每个 TP Rank 上复制，并独立计算。</t>
   </si>
   <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>Hyper-Connections 与块归一化</t>
-  </si>
-  <si>
-    <t>辅助</t>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Hyper-Connections and block norms</t>
+  </si>
+  <si>
+    <t>Auxiliary</t>
   </si>
   <si>
     <t>HC 计算为近似值；sigmoid/exp 仅做定性跟踪。</t>
@@ -877,124 +877,124 @@
     <t>LM Head</t>
   </si>
   <si>
-    <t>模型尾部</t>
+    <t>Tail</t>
   </si>
   <si>
     <t>推理路径仅根据最后一个隐藏令牌计算 logits。</t>
   </si>
   <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>TP 集合通信</t>
-  </si>
-  <si>
-    <t>Embedding + 每个块 + LM Head</t>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>TP collectives</t>
+  </si>
+  <si>
+    <t>Embedding + each block + LM head</t>
   </si>
   <si>
     <t>TP=1 时为零。这是传输量，不是 HBM 流量。</t>
   </si>
   <si>
-    <t>场景汇总</t>
-  </si>
-  <si>
-    <t>指标</t>
+    <t>Scenario summary</t>
+  </si>
+  <si>
+    <t>Metric</t>
   </si>
   <si>
     <t>TP1</t>
   </si>
   <si>
-    <t>TP8/每 Rank</t>
-  </si>
-  <si>
-    <t>注意力主要 FLOPs</t>
-  </si>
-  <si>
-    <t>混合专家主要 FLOPs</t>
-  </si>
-  <si>
-    <t>其他推理 FLOPs</t>
-  </si>
-  <si>
-    <t>总推理 FLOPs</t>
-  </si>
-  <si>
-    <t>注意力 HBM 流量</t>
-  </si>
-  <si>
-    <t>混合专家 HBM 流量</t>
-  </si>
-  <si>
-    <t>其他 HBM 流量</t>
-  </si>
-  <si>
-    <t>总 HBM 流量</t>
-  </si>
-  <si>
-    <t>卡间互连传输量</t>
-  </si>
-  <si>
-    <t>算术强度</t>
-  </si>
-  <si>
-    <t>一次推理所需计算量</t>
-  </si>
-  <si>
-    <t>目标时延所需 HBM 带宽</t>
-  </si>
-  <si>
-    <t>1M 上下文解码 - TP1 与 TP8 推理对比</t>
-  </si>
-  <si>
-    <t>原始窗口候选数</t>
+    <t>TP8/rank</t>
+  </si>
+  <si>
+    <t>Attention major FLOPs</t>
+  </si>
+  <si>
+    <t>MoE major FLOPs</t>
+  </si>
+  <si>
+    <t>Other inference FLOPs</t>
+  </si>
+  <si>
+    <t>Total inference FLOPs</t>
+  </si>
+  <si>
+    <t>Attention HBM traffic</t>
+  </si>
+  <si>
+    <t>MoE HBM traffic</t>
+  </si>
+  <si>
+    <t>Other HBM traffic</t>
+  </si>
+  <si>
+    <t>Total HBM traffic</t>
+  </si>
+  <si>
+    <t>Interconnect transfer</t>
+  </si>
+  <si>
+    <t>Arithmetic intensity</t>
+  </si>
+  <si>
+    <t>One-inference compute demand</t>
+  </si>
+  <si>
+    <t>Required HBM at target</t>
+  </si>
+  <si>
+    <t>1M-context Decode - TP1 vs TP8 inference comparison</t>
+  </si>
+  <si>
+    <t>Raw-window candidates</t>
   </si>
   <si>
     <t>解码时原始滑动窗口可见的候选条目数量，受窗口大小和当前上下文长度限制。</t>
   </si>
   <si>
-    <t>短压缩 Top-K 候选数</t>
+    <t>Short-compressed Top-K candidates</t>
   </si>
   <si>
     <t>解码时短压缩路径最终保留的 Top-K 候选数量，取 Top-K 与已生成压缩条目数的较小值。</t>
   </si>
   <si>
-    <t>长压缩候选数</t>
+    <t>Long-compressed candidates</t>
   </si>
   <si>
     <t>解码时长压缩路径按长压缩比例生成的候选条目数量。</t>
   </si>
   <si>
-    <t>Indexer 扫描候选数</t>
+    <t>Indexer scan candidates</t>
   </si>
   <si>
     <t>解码时 ratio-4 Indexer 需要扫描的压缩条目数量，用于估算索引器评分计算量。</t>
   </si>
   <si>
-    <t>推理路径数据类型（dtype）总表</t>
+    <t>Inference-Path Data Types (dtype) Overview</t>
   </si>
   <si>
     <t>集中记录各算子模块的参数存储、激活类型和逐层注意力/路由模式。</t>
   </si>
   <si>
-    <t>数据类型（dtype）：模块级存储与计算类型</t>
-  </si>
-  <si>
-    <t>适用范围</t>
-  </si>
-  <si>
-    <t>模块/张量</t>
-  </si>
-  <si>
-    <t>落盘/参数存储</t>
-  </si>
-  <si>
-    <t>激活/中间计算</t>
-  </si>
-  <si>
-    <t>全局配置</t>
-  </si>
-  <si>
-    <t>torch_dtype / 主干激活</t>
+    <t>Data types (dtype): module-level storage and compute types</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Module/tensor</t>
+  </si>
+  <si>
+    <t>Checkpoint/parameter storage</t>
+  </si>
+  <si>
+    <t>Activation/intermediate computation</t>
+  </si>
+  <si>
+    <t>Global config</t>
+  </si>
+  <si>
+    <t>torch_dtype / main activations</t>
   </si>
   <si>
     <t>BF16</t>
@@ -1003,106 +1003,106 @@
     <t>config.json 的 torch_dtype=bfloat16；隐藏状态与残差主路径使用 BF16。</t>
   </si>
   <si>
-    <t>普通量化线性层</t>
-  </si>
-  <si>
-    <t>FP8 E4M3 + FP8 E8M0 缩放因子</t>
-  </si>
-  <si>
-    <t>动态 FP8 激活量化</t>
+    <t>Standard quantized linear layers</t>
+  </si>
+  <si>
+    <t>FP8 E4M3 + FP8 E8M0 scale factors</t>
+  </si>
+  <si>
+    <t>Dynamic FP8 activation quantization</t>
   </si>
   <si>
     <t>quantization_config：quant_method=fp8，fmt=e4m3，scale_fmt=ue8m0。</t>
   </si>
   <si>
-    <t>所有层 0-42</t>
-  </si>
-  <si>
-    <t>注意力主投影 wq_a/wq_b/wkv/wo_b</t>
-  </si>
-  <si>
-    <t>FP8 GEMM；输入由 BF16 动态量化</t>
+    <t>All layers 0-42</t>
+  </si>
+  <si>
+    <t>Main attention projections wq_a/wq_b/wkv/wo_b</t>
+  </si>
+  <si>
+    <t>FP8 GEMM; BF16 input dynamically quantized</t>
   </si>
   <si>
     <t>大多数注意力线性权重。</t>
   </si>
   <si>
-    <t>注意力输出投影 wo_a</t>
-  </si>
-  <si>
-    <t>BF16 张量积（einsum）</t>
+    <t>Attention output projection wo_a</t>
+  </si>
+  <si>
+    <t>BF16 tensor product (einsum)</t>
   </si>
   <si>
     <t>检查点中为 FP8，转换后在推理实现中按 BF16 使用。</t>
   </si>
   <si>
-    <t>RMSNorm 权重与归一化</t>
-  </si>
-  <si>
-    <t>权重 BF16；实现参数 FP32</t>
-  </si>
-  <si>
-    <t>FP32 计算，输出回 BF16</t>
+    <t>RMSNorm weights and normalization</t>
+  </si>
+  <si>
+    <t>BF16 weights; FP32 implementation parameters</t>
+  </si>
+  <si>
+    <t>FP32 compute, output cast to BF16</t>
   </si>
   <si>
     <t>Norm 计算先转 FP32 以提高稳定性。</t>
   </si>
   <si>
-    <t>ratio-4 / ratio-128 层</t>
-  </si>
-  <si>
-    <t>主 Compressor wkv/wgate/ape</t>
-  </si>
-  <si>
-    <t>检查点主要为 BF16；实现参数 FP32</t>
-  </si>
-  <si>
-    <t>FP32 压缩/softmax</t>
+    <t>Ratio-4 / ratio-128 layers</t>
+  </si>
+  <si>
+    <t>Main Compressor wkv/wgate/ape</t>
+  </si>
+  <si>
+    <t>Checkpoint mainly BF16; FP32 implementation parameters</t>
+  </si>
+  <si>
+    <t>FP32 compression/softmax</t>
   </si>
   <si>
     <t>Compressor 参数在推理实现中提升到 FP32。</t>
   </si>
   <si>
-    <t>ratio-4 层</t>
-  </si>
-  <si>
-    <t>Indexer 投影与评分</t>
-  </si>
-  <si>
-    <t>wq_b FP8；weights_proj BF16</t>
-  </si>
-  <si>
-    <t>QAT/FP4 模拟 QKV；评分 FP32</t>
+    <t>Ratio-4 layers</t>
+  </si>
+  <si>
+    <t>Indexer projections and scoring</t>
+  </si>
+  <si>
+    <t>wq_b FP8; weights_proj BF16</t>
+  </si>
+  <si>
+    <t>QAT/FP4 simulated QKV; FP32 scoring</t>
   </si>
   <si>
     <t>仅 ratio-4 层启用 Indexer。</t>
   </si>
   <si>
-    <t>路由专家 w1/w2/w3</t>
-  </si>
-  <si>
-    <t>FP4 E2M1 打包 + FP8 E8M0 缩放因子</t>
-  </si>
-  <si>
-    <t>FP4 GEMM；SwiGLU FP32；输出回 BF16</t>
+    <t>Routed experts w1/w2/w3</t>
+  </si>
+  <si>
+    <t>FP4 E2M1 packed + FP8 E8M0 scale factors</t>
+  </si>
+  <si>
+    <t>FP4 GEMM; SwiGLU FP32; output cast to BF16</t>
   </si>
   <si>
     <t>专家数据类型为 fp4；每个令牌激活 6 个路由专家。</t>
   </si>
   <si>
-    <t>共享专家 w1/w2/w3</t>
-  </si>
-  <si>
-    <t>FP8 GEMM；SwiGLU FP32</t>
+    <t>Shared experts w1/w2/w3</t>
+  </si>
+  <si>
+    <t>FP8 GEMM; SwiGLU FP32</t>
   </si>
   <si>
     <t>每层 1 个共享专家，跨 TP Rank 复制。</t>
   </si>
   <si>
-    <t>Router 分数/路由权重</t>
-  </si>
-  <si>
-    <t>偏置 FP32；哈希表 INT32</t>
+    <t>Router scores/routing weights</t>
+  </si>
+  <si>
+    <t>FP32 bias; INT32 hash table</t>
   </si>
   <si>
     <t>FP32</t>
@@ -1111,88 +1111,88 @@
     <t>sqrt(softplus) 评分、Top-K 和归一化在 FP32 中完成。</t>
   </si>
   <si>
-    <t>第 0-2 层</t>
-  </si>
-  <si>
-    <t>哈希路由表</t>
+    <t>Layers 0-2</t>
+  </si>
+  <si>
+    <t>Hash routing table</t>
   </si>
   <si>
     <t>INT32</t>
   </si>
   <si>
-    <t>INT32 索引</t>
+    <t>INT32 indexing</t>
   </si>
   <si>
     <t>前 3 层使用令牌编号到专家编号的预计算路由。</t>
   </si>
   <si>
-    <t>mHC 参数 / 注意力 Sink</t>
+    <t>mHC parameters / attention sinks</t>
   </si>
   <si>
     <t>HC 混合、Sinkhorn 与 Sink 参数使用 FP32。</t>
   </si>
   <si>
-    <t>KV 缓存</t>
-  </si>
-  <si>
-    <t>BF16；部分非 RoPE 维度使用 FP8 模拟</t>
+    <t>KV cache</t>
+  </si>
+  <si>
+    <t>BF16; partial non-RoPE dimensions simulated with FP8</t>
   </si>
   <si>
     <t>当前推理实现中的 KV 缓存为 BF16。</t>
   </si>
   <si>
-    <t>最终归一化 / HC Head</t>
-  </si>
-  <si>
-    <t>FP32 推理参数</t>
+    <t>Model tail</t>
+  </si>
+  <si>
+    <t>Final normalization / HC head</t>
+  </si>
+  <si>
+    <t>FP32 inference parameters</t>
   </si>
   <si>
     <t>最终 HC 归约与 RMSNorm。</t>
   </si>
   <si>
-    <t>LM Head / Logits</t>
-  </si>
-  <si>
-    <t>checkpoint BF16；实现参数 FP32</t>
-  </si>
-  <si>
-    <t>FP32 线性层与 Logits</t>
+    <t>LM head / Logits</t>
+  </si>
+  <si>
+    <t>Checkpoint BF16; FP32 implementation parameters</t>
+  </si>
+  <si>
+    <t>FP32 linear layer and Logits</t>
   </si>
   <si>
     <t>词表并行；Logits 以 FP32 计算。</t>
   </si>
   <si>
-    <t>43 层逐层 dtype、注意力与路由模式</t>
-  </si>
-  <si>
-    <t>层 ID</t>
-  </si>
-  <si>
-    <t>注意力模式</t>
-  </si>
-  <si>
-    <t>压缩比例</t>
-  </si>
-  <si>
-    <t>路由模式</t>
-  </si>
-  <si>
-    <t>隐藏状态 / 残差</t>
-  </si>
-  <si>
-    <t>注意力主投影</t>
-  </si>
-  <si>
-    <t>路由专家</t>
-  </si>
-  <si>
-    <t>归一化 / HC / Router 计算</t>
-  </si>
-  <si>
-    <t>窗口</t>
-  </si>
-  <si>
-    <t>哈希路由（INT32）</t>
+    <t>43-layer dtype, attention, and routing modes</t>
+  </si>
+  <si>
+    <t>Layer ID</t>
+  </si>
+  <si>
+    <t>Attention mode</t>
+  </si>
+  <si>
+    <t>Compression ratio</t>
+  </si>
+  <si>
+    <t>Routing mode</t>
+  </si>
+  <si>
+    <t>Hidden state / residual</t>
+  </si>
+  <si>
+    <t>Main attention projections</t>
+  </si>
+  <si>
+    <t>Normalization / HC / Router computation</t>
+  </si>
+  <si>
+    <t>Window</t>
+  </si>
+  <si>
+    <t>Hash routing (INT32)</t>
   </si>
   <si>
     <t>FP8 E4M3; wo_a BF16</t>
@@ -1204,52 +1204,49 @@
     <t>FP8 E4M3</t>
   </si>
   <si>
-    <t>短压缩稀疏</t>
-  </si>
-  <si>
-    <t>长压缩</t>
-  </si>
-  <si>
-    <t>评分路由（FP32）</t>
-  </si>
-  <si>
-    <t>参数与缓存：8K 预填充 参数与容量</t>
-  </si>
-  <si>
-    <t>大类</t>
-  </si>
-  <si>
-    <t>参数组件</t>
-  </si>
-  <si>
-    <t>全局参数量</t>
-  </si>
-  <si>
-    <t>TP1 参数量/rank</t>
-  </si>
-  <si>
-    <t>TP8 参数量/rank</t>
-  </si>
-  <si>
-    <t>TP1 容量/rank</t>
-  </si>
-  <si>
-    <t>TP8 容量/rank</t>
-  </si>
-  <si>
-    <t>核心 Q/K/O 投影</t>
+    <t>Short-compression sparse</t>
+  </si>
+  <si>
+    <t>Long-compression</t>
+  </si>
+  <si>
+    <t>Score routing (FP32)</t>
+  </si>
+  <si>
+    <t>Parameters and cache: 8K Prefill parameters and capacity</t>
+  </si>
+  <si>
+    <t>Parameter component</t>
+  </si>
+  <si>
+    <t>Global parameter count</t>
+  </si>
+  <si>
+    <t>TP1 parameter count/rank</t>
+  </si>
+  <si>
+    <t>TP8 parameter count/rank</t>
+  </si>
+  <si>
+    <t>TP1 capacity/rank</t>
+  </si>
+  <si>
+    <t>TP8 capacity/rank</t>
+  </si>
+  <si>
+    <t>Core Q/K/O projections</t>
   </si>
   <si>
     <t>Wq_a/Wkv 复制；Q/O 输出维度按 TP 分片。</t>
   </si>
   <si>
-    <t>KV 压缩器</t>
+    <t>KV compressors</t>
   </si>
   <si>
     <t>FP32 推理 Compressor 在每个 TP Rank 上复制。</t>
   </si>
   <si>
-    <t>ratio-4 Indexer</t>
+    <t>Ratio-4 Indexers</t>
   </si>
   <si>
     <t>Indexer Q/权重投影按 TP 分片；Indexer Compressor 复制。</t>
@@ -1261,7 +1258,7 @@
     <t>FP8 共享专家在每个 Rank 上复制。</t>
   </si>
   <si>
-    <t>Router 与哈希表</t>
+    <t>Router and hash tables</t>
   </si>
   <si>
     <t>Gate、偏置和令牌到专家的映射表在每个 Rank 上复制。</t>
@@ -1273,6 +1270,9 @@
     <t>Embedding 按词表维度并行。</t>
   </si>
   <si>
+    <t>LM head</t>
+  </si>
+  <si>
     <t>FP32 推理 LM Head 按词表维度并行。</t>
   </si>
   <si>
@@ -1282,184 +1282,175 @@
     <t>HC 参数在每个 Rank 上复制；仅用于推理。</t>
   </si>
   <si>
-    <t>归一化与注意力 Sink</t>
+    <t>Norms and attention sinks</t>
   </si>
   <si>
     <t>仅本地注意力 Sink 向量按 TP 分片。</t>
   </si>
   <si>
-    <t>尾部 HC 与最终归一化</t>
+    <t>Tail HC and final norm</t>
   </si>
   <si>
     <t>模型尾部推理参数在每个 Rank 上复制。</t>
   </si>
   <si>
-    <t>参数量与参数容量汇总</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>当前场景 KV 缓存与 Compressor 状态（每 Rank，TP 间复制）</t>
-  </si>
-  <si>
-    <t>项目</t>
+    <t>Parameter count and capacity summary</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Current scenario KV cache and Compressor state (per Rank, replicated across TP)</t>
+  </si>
+  <si>
+    <t>Item</t>
   </si>
   <si>
     <t>TP1/rank</t>
   </si>
   <si>
-    <t>TP8/rank</t>
-  </si>
-  <si>
-    <t>预填充有效主 KV 缓存</t>
+    <t>Prefill effective main KV</t>
   </si>
   <si>
     <t>预填充阶段已生成的主注意力 KV。</t>
   </si>
   <si>
-    <t>预填充有效 Indexer KV 缓存</t>
+    <t>Prefill effective Indexer KV</t>
   </si>
   <si>
     <t>预填充阶段已生成的 ratio-4 Indexer KV。</t>
   </si>
   <si>
-    <t>预填充 Compressor 状态</t>
+    <t>Prefill compressor states</t>
   </si>
   <si>
     <t>预填充阶段的 Compressor 与 Indexer 状态。</t>
   </si>
   <si>
-    <t>预填充预分配 KV + 状态</t>
+    <t>Prefill preallocated KV + states</t>
   </si>
   <si>
     <t>按 MaxContext 为预填充阶段预分配。</t>
   </si>
   <si>
-    <t>单 Rank 设备驻留容量（默认均匀分片）</t>
-  </si>
-  <si>
-    <t>配置</t>
+    <t>Per-rank device resident capacity (default even sharding)</t>
+  </si>
+  <si>
+    <t>Configuration</t>
   </si>
   <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>注意力参数</t>
-  </si>
-  <si>
-    <t>混合专家参数</t>
-  </si>
-  <si>
-    <t>其他参数</t>
-  </si>
-  <si>
-    <t>参数总计</t>
-  </si>
-  <si>
-    <t>当前场景 KV+状态</t>
-  </si>
-  <si>
-    <t>总驻留</t>
-  </si>
-  <si>
-    <t>逻辑参数量</t>
-  </si>
-  <si>
-    <t>有效</t>
-  </si>
-  <si>
-    <t>任一 Rank</t>
-  </si>
-  <si>
-    <t>1 个 Rank 均相同</t>
+    <t>Attention parameters</t>
+  </si>
+  <si>
+    <t>MoE parameters</t>
+  </si>
+  <si>
+    <t>Other parameters</t>
+  </si>
+  <si>
+    <t>Total parameters</t>
+  </si>
+  <si>
+    <t>Current scenario KV+state</t>
+  </si>
+  <si>
+    <t>Total resident</t>
+  </si>
+  <si>
+    <t>Logical parameter count</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Any Rank</t>
+  </si>
+  <si>
+    <t>All 1 ranks identical</t>
   </si>
   <si>
     <t>TP8</t>
   </si>
   <si>
-    <t>8 个 Rank 均相同</t>
-  </si>
-  <si>
-    <t>参数与缓存：1M 解码 参数与容量</t>
-  </si>
-  <si>
-    <t>解码有效主 KV 缓存</t>
+    <t>All 8 ranks identical</t>
+  </si>
+  <si>
+    <t>Parameters and cache: 1M-context Decode parameters and capacity</t>
+  </si>
+  <si>
+    <t>Decode effective main KV</t>
   </si>
   <si>
     <t>解码阶段的主注意力 KV。</t>
   </si>
   <si>
-    <t>解码有效 Indexer KV 缓存</t>
+    <t>Decode effective Indexer KV</t>
   </si>
   <si>
     <t>解码阶段的 ratio-4 Indexer KV。</t>
   </si>
   <si>
-    <t>解码 Compressor 状态</t>
+    <t>Decode compressor states</t>
   </si>
   <si>
     <t>解码阶段的 Compressor 与 Indexer 状态。</t>
   </si>
   <si>
-    <t>解码预分配 KV + 状态</t>
+    <t>Decode preallocated KV + states</t>
   </si>
   <si>
     <t>按 MaxContext 为解码阶段预分配。</t>
   </si>
   <si>
-    <t>TP1 / TP8 推理资源对比图</t>
+    <t>TP1 / TP8 Inference Resource Comparison Charts</t>
   </si>
   <si>
     <t>计算量、HBM、参数、缓存与驻留容量集中在一张资源表；隐藏列保留公式原值和图表缩放源。</t>
   </si>
   <si>
-    <t>资源项目</t>
-  </si>
-  <si>
-    <t>预填充 TP1</t>
-  </si>
-  <si>
-    <t>预填充 TP8/每 Rank</t>
-  </si>
-  <si>
-    <t>解码 TP1</t>
-  </si>
-  <si>
-    <t>解码 TP8/每 Rank</t>
-  </si>
-  <si>
-    <t>注意力计算量</t>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Prefill TP1</t>
+  </si>
+  <si>
+    <t>Prefill TP8/rank</t>
+  </si>
+  <si>
+    <t>Decode TP1</t>
+  </si>
+  <si>
+    <t>Decode TP8/rank</t>
+  </si>
+  <si>
+    <t>Attention FLOPs</t>
   </si>
   <si>
     <t>单次预填充或解码步骤的每 Rank 逻辑 FLOPs。</t>
   </si>
   <si>
-    <t>混合专家计算量</t>
-  </si>
-  <si>
-    <t>其他推理计算量</t>
-  </si>
-  <si>
-    <t>总推理计算量</t>
+    <t>MoE FLOPs</t>
   </si>
   <si>
     <t>本地逻辑 HBM 读写量，不含缓存复用和算子融合。</t>
   </si>
   <si>
-    <t>注意力所需 HBM 带宽</t>
+    <t>Attention required HBM bandwidth</t>
   </si>
   <si>
     <t>按参数页中的目标时延换算；不是实测带宽。</t>
   </si>
   <si>
-    <t>混合专家所需 HBM 带宽</t>
-  </si>
-  <si>
-    <t>其他所需 HBM 带宽</t>
-  </si>
-  <si>
-    <t>目标时延所需计算性能</t>
+    <t>MoE required HBM bandwidth</t>
+  </si>
+  <si>
+    <t>Other required HBM bandwidth</t>
+  </si>
+  <si>
+    <t>Compute required at target latency</t>
   </si>
   <si>
     <t>按目标时延折算的每 Rank 最低计算吞吐需求。</t>
@@ -1468,91 +1459,88 @@
     <t>Ring 集合通信每 Rank 发送加接收；TP1 为 0。</t>
   </si>
   <si>
-    <t>目标时延所需互连带宽</t>
+    <t>Required interconnect bandwidth</t>
   </si>
   <si>
     <t>未考虑通信与计算重叠、拓扑和协议效率。</t>
   </si>
   <si>
-    <t>注意力逻辑参数量</t>
+    <t>Attention logical parameter count</t>
   </si>
   <si>
     <t>注意力投影、Compressor、Indexer。</t>
   </si>
   <si>
-    <t>混合专家逻辑参数量</t>
+    <t>MoE logical parameter count</t>
   </si>
   <si>
     <t>路由/共享专家与 Router。</t>
   </si>
   <si>
-    <t>其他逻辑参数量</t>
+    <t>Other logical parameter count</t>
   </si>
   <si>
     <t>Embedding、LM Head、HC 与 Norm。</t>
   </si>
   <si>
-    <t>总逻辑参数量</t>
+    <t>Total logical parameter count</t>
   </si>
   <si>
     <t>不包含 MTP。</t>
   </si>
   <si>
-    <t>注意力参数容量</t>
+    <t>Attention parameter capacity</t>
   </si>
   <si>
     <t>按推理 dtype 与量化 Scale 计算。</t>
   </si>
   <si>
-    <t>混合专家参数容量</t>
+    <t>MoE parameter capacity</t>
   </si>
   <si>
     <t>路由专家 FP4、共享专家 FP8、Router 复制。</t>
   </si>
   <si>
-    <t>其他参数容量</t>
-  </si>
-  <si>
-    <t>总参数容量</t>
+    <t>Other parameter capacity</t>
+  </si>
+  <si>
+    <t>Total parameter capacity</t>
   </si>
   <si>
     <t>每 Rank 静态参数驻留。</t>
   </si>
   <si>
-    <t>有效主 KV 缓存</t>
+    <t>Effective main KV cache</t>
   </si>
   <si>
     <t>KV 与 Compressor 状态在当前实现中每个 TP Rank 复制。</t>
   </si>
   <si>
-    <t>有效 Indexer KV 缓存</t>
-  </si>
-  <si>
-    <t>Compressor 状态</t>
-  </si>
-  <si>
-    <t>预分配 KV + 状态</t>
-  </si>
-  <si>
-    <t>总驻留容量</t>
+    <t>Effective Indexer KV cache</t>
+  </si>
+  <si>
+    <t>Compressor State</t>
+  </si>
+  <si>
+    <t>Preallocated KV + state</t>
+  </si>
+  <si>
+    <t>Total resident capacity</t>
   </si>
   <si>
     <t>参数 + 按 MaxContext 预分配的 KV/状态；不含临时工作区。</t>
   </si>
   <si>
-    <t>一次推理所需芯片计算量</t>
-  </si>
-  <si>
     <t>单次推理调用的单 Rank 总 FLOPs；不除以目标时延。</t>
   </si>
   <si>
-    <t>单次推理 GFLOPs</t>
-  </si>
-  <si>
-    <t>预填充 TP8</t>
-  </si>
-  <si>
-    <t>解码 TP8</t>
+    <t>One-inference TFLOPs</t>
+  </si>
+  <si>
+    <t>Prefill TP8</t>
+  </si>
+  <si>
+    <t>Decode TP8</t>
   </si>
   <si>
     <t>TP1 TFLOPs</t>
@@ -1573,25 +1561,25 @@
     <t>TP8 GB</t>
   </si>
   <si>
-    <t>预填充</t>
-  </si>
-  <si>
-    <t>解码</t>
-  </si>
-  <si>
-    <t>单 Rank 推理硬件资源汇总</t>
+    <t>Prefill</t>
+  </si>
+  <si>
+    <t>Decode</t>
+  </si>
+  <si>
+    <t>Per-Rank Inference Hardware Resource Summary</t>
   </si>
   <si>
     <t>TP1 与 TP8 分区独立展示；所有值均为单个 Rank，不进行跨 Rank 或跨 TP 求和。</t>
   </si>
   <si>
-    <t>TP1（配置值=1）单 Rank 资源</t>
-  </si>
-  <si>
-    <t>预填充/每 Rank</t>
-  </si>
-  <si>
-    <t>解码/每 Rank</t>
+    <t>TP1 (configured size=1) per-rank resources</t>
+  </si>
+  <si>
+    <t>Prefill/rank</t>
+  </si>
+  <si>
+    <t>Decode/rank</t>
   </si>
   <si>
     <t>单次推理调用的单 Rank 计算量。</t>
@@ -1633,25 +1621,25 @@
     <t>参数 + 预分配 KV/状态；不含临时工作区。</t>
   </si>
   <si>
-    <t>TP8（配置值=8）单 Rank 资源</t>
-  </si>
-  <si>
-    <t>逐层注意力与路由配置</t>
+    <t>TP8 (configured size=8) per-rank resources</t>
+  </si>
+  <si>
+    <t>Per-Layer Attention and Routing Configuration</t>
   </si>
   <si>
     <t>可编辑启用状态和模式；压缩比例与路由行为会自动更新。</t>
   </si>
   <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>注意力行为</t>
-  </si>
-  <si>
-    <t>路由行为</t>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Attention behavior</t>
+  </si>
+  <si>
+    <t>Routing behavior</t>
   </si>
   <si>
     <t>window</t>
@@ -1663,34 +1651,31 @@
     <t>long</t>
   </si>
   <si>
-    <t>方法与统计边界</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>定义</t>
-  </si>
-  <si>
-    <t>统计范围</t>
+    <t>Methodology and Limits</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Definition</t>
   </si>
   <si>
     <t>仅统计 43 层主推理路径；不含 MTP、反向传播、梯度、优化器状态和训练激活。Layer_Config 最多可维护 64 层。</t>
   </si>
   <si>
-    <t>计算量</t>
+    <t>FLOPs</t>
   </si>
   <si>
     <t>矩阵乘加按 2 FLOPs 计。注意力与 MoE 主要 GEMM 使用显式公式；HC 与逐元素运算为近似估计。</t>
   </si>
   <si>
-    <t>预填充注意力</t>
+    <t>Prefill attention</t>
   </si>
   <si>
     <t>使用因果候选对数量，不直接使用 S×S；原始窗口、压缩 KV 和 Indexer 扫描分别统计。</t>
   </si>
   <si>
-    <t>解码注意力</t>
+    <t>Decode attention</t>
   </si>
   <si>
     <t>每个解码令牌在解码上下文长度下建模；ratio-4 主注意力取 Top-K，但 Indexer 需要扫描全部已完成压缩项。</t>
@@ -1699,13 +1684,13 @@
     <t>每个令牌执行 Top-K 路由专家和共享专家。HBM 参数读取按专家至少被命中一次的概率估计。</t>
   </si>
   <si>
-    <t>HBM 流量</t>
+    <t>HBM traffic</t>
   </si>
   <si>
     <t>统计本地逻辑参数、激活和 KV 的读取与写入；不模拟 L2 命中、算子融合、分块、Allocator 或厂商 Kernel 内部复用。</t>
   </si>
   <si>
-    <t>参数容量</t>
+    <t>Memory</t>
   </si>
   <si>
     <t>按推理运行 dtype 估算：路由专家 FP4、多数投影 FP8、Wo_a BF16、Compressor FP32、LM Head FP32，并计入量化 Scale。</t>
@@ -1714,28 +1699,28 @@
     <t>有效容量表示已填充项；预分配容量使用 MaxContext。当前实现的 KV 和 Compressor 状态在每个 TP Rank 上完整复制。</t>
   </si>
   <si>
-    <t>TP 分片</t>
+    <t>TP</t>
   </si>
   <si>
     <t>Wq_a、Wkv、Compressor、Router、HC、共享专家复制；Q/O 部分投影、路由专家、Embedding 和 LM Head 按 TP 分片。</t>
   </si>
   <si>
-    <t>卡间通信</t>
-  </si>
-  <si>
     <t>Ring 公式给出每 Rank 发送加接收的数据量。TP1 为 0；该数值是传输量，不是实测 GB/s 或时延。</t>
   </si>
   <si>
-    <t>硬件下界</t>
+    <t>Roofline</t>
   </si>
   <si>
     <t>计算/HBM/互连下界使用参数页中的可编辑硬件峰值并假设互不重叠；真实运行时间必须通过性能分析验证。</t>
   </si>
   <si>
+    <t>Units</t>
+  </si>
+  <si>
     <t>FLOPs 使用 M/G/T/P 十进制单位；容量与流量使用 KB/MB/GB/TB，1 GB=10^9 字节；场景页容量明细保留原始公式。</t>
   </si>
   <si>
-    <t>公式维护</t>
+    <t>Formula maintenance</t>
   </si>
   <si>
     <t>蓝色单元格为输入；结果由 Excel 公式计算并在打开时完整重算。隐藏列保留原始未缩放值，便于审计。</t>
@@ -1746,30 +1731,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="29">
-    <numFmt numFmtId="164" formatCode="0.######## &quot;Rank&quot;"/>
-    <numFmt numFmtId="165" formatCode="0.######## &quot;序列&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.######## &quot;令牌&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.######## &quot;元素&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.######## &quot;头&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.######## &quot;组&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.######## &quot;专家&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.######## &quot;专家/令牌&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.######## &quot;令牌/条目&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.######## &quot;条目&quot;"/>
-    <numFmt numFmtId="174" formatCode="0.######## &quot;流&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.######## &quot;迭代&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.######## &quot;层&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.######## &quot;字节&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.######## &quot;ranks&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.######## &quot;sequences&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.######## &quot;tokens&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.######## &quot;elements&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.######## &quot;heads&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.######## &quot;groups&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.######## &quot;experts&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.######## &quot;experts/token&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.######## &quot;tokens/entry&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.######## &quot;entries&quot;"/>
+    <numFmt numFmtId="174" formatCode="0.######## &quot;streams&quot;"/>
+    <numFmt numFmtId="175" formatCode="0.######## &quot;iterations&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.######## &quot;layers&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.######## &quot;bytes&quot;"/>
     <numFmt numFmtId="178" formatCode="0.######## &quot;TFLOP/s&quot;"/>
     <numFmt numFmtId="179" formatCode="0.######## &quot;GB/s&quot;"/>
     <numFmt numFmtId="180" formatCode="0.######## &quot;ms&quot;"/>
-    <numFmt numFmtId="181" formatCode="0.######## &quot;头/Rank&quot;"/>
-    <numFmt numFmtId="182" formatCode="0.######## &quot;专家/Rank&quot;"/>
-    <numFmt numFmtId="183" formatCode="0.######## &quot;组/Rank&quot;"/>
-    <numFmt numFmtId="184" formatCode="0.######## &quot;令牌/Rank&quot;"/>
-    <numFmt numFmtId="185" formatCode="0.######## &quot;令牌行&quot;"/>
-    <numFmt numFmtId="186" formatCode="0.######## &quot;对数/序列&quot;"/>
-    <numFmt numFmtId="187" formatCode="0.######## &quot;概率&quot;"/>
+    <numFmt numFmtId="181" formatCode="0.######## &quot;heads/rank&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.######## &quot;experts/rank&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.######## &quot;groups/rank&quot;"/>
+    <numFmt numFmtId="184" formatCode="0.######## &quot;tokens/rank&quot;"/>
+    <numFmt numFmtId="185" formatCode="0.######## &quot;token rows&quot;"/>
+    <numFmt numFmtId="186" formatCode="0.######## &quot;pairs/sequence&quot;"/>
+    <numFmt numFmtId="187" formatCode="0.######## &quot;probability&quot;"/>
     <numFmt numFmtId="188" formatCode="#,##0.000"/>
     <numFmt numFmtId="189" formatCode="#,##0.000 &quot;GB&quot;"/>
     <numFmt numFmtId="190" formatCode="#,##0.000 &quot;G&quot;"/>
@@ -1955,7 +1940,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>一次推理所需总计算量/单 Rank</a:t>
+              <a:t>Total compute per inference / rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1971,10 +1956,10 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>单次推理 GFLOPs</c:v>
+            <c:v>One-inference TFLOPs</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1983,16 +1968,16 @@
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>预填充 TP1</c:v>
+                  <c:v>Prefill TP1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>预填充 TP8</c:v>
+                  <c:v>Prefill TP8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>解码 TP1</c:v>
+                  <c:v>Decode TP1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>解码 TP8</c:v>
+                  <c:v>Decode TP8</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2004,21 +1989,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>228384.427393024</c:v>
+                  <c:v>228.384427393024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55639.31418624</c:v>
+                  <c:v>55.63931418624</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>140.354134102</c:v>
+                  <c:v>0.140354134102</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.548076118</c:v>
+                  <c:v>0.023548076118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
@@ -2053,14 +2039,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>GFLOPs</a:t>
+                  <a:t>TFLOPs</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -2096,7 +2082,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>预填充每 Rank 计算量</a:t>
+              <a:t>Prefill compute per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2124,13 +2110,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2170,13 +2156,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2200,6 +2186,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:barChart>
@@ -2277,7 +2264,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>解码每 Rank 计算量</a:t>
+              <a:t>Decode compute per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2305,13 +2292,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2351,13 +2338,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2381,6 +2368,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:barChart>
@@ -2458,7 +2446,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>预填充每 Rank HBM 流量</a:t>
+              <a:t>Prefill HBM traffic per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2486,13 +2474,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2532,13 +2520,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2562,6 +2550,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50040001"/>
         <c:axId val="50040002"/>
       </c:barChart>
@@ -2639,7 +2628,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>解码每 Rank HBM 流量</a:t>
+              <a:t>Decode HBM traffic per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2667,13 +2656,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2713,13 +2702,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2743,6 +2732,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50050001"/>
         <c:axId val="50050002"/>
       </c:barChart>
@@ -2820,7 +2810,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>静态参数容量/单 Rank</a:t>
+              <a:t>Static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2848,13 +2838,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2894,13 +2884,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>注意力</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>混合专家</c:v>
+                  <c:v>MoE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>其他</c:v>
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2924,6 +2914,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50060001"/>
         <c:axId val="50060002"/>
       </c:barChart>
@@ -3001,7 +2992,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>TP1 vs TP8：单 Rank 推理驻留容量</a:t>
+              <a:t>TP1 vs TP8: inference resident capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3029,10 +3020,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>预填充</c:v>
+                  <c:v>Prefill</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>解码</c:v>
+                  <c:v>Decode</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3069,10 +3060,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>预填充</c:v>
+                  <c:v>Prefill</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>解码</c:v>
+                  <c:v>Decode</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3093,6 +3084,7 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapWidth val="30"/>
         <c:axId val="50070001"/>
         <c:axId val="50070002"/>
       </c:barChart>
@@ -3373,17 +3365,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PF_Inference_Detail" displayName="PF_Inference_Detail" ref="A32:K44" totalsRowShown="0">
   <autoFilter ref="A32:K44"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="类别"/>
-    <tableColumn id="2" name="算子/项目"/>
-    <tableColumn id="3" name="层范围"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Operator/item"/>
+    <tableColumn id="3" name="Layer scope"/>
     <tableColumn id="4" name="TP1 FLOPs"/>
     <tableColumn id="5" name="TP8 FLOPs/rank"/>
     <tableColumn id="6" name="TP1 HBM/rank"/>
     <tableColumn id="7" name="TP8 HBM/rank"/>
-    <tableColumn id="8" name="TP1 卡间互连"/>
-    <tableColumn id="9" name="TP8 卡间互连/rank"/>
-    <tableColumn id="10" name="统计类型"/>
-    <tableColumn id="11" name="说明"/>
+    <tableColumn id="8" name="TP1 Interconnect"/>
+    <tableColumn id="9" name="TP8 Interconnect/rank"/>
+    <tableColumn id="10" name="Accounting"/>
+    <tableColumn id="11" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3393,16 +3385,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DC_Embedded_Rank_Memory" displayName="DC_Embedded_Rank_Memory" ref="A77:J79" totalsRowShown="0">
   <autoFilter ref="A77:J79"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="配置"/>
+    <tableColumn id="1" name="Configuration"/>
     <tableColumn id="2" name="Rank"/>
-    <tableColumn id="3" name="注意力参数"/>
-    <tableColumn id="4" name="混合专家参数"/>
-    <tableColumn id="5" name="其他参数"/>
-    <tableColumn id="6" name="参数总计"/>
-    <tableColumn id="7" name="当前场景 KV+状态"/>
-    <tableColumn id="8" name="总驻留"/>
-    <tableColumn id="9" name="逻辑参数量"/>
-    <tableColumn id="10" name="有效"/>
+    <tableColumn id="3" name="Attention parameters"/>
+    <tableColumn id="4" name="MoE parameters"/>
+    <tableColumn id="5" name="Other parameters"/>
+    <tableColumn id="6" name="Total parameters"/>
+    <tableColumn id="7" name="Current scenario KV+state"/>
+    <tableColumn id="8" name="Total resident"/>
+    <tableColumn id="9" name="Logical parameter count"/>
+    <tableColumn id="10" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3412,11 +3404,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DType_Module" displayName="DType_Module" ref="A5:E20" totalsRowShown="0">
   <autoFilter ref="A5:E20"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="适用范围"/>
-    <tableColumn id="2" name="模块/张量"/>
-    <tableColumn id="3" name="落盘/参数存储"/>
-    <tableColumn id="4" name="激活/中间计算"/>
-    <tableColumn id="5" name="说明"/>
+    <tableColumn id="1" name="Scope"/>
+    <tableColumn id="2" name="Module/tensor"/>
+    <tableColumn id="3" name="Checkpoint/parameter storage"/>
+    <tableColumn id="4" name="Activation/intermediate computation"/>
+    <tableColumn id="5" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3426,15 +3418,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="DType_Layer" displayName="DType_Layer" ref="A23:I66" totalsRowShown="0">
   <autoFilter ref="A23:I66"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="层 ID"/>
-    <tableColumn id="2" name="注意力模式"/>
-    <tableColumn id="3" name="压缩比例"/>
-    <tableColumn id="4" name="路由模式"/>
-    <tableColumn id="5" name="隐藏状态 / 残差"/>
-    <tableColumn id="6" name="注意力主投影"/>
-    <tableColumn id="7" name="路由专家"/>
-    <tableColumn id="8" name="共享专家"/>
-    <tableColumn id="9" name="归一化 / HC / Router 计算"/>
+    <tableColumn id="1" name="Layer ID"/>
+    <tableColumn id="2" name="Attention mode"/>
+    <tableColumn id="3" name="Compression ratio"/>
+    <tableColumn id="4" name="Routing mode"/>
+    <tableColumn id="5" name="Hidden state / residual"/>
+    <tableColumn id="6" name="Main attention projections"/>
+    <tableColumn id="7" name="Routed experts"/>
+    <tableColumn id="8" name="Shared experts"/>
+    <tableColumn id="9" name="Normalization / HC / Router computation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3444,12 +3436,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Comparison_Resource_Overview" displayName="Comparison_Resource_Overview" ref="A4:F32" totalsRowShown="0">
   <autoFilter ref="A4:F32"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="资源项目"/>
-    <tableColumn id="2" name="预填充 TP1"/>
-    <tableColumn id="3" name="预填充 TP8/每 Rank"/>
-    <tableColumn id="4" name="解码 TP1"/>
-    <tableColumn id="5" name="解码 TP8/每 Rank"/>
-    <tableColumn id="6" name="说明"/>
+    <tableColumn id="1" name="Resource"/>
+    <tableColumn id="2" name="Prefill TP1"/>
+    <tableColumn id="3" name="Prefill TP8/rank"/>
+    <tableColumn id="4" name="Decode TP1"/>
+    <tableColumn id="5" name="Decode TP8/rank"/>
+    <tableColumn id="6" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3459,14 +3451,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PF_Embedded_Parameter_Detail" displayName="PF_Embedded_Parameter_Detail" ref="A48:H59" totalsRowShown="0">
   <autoFilter ref="A48:H59"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="大类"/>
-    <tableColumn id="2" name="参数组件"/>
-    <tableColumn id="3" name="全局参数量"/>
-    <tableColumn id="4" name="TP1 参数量/rank"/>
-    <tableColumn id="5" name="TP8 参数量/rank"/>
-    <tableColumn id="6" name="TP1 容量/rank"/>
-    <tableColumn id="7" name="TP8 容量/rank"/>
-    <tableColumn id="8" name="说明"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Parameter component"/>
+    <tableColumn id="3" name="Global parameter count"/>
+    <tableColumn id="4" name="TP1 parameter count/rank"/>
+    <tableColumn id="5" name="TP8 parameter count/rank"/>
+    <tableColumn id="6" name="TP1 capacity/rank"/>
+    <tableColumn id="7" name="TP8 capacity/rank"/>
+    <tableColumn id="8" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3476,11 +3468,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PF_Embedded_Parameter_Summary" displayName="PF_Embedded_Parameter_Summary" ref="A62:E66" totalsRowShown="0">
   <autoFilter ref="A62:E66"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="大类"/>
-    <tableColumn id="2" name="TP1 参数量/rank"/>
-    <tableColumn id="3" name="TP8 参数量/rank"/>
-    <tableColumn id="4" name="TP1 容量/rank"/>
-    <tableColumn id="5" name="TP8 容量/rank"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="TP1 parameter count/rank"/>
+    <tableColumn id="3" name="TP8 parameter count/rank"/>
+    <tableColumn id="4" name="TP1 capacity/rank"/>
+    <tableColumn id="5" name="TP8 capacity/rank"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3490,10 +3482,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PF_Embedded_Cache" displayName="PF_Embedded_Cache" ref="A69:D73" totalsRowShown="0">
   <autoFilter ref="A69:D73"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="项目"/>
+    <tableColumn id="1" name="Item"/>
     <tableColumn id="2" name="TP1/rank"/>
     <tableColumn id="3" name="TP8/rank"/>
-    <tableColumn id="4" name="说明"/>
+    <tableColumn id="4" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3503,16 +3495,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PF_Embedded_Rank_Memory" displayName="PF_Embedded_Rank_Memory" ref="A77:J79" totalsRowShown="0">
   <autoFilter ref="A77:J79"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="配置"/>
+    <tableColumn id="1" name="Configuration"/>
     <tableColumn id="2" name="Rank"/>
-    <tableColumn id="3" name="注意力参数"/>
-    <tableColumn id="4" name="混合专家参数"/>
-    <tableColumn id="5" name="其他参数"/>
-    <tableColumn id="6" name="参数总计"/>
-    <tableColumn id="7" name="当前场景 KV+状态"/>
-    <tableColumn id="8" name="总驻留"/>
-    <tableColumn id="9" name="逻辑参数量"/>
-    <tableColumn id="10" name="有效"/>
+    <tableColumn id="3" name="Attention parameters"/>
+    <tableColumn id="4" name="MoE parameters"/>
+    <tableColumn id="5" name="Other parameters"/>
+    <tableColumn id="6" name="Total parameters"/>
+    <tableColumn id="7" name="Current scenario KV+state"/>
+    <tableColumn id="8" name="Total resident"/>
+    <tableColumn id="9" name="Logical parameter count"/>
+    <tableColumn id="10" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3522,17 +3514,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DC_Inference_Detail" displayName="DC_Inference_Detail" ref="A32:K44" totalsRowShown="0">
   <autoFilter ref="A32:K44"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="类别"/>
-    <tableColumn id="2" name="算子/项目"/>
-    <tableColumn id="3" name="层范围"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Operator/item"/>
+    <tableColumn id="3" name="Layer scope"/>
     <tableColumn id="4" name="TP1 FLOPs"/>
     <tableColumn id="5" name="TP8 FLOPs/rank"/>
     <tableColumn id="6" name="TP1 HBM/rank"/>
     <tableColumn id="7" name="TP8 HBM/rank"/>
-    <tableColumn id="8" name="TP1 卡间互连"/>
-    <tableColumn id="9" name="TP8 卡间互连/rank"/>
-    <tableColumn id="10" name="统计类型"/>
-    <tableColumn id="11" name="说明"/>
+    <tableColumn id="8" name="TP1 Interconnect"/>
+    <tableColumn id="9" name="TP8 Interconnect/rank"/>
+    <tableColumn id="10" name="Accounting"/>
+    <tableColumn id="11" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3542,14 +3534,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="DC_Embedded_Parameter_Detail" displayName="DC_Embedded_Parameter_Detail" ref="A48:H59" totalsRowShown="0">
   <autoFilter ref="A48:H59"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="大类"/>
-    <tableColumn id="2" name="参数组件"/>
-    <tableColumn id="3" name="全局参数量"/>
-    <tableColumn id="4" name="TP1 参数量/rank"/>
-    <tableColumn id="5" name="TP8 参数量/rank"/>
-    <tableColumn id="6" name="TP1 容量/rank"/>
-    <tableColumn id="7" name="TP8 容量/rank"/>
-    <tableColumn id="8" name="说明"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Parameter component"/>
+    <tableColumn id="3" name="Global parameter count"/>
+    <tableColumn id="4" name="TP1 parameter count/rank"/>
+    <tableColumn id="5" name="TP8 parameter count/rank"/>
+    <tableColumn id="6" name="TP1 capacity/rank"/>
+    <tableColumn id="7" name="TP8 capacity/rank"/>
+    <tableColumn id="8" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3559,11 +3551,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="DC_Embedded_Parameter_Summary" displayName="DC_Embedded_Parameter_Summary" ref="A62:E66" totalsRowShown="0">
   <autoFilter ref="A62:E66"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="大类"/>
-    <tableColumn id="2" name="TP1 参数量/rank"/>
-    <tableColumn id="3" name="TP8 参数量/rank"/>
-    <tableColumn id="4" name="TP1 容量/rank"/>
-    <tableColumn id="5" name="TP8 容量/rank"/>
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="TP1 parameter count/rank"/>
+    <tableColumn id="3" name="TP8 parameter count/rank"/>
+    <tableColumn id="4" name="TP1 capacity/rank"/>
+    <tableColumn id="5" name="TP8 capacity/rank"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3573,10 +3565,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="DC_Embedded_Cache" displayName="DC_Embedded_Cache" ref="A69:D73" totalsRowShown="0">
   <autoFilter ref="A69:D73"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="项目"/>
+    <tableColumn id="1" name="Item"/>
     <tableColumn id="2" name="TP1/rank"/>
     <tableColumn id="3" name="TP8/rank"/>
-    <tableColumn id="4" name="说明"/>
+    <tableColumn id="4" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5125,11 +5117,11 @@
         <v>23.172 TFLOPs</v>
       </c>
       <c r="AE13" s="32">
-        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"注意力",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"Attention",$J$33:$J$44,"Major")</f>
         <v>102836037746688.0</v>
       </c>
       <c r="AF13" s="32">
-        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"注意力",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"Attention",$J$33:$J$44,"Major")</f>
         <v>23172382457856.0</v>
       </c>
     </row>
@@ -5146,11 +5138,11 @@
         <v>31.766 TFLOPs</v>
       </c>
       <c r="AE14" s="32">
-        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"混合专家",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"MoE",$J$33:$J$44,"Major")</f>
         <v>124846109360128.0</v>
       </c>
       <c r="AF14" s="32">
-        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"混合专家",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"MoE",$J$33:$J$44,"Major")</f>
         <v>31765578121216.0</v>
       </c>
     </row>
@@ -5167,11 +5159,11 @@
         <v>701.354 GFLOPs</v>
       </c>
       <c r="AE15" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$U$33:$U$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$U$33:$U$44)</f>
         <v>702280286208.0</v>
       </c>
       <c r="AF15" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$V$33:$V$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$V$33:$V$44)</f>
         <v>701353607168.0</v>
       </c>
     </row>
@@ -5209,11 +5201,11 @@
         <v>231.532 GB</v>
       </c>
       <c r="AE17" s="32">
-        <f>SUMIF($A$33:$A$44,"注意力",$W$33:$W$44)+SUMIF($A$33:$A$44,"注意力",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"Attention",$W$33:$W$44)+SUMIF($A$33:$A$44,"Attention",$X$33:$X$44)</f>
         <v>358037814400.0</v>
       </c>
       <c r="AF17" s="32">
-        <f>SUMIF($A$33:$A$44,"注意力",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"注意力",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"Attention",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"Attention",$Z$33:$Z$44)</f>
         <v>231531806144.0</v>
       </c>
     </row>
@@ -5230,11 +5222,11 @@
         <v>32.915 GB</v>
       </c>
       <c r="AE18" s="32">
-        <f>SUMIF($A$33:$A$44,"混合专家",$W$33:$W$44)+SUMIF($A$33:$A$44,"混合专家",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"MoE",$W$33:$W$44)+SUMIF($A$33:$A$44,"MoE",$X$33:$X$44)</f>
         <v>191988670976.0</v>
       </c>
       <c r="AF18" s="32">
-        <f>SUMIF($A$33:$A$44,"混合专家",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"混合专家",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"MoE",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"MoE",$Z$33:$Z$44)</f>
         <v>32915497472.0</v>
       </c>
     </row>
@@ -5251,11 +5243,11 @@
         <v>92.742 GB</v>
       </c>
       <c r="AE19" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$W$33:$W$44)+SUMIF($A$33:$A$44,"其他",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$W$33:$W$44)+SUMIF($A$33:$A$44,"Other",$X$33:$X$44)</f>
         <v>94595729480.0</v>
       </c>
       <c r="AF19" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"其他",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"Other",$Z$33:$Z$44)</f>
         <v>92741918920.0</v>
       </c>
     </row>
@@ -5411,7 +5403,7 @@
         <v>230</v>
       </c>
       <c r="K32" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -5419,10 +5411,10 @@
         <v>40</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D33" s="31" t="str">
         <f>TEXT(IF(ABS(U33)&gt;=1E15,U33/1E15,IF(ABS(U33)&gt;=1E12,U33/1E12,IF(ABS(U33)&gt;=1E9,U33/1E9,IF(ABS(U33)&gt;=1E6,U33/1E6,U33)))),"#,##0.000")&amp;IF((IF(ABS(U33)&gt;=1E15,"PFLOPs",IF(ABS(U33)&gt;=1E12,"TFLOPs",IF(ABS(U33)&gt;=1E9,"GFLOPs",IF(ABS(U33)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U33)&gt;=1E15,"PFLOPs",IF(ABS(U33)&gt;=1E12,"TFLOPs",IF(ABS(U33)&gt;=1E9,"GFLOPs",IF(ABS(U33)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5449,10 +5441,10 @@
         <v>0.000 B</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="T33" s="32">
         <f>PF_Rows*TotalLayers*2*(HiddenSize*QLoraRank+QLoraRank*NumHeads*HeadDim+HiddenSize*HeadDim+NumHeads*HeadDim*OLoraRank+OGroups*OLoraRank*HiddenSize)</f>
@@ -5504,10 +5496,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D34" s="31" t="str">
         <f>TEXT(IF(ABS(U34)&gt;=1E15,U34/1E15,IF(ABS(U34)&gt;=1E12,U34/1E12,IF(ABS(U34)&gt;=1E9,U34/1E9,IF(ABS(U34)&gt;=1E6,U34/1E6,U34)))),"#,##0.000")&amp;IF((IF(ABS(U34)&gt;=1E15,"PFLOPs",IF(ABS(U34)&gt;=1E12,"TFLOPs",IF(ABS(U34)&gt;=1E9,"GFLOPs",IF(ABS(U34)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U34)&gt;=1E15,"PFLOPs",IF(ABS(U34)&gt;=1E12,"TFLOPs",IF(ABS(U34)&gt;=1E9,"GFLOPs",IF(ABS(U34)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5534,10 +5526,10 @@
         <v>0.000 B</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T34" s="32">
         <f>4*PrefillBatch*NumHeads*HeadDim*(WindowLayers*PF_RawPairs+ShortLayers*(PF_RawPairs+PF_ShortPairs)+LongLayers*(PF_RawPairs+PF_LongPairs))</f>
@@ -5589,10 +5581,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D35" s="31" t="str">
         <f>TEXT(IF(ABS(U35)&gt;=1E15,U35/1E15,IF(ABS(U35)&gt;=1E12,U35/1E12,IF(ABS(U35)&gt;=1E9,U35/1E9,IF(ABS(U35)&gt;=1E6,U35/1E6,U35)))),"#,##0.000")&amp;IF((IF(ABS(U35)&gt;=1E15,"PFLOPs",IF(ABS(U35)&gt;=1E12,"TFLOPs",IF(ABS(U35)&gt;=1E9,"GFLOPs",IF(ABS(U35)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U35)&gt;=1E15,"PFLOPs",IF(ABS(U35)&gt;=1E12,"TFLOPs",IF(ABS(U35)&gt;=1E9,"GFLOPs",IF(ABS(U35)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5619,7 +5611,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>240</v>
@@ -5677,7 +5669,7 @@
         <v>241</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D36" s="31" t="str">
         <f>TEXT(IF(ABS(U36)&gt;=1E15,U36/1E15,IF(ABS(U36)&gt;=1E12,U36/1E12,IF(ABS(U36)&gt;=1E9,U36/1E9,IF(ABS(U36)&gt;=1E6,U36/1E6,U36)))),"#,##0.000")&amp;IF((IF(ABS(U36)&gt;=1E15,"PFLOPs",IF(ABS(U36)&gt;=1E12,"TFLOPs",IF(ABS(U36)&gt;=1E9,"GFLOPs",IF(ABS(U36)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U36)&gt;=1E15,"PFLOPs",IF(ABS(U36)&gt;=1E12,"TFLOPs",IF(ABS(U36)&gt;=1E9,"GFLOPs",IF(ABS(U36)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5704,7 +5696,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>242</v>
@@ -5789,7 +5781,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>245</v>
@@ -5847,7 +5839,7 @@
         <v>246</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D38" s="31" t="str">
         <f>TEXT(IF(ABS(U38)&gt;=1E15,U38/1E15,IF(ABS(U38)&gt;=1E12,U38/1E12,IF(ABS(U38)&gt;=1E9,U38/1E9,IF(ABS(U38)&gt;=1E6,U38/1E6,U38)))),"#,##0.000")&amp;IF((IF(ABS(U38)&gt;=1E15,"PFLOPs",IF(ABS(U38)&gt;=1E12,"TFLOPs",IF(ABS(U38)&gt;=1E9,"GFLOPs",IF(ABS(U38)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U38)&gt;=1E15,"PFLOPs",IF(ABS(U38)&gt;=1E12,"TFLOPs",IF(ABS(U38)&gt;=1E9,"GFLOPs",IF(ABS(U38)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5874,7 +5866,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>247</v>
@@ -5932,7 +5924,7 @@
         <v>248</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D39" s="31" t="str">
         <f>TEXT(IF(ABS(U39)&gt;=1E15,U39/1E15,IF(ABS(U39)&gt;=1E12,U39/1E12,IF(ABS(U39)&gt;=1E9,U39/1E9,IF(ABS(U39)&gt;=1E6,U39/1E6,U39)))),"#,##0.000")&amp;IF((IF(ABS(U39)&gt;=1E15,"PFLOPs",IF(ABS(U39)&gt;=1E12,"TFLOPs",IF(ABS(U39)&gt;=1E9,"GFLOPs",IF(ABS(U39)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U39)&gt;=1E15,"PFLOPs",IF(ABS(U39)&gt;=1E12,"TFLOPs",IF(ABS(U39)&gt;=1E9,"GFLOPs",IF(ABS(U39)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -5959,7 +5951,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>249</v>
@@ -6017,7 +6009,7 @@
         <v>250</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D40" s="31" t="str">
         <f>TEXT(IF(ABS(U40)&gt;=1E15,U40/1E15,IF(ABS(U40)&gt;=1E12,U40/1E12,IF(ABS(U40)&gt;=1E9,U40/1E9,IF(ABS(U40)&gt;=1E6,U40/1E6,U40)))),"#,##0.000")&amp;IF((IF(ABS(U40)&gt;=1E15,"PFLOPs",IF(ABS(U40)&gt;=1E12,"TFLOPs",IF(ABS(U40)&gt;=1E9,"GFLOPs",IF(ABS(U40)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U40)&gt;=1E15,"PFLOPs",IF(ABS(U40)&gt;=1E12,"TFLOPs",IF(ABS(U40)&gt;=1E9,"GFLOPs",IF(ABS(U40)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -6044,7 +6036,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>251</v>
@@ -6102,7 +6094,7 @@
         <v>252</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D41" s="31" t="str">
         <f>TEXT(IF(ABS(U41)&gt;=1E15,U41/1E15,IF(ABS(U41)&gt;=1E12,U41/1E12,IF(ABS(U41)&gt;=1E9,U41/1E9,IF(ABS(U41)&gt;=1E6,U41/1E6,U41)))),"#,##0.000")&amp;IF((IF(ABS(U41)&gt;=1E15,"PFLOPs",IF(ABS(U41)&gt;=1E12,"TFLOPs",IF(ABS(U41)&gt;=1E9,"GFLOPs",IF(ABS(U41)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U41)&gt;=1E15,"PFLOPs",IF(ABS(U41)&gt;=1E12,"TFLOPs",IF(ABS(U41)&gt;=1E9,"GFLOPs",IF(ABS(U41)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -6129,7 +6121,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>253</v>
@@ -6187,7 +6179,7 @@
         <v>255</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D42" s="31" t="str">
         <f>TEXT(IF(ABS(U42)&gt;=1E15,U42/1E15,IF(ABS(U42)&gt;=1E12,U42/1E12,IF(ABS(U42)&gt;=1E9,U42/1E9,IF(ABS(U42)&gt;=1E6,U42/1E6,U42)))),"#,##0.000")&amp;IF((IF(ABS(U42)&gt;=1E15,"PFLOPs",IF(ABS(U42)&gt;=1E12,"TFLOPs",IF(ABS(U42)&gt;=1E9,"GFLOPs",IF(ABS(U42)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U42)&gt;=1E15,"PFLOPs",IF(ABS(U42)&gt;=1E12,"TFLOPs",IF(ABS(U42)&gt;=1E9,"GFLOPs",IF(ABS(U42)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -6299,7 +6291,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>260</v>
@@ -6448,28 +6440,28 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
         <v>372</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>373</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>374</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>375</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>376</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>377</v>
       </c>
-      <c r="G48" t="s">
-        <v>378</v>
-      </c>
       <c r="H48" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:41">
@@ -6477,7 +6469,7 @@
         <v>40</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C49" s="31" t="str">
         <f>TEXT(IF(ABS(AG49)&gt;=1E12,AG49/1E12,IF(ABS(AG49)&gt;=1E9,AG49/1E9,IF(ABS(AG49)&gt;=1E6,AG49/1E6,IF(ABS(AG49)&gt;=1E3,AG49/1E3,AG49)))),"#,##0.000")&amp;IF((IF(ABS(AG49)&gt;=1E12,"T",IF(ABS(AG49)&gt;=1E9,"G",IF(ABS(AG49)&gt;=1E6,"M",IF(ABS(AG49)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG49)&gt;=1E12,"T",IF(ABS(AG49)&gt;=1E9,"G",IF(ABS(AG49)&gt;=1E6,"M",IF(ABS(AG49)&gt;=1E3,"K",""))))))</f>
@@ -6500,7 +6492,7 @@
         <v>991.991 MB</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG49" s="32">
         <f>TotalLayers*(HiddenSize*QLoraRank+QLoraRank*NumHeads*HeadDim+HiddenSize*HeadDim+NumHeads*HeadDim*OLoraRank+OGroups*OLoraRank*HiddenSize)</f>
@@ -6528,7 +6520,7 @@
         <v>40</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C50" s="31" t="str">
         <f>TEXT(IF(ABS(AG50)&gt;=1E12,AG50/1E12,IF(ABS(AG50)&gt;=1E9,AG50/1E9,IF(ABS(AG50)&gt;=1E6,AG50/1E6,IF(ABS(AG50)&gt;=1E3,AG50/1E3,AG50)))),"#,##0.000")&amp;IF((IF(ABS(AG50)&gt;=1E12,"T",IF(ABS(AG50)&gt;=1E9,"G",IF(ABS(AG50)&gt;=1E6,"M",IF(ABS(AG50)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG50)&gt;=1E12,"T",IF(ABS(AG50)&gt;=1E9,"G",IF(ABS(AG50)&gt;=1E6,"M",IF(ABS(AG50)&gt;=1E3,"K",""))))))</f>
@@ -6551,7 +6543,7 @@
         <v>1.046 GB</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG50" s="32">
         <f>ShortLayers*(2*HiddenSize*(2*HeadDim)+ShortRatio*2*HeadDim+HeadDim)+LongLayers*(2*HiddenSize*HeadDim+LongRatio*HeadDim+HeadDim)</f>
@@ -6579,7 +6571,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C51" s="31" t="str">
         <f>TEXT(IF(ABS(AG51)&gt;=1E12,AG51/1E12,IF(ABS(AG51)&gt;=1E9,AG51/1E9,IF(ABS(AG51)&gt;=1E6,AG51/1E6,IF(ABS(AG51)&gt;=1E3,AG51/1E3,AG51)))),"#,##0.000")&amp;IF((IF(ABS(AG51)&gt;=1E12,"T",IF(ABS(AG51)&gt;=1E9,"G",IF(ABS(AG51)&gt;=1E6,"M",IF(ABS(AG51)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG51)&gt;=1E12,"T",IF(ABS(AG51)&gt;=1E9,"G",IF(ABS(AG51)&gt;=1E6,"M",IF(ABS(AG51)&gt;=1E3,"K",""))))))</f>
@@ -6602,7 +6594,7 @@
         <v>199.655 MB</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG51" s="32">
         <f>ShortLayers*(QLoraRank*IndexHeads*IndexHeadDim+HiddenSize*IndexHeads+2*HiddenSize*(2*IndexHeadDim)+ShortRatio*2*IndexHeadDim+IndexHeadDim)</f>
@@ -6630,7 +6622,7 @@
         <v>59</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>361</v>
+        <v>60</v>
       </c>
       <c r="C52" s="31" t="str">
         <f>TEXT(IF(ABS(AG52)&gt;=1E12,AG52/1E12,IF(ABS(AG52)&gt;=1E9,AG52/1E9,IF(ABS(AG52)&gt;=1E6,AG52/1E6,IF(ABS(AG52)&gt;=1E3,AG52/1E3,AG52)))),"#,##0.000")&amp;IF((IF(ABS(AG52)&gt;=1E12,"T",IF(ABS(AG52)&gt;=1E9,"G",IF(ABS(AG52)&gt;=1E6,"M",IF(ABS(AG52)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG52)&gt;=1E12,"T",IF(ABS(AG52)&gt;=1E9,"G",IF(ABS(AG52)&gt;=1E6,"M",IF(ABS(AG52)&gt;=1E3,"K",""))))))</f>
@@ -6653,7 +6645,7 @@
         <v>18.396 GB</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG52" s="32">
         <f>TotalLayers*RoutedExperts*3*HiddenSize*ExpertInter</f>
@@ -6681,7 +6673,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="C53" s="31" t="str">
         <f>TEXT(IF(ABS(AG53)&gt;=1E12,AG53/1E12,IF(ABS(AG53)&gt;=1E9,AG53/1E9,IF(ABS(AG53)&gt;=1E6,AG53/1E6,IF(ABS(AG53)&gt;=1E3,AG53/1E3,AG53)))),"#,##0.000")&amp;IF((IF(ABS(AG53)&gt;=1E12,"T",IF(ABS(AG53)&gt;=1E9,"G",IF(ABS(AG53)&gt;=1E6,"M",IF(ABS(AG53)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG53)&gt;=1E12,"T",IF(ABS(AG53)&gt;=1E9,"G",IF(ABS(AG53)&gt;=1E6,"M",IF(ABS(AG53)&gt;=1E3,"K",""))))))</f>
@@ -6704,7 +6696,7 @@
         <v>1.082 GB</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG53" s="32">
         <f>TotalLayers*SharedExperts*3*HiddenSize*ExpertInter</f>
@@ -6732,7 +6724,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" s="31" t="str">
         <f>TEXT(IF(ABS(AG54)&gt;=1E12,AG54/1E12,IF(ABS(AG54)&gt;=1E9,AG54/1E9,IF(ABS(AG54)&gt;=1E6,AG54/1E6,IF(ABS(AG54)&gt;=1E3,AG54/1E3,AG54)))),"#,##0.000")&amp;IF((IF(ABS(AG54)&gt;=1E12,"T",IF(ABS(AG54)&gt;=1E9,"G",IF(ABS(AG54)&gt;=1E6,"M",IF(ABS(AG54)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG54)&gt;=1E12,"T",IF(ABS(AG54)&gt;=1E9,"G",IF(ABS(AG54)&gt;=1E6,"M",IF(ABS(AG54)&gt;=1E3,"K",""))))))</f>
@@ -6755,7 +6747,7 @@
         <v>99.527 MB</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG54" s="32">
         <f>TotalLayers*RoutedExperts*HiddenSize+(TotalLayers-ActiveHashLayers)*RoutedExperts+ActiveHashLayers*VocabSize*ActivatedExperts</f>
@@ -6783,7 +6775,7 @@
         <v>254</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" s="31" t="str">
         <f>TEXT(IF(ABS(AG55)&gt;=1E12,AG55/1E12,IF(ABS(AG55)&gt;=1E9,AG55/1E9,IF(ABS(AG55)&gt;=1E6,AG55/1E6,IF(ABS(AG55)&gt;=1E3,AG55/1E3,AG55)))),"#,##0.000")&amp;IF((IF(ABS(AG55)&gt;=1E12,"T",IF(ABS(AG55)&gt;=1E9,"G",IF(ABS(AG55)&gt;=1E6,"M",IF(ABS(AG55)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG55)&gt;=1E12,"T",IF(ABS(AG55)&gt;=1E9,"G",IF(ABS(AG55)&gt;=1E6,"M",IF(ABS(AG55)&gt;=1E3,"K",""))))))</f>
@@ -6806,7 +6798,7 @@
         <v>132.383 MB</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG55" s="32">
         <f>VocabSize*HiddenSize</f>
@@ -6834,7 +6826,7 @@
         <v>254</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>258</v>
+        <v>390</v>
       </c>
       <c r="C56" s="31" t="str">
         <f>TEXT(IF(ABS(AG56)&gt;=1E12,AG56/1E12,IF(ABS(AG56)&gt;=1E9,AG56/1E9,IF(ABS(AG56)&gt;=1E6,AG56/1E6,IF(ABS(AG56)&gt;=1E3,AG56/1E3,AG56)))),"#,##0.000")&amp;IF((IF(ABS(AG56)&gt;=1E12,"T",IF(ABS(AG56)&gt;=1E9,"G",IF(ABS(AG56)&gt;=1E6,"M",IF(ABS(AG56)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG56)&gt;=1E12,"T",IF(ABS(AG56)&gt;=1E9,"G",IF(ABS(AG56)&gt;=1E6,"M",IF(ABS(AG56)&gt;=1E3,"K",""))))))</f>
@@ -7044,19 +7036,19 @@
     </row>
     <row r="62" spans="1:41">
       <c r="A62" t="s">
-        <v>372</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
+        <v>374</v>
+      </c>
+      <c r="C62" t="s">
         <v>375</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>376</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>377</v>
-      </c>
-      <c r="E62" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:41">
@@ -7080,19 +7072,19 @@
         <v>2.238 GB</v>
       </c>
       <c r="AL63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AH$49:$AH$59)</f>
         <v>5086249088.0</v>
       </c>
       <c r="AM63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AI$49:$AI$59)</f>
         <v>1139835008.0</v>
       </c>
       <c r="AN63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AJ$49:$AJ$59)</f>
         <v>7451384960</v>
       </c>
       <c r="AO63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AK$49:$AK$59)</f>
         <v>2237504960</v>
       </c>
     </row>
@@ -7117,19 +7109,19 @@
         <v>19.578 GB</v>
       </c>
       <c r="AL64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AH$49:$AH$59)</f>
         <v>278154947072.0</v>
       </c>
       <c r="AM64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AI$49:$AI$59)</f>
         <v>35757730304.0</v>
       </c>
       <c r="AN64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AJ$49:$AJ$59)</f>
         <v>148351461888.0</v>
       </c>
       <c r="AO64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AK$49:$AK$59)</f>
         <v>19577940480.0</v>
       </c>
     </row>
@@ -7154,19 +7146,19 @@
         <v>534.377 MB</v>
       </c>
       <c r="AL65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AH$49:$AH$59)</f>
         <v>1093371351.0</v>
       </c>
       <c r="AM65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AI$49:$AI$59)</f>
         <v>166689903.0</v>
       </c>
       <c r="AN65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AJ$49:$AJ$59)</f>
         <v>3314423644.0</v>
       </c>
       <c r="AO65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AK$49:$AK$59)</f>
         <v>534376892.0</v>
       </c>
     </row>
@@ -7223,15 +7215,15 @@
         <v>402</v>
       </c>
       <c r="C69" t="s">
-        <v>403</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:43">
       <c r="A70" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B70" s="31" t="str">
         <f>TEXT(IF(ABS(AP70)&gt;=1E12,AP70/1E12,IF(ABS(AP70)&gt;=1E9,AP70/1E9,IF(ABS(AP70)&gt;=1E6,AP70/1E6,IF(ABS(AP70)&gt;=1E3,AP70/1E3,AP70)))),"#,##0.000")&amp;IF((IF(ABS(AP70)&gt;=1E12,"TB",IF(ABS(AP70)&gt;=1E9,"GB",IF(ABS(AP70)&gt;=1E6,"MB",IF(ABS(AP70)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP70)&gt;=1E12,"TB",IF(ABS(AP70)&gt;=1E9,"GB",IF(ABS(AP70)&gt;=1E6,"MB",IF(ABS(AP70)&gt;=1E3,"KB","bytes"))))))</f>
@@ -7242,7 +7234,7 @@
         <v>50.987 MB</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AP70" s="32">
         <f>PrefillBatch*HeadDim*BF16Bytes*(WindowLayers*MIN(PrefillSequence,WindowSize)+ShortLayers*(MIN(PrefillSequence,WindowSize)+INT(PrefillSequence/ShortRatio))+LongLayers*(MIN(PrefillSequence,WindowSize)+INT(PrefillSequence/LongRatio)))</f>
@@ -7255,7 +7247,7 @@
     </row>
     <row r="71" spans="1:43">
       <c r="A71" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B71" s="31" t="str">
         <f>TEXT(IF(ABS(AP71)&gt;=1E12,AP71/1E12,IF(ABS(AP71)&gt;=1E9,AP71/1E9,IF(ABS(AP71)&gt;=1E6,AP71/1E6,IF(ABS(AP71)&gt;=1E3,AP71/1E3,AP71)))),"#,##0.000")&amp;IF((IF(ABS(AP71)&gt;=1E12,"TB",IF(ABS(AP71)&gt;=1E9,"GB",IF(ABS(AP71)&gt;=1E6,"MB",IF(ABS(AP71)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP71)&gt;=1E12,"TB",IF(ABS(AP71)&gt;=1E9,"GB",IF(ABS(AP71)&gt;=1E6,"MB",IF(ABS(AP71)&gt;=1E3,"KB","bytes"))))))</f>
@@ -7266,7 +7258,7 @@
         <v>11.010 MB</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AP71" s="32">
         <f>PrefillBatch*ShortLayers*INT(PrefillSequence/ShortRatio)*IndexHeadDim*BF16Bytes</f>
@@ -7279,7 +7271,7 @@
     </row>
     <row r="72" spans="1:43">
       <c r="A72" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B72" s="31" t="str">
         <f>TEXT(IF(ABS(AP72)&gt;=1E12,AP72/1E12,IF(ABS(AP72)&gt;=1E9,AP72/1E9,IF(ABS(AP72)&gt;=1E6,AP72/1E6,IF(ABS(AP72)&gt;=1E3,AP72/1E3,AP72)))),"#,##0.000")&amp;IF((IF(ABS(AP72)&gt;=1E12,"TB",IF(ABS(AP72)&gt;=1E9,"GB",IF(ABS(AP72)&gt;=1E6,"MB",IF(ABS(AP72)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP72)&gt;=1E12,"TB",IF(ABS(AP72)&gt;=1E9,"GB",IF(ABS(AP72)&gt;=1E6,"MB",IF(ABS(AP72)&gt;=1E3,"KB","bytes"))))))</f>
@@ -7290,7 +7282,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AP72" s="32">
         <f>PrefillBatch*FP32Bytes*(ShortLayers*2*(2*ShortRatio)*(2*HeadDim)+LongLayers*2*LongRatio*HeadDim+ShortLayers*2*(2*ShortRatio)*(2*IndexHeadDim))</f>
@@ -7303,7 +7295,7 @@
     </row>
     <row r="73" spans="1:43">
       <c r="A73" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B73" s="31" t="str">
         <f>TEXT(IF(ABS(AP73)&gt;=1E12,AP73/1E12,IF(ABS(AP73)&gt;=1E9,AP73/1E9,IF(ABS(AP73)&gt;=1E6,AP73/1E6,IF(ABS(AP73)&gt;=1E3,AP73/1E3,AP73)))),"#,##0.000")&amp;IF((IF(ABS(AP73)&gt;=1E12,"TB",IF(ABS(AP73)&gt;=1E9,"GB",IF(ABS(AP73)&gt;=1E6,"MB",IF(ABS(AP73)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP73)&gt;=1E12,"TB",IF(ABS(AP73)&gt;=1E9,"GB",IF(ABS(AP73)&gt;=1E6,"MB",IF(ABS(AP73)&gt;=1E3,"KB","bytes"))))))</f>
@@ -7314,7 +7306,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AP73" s="32">
         <f>PrefillBatch*(HeadDim*BF16Bytes*(WindowLayers*WindowSize+ShortLayers*(WindowSize+INT(MaxContext/ShortRatio))+LongLayers*(WindowSize+INT(MaxContext/LongRatio)))+ShortLayers*INT(MaxContext/ShortRatio)*IndexHeadDim*BF16Bytes)+PrefillBatch*FP32Bytes*(ShortLayers*2*(2*ShortRatio)*(2*HeadDim)+LongLayers*2*LongRatio*HeadDim+ShortLayers*2*(2*ShortRatio)*(2*IndexHeadDim))</f>
@@ -7327,7 +7319,7 @@
     </row>
     <row r="76" spans="1:43">
       <c r="A76" s="30" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B76" s="30"/>
       <c r="C76" s="30"/>
@@ -7341,34 +7333,34 @@
     </row>
     <row r="77" spans="1:43">
       <c r="A77" t="s">
+        <v>412</v>
+      </c>
+      <c r="B77" t="s">
         <v>413</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>414</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>415</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>416</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>417</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>418</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>419</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>420</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>421</v>
-      </c>
-      <c r="J77" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:43">
@@ -7376,7 +7368,7 @@
         <v>267</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C78" s="34">
         <f>'Prefill_8K'!$AN$63/1E9</f>
@@ -7407,15 +7399,15 @@
         <v>284.334567511</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79" spans="1:43">
       <c r="A79" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C79" s="34">
         <f>'Prefill_8K'!$AO$63/1E9</f>
@@ -7446,7 +7438,7 @@
         <v>37.064255215</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -7630,11 +7622,11 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="AE13" s="32">
-        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"注意力",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"Attention",$J$33:$J$44,"Major")</f>
         <v>123969470464.0</v>
       </c>
       <c r="AF13" s="32">
-        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"注意力",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"Attention",$J$33:$J$44,"Major")</f>
         <v>19452461056.0</v>
       </c>
     </row>
@@ -7651,11 +7643,11 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="AE14" s="32">
-        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"混合专家",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($U$33:$U$44,$A$33:$A$44,"MoE",$J$33:$J$44,"Major")</f>
         <v>15240003584.0</v>
       </c>
       <c r="AF14" s="32">
-        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"混合专家",$J$33:$J$44,"主要")</f>
+        <f>SUMIFS($V$33:$V$44,$A$33:$A$44,"MoE",$J$33:$J$44,"Major")</f>
         <v>3877634048.0</v>
       </c>
     </row>
@@ -7672,11 +7664,11 @@
         <v>217.981 MFLOPs</v>
       </c>
       <c r="AE15" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$U$33:$U$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$U$33:$U$44)</f>
         <v>1144660054.0</v>
       </c>
       <c r="AF15" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$V$33:$V$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$V$33:$V$44)</f>
         <v>217981014.0</v>
       </c>
     </row>
@@ -7714,11 +7706,11 @@
         <v>4.035 GB</v>
       </c>
       <c r="AE17" s="32">
-        <f>SUMIF($A$33:$A$44,"注意力",$W$33:$W$44)+SUMIF($A$33:$A$44,"注意力",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"Attention",$W$33:$W$44)+SUMIF($A$33:$A$44,"Attention",$X$33:$X$44)</f>
         <v>10492228352.0</v>
       </c>
       <c r="AF17" s="32">
-        <f>SUMIF($A$33:$A$44,"注意力",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"注意力",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"Attention",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"Attention",$Z$33:$Z$44)</f>
         <v>4035232528.0</v>
       </c>
     </row>
@@ -7735,11 +7727,11 @@
         <v>1.605 GB</v>
       </c>
       <c r="AE18" s="32">
-        <f>SUMIF($A$33:$A$44,"混合专家",$W$33:$W$44)+SUMIF($A$33:$A$44,"混合专家",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"MoE",$W$33:$W$44)+SUMIF($A$33:$A$44,"MoE",$X$33:$X$44)</f>
         <v>4627033672.0</v>
       </c>
       <c r="AF18" s="32">
-        <f>SUMIF($A$33:$A$44,"混合专家",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"混合专家",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"MoE",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"MoE",$Z$33:$Z$44)</f>
         <v>1605205576.0</v>
       </c>
     </row>
@@ -7756,11 +7748,11 @@
         <v>411.394 MB</v>
       </c>
       <c r="AE19" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$W$33:$W$44)+SUMIF($A$33:$A$44,"其他",$X$33:$X$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$W$33:$W$44)+SUMIF($A$33:$A$44,"Other",$X$33:$X$44)</f>
         <v>2265204808.0</v>
       </c>
       <c r="AF19" s="32">
-        <f>SUMIF($A$33:$A$44,"其他",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"其他",$Z$33:$Z$44)</f>
+        <f>SUMIF($A$33:$A$44,"Other",$Y$33:$Y$44)+SUMIF($A$33:$A$44,"Other",$Z$33:$Z$44)</f>
         <v>411394248.0</v>
       </c>
     </row>
@@ -7916,7 +7908,7 @@
         <v>230</v>
       </c>
       <c r="K32" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -7924,10 +7916,10 @@
         <v>40</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D33" s="31" t="str">
         <f>TEXT(IF(ABS(U33)&gt;=1E15,U33/1E15,IF(ABS(U33)&gt;=1E12,U33/1E12,IF(ABS(U33)&gt;=1E9,U33/1E9,IF(ABS(U33)&gt;=1E6,U33/1E6,U33)))),"#,##0.000")&amp;IF((IF(ABS(U33)&gt;=1E15,"PFLOPs",IF(ABS(U33)&gt;=1E12,"TFLOPs",IF(ABS(U33)&gt;=1E9,"GFLOPs",IF(ABS(U33)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U33)&gt;=1E15,"PFLOPs",IF(ABS(U33)&gt;=1E12,"TFLOPs",IF(ABS(U33)&gt;=1E9,"GFLOPs",IF(ABS(U33)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -7954,10 +7946,10 @@
         <v>0.000 B</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="T33" s="32">
         <f>DC_Rows*TotalLayers*2*(HiddenSize*QLoraRank+QLoraRank*NumHeads*HeadDim+HiddenSize*HeadDim+NumHeads*HeadDim*OLoraRank+OGroups*OLoraRank*HiddenSize)</f>
@@ -8009,10 +8001,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D34" s="31" t="str">
         <f>TEXT(IF(ABS(U34)&gt;=1E15,U34/1E15,IF(ABS(U34)&gt;=1E12,U34/1E12,IF(ABS(U34)&gt;=1E9,U34/1E9,IF(ABS(U34)&gt;=1E6,U34/1E6,U34)))),"#,##0.000")&amp;IF((IF(ABS(U34)&gt;=1E15,"PFLOPs",IF(ABS(U34)&gt;=1E12,"TFLOPs",IF(ABS(U34)&gt;=1E9,"GFLOPs",IF(ABS(U34)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U34)&gt;=1E15,"PFLOPs",IF(ABS(U34)&gt;=1E12,"TFLOPs",IF(ABS(U34)&gt;=1E9,"GFLOPs",IF(ABS(U34)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8039,10 +8031,10 @@
         <v>0.000 B</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T34" s="32">
         <f>4*DecodeBatch*NumHeads*HeadDim*(WindowLayers*DC_RawPairs+ShortLayers*(DC_RawPairs+DC_ShortPairs)+LongLayers*(DC_RawPairs+DC_LongPairs))</f>
@@ -8094,10 +8086,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D35" s="31" t="str">
         <f>TEXT(IF(ABS(U35)&gt;=1E15,U35/1E15,IF(ABS(U35)&gt;=1E12,U35/1E12,IF(ABS(U35)&gt;=1E9,U35/1E9,IF(ABS(U35)&gt;=1E6,U35/1E6,U35)))),"#,##0.000")&amp;IF((IF(ABS(U35)&gt;=1E15,"PFLOPs",IF(ABS(U35)&gt;=1E12,"TFLOPs",IF(ABS(U35)&gt;=1E9,"GFLOPs",IF(ABS(U35)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U35)&gt;=1E15,"PFLOPs",IF(ABS(U35)&gt;=1E12,"TFLOPs",IF(ABS(U35)&gt;=1E9,"GFLOPs",IF(ABS(U35)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8124,7 +8116,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>240</v>
@@ -8182,7 +8174,7 @@
         <v>241</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D36" s="31" t="str">
         <f>TEXT(IF(ABS(U36)&gt;=1E15,U36/1E15,IF(ABS(U36)&gt;=1E12,U36/1E12,IF(ABS(U36)&gt;=1E9,U36/1E9,IF(ABS(U36)&gt;=1E6,U36/1E6,U36)))),"#,##0.000")&amp;IF((IF(ABS(U36)&gt;=1E15,"PFLOPs",IF(ABS(U36)&gt;=1E12,"TFLOPs",IF(ABS(U36)&gt;=1E9,"GFLOPs",IF(ABS(U36)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U36)&gt;=1E15,"PFLOPs",IF(ABS(U36)&gt;=1E12,"TFLOPs",IF(ABS(U36)&gt;=1E9,"GFLOPs",IF(ABS(U36)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8209,7 +8201,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>242</v>
@@ -8294,7 +8286,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>245</v>
@@ -8352,7 +8344,7 @@
         <v>246</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="D38" s="31" t="str">
         <f>TEXT(IF(ABS(U38)&gt;=1E15,U38/1E15,IF(ABS(U38)&gt;=1E12,U38/1E12,IF(ABS(U38)&gt;=1E9,U38/1E9,IF(ABS(U38)&gt;=1E6,U38/1E6,U38)))),"#,##0.000")&amp;IF((IF(ABS(U38)&gt;=1E15,"PFLOPs",IF(ABS(U38)&gt;=1E12,"TFLOPs",IF(ABS(U38)&gt;=1E9,"GFLOPs",IF(ABS(U38)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U38)&gt;=1E15,"PFLOPs",IF(ABS(U38)&gt;=1E12,"TFLOPs",IF(ABS(U38)&gt;=1E9,"GFLOPs",IF(ABS(U38)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8379,7 +8371,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>247</v>
@@ -8437,7 +8429,7 @@
         <v>248</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D39" s="31" t="str">
         <f>TEXT(IF(ABS(U39)&gt;=1E15,U39/1E15,IF(ABS(U39)&gt;=1E12,U39/1E12,IF(ABS(U39)&gt;=1E9,U39/1E9,IF(ABS(U39)&gt;=1E6,U39/1E6,U39)))),"#,##0.000")&amp;IF((IF(ABS(U39)&gt;=1E15,"PFLOPs",IF(ABS(U39)&gt;=1E12,"TFLOPs",IF(ABS(U39)&gt;=1E9,"GFLOPs",IF(ABS(U39)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U39)&gt;=1E15,"PFLOPs",IF(ABS(U39)&gt;=1E12,"TFLOPs",IF(ABS(U39)&gt;=1E9,"GFLOPs",IF(ABS(U39)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8464,7 +8456,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>249</v>
@@ -8522,7 +8514,7 @@
         <v>250</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D40" s="31" t="str">
         <f>TEXT(IF(ABS(U40)&gt;=1E15,U40/1E15,IF(ABS(U40)&gt;=1E12,U40/1E12,IF(ABS(U40)&gt;=1E9,U40/1E9,IF(ABS(U40)&gt;=1E6,U40/1E6,U40)))),"#,##0.000")&amp;IF((IF(ABS(U40)&gt;=1E15,"PFLOPs",IF(ABS(U40)&gt;=1E12,"TFLOPs",IF(ABS(U40)&gt;=1E9,"GFLOPs",IF(ABS(U40)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U40)&gt;=1E15,"PFLOPs",IF(ABS(U40)&gt;=1E12,"TFLOPs",IF(ABS(U40)&gt;=1E9,"GFLOPs",IF(ABS(U40)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8549,7 +8541,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>251</v>
@@ -8607,7 +8599,7 @@
         <v>252</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D41" s="31" t="str">
         <f>TEXT(IF(ABS(U41)&gt;=1E15,U41/1E15,IF(ABS(U41)&gt;=1E12,U41/1E12,IF(ABS(U41)&gt;=1E9,U41/1E9,IF(ABS(U41)&gt;=1E6,U41/1E6,U41)))),"#,##0.000")&amp;IF((IF(ABS(U41)&gt;=1E15,"PFLOPs",IF(ABS(U41)&gt;=1E12,"TFLOPs",IF(ABS(U41)&gt;=1E9,"GFLOPs",IF(ABS(U41)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U41)&gt;=1E15,"PFLOPs",IF(ABS(U41)&gt;=1E12,"TFLOPs",IF(ABS(U41)&gt;=1E9,"GFLOPs",IF(ABS(U41)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8634,7 +8626,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>253</v>
@@ -8692,7 +8684,7 @@
         <v>255</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D42" s="31" t="str">
         <f>TEXT(IF(ABS(U42)&gt;=1E15,U42/1E15,IF(ABS(U42)&gt;=1E12,U42/1E12,IF(ABS(U42)&gt;=1E9,U42/1E9,IF(ABS(U42)&gt;=1E6,U42/1E6,U42)))),"#,##0.000")&amp;IF((IF(ABS(U42)&gt;=1E15,"PFLOPs",IF(ABS(U42)&gt;=1E12,"TFLOPs",IF(ABS(U42)&gt;=1E9,"GFLOPs",IF(ABS(U42)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(U42)&gt;=1E15,"PFLOPs",IF(ABS(U42)&gt;=1E12,"TFLOPs",IF(ABS(U42)&gt;=1E9,"GFLOPs",IF(ABS(U42)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -8804,7 +8796,7 @@
         <v>0.000 B</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>260</v>
@@ -8941,7 +8933,7 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" s="30" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B47" s="30"/>
       <c r="C47" s="30"/>
@@ -8953,28 +8945,28 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
         <v>372</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>373</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>374</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>375</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>376</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>377</v>
       </c>
-      <c r="G48" t="s">
-        <v>378</v>
-      </c>
       <c r="H48" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:41">
@@ -8982,7 +8974,7 @@
         <v>40</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C49" s="31" t="str">
         <f>TEXT(IF(ABS(AG49)&gt;=1E12,AG49/1E12,IF(ABS(AG49)&gt;=1E9,AG49/1E9,IF(ABS(AG49)&gt;=1E6,AG49/1E6,IF(ABS(AG49)&gt;=1E3,AG49/1E3,AG49)))),"#,##0.000")&amp;IF((IF(ABS(AG49)&gt;=1E12,"T",IF(ABS(AG49)&gt;=1E9,"G",IF(ABS(AG49)&gt;=1E6,"M",IF(ABS(AG49)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG49)&gt;=1E12,"T",IF(ABS(AG49)&gt;=1E9,"G",IF(ABS(AG49)&gt;=1E6,"M",IF(ABS(AG49)&gt;=1E3,"K",""))))))</f>
@@ -9005,7 +8997,7 @@
         <v>991.991 MB</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG49" s="32">
         <f>TotalLayers*(HiddenSize*QLoraRank+QLoraRank*NumHeads*HeadDim+HiddenSize*HeadDim+NumHeads*HeadDim*OLoraRank+OGroups*OLoraRank*HiddenSize)</f>
@@ -9033,7 +9025,7 @@
         <v>40</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C50" s="31" t="str">
         <f>TEXT(IF(ABS(AG50)&gt;=1E12,AG50/1E12,IF(ABS(AG50)&gt;=1E9,AG50/1E9,IF(ABS(AG50)&gt;=1E6,AG50/1E6,IF(ABS(AG50)&gt;=1E3,AG50/1E3,AG50)))),"#,##0.000")&amp;IF((IF(ABS(AG50)&gt;=1E12,"T",IF(ABS(AG50)&gt;=1E9,"G",IF(ABS(AG50)&gt;=1E6,"M",IF(ABS(AG50)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG50)&gt;=1E12,"T",IF(ABS(AG50)&gt;=1E9,"G",IF(ABS(AG50)&gt;=1E6,"M",IF(ABS(AG50)&gt;=1E3,"K",""))))))</f>
@@ -9056,7 +9048,7 @@
         <v>1.046 GB</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG50" s="32">
         <f>ShortLayers*(2*HiddenSize*(2*HeadDim)+ShortRatio*2*HeadDim+HeadDim)+LongLayers*(2*HiddenSize*HeadDim+LongRatio*HeadDim+HeadDim)</f>
@@ -9084,7 +9076,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C51" s="31" t="str">
         <f>TEXT(IF(ABS(AG51)&gt;=1E12,AG51/1E12,IF(ABS(AG51)&gt;=1E9,AG51/1E9,IF(ABS(AG51)&gt;=1E6,AG51/1E6,IF(ABS(AG51)&gt;=1E3,AG51/1E3,AG51)))),"#,##0.000")&amp;IF((IF(ABS(AG51)&gt;=1E12,"T",IF(ABS(AG51)&gt;=1E9,"G",IF(ABS(AG51)&gt;=1E6,"M",IF(ABS(AG51)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG51)&gt;=1E12,"T",IF(ABS(AG51)&gt;=1E9,"G",IF(ABS(AG51)&gt;=1E6,"M",IF(ABS(AG51)&gt;=1E3,"K",""))))))</f>
@@ -9107,7 +9099,7 @@
         <v>199.655 MB</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG51" s="32">
         <f>ShortLayers*(QLoraRank*IndexHeads*IndexHeadDim+HiddenSize*IndexHeads+2*HiddenSize*(2*IndexHeadDim)+ShortRatio*2*IndexHeadDim+IndexHeadDim)</f>
@@ -9135,7 +9127,7 @@
         <v>59</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>361</v>
+        <v>60</v>
       </c>
       <c r="C52" s="31" t="str">
         <f>TEXT(IF(ABS(AG52)&gt;=1E12,AG52/1E12,IF(ABS(AG52)&gt;=1E9,AG52/1E9,IF(ABS(AG52)&gt;=1E6,AG52/1E6,IF(ABS(AG52)&gt;=1E3,AG52/1E3,AG52)))),"#,##0.000")&amp;IF((IF(ABS(AG52)&gt;=1E12,"T",IF(ABS(AG52)&gt;=1E9,"G",IF(ABS(AG52)&gt;=1E6,"M",IF(ABS(AG52)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG52)&gt;=1E12,"T",IF(ABS(AG52)&gt;=1E9,"G",IF(ABS(AG52)&gt;=1E6,"M",IF(ABS(AG52)&gt;=1E3,"K",""))))))</f>
@@ -9158,7 +9150,7 @@
         <v>18.396 GB</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG52" s="32">
         <f>TotalLayers*RoutedExperts*3*HiddenSize*ExpertInter</f>
@@ -9186,7 +9178,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="C53" s="31" t="str">
         <f>TEXT(IF(ABS(AG53)&gt;=1E12,AG53/1E12,IF(ABS(AG53)&gt;=1E9,AG53/1E9,IF(ABS(AG53)&gt;=1E6,AG53/1E6,IF(ABS(AG53)&gt;=1E3,AG53/1E3,AG53)))),"#,##0.000")&amp;IF((IF(ABS(AG53)&gt;=1E12,"T",IF(ABS(AG53)&gt;=1E9,"G",IF(ABS(AG53)&gt;=1E6,"M",IF(ABS(AG53)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG53)&gt;=1E12,"T",IF(ABS(AG53)&gt;=1E9,"G",IF(ABS(AG53)&gt;=1E6,"M",IF(ABS(AG53)&gt;=1E3,"K",""))))))</f>
@@ -9209,7 +9201,7 @@
         <v>1.082 GB</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG53" s="32">
         <f>TotalLayers*SharedExperts*3*HiddenSize*ExpertInter</f>
@@ -9237,7 +9229,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" s="31" t="str">
         <f>TEXT(IF(ABS(AG54)&gt;=1E12,AG54/1E12,IF(ABS(AG54)&gt;=1E9,AG54/1E9,IF(ABS(AG54)&gt;=1E6,AG54/1E6,IF(ABS(AG54)&gt;=1E3,AG54/1E3,AG54)))),"#,##0.000")&amp;IF((IF(ABS(AG54)&gt;=1E12,"T",IF(ABS(AG54)&gt;=1E9,"G",IF(ABS(AG54)&gt;=1E6,"M",IF(ABS(AG54)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG54)&gt;=1E12,"T",IF(ABS(AG54)&gt;=1E9,"G",IF(ABS(AG54)&gt;=1E6,"M",IF(ABS(AG54)&gt;=1E3,"K",""))))))</f>
@@ -9260,7 +9252,7 @@
         <v>99.527 MB</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG54" s="32">
         <f>TotalLayers*RoutedExperts*HiddenSize+(TotalLayers-ActiveHashLayers)*RoutedExperts+ActiveHashLayers*VocabSize*ActivatedExperts</f>
@@ -9288,7 +9280,7 @@
         <v>254</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" s="31" t="str">
         <f>TEXT(IF(ABS(AG55)&gt;=1E12,AG55/1E12,IF(ABS(AG55)&gt;=1E9,AG55/1E9,IF(ABS(AG55)&gt;=1E6,AG55/1E6,IF(ABS(AG55)&gt;=1E3,AG55/1E3,AG55)))),"#,##0.000")&amp;IF((IF(ABS(AG55)&gt;=1E12,"T",IF(ABS(AG55)&gt;=1E9,"G",IF(ABS(AG55)&gt;=1E6,"M",IF(ABS(AG55)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG55)&gt;=1E12,"T",IF(ABS(AG55)&gt;=1E9,"G",IF(ABS(AG55)&gt;=1E6,"M",IF(ABS(AG55)&gt;=1E3,"K",""))))))</f>
@@ -9311,7 +9303,7 @@
         <v>132.383 MB</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG55" s="32">
         <f>VocabSize*HiddenSize</f>
@@ -9339,7 +9331,7 @@
         <v>254</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>258</v>
+        <v>390</v>
       </c>
       <c r="C56" s="31" t="str">
         <f>TEXT(IF(ABS(AG56)&gt;=1E12,AG56/1E12,IF(ABS(AG56)&gt;=1E9,AG56/1E9,IF(ABS(AG56)&gt;=1E6,AG56/1E6,IF(ABS(AG56)&gt;=1E3,AG56/1E3,AG56)))),"#,##0.000")&amp;IF((IF(ABS(AG56)&gt;=1E12,"T",IF(ABS(AG56)&gt;=1E9,"G",IF(ABS(AG56)&gt;=1E6,"M",IF(ABS(AG56)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(AG56)&gt;=1E12,"T",IF(ABS(AG56)&gt;=1E9,"G",IF(ABS(AG56)&gt;=1E6,"M",IF(ABS(AG56)&gt;=1E3,"K",""))))))</f>
@@ -9549,19 +9541,19 @@
     </row>
     <row r="62" spans="1:41">
       <c r="A62" t="s">
-        <v>372</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
+        <v>374</v>
+      </c>
+      <c r="C62" t="s">
         <v>375</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>376</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>377</v>
-      </c>
-      <c r="E62" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:41">
@@ -9585,19 +9577,19 @@
         <v>2.238 GB</v>
       </c>
       <c r="AL63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AH$49:$AH$59)</f>
         <v>5086249088.0</v>
       </c>
       <c r="AM63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AI$49:$AI$59)</f>
         <v>1139835008.0</v>
       </c>
       <c r="AN63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AJ$49:$AJ$59)</f>
         <v>7451384960</v>
       </c>
       <c r="AO63" s="32">
-        <f>SUMIF($A$49:$A$59,"注意力",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"Attention",$AK$49:$AK$59)</f>
         <v>2237504960</v>
       </c>
     </row>
@@ -9622,19 +9614,19 @@
         <v>19.578 GB</v>
       </c>
       <c r="AL64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AH$49:$AH$59)</f>
         <v>278154947072.0</v>
       </c>
       <c r="AM64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AI$49:$AI$59)</f>
         <v>35757730304.0</v>
       </c>
       <c r="AN64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AJ$49:$AJ$59)</f>
         <v>148351461888.0</v>
       </c>
       <c r="AO64" s="32">
-        <f>SUMIF($A$49:$A$59,"混合专家",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"MoE",$AK$49:$AK$59)</f>
         <v>19577940480.0</v>
       </c>
     </row>
@@ -9659,19 +9651,19 @@
         <v>534.377 MB</v>
       </c>
       <c r="AL65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AH$49:$AH$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AH$49:$AH$59)</f>
         <v>1093371351.0</v>
       </c>
       <c r="AM65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AI$49:$AI$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AI$49:$AI$59)</f>
         <v>166689903.0</v>
       </c>
       <c r="AN65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AJ$49:$AJ$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AJ$49:$AJ$59)</f>
         <v>3314423644.0</v>
       </c>
       <c r="AO65" s="32">
-        <f>SUMIF($A$49:$A$59,"其他",$AK$49:$AK$59)</f>
+        <f>SUMIF($A$49:$A$59,"Other",$AK$49:$AK$59)</f>
         <v>534376892.0</v>
       </c>
     </row>
@@ -9728,15 +9720,15 @@
         <v>402</v>
       </c>
       <c r="C69" t="s">
-        <v>403</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:43">
       <c r="A70" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B70" s="31" t="str">
         <f>TEXT(IF(ABS(AP70)&gt;=1E12,AP70/1E12,IF(ABS(AP70)&gt;=1E9,AP70/1E9,IF(ABS(AP70)&gt;=1E6,AP70/1E6,IF(ABS(AP70)&gt;=1E3,AP70/1E3,AP70)))),"#,##0.000")&amp;IF((IF(ABS(AP70)&gt;=1E12,"TB",IF(ABS(AP70)&gt;=1E9,"GB",IF(ABS(AP70)&gt;=1E6,"MB",IF(ABS(AP70)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP70)&gt;=1E12,"TB",IF(ABS(AP70)&gt;=1E9,"GB",IF(ABS(AP70)&gt;=1E6,"MB",IF(ABS(AP70)&gt;=1E3,"KB","bytes"))))))</f>
@@ -9747,7 +9739,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AP70" s="32">
         <f>DecodeBatch*HeadDim*BF16Bytes*(WindowLayers*MIN(DecodeContext,WindowSize)+ShortLayers*(MIN(DecodeContext,WindowSize)+INT(DecodeContext/ShortRatio))+LongLayers*(MIN(DecodeContext,WindowSize)+INT(DecodeContext/LongRatio)))</f>
@@ -9760,7 +9752,7 @@
     </row>
     <row r="71" spans="1:43">
       <c r="A71" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B71" s="31" t="str">
         <f>TEXT(IF(ABS(AP71)&gt;=1E12,AP71/1E12,IF(ABS(AP71)&gt;=1E9,AP71/1E9,IF(ABS(AP71)&gt;=1E6,AP71/1E6,IF(ABS(AP71)&gt;=1E3,AP71/1E3,AP71)))),"#,##0.000")&amp;IF((IF(ABS(AP71)&gt;=1E12,"TB",IF(ABS(AP71)&gt;=1E9,"GB",IF(ABS(AP71)&gt;=1E6,"MB",IF(ABS(AP71)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP71)&gt;=1E12,"TB",IF(ABS(AP71)&gt;=1E9,"GB",IF(ABS(AP71)&gt;=1E6,"MB",IF(ABS(AP71)&gt;=1E3,"KB","bytes"))))))</f>
@@ -9771,7 +9763,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AP71" s="32">
         <f>DecodeBatch*ShortLayers*INT(DecodeContext/ShortRatio)*IndexHeadDim*BF16Bytes</f>
@@ -9784,7 +9776,7 @@
     </row>
     <row r="72" spans="1:43">
       <c r="A72" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B72" s="31" t="str">
         <f>TEXT(IF(ABS(AP72)&gt;=1E12,AP72/1E12,IF(ABS(AP72)&gt;=1E9,AP72/1E9,IF(ABS(AP72)&gt;=1E6,AP72/1E6,IF(ABS(AP72)&gt;=1E3,AP72/1E3,AP72)))),"#,##0.000")&amp;IF((IF(ABS(AP72)&gt;=1E12,"TB",IF(ABS(AP72)&gt;=1E9,"GB",IF(ABS(AP72)&gt;=1E6,"MB",IF(ABS(AP72)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP72)&gt;=1E12,"TB",IF(ABS(AP72)&gt;=1E9,"GB",IF(ABS(AP72)&gt;=1E6,"MB",IF(ABS(AP72)&gt;=1E3,"KB","bytes"))))))</f>
@@ -9795,7 +9787,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AP72" s="32">
         <f>DecodeBatch*FP32Bytes*(ShortLayers*2*(2*ShortRatio)*(2*HeadDim)+LongLayers*2*LongRatio*HeadDim+ShortLayers*2*(2*ShortRatio)*(2*IndexHeadDim))</f>
@@ -9808,7 +9800,7 @@
     </row>
     <row r="73" spans="1:43">
       <c r="A73" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B73" s="31" t="str">
         <f>TEXT(IF(ABS(AP73)&gt;=1E12,AP73/1E12,IF(ABS(AP73)&gt;=1E9,AP73/1E9,IF(ABS(AP73)&gt;=1E6,AP73/1E6,IF(ABS(AP73)&gt;=1E3,AP73/1E3,AP73)))),"#,##0.000")&amp;IF((IF(ABS(AP73)&gt;=1E12,"TB",IF(ABS(AP73)&gt;=1E9,"GB",IF(ABS(AP73)&gt;=1E6,"MB",IF(ABS(AP73)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(AP73)&gt;=1E12,"TB",IF(ABS(AP73)&gt;=1E9,"GB",IF(ABS(AP73)&gt;=1E6,"MB",IF(ABS(AP73)&gt;=1E3,"KB","bytes"))))))</f>
@@ -9819,7 +9811,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AP73" s="32">
         <f>DecodeBatch*(HeadDim*BF16Bytes*(WindowLayers*WindowSize+ShortLayers*(WindowSize+INT(MaxContext/ShortRatio))+LongLayers*(WindowSize+INT(MaxContext/LongRatio)))+ShortLayers*INT(MaxContext/ShortRatio)*IndexHeadDim*BF16Bytes)+DecodeBatch*FP32Bytes*(ShortLayers*2*(2*ShortRatio)*(2*HeadDim)+LongLayers*2*LongRatio*HeadDim+ShortLayers*2*(2*ShortRatio)*(2*IndexHeadDim))</f>
@@ -9832,7 +9824,7 @@
     </row>
     <row r="76" spans="1:43">
       <c r="A76" s="30" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B76" s="30"/>
       <c r="C76" s="30"/>
@@ -9846,34 +9838,34 @@
     </row>
     <row r="77" spans="1:43">
       <c r="A77" t="s">
+        <v>412</v>
+      </c>
+      <c r="B77" t="s">
         <v>413</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>414</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>415</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>416</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>417</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>418</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>419</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>420</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>421</v>
-      </c>
-      <c r="J77" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:43">
@@ -9881,7 +9873,7 @@
         <v>267</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C78" s="34">
         <f>'Decode_1M'!$AN$63/1E9</f>
@@ -9912,15 +9904,15 @@
         <v>284.334567511</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79" spans="1:43">
       <c r="A79" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C79" s="34">
         <f>'Decode_1M'!$AO$63/1E9</f>
@@ -9951,7 +9943,7 @@
         <v>37.064255215</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -10019,7 +10011,7 @@
         <v>296</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10245,41 +10237,41 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>314</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="30" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -10292,28 +10284,28 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B23" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D23" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E23" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G23" t="s">
-        <v>361</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="I23" t="s">
         <v>362</v>
@@ -11593,37 +11585,37 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B4" t="s">
         <v>438</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>439</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>440</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>441</v>
       </c>
-      <c r="E4" t="s">
-        <v>442</v>
-      </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B5" s="31" t="str">
         <f>TEXT(IF(ABS(G5)&gt;=1E15,G5/1E15,IF(ABS(G5)&gt;=1E12,G5/1E12,IF(ABS(G5)&gt;=1E9,G5/1E9,IF(ABS(G5)&gt;=1E6,G5/1E6,G5)))),"#,##0.000")&amp;IF((IF(ABS(G5)&gt;=1E15,"PFLOPs",IF(ABS(G5)&gt;=1E12,"TFLOPs",IF(ABS(G5)&gt;=1E9,"GFLOPs",IF(ABS(G5)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G5)&gt;=1E15,"PFLOPs",IF(ABS(G5)&gt;=1E12,"TFLOPs",IF(ABS(G5)&gt;=1E9,"GFLOPs",IF(ABS(G5)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11642,7 +11634,7 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G5" s="32">
         <f>'Prefill_8K'!$AE$13</f>
@@ -11663,7 +11655,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B6" s="31" t="str">
         <f>TEXT(IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6)))),"#,##0.000")&amp;IF((IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11682,7 +11674,7 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G6" s="32">
         <f>'Prefill_8K'!$AE$14</f>
@@ -11703,7 +11695,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="B7" s="31" t="str">
         <f>TEXT(IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7)))),"#,##0.000")&amp;IF((IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11722,7 +11714,7 @@
         <v>217.981 MFLOPs</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G7" s="32">
         <f>'Prefill_8K'!$AE$15</f>
@@ -11743,7 +11735,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="33" t="s">
-        <v>447</v>
+        <v>272</v>
       </c>
       <c r="B8" s="33" t="str">
         <f>TEXT(IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8)))),"#,##0.000")&amp;IF((IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11762,7 +11754,7 @@
         <v>23.548 GFLOPs</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G8" s="32">
         <f>'Prefill_8K'!$AE$16</f>
@@ -11802,7 +11794,7 @@
         <v>4.035 GB</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G9" s="32">
         <f>'Prefill_8K'!$AE$17</f>
@@ -11842,7 +11834,7 @@
         <v>1.605 GB</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G10" s="32">
         <f>'Prefill_8K'!$AE$18</f>
@@ -11882,7 +11874,7 @@
         <v>411.394 MB</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G11" s="32">
         <f>'Prefill_8K'!$AE$19</f>
@@ -11922,7 +11914,7 @@
         <v>6.052 GB</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G12" s="32">
         <f>'Prefill_8K'!$AE$20</f>
@@ -11943,7 +11935,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B13" s="31" t="str">
         <f>TEXT(G13,"#,##0.000")&amp;" GB/s"</f>
@@ -11962,7 +11954,7 @@
         <v>403.523 GB/s</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G13" s="32">
         <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
@@ -11983,7 +11975,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>TEXT(G14,"#,##0.000")&amp;" GB/s"</f>
@@ -12002,7 +11994,7 @@
         <v>160.521 GB/s</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G14" s="32">
         <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
@@ -12023,7 +12015,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B15" s="31" t="str">
         <f>TEXT(G15,"#,##0.000")&amp;" GB/s"</f>
@@ -12042,7 +12034,7 @@
         <v>41.139 GB/s</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G15" s="32">
         <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
@@ -12063,7 +12055,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B16" s="31" t="str">
         <f>TEXT(G16,"#,##0.000")&amp;" TFLOP/s"</f>
@@ -12082,7 +12074,7 @@
         <v>2.355 TFLOP/s</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G16" s="32">
         <f>'Prefill_8K'!$AE$16/(PrefillTargetMs/1000)/1E12</f>
@@ -12122,7 +12114,7 @@
         <v>5.865 MB</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G17" s="32">
         <f>'Prefill_8K'!$AE$21</f>
@@ -12143,7 +12135,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B18" s="31" t="str">
         <f>TEXT(G18,"#,##0.000")&amp;" GB/s"</f>
@@ -12162,7 +12154,7 @@
         <v>0.587 GB/s</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G18" s="32">
         <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
@@ -12183,7 +12175,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B19" s="31" t="str">
         <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K",""))))))</f>
@@ -12202,7 +12194,7 @@
         <v>1.140 G</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G19" s="32">
         <f>'Prefill_8K'!$AL$63</f>
@@ -12223,7 +12215,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B20" s="31" t="str">
         <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K",""))))))</f>
@@ -12242,7 +12234,7 @@
         <v>35.758 G</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G20" s="32">
         <f>'Prefill_8K'!$AL$64</f>
@@ -12263,7 +12255,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B21" s="31" t="str">
         <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K",""))))))</f>
@@ -12282,7 +12274,7 @@
         <v>166.690 M</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G21" s="32">
         <f>'Prefill_8K'!$AL$65</f>
@@ -12303,7 +12295,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="33" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B22" s="33" t="str">
         <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K",""))))))</f>
@@ -12322,7 +12314,7 @@
         <v>37.064 G</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G22" s="32">
         <f>'Prefill_8K'!$AL$66</f>
@@ -12343,7 +12335,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B23" s="31" t="str">
         <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12362,7 +12354,7 @@
         <v>2.238 GB</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G23" s="32">
         <f>'Prefill_8K'!$AN$63</f>
@@ -12383,7 +12375,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B24" s="31" t="str">
         <f>TEXT(IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12402,7 +12394,7 @@
         <v>19.578 GB</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G24" s="32">
         <f>'Prefill_8K'!$AN$64</f>
@@ -12423,7 +12415,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B25" s="31" t="str">
         <f>TEXT(IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25)))),"#,##0.000")&amp;IF((IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12442,7 +12434,7 @@
         <v>534.377 MB</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G25" s="32">
         <f>'Prefill_8K'!$AN$65</f>
@@ -12463,7 +12455,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="33" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B26" s="33" t="str">
         <f>TEXT(IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26)))),"#,##0.000")&amp;IF((IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12482,7 +12474,7 @@
         <v>22.350 GB</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G26" s="32">
         <f>'Prefill_8K'!$AN$66</f>
@@ -12503,7 +12495,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B27" s="31" t="str">
         <f>TEXT(IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27)))),"#,##0.000")&amp;IF((IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12522,7 +12514,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G27" s="32">
         <f>'Prefill_8K'!$AP$70</f>
@@ -12543,7 +12535,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B28" s="31" t="str">
         <f>TEXT(IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12562,7 +12554,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G28" s="32">
         <f>'Prefill_8K'!$AP$71</f>
@@ -12583,7 +12575,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B29" s="31" t="str">
         <f>TEXT(IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29)))),"#,##0.000")&amp;IF((IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12602,7 +12594,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G29" s="32">
         <f>'Prefill_8K'!$AP$72</f>
@@ -12623,7 +12615,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B30" s="31" t="str">
         <f>TEXT(IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30)))),"#,##0.000")&amp;IF((IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12642,7 +12634,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G30" s="32">
         <f>'Prefill_8K'!$AP$73</f>
@@ -12663,7 +12655,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="33" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B31" s="33" t="str">
         <f>TEXT(IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31)))),"#,##0.000")&amp;IF((IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12682,7 +12674,7 @@
         <v>29.582 GB</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="G31" s="32">
         <f>'Prefill_8K'!$AN$66+'Prefill_8K'!$AP$73</f>
@@ -12703,7 +12695,7 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="33" t="s">
-        <v>480</v>
+        <v>279</v>
       </c>
       <c r="B32" s="33" t="str">
         <f>TEXT(IF(ABS(G32)&gt;=1E15,G32/1E15,IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12722,7 +12714,7 @@
         <v>23.548 GFLOPs</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G32" s="32">
         <f>'Prefill_8K'!$AE$16</f>
@@ -12746,43 +12738,43 @@
         <v>2</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="19:21">
       <c r="S36" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T36" s="32">
-        <f>G32/1e+09</f>
-        <v>228384.427393024</v>
+        <f>G32/1e+12</f>
+        <v>228.384427393024</v>
       </c>
     </row>
     <row r="37" spans="19:21">
       <c r="S37" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="T37" s="32">
-        <f>H32/1e+09</f>
-        <v>55639.31418624</v>
+        <f>H32/1e+12</f>
+        <v>55.63931418624</v>
       </c>
     </row>
     <row r="38" spans="19:21">
       <c r="S38" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T38" s="32">
-        <f>I32/1e+09</f>
-        <v>140.354134102</v>
+        <f>I32/1e+12</f>
+        <v>0.140354134102</v>
       </c>
     </row>
     <row r="39" spans="19:21">
       <c r="S39" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="T39" s="32">
-        <f>J32/1e+09</f>
-        <v>23.548076118</v>
+        <f>J32/1e+12</f>
+        <v>0.023548076118</v>
       </c>
     </row>
     <row r="42" spans="19:21">
@@ -12790,10 +12782,10 @@
         <v>2</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="43" spans="19:21">
@@ -12840,10 +12832,10 @@
         <v>2</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="50" spans="19:21">
@@ -12890,10 +12882,10 @@
         <v>2</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57" spans="19:21">
@@ -12940,10 +12932,10 @@
         <v>2</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="19:21">
@@ -12990,10 +12982,10 @@
         <v>2</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="71" spans="19:21">
@@ -13040,15 +13032,15 @@
         <v>2</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="78" spans="19:21">
       <c r="S78" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="T78" s="32">
         <f>G31/1e+09</f>
@@ -13061,7 +13053,7 @@
     </row>
     <row r="79" spans="19:21">
       <c r="S79" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="T79" s="32">
         <f>I31/1e+09</f>
@@ -13094,17 +13086,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -13112,21 +13104,21 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B6" s="31" t="str">
         <f>TEXT(IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6)))),"#,##0.000")&amp;IF((IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13137,7 +13129,7 @@
         <v>123.969 GFLOPs</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G6" s="32">
         <f>'Prefill_8K'!$AE$13</f>
@@ -13150,7 +13142,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B7" s="31" t="str">
         <f>TEXT(IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7)))),"#,##0.000")&amp;IF((IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13161,7 +13153,7 @@
         <v>15.240 GFLOPs</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G7" s="32">
         <f>'Prefill_8K'!$AE$14</f>
@@ -13174,7 +13166,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="B8" s="31" t="str">
         <f>TEXT(IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8)))),"#,##0.000")&amp;IF((IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13185,7 +13177,7 @@
         <v>1.145 GFLOPs</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G8" s="32">
         <f>'Prefill_8K'!$AE$15</f>
@@ -13198,7 +13190,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="33" t="s">
-        <v>447</v>
+        <v>272</v>
       </c>
       <c r="B9" s="33" t="str">
         <f>TEXT(IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9)))),"#,##0.000")&amp;IF((IF(ABS(G9)&gt;=1E15,"PFLOPs",IF(ABS(G9)&gt;=1E12,"TFLOPs",IF(ABS(G9)&gt;=1E9,"GFLOPs",IF(ABS(G9)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G9)&gt;=1E15,"PFLOPs",IF(ABS(G9)&gt;=1E12,"TFLOPs",IF(ABS(G9)&gt;=1E9,"GFLOPs",IF(ABS(G9)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13209,7 +13201,7 @@
         <v>140.354 GFLOPs</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G9" s="32">
         <f>'Prefill_8K'!$AE$16</f>
@@ -13233,7 +13225,7 @@
         <v>10.492 GB</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G10" s="32">
         <f>'Prefill_8K'!$AE$17</f>
@@ -13257,7 +13249,7 @@
         <v>4.627 GB</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G11" s="32">
         <f>'Prefill_8K'!$AE$18</f>
@@ -13281,7 +13273,7 @@
         <v>2.265 GB</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G12" s="32">
         <f>'Prefill_8K'!$AE$19</f>
@@ -13305,7 +13297,7 @@
         <v>17.384 GB</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G13" s="32">
         <f>'Prefill_8K'!$AE$20</f>
@@ -13318,7 +13310,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>TEXT(G14,"#,##0.000")&amp;" GB/s"</f>
@@ -13329,7 +13321,7 @@
         <v>1,049.223 GB/s</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G14" s="32">
         <f>'Prefill_8K'!$AE$17/(PrefillTargetMs/1000)/1E9</f>
@@ -13342,7 +13334,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B15" s="31" t="str">
         <f>TEXT(G15,"#,##0.000")&amp;" GB/s"</f>
@@ -13353,7 +13345,7 @@
         <v>462.703 GB/s</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G15" s="32">
         <f>'Prefill_8K'!$AE$18/(PrefillTargetMs/1000)/1E9</f>
@@ -13366,7 +13358,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B16" s="31" t="str">
         <f>TEXT(G16,"#,##0.000")&amp;" GB/s"</f>
@@ -13377,7 +13369,7 @@
         <v>226.520 GB/s</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G16" s="32">
         <f>'Prefill_8K'!$AE$19/(PrefillTargetMs/1000)/1E9</f>
@@ -13390,7 +13382,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>480</v>
+        <v>279</v>
       </c>
       <c r="B17" s="31" t="str">
         <f>TEXT(IF(ABS(G17)&gt;=1E15,G17/1E15,IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E15,"PFLOPs",IF(ABS(G17)&gt;=1E12,"TFLOPs",IF(ABS(G17)&gt;=1E9,"GFLOPs",IF(ABS(G17)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E15,"PFLOPs",IF(ABS(G17)&gt;=1E12,"TFLOPs",IF(ABS(G17)&gt;=1E9,"GFLOPs",IF(ABS(G17)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13401,7 +13393,7 @@
         <v>140.354 GFLOPs</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G17" s="32">
         <f>'Prefill_8K'!$AE$16</f>
@@ -13425,7 +13417,7 @@
         <v>0.000 B</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G18" s="32">
         <f>'Prefill_8K'!$AE$21</f>
@@ -13438,7 +13430,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B19" s="31" t="str">
         <f>TEXT(G19,"#,##0.000")&amp;" GB/s"</f>
@@ -13449,7 +13441,7 @@
         <v>0.000 GB/s</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G19" s="32">
         <f>'Prefill_8K'!$AE$21/(PrefillTargetMs/1000)/1E9</f>
@@ -13462,7 +13454,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B20" s="31" t="str">
         <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K",""))))))</f>
@@ -13473,7 +13465,7 @@
         <v>5.086 G</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G20" s="32">
         <f>'Prefill_8K'!$AL$63</f>
@@ -13486,7 +13478,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B21" s="31" t="str">
         <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K",""))))))</f>
@@ -13497,7 +13489,7 @@
         <v>278.155 G</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G21" s="32">
         <f>'Prefill_8K'!$AL$64</f>
@@ -13510,7 +13502,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B22" s="31" t="str">
         <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K",""))))))</f>
@@ -13521,7 +13513,7 @@
         <v>1.093 G</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G22" s="32">
         <f>'Prefill_8K'!$AL$65</f>
@@ -13534,7 +13526,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="33" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B23" s="33" t="str">
         <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"T",IF(ABS(G23)&gt;=1E9,"G",IF(ABS(G23)&gt;=1E6,"M",IF(ABS(G23)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"T",IF(ABS(G23)&gt;=1E9,"G",IF(ABS(G23)&gt;=1E6,"M",IF(ABS(G23)&gt;=1E3,"K",""))))))</f>
@@ -13545,7 +13537,7 @@
         <v>284.335 G</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G23" s="32">
         <f>'Prefill_8K'!$AL$66</f>
@@ -13558,7 +13550,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B24" s="31" t="str">
         <f>TEXT(IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13569,7 +13561,7 @@
         <v>7.451 GB</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G24" s="32">
         <f>'Prefill_8K'!$AN$63</f>
@@ -13582,7 +13574,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B25" s="31" t="str">
         <f>TEXT(IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25)))),"#,##0.000")&amp;IF((IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13593,7 +13585,7 @@
         <v>148.351 GB</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G25" s="32">
         <f>'Prefill_8K'!$AN$64</f>
@@ -13606,7 +13598,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B26" s="31" t="str">
         <f>TEXT(IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26)))),"#,##0.000")&amp;IF((IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13617,7 +13609,7 @@
         <v>3.314 GB</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G26" s="32">
         <f>'Prefill_8K'!$AN$65</f>
@@ -13630,7 +13622,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="33" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B27" s="33" t="str">
         <f>TEXT(IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27)))),"#,##0.000")&amp;IF((IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13641,7 +13633,7 @@
         <v>159.117 GB</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G27" s="32">
         <f>'Prefill_8K'!$AN$66</f>
@@ -13654,7 +13646,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B28" s="31" t="str">
         <f>TEXT(IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13665,7 +13657,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G28" s="32">
         <f>'Prefill_8K'!$AP$70</f>
@@ -13678,7 +13670,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B29" s="31" t="str">
         <f>TEXT(IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29)))),"#,##0.000")&amp;IF((IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13689,7 +13681,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G29" s="32">
         <f>'Prefill_8K'!$AP$71</f>
@@ -13702,7 +13694,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B30" s="31" t="str">
         <f>TEXT(IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30)))),"#,##0.000")&amp;IF((IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13713,7 +13705,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G30" s="32">
         <f>'Prefill_8K'!$AP$72</f>
@@ -13726,7 +13718,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B31" s="31" t="str">
         <f>TEXT(IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31)))),"#,##0.000")&amp;IF((IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13737,7 +13729,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G31" s="32">
         <f>'Prefill_8K'!$AP$73</f>
@@ -13750,7 +13742,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="33" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B32" s="33" t="str">
         <f>TEXT(IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E12,"TB",IF(ABS(G32)&gt;=1E9,"GB",IF(ABS(G32)&gt;=1E6,"MB",IF(ABS(G32)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E12,"TB",IF(ABS(G32)&gt;=1E9,"GB",IF(ABS(G32)&gt;=1E6,"MB",IF(ABS(G32)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13761,7 +13753,7 @@
         <v>166.349 GB</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G32" s="32">
         <f>'Prefill_8K'!$AN$66+'Prefill_8K'!$AP$73</f>
@@ -13774,7 +13766,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="30" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -13782,21 +13774,21 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B36" s="31" t="str">
         <f>TEXT(IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36)))),"#,##0.000")&amp;IF((IF(ABS(G36)&gt;=1E15,"PFLOPs",IF(ABS(G36)&gt;=1E12,"TFLOPs",IF(ABS(G36)&gt;=1E9,"GFLOPs",IF(ABS(G36)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G36)&gt;=1E15,"PFLOPs",IF(ABS(G36)&gt;=1E12,"TFLOPs",IF(ABS(G36)&gt;=1E9,"GFLOPs",IF(ABS(G36)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13807,7 +13799,7 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G36" s="32">
         <f>'Prefill_8K'!$AF$13</f>
@@ -13820,7 +13812,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B37" s="31" t="str">
         <f>TEXT(IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37)))),"#,##0.000")&amp;IF((IF(ABS(G37)&gt;=1E15,"PFLOPs",IF(ABS(G37)&gt;=1E12,"TFLOPs",IF(ABS(G37)&gt;=1E9,"GFLOPs",IF(ABS(G37)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G37)&gt;=1E15,"PFLOPs",IF(ABS(G37)&gt;=1E12,"TFLOPs",IF(ABS(G37)&gt;=1E9,"GFLOPs",IF(ABS(G37)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13831,7 +13823,7 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G37" s="32">
         <f>'Prefill_8K'!$AF$14</f>
@@ -13844,7 +13836,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="B38" s="31" t="str">
         <f>TEXT(IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38)))),"#,##0.000")&amp;IF((IF(ABS(G38)&gt;=1E15,"PFLOPs",IF(ABS(G38)&gt;=1E12,"TFLOPs",IF(ABS(G38)&gt;=1E9,"GFLOPs",IF(ABS(G38)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G38)&gt;=1E15,"PFLOPs",IF(ABS(G38)&gt;=1E12,"TFLOPs",IF(ABS(G38)&gt;=1E9,"GFLOPs",IF(ABS(G38)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13855,7 +13847,7 @@
         <v>217.981 MFLOPs</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G38" s="32">
         <f>'Prefill_8K'!$AF$15</f>
@@ -13868,7 +13860,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="33" t="s">
-        <v>447</v>
+        <v>272</v>
       </c>
       <c r="B39" s="33" t="str">
         <f>TEXT(IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39)))),"#,##0.000")&amp;IF((IF(ABS(G39)&gt;=1E15,"PFLOPs",IF(ABS(G39)&gt;=1E12,"TFLOPs",IF(ABS(G39)&gt;=1E9,"GFLOPs",IF(ABS(G39)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G39)&gt;=1E15,"PFLOPs",IF(ABS(G39)&gt;=1E12,"TFLOPs",IF(ABS(G39)&gt;=1E9,"GFLOPs",IF(ABS(G39)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -13879,7 +13871,7 @@
         <v>23.548 GFLOPs</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G39" s="32">
         <f>'Prefill_8K'!$AF$16</f>
@@ -13903,7 +13895,7 @@
         <v>4.035 GB</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G40" s="32">
         <f>'Prefill_8K'!$AF$17</f>
@@ -13927,7 +13919,7 @@
         <v>1.605 GB</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G41" s="32">
         <f>'Prefill_8K'!$AF$18</f>
@@ -13951,7 +13943,7 @@
         <v>411.394 MB</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G42" s="32">
         <f>'Prefill_8K'!$AF$19</f>
@@ -13975,7 +13967,7 @@
         <v>6.052 GB</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G43" s="32">
         <f>'Prefill_8K'!$AF$20</f>
@@ -13988,7 +13980,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B44" s="31" t="str">
         <f>TEXT(G44,"#,##0.000")&amp;" GB/s"</f>
@@ -13999,7 +13991,7 @@
         <v>403.523 GB/s</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G44" s="32">
         <f>'Prefill_8K'!$AF$17/(PrefillTargetMs/1000)/1E9</f>
@@ -14012,7 +14004,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B45" s="31" t="str">
         <f>TEXT(G45,"#,##0.000")&amp;" GB/s"</f>
@@ -14023,7 +14015,7 @@
         <v>160.521 GB/s</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G45" s="32">
         <f>'Prefill_8K'!$AF$18/(PrefillTargetMs/1000)/1E9</f>
@@ -14036,7 +14028,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B46" s="31" t="str">
         <f>TEXT(G46,"#,##0.000")&amp;" GB/s"</f>
@@ -14047,7 +14039,7 @@
         <v>41.139 GB/s</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G46" s="32">
         <f>'Prefill_8K'!$AF$19/(PrefillTargetMs/1000)/1E9</f>
@@ -14060,7 +14052,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>480</v>
+        <v>279</v>
       </c>
       <c r="B47" s="31" t="str">
         <f>TEXT(IF(ABS(G47)&gt;=1E15,G47/1E15,IF(ABS(G47)&gt;=1E12,G47/1E12,IF(ABS(G47)&gt;=1E9,G47/1E9,IF(ABS(G47)&gt;=1E6,G47/1E6,G47)))),"#,##0.000")&amp;IF((IF(ABS(G47)&gt;=1E15,"PFLOPs",IF(ABS(G47)&gt;=1E12,"TFLOPs",IF(ABS(G47)&gt;=1E9,"GFLOPs",IF(ABS(G47)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G47)&gt;=1E15,"PFLOPs",IF(ABS(G47)&gt;=1E12,"TFLOPs",IF(ABS(G47)&gt;=1E9,"GFLOPs",IF(ABS(G47)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -14071,7 +14063,7 @@
         <v>23.548 GFLOPs</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G47" s="32">
         <f>'Prefill_8K'!$AF$16</f>
@@ -14095,7 +14087,7 @@
         <v>5.865 MB</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G48" s="32">
         <f>'Prefill_8K'!$AF$21</f>
@@ -14108,7 +14100,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B49" s="31" t="str">
         <f>TEXT(G49,"#,##0.000")&amp;" GB/s"</f>
@@ -14119,7 +14111,7 @@
         <v>0.587 GB/s</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G49" s="32">
         <f>'Prefill_8K'!$AF$21/(PrefillTargetMs/1000)/1E9</f>
@@ -14132,7 +14124,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B50" s="31" t="str">
         <f>TEXT(IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50)))),"#,##0.000")&amp;IF((IF(ABS(G50)&gt;=1E12,"T",IF(ABS(G50)&gt;=1E9,"G",IF(ABS(G50)&gt;=1E6,"M",IF(ABS(G50)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G50)&gt;=1E12,"T",IF(ABS(G50)&gt;=1E9,"G",IF(ABS(G50)&gt;=1E6,"M",IF(ABS(G50)&gt;=1E3,"K",""))))))</f>
@@ -14143,7 +14135,7 @@
         <v>1.140 G</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G50" s="32">
         <f>'Prefill_8K'!$AM$63</f>
@@ -14156,7 +14148,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B51" s="31" t="str">
         <f>TEXT(IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51)))),"#,##0.000")&amp;IF((IF(ABS(G51)&gt;=1E12,"T",IF(ABS(G51)&gt;=1E9,"G",IF(ABS(G51)&gt;=1E6,"M",IF(ABS(G51)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G51)&gt;=1E12,"T",IF(ABS(G51)&gt;=1E9,"G",IF(ABS(G51)&gt;=1E6,"M",IF(ABS(G51)&gt;=1E3,"K",""))))))</f>
@@ -14167,7 +14159,7 @@
         <v>35.758 G</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G51" s="32">
         <f>'Prefill_8K'!$AM$64</f>
@@ -14180,7 +14172,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B52" s="31" t="str">
         <f>TEXT(IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52)))),"#,##0.000")&amp;IF((IF(ABS(G52)&gt;=1E12,"T",IF(ABS(G52)&gt;=1E9,"G",IF(ABS(G52)&gt;=1E6,"M",IF(ABS(G52)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G52)&gt;=1E12,"T",IF(ABS(G52)&gt;=1E9,"G",IF(ABS(G52)&gt;=1E6,"M",IF(ABS(G52)&gt;=1E3,"K",""))))))</f>
@@ -14191,7 +14183,7 @@
         <v>166.690 M</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G52" s="32">
         <f>'Prefill_8K'!$AM$65</f>
@@ -14204,7 +14196,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="33" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B53" s="33" t="str">
         <f>TEXT(IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53)))),"#,##0.000")&amp;IF((IF(ABS(G53)&gt;=1E12,"T",IF(ABS(G53)&gt;=1E9,"G",IF(ABS(G53)&gt;=1E6,"M",IF(ABS(G53)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G53)&gt;=1E12,"T",IF(ABS(G53)&gt;=1E9,"G",IF(ABS(G53)&gt;=1E6,"M",IF(ABS(G53)&gt;=1E3,"K",""))))))</f>
@@ -14215,7 +14207,7 @@
         <v>37.064 G</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G53" s="32">
         <f>'Prefill_8K'!$AM$66</f>
@@ -14228,7 +14220,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B54" s="31" t="str">
         <f>TEXT(IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54)))),"#,##0.000")&amp;IF((IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14239,7 +14231,7 @@
         <v>2.238 GB</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G54" s="32">
         <f>'Prefill_8K'!$AO$63</f>
@@ -14252,7 +14244,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B55" s="31" t="str">
         <f>TEXT(IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55)))),"#,##0.000")&amp;IF((IF(ABS(G55)&gt;=1E12,"TB",IF(ABS(G55)&gt;=1E9,"GB",IF(ABS(G55)&gt;=1E6,"MB",IF(ABS(G55)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G55)&gt;=1E12,"TB",IF(ABS(G55)&gt;=1E9,"GB",IF(ABS(G55)&gt;=1E6,"MB",IF(ABS(G55)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14263,7 +14255,7 @@
         <v>19.578 GB</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G55" s="32">
         <f>'Prefill_8K'!$AO$64</f>
@@ -14276,7 +14268,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B56" s="31" t="str">
         <f>TEXT(IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56)))),"#,##0.000")&amp;IF((IF(ABS(G56)&gt;=1E12,"TB",IF(ABS(G56)&gt;=1E9,"GB",IF(ABS(G56)&gt;=1E6,"MB",IF(ABS(G56)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G56)&gt;=1E12,"TB",IF(ABS(G56)&gt;=1E9,"GB",IF(ABS(G56)&gt;=1E6,"MB",IF(ABS(G56)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14287,7 +14279,7 @@
         <v>534.377 MB</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G56" s="32">
         <f>'Prefill_8K'!$AO$65</f>
@@ -14300,7 +14292,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="33" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B57" s="33" t="str">
         <f>TEXT(IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57)))),"#,##0.000")&amp;IF((IF(ABS(G57)&gt;=1E12,"TB",IF(ABS(G57)&gt;=1E9,"GB",IF(ABS(G57)&gt;=1E6,"MB",IF(ABS(G57)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G57)&gt;=1E12,"TB",IF(ABS(G57)&gt;=1E9,"GB",IF(ABS(G57)&gt;=1E6,"MB",IF(ABS(G57)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14311,7 +14303,7 @@
         <v>22.350 GB</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G57" s="32">
         <f>'Prefill_8K'!$AO$66</f>
@@ -14324,7 +14316,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B58" s="31" t="str">
         <f>TEXT(IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58)))),"#,##0.000")&amp;IF((IF(ABS(G58)&gt;=1E12,"TB",IF(ABS(G58)&gt;=1E9,"GB",IF(ABS(G58)&gt;=1E6,"MB",IF(ABS(G58)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G58)&gt;=1E12,"TB",IF(ABS(G58)&gt;=1E9,"GB",IF(ABS(G58)&gt;=1E6,"MB",IF(ABS(G58)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14335,7 +14327,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G58" s="32">
         <f>'Prefill_8K'!$AQ$70</f>
@@ -14348,7 +14340,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B59" s="31" t="str">
         <f>TEXT(IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59)))),"#,##0.000")&amp;IF((IF(ABS(G59)&gt;=1E12,"TB",IF(ABS(G59)&gt;=1E9,"GB",IF(ABS(G59)&gt;=1E6,"MB",IF(ABS(G59)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G59)&gt;=1E12,"TB",IF(ABS(G59)&gt;=1E9,"GB",IF(ABS(G59)&gt;=1E6,"MB",IF(ABS(G59)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14359,7 +14351,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G59" s="32">
         <f>'Prefill_8K'!$AQ$71</f>
@@ -14372,7 +14364,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B60" s="31" t="str">
         <f>TEXT(IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60)))),"#,##0.000")&amp;IF((IF(ABS(G60)&gt;=1E12,"TB",IF(ABS(G60)&gt;=1E9,"GB",IF(ABS(G60)&gt;=1E6,"MB",IF(ABS(G60)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G60)&gt;=1E12,"TB",IF(ABS(G60)&gt;=1E9,"GB",IF(ABS(G60)&gt;=1E6,"MB",IF(ABS(G60)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14383,7 +14375,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G60" s="32">
         <f>'Prefill_8K'!$AQ$72</f>
@@ -14396,7 +14388,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B61" s="31" t="str">
         <f>TEXT(IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61)))),"#,##0.000")&amp;IF((IF(ABS(G61)&gt;=1E12,"TB",IF(ABS(G61)&gt;=1E9,"GB",IF(ABS(G61)&gt;=1E6,"MB",IF(ABS(G61)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G61)&gt;=1E12,"TB",IF(ABS(G61)&gt;=1E9,"GB",IF(ABS(G61)&gt;=1E6,"MB",IF(ABS(G61)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14407,7 +14399,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G61" s="32">
         <f>'Prefill_8K'!$AQ$73</f>
@@ -14420,7 +14412,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="33" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B62" s="33" t="str">
         <f>TEXT(IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62)))),"#,##0.000")&amp;IF((IF(ABS(G62)&gt;=1E12,"TB",IF(ABS(G62)&gt;=1E9,"GB",IF(ABS(G62)&gt;=1E6,"MB",IF(ABS(G62)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G62)&gt;=1E12,"TB",IF(ABS(G62)&gt;=1E9,"GB",IF(ABS(G62)&gt;=1E6,"MB",IF(ABS(G62)&gt;=1E3,"KB","bytes"))))))</f>
@@ -14431,7 +14423,7 @@
         <v>29.582 GB</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G62" s="32">
         <f>'Prefill_8K'!$AO$66+'Prefill_8K'!$AQ$73</f>
@@ -14463,32 +14455,32 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -14499,19 +14491,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D4" s="38">
         <f>IF(C4="window",0,IF(C4="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E4" s="4" t="str">
-        <f>IF(B4=0,"未启用",IF(C4="window","原始滑动窗口",IF(C4="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>原始滑动窗口</v>
+        <f>IF(B4=0,"inactive",IF(C4="window","raw sliding window",IF(C4="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>raw sliding window</v>
       </c>
       <c r="F4" s="4" t="str">
-        <f>IF(B4=0,"未启用",IF(A4&lt;HashLayers,"哈希","评分"))</f>
-        <v>哈希</v>
+        <f>IF(B4=0,"inactive",IF(A4&lt;HashLayers,"hash","score"))</f>
+        <v>hash</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -14522,19 +14514,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D5" s="38">
         <f>IF(C5="window",0,IF(C5="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E5" s="4" t="str">
-        <f>IF(B5=0,"未启用",IF(C5="window","原始滑动窗口",IF(C5="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>原始滑动窗口</v>
+        <f>IF(B5=0,"inactive",IF(C5="window","raw sliding window",IF(C5="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>raw sliding window</v>
       </c>
       <c r="F5" s="4" t="str">
-        <f>IF(B5=0,"未启用",IF(A5&lt;HashLayers,"哈希","评分"))</f>
-        <v>哈希</v>
+        <f>IF(B5=0,"inactive",IF(A5&lt;HashLayers,"hash","score"))</f>
+        <v>hash</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -14545,19 +14537,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D6" s="38">
         <f>IF(C6="window",0,IF(C6="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E6" s="4" t="str">
-        <f>IF(B6=0,"未启用",IF(C6="window","原始滑动窗口",IF(C6="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B6=0,"inactive",IF(C6="window","raw sliding window",IF(C6="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F6" s="4" t="str">
-        <f>IF(B6=0,"未启用",IF(A6&lt;HashLayers,"哈希","评分"))</f>
-        <v>哈希</v>
+        <f>IF(B6=0,"inactive",IF(A6&lt;HashLayers,"hash","score"))</f>
+        <v>hash</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -14568,19 +14560,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D7" s="38">
         <f>IF(C7="window",0,IF(C7="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E7" s="4" t="str">
-        <f>IF(B7=0,"未启用",IF(C7="window","原始滑动窗口",IF(C7="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B7=0,"inactive",IF(C7="window","raw sliding window",IF(C7="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F7" s="4" t="str">
-        <f>IF(B7=0,"未启用",IF(A7&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B7=0,"inactive",IF(A7&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -14591,19 +14583,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D8" s="38">
         <f>IF(C8="window",0,IF(C8="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E8" s="4" t="str">
-        <f>IF(B8=0,"未启用",IF(C8="window","原始滑动窗口",IF(C8="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B8=0,"inactive",IF(C8="window","raw sliding window",IF(C8="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F8" s="4" t="str">
-        <f>IF(B8=0,"未启用",IF(A8&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B8=0,"inactive",IF(A8&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -14614,19 +14606,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D9" s="38">
         <f>IF(C9="window",0,IF(C9="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E9" s="4" t="str">
-        <f>IF(B9=0,"未启用",IF(C9="window","原始滑动窗口",IF(C9="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B9=0,"inactive",IF(C9="window","raw sliding window",IF(C9="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F9" s="4" t="str">
-        <f>IF(B9=0,"未启用",IF(A9&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B9=0,"inactive",IF(A9&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -14637,19 +14629,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D10" s="38">
         <f>IF(C10="window",0,IF(C10="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E10" s="4" t="str">
-        <f>IF(B10=0,"未启用",IF(C10="window","原始滑动窗口",IF(C10="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B10=0,"inactive",IF(C10="window","raw sliding window",IF(C10="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F10" s="4" t="str">
-        <f>IF(B10=0,"未启用",IF(A10&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B10=0,"inactive",IF(A10&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -14660,19 +14652,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D11" s="38">
         <f>IF(C11="window",0,IF(C11="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E11" s="4" t="str">
-        <f>IF(B11=0,"未启用",IF(C11="window","原始滑动窗口",IF(C11="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B11=0,"inactive",IF(C11="window","raw sliding window",IF(C11="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F11" s="4" t="str">
-        <f>IF(B11=0,"未启用",IF(A11&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B11=0,"inactive",IF(A11&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -14683,19 +14675,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D12" s="38">
         <f>IF(C12="window",0,IF(C12="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f>IF(B12=0,"未启用",IF(C12="window","原始滑动窗口",IF(C12="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B12=0,"inactive",IF(C12="window","raw sliding window",IF(C12="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f>IF(B12=0,"未启用",IF(A12&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B12=0,"inactive",IF(A12&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -14706,19 +14698,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D13" s="38">
         <f>IF(C13="window",0,IF(C13="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f>IF(B13=0,"未启用",IF(C13="window","原始滑动窗口",IF(C13="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B13=0,"inactive",IF(C13="window","raw sliding window",IF(C13="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F13" s="4" t="str">
-        <f>IF(B13=0,"未启用",IF(A13&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B13=0,"inactive",IF(A13&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -14729,19 +14721,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D14" s="38">
         <f>IF(C14="window",0,IF(C14="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E14" s="4" t="str">
-        <f>IF(B14=0,"未启用",IF(C14="window","原始滑动窗口",IF(C14="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B14=0,"inactive",IF(C14="window","raw sliding window",IF(C14="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F14" s="4" t="str">
-        <f>IF(B14=0,"未启用",IF(A14&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B14=0,"inactive",IF(A14&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -14752,19 +14744,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D15" s="38">
         <f>IF(C15="window",0,IF(C15="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E15" s="4" t="str">
-        <f>IF(B15=0,"未启用",IF(C15="window","原始滑动窗口",IF(C15="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B15=0,"inactive",IF(C15="window","raw sliding window",IF(C15="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F15" s="4" t="str">
-        <f>IF(B15=0,"未启用",IF(A15&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B15=0,"inactive",IF(A15&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -14775,19 +14767,19 @@
         <v>1</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D16" s="38">
         <f>IF(C16="window",0,IF(C16="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E16" s="4" t="str">
-        <f>IF(B16=0,"未启用",IF(C16="window","原始滑动窗口",IF(C16="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B16=0,"inactive",IF(C16="window","raw sliding window",IF(C16="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F16" s="4" t="str">
-        <f>IF(B16=0,"未启用",IF(A16&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B16=0,"inactive",IF(A16&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -14798,19 +14790,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D17" s="38">
         <f>IF(C17="window",0,IF(C17="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E17" s="4" t="str">
-        <f>IF(B17=0,"未启用",IF(C17="window","原始滑动窗口",IF(C17="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B17=0,"inactive",IF(C17="window","raw sliding window",IF(C17="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F17" s="4" t="str">
-        <f>IF(B17=0,"未启用",IF(A17&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B17=0,"inactive",IF(A17&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -14821,19 +14813,19 @@
         <v>1</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D18" s="38">
         <f>IF(C18="window",0,IF(C18="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E18" s="4" t="str">
-        <f>IF(B18=0,"未启用",IF(C18="window","原始滑动窗口",IF(C18="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B18=0,"inactive",IF(C18="window","raw sliding window",IF(C18="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F18" s="4" t="str">
-        <f>IF(B18=0,"未启用",IF(A18&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B18=0,"inactive",IF(A18&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -14844,19 +14836,19 @@
         <v>1</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D19" s="38">
         <f>IF(C19="window",0,IF(C19="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E19" s="4" t="str">
-        <f>IF(B19=0,"未启用",IF(C19="window","原始滑动窗口",IF(C19="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B19=0,"inactive",IF(C19="window","raw sliding window",IF(C19="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F19" s="4" t="str">
-        <f>IF(B19=0,"未启用",IF(A19&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B19=0,"inactive",IF(A19&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -14867,19 +14859,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D20" s="38">
         <f>IF(C20="window",0,IF(C20="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E20" s="4" t="str">
-        <f>IF(B20=0,"未启用",IF(C20="window","原始滑动窗口",IF(C20="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B20=0,"inactive",IF(C20="window","raw sliding window",IF(C20="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F20" s="4" t="str">
-        <f>IF(B20=0,"未启用",IF(A20&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B20=0,"inactive",IF(A20&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -14890,19 +14882,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D21" s="38">
         <f>IF(C21="window",0,IF(C21="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E21" s="4" t="str">
-        <f>IF(B21=0,"未启用",IF(C21="window","原始滑动窗口",IF(C21="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B21=0,"inactive",IF(C21="window","raw sliding window",IF(C21="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F21" s="4" t="str">
-        <f>IF(B21=0,"未启用",IF(A21&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B21=0,"inactive",IF(A21&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -14913,19 +14905,19 @@
         <v>1</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D22" s="38">
         <f>IF(C22="window",0,IF(C22="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E22" s="4" t="str">
-        <f>IF(B22=0,"未启用",IF(C22="window","原始滑动窗口",IF(C22="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B22=0,"inactive",IF(C22="window","raw sliding window",IF(C22="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F22" s="4" t="str">
-        <f>IF(B22=0,"未启用",IF(A22&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B22=0,"inactive",IF(A22&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -14936,19 +14928,19 @@
         <v>1</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D23" s="38">
         <f>IF(C23="window",0,IF(C23="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E23" s="4" t="str">
-        <f>IF(B23=0,"未启用",IF(C23="window","原始滑动窗口",IF(C23="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B23=0,"inactive",IF(C23="window","raw sliding window",IF(C23="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F23" s="4" t="str">
-        <f>IF(B23=0,"未启用",IF(A23&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B23=0,"inactive",IF(A23&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -14959,19 +14951,19 @@
         <v>1</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D24" s="38">
         <f>IF(C24="window",0,IF(C24="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E24" s="4" t="str">
-        <f>IF(B24=0,"未启用",IF(C24="window","原始滑动窗口",IF(C24="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B24=0,"inactive",IF(C24="window","raw sliding window",IF(C24="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F24" s="4" t="str">
-        <f>IF(B24=0,"未启用",IF(A24&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B24=0,"inactive",IF(A24&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -14982,19 +14974,19 @@
         <v>1</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D25" s="38">
         <f>IF(C25="window",0,IF(C25="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E25" s="4" t="str">
-        <f>IF(B25=0,"未启用",IF(C25="window","原始滑动窗口",IF(C25="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B25=0,"inactive",IF(C25="window","raw sliding window",IF(C25="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F25" s="4" t="str">
-        <f>IF(B25=0,"未启用",IF(A25&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B25=0,"inactive",IF(A25&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -15005,19 +14997,19 @@
         <v>1</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D26" s="38">
         <f>IF(C26="window",0,IF(C26="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E26" s="4" t="str">
-        <f>IF(B26=0,"未启用",IF(C26="window","原始滑动窗口",IF(C26="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B26=0,"inactive",IF(C26="window","raw sliding window",IF(C26="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F26" s="4" t="str">
-        <f>IF(B26=0,"未启用",IF(A26&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B26=0,"inactive",IF(A26&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -15028,19 +15020,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D27" s="38">
         <f>IF(C27="window",0,IF(C27="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E27" s="4" t="str">
-        <f>IF(B27=0,"未启用",IF(C27="window","原始滑动窗口",IF(C27="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B27=0,"inactive",IF(C27="window","raw sliding window",IF(C27="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F27" s="4" t="str">
-        <f>IF(B27=0,"未启用",IF(A27&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B27=0,"inactive",IF(A27&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -15051,19 +15043,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D28" s="38">
         <f>IF(C28="window",0,IF(C28="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E28" s="4" t="str">
-        <f>IF(B28=0,"未启用",IF(C28="window","原始滑动窗口",IF(C28="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B28=0,"inactive",IF(C28="window","raw sliding window",IF(C28="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F28" s="4" t="str">
-        <f>IF(B28=0,"未启用",IF(A28&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B28=0,"inactive",IF(A28&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -15074,19 +15066,19 @@
         <v>1</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D29" s="38">
         <f>IF(C29="window",0,IF(C29="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E29" s="4" t="str">
-        <f>IF(B29=0,"未启用",IF(C29="window","原始滑动窗口",IF(C29="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B29=0,"inactive",IF(C29="window","raw sliding window",IF(C29="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F29" s="4" t="str">
-        <f>IF(B29=0,"未启用",IF(A29&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B29=0,"inactive",IF(A29&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -15097,19 +15089,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D30" s="38">
         <f>IF(C30="window",0,IF(C30="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E30" s="4" t="str">
-        <f>IF(B30=0,"未启用",IF(C30="window","原始滑动窗口",IF(C30="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B30=0,"inactive",IF(C30="window","raw sliding window",IF(C30="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F30" s="4" t="str">
-        <f>IF(B30=0,"未启用",IF(A30&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B30=0,"inactive",IF(A30&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -15120,19 +15112,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D31" s="38">
         <f>IF(C31="window",0,IF(C31="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E31" s="4" t="str">
-        <f>IF(B31=0,"未启用",IF(C31="window","原始滑动窗口",IF(C31="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B31=0,"inactive",IF(C31="window","raw sliding window",IF(C31="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F31" s="4" t="str">
-        <f>IF(B31=0,"未启用",IF(A31&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B31=0,"inactive",IF(A31&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -15143,19 +15135,19 @@
         <v>1</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D32" s="38">
         <f>IF(C32="window",0,IF(C32="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E32" s="4" t="str">
-        <f>IF(B32=0,"未启用",IF(C32="window","原始滑动窗口",IF(C32="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B32=0,"inactive",IF(C32="window","raw sliding window",IF(C32="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F32" s="4" t="str">
-        <f>IF(B32=0,"未启用",IF(A32&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B32=0,"inactive",IF(A32&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -15166,19 +15158,19 @@
         <v>1</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D33" s="38">
         <f>IF(C33="window",0,IF(C33="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E33" s="4" t="str">
-        <f>IF(B33=0,"未启用",IF(C33="window","原始滑动窗口",IF(C33="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B33=0,"inactive",IF(C33="window","raw sliding window",IF(C33="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F33" s="4" t="str">
-        <f>IF(B33=0,"未启用",IF(A33&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B33=0,"inactive",IF(A33&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -15189,19 +15181,19 @@
         <v>1</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D34" s="38">
         <f>IF(C34="window",0,IF(C34="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E34" s="4" t="str">
-        <f>IF(B34=0,"未启用",IF(C34="window","原始滑动窗口",IF(C34="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B34=0,"inactive",IF(C34="window","raw sliding window",IF(C34="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F34" s="4" t="str">
-        <f>IF(B34=0,"未启用",IF(A34&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B34=0,"inactive",IF(A34&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -15212,19 +15204,19 @@
         <v>1</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D35" s="38">
         <f>IF(C35="window",0,IF(C35="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E35" s="4" t="str">
-        <f>IF(B35=0,"未启用",IF(C35="window","原始滑动窗口",IF(C35="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B35=0,"inactive",IF(C35="window","raw sliding window",IF(C35="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F35" s="4" t="str">
-        <f>IF(B35=0,"未启用",IF(A35&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B35=0,"inactive",IF(A35&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -15235,19 +15227,19 @@
         <v>1</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D36" s="38">
         <f>IF(C36="window",0,IF(C36="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E36" s="4" t="str">
-        <f>IF(B36=0,"未启用",IF(C36="window","原始滑动窗口",IF(C36="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B36=0,"inactive",IF(C36="window","raw sliding window",IF(C36="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F36" s="4" t="str">
-        <f>IF(B36=0,"未启用",IF(A36&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B36=0,"inactive",IF(A36&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -15258,19 +15250,19 @@
         <v>1</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D37" s="38">
         <f>IF(C37="window",0,IF(C37="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E37" s="4" t="str">
-        <f>IF(B37=0,"未启用",IF(C37="window","原始滑动窗口",IF(C37="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B37=0,"inactive",IF(C37="window","raw sliding window",IF(C37="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F37" s="4" t="str">
-        <f>IF(B37=0,"未启用",IF(A37&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B37=0,"inactive",IF(A37&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -15281,19 +15273,19 @@
         <v>1</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D38" s="38">
         <f>IF(C38="window",0,IF(C38="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E38" s="4" t="str">
-        <f>IF(B38=0,"未启用",IF(C38="window","原始滑动窗口",IF(C38="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B38=0,"inactive",IF(C38="window","raw sliding window",IF(C38="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F38" s="4" t="str">
-        <f>IF(B38=0,"未启用",IF(A38&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B38=0,"inactive",IF(A38&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -15304,19 +15296,19 @@
         <v>1</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D39" s="38">
         <f>IF(C39="window",0,IF(C39="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E39" s="4" t="str">
-        <f>IF(B39=0,"未启用",IF(C39="window","原始滑动窗口",IF(C39="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B39=0,"inactive",IF(C39="window","raw sliding window",IF(C39="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F39" s="4" t="str">
-        <f>IF(B39=0,"未启用",IF(A39&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B39=0,"inactive",IF(A39&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -15327,19 +15319,19 @@
         <v>1</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D40" s="38">
         <f>IF(C40="window",0,IF(C40="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E40" s="4" t="str">
-        <f>IF(B40=0,"未启用",IF(C40="window","原始滑动窗口",IF(C40="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B40=0,"inactive",IF(C40="window","raw sliding window",IF(C40="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F40" s="4" t="str">
-        <f>IF(B40=0,"未启用",IF(A40&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B40=0,"inactive",IF(A40&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -15350,19 +15342,19 @@
         <v>1</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D41" s="38">
         <f>IF(C41="window",0,IF(C41="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E41" s="4" t="str">
-        <f>IF(B41=0,"未启用",IF(C41="window","原始滑动窗口",IF(C41="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B41=0,"inactive",IF(C41="window","raw sliding window",IF(C41="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F41" s="4" t="str">
-        <f>IF(B41=0,"未启用",IF(A41&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B41=0,"inactive",IF(A41&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -15373,19 +15365,19 @@
         <v>1</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D42" s="38">
         <f>IF(C42="window",0,IF(C42="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E42" s="4" t="str">
-        <f>IF(B42=0,"未启用",IF(C42="window","原始滑动窗口",IF(C42="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B42=0,"inactive",IF(C42="window","raw sliding window",IF(C42="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F42" s="4" t="str">
-        <f>IF(B42=0,"未启用",IF(A42&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B42=0,"inactive",IF(A42&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -15396,19 +15388,19 @@
         <v>1</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D43" s="38">
         <f>IF(C43="window",0,IF(C43="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E43" s="4" t="str">
-        <f>IF(B43=0,"未启用",IF(C43="window","原始滑动窗口",IF(C43="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B43=0,"inactive",IF(C43="window","raw sliding window",IF(C43="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F43" s="4" t="str">
-        <f>IF(B43=0,"未启用",IF(A43&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B43=0,"inactive",IF(A43&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -15419,19 +15411,19 @@
         <v>1</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D44" s="38">
         <f>IF(C44="window",0,IF(C44="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E44" s="4" t="str">
-        <f>IF(B44=0,"未启用",IF(C44="window","原始滑动窗口",IF(C44="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B44=0,"inactive",IF(C44="window","raw sliding window",IF(C44="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F44" s="4" t="str">
-        <f>IF(B44=0,"未启用",IF(A44&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B44=0,"inactive",IF(A44&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -15442,19 +15434,19 @@
         <v>1</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D45" s="38">
         <f>IF(C45="window",0,IF(C45="short",ShortRatio,LongRatio))</f>
         <v>128</v>
       </c>
       <c r="E45" s="4" t="str">
-        <f>IF(B45=0,"未启用",IF(C45="window","原始滑动窗口",IF(C45="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>确定性压缩 KV</v>
+        <f>IF(B45=0,"inactive",IF(C45="window","raw sliding window",IF(C45="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>deterministic compressed KV</v>
       </c>
       <c r="F45" s="4" t="str">
-        <f>IF(B45=0,"未启用",IF(A45&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B45=0,"inactive",IF(A45&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -15465,19 +15457,19 @@
         <v>1</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D46" s="38">
         <f>IF(C46="window",0,IF(C46="short",ShortRatio,LongRatio))</f>
         <v>4</v>
       </c>
       <c r="E46" s="4" t="str">
-        <f>IF(B46=0,"未启用",IF(C46="window","原始滑动窗口",IF(C46="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>压缩 KV + Indexer Top-K</v>
+        <f>IF(B46=0,"inactive",IF(C46="window","raw sliding window",IF(C46="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F46" s="4" t="str">
-        <f>IF(B46=0,"未启用",IF(A46&lt;HashLayers,"哈希","评分"))</f>
-        <v>评分</v>
+        <f>IF(B46=0,"inactive",IF(A46&lt;HashLayers,"hash","score"))</f>
+        <v>score</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -15488,19 +15480,19 @@
         <v>0</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D47" s="38">
         <f>IF(C47="window",0,IF(C47="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E47" s="4" t="str">
-        <f>IF(B47=0,"未启用",IF(C47="window","原始滑动窗口",IF(C47="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B47=0,"inactive",IF(C47="window","raw sliding window",IF(C47="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F47" s="4" t="str">
-        <f>IF(B47=0,"未启用",IF(A47&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B47=0,"inactive",IF(A47&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -15511,19 +15503,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D48" s="38">
         <f>IF(C48="window",0,IF(C48="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E48" s="4" t="str">
-        <f>IF(B48=0,"未启用",IF(C48="window","原始滑动窗口",IF(C48="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B48=0,"inactive",IF(C48="window","raw sliding window",IF(C48="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F48" s="4" t="str">
-        <f>IF(B48=0,"未启用",IF(A48&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B48=0,"inactive",IF(A48&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -15534,19 +15526,19 @@
         <v>0</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D49" s="38">
         <f>IF(C49="window",0,IF(C49="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E49" s="4" t="str">
-        <f>IF(B49=0,"未启用",IF(C49="window","原始滑动窗口",IF(C49="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B49=0,"inactive",IF(C49="window","raw sliding window",IF(C49="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F49" s="4" t="str">
-        <f>IF(B49=0,"未启用",IF(A49&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B49=0,"inactive",IF(A49&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -15557,19 +15549,19 @@
         <v>0</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D50" s="38">
         <f>IF(C50="window",0,IF(C50="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E50" s="4" t="str">
-        <f>IF(B50=0,"未启用",IF(C50="window","原始滑动窗口",IF(C50="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B50=0,"inactive",IF(C50="window","raw sliding window",IF(C50="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F50" s="4" t="str">
-        <f>IF(B50=0,"未启用",IF(A50&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B50=0,"inactive",IF(A50&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -15580,19 +15572,19 @@
         <v>0</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D51" s="38">
         <f>IF(C51="window",0,IF(C51="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E51" s="4" t="str">
-        <f>IF(B51=0,"未启用",IF(C51="window","原始滑动窗口",IF(C51="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B51=0,"inactive",IF(C51="window","raw sliding window",IF(C51="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F51" s="4" t="str">
-        <f>IF(B51=0,"未启用",IF(A51&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B51=0,"inactive",IF(A51&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -15603,19 +15595,19 @@
         <v>0</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D52" s="38">
         <f>IF(C52="window",0,IF(C52="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E52" s="4" t="str">
-        <f>IF(B52=0,"未启用",IF(C52="window","原始滑动窗口",IF(C52="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B52=0,"inactive",IF(C52="window","raw sliding window",IF(C52="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F52" s="4" t="str">
-        <f>IF(B52=0,"未启用",IF(A52&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B52=0,"inactive",IF(A52&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -15626,19 +15618,19 @@
         <v>0</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D53" s="38">
         <f>IF(C53="window",0,IF(C53="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E53" s="4" t="str">
-        <f>IF(B53=0,"未启用",IF(C53="window","原始滑动窗口",IF(C53="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B53=0,"inactive",IF(C53="window","raw sliding window",IF(C53="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F53" s="4" t="str">
-        <f>IF(B53=0,"未启用",IF(A53&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B53=0,"inactive",IF(A53&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -15649,19 +15641,19 @@
         <v>0</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D54" s="38">
         <f>IF(C54="window",0,IF(C54="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E54" s="4" t="str">
-        <f>IF(B54=0,"未启用",IF(C54="window","原始滑动窗口",IF(C54="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B54=0,"inactive",IF(C54="window","raw sliding window",IF(C54="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F54" s="4" t="str">
-        <f>IF(B54=0,"未启用",IF(A54&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B54=0,"inactive",IF(A54&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -15672,19 +15664,19 @@
         <v>0</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D55" s="38">
         <f>IF(C55="window",0,IF(C55="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E55" s="4" t="str">
-        <f>IF(B55=0,"未启用",IF(C55="window","原始滑动窗口",IF(C55="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B55=0,"inactive",IF(C55="window","raw sliding window",IF(C55="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F55" s="4" t="str">
-        <f>IF(B55=0,"未启用",IF(A55&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B55=0,"inactive",IF(A55&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -15695,19 +15687,19 @@
         <v>0</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D56" s="38">
         <f>IF(C56="window",0,IF(C56="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E56" s="4" t="str">
-        <f>IF(B56=0,"未启用",IF(C56="window","原始滑动窗口",IF(C56="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B56=0,"inactive",IF(C56="window","raw sliding window",IF(C56="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F56" s="4" t="str">
-        <f>IF(B56=0,"未启用",IF(A56&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B56=0,"inactive",IF(A56&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -15718,19 +15710,19 @@
         <v>0</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D57" s="38">
         <f>IF(C57="window",0,IF(C57="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E57" s="4" t="str">
-        <f>IF(B57=0,"未启用",IF(C57="window","原始滑动窗口",IF(C57="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B57=0,"inactive",IF(C57="window","raw sliding window",IF(C57="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F57" s="4" t="str">
-        <f>IF(B57=0,"未启用",IF(A57&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B57=0,"inactive",IF(A57&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -15741,19 +15733,19 @@
         <v>0</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D58" s="38">
         <f>IF(C58="window",0,IF(C58="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E58" s="4" t="str">
-        <f>IF(B58=0,"未启用",IF(C58="window","原始滑动窗口",IF(C58="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B58=0,"inactive",IF(C58="window","raw sliding window",IF(C58="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F58" s="4" t="str">
-        <f>IF(B58=0,"未启用",IF(A58&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B58=0,"inactive",IF(A58&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -15764,19 +15756,19 @@
         <v>0</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D59" s="38">
         <f>IF(C59="window",0,IF(C59="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E59" s="4" t="str">
-        <f>IF(B59=0,"未启用",IF(C59="window","原始滑动窗口",IF(C59="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B59=0,"inactive",IF(C59="window","raw sliding window",IF(C59="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F59" s="4" t="str">
-        <f>IF(B59=0,"未启用",IF(A59&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B59=0,"inactive",IF(A59&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -15787,19 +15779,19 @@
         <v>0</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D60" s="38">
         <f>IF(C60="window",0,IF(C60="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E60" s="4" t="str">
-        <f>IF(B60=0,"未启用",IF(C60="window","原始滑动窗口",IF(C60="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B60=0,"inactive",IF(C60="window","raw sliding window",IF(C60="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F60" s="4" t="str">
-        <f>IF(B60=0,"未启用",IF(A60&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B60=0,"inactive",IF(A60&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -15810,19 +15802,19 @@
         <v>0</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D61" s="38">
         <f>IF(C61="window",0,IF(C61="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E61" s="4" t="str">
-        <f>IF(B61=0,"未启用",IF(C61="window","原始滑动窗口",IF(C61="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B61=0,"inactive",IF(C61="window","raw sliding window",IF(C61="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F61" s="4" t="str">
-        <f>IF(B61=0,"未启用",IF(A61&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B61=0,"inactive",IF(A61&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -15833,19 +15825,19 @@
         <v>0</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D62" s="38">
         <f>IF(C62="window",0,IF(C62="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E62" s="4" t="str">
-        <f>IF(B62=0,"未启用",IF(C62="window","原始滑动窗口",IF(C62="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B62=0,"inactive",IF(C62="window","raw sliding window",IF(C62="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F62" s="4" t="str">
-        <f>IF(B62=0,"未启用",IF(A62&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B62=0,"inactive",IF(A62&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -15856,19 +15848,19 @@
         <v>0</v>
       </c>
       <c r="C63" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D63" s="38">
         <f>IF(C63="window",0,IF(C63="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E63" s="4" t="str">
-        <f>IF(B63=0,"未启用",IF(C63="window","原始滑动窗口",IF(C63="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B63=0,"inactive",IF(C63="window","raw sliding window",IF(C63="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F63" s="4" t="str">
-        <f>IF(B63=0,"未启用",IF(A63&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B63=0,"inactive",IF(A63&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -15879,19 +15871,19 @@
         <v>0</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D64" s="38">
         <f>IF(C64="window",0,IF(C64="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E64" s="4" t="str">
-        <f>IF(B64=0,"未启用",IF(C64="window","原始滑动窗口",IF(C64="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B64=0,"inactive",IF(C64="window","raw sliding window",IF(C64="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F64" s="4" t="str">
-        <f>IF(B64=0,"未启用",IF(A64&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B64=0,"inactive",IF(A64&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -15902,19 +15894,19 @@
         <v>0</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D65" s="38">
         <f>IF(C65="window",0,IF(C65="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E65" s="4" t="str">
-        <f>IF(B65=0,"未启用",IF(C65="window","原始滑动窗口",IF(C65="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B65=0,"inactive",IF(C65="window","raw sliding window",IF(C65="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F65" s="4" t="str">
-        <f>IF(B65=0,"未启用",IF(A65&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B65=0,"inactive",IF(A65&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -15925,19 +15917,19 @@
         <v>0</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D66" s="38">
         <f>IF(C66="window",0,IF(C66="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E66" s="4" t="str">
-        <f>IF(B66=0,"未启用",IF(C66="window","原始滑动窗口",IF(C66="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B66=0,"inactive",IF(C66="window","raw sliding window",IF(C66="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F66" s="4" t="str">
-        <f>IF(B66=0,"未启用",IF(A66&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B66=0,"inactive",IF(A66&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -15948,19 +15940,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D67" s="38">
         <f>IF(C67="window",0,IF(C67="short",ShortRatio,LongRatio))</f>
         <v>0</v>
       </c>
       <c r="E67" s="4" t="str">
-        <f>IF(B67=0,"未启用",IF(C67="window","原始滑动窗口",IF(C67="short","压缩 KV + Indexer Top-K","确定性压缩 KV")))</f>
-        <v>未启用</v>
+        <f>IF(B67=0,"inactive",IF(C67="window","raw sliding window",IF(C67="short","compressed KV + Indexer Top-K","deterministic compressed KV")))</f>
+        <v>inactive</v>
       </c>
       <c r="F67" s="4" t="str">
-        <f>IF(B67=0,"未启用",IF(A67&lt;HashLayers,"哈希","评分"))</f>
-        <v>未启用</v>
+        <f>IF(B67=0,"inactive",IF(A67&lt;HashLayers,"hash","score"))</f>
+        <v>inactive</v>
       </c>
     </row>
   </sheetData>
@@ -15988,47 +15980,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>524</v>
+        <v>293</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -16036,23 +16028,23 @@
         <v>59</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -16060,47 +16052,47 @@
         <v>344</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>540</v>
+        <v>261</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>538</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -763,7 +763,7 @@
     <t>在当前场景令牌数下，单个路由专家至少被激活一次的概率，用于估算路由专家参数读取量。</t>
   </si>
   <si>
-    <t>Inference calculation detail</t>
+    <t>推理计算明细</t>
   </si>
   <si>
     <t>Operator/item</t>
@@ -1213,7 +1213,7 @@
     <t>Score routing (FP32)</t>
   </si>
   <si>
-    <t>Parameters and cache: 8K Prefill parameters and capacity</t>
+    <t>参数与缓存：8K 预填充 参数与容量</t>
   </si>
   <si>
     <t>Parameter component</t>
@@ -1294,13 +1294,13 @@
     <t>模型尾部推理参数在每个 Rank 上复制。</t>
   </si>
   <si>
-    <t>Parameter count and capacity summary</t>
+    <t>参数量与参数容量汇总</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Current scenario KV cache and Compressor state (per Rank, replicated across TP)</t>
+    <t>当前场景 KV 缓存与 Compressor 状态（每 Rank，TP 间复制）</t>
   </si>
   <si>
     <t>Item</t>
@@ -1333,7 +1333,7 @@
     <t>按 MaxContext 为预填充阶段预分配。</t>
   </si>
   <si>
-    <t>Per-rank device resident capacity (default even sharding)</t>
+    <t>单 Rank 设备驻留容量（默认均匀分片）</t>
   </si>
   <si>
     <t>Configuration</t>
@@ -1378,7 +1378,7 @@
     <t>All 8 ranks identical</t>
   </si>
   <si>
-    <t>Parameters and cache: 1M-context Decode parameters and capacity</t>
+    <t>参数与缓存：1M 解码 参数与容量</t>
   </si>
   <si>
     <t>Decode effective main KV</t>
@@ -3210,14 +3210,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -3270,14 +3270,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -3330,14 +3330,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
       <xdr:row>101</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="551">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -709,7 +709,7 @@
     <t>8K Prefill - TP1 vs TP8 inference resources</t>
   </si>
   <si>
-    <t>容量为单 Rank 资源；分类容量是静态参数，整网容量另含 MaxContext 预分配 KV/State。可见通信列为原始集合通信数据量，HBM 读写量保留在隐藏审计列。</t>
+    <t>容量为单 Rank 资源；分类容量是静态参数，整网容量另含 MaxContext 预分配 KV/State。可见通信列为原始集合通信数据量，底层 HBM 访问量仅保留在隐藏审计列中用于推导目标带宽。</t>
   </si>
   <si>
     <t>Helper metric</t>
@@ -865,7 +865,7 @@
     <t>residual</t>
   </si>
   <si>
-    <t>HC state workspace；临时 workspace 不重复计入 HBM 和驻留容量。</t>
+    <t>HC state workspace；临时 workspace 不重复计入目标 HBM 带宽推导和驻留容量。</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1039,7 +1039,7 @@
     <t>Router score projection</t>
   </si>
   <si>
-    <t>BF16 gate + FP32 bias + INT32 hash table</t>
+    <t>BF16 gate + FP32 bias + INT32 Token-ID lookup table</t>
   </si>
   <si>
     <t>BF16 hidden; FP32 scores; INT32 indices</t>
@@ -1105,7 +1105,7 @@
     <t>HC state workspace</t>
   </si>
   <si>
-    <t>临时 BF16 residual/HC state 不重复计入 HBM 流量；驻留容量口径在场景汇总中单独说明。</t>
+    <t>临时 BF16 residual/HC state 不重复计入目标 HBM 带宽推导；驻留容量口径在场景汇总中单独说明。</t>
   </si>
   <si>
     <t>Tail</t>
@@ -1300,16 +1300,16 @@
     <t>Router scores/routing weights</t>
   </si>
   <si>
-    <t>FP32 bias; INT32 hash table</t>
-  </si>
-  <si>
-    <t>sqrt(softplus) 评分、Top-K 和归一化在 FP32 中完成。</t>
+    <t>FP32 bias; INT32 Token-ID lookup table</t>
+  </si>
+  <si>
+    <t>sqrt(softplus) 评分、Top-K 和归一化在 FP32 中完成；前 3 层使用 Token-ID 查表路由。</t>
   </si>
   <si>
     <t>Layers 0-2</t>
   </si>
   <si>
-    <t>Hash routing table</t>
+    <t>Token-ID routing table</t>
   </si>
   <si>
     <t>INT32</t>
@@ -1387,7 +1387,7 @@
     <t>Window</t>
   </si>
   <si>
-    <t>Hash routing (INT32)</t>
+    <t>Token-ID lookup routing (INT32)</t>
   </si>
   <si>
     <t>FP8 E4M3; wo_a BF16</t>
@@ -1411,7 +1411,7 @@
     <t>TP1 / TP8 Inference Resource Comparison Charts</t>
   </si>
   <si>
-    <t>计算量、HBM、参数、缓存与驻留容量集中在一张资源表；隐藏列保留公式原值和图表缩放源。</t>
+    <t>计算量、目标 HBM 带宽、参数、缓存、驻留容量与集合通信量集中在一张资源表；隐藏列保留底层访问公式和图表缩放源。</t>
   </si>
   <si>
     <t>Resource</t>
@@ -1444,31 +1444,16 @@
     <t>总推理 FLOPs</t>
   </si>
   <si>
-    <t>注意力 HBM 流量</t>
-  </si>
-  <si>
-    <t>本地逻辑 HBM 读写量，不含缓存复用和算子融合。</t>
-  </si>
-  <si>
-    <t>混合专家 HBM 流量</t>
-  </si>
-  <si>
-    <t>其他 HBM 流量</t>
-  </si>
-  <si>
-    <t>总 HBM 流量</t>
-  </si>
-  <si>
-    <t>Attention required HBM bandwidth</t>
+    <t>注意力所需 HBM 带宽</t>
   </si>
   <si>
     <t>按参数页中的目标时延换算；不是实测带宽。</t>
   </si>
   <si>
-    <t>MoE required HBM bandwidth</t>
-  </si>
-  <si>
-    <t>Other required HBM bandwidth</t>
+    <t>混合专家所需 HBM 带宽</t>
+  </si>
+  <si>
+    <t>其他所需 HBM 带宽</t>
   </si>
   <si>
     <t>Compute required at target latency</t>
@@ -1489,46 +1474,46 @@
     <t>未考虑通信与计算重叠、拓扑和协议效率。</t>
   </si>
   <si>
-    <t>Attention logical parameter count</t>
+    <t>注意力逻辑参数量</t>
   </si>
   <si>
     <t>注意力投影、Compressor、Indexer。</t>
   </si>
   <si>
-    <t>MoE logical parameter count</t>
+    <t>混合专家逻辑参数量</t>
   </si>
   <si>
     <t>路由/共享专家与 Router。</t>
   </si>
   <si>
-    <t>Other logical parameter count</t>
+    <t>其他逻辑参数量</t>
   </si>
   <si>
     <t>Embedding、LM Head、HC 与 Norm。</t>
   </si>
   <si>
-    <t>Total logical parameter count</t>
+    <t>总逻辑参数量</t>
   </si>
   <si>
     <t>不包含 MTP。</t>
   </si>
   <si>
-    <t>Attention parameter capacity</t>
+    <t>注意力参数容量</t>
   </si>
   <si>
     <t>按推理 dtype 与量化 Scale 计算。</t>
   </si>
   <si>
-    <t>MoE parameter capacity</t>
+    <t>混合专家参数容量</t>
   </si>
   <si>
     <t>路由专家 FP4、共享专家 FP8、Router 复制。</t>
   </si>
   <si>
-    <t>Other parameter capacity</t>
-  </si>
-  <si>
-    <t>Total parameter capacity</t>
+    <t>其他参数容量</t>
+  </si>
+  <si>
+    <t>总参数容量</t>
   </si>
   <si>
     <t>每 Rank 静态参数驻留。</t>
@@ -1615,9 +1600,6 @@
     <t>单次推理调用的单 Rank 计算量。</t>
   </si>
   <si>
-    <t>本地逻辑 HBM 读写量，不含缓存复用。</t>
-  </si>
-  <si>
     <t>按参数页中的目标时延换算。</t>
   </si>
   <si>
@@ -1711,13 +1693,13 @@
     <t>每个解码令牌在解码上下文长度下建模；ratio-4 主注意力取 Top-K，但 Indexer 需要扫描全部已完成压缩项。</t>
   </si>
   <si>
-    <t>每个令牌执行 Top-K 路由专家和共享专家。HBM 参数读取按专家至少被命中一次的概率估计。</t>
-  </si>
-  <si>
-    <t>HBM traffic</t>
-  </si>
-  <si>
-    <t>统计本地逻辑参数、激活和 KV 的读取与写入；不模拟 L2 命中、算子融合、分块、Allocator 或厂商 Kernel 内部复用。</t>
+    <t>每个令牌执行 Top-K 路由专家和共享专家；专家命中概率用于估算逻辑访问需求。</t>
+  </si>
+  <si>
+    <t>Required HBM bandwidth</t>
+  </si>
+  <si>
+    <t>仅按目标时延推导所需 HBM 带宽，不把本地逻辑读写量作为独立可见统计；不模拟 L2 命中、算子融合、分块、Allocator 或厂商 Kernel 内部复用。</t>
   </si>
   <si>
     <t>Memory</t>
@@ -1729,13 +1711,13 @@
     <t>Scenario tables</t>
   </si>
   <si>
-    <t>Prefill_8K 和 Decode_1M 各含两张表：整网资源汇总与典型层/模块明细；两张表共享 TP1/TP8 的容量、算力、集合通信数据量、参数类型和激活类型列；HBM 读写量保留在隐藏审计列。</t>
+    <t>Prefill_8K 和 Decode_1M 各含两张表：整网资源汇总与典型层/模块明细；两张表共享 TP1/TP8 的容量、算力、集合通信数据量、参数类型和激活类型列；底层 HBM 访问量仅保留在隐藏审计列中用于推导目标带宽。</t>
   </si>
   <si>
     <t>Resource categories</t>
   </si>
   <si>
-    <t>汇总分类为 Attention、MoE、Embedding、LM Head、Norm、HC、residual；residual 是 BF16/HC state 工作区，不重复计入驻留容量或 HBM 流量。</t>
+    <t>汇总分类为 Attention、MoE、Embedding、LM Head、Norm、HC、residual；residual 是 BF16/HC state 工作区，不重复计入驻留容量或目标 HBM 带宽推导。</t>
   </si>
   <si>
     <t>有效容量表示已填充项；预分配容量使用 MaxContext。当前实现的 KV 和 Compressor 状态在每个 TP Rank 上完整复制。</t>
@@ -2005,7 +1987,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$36:$S$39</c:f>
+              <c:f>Comparison!$S$32:$S$35</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2025,7 +2007,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$36:$T$39</c:f>
+              <c:f>Comparison!$T$32:$T$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2147,7 +2129,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$43:$S$45</c:f>
+              <c:f>Comparison!$S$39:$S$41</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2164,7 +2146,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$43:$T$45</c:f>
+              <c:f>Comparison!$T$39:$T$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2193,7 +2175,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$43:$S$45</c:f>
+              <c:f>Comparison!$S$39:$S$41</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2210,7 +2192,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$43:$U$45</c:f>
+              <c:f>Comparison!$U$39:$U$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2329,7 +2311,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$50:$S$52</c:f>
+              <c:f>Comparison!$S$46:$S$48</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2346,7 +2328,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$50:$T$52</c:f>
+              <c:f>Comparison!$T$46:$T$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2375,7 +2357,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$50:$S$52</c:f>
+              <c:f>Comparison!$S$46:$S$48</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2392,7 +2374,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$50:$U$52</c:f>
+              <c:f>Comparison!$U$46:$U$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2487,7 +2469,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Prefill HBM traffic per rank</a:t>
+              <a:t>Static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2511,7 +2493,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$57:$S$59</c:f>
+              <c:f>Comparison!$S$53:$S$55</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2528,18 +2510,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$57:$T$59</c:f>
+              <c:f>Comparison!$T$53:$T$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>358.0378144</c:v>
+                  <c:v>7.45138496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>191.988670976</c:v>
+                  <c:v>148.351461888</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>106.744396636</c:v>
+                  <c:v>3.314423644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2557,7 +2539,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$57:$S$59</c:f>
+              <c:f>Comparison!$S$53:$S$55</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2574,18 +2556,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$57:$U$59</c:f>
+              <c:f>Comparison!$U$53:$U$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>231.531806144</c:v>
+                  <c:v>2.23750496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32.915497472</c:v>
+                  <c:v>19.57794048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104.890576444</c:v>
+                  <c:v>0.534376892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2669,7 +2651,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Decode HBM traffic per rank</a:t>
+              <a:t>TP1 vs TP8: inference resident capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2693,35 +2675,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$64:$S$66</c:f>
+              <c:f>Comparison!$S$60:$S$61</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Attention</c:v>
+                  <c:v>Prefill</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>MoE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Other</c:v>
+                  <c:v>Decode</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$64:$T$66</c:f>
+              <c:f>Comparison!$T$60:$T$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10.492228352</c:v>
+                  <c:v>166.349315548</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.627033672</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.268650332</c:v>
+                  <c:v>166.349315548</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2739,35 +2715,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$64:$S$66</c:f>
+              <c:f>Comparison!$S$60:$S$61</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Attention</c:v>
+                  <c:v>Prefill</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>MoE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Other</c:v>
+                  <c:v>Decode</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$64:$U$66</c:f>
+              <c:f>Comparison!$U$60:$U$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>4.035232528</c:v>
+                  <c:v>29.581867388</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.605205576</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.41483014</c:v>
+                  <c:v>29.581867388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2835,371 +2805,19 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="10"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Static parameter capacity per rank</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>TP1 GB</c:v>
-          </c:tx>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-            <c:showVal val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Comparison!$S$71:$S$73</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Attention</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>MoE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Other</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$T$71:$T$73</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>7.45138496</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>148.351461888</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.314423644</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>TP8 GB</c:v>
-          </c:tx>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-            <c:showVal val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Comparison!$S$71:$S$73</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Attention</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>MoE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Other</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$U$71:$U$73</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2.23750496</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.57794048</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.534376892</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="30"/>
-        <c:axId val="50060001"/>
-        <c:axId val="50060002"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="50060001"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="b"/>
-        <c:tickLblPos val="low"/>
-        <c:crossAx val="50060002"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="50060002"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>GB</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-        </c:title>
-        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50060001"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout/>
-    </c:legend>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="10"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>TP1 vs TP8: inference resident capacity per rank</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>TP1 GB</c:v>
-          </c:tx>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-            <c:showVal val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Comparison!$S$78:$S$79</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Prefill</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Decode</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$T$78:$T$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>166.349315548</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>166.349315548</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>TP8 GB</c:v>
-          </c:tx>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-            <c:showVal val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Comparison!$S$78:$S$79</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Prefill</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Decode</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$U$78:$U$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>29.581867388</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>29.581867388</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="30"/>
-        <c:axId val="50070001"/>
-        <c:axId val="50070002"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="50070001"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="b"/>
-        <c:tickLblPos val="low"/>
-        <c:crossAx val="50070002"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="50070002"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>GB</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-        </c:title>
-        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="50070001"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout/>
-    </c:legend>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3223,13 +2841,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3253,13 +2871,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3283,13 +2901,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3313,13 +2931,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3334,66 +2952,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3515,8 +3073,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Comparison_Resource_Overview" displayName="Comparison_Resource_Overview" ref="A4:F32" totalsRowShown="0">
-  <autoFilter ref="A4:F32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Comparison_Resource_Overview" displayName="Comparison_Resource_Overview" ref="A4:F28" totalsRowShown="0">
+  <autoFilter ref="A4:F28"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Resource"/>
     <tableColumn id="2" name="Prefill TP1"/>
@@ -11848,7 +11406,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U79"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -12053,39 +11611,39 @@
         <v>448</v>
       </c>
       <c r="B9" s="33" t="str">
-        <f>TEXT(IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,IF(ABS(G9)&gt;=1E3,G9/1E3,G9)))),"#,##0.000")&amp;IF((IF(ABS(G9)&gt;=1E12,"TB",IF(ABS(G9)&gt;=1E9,"GB",IF(ABS(G9)&gt;=1E6,"MB",IF(ABS(G9)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G9)&gt;=1E12,"TB",IF(ABS(G9)&gt;=1E9,"GB",IF(ABS(G9)&gt;=1E6,"MB",IF(ABS(G9)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>358.038 GB</v>
+        <f>TEXT(G9,"#,##0.000")&amp;" GB/s"</f>
+        <v>358.038 GB/s</v>
       </c>
       <c r="C9" s="33" t="str">
-        <f>TEXT(IF(ABS(H9)&gt;=1E12,H9/1E12,IF(ABS(H9)&gt;=1E9,H9/1E9,IF(ABS(H9)&gt;=1E6,H9/1E6,IF(ABS(H9)&gt;=1E3,H9/1E3,H9)))),"#,##0.000")&amp;IF((IF(ABS(H9)&gt;=1E12,"TB",IF(ABS(H9)&gt;=1E9,"GB",IF(ABS(H9)&gt;=1E6,"MB",IF(ABS(H9)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H9)&gt;=1E12,"TB",IF(ABS(H9)&gt;=1E9,"GB",IF(ABS(H9)&gt;=1E6,"MB",IF(ABS(H9)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>231.532 GB</v>
+        <f>TEXT(H9,"#,##0.000")&amp;" GB/s"</f>
+        <v>231.532 GB/s</v>
       </c>
       <c r="D9" s="33" t="str">
-        <f>TEXT(IF(ABS(I9)&gt;=1E12,I9/1E12,IF(ABS(I9)&gt;=1E9,I9/1E9,IF(ABS(I9)&gt;=1E6,I9/1E6,IF(ABS(I9)&gt;=1E3,I9/1E3,I9)))),"#,##0.000")&amp;IF((IF(ABS(I9)&gt;=1E12,"TB",IF(ABS(I9)&gt;=1E9,"GB",IF(ABS(I9)&gt;=1E6,"MB",IF(ABS(I9)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I9)&gt;=1E12,"TB",IF(ABS(I9)&gt;=1E9,"GB",IF(ABS(I9)&gt;=1E6,"MB",IF(ABS(I9)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>10.492 GB</v>
+        <f>TEXT(I9,"#,##0.000")&amp;" GB/s"</f>
+        <v>1,049.223 GB/s</v>
       </c>
       <c r="E9" s="33" t="str">
-        <f>TEXT(IF(ABS(J9)&gt;=1E12,J9/1E12,IF(ABS(J9)&gt;=1E9,J9/1E9,IF(ABS(J9)&gt;=1E6,J9/1E6,IF(ABS(J9)&gt;=1E3,J9/1E3,J9)))),"#,##0.000")&amp;IF((IF(ABS(J9)&gt;=1E12,"TB",IF(ABS(J9)&gt;=1E9,"GB",IF(ABS(J9)&gt;=1E6,"MB",IF(ABS(J9)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J9)&gt;=1E12,"TB",IF(ABS(J9)&gt;=1E9,"GB",IF(ABS(J9)&gt;=1E6,"MB",IF(ABS(J9)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>4.035 GB</v>
+        <f>TEXT(J9,"#,##0.000")&amp;" GB/s"</f>
+        <v>403.523 GB/s</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>449</v>
       </c>
       <c r="G9" s="32">
-        <f>'Prefill_8K'!$AG$14</f>
-        <v>358037814400.0</v>
+        <f>'Prefill_8K'!$AG$14/(PrefillTargetMs/1000)/1E9</f>
+        <v>358.0378144</v>
       </c>
       <c r="H9" s="32">
-        <f>'Prefill_8K'!$AJ$14</f>
-        <v>231531806144.0</v>
+        <f>'Prefill_8K'!$AJ$14/(PrefillTargetMs/1000)/1E9</f>
+        <v>231.531806144</v>
       </c>
       <c r="I9" s="32">
-        <f>'Decode_1M'!$AG$14</f>
-        <v>10492228352.0</v>
+        <f>'Decode_1M'!$AG$14/(DecodeTargetMs/1000)/1E9</f>
+        <v>1049.2228352</v>
       </c>
       <c r="J9" s="32">
-        <f>'Decode_1M'!$AJ$14</f>
-        <v>4035232528.0</v>
+        <f>'Decode_1M'!$AJ$14/(DecodeTargetMs/1000)/1E9</f>
+        <v>403.5232528</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -12093,39 +11651,39 @@
         <v>450</v>
       </c>
       <c r="B10" s="33" t="str">
-        <f>TEXT(IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10)))),"#,##0.000")&amp;IF((IF(ABS(G10)&gt;=1E12,"TB",IF(ABS(G10)&gt;=1E9,"GB",IF(ABS(G10)&gt;=1E6,"MB",IF(ABS(G10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G10)&gt;=1E12,"TB",IF(ABS(G10)&gt;=1E9,"GB",IF(ABS(G10)&gt;=1E6,"MB",IF(ABS(G10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>191.989 GB</v>
+        <f>TEXT(G10,"#,##0.000")&amp;" GB/s"</f>
+        <v>191.989 GB/s</v>
       </c>
       <c r="C10" s="33" t="str">
-        <f>TEXT(IF(ABS(H10)&gt;=1E12,H10/1E12,IF(ABS(H10)&gt;=1E9,H10/1E9,IF(ABS(H10)&gt;=1E6,H10/1E6,IF(ABS(H10)&gt;=1E3,H10/1E3,H10)))),"#,##0.000")&amp;IF((IF(ABS(H10)&gt;=1E12,"TB",IF(ABS(H10)&gt;=1E9,"GB",IF(ABS(H10)&gt;=1E6,"MB",IF(ABS(H10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H10)&gt;=1E12,"TB",IF(ABS(H10)&gt;=1E9,"GB",IF(ABS(H10)&gt;=1E6,"MB",IF(ABS(H10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>32.915 GB</v>
+        <f>TEXT(H10,"#,##0.000")&amp;" GB/s"</f>
+        <v>32.915 GB/s</v>
       </c>
       <c r="D10" s="33" t="str">
-        <f>TEXT(IF(ABS(I10)&gt;=1E12,I10/1E12,IF(ABS(I10)&gt;=1E9,I10/1E9,IF(ABS(I10)&gt;=1E6,I10/1E6,IF(ABS(I10)&gt;=1E3,I10/1E3,I10)))),"#,##0.000")&amp;IF((IF(ABS(I10)&gt;=1E12,"TB",IF(ABS(I10)&gt;=1E9,"GB",IF(ABS(I10)&gt;=1E6,"MB",IF(ABS(I10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I10)&gt;=1E12,"TB",IF(ABS(I10)&gt;=1E9,"GB",IF(ABS(I10)&gt;=1E6,"MB",IF(ABS(I10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>4.627 GB</v>
+        <f>TEXT(I10,"#,##0.000")&amp;" GB/s"</f>
+        <v>462.703 GB/s</v>
       </c>
       <c r="E10" s="33" t="str">
-        <f>TEXT(IF(ABS(J10)&gt;=1E12,J10/1E12,IF(ABS(J10)&gt;=1E9,J10/1E9,IF(ABS(J10)&gt;=1E6,J10/1E6,IF(ABS(J10)&gt;=1E3,J10/1E3,J10)))),"#,##0.000")&amp;IF((IF(ABS(J10)&gt;=1E12,"TB",IF(ABS(J10)&gt;=1E9,"GB",IF(ABS(J10)&gt;=1E6,"MB",IF(ABS(J10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J10)&gt;=1E12,"TB",IF(ABS(J10)&gt;=1E9,"GB",IF(ABS(J10)&gt;=1E6,"MB",IF(ABS(J10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.605 GB</v>
+        <f>TEXT(J10,"#,##0.000")&amp;" GB/s"</f>
+        <v>160.521 GB/s</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>449</v>
       </c>
       <c r="G10" s="32">
-        <f>'Prefill_8K'!$AG$15</f>
-        <v>191988670976.0</v>
+        <f>'Prefill_8K'!$AG$15/(PrefillTargetMs/1000)/1E9</f>
+        <v>191.988670976</v>
       </c>
       <c r="H10" s="32">
-        <f>'Prefill_8K'!$AJ$15</f>
-        <v>32915497472.0</v>
+        <f>'Prefill_8K'!$AJ$15/(PrefillTargetMs/1000)/1E9</f>
+        <v>32.915497472</v>
       </c>
       <c r="I10" s="32">
-        <f>'Decode_1M'!$AG$15</f>
-        <v>4627033672.0</v>
+        <f>'Decode_1M'!$AG$15/(DecodeTargetMs/1000)/1E9</f>
+        <v>462.7033672</v>
       </c>
       <c r="J10" s="32">
-        <f>'Decode_1M'!$AJ$15</f>
-        <v>1605205576.0</v>
+        <f>'Decode_1M'!$AJ$15/(DecodeTargetMs/1000)/1E9</f>
+        <v>160.5205576</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -12133,1209 +11691,949 @@
         <v>451</v>
       </c>
       <c r="B11" s="33" t="str">
-        <f>TEXT(IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11)))),"#,##0.000")&amp;IF((IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>106.744 GB</v>
+        <f>TEXT(G11,"#,##0.000")&amp;" GB/s"</f>
+        <v>106.744 GB/s</v>
       </c>
       <c r="C11" s="33" t="str">
-        <f>TEXT(IF(ABS(H11)&gt;=1E12,H11/1E12,IF(ABS(H11)&gt;=1E9,H11/1E9,IF(ABS(H11)&gt;=1E6,H11/1E6,IF(ABS(H11)&gt;=1E3,H11/1E3,H11)))),"#,##0.000")&amp;IF((IF(ABS(H11)&gt;=1E12,"TB",IF(ABS(H11)&gt;=1E9,"GB",IF(ABS(H11)&gt;=1E6,"MB",IF(ABS(H11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H11)&gt;=1E12,"TB",IF(ABS(H11)&gt;=1E9,"GB",IF(ABS(H11)&gt;=1E6,"MB",IF(ABS(H11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>104.891 GB</v>
+        <f>TEXT(H11,"#,##0.000")&amp;" GB/s"</f>
+        <v>104.891 GB/s</v>
       </c>
       <c r="D11" s="33" t="str">
-        <f>TEXT(IF(ABS(I11)&gt;=1E12,I11/1E12,IF(ABS(I11)&gt;=1E9,I11/1E9,IF(ABS(I11)&gt;=1E6,I11/1E6,IF(ABS(I11)&gt;=1E3,I11/1E3,I11)))),"#,##0.000")&amp;IF((IF(ABS(I11)&gt;=1E12,"TB",IF(ABS(I11)&gt;=1E9,"GB",IF(ABS(I11)&gt;=1E6,"MB",IF(ABS(I11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I11)&gt;=1E12,"TB",IF(ABS(I11)&gt;=1E9,"GB",IF(ABS(I11)&gt;=1E6,"MB",IF(ABS(I11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.269 GB</v>
+        <f>TEXT(I11,"#,##0.000")&amp;" GB/s"</f>
+        <v>226.865 GB/s</v>
       </c>
       <c r="E11" s="33" t="str">
-        <f>TEXT(IF(ABS(J11)&gt;=1E12,J11/1E12,IF(ABS(J11)&gt;=1E9,J11/1E9,IF(ABS(J11)&gt;=1E6,J11/1E6,IF(ABS(J11)&gt;=1E3,J11/1E3,J11)))),"#,##0.000")&amp;IF((IF(ABS(J11)&gt;=1E12,"TB",IF(ABS(J11)&gt;=1E9,"GB",IF(ABS(J11)&gt;=1E6,"MB",IF(ABS(J11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J11)&gt;=1E12,"TB",IF(ABS(J11)&gt;=1E9,"GB",IF(ABS(J11)&gt;=1E6,"MB",IF(ABS(J11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>414.830 MB</v>
+        <f>TEXT(J11,"#,##0.000")&amp;" GB/s"</f>
+        <v>41.483 GB/s</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>449</v>
       </c>
       <c r="G11" s="32">
-        <f>'Prefill_8K'!$AQ$48</f>
-        <v>106744396636.0</v>
+        <f>'Prefill_8K'!$AQ$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>106.744396636</v>
       </c>
       <c r="H11" s="32">
-        <f>'Prefill_8K'!$AR$48</f>
-        <v>104890576444.0</v>
+        <f>'Prefill_8K'!$AR$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>104.890576444</v>
       </c>
       <c r="I11" s="32">
-        <f>'Decode_1M'!$AQ$48</f>
-        <v>2268650332.0</v>
+        <f>'Decode_1M'!$AQ$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>226.8650332</v>
       </c>
       <c r="J11" s="32">
-        <f>'Decode_1M'!$AR$48</f>
-        <v>414830140.0</v>
+        <f>'Decode_1M'!$AR$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>41.483014</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B12" s="31" t="str">
-        <f>TEXT(IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12)))),"#,##0.000")&amp;IF((IF(ABS(G12)&gt;=1E12,"TB",IF(ABS(G12)&gt;=1E9,"GB",IF(ABS(G12)&gt;=1E6,"MB",IF(ABS(G12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G12)&gt;=1E12,"TB",IF(ABS(G12)&gt;=1E9,"GB",IF(ABS(G12)&gt;=1E6,"MB",IF(ABS(G12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>656.771 GB</v>
-      </c>
-      <c r="C12" s="31" t="str">
-        <f>TEXT(IF(ABS(H12)&gt;=1E12,H12/1E12,IF(ABS(H12)&gt;=1E9,H12/1E9,IF(ABS(H12)&gt;=1E6,H12/1E6,IF(ABS(H12)&gt;=1E3,H12/1E3,H12)))),"#,##0.000")&amp;IF((IF(ABS(H12)&gt;=1E12,"TB",IF(ABS(H12)&gt;=1E9,"GB",IF(ABS(H12)&gt;=1E6,"MB",IF(ABS(H12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H12)&gt;=1E12,"TB",IF(ABS(H12)&gt;=1E9,"GB",IF(ABS(H12)&gt;=1E6,"MB",IF(ABS(H12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>369.338 GB</v>
-      </c>
-      <c r="D12" s="31" t="str">
-        <f>TEXT(IF(ABS(I12)&gt;=1E12,I12/1E12,IF(ABS(I12)&gt;=1E9,I12/1E9,IF(ABS(I12)&gt;=1E6,I12/1E6,IF(ABS(I12)&gt;=1E3,I12/1E3,I12)))),"#,##0.000")&amp;IF((IF(ABS(I12)&gt;=1E12,"TB",IF(ABS(I12)&gt;=1E9,"GB",IF(ABS(I12)&gt;=1E6,"MB",IF(ABS(I12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I12)&gt;=1E12,"TB",IF(ABS(I12)&gt;=1E9,"GB",IF(ABS(I12)&gt;=1E6,"MB",IF(ABS(I12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>17.388 GB</v>
-      </c>
-      <c r="E12" s="31" t="str">
-        <f>TEXT(IF(ABS(J12)&gt;=1E12,J12/1E12,IF(ABS(J12)&gt;=1E9,J12/1E9,IF(ABS(J12)&gt;=1E6,J12/1E6,IF(ABS(J12)&gt;=1E3,J12/1E3,J12)))),"#,##0.000")&amp;IF((IF(ABS(J12)&gt;=1E12,"TB",IF(ABS(J12)&gt;=1E9,"GB",IF(ABS(J12)&gt;=1E6,"MB",IF(ABS(J12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J12)&gt;=1E12,"TB",IF(ABS(J12)&gt;=1E9,"GB",IF(ABS(J12)&gt;=1E6,"MB",IF(ABS(J12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>6.055 GB</v>
+      <c r="B12" s="33" t="str">
+        <f>TEXT(G12,"#,##0.000")&amp;" TFLOP/s"</f>
+        <v>228.398 TFLOP/s</v>
+      </c>
+      <c r="C12" s="33" t="str">
+        <f>TEXT(H12,"#,##0.000")&amp;" TFLOP/s"</f>
+        <v>55.653 TFLOP/s</v>
+      </c>
+      <c r="D12" s="33" t="str">
+        <f>TEXT(I12,"#,##0.000")&amp;" TFLOP/s"</f>
+        <v>14.036 TFLOP/s</v>
+      </c>
+      <c r="E12" s="33" t="str">
+        <f>TEXT(J12,"#,##0.000")&amp;" TFLOP/s"</f>
+        <v>2.355 TFLOP/s</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G12" s="32">
-        <f>'Prefill_8K'!$AG$13</f>
-        <v>656770882012.0</v>
+        <f>'Prefill_8K'!$AF$13/(PrefillTargetMs/1000)/1E12</f>
+        <v>228.39768211456</v>
       </c>
       <c r="H12" s="32">
-        <f>'Prefill_8K'!$AJ$13</f>
-        <v>369337880060.0</v>
+        <f>'Prefill_8K'!$AI$13/(PrefillTargetMs/1000)/1E12</f>
+        <v>55.652568907776</v>
       </c>
       <c r="I12" s="32">
-        <f>'Decode_1M'!$AG$13</f>
-        <v>17387912356.0</v>
+        <f>'Decode_1M'!$AF$13/(DecodeTargetMs/1000)/1E12</f>
+        <v>14.035575211</v>
       </c>
       <c r="J12" s="32">
-        <f>'Decode_1M'!$AJ$13</f>
-        <v>6055268244.0</v>
+        <f>'Decode_1M'!$AI$13/(DecodeTargetMs/1000)/1E12</f>
+        <v>2.3549694126</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B13" s="33" t="str">
-        <f>TEXT(G13,"#,##0.000")&amp;" GB/s"</f>
-        <v>358.038 GB/s</v>
+        <f>TEXT(IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13)))),"#,##0.000")&amp;IF((IF(ABS(G13)&gt;=1E12,"TB",IF(ABS(G13)&gt;=1E9,"GB",IF(ABS(G13)&gt;=1E6,"MB",IF(ABS(G13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G13)&gt;=1E12,"TB",IF(ABS(G13)&gt;=1E9,"GB",IF(ABS(G13)&gt;=1E6,"MB",IF(ABS(G13)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>0.000 B</v>
       </c>
       <c r="C13" s="33" t="str">
-        <f>TEXT(H13,"#,##0.000")&amp;" GB/s"</f>
-        <v>231.532 GB/s</v>
+        <f>TEXT(IF(ABS(H13)&gt;=1E12,H13/1E12,IF(ABS(H13)&gt;=1E9,H13/1E9,IF(ABS(H13)&gt;=1E6,H13/1E6,IF(ABS(H13)&gt;=1E3,H13/1E3,H13)))),"#,##0.000")&amp;IF((IF(ABS(H13)&gt;=1E12,"TB",IF(ABS(H13)&gt;=1E9,"GB",IF(ABS(H13)&gt;=1E6,"MB",IF(ABS(H13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H13)&gt;=1E12,"TB",IF(ABS(H13)&gt;=1E9,"GB",IF(ABS(H13)&gt;=1E6,"MB",IF(ABS(H13)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>40.635 GB</v>
       </c>
       <c r="D13" s="33" t="str">
-        <f>TEXT(I13,"#,##0.000")&amp;" GB/s"</f>
-        <v>1,049.223 GB/s</v>
+        <f>TEXT(IF(ABS(I13)&gt;=1E12,I13/1E12,IF(ABS(I13)&gt;=1E9,I13/1E9,IF(ABS(I13)&gt;=1E6,I13/1E6,IF(ABS(I13)&gt;=1E3,I13/1E3,I13)))),"#,##0.000")&amp;IF((IF(ABS(I13)&gt;=1E12,"TB",IF(ABS(I13)&gt;=1E9,"GB",IF(ABS(I13)&gt;=1E6,"MB",IF(ABS(I13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I13)&gt;=1E12,"TB",IF(ABS(I13)&gt;=1E9,"GB",IF(ABS(I13)&gt;=1E6,"MB",IF(ABS(I13)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>0.000 B</v>
       </c>
       <c r="E13" s="33" t="str">
-        <f>TEXT(J13,"#,##0.000")&amp;" GB/s"</f>
-        <v>403.523 GB/s</v>
+        <f>TEXT(IF(ABS(J13)&gt;=1E12,J13/1E12,IF(ABS(J13)&gt;=1E9,J13/1E9,IF(ABS(J13)&gt;=1E6,J13/1E6,IF(ABS(J13)&gt;=1E3,J13/1E3,J13)))),"#,##0.000")&amp;IF((IF(ABS(J13)&gt;=1E12,"TB",IF(ABS(J13)&gt;=1E9,"GB",IF(ABS(J13)&gt;=1E6,"MB",IF(ABS(J13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J13)&gt;=1E12,"TB",IF(ABS(J13)&gt;=1E9,"GB",IF(ABS(J13)&gt;=1E6,"MB",IF(ABS(J13)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>5.865 MB</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G13" s="32">
-        <f>'Prefill_8K'!$AG$14/(PrefillTargetMs/1000)/1E9</f>
-        <v>358.0378144</v>
+        <f>'Prefill_8K'!$AS$48</f>
+        <v>0.0</v>
       </c>
       <c r="H13" s="32">
-        <f>'Prefill_8K'!$AJ$14/(PrefillTargetMs/1000)/1E9</f>
-        <v>231.531806144</v>
+        <f>'Prefill_8K'!$AT$48</f>
+        <v>40635322112.0</v>
       </c>
       <c r="I13" s="32">
-        <f>'Decode_1M'!$AG$14/(DecodeTargetMs/1000)/1E9</f>
-        <v>1049.2228352</v>
+        <f>'Decode_1M'!$AS$48</f>
+        <v>0.0</v>
       </c>
       <c r="J13" s="32">
-        <f>'Decode_1M'!$AJ$14/(DecodeTargetMs/1000)/1E9</f>
-        <v>403.5232528</v>
+        <f>'Decode_1M'!$AT$48</f>
+        <v>5865216.0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B14" s="33" t="str">
         <f>TEXT(G14,"#,##0.000")&amp;" GB/s"</f>
-        <v>191.989 GB/s</v>
+        <v>0.000 GB/s</v>
       </c>
       <c r="C14" s="33" t="str">
         <f>TEXT(H14,"#,##0.000")&amp;" GB/s"</f>
-        <v>32.915 GB/s</v>
+        <v>40.635 GB/s</v>
       </c>
       <c r="D14" s="33" t="str">
         <f>TEXT(I14,"#,##0.000")&amp;" GB/s"</f>
-        <v>462.703 GB/s</v>
+        <v>0.000 GB/s</v>
       </c>
       <c r="E14" s="33" t="str">
         <f>TEXT(J14,"#,##0.000")&amp;" GB/s"</f>
-        <v>160.521 GB/s</v>
+        <v>0.587 GB/s</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G14" s="32">
-        <f>'Prefill_8K'!$AG$15/(PrefillTargetMs/1000)/1E9</f>
-        <v>191.988670976</v>
+        <f>'Prefill_8K'!$AS$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>0.0</v>
       </c>
       <c r="H14" s="32">
-        <f>'Prefill_8K'!$AJ$15/(PrefillTargetMs/1000)/1E9</f>
-        <v>32.915497472</v>
+        <f>'Prefill_8K'!$AT$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>40.635322112</v>
       </c>
       <c r="I14" s="32">
-        <f>'Decode_1M'!$AG$15/(DecodeTargetMs/1000)/1E9</f>
-        <v>462.7033672</v>
+        <f>'Decode_1M'!$AS$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.0</v>
       </c>
       <c r="J14" s="32">
-        <f>'Decode_1M'!$AJ$15/(DecodeTargetMs/1000)/1E9</f>
-        <v>160.5205576</v>
+        <f>'Decode_1M'!$AT$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.5865216</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B15" s="33" t="str">
-        <f>TEXT(G15,"#,##0.000")&amp;" GB/s"</f>
-        <v>106.744 GB/s</v>
+        <f>TEXT(IF(ABS(G15)&gt;=1E12,G15/1E12,IF(ABS(G15)&gt;=1E9,G15/1E9,IF(ABS(G15)&gt;=1E6,G15/1E6,IF(ABS(G15)&gt;=1E3,G15/1E3,G15)))),"#,##0.000")&amp;IF((IF(ABS(G15)&gt;=1E12,"T",IF(ABS(G15)&gt;=1E9,"G",IF(ABS(G15)&gt;=1E6,"M",IF(ABS(G15)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G15)&gt;=1E12,"T",IF(ABS(G15)&gt;=1E9,"G",IF(ABS(G15)&gt;=1E6,"M",IF(ABS(G15)&gt;=1E3,"K",""))))))</f>
+        <v>5.086 G</v>
       </c>
       <c r="C15" s="33" t="str">
-        <f>TEXT(H15,"#,##0.000")&amp;" GB/s"</f>
-        <v>104.891 GB/s</v>
+        <f>TEXT(IF(ABS(H15)&gt;=1E12,H15/1E12,IF(ABS(H15)&gt;=1E9,H15/1E9,IF(ABS(H15)&gt;=1E6,H15/1E6,IF(ABS(H15)&gt;=1E3,H15/1E3,H15)))),"#,##0.000")&amp;IF((IF(ABS(H15)&gt;=1E12,"T",IF(ABS(H15)&gt;=1E9,"G",IF(ABS(H15)&gt;=1E6,"M",IF(ABS(H15)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H15)&gt;=1E12,"T",IF(ABS(H15)&gt;=1E9,"G",IF(ABS(H15)&gt;=1E6,"M",IF(ABS(H15)&gt;=1E3,"K",""))))))</f>
+        <v>1.140 G</v>
       </c>
       <c r="D15" s="33" t="str">
-        <f>TEXT(I15,"#,##0.000")&amp;" GB/s"</f>
-        <v>226.865 GB/s</v>
+        <f>TEXT(IF(ABS(I15)&gt;=1E12,I15/1E12,IF(ABS(I15)&gt;=1E9,I15/1E9,IF(ABS(I15)&gt;=1E6,I15/1E6,IF(ABS(I15)&gt;=1E3,I15/1E3,I15)))),"#,##0.000")&amp;IF((IF(ABS(I15)&gt;=1E12,"T",IF(ABS(I15)&gt;=1E9,"G",IF(ABS(I15)&gt;=1E6,"M",IF(ABS(I15)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I15)&gt;=1E12,"T",IF(ABS(I15)&gt;=1E9,"G",IF(ABS(I15)&gt;=1E6,"M",IF(ABS(I15)&gt;=1E3,"K",""))))))</f>
+        <v>5.086 G</v>
       </c>
       <c r="E15" s="33" t="str">
-        <f>TEXT(J15,"#,##0.000")&amp;" GB/s"</f>
-        <v>41.483 GB/s</v>
+        <f>TEXT(IF(ABS(J15)&gt;=1E12,J15/1E12,IF(ABS(J15)&gt;=1E9,J15/1E9,IF(ABS(J15)&gt;=1E6,J15/1E6,IF(ABS(J15)&gt;=1E3,J15/1E3,J15)))),"#,##0.000")&amp;IF((IF(ABS(J15)&gt;=1E12,"T",IF(ABS(J15)&gt;=1E9,"G",IF(ABS(J15)&gt;=1E6,"M",IF(ABS(J15)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J15)&gt;=1E12,"T",IF(ABS(J15)&gt;=1E9,"G",IF(ABS(J15)&gt;=1E6,"M",IF(ABS(J15)&gt;=1E3,"K",""))))))</f>
+        <v>1.140 G</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="G15" s="32">
-        <f>'Prefill_8K'!$AQ$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>106.744396636</v>
+        <f>'Prefill_8K'!$AY$49</f>
+        <v>5086249088.0</v>
       </c>
       <c r="H15" s="32">
-        <f>'Prefill_8K'!$AR$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>104.890576444</v>
+        <f>'Prefill_8K'!$AZ$49</f>
+        <v>1139835008.0</v>
       </c>
       <c r="I15" s="32">
-        <f>'Decode_1M'!$AQ$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>226.8650332</v>
+        <f>'Prefill_8K'!$AY$49</f>
+        <v>5086249088.0</v>
       </c>
       <c r="J15" s="32">
-        <f>'Decode_1M'!$AR$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>41.483014</v>
+        <f>'Prefill_8K'!$AZ$49</f>
+        <v>1139835008.0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B16" s="33" t="str">
-        <f>TEXT(G16,"#,##0.000")&amp;" TFLOP/s"</f>
-        <v>228.398 TFLOP/s</v>
+        <f>TEXT(IF(ABS(G16)&gt;=1E12,G16/1E12,IF(ABS(G16)&gt;=1E9,G16/1E9,IF(ABS(G16)&gt;=1E6,G16/1E6,IF(ABS(G16)&gt;=1E3,G16/1E3,G16)))),"#,##0.000")&amp;IF((IF(ABS(G16)&gt;=1E12,"T",IF(ABS(G16)&gt;=1E9,"G",IF(ABS(G16)&gt;=1E6,"M",IF(ABS(G16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G16)&gt;=1E12,"T",IF(ABS(G16)&gt;=1E9,"G",IF(ABS(G16)&gt;=1E6,"M",IF(ABS(G16)&gt;=1E3,"K",""))))))</f>
+        <v>278.155 G</v>
       </c>
       <c r="C16" s="33" t="str">
-        <f>TEXT(H16,"#,##0.000")&amp;" TFLOP/s"</f>
-        <v>55.653 TFLOP/s</v>
+        <f>TEXT(IF(ABS(H16)&gt;=1E12,H16/1E12,IF(ABS(H16)&gt;=1E9,H16/1E9,IF(ABS(H16)&gt;=1E6,H16/1E6,IF(ABS(H16)&gt;=1E3,H16/1E3,H16)))),"#,##0.000")&amp;IF((IF(ABS(H16)&gt;=1E12,"T",IF(ABS(H16)&gt;=1E9,"G",IF(ABS(H16)&gt;=1E6,"M",IF(ABS(H16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H16)&gt;=1E12,"T",IF(ABS(H16)&gt;=1E9,"G",IF(ABS(H16)&gt;=1E6,"M",IF(ABS(H16)&gt;=1E3,"K",""))))))</f>
+        <v>35.758 G</v>
       </c>
       <c r="D16" s="33" t="str">
-        <f>TEXT(I16,"#,##0.000")&amp;" TFLOP/s"</f>
-        <v>14.036 TFLOP/s</v>
+        <f>TEXT(IF(ABS(I16)&gt;=1E12,I16/1E12,IF(ABS(I16)&gt;=1E9,I16/1E9,IF(ABS(I16)&gt;=1E6,I16/1E6,IF(ABS(I16)&gt;=1E3,I16/1E3,I16)))),"#,##0.000")&amp;IF((IF(ABS(I16)&gt;=1E12,"T",IF(ABS(I16)&gt;=1E9,"G",IF(ABS(I16)&gt;=1E6,"M",IF(ABS(I16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I16)&gt;=1E12,"T",IF(ABS(I16)&gt;=1E9,"G",IF(ABS(I16)&gt;=1E6,"M",IF(ABS(I16)&gt;=1E3,"K",""))))))</f>
+        <v>278.155 G</v>
       </c>
       <c r="E16" s="33" t="str">
-        <f>TEXT(J16,"#,##0.000")&amp;" TFLOP/s"</f>
-        <v>2.355 TFLOP/s</v>
+        <f>TEXT(IF(ABS(J16)&gt;=1E12,J16/1E12,IF(ABS(J16)&gt;=1E9,J16/1E9,IF(ABS(J16)&gt;=1E6,J16/1E6,IF(ABS(J16)&gt;=1E3,J16/1E3,J16)))),"#,##0.000")&amp;IF((IF(ABS(J16)&gt;=1E12,"T",IF(ABS(J16)&gt;=1E9,"G",IF(ABS(J16)&gt;=1E6,"M",IF(ABS(J16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J16)&gt;=1E12,"T",IF(ABS(J16)&gt;=1E9,"G",IF(ABS(J16)&gt;=1E6,"M",IF(ABS(J16)&gt;=1E3,"K",""))))))</f>
+        <v>35.758 G</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G16" s="32">
-        <f>'Prefill_8K'!$AF$13/(PrefillTargetMs/1000)/1E12</f>
-        <v>228.39768211456</v>
-      </c>
-      <c r="H16" s="32">
-        <f>'Prefill_8K'!$AI$13/(PrefillTargetMs/1000)/1E12</f>
-        <v>55.652568907776</v>
-      </c>
-      <c r="I16" s="32">
-        <f>'Decode_1M'!$AF$13/(DecodeTargetMs/1000)/1E12</f>
-        <v>14.035575211</v>
-      </c>
-      <c r="J16" s="32">
-        <f>'Decode_1M'!$AI$13/(DecodeTargetMs/1000)/1E12</f>
-        <v>2.3549694126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="B17" s="33" t="str">
-        <f>TEXT(IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,IF(ABS(G17)&gt;=1E3,G17/1E3,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>0.000 B</v>
-      </c>
-      <c r="C17" s="33" t="str">
-        <f>TEXT(IF(ABS(H17)&gt;=1E12,H17/1E12,IF(ABS(H17)&gt;=1E9,H17/1E9,IF(ABS(H17)&gt;=1E6,H17/1E6,IF(ABS(H17)&gt;=1E3,H17/1E3,H17)))),"#,##0.000")&amp;IF((IF(ABS(H17)&gt;=1E12,"TB",IF(ABS(H17)&gt;=1E9,"GB",IF(ABS(H17)&gt;=1E6,"MB",IF(ABS(H17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H17)&gt;=1E12,"TB",IF(ABS(H17)&gt;=1E9,"GB",IF(ABS(H17)&gt;=1E6,"MB",IF(ABS(H17)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>40.635 GB</v>
-      </c>
-      <c r="D17" s="33" t="str">
-        <f>TEXT(IF(ABS(I17)&gt;=1E12,I17/1E12,IF(ABS(I17)&gt;=1E9,I17/1E9,IF(ABS(I17)&gt;=1E6,I17/1E6,IF(ABS(I17)&gt;=1E3,I17/1E3,I17)))),"#,##0.000")&amp;IF((IF(ABS(I17)&gt;=1E12,"TB",IF(ABS(I17)&gt;=1E9,"GB",IF(ABS(I17)&gt;=1E6,"MB",IF(ABS(I17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I17)&gt;=1E12,"TB",IF(ABS(I17)&gt;=1E9,"GB",IF(ABS(I17)&gt;=1E6,"MB",IF(ABS(I17)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>0.000 B</v>
-      </c>
-      <c r="E17" s="33" t="str">
-        <f>TEXT(IF(ABS(J17)&gt;=1E12,J17/1E12,IF(ABS(J17)&gt;=1E9,J17/1E9,IF(ABS(J17)&gt;=1E6,J17/1E6,IF(ABS(J17)&gt;=1E3,J17/1E3,J17)))),"#,##0.000")&amp;IF((IF(ABS(J17)&gt;=1E12,"TB",IF(ABS(J17)&gt;=1E9,"GB",IF(ABS(J17)&gt;=1E6,"MB",IF(ABS(J17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J17)&gt;=1E12,"TB",IF(ABS(J17)&gt;=1E9,"GB",IF(ABS(J17)&gt;=1E6,"MB",IF(ABS(J17)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.865 MB</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="G17" s="32">
-        <f>'Prefill_8K'!$AS$48</f>
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="32">
-        <f>'Prefill_8K'!$AT$48</f>
-        <v>40635322112.0</v>
-      </c>
-      <c r="I17" s="32">
-        <f>'Decode_1M'!$AS$48</f>
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="32">
-        <f>'Decode_1M'!$AT$48</f>
-        <v>5865216.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="B18" s="33" t="str">
-        <f>TEXT(G18,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.000 GB/s</v>
-      </c>
-      <c r="C18" s="33" t="str">
-        <f>TEXT(H18,"#,##0.000")&amp;" GB/s"</f>
-        <v>40.635 GB/s</v>
-      </c>
-      <c r="D18" s="33" t="str">
-        <f>TEXT(I18,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.000 GB/s</v>
-      </c>
-      <c r="E18" s="33" t="str">
-        <f>TEXT(J18,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.587 GB/s</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="G18" s="32">
-        <f>'Prefill_8K'!$AS$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="32">
-        <f>'Prefill_8K'!$AT$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>40.635322112</v>
-      </c>
-      <c r="I18" s="32">
-        <f>'Decode_1M'!$AS$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="32">
-        <f>'Decode_1M'!$AT$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.5865216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="B19" s="33" t="str">
-        <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K",""))))))</f>
-        <v>5.086 G</v>
-      </c>
-      <c r="C19" s="33" t="str">
-        <f>TEXT(IF(ABS(H19)&gt;=1E12,H19/1E12,IF(ABS(H19)&gt;=1E9,H19/1E9,IF(ABS(H19)&gt;=1E6,H19/1E6,IF(ABS(H19)&gt;=1E3,H19/1E3,H19)))),"#,##0.000")&amp;IF((IF(ABS(H19)&gt;=1E12,"T",IF(ABS(H19)&gt;=1E9,"G",IF(ABS(H19)&gt;=1E6,"M",IF(ABS(H19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H19)&gt;=1E12,"T",IF(ABS(H19)&gt;=1E9,"G",IF(ABS(H19)&gt;=1E6,"M",IF(ABS(H19)&gt;=1E3,"K",""))))))</f>
-        <v>1.140 G</v>
-      </c>
-      <c r="D19" s="33" t="str">
-        <f>TEXT(IF(ABS(I19)&gt;=1E12,I19/1E12,IF(ABS(I19)&gt;=1E9,I19/1E9,IF(ABS(I19)&gt;=1E6,I19/1E6,IF(ABS(I19)&gt;=1E3,I19/1E3,I19)))),"#,##0.000")&amp;IF((IF(ABS(I19)&gt;=1E12,"T",IF(ABS(I19)&gt;=1E9,"G",IF(ABS(I19)&gt;=1E6,"M",IF(ABS(I19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I19)&gt;=1E12,"T",IF(ABS(I19)&gt;=1E9,"G",IF(ABS(I19)&gt;=1E6,"M",IF(ABS(I19)&gt;=1E3,"K",""))))))</f>
-        <v>5.086 G</v>
-      </c>
-      <c r="E19" s="33" t="str">
-        <f>TEXT(IF(ABS(J19)&gt;=1E12,J19/1E12,IF(ABS(J19)&gt;=1E9,J19/1E9,IF(ABS(J19)&gt;=1E6,J19/1E6,IF(ABS(J19)&gt;=1E3,J19/1E3,J19)))),"#,##0.000")&amp;IF((IF(ABS(J19)&gt;=1E12,"T",IF(ABS(J19)&gt;=1E9,"G",IF(ABS(J19)&gt;=1E6,"M",IF(ABS(J19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J19)&gt;=1E12,"T",IF(ABS(J19)&gt;=1E9,"G",IF(ABS(J19)&gt;=1E6,"M",IF(ABS(J19)&gt;=1E3,"K",""))))))</f>
-        <v>1.140 G</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="G19" s="32">
-        <f>'Prefill_8K'!$AY$49</f>
-        <v>5086249088.0</v>
-      </c>
-      <c r="H19" s="32">
-        <f>'Prefill_8K'!$AZ$49</f>
-        <v>1139835008.0</v>
-      </c>
-      <c r="I19" s="32">
-        <f>'Prefill_8K'!$AY$49</f>
-        <v>5086249088.0</v>
-      </c>
-      <c r="J19" s="32">
-        <f>'Prefill_8K'!$AZ$49</f>
-        <v>1139835008.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="B20" s="33" t="str">
-        <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K",""))))))</f>
-        <v>278.155 G</v>
-      </c>
-      <c r="C20" s="33" t="str">
-        <f>TEXT(IF(ABS(H20)&gt;=1E12,H20/1E12,IF(ABS(H20)&gt;=1E9,H20/1E9,IF(ABS(H20)&gt;=1E6,H20/1E6,IF(ABS(H20)&gt;=1E3,H20/1E3,H20)))),"#,##0.000")&amp;IF((IF(ABS(H20)&gt;=1E12,"T",IF(ABS(H20)&gt;=1E9,"G",IF(ABS(H20)&gt;=1E6,"M",IF(ABS(H20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H20)&gt;=1E12,"T",IF(ABS(H20)&gt;=1E9,"G",IF(ABS(H20)&gt;=1E6,"M",IF(ABS(H20)&gt;=1E3,"K",""))))))</f>
-        <v>35.758 G</v>
-      </c>
-      <c r="D20" s="33" t="str">
-        <f>TEXT(IF(ABS(I20)&gt;=1E12,I20/1E12,IF(ABS(I20)&gt;=1E9,I20/1E9,IF(ABS(I20)&gt;=1E6,I20/1E6,IF(ABS(I20)&gt;=1E3,I20/1E3,I20)))),"#,##0.000")&amp;IF((IF(ABS(I20)&gt;=1E12,"T",IF(ABS(I20)&gt;=1E9,"G",IF(ABS(I20)&gt;=1E6,"M",IF(ABS(I20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I20)&gt;=1E12,"T",IF(ABS(I20)&gt;=1E9,"G",IF(ABS(I20)&gt;=1E6,"M",IF(ABS(I20)&gt;=1E3,"K",""))))))</f>
-        <v>278.155 G</v>
-      </c>
-      <c r="E20" s="33" t="str">
-        <f>TEXT(IF(ABS(J20)&gt;=1E12,J20/1E12,IF(ABS(J20)&gt;=1E9,J20/1E9,IF(ABS(J20)&gt;=1E6,J20/1E6,IF(ABS(J20)&gt;=1E3,J20/1E3,J20)))),"#,##0.000")&amp;IF((IF(ABS(J20)&gt;=1E12,"T",IF(ABS(J20)&gt;=1E9,"G",IF(ABS(J20)&gt;=1E6,"M",IF(ABS(J20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J20)&gt;=1E12,"T",IF(ABS(J20)&gt;=1E9,"G",IF(ABS(J20)&gt;=1E6,"M",IF(ABS(J20)&gt;=1E3,"K",""))))))</f>
-        <v>35.758 G</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="G20" s="32">
         <f>'Prefill_8K'!$AY$50</f>
         <v>278154947072.0</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H16" s="32">
         <f>'Prefill_8K'!$AZ$50</f>
         <v>35757730304.0</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I16" s="32">
         <f>'Prefill_8K'!$AY$50</f>
         <v>278154947072.0</v>
       </c>
-      <c r="J20" s="32">
+      <c r="J16" s="32">
         <f>'Prefill_8K'!$AZ$50</f>
         <v>35757730304.0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="B21" s="33" t="str">
-        <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K",""))))))</f>
+    <row r="17" spans="1:20">
+      <c r="A17" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B17" s="33" t="str">
+        <f>TEXT(IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,IF(ABS(G17)&gt;=1E3,G17/1E3,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E12,"T",IF(ABS(G17)&gt;=1E9,"G",IF(ABS(G17)&gt;=1E6,"M",IF(ABS(G17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E12,"T",IF(ABS(G17)&gt;=1E9,"G",IF(ABS(G17)&gt;=1E6,"M",IF(ABS(G17)&gt;=1E3,"K",""))))))</f>
         <v>1.093 G</v>
       </c>
-      <c r="C21" s="33" t="str">
-        <f>TEXT(IF(ABS(H21)&gt;=1E12,H21/1E12,IF(ABS(H21)&gt;=1E9,H21/1E9,IF(ABS(H21)&gt;=1E6,H21/1E6,IF(ABS(H21)&gt;=1E3,H21/1E3,H21)))),"#,##0.000")&amp;IF((IF(ABS(H21)&gt;=1E12,"T",IF(ABS(H21)&gt;=1E9,"G",IF(ABS(H21)&gt;=1E6,"M",IF(ABS(H21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H21)&gt;=1E12,"T",IF(ABS(H21)&gt;=1E9,"G",IF(ABS(H21)&gt;=1E6,"M",IF(ABS(H21)&gt;=1E3,"K",""))))))</f>
+      <c r="C17" s="33" t="str">
+        <f>TEXT(IF(ABS(H17)&gt;=1E12,H17/1E12,IF(ABS(H17)&gt;=1E9,H17/1E9,IF(ABS(H17)&gt;=1E6,H17/1E6,IF(ABS(H17)&gt;=1E3,H17/1E3,H17)))),"#,##0.000")&amp;IF((IF(ABS(H17)&gt;=1E12,"T",IF(ABS(H17)&gt;=1E9,"G",IF(ABS(H17)&gt;=1E6,"M",IF(ABS(H17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H17)&gt;=1E12,"T",IF(ABS(H17)&gt;=1E9,"G",IF(ABS(H17)&gt;=1E6,"M",IF(ABS(H17)&gt;=1E3,"K",""))))))</f>
         <v>166.690 M</v>
       </c>
-      <c r="D21" s="33" t="str">
-        <f>TEXT(IF(ABS(I21)&gt;=1E12,I21/1E12,IF(ABS(I21)&gt;=1E9,I21/1E9,IF(ABS(I21)&gt;=1E6,I21/1E6,IF(ABS(I21)&gt;=1E3,I21/1E3,I21)))),"#,##0.000")&amp;IF((IF(ABS(I21)&gt;=1E12,"T",IF(ABS(I21)&gt;=1E9,"G",IF(ABS(I21)&gt;=1E6,"M",IF(ABS(I21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I21)&gt;=1E12,"T",IF(ABS(I21)&gt;=1E9,"G",IF(ABS(I21)&gt;=1E6,"M",IF(ABS(I21)&gt;=1E3,"K",""))))))</f>
+      <c r="D17" s="33" t="str">
+        <f>TEXT(IF(ABS(I17)&gt;=1E12,I17/1E12,IF(ABS(I17)&gt;=1E9,I17/1E9,IF(ABS(I17)&gt;=1E6,I17/1E6,IF(ABS(I17)&gt;=1E3,I17/1E3,I17)))),"#,##0.000")&amp;IF((IF(ABS(I17)&gt;=1E12,"T",IF(ABS(I17)&gt;=1E9,"G",IF(ABS(I17)&gt;=1E6,"M",IF(ABS(I17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I17)&gt;=1E12,"T",IF(ABS(I17)&gt;=1E9,"G",IF(ABS(I17)&gt;=1E6,"M",IF(ABS(I17)&gt;=1E3,"K",""))))))</f>
         <v>1.093 G</v>
       </c>
-      <c r="E21" s="33" t="str">
-        <f>TEXT(IF(ABS(J21)&gt;=1E12,J21/1E12,IF(ABS(J21)&gt;=1E9,J21/1E9,IF(ABS(J21)&gt;=1E6,J21/1E6,IF(ABS(J21)&gt;=1E3,J21/1E3,J21)))),"#,##0.000")&amp;IF((IF(ABS(J21)&gt;=1E12,"T",IF(ABS(J21)&gt;=1E9,"G",IF(ABS(J21)&gt;=1E6,"M",IF(ABS(J21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J21)&gt;=1E12,"T",IF(ABS(J21)&gt;=1E9,"G",IF(ABS(J21)&gt;=1E6,"M",IF(ABS(J21)&gt;=1E3,"K",""))))))</f>
+      <c r="E17" s="33" t="str">
+        <f>TEXT(IF(ABS(J17)&gt;=1E12,J17/1E12,IF(ABS(J17)&gt;=1E9,J17/1E9,IF(ABS(J17)&gt;=1E6,J17/1E6,IF(ABS(J17)&gt;=1E3,J17/1E3,J17)))),"#,##0.000")&amp;IF((IF(ABS(J17)&gt;=1E12,"T",IF(ABS(J17)&gt;=1E9,"G",IF(ABS(J17)&gt;=1E6,"M",IF(ABS(J17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J17)&gt;=1E12,"T",IF(ABS(J17)&gt;=1E9,"G",IF(ABS(J17)&gt;=1E6,"M",IF(ABS(J17)&gt;=1E3,"K",""))))))</f>
         <v>166.690 M</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="G21" s="32">
+      <c r="F17" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G17" s="32">
         <f>'Prefill_8K'!$AY$51</f>
         <v>1093371351.0</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H17" s="32">
         <f>'Prefill_8K'!$AZ$51</f>
         <v>166689903.0</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I17" s="32">
         <f>'Prefill_8K'!$AY$51</f>
         <v>1093371351.0</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J17" s="32">
         <f>'Prefill_8K'!$AZ$51</f>
         <v>166689903.0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="B22" s="31" t="str">
-        <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K",""))))))</f>
+    <row r="18" spans="1:20">
+      <c r="A18" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B18" s="31" t="str">
+        <f>TEXT(IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18)))),"#,##0.000")&amp;IF((IF(ABS(G18)&gt;=1E12,"T",IF(ABS(G18)&gt;=1E9,"G",IF(ABS(G18)&gt;=1E6,"M",IF(ABS(G18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G18)&gt;=1E12,"T",IF(ABS(G18)&gt;=1E9,"G",IF(ABS(G18)&gt;=1E6,"M",IF(ABS(G18)&gt;=1E3,"K",""))))))</f>
         <v>284.335 G</v>
       </c>
-      <c r="C22" s="31" t="str">
-        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"T",IF(ABS(H22)&gt;=1E9,"G",IF(ABS(H22)&gt;=1E6,"M",IF(ABS(H22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"T",IF(ABS(H22)&gt;=1E9,"G",IF(ABS(H22)&gt;=1E6,"M",IF(ABS(H22)&gt;=1E3,"K",""))))))</f>
+      <c r="C18" s="31" t="str">
+        <f>TEXT(IF(ABS(H18)&gt;=1E12,H18/1E12,IF(ABS(H18)&gt;=1E9,H18/1E9,IF(ABS(H18)&gt;=1E6,H18/1E6,IF(ABS(H18)&gt;=1E3,H18/1E3,H18)))),"#,##0.000")&amp;IF((IF(ABS(H18)&gt;=1E12,"T",IF(ABS(H18)&gt;=1E9,"G",IF(ABS(H18)&gt;=1E6,"M",IF(ABS(H18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H18)&gt;=1E12,"T",IF(ABS(H18)&gt;=1E9,"G",IF(ABS(H18)&gt;=1E6,"M",IF(ABS(H18)&gt;=1E3,"K",""))))))</f>
         <v>37.064 G</v>
       </c>
-      <c r="D22" s="31" t="str">
-        <f>TEXT(IF(ABS(I22)&gt;=1E12,I22/1E12,IF(ABS(I22)&gt;=1E9,I22/1E9,IF(ABS(I22)&gt;=1E6,I22/1E6,IF(ABS(I22)&gt;=1E3,I22/1E3,I22)))),"#,##0.000")&amp;IF((IF(ABS(I22)&gt;=1E12,"T",IF(ABS(I22)&gt;=1E9,"G",IF(ABS(I22)&gt;=1E6,"M",IF(ABS(I22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I22)&gt;=1E12,"T",IF(ABS(I22)&gt;=1E9,"G",IF(ABS(I22)&gt;=1E6,"M",IF(ABS(I22)&gt;=1E3,"K",""))))))</f>
+      <c r="D18" s="31" t="str">
+        <f>TEXT(IF(ABS(I18)&gt;=1E12,I18/1E12,IF(ABS(I18)&gt;=1E9,I18/1E9,IF(ABS(I18)&gt;=1E6,I18/1E6,IF(ABS(I18)&gt;=1E3,I18/1E3,I18)))),"#,##0.000")&amp;IF((IF(ABS(I18)&gt;=1E12,"T",IF(ABS(I18)&gt;=1E9,"G",IF(ABS(I18)&gt;=1E6,"M",IF(ABS(I18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(I18)&gt;=1E12,"T",IF(ABS(I18)&gt;=1E9,"G",IF(ABS(I18)&gt;=1E6,"M",IF(ABS(I18)&gt;=1E3,"K",""))))))</f>
         <v>284.335 G</v>
       </c>
-      <c r="E22" s="31" t="str">
-        <f>TEXT(IF(ABS(J22)&gt;=1E12,J22/1E12,IF(ABS(J22)&gt;=1E9,J22/1E9,IF(ABS(J22)&gt;=1E6,J22/1E6,IF(ABS(J22)&gt;=1E3,J22/1E3,J22)))),"#,##0.000")&amp;IF((IF(ABS(J22)&gt;=1E12,"T",IF(ABS(J22)&gt;=1E9,"G",IF(ABS(J22)&gt;=1E6,"M",IF(ABS(J22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J22)&gt;=1E12,"T",IF(ABS(J22)&gt;=1E9,"G",IF(ABS(J22)&gt;=1E6,"M",IF(ABS(J22)&gt;=1E3,"K",""))))))</f>
+      <c r="E18" s="31" t="str">
+        <f>TEXT(IF(ABS(J18)&gt;=1E12,J18/1E12,IF(ABS(J18)&gt;=1E9,J18/1E9,IF(ABS(J18)&gt;=1E6,J18/1E6,IF(ABS(J18)&gt;=1E3,J18/1E3,J18)))),"#,##0.000")&amp;IF((IF(ABS(J18)&gt;=1E12,"T",IF(ABS(J18)&gt;=1E9,"G",IF(ABS(J18)&gt;=1E6,"M",IF(ABS(J18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(J18)&gt;=1E12,"T",IF(ABS(J18)&gt;=1E9,"G",IF(ABS(J18)&gt;=1E6,"M",IF(ABS(J18)&gt;=1E3,"K",""))))))</f>
         <v>37.064 G</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="G22" s="32">
+      <c r="F18" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G18" s="32">
         <f>'Prefill_8K'!$AY$52</f>
         <v>284334567511.0</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H18" s="32">
         <f>'Prefill_8K'!$AZ$52</f>
         <v>37064255215.0</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I18" s="32">
         <f>'Prefill_8K'!$AY$52</f>
         <v>284334567511.0</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J18" s="32">
         <f>'Prefill_8K'!$AZ$52</f>
         <v>37064255215.0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="19" spans="1:20">
+      <c r="A19" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B19" s="33" t="str">
+        <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.451 GB</v>
+      </c>
+      <c r="C19" s="33" t="str">
+        <f>TEXT(IF(ABS(H19)&gt;=1E12,H19/1E12,IF(ABS(H19)&gt;=1E9,H19/1E9,IF(ABS(H19)&gt;=1E6,H19/1E6,IF(ABS(H19)&gt;=1E3,H19/1E3,H19)))),"#,##0.000")&amp;IF((IF(ABS(H19)&gt;=1E12,"TB",IF(ABS(H19)&gt;=1E9,"GB",IF(ABS(H19)&gt;=1E6,"MB",IF(ABS(H19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H19)&gt;=1E12,"TB",IF(ABS(H19)&gt;=1E9,"GB",IF(ABS(H19)&gt;=1E6,"MB",IF(ABS(H19)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>2.238 GB</v>
+      </c>
+      <c r="D19" s="33" t="str">
+        <f>TEXT(IF(ABS(I19)&gt;=1E12,I19/1E12,IF(ABS(I19)&gt;=1E9,I19/1E9,IF(ABS(I19)&gt;=1E6,I19/1E6,IF(ABS(I19)&gt;=1E3,I19/1E3,I19)))),"#,##0.000")&amp;IF((IF(ABS(I19)&gt;=1E12,"TB",IF(ABS(I19)&gt;=1E9,"GB",IF(ABS(I19)&gt;=1E6,"MB",IF(ABS(I19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I19)&gt;=1E12,"TB",IF(ABS(I19)&gt;=1E9,"GB",IF(ABS(I19)&gt;=1E6,"MB",IF(ABS(I19)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.451 GB</v>
+      </c>
+      <c r="E19" s="33" t="str">
+        <f>TEXT(IF(ABS(J19)&gt;=1E12,J19/1E12,IF(ABS(J19)&gt;=1E9,J19/1E9,IF(ABS(J19)&gt;=1E6,J19/1E6,IF(ABS(J19)&gt;=1E3,J19/1E3,J19)))),"#,##0.000")&amp;IF((IF(ABS(J19)&gt;=1E12,"TB",IF(ABS(J19)&gt;=1E9,"GB",IF(ABS(J19)&gt;=1E6,"MB",IF(ABS(J19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J19)&gt;=1E12,"TB",IF(ABS(J19)&gt;=1E9,"GB",IF(ABS(J19)&gt;=1E6,"MB",IF(ABS(J19)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>2.238 GB</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="G19" s="32">
+        <f>'Prefill_8K'!$BA$49</f>
+        <v>7451384960</v>
+      </c>
+      <c r="H19" s="32">
+        <f>'Prefill_8K'!$BB$49</f>
+        <v>2237504960</v>
+      </c>
+      <c r="I19" s="32">
+        <f>'Prefill_8K'!$BA$49</f>
+        <v>7451384960</v>
+      </c>
+      <c r="J19" s="32">
+        <f>'Prefill_8K'!$BB$49</f>
+        <v>2237504960</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B20" s="33" t="str">
+        <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>148.351 GB</v>
+      </c>
+      <c r="C20" s="33" t="str">
+        <f>TEXT(IF(ABS(H20)&gt;=1E12,H20/1E12,IF(ABS(H20)&gt;=1E9,H20/1E9,IF(ABS(H20)&gt;=1E6,H20/1E6,IF(ABS(H20)&gt;=1E3,H20/1E3,H20)))),"#,##0.000")&amp;IF((IF(ABS(H20)&gt;=1E12,"TB",IF(ABS(H20)&gt;=1E9,"GB",IF(ABS(H20)&gt;=1E6,"MB",IF(ABS(H20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H20)&gt;=1E12,"TB",IF(ABS(H20)&gt;=1E9,"GB",IF(ABS(H20)&gt;=1E6,"MB",IF(ABS(H20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>19.578 GB</v>
+      </c>
+      <c r="D20" s="33" t="str">
+        <f>TEXT(IF(ABS(I20)&gt;=1E12,I20/1E12,IF(ABS(I20)&gt;=1E9,I20/1E9,IF(ABS(I20)&gt;=1E6,I20/1E6,IF(ABS(I20)&gt;=1E3,I20/1E3,I20)))),"#,##0.000")&amp;IF((IF(ABS(I20)&gt;=1E12,"TB",IF(ABS(I20)&gt;=1E9,"GB",IF(ABS(I20)&gt;=1E6,"MB",IF(ABS(I20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I20)&gt;=1E12,"TB",IF(ABS(I20)&gt;=1E9,"GB",IF(ABS(I20)&gt;=1E6,"MB",IF(ABS(I20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>148.351 GB</v>
+      </c>
+      <c r="E20" s="33" t="str">
+        <f>TEXT(IF(ABS(J20)&gt;=1E12,J20/1E12,IF(ABS(J20)&gt;=1E9,J20/1E9,IF(ABS(J20)&gt;=1E6,J20/1E6,IF(ABS(J20)&gt;=1E3,J20/1E3,J20)))),"#,##0.000")&amp;IF((IF(ABS(J20)&gt;=1E12,"TB",IF(ABS(J20)&gt;=1E9,"GB",IF(ABS(J20)&gt;=1E6,"MB",IF(ABS(J20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J20)&gt;=1E12,"TB",IF(ABS(J20)&gt;=1E9,"GB",IF(ABS(J20)&gt;=1E6,"MB",IF(ABS(J20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>19.578 GB</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G20" s="32">
+        <f>'Prefill_8K'!$BA$50</f>
+        <v>148351461888.0</v>
+      </c>
+      <c r="H20" s="32">
+        <f>'Prefill_8K'!$BB$50</f>
+        <v>19577940480.0</v>
+      </c>
+      <c r="I20" s="32">
+        <f>'Prefill_8K'!$BA$50</f>
+        <v>148351461888.0</v>
+      </c>
+      <c r="J20" s="32">
+        <f>'Prefill_8K'!$BB$50</f>
+        <v>19577940480.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B21" s="33" t="str">
+        <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>3.314 GB</v>
+      </c>
+      <c r="C21" s="33" t="str">
+        <f>TEXT(IF(ABS(H21)&gt;=1E12,H21/1E12,IF(ABS(H21)&gt;=1E9,H21/1E9,IF(ABS(H21)&gt;=1E6,H21/1E6,IF(ABS(H21)&gt;=1E3,H21/1E3,H21)))),"#,##0.000")&amp;IF((IF(ABS(H21)&gt;=1E12,"TB",IF(ABS(H21)&gt;=1E9,"GB",IF(ABS(H21)&gt;=1E6,"MB",IF(ABS(H21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H21)&gt;=1E12,"TB",IF(ABS(H21)&gt;=1E9,"GB",IF(ABS(H21)&gt;=1E6,"MB",IF(ABS(H21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>534.377 MB</v>
+      </c>
+      <c r="D21" s="33" t="str">
+        <f>TEXT(IF(ABS(I21)&gt;=1E12,I21/1E12,IF(ABS(I21)&gt;=1E9,I21/1E9,IF(ABS(I21)&gt;=1E6,I21/1E6,IF(ABS(I21)&gt;=1E3,I21/1E3,I21)))),"#,##0.000")&amp;IF((IF(ABS(I21)&gt;=1E12,"TB",IF(ABS(I21)&gt;=1E9,"GB",IF(ABS(I21)&gt;=1E6,"MB",IF(ABS(I21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I21)&gt;=1E12,"TB",IF(ABS(I21)&gt;=1E9,"GB",IF(ABS(I21)&gt;=1E6,"MB",IF(ABS(I21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>3.314 GB</v>
+      </c>
+      <c r="E21" s="33" t="str">
+        <f>TEXT(IF(ABS(J21)&gt;=1E12,J21/1E12,IF(ABS(J21)&gt;=1E9,J21/1E9,IF(ABS(J21)&gt;=1E6,J21/1E6,IF(ABS(J21)&gt;=1E3,J21/1E3,J21)))),"#,##0.000")&amp;IF((IF(ABS(J21)&gt;=1E12,"TB",IF(ABS(J21)&gt;=1E9,"GB",IF(ABS(J21)&gt;=1E6,"MB",IF(ABS(J21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J21)&gt;=1E12,"TB",IF(ABS(J21)&gt;=1E9,"GB",IF(ABS(J21)&gt;=1E6,"MB",IF(ABS(J21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>534.377 MB</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G21" s="32">
+        <f>'Prefill_8K'!$BA$51</f>
+        <v>3314423644.0</v>
+      </c>
+      <c r="H21" s="32">
+        <f>'Prefill_8K'!$BB$51</f>
+        <v>534376892.0</v>
+      </c>
+      <c r="I21" s="32">
+        <f>'Prefill_8K'!$BA$51</f>
+        <v>3314423644.0</v>
+      </c>
+      <c r="J21" s="32">
+        <f>'Prefill_8K'!$BB$51</f>
+        <v>534376892.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="B22" s="31" t="str">
+        <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>159.117 GB</v>
+      </c>
+      <c r="C22" s="31" t="str">
+        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>22.350 GB</v>
+      </c>
+      <c r="D22" s="31" t="str">
+        <f>TEXT(IF(ABS(I22)&gt;=1E12,I22/1E12,IF(ABS(I22)&gt;=1E9,I22/1E9,IF(ABS(I22)&gt;=1E6,I22/1E6,IF(ABS(I22)&gt;=1E3,I22/1E3,I22)))),"#,##0.000")&amp;IF((IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>159.117 GB</v>
+      </c>
+      <c r="E22" s="31" t="str">
+        <f>TEXT(IF(ABS(J22)&gt;=1E12,J22/1E12,IF(ABS(J22)&gt;=1E9,J22/1E9,IF(ABS(J22)&gt;=1E6,J22/1E6,IF(ABS(J22)&gt;=1E3,J22/1E3,J22)))),"#,##0.000")&amp;IF((IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>22.350 GB</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="G22" s="32">
+        <f>'Prefill_8K'!$BA$52</f>
+        <v>159117270492.0</v>
+      </c>
+      <c r="H22" s="32">
+        <f>'Prefill_8K'!$BB$52</f>
+        <v>22349822332.0</v>
+      </c>
+      <c r="I22" s="32">
+        <f>'Prefill_8K'!$BA$52</f>
+        <v>159117270492.0</v>
+      </c>
+      <c r="J22" s="32">
+        <f>'Prefill_8K'!$BB$52</f>
+        <v>22349822332.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B23" s="33" t="str">
         <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.451 GB</v>
+        <v>50.987 MB</v>
       </c>
       <c r="C23" s="33" t="str">
         <f>TEXT(IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,IF(ABS(H23)&gt;=1E3,H23/1E3,H23)))),"#,##0.000")&amp;IF((IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.238 GB</v>
+        <v>50.987 MB</v>
       </c>
       <c r="D23" s="33" t="str">
         <f>TEXT(IF(ABS(I23)&gt;=1E12,I23/1E12,IF(ABS(I23)&gt;=1E9,I23/1E9,IF(ABS(I23)&gt;=1E6,I23/1E6,IF(ABS(I23)&gt;=1E3,I23/1E3,I23)))),"#,##0.000")&amp;IF((IF(ABS(I23)&gt;=1E12,"TB",IF(ABS(I23)&gt;=1E9,"GB",IF(ABS(I23)&gt;=1E6,"MB",IF(ABS(I23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I23)&gt;=1E12,"TB",IF(ABS(I23)&gt;=1E9,"GB",IF(ABS(I23)&gt;=1E6,"MB",IF(ABS(I23)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.451 GB</v>
+        <v>5.811 GB</v>
       </c>
       <c r="E23" s="33" t="str">
         <f>TEXT(IF(ABS(J23)&gt;=1E12,J23/1E12,IF(ABS(J23)&gt;=1E9,J23/1E9,IF(ABS(J23)&gt;=1E6,J23/1E6,IF(ABS(J23)&gt;=1E3,J23/1E3,J23)))),"#,##0.000")&amp;IF((IF(ABS(J23)&gt;=1E12,"TB",IF(ABS(J23)&gt;=1E9,"GB",IF(ABS(J23)&gt;=1E6,"MB",IF(ABS(J23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J23)&gt;=1E12,"TB",IF(ABS(J23)&gt;=1E9,"GB",IF(ABS(J23)&gt;=1E6,"MB",IF(ABS(J23)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.238 GB</v>
+        <v>5.811 GB</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G23" s="32">
-        <f>'Prefill_8K'!$BA$49</f>
-        <v>7451384960</v>
+        <f>'Prefill_8K'!$U$35</f>
+        <v>50987008</v>
       </c>
       <c r="H23" s="32">
-        <f>'Prefill_8K'!$BB$49</f>
-        <v>2237504960</v>
+        <f>'Prefill_8K'!$X$35</f>
+        <v>50987008</v>
       </c>
       <c r="I23" s="32">
-        <f>'Prefill_8K'!$BA$49</f>
-        <v>7451384960</v>
+        <f>'Decode_1M'!$U$35</f>
+        <v>5810552832</v>
       </c>
       <c r="J23" s="32">
-        <f>'Prefill_8K'!$BB$49</f>
-        <v>2237504960</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <f>'Decode_1M'!$X$35</f>
+        <v>5810552832</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B24" s="33" t="str">
         <f>TEXT(IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>148.351 GB</v>
+        <v>11.010 MB</v>
       </c>
       <c r="C24" s="33" t="str">
         <f>TEXT(IF(ABS(H24)&gt;=1E12,H24/1E12,IF(ABS(H24)&gt;=1E9,H24/1E9,IF(ABS(H24)&gt;=1E6,H24/1E6,IF(ABS(H24)&gt;=1E3,H24/1E3,H24)))),"#,##0.000")&amp;IF((IF(ABS(H24)&gt;=1E12,"TB",IF(ABS(H24)&gt;=1E9,"GB",IF(ABS(H24)&gt;=1E6,"MB",IF(ABS(H24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H24)&gt;=1E12,"TB",IF(ABS(H24)&gt;=1E9,"GB",IF(ABS(H24)&gt;=1E6,"MB",IF(ABS(H24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>19.578 GB</v>
+        <v>11.010 MB</v>
       </c>
       <c r="D24" s="33" t="str">
         <f>TEXT(IF(ABS(I24)&gt;=1E12,I24/1E12,IF(ABS(I24)&gt;=1E9,I24/1E9,IF(ABS(I24)&gt;=1E6,I24/1E6,IF(ABS(I24)&gt;=1E3,I24/1E3,I24)))),"#,##0.000")&amp;IF((IF(ABS(I24)&gt;=1E12,"TB",IF(ABS(I24)&gt;=1E9,"GB",IF(ABS(I24)&gt;=1E6,"MB",IF(ABS(I24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I24)&gt;=1E12,"TB",IF(ABS(I24)&gt;=1E9,"GB",IF(ABS(I24)&gt;=1E6,"MB",IF(ABS(I24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>148.351 GB</v>
+        <v>1.409 GB</v>
       </c>
       <c r="E24" s="33" t="str">
         <f>TEXT(IF(ABS(J24)&gt;=1E12,J24/1E12,IF(ABS(J24)&gt;=1E9,J24/1E9,IF(ABS(J24)&gt;=1E6,J24/1E6,IF(ABS(J24)&gt;=1E3,J24/1E3,J24)))),"#,##0.000")&amp;IF((IF(ABS(J24)&gt;=1E12,"TB",IF(ABS(J24)&gt;=1E9,"GB",IF(ABS(J24)&gt;=1E6,"MB",IF(ABS(J24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J24)&gt;=1E12,"TB",IF(ABS(J24)&gt;=1E9,"GB",IF(ABS(J24)&gt;=1E6,"MB",IF(ABS(J24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>19.578 GB</v>
+        <v>1.409 GB</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>474</v>
       </c>
       <c r="G24" s="32">
-        <f>'Prefill_8K'!$BA$50</f>
-        <v>148351461888.0</v>
+        <f>'Prefill_8K'!$U$36</f>
+        <v>11010048</v>
       </c>
       <c r="H24" s="32">
-        <f>'Prefill_8K'!$BB$50</f>
-        <v>19577940480.0</v>
+        <f>'Prefill_8K'!$X$36</f>
+        <v>11010048</v>
       </c>
       <c r="I24" s="32">
-        <f>'Prefill_8K'!$BA$50</f>
-        <v>148351461888.0</v>
+        <f>'Decode_1M'!$U$36</f>
+        <v>1409286144</v>
       </c>
       <c r="J24" s="32">
-        <f>'Prefill_8K'!$BB$50</f>
-        <v>19577940480.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <f>'Decode_1M'!$X$36</f>
+        <v>1409286144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B25" s="33" t="str">
         <f>TEXT(IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25)))),"#,##0.000")&amp;IF((IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>3.314 GB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="C25" s="33" t="str">
         <f>TEXT(IF(ABS(H25)&gt;=1E12,H25/1E12,IF(ABS(H25)&gt;=1E9,H25/1E9,IF(ABS(H25)&gt;=1E6,H25/1E6,IF(ABS(H25)&gt;=1E3,H25/1E3,H25)))),"#,##0.000")&amp;IF((IF(ABS(H25)&gt;=1E12,"TB",IF(ABS(H25)&gt;=1E9,"GB",IF(ABS(H25)&gt;=1E6,"MB",IF(ABS(H25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H25)&gt;=1E12,"TB",IF(ABS(H25)&gt;=1E9,"GB",IF(ABS(H25)&gt;=1E6,"MB",IF(ABS(H25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>534.377 MB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="D25" s="33" t="str">
         <f>TEXT(IF(ABS(I25)&gt;=1E12,I25/1E12,IF(ABS(I25)&gt;=1E9,I25/1E9,IF(ABS(I25)&gt;=1E6,I25/1E6,IF(ABS(I25)&gt;=1E3,I25/1E3,I25)))),"#,##0.000")&amp;IF((IF(ABS(I25)&gt;=1E12,"TB",IF(ABS(I25)&gt;=1E9,"GB",IF(ABS(I25)&gt;=1E6,"MB",IF(ABS(I25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I25)&gt;=1E12,"TB",IF(ABS(I25)&gt;=1E9,"GB",IF(ABS(I25)&gt;=1E6,"MB",IF(ABS(I25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>3.314 GB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="E25" s="33" t="str">
         <f>TEXT(IF(ABS(J25)&gt;=1E12,J25/1E12,IF(ABS(J25)&gt;=1E9,J25/1E9,IF(ABS(J25)&gt;=1E6,J25/1E6,IF(ABS(J25)&gt;=1E3,J25/1E3,J25)))),"#,##0.000")&amp;IF((IF(ABS(J25)&gt;=1E12,"TB",IF(ABS(J25)&gt;=1E9,"GB",IF(ABS(J25)&gt;=1E6,"MB",IF(ABS(J25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J25)&gt;=1E12,"TB",IF(ABS(J25)&gt;=1E9,"GB",IF(ABS(J25)&gt;=1E6,"MB",IF(ABS(J25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>534.377 MB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="G25" s="32">
-        <f>'Prefill_8K'!$BA$51</f>
-        <v>3314423644.0</v>
+        <f>'Prefill_8K'!$U$37</f>
+        <v>12206080</v>
       </c>
       <c r="H25" s="32">
-        <f>'Prefill_8K'!$BB$51</f>
-        <v>534376892.0</v>
+        <f>'Prefill_8K'!$X$37</f>
+        <v>12206080</v>
       </c>
       <c r="I25" s="32">
-        <f>'Prefill_8K'!$BA$51</f>
-        <v>3314423644.0</v>
+        <f>'Decode_1M'!$U$37</f>
+        <v>12206080</v>
       </c>
       <c r="J25" s="32">
-        <f>'Prefill_8K'!$BB$51</f>
-        <v>534376892.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="B26" s="31" t="str">
+        <f>'Decode_1M'!$X$37</f>
+        <v>12206080</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B26" s="33" t="str">
         <f>TEXT(IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26)))),"#,##0.000")&amp;IF((IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>159.117 GB</v>
-      </c>
-      <c r="C26" s="31" t="str">
+        <v>7.232 GB</v>
+      </c>
+      <c r="C26" s="33" t="str">
         <f>TEXT(IF(ABS(H26)&gt;=1E12,H26/1E12,IF(ABS(H26)&gt;=1E9,H26/1E9,IF(ABS(H26)&gt;=1E6,H26/1E6,IF(ABS(H26)&gt;=1E3,H26/1E3,H26)))),"#,##0.000")&amp;IF((IF(ABS(H26)&gt;=1E12,"TB",IF(ABS(H26)&gt;=1E9,"GB",IF(ABS(H26)&gt;=1E6,"MB",IF(ABS(H26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H26)&gt;=1E12,"TB",IF(ABS(H26)&gt;=1E9,"GB",IF(ABS(H26)&gt;=1E6,"MB",IF(ABS(H26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>22.350 GB</v>
-      </c>
-      <c r="D26" s="31" t="str">
+        <v>7.232 GB</v>
+      </c>
+      <c r="D26" s="33" t="str">
         <f>TEXT(IF(ABS(I26)&gt;=1E12,I26/1E12,IF(ABS(I26)&gt;=1E9,I26/1E9,IF(ABS(I26)&gt;=1E6,I26/1E6,IF(ABS(I26)&gt;=1E3,I26/1E3,I26)))),"#,##0.000")&amp;IF((IF(ABS(I26)&gt;=1E12,"TB",IF(ABS(I26)&gt;=1E9,"GB",IF(ABS(I26)&gt;=1E6,"MB",IF(ABS(I26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I26)&gt;=1E12,"TB",IF(ABS(I26)&gt;=1E9,"GB",IF(ABS(I26)&gt;=1E6,"MB",IF(ABS(I26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>159.117 GB</v>
-      </c>
-      <c r="E26" s="31" t="str">
+        <v>7.232 GB</v>
+      </c>
+      <c r="E26" s="33" t="str">
         <f>TEXT(IF(ABS(J26)&gt;=1E12,J26/1E12,IF(ABS(J26)&gt;=1E9,J26/1E9,IF(ABS(J26)&gt;=1E6,J26/1E6,IF(ABS(J26)&gt;=1E3,J26/1E3,J26)))),"#,##0.000")&amp;IF((IF(ABS(J26)&gt;=1E12,"TB",IF(ABS(J26)&gt;=1E9,"GB",IF(ABS(J26)&gt;=1E6,"MB",IF(ABS(J26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J26)&gt;=1E12,"TB",IF(ABS(J26)&gt;=1E9,"GB",IF(ABS(J26)&gt;=1E6,"MB",IF(ABS(J26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>22.350 GB</v>
+        <v>7.232 GB</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G26" s="32">
-        <f>'Prefill_8K'!$BA$52</f>
-        <v>159117270492.0</v>
+        <f>'Prefill_8K'!$U$38</f>
+        <v>7232045056</v>
       </c>
       <c r="H26" s="32">
-        <f>'Prefill_8K'!$BB$52</f>
-        <v>22349822332.0</v>
+        <f>'Prefill_8K'!$X$38</f>
+        <v>7232045056</v>
       </c>
       <c r="I26" s="32">
-        <f>'Prefill_8K'!$BA$52</f>
-        <v>159117270492.0</v>
+        <f>'Decode_1M'!$U$38</f>
+        <v>7232045056</v>
       </c>
       <c r="J26" s="32">
-        <f>'Prefill_8K'!$BB$52</f>
-        <v>22349822332.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4" t="s">
+        <f>'Decode_1M'!$X$38</f>
+        <v>7232045056</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="31" t="s">
         <v>478</v>
       </c>
-      <c r="B27" s="33" t="str">
+      <c r="B27" s="31" t="str">
         <f>TEXT(IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27)))),"#,##0.000")&amp;IF((IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>50.987 MB</v>
-      </c>
-      <c r="C27" s="33" t="str">
+        <v>166.349 GB</v>
+      </c>
+      <c r="C27" s="31" t="str">
         <f>TEXT(IF(ABS(H27)&gt;=1E12,H27/1E12,IF(ABS(H27)&gt;=1E9,H27/1E9,IF(ABS(H27)&gt;=1E6,H27/1E6,IF(ABS(H27)&gt;=1E3,H27/1E3,H27)))),"#,##0.000")&amp;IF((IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>50.987 MB</v>
-      </c>
-      <c r="D27" s="33" t="str">
+        <v>29.582 GB</v>
+      </c>
+      <c r="D27" s="31" t="str">
         <f>TEXT(IF(ABS(I27)&gt;=1E12,I27/1E12,IF(ABS(I27)&gt;=1E9,I27/1E9,IF(ABS(I27)&gt;=1E6,I27/1E6,IF(ABS(I27)&gt;=1E3,I27/1E3,I27)))),"#,##0.000")&amp;IF((IF(ABS(I27)&gt;=1E12,"TB",IF(ABS(I27)&gt;=1E9,"GB",IF(ABS(I27)&gt;=1E6,"MB",IF(ABS(I27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I27)&gt;=1E12,"TB",IF(ABS(I27)&gt;=1E9,"GB",IF(ABS(I27)&gt;=1E6,"MB",IF(ABS(I27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.811 GB</v>
-      </c>
-      <c r="E27" s="33" t="str">
+        <v>166.349 GB</v>
+      </c>
+      <c r="E27" s="31" t="str">
         <f>TEXT(IF(ABS(J27)&gt;=1E12,J27/1E12,IF(ABS(J27)&gt;=1E9,J27/1E9,IF(ABS(J27)&gt;=1E6,J27/1E6,IF(ABS(J27)&gt;=1E3,J27/1E3,J27)))),"#,##0.000")&amp;IF((IF(ABS(J27)&gt;=1E12,"TB",IF(ABS(J27)&gt;=1E9,"GB",IF(ABS(J27)&gt;=1E6,"MB",IF(ABS(J27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J27)&gt;=1E12,"TB",IF(ABS(J27)&gt;=1E9,"GB",IF(ABS(J27)&gt;=1E6,"MB",IF(ABS(J27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.811 GB</v>
+        <v>29.582 GB</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>479</v>
       </c>
       <c r="G27" s="32">
-        <f>'Prefill_8K'!$U$35</f>
-        <v>50987008</v>
-      </c>
-      <c r="H27" s="32">
-        <f>'Prefill_8K'!$X$35</f>
-        <v>50987008</v>
-      </c>
-      <c r="I27" s="32">
-        <f>'Decode_1M'!$U$35</f>
-        <v>5810552832</v>
-      </c>
-      <c r="J27" s="32">
-        <f>'Decode_1M'!$X$35</f>
-        <v>5810552832</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="B28" s="33" t="str">
-        <f>TEXT(IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>11.010 MB</v>
-      </c>
-      <c r="C28" s="33" t="str">
-        <f>TEXT(IF(ABS(H28)&gt;=1E12,H28/1E12,IF(ABS(H28)&gt;=1E9,H28/1E9,IF(ABS(H28)&gt;=1E6,H28/1E6,IF(ABS(H28)&gt;=1E3,H28/1E3,H28)))),"#,##0.000")&amp;IF((IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>11.010 MB</v>
-      </c>
-      <c r="D28" s="33" t="str">
-        <f>TEXT(IF(ABS(I28)&gt;=1E12,I28/1E12,IF(ABS(I28)&gt;=1E9,I28/1E9,IF(ABS(I28)&gt;=1E6,I28/1E6,IF(ABS(I28)&gt;=1E3,I28/1E3,I28)))),"#,##0.000")&amp;IF((IF(ABS(I28)&gt;=1E12,"TB",IF(ABS(I28)&gt;=1E9,"GB",IF(ABS(I28)&gt;=1E6,"MB",IF(ABS(I28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I28)&gt;=1E12,"TB",IF(ABS(I28)&gt;=1E9,"GB",IF(ABS(I28)&gt;=1E6,"MB",IF(ABS(I28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.409 GB</v>
-      </c>
-      <c r="E28" s="33" t="str">
-        <f>TEXT(IF(ABS(J28)&gt;=1E12,J28/1E12,IF(ABS(J28)&gt;=1E9,J28/1E9,IF(ABS(J28)&gt;=1E6,J28/1E6,IF(ABS(J28)&gt;=1E3,J28/1E3,J28)))),"#,##0.000")&amp;IF((IF(ABS(J28)&gt;=1E12,"TB",IF(ABS(J28)&gt;=1E9,"GB",IF(ABS(J28)&gt;=1E6,"MB",IF(ABS(J28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J28)&gt;=1E12,"TB",IF(ABS(J28)&gt;=1E9,"GB",IF(ABS(J28)&gt;=1E6,"MB",IF(ABS(J28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.409 GB</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="G28" s="32">
-        <f>'Prefill_8K'!$U$36</f>
-        <v>11010048</v>
-      </c>
-      <c r="H28" s="32">
-        <f>'Prefill_8K'!$X$36</f>
-        <v>11010048</v>
-      </c>
-      <c r="I28" s="32">
-        <f>'Decode_1M'!$U$36</f>
-        <v>1409286144</v>
-      </c>
-      <c r="J28" s="32">
-        <f>'Decode_1M'!$X$36</f>
-        <v>1409286144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B29" s="33" t="str">
-        <f>TEXT(IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29)))),"#,##0.000")&amp;IF((IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="C29" s="33" t="str">
-        <f>TEXT(IF(ABS(H29)&gt;=1E12,H29/1E12,IF(ABS(H29)&gt;=1E9,H29/1E9,IF(ABS(H29)&gt;=1E6,H29/1E6,IF(ABS(H29)&gt;=1E3,H29/1E3,H29)))),"#,##0.000")&amp;IF((IF(ABS(H29)&gt;=1E12,"TB",IF(ABS(H29)&gt;=1E9,"GB",IF(ABS(H29)&gt;=1E6,"MB",IF(ABS(H29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H29)&gt;=1E12,"TB",IF(ABS(H29)&gt;=1E9,"GB",IF(ABS(H29)&gt;=1E6,"MB",IF(ABS(H29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="D29" s="33" t="str">
-        <f>TEXT(IF(ABS(I29)&gt;=1E12,I29/1E12,IF(ABS(I29)&gt;=1E9,I29/1E9,IF(ABS(I29)&gt;=1E6,I29/1E6,IF(ABS(I29)&gt;=1E3,I29/1E3,I29)))),"#,##0.000")&amp;IF((IF(ABS(I29)&gt;=1E12,"TB",IF(ABS(I29)&gt;=1E9,"GB",IF(ABS(I29)&gt;=1E6,"MB",IF(ABS(I29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I29)&gt;=1E12,"TB",IF(ABS(I29)&gt;=1E9,"GB",IF(ABS(I29)&gt;=1E6,"MB",IF(ABS(I29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="E29" s="33" t="str">
-        <f>TEXT(IF(ABS(J29)&gt;=1E12,J29/1E12,IF(ABS(J29)&gt;=1E9,J29/1E9,IF(ABS(J29)&gt;=1E6,J29/1E6,IF(ABS(J29)&gt;=1E3,J29/1E3,J29)))),"#,##0.000")&amp;IF((IF(ABS(J29)&gt;=1E12,"TB",IF(ABS(J29)&gt;=1E9,"GB",IF(ABS(J29)&gt;=1E6,"MB",IF(ABS(J29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J29)&gt;=1E12,"TB",IF(ABS(J29)&gt;=1E9,"GB",IF(ABS(J29)&gt;=1E6,"MB",IF(ABS(J29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="G29" s="32">
-        <f>'Prefill_8K'!$U$37</f>
-        <v>12206080</v>
-      </c>
-      <c r="H29" s="32">
-        <f>'Prefill_8K'!$X$37</f>
-        <v>12206080</v>
-      </c>
-      <c r="I29" s="32">
-        <f>'Decode_1M'!$U$37</f>
-        <v>12206080</v>
-      </c>
-      <c r="J29" s="32">
-        <f>'Decode_1M'!$X$37</f>
-        <v>12206080</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="B30" s="33" t="str">
-        <f>TEXT(IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30)))),"#,##0.000")&amp;IF((IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.232 GB</v>
-      </c>
-      <c r="C30" s="33" t="str">
-        <f>TEXT(IF(ABS(H30)&gt;=1E12,H30/1E12,IF(ABS(H30)&gt;=1E9,H30/1E9,IF(ABS(H30)&gt;=1E6,H30/1E6,IF(ABS(H30)&gt;=1E3,H30/1E3,H30)))),"#,##0.000")&amp;IF((IF(ABS(H30)&gt;=1E12,"TB",IF(ABS(H30)&gt;=1E9,"GB",IF(ABS(H30)&gt;=1E6,"MB",IF(ABS(H30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H30)&gt;=1E12,"TB",IF(ABS(H30)&gt;=1E9,"GB",IF(ABS(H30)&gt;=1E6,"MB",IF(ABS(H30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.232 GB</v>
-      </c>
-      <c r="D30" s="33" t="str">
-        <f>TEXT(IF(ABS(I30)&gt;=1E12,I30/1E12,IF(ABS(I30)&gt;=1E9,I30/1E9,IF(ABS(I30)&gt;=1E6,I30/1E6,IF(ABS(I30)&gt;=1E3,I30/1E3,I30)))),"#,##0.000")&amp;IF((IF(ABS(I30)&gt;=1E12,"TB",IF(ABS(I30)&gt;=1E9,"GB",IF(ABS(I30)&gt;=1E6,"MB",IF(ABS(I30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I30)&gt;=1E12,"TB",IF(ABS(I30)&gt;=1E9,"GB",IF(ABS(I30)&gt;=1E6,"MB",IF(ABS(I30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.232 GB</v>
-      </c>
-      <c r="E30" s="33" t="str">
-        <f>TEXT(IF(ABS(J30)&gt;=1E12,J30/1E12,IF(ABS(J30)&gt;=1E9,J30/1E9,IF(ABS(J30)&gt;=1E6,J30/1E6,IF(ABS(J30)&gt;=1E3,J30/1E3,J30)))),"#,##0.000")&amp;IF((IF(ABS(J30)&gt;=1E12,"TB",IF(ABS(J30)&gt;=1E9,"GB",IF(ABS(J30)&gt;=1E6,"MB",IF(ABS(J30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J30)&gt;=1E12,"TB",IF(ABS(J30)&gt;=1E9,"GB",IF(ABS(J30)&gt;=1E6,"MB",IF(ABS(J30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.232 GB</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="G30" s="32">
-        <f>'Prefill_8K'!$U$38</f>
-        <v>7232045056</v>
-      </c>
-      <c r="H30" s="32">
-        <f>'Prefill_8K'!$X$38</f>
-        <v>7232045056</v>
-      </c>
-      <c r="I30" s="32">
-        <f>'Decode_1M'!$U$38</f>
-        <v>7232045056</v>
-      </c>
-      <c r="J30" s="32">
-        <f>'Decode_1M'!$X$38</f>
-        <v>7232045056</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="31" t="s">
-        <v>483</v>
-      </c>
-      <c r="B31" s="31" t="str">
-        <f>TEXT(IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31)))),"#,##0.000")&amp;IF((IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>166.349 GB</v>
-      </c>
-      <c r="C31" s="31" t="str">
-        <f>TEXT(IF(ABS(H31)&gt;=1E12,H31/1E12,IF(ABS(H31)&gt;=1E9,H31/1E9,IF(ABS(H31)&gt;=1E6,H31/1E6,IF(ABS(H31)&gt;=1E3,H31/1E3,H31)))),"#,##0.000")&amp;IF((IF(ABS(H31)&gt;=1E12,"TB",IF(ABS(H31)&gt;=1E9,"GB",IF(ABS(H31)&gt;=1E6,"MB",IF(ABS(H31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H31)&gt;=1E12,"TB",IF(ABS(H31)&gt;=1E9,"GB",IF(ABS(H31)&gt;=1E6,"MB",IF(ABS(H31)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>29.582 GB</v>
-      </c>
-      <c r="D31" s="31" t="str">
-        <f>TEXT(IF(ABS(I31)&gt;=1E12,I31/1E12,IF(ABS(I31)&gt;=1E9,I31/1E9,IF(ABS(I31)&gt;=1E6,I31/1E6,IF(ABS(I31)&gt;=1E3,I31/1E3,I31)))),"#,##0.000")&amp;IF((IF(ABS(I31)&gt;=1E12,"TB",IF(ABS(I31)&gt;=1E9,"GB",IF(ABS(I31)&gt;=1E6,"MB",IF(ABS(I31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I31)&gt;=1E12,"TB",IF(ABS(I31)&gt;=1E9,"GB",IF(ABS(I31)&gt;=1E6,"MB",IF(ABS(I31)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>166.349 GB</v>
-      </c>
-      <c r="E31" s="31" t="str">
-        <f>TEXT(IF(ABS(J31)&gt;=1E12,J31/1E12,IF(ABS(J31)&gt;=1E9,J31/1E9,IF(ABS(J31)&gt;=1E6,J31/1E6,IF(ABS(J31)&gt;=1E3,J31/1E3,J31)))),"#,##0.000")&amp;IF((IF(ABS(J31)&gt;=1E12,"TB",IF(ABS(J31)&gt;=1E9,"GB",IF(ABS(J31)&gt;=1E6,"MB",IF(ABS(J31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J31)&gt;=1E12,"TB",IF(ABS(J31)&gt;=1E9,"GB",IF(ABS(J31)&gt;=1E6,"MB",IF(ABS(J31)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>29.582 GB</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="G31" s="32">
         <f>'Prefill_8K'!$BA$52+'Prefill_8K'!$U$38</f>
         <v>166349315548.0</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H27" s="32">
         <f>'Prefill_8K'!$BB$52+'Prefill_8K'!$X$38</f>
         <v>29581867388.0</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I27" s="32">
         <f>'Prefill_8K'!$BA$52+'Decode_1M'!$U$38</f>
         <v>166349315548.0</v>
       </c>
-      <c r="J31" s="32">
+      <c r="J27" s="32">
         <f>'Prefill_8K'!$BB$52+'Decode_1M'!$X$38</f>
         <v>29581867388.0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="B32" s="31" t="str">
-        <f>TEXT(IF(ABS(G32)&gt;=1E15,G32/1E15,IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+    <row r="28" spans="1:20">
+      <c r="A28" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="B28" s="31" t="str">
+        <f>TEXT(IF(ABS(G28)&gt;=1E15,G28/1E15,IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E15,"PFLOPs",IF(ABS(G28)&gt;=1E12,"TFLOPs",IF(ABS(G28)&gt;=1E9,"GFLOPs",IF(ABS(G28)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E15,"PFLOPs",IF(ABS(G28)&gt;=1E12,"TFLOPs",IF(ABS(G28)&gt;=1E9,"GFLOPs",IF(ABS(G28)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>228.398 TFLOPs</v>
       </c>
-      <c r="C32" s="31" t="str">
-        <f>TEXT(IF(ABS(H32)&gt;=1E15,H32/1E15,IF(ABS(H32)&gt;=1E12,H32/1E12,IF(ABS(H32)&gt;=1E9,H32/1E9,IF(ABS(H32)&gt;=1E6,H32/1E6,H32)))),"#,##0.000")&amp;IF((IF(ABS(H32)&gt;=1E15,"PFLOPs",IF(ABS(H32)&gt;=1E12,"TFLOPs",IF(ABS(H32)&gt;=1E9,"GFLOPs",IF(ABS(H32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H32)&gt;=1E15,"PFLOPs",IF(ABS(H32)&gt;=1E12,"TFLOPs",IF(ABS(H32)&gt;=1E9,"GFLOPs",IF(ABS(H32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="C28" s="31" t="str">
+        <f>TEXT(IF(ABS(H28)&gt;=1E15,H28/1E15,IF(ABS(H28)&gt;=1E12,H28/1E12,IF(ABS(H28)&gt;=1E9,H28/1E9,IF(ABS(H28)&gt;=1E6,H28/1E6,H28)))),"#,##0.000")&amp;IF((IF(ABS(H28)&gt;=1E15,"PFLOPs",IF(ABS(H28)&gt;=1E12,"TFLOPs",IF(ABS(H28)&gt;=1E9,"GFLOPs",IF(ABS(H28)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H28)&gt;=1E15,"PFLOPs",IF(ABS(H28)&gt;=1E12,"TFLOPs",IF(ABS(H28)&gt;=1E9,"GFLOPs",IF(ABS(H28)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>55.653 TFLOPs</v>
       </c>
-      <c r="D32" s="31" t="str">
-        <f>TEXT(IF(ABS(I32)&gt;=1E15,I32/1E15,IF(ABS(I32)&gt;=1E12,I32/1E12,IF(ABS(I32)&gt;=1E9,I32/1E9,IF(ABS(I32)&gt;=1E6,I32/1E6,I32)))),"#,##0.000")&amp;IF((IF(ABS(I32)&gt;=1E15,"PFLOPs",IF(ABS(I32)&gt;=1E12,"TFLOPs",IF(ABS(I32)&gt;=1E9,"GFLOPs",IF(ABS(I32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(I32)&gt;=1E15,"PFLOPs",IF(ABS(I32)&gt;=1E12,"TFLOPs",IF(ABS(I32)&gt;=1E9,"GFLOPs",IF(ABS(I32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="D28" s="31" t="str">
+        <f>TEXT(IF(ABS(I28)&gt;=1E15,I28/1E15,IF(ABS(I28)&gt;=1E12,I28/1E12,IF(ABS(I28)&gt;=1E9,I28/1E9,IF(ABS(I28)&gt;=1E6,I28/1E6,I28)))),"#,##0.000")&amp;IF((IF(ABS(I28)&gt;=1E15,"PFLOPs",IF(ABS(I28)&gt;=1E12,"TFLOPs",IF(ABS(I28)&gt;=1E9,"GFLOPs",IF(ABS(I28)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(I28)&gt;=1E15,"PFLOPs",IF(ABS(I28)&gt;=1E12,"TFLOPs",IF(ABS(I28)&gt;=1E9,"GFLOPs",IF(ABS(I28)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>140.356 GFLOPs</v>
       </c>
-      <c r="E32" s="31" t="str">
-        <f>TEXT(IF(ABS(J32)&gt;=1E15,J32/1E15,IF(ABS(J32)&gt;=1E12,J32/1E12,IF(ABS(J32)&gt;=1E9,J32/1E9,IF(ABS(J32)&gt;=1E6,J32/1E6,J32)))),"#,##0.000")&amp;IF((IF(ABS(J32)&gt;=1E15,"PFLOPs",IF(ABS(J32)&gt;=1E12,"TFLOPs",IF(ABS(J32)&gt;=1E9,"GFLOPs",IF(ABS(J32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(J32)&gt;=1E15,"PFLOPs",IF(ABS(J32)&gt;=1E12,"TFLOPs",IF(ABS(J32)&gt;=1E9,"GFLOPs",IF(ABS(J32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="E28" s="31" t="str">
+        <f>TEXT(IF(ABS(J28)&gt;=1E15,J28/1E15,IF(ABS(J28)&gt;=1E12,J28/1E12,IF(ABS(J28)&gt;=1E9,J28/1E9,IF(ABS(J28)&gt;=1E6,J28/1E6,J28)))),"#,##0.000")&amp;IF((IF(ABS(J28)&gt;=1E15,"PFLOPs",IF(ABS(J28)&gt;=1E12,"TFLOPs",IF(ABS(J28)&gt;=1E9,"GFLOPs",IF(ABS(J28)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(J28)&gt;=1E15,"PFLOPs",IF(ABS(J28)&gt;=1E12,"TFLOPs",IF(ABS(J28)&gt;=1E9,"GFLOPs",IF(ABS(J28)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>23.550 GFLOPs</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="G32" s="32">
+      <c r="F28" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="G28" s="32">
         <f>'Prefill_8K'!$AF$13</f>
         <v>228397682114560.0</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H28" s="32">
         <f>'Prefill_8K'!$AI$13</f>
         <v>55652568907776.0</v>
       </c>
-      <c r="I32" s="32">
+      <c r="I28" s="32">
         <f>'Decode_1M'!$AF$13</f>
         <v>140355752110.0</v>
       </c>
-      <c r="J32" s="32">
+      <c r="J28" s="32">
         <f>'Decode_1M'!$AI$13</f>
         <v>23549694126.0</v>
       </c>
     </row>
+    <row r="31" spans="1:20">
+      <c r="S31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="S32" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="T32" s="32">
+        <f>G28/1e+12</f>
+        <v>228.39768211456</v>
+      </c>
+    </row>
+    <row r="33" spans="19:21">
+      <c r="S33" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="T33" s="32">
+        <f>H28/1e+12</f>
+        <v>55.652568907776</v>
+      </c>
+    </row>
+    <row r="34" spans="19:21">
+      <c r="S34" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="T34" s="32">
+        <f>I28/1e+12</f>
+        <v>0.14035575211</v>
+      </c>
+    </row>
     <row r="35" spans="19:21">
-      <c r="S35" s="3" t="s">
+      <c r="S35" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="T35" s="32">
+        <f>J28/1e+12</f>
+        <v>0.023549694126</v>
+      </c>
+    </row>
+    <row r="38" spans="19:21">
+      <c r="S38" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="36" spans="19:21">
-      <c r="S36" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="T36" s="32">
-        <f>G32/1e+12</f>
-        <v>228.39768211456</v>
-      </c>
-    </row>
-    <row r="37" spans="19:21">
-      <c r="S37" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="T37" s="32">
-        <f>H32/1e+12</f>
-        <v>55.652568907776</v>
-      </c>
-    </row>
-    <row r="38" spans="19:21">
-      <c r="S38" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="T38" s="32">
-        <f>I32/1e+12</f>
-        <v>0.14035575211</v>
+      <c r="T38" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="39" spans="19:21">
       <c r="S39" s="4" t="s">
-        <v>489</v>
+        <v>40</v>
       </c>
       <c r="T39" s="32">
-        <f>J32/1e+12</f>
-        <v>0.023549694126</v>
-      </c>
-    </row>
-    <row r="42" spans="19:21">
-      <c r="S42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="43" spans="19:21">
-      <c r="S43" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T43" s="32">
         <f>G5/1e+12</f>
         <v>102.836037746688</v>
       </c>
-      <c r="U43" s="32">
+      <c r="U39" s="32">
         <f>H5/1e+12</f>
         <v>23.172382457856</v>
       </c>
     </row>
-    <row r="44" spans="19:21">
-      <c r="S44" s="4" t="s">
+    <row r="40" spans="19:21">
+      <c r="S40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T40" s="32">
         <f>G6/1e+12</f>
         <v>124.846109360128</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U40" s="32">
         <f>H6/1e+12</f>
         <v>31.765578121216</v>
       </c>
     </row>
-    <row r="45" spans="19:21">
-      <c r="S45" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="T45" s="32">
+    <row r="41" spans="19:21">
+      <c r="S41" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="T41" s="32">
         <f>G7/1e+12</f>
         <v>0.715535007744</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U41" s="32">
         <f>H7/1e+12</f>
         <v>0.714608328704</v>
       </c>
     </row>
-    <row r="49" spans="19:21">
-      <c r="S49" s="3" t="s">
+    <row r="45" spans="19:21">
+      <c r="S45" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="50" spans="19:21">
-      <c r="S50" s="4" t="s">
+      <c r="T45" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="46" spans="19:21">
+      <c r="S46" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T46" s="32">
         <f>I5/1e+09</f>
         <v>123.969470464</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U46" s="32">
         <f>J5/1e+09</f>
         <v>19.452461056</v>
       </c>
     </row>
-    <row r="51" spans="19:21">
-      <c r="S51" s="4" t="s">
+    <row r="47" spans="19:21">
+      <c r="S47" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T51" s="32">
+      <c r="T47" s="32">
         <f>I6/1e+09</f>
         <v>15.240003584</v>
       </c>
-      <c r="U51" s="32">
+      <c r="U47" s="32">
         <f>J6/1e+09</f>
         <v>3.877634048</v>
       </c>
     </row>
-    <row r="52" spans="19:21">
-      <c r="S52" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="T52" s="32">
+    <row r="48" spans="19:21">
+      <c r="S48" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="T48" s="32">
         <f>I7/1e+09</f>
         <v>1.146278062</v>
       </c>
-      <c r="U52" s="32">
+      <c r="U48" s="32">
         <f>J7/1e+09</f>
         <v>0.219599022</v>
       </c>
     </row>
-    <row r="56" spans="19:21">
-      <c r="S56" s="3" t="s">
+    <row r="52" spans="19:21">
+      <c r="S52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T56" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="57" spans="19:21">
-      <c r="S57" s="4" t="s">
+      <c r="T52" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="53" spans="19:21">
+      <c r="S53" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T57" s="32">
-        <f>G9/1e+09</f>
-        <v>358.0378144</v>
-      </c>
-      <c r="U57" s="32">
-        <f>H9/1e+09</f>
-        <v>231.531806144</v>
-      </c>
-    </row>
-    <row r="58" spans="19:21">
-      <c r="S58" s="4" t="s">
+      <c r="T53" s="32">
+        <f>G19/1e+09</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="U53" s="32">
+        <f>H19/1e+09</f>
+        <v>2.23750496</v>
+      </c>
+    </row>
+    <row r="54" spans="19:21">
+      <c r="S54" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T58" s="32">
-        <f>G10/1e+09</f>
-        <v>191.988670976</v>
-      </c>
-      <c r="U58" s="32">
-        <f>H10/1e+09</f>
-        <v>32.915497472</v>
+      <c r="T54" s="32">
+        <f>G20/1e+09</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="U54" s="32">
+        <f>H20/1e+09</f>
+        <v>19.57794048</v>
+      </c>
+    </row>
+    <row r="55" spans="19:21">
+      <c r="S55" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="T55" s="32">
+        <f>G21/1e+09</f>
+        <v>3.314423644</v>
+      </c>
+      <c r="U55" s="32">
+        <f>H21/1e+09</f>
+        <v>0.534376892</v>
       </c>
     </row>
     <row r="59" spans="19:21">
-      <c r="S59" s="4" t="s">
+      <c r="S59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="60" spans="19:21">
+      <c r="S60" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="T59" s="32">
-        <f>G11/1e+09</f>
-        <v>106.744396636</v>
-      </c>
-      <c r="U59" s="32">
-        <f>H11/1e+09</f>
-        <v>104.890576444</v>
-      </c>
-    </row>
-    <row r="63" spans="19:21">
-      <c r="S63" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="64" spans="19:21">
-      <c r="S64" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T64" s="32">
-        <f>I9/1e+09</f>
-        <v>10.492228352</v>
-      </c>
-      <c r="U64" s="32">
-        <f>J9/1e+09</f>
-        <v>4.035232528</v>
-      </c>
-    </row>
-    <row r="65" spans="19:21">
-      <c r="S65" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T65" s="32">
-        <f>I10/1e+09</f>
-        <v>4.627033672</v>
-      </c>
-      <c r="U65" s="32">
-        <f>J10/1e+09</f>
-        <v>1.605205576</v>
-      </c>
-    </row>
-    <row r="66" spans="19:21">
-      <c r="S66" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="T66" s="32">
-        <f>I11/1e+09</f>
-        <v>2.268650332</v>
-      </c>
-      <c r="U66" s="32">
-        <f>J11/1e+09</f>
-        <v>0.41483014</v>
-      </c>
-    </row>
-    <row r="70" spans="19:21">
-      <c r="S70" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T70" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="U70" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="71" spans="19:21">
-      <c r="S71" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T71" s="32">
-        <f>G23/1e+09</f>
-        <v>7.45138496</v>
-      </c>
-      <c r="U71" s="32">
-        <f>H23/1e+09</f>
-        <v>2.23750496</v>
-      </c>
-    </row>
-    <row r="72" spans="19:21">
-      <c r="S72" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T72" s="32">
-        <f>G24/1e+09</f>
-        <v>148.351461888</v>
-      </c>
-      <c r="U72" s="32">
-        <f>H24/1e+09</f>
-        <v>19.57794048</v>
-      </c>
-    </row>
-    <row r="73" spans="19:21">
-      <c r="S73" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="T73" s="32">
-        <f>G25/1e+09</f>
-        <v>3.314423644</v>
-      </c>
-      <c r="U73" s="32">
-        <f>H25/1e+09</f>
-        <v>0.534376892</v>
-      </c>
-    </row>
-    <row r="77" spans="19:21">
-      <c r="S77" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T77" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="U77" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="78" spans="19:21">
-      <c r="S78" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="T78" s="32">
-        <f>G31/1e+09</f>
+      <c r="T60" s="32">
+        <f>G27/1e+09</f>
         <v>166.349315548</v>
       </c>
-      <c r="U78" s="32">
-        <f>H31/1e+09</f>
+      <c r="U60" s="32">
+        <f>H27/1e+09</f>
         <v>29.581867388</v>
       </c>
     </row>
-    <row r="79" spans="19:21">
-      <c r="S79" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="T79" s="32">
-        <f>I31/1e+09</f>
+    <row r="61" spans="19:21">
+      <c r="S61" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="T61" s="32">
+        <f>I27/1e+09</f>
         <v>166.349315548</v>
       </c>
-      <c r="U79" s="32">
-        <f>J31/1e+09</f>
+      <c r="U61" s="32">
+        <f>J27/1e+09</f>
         <v>29.581867388</v>
       </c>
     </row>
@@ -13350,7 +12648,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -13361,17 +12659,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -13382,10 +12680,10 @@
         <v>438</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>363</v>
@@ -13404,7 +12702,7 @@
         <v>123.969 GFLOPs</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G6" s="32">
         <f>'Prefill_8K'!$AF$14</f>
@@ -13428,7 +12726,7 @@
         <v>15.240 GFLOPs</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G7" s="32">
         <f>'Prefill_8K'!$AF$15</f>
@@ -13452,7 +12750,7 @@
         <v>1.146 GFLOPs</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G8" s="32">
         <f>'Prefill_8K'!$AO$48</f>
@@ -13476,7 +12774,7 @@
         <v>140.356 GFLOPs</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G9" s="32">
         <f>'Prefill_8K'!$AF$13</f>
@@ -13492,23 +12790,23 @@
         <v>448</v>
       </c>
       <c r="B10" s="33" t="str">
-        <f>TEXT(IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10)))),"#,##0.000")&amp;IF((IF(ABS(G10)&gt;=1E12,"TB",IF(ABS(G10)&gt;=1E9,"GB",IF(ABS(G10)&gt;=1E6,"MB",IF(ABS(G10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G10)&gt;=1E12,"TB",IF(ABS(G10)&gt;=1E9,"GB",IF(ABS(G10)&gt;=1E6,"MB",IF(ABS(G10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>358.038 GB</v>
+        <f>TEXT(G10,"#,##0.000")&amp;" GB/s"</f>
+        <v>358.038 GB/s</v>
       </c>
       <c r="C10" s="33" t="str">
-        <f>TEXT(IF(ABS(H10)&gt;=1E12,H10/1E12,IF(ABS(H10)&gt;=1E9,H10/1E9,IF(ABS(H10)&gt;=1E6,H10/1E6,IF(ABS(H10)&gt;=1E3,H10/1E3,H10)))),"#,##0.000")&amp;IF((IF(ABS(H10)&gt;=1E12,"TB",IF(ABS(H10)&gt;=1E9,"GB",IF(ABS(H10)&gt;=1E6,"MB",IF(ABS(H10)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H10)&gt;=1E12,"TB",IF(ABS(H10)&gt;=1E9,"GB",IF(ABS(H10)&gt;=1E6,"MB",IF(ABS(H10)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>10.492 GB</v>
+        <f>TEXT(H10,"#,##0.000")&amp;" GB/s"</f>
+        <v>1,049.223 GB/s</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G10" s="32">
-        <f>'Prefill_8K'!$AG$14</f>
-        <v>358037814400.0</v>
+        <f>'Prefill_8K'!$AG$14/(PrefillTargetMs/1000)/1E9</f>
+        <v>358.0378144</v>
       </c>
       <c r="H10" s="32">
-        <f>'Decode_1M'!$AG$14</f>
-        <v>10492228352.0</v>
+        <f>'Decode_1M'!$AG$14/(DecodeTargetMs/1000)/1E9</f>
+        <v>1049.2228352</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -13516,23 +12814,23 @@
         <v>450</v>
       </c>
       <c r="B11" s="33" t="str">
-        <f>TEXT(IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11)))),"#,##0.000")&amp;IF((IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>191.989 GB</v>
+        <f>TEXT(G11,"#,##0.000")&amp;" GB/s"</f>
+        <v>191.989 GB/s</v>
       </c>
       <c r="C11" s="33" t="str">
-        <f>TEXT(IF(ABS(H11)&gt;=1E12,H11/1E12,IF(ABS(H11)&gt;=1E9,H11/1E9,IF(ABS(H11)&gt;=1E6,H11/1E6,IF(ABS(H11)&gt;=1E3,H11/1E3,H11)))),"#,##0.000")&amp;IF((IF(ABS(H11)&gt;=1E12,"TB",IF(ABS(H11)&gt;=1E9,"GB",IF(ABS(H11)&gt;=1E6,"MB",IF(ABS(H11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H11)&gt;=1E12,"TB",IF(ABS(H11)&gt;=1E9,"GB",IF(ABS(H11)&gt;=1E6,"MB",IF(ABS(H11)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>4.627 GB</v>
+        <f>TEXT(H11,"#,##0.000")&amp;" GB/s"</f>
+        <v>462.703 GB/s</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G11" s="32">
-        <f>'Prefill_8K'!$AG$15</f>
-        <v>191988670976.0</v>
+        <f>'Prefill_8K'!$AG$15/(PrefillTargetMs/1000)/1E9</f>
+        <v>191.988670976</v>
       </c>
       <c r="H11" s="32">
-        <f>'Decode_1M'!$AG$15</f>
-        <v>4627033672.0</v>
+        <f>'Decode_1M'!$AG$15/(DecodeTargetMs/1000)/1E9</f>
+        <v>462.7033672</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -13540,613 +12838,613 @@
         <v>451</v>
       </c>
       <c r="B12" s="33" t="str">
-        <f>TEXT(IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12)))),"#,##0.000")&amp;IF((IF(ABS(G12)&gt;=1E12,"TB",IF(ABS(G12)&gt;=1E9,"GB",IF(ABS(G12)&gt;=1E6,"MB",IF(ABS(G12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G12)&gt;=1E12,"TB",IF(ABS(G12)&gt;=1E9,"GB",IF(ABS(G12)&gt;=1E6,"MB",IF(ABS(G12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>106.744 GB</v>
+        <f>TEXT(G12,"#,##0.000")&amp;" GB/s"</f>
+        <v>106.744 GB/s</v>
       </c>
       <c r="C12" s="33" t="str">
-        <f>TEXT(IF(ABS(H12)&gt;=1E12,H12/1E12,IF(ABS(H12)&gt;=1E9,H12/1E9,IF(ABS(H12)&gt;=1E6,H12/1E6,IF(ABS(H12)&gt;=1E3,H12/1E3,H12)))),"#,##0.000")&amp;IF((IF(ABS(H12)&gt;=1E12,"TB",IF(ABS(H12)&gt;=1E9,"GB",IF(ABS(H12)&gt;=1E6,"MB",IF(ABS(H12)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H12)&gt;=1E12,"TB",IF(ABS(H12)&gt;=1E9,"GB",IF(ABS(H12)&gt;=1E6,"MB",IF(ABS(H12)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.269 GB</v>
+        <f>TEXT(H12,"#,##0.000")&amp;" GB/s"</f>
+        <v>226.865 GB/s</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G12" s="32">
-        <f>'Prefill_8K'!$AQ$48</f>
-        <v>106744396636.0</v>
+        <f>'Prefill_8K'!$AQ$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>106.744396636</v>
       </c>
       <c r="H12" s="32">
-        <f>'Decode_1M'!$AQ$48</f>
-        <v>2268650332.0</v>
+        <f>'Decode_1M'!$AQ$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>226.8650332</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="B13" s="31" t="str">
-        <f>TEXT(IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13)))),"#,##0.000")&amp;IF((IF(ABS(G13)&gt;=1E12,"TB",IF(ABS(G13)&gt;=1E9,"GB",IF(ABS(G13)&gt;=1E6,"MB",IF(ABS(G13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G13)&gt;=1E12,"TB",IF(ABS(G13)&gt;=1E9,"GB",IF(ABS(G13)&gt;=1E6,"MB",IF(ABS(G13)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>656.771 GB</v>
-      </c>
-      <c r="C13" s="31" t="str">
-        <f>TEXT(IF(ABS(H13)&gt;=1E12,H13/1E12,IF(ABS(H13)&gt;=1E9,H13/1E9,IF(ABS(H13)&gt;=1E6,H13/1E6,IF(ABS(H13)&gt;=1E3,H13/1E3,H13)))),"#,##0.000")&amp;IF((IF(ABS(H13)&gt;=1E12,"TB",IF(ABS(H13)&gt;=1E9,"GB",IF(ABS(H13)&gt;=1E6,"MB",IF(ABS(H13)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H13)&gt;=1E12,"TB",IF(ABS(H13)&gt;=1E9,"GB",IF(ABS(H13)&gt;=1E6,"MB",IF(ABS(H13)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>17.388 GB</v>
+      <c r="A13" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B13" s="33" t="str">
+        <f>TEXT(IF(ABS(G13)&gt;=1E15,G13/1E15,IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,G13)))),"#,##0.000")&amp;IF((IF(ABS(G13)&gt;=1E15,"PFLOPs",IF(ABS(G13)&gt;=1E12,"TFLOPs",IF(ABS(G13)&gt;=1E9,"GFLOPs",IF(ABS(G13)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G13)&gt;=1E15,"PFLOPs",IF(ABS(G13)&gt;=1E12,"TFLOPs",IF(ABS(G13)&gt;=1E9,"GFLOPs",IF(ABS(G13)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>228.398 TFLOPs</v>
+      </c>
+      <c r="C13" s="33" t="str">
+        <f>TEXT(IF(ABS(H13)&gt;=1E15,H13/1E15,IF(ABS(H13)&gt;=1E12,H13/1E12,IF(ABS(H13)&gt;=1E9,H13/1E9,IF(ABS(H13)&gt;=1E6,H13/1E6,H13)))),"#,##0.000")&amp;IF((IF(ABS(H13)&gt;=1E15,"PFLOPs",IF(ABS(H13)&gt;=1E12,"TFLOPs",IF(ABS(H13)&gt;=1E9,"GFLOPs",IF(ABS(H13)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H13)&gt;=1E15,"PFLOPs",IF(ABS(H13)&gt;=1E12,"TFLOPs",IF(ABS(H13)&gt;=1E9,"GFLOPs",IF(ABS(H13)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>140.356 GFLOPs</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G13" s="32">
-        <f>'Prefill_8K'!$AG$13</f>
-        <v>656770882012.0</v>
+        <f>'Prefill_8K'!$AF$13</f>
+        <v>228397682114560.0</v>
       </c>
       <c r="H13" s="32">
-        <f>'Decode_1M'!$AG$13</f>
-        <v>17387912356.0</v>
+        <f>'Decode_1M'!$AF$13</f>
+        <v>140355752110.0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B14" s="33" t="str">
-        <f>TEXT(G14,"#,##0.000")&amp;" GB/s"</f>
-        <v>358.038 GB/s</v>
+        <f>TEXT(IF(ABS(G14)&gt;=1E12,G14/1E12,IF(ABS(G14)&gt;=1E9,G14/1E9,IF(ABS(G14)&gt;=1E6,G14/1E6,IF(ABS(G14)&gt;=1E3,G14/1E3,G14)))),"#,##0.000")&amp;IF((IF(ABS(G14)&gt;=1E12,"TB",IF(ABS(G14)&gt;=1E9,"GB",IF(ABS(G14)&gt;=1E6,"MB",IF(ABS(G14)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G14)&gt;=1E12,"TB",IF(ABS(G14)&gt;=1E9,"GB",IF(ABS(G14)&gt;=1E6,"MB",IF(ABS(G14)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>0.000 B</v>
       </c>
       <c r="C14" s="33" t="str">
-        <f>TEXT(H14,"#,##0.000")&amp;" GB/s"</f>
-        <v>1,049.223 GB/s</v>
+        <f>TEXT(IF(ABS(H14)&gt;=1E12,H14/1E12,IF(ABS(H14)&gt;=1E9,H14/1E9,IF(ABS(H14)&gt;=1E6,H14/1E6,IF(ABS(H14)&gt;=1E3,H14/1E3,H14)))),"#,##0.000")&amp;IF((IF(ABS(H14)&gt;=1E12,"TB",IF(ABS(H14)&gt;=1E9,"GB",IF(ABS(H14)&gt;=1E6,"MB",IF(ABS(H14)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H14)&gt;=1E12,"TB",IF(ABS(H14)&gt;=1E9,"GB",IF(ABS(H14)&gt;=1E6,"MB",IF(ABS(H14)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>0.000 B</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G14" s="32">
-        <f>'Prefill_8K'!$AG$14/(PrefillTargetMs/1000)/1E9</f>
-        <v>358.0378144</v>
+        <f>'Prefill_8K'!$AS$48</f>
+        <v>0.0</v>
       </c>
       <c r="H14" s="32">
-        <f>'Decode_1M'!$AG$14/(DecodeTargetMs/1000)/1E9</f>
-        <v>1049.2228352</v>
+        <f>'Decode_1M'!$AS$48</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B15" s="33" t="str">
         <f>TEXT(G15,"#,##0.000")&amp;" GB/s"</f>
-        <v>191.989 GB/s</v>
+        <v>0.000 GB/s</v>
       </c>
       <c r="C15" s="33" t="str">
         <f>TEXT(H15,"#,##0.000")&amp;" GB/s"</f>
-        <v>462.703 GB/s</v>
+        <v>0.000 GB/s</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>506</v>
+        <v>457</v>
       </c>
       <c r="G15" s="32">
-        <f>'Prefill_8K'!$AG$15/(PrefillTargetMs/1000)/1E9</f>
-        <v>191.988670976</v>
+        <f>'Prefill_8K'!$AS$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>0.0</v>
       </c>
       <c r="H15" s="32">
-        <f>'Decode_1M'!$AG$15/(DecodeTargetMs/1000)/1E9</f>
-        <v>462.7033672</v>
+        <f>'Decode_1M'!$AS$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B16" s="33" t="str">
-        <f>TEXT(G16,"#,##0.000")&amp;" GB/s"</f>
-        <v>106.744 GB/s</v>
+        <f>TEXT(IF(ABS(G16)&gt;=1E12,G16/1E12,IF(ABS(G16)&gt;=1E9,G16/1E9,IF(ABS(G16)&gt;=1E6,G16/1E6,IF(ABS(G16)&gt;=1E3,G16/1E3,G16)))),"#,##0.000")&amp;IF((IF(ABS(G16)&gt;=1E12,"T",IF(ABS(G16)&gt;=1E9,"G",IF(ABS(G16)&gt;=1E6,"M",IF(ABS(G16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G16)&gt;=1E12,"T",IF(ABS(G16)&gt;=1E9,"G",IF(ABS(G16)&gt;=1E6,"M",IF(ABS(G16)&gt;=1E3,"K",""))))))</f>
+        <v>5.086 G</v>
       </c>
       <c r="C16" s="33" t="str">
-        <f>TEXT(H16,"#,##0.000")&amp;" GB/s"</f>
-        <v>226.865 GB/s</v>
+        <f>TEXT(IF(ABS(H16)&gt;=1E12,H16/1E12,IF(ABS(H16)&gt;=1E9,H16/1E9,IF(ABS(H16)&gt;=1E6,H16/1E6,IF(ABS(H16)&gt;=1E3,H16/1E3,H16)))),"#,##0.000")&amp;IF((IF(ABS(H16)&gt;=1E12,"T",IF(ABS(H16)&gt;=1E9,"G",IF(ABS(H16)&gt;=1E6,"M",IF(ABS(H16)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H16)&gt;=1E12,"T",IF(ABS(H16)&gt;=1E9,"G",IF(ABS(H16)&gt;=1E6,"M",IF(ABS(H16)&gt;=1E3,"K",""))))))</f>
+        <v>5.086 G</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="G16" s="32">
-        <f>'Prefill_8K'!$AQ$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>106.744396636</v>
+        <f>'Prefill_8K'!$AY$49</f>
+        <v>5086249088.0</v>
       </c>
       <c r="H16" s="32">
-        <f>'Decode_1M'!$AQ$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>226.8650332</v>
+        <f>'Prefill_8K'!$AY$49</f>
+        <v>5086249088.0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="B17" s="33" t="str">
-        <f>TEXT(IF(ABS(G17)&gt;=1E15,G17/1E15,IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E15,"PFLOPs",IF(ABS(G17)&gt;=1E12,"TFLOPs",IF(ABS(G17)&gt;=1E9,"GFLOPs",IF(ABS(G17)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E15,"PFLOPs",IF(ABS(G17)&gt;=1E12,"TFLOPs",IF(ABS(G17)&gt;=1E9,"GFLOPs",IF(ABS(G17)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>228.398 TFLOPs</v>
+        <f>TEXT(IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,IF(ABS(G17)&gt;=1E3,G17/1E3,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E12,"T",IF(ABS(G17)&gt;=1E9,"G",IF(ABS(G17)&gt;=1E6,"M",IF(ABS(G17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E12,"T",IF(ABS(G17)&gt;=1E9,"G",IF(ABS(G17)&gt;=1E6,"M",IF(ABS(G17)&gt;=1E3,"K",""))))))</f>
+        <v>278.155 G</v>
       </c>
       <c r="C17" s="33" t="str">
-        <f>TEXT(IF(ABS(H17)&gt;=1E15,H17/1E15,IF(ABS(H17)&gt;=1E12,H17/1E12,IF(ABS(H17)&gt;=1E9,H17/1E9,IF(ABS(H17)&gt;=1E6,H17/1E6,H17)))),"#,##0.000")&amp;IF((IF(ABS(H17)&gt;=1E15,"PFLOPs",IF(ABS(H17)&gt;=1E12,"TFLOPs",IF(ABS(H17)&gt;=1E9,"GFLOPs",IF(ABS(H17)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H17)&gt;=1E15,"PFLOPs",IF(ABS(H17)&gt;=1E12,"TFLOPs",IF(ABS(H17)&gt;=1E9,"GFLOPs",IF(ABS(H17)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>140.356 GFLOPs</v>
+        <f>TEXT(IF(ABS(H17)&gt;=1E12,H17/1E12,IF(ABS(H17)&gt;=1E9,H17/1E9,IF(ABS(H17)&gt;=1E6,H17/1E6,IF(ABS(H17)&gt;=1E3,H17/1E3,H17)))),"#,##0.000")&amp;IF((IF(ABS(H17)&gt;=1E12,"T",IF(ABS(H17)&gt;=1E9,"G",IF(ABS(H17)&gt;=1E6,"M",IF(ABS(H17)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H17)&gt;=1E12,"T",IF(ABS(H17)&gt;=1E9,"G",IF(ABS(H17)&gt;=1E6,"M",IF(ABS(H17)&gt;=1E3,"K",""))))))</f>
+        <v>278.155 G</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>507</v>
+        <v>461</v>
       </c>
       <c r="G17" s="32">
-        <f>'Prefill_8K'!$AF$13</f>
-        <v>228397682114560.0</v>
+        <f>'Prefill_8K'!$AY$50</f>
+        <v>278154947072.0</v>
       </c>
       <c r="H17" s="32">
-        <f>'Decode_1M'!$AF$13</f>
-        <v>140355752110.0</v>
+        <f>'Prefill_8K'!$AY$50</f>
+        <v>278154947072.0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B18" s="33" t="str">
-        <f>TEXT(IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18)))),"#,##0.000")&amp;IF((IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>0.000 B</v>
+        <f>TEXT(IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18)))),"#,##0.000")&amp;IF((IF(ABS(G18)&gt;=1E12,"T",IF(ABS(G18)&gt;=1E9,"G",IF(ABS(G18)&gt;=1E6,"M",IF(ABS(G18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G18)&gt;=1E12,"T",IF(ABS(G18)&gt;=1E9,"G",IF(ABS(G18)&gt;=1E6,"M",IF(ABS(G18)&gt;=1E3,"K",""))))))</f>
+        <v>1.093 G</v>
       </c>
       <c r="C18" s="33" t="str">
-        <f>TEXT(IF(ABS(H18)&gt;=1E12,H18/1E12,IF(ABS(H18)&gt;=1E9,H18/1E9,IF(ABS(H18)&gt;=1E6,H18/1E6,IF(ABS(H18)&gt;=1E3,H18/1E3,H18)))),"#,##0.000")&amp;IF((IF(ABS(H18)&gt;=1E12,"TB",IF(ABS(H18)&gt;=1E9,"GB",IF(ABS(H18)&gt;=1E6,"MB",IF(ABS(H18)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H18)&gt;=1E12,"TB",IF(ABS(H18)&gt;=1E9,"GB",IF(ABS(H18)&gt;=1E6,"MB",IF(ABS(H18)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>0.000 B</v>
+        <f>TEXT(IF(ABS(H18)&gt;=1E12,H18/1E12,IF(ABS(H18)&gt;=1E9,H18/1E9,IF(ABS(H18)&gt;=1E6,H18/1E6,IF(ABS(H18)&gt;=1E3,H18/1E3,H18)))),"#,##0.000")&amp;IF((IF(ABS(H18)&gt;=1E12,"T",IF(ABS(H18)&gt;=1E9,"G",IF(ABS(H18)&gt;=1E6,"M",IF(ABS(H18)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H18)&gt;=1E12,"T",IF(ABS(H18)&gt;=1E9,"G",IF(ABS(H18)&gt;=1E6,"M",IF(ABS(H18)&gt;=1E3,"K",""))))))</f>
+        <v>1.093 G</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G18" s="32">
-        <f>'Prefill_8K'!$AS$48</f>
-        <v>0.0</v>
+        <f>'Prefill_8K'!$AY$51</f>
+        <v>1093371351.0</v>
       </c>
       <c r="H18" s="32">
-        <f>'Decode_1M'!$AS$48</f>
-        <v>0.0</v>
+        <f>'Prefill_8K'!$AY$51</f>
+        <v>1093371351.0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="B19" s="33" t="str">
-        <f>TEXT(G19,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.000 GB/s</v>
-      </c>
-      <c r="C19" s="33" t="str">
-        <f>TEXT(H19,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.000 GB/s</v>
+      <c r="A19" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B19" s="31" t="str">
+        <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"T",IF(ABS(G19)&gt;=1E9,"G",IF(ABS(G19)&gt;=1E6,"M",IF(ABS(G19)&gt;=1E3,"K",""))))))</f>
+        <v>284.335 G</v>
+      </c>
+      <c r="C19" s="31" t="str">
+        <f>TEXT(IF(ABS(H19)&gt;=1E12,H19/1E12,IF(ABS(H19)&gt;=1E9,H19/1E9,IF(ABS(H19)&gt;=1E6,H19/1E6,IF(ABS(H19)&gt;=1E3,H19/1E3,H19)))),"#,##0.000")&amp;IF((IF(ABS(H19)&gt;=1E12,"T",IF(ABS(H19)&gt;=1E9,"G",IF(ABS(H19)&gt;=1E6,"M",IF(ABS(H19)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H19)&gt;=1E12,"T",IF(ABS(H19)&gt;=1E9,"G",IF(ABS(H19)&gt;=1E6,"M",IF(ABS(H19)&gt;=1E3,"K",""))))))</f>
+        <v>284.335 G</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="G19" s="32">
-        <f>'Prefill_8K'!$AS$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>0.0</v>
+        <f>'Prefill_8K'!$AY$52</f>
+        <v>284334567511.0</v>
       </c>
       <c r="H19" s="32">
-        <f>'Decode_1M'!$AS$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.0</v>
+        <f>'Prefill_8K'!$AY$52</f>
+        <v>284334567511.0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B20" s="33" t="str">
-        <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"T",IF(ABS(G20)&gt;=1E9,"G",IF(ABS(G20)&gt;=1E6,"M",IF(ABS(G20)&gt;=1E3,"K",""))))))</f>
-        <v>5.086 G</v>
+        <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.451 GB</v>
       </c>
       <c r="C20" s="33" t="str">
-        <f>TEXT(IF(ABS(H20)&gt;=1E12,H20/1E12,IF(ABS(H20)&gt;=1E9,H20/1E9,IF(ABS(H20)&gt;=1E6,H20/1E6,IF(ABS(H20)&gt;=1E3,H20/1E3,H20)))),"#,##0.000")&amp;IF((IF(ABS(H20)&gt;=1E12,"T",IF(ABS(H20)&gt;=1E9,"G",IF(ABS(H20)&gt;=1E6,"M",IF(ABS(H20)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H20)&gt;=1E12,"T",IF(ABS(H20)&gt;=1E9,"G",IF(ABS(H20)&gt;=1E6,"M",IF(ABS(H20)&gt;=1E3,"K",""))))))</f>
-        <v>5.086 G</v>
+        <f>TEXT(IF(ABS(H20)&gt;=1E12,H20/1E12,IF(ABS(H20)&gt;=1E9,H20/1E9,IF(ABS(H20)&gt;=1E6,H20/1E6,IF(ABS(H20)&gt;=1E3,H20/1E3,H20)))),"#,##0.000")&amp;IF((IF(ABS(H20)&gt;=1E12,"TB",IF(ABS(H20)&gt;=1E9,"GB",IF(ABS(H20)&gt;=1E6,"MB",IF(ABS(H20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H20)&gt;=1E12,"TB",IF(ABS(H20)&gt;=1E9,"GB",IF(ABS(H20)&gt;=1E6,"MB",IF(ABS(H20)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.451 GB</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="G20" s="32">
-        <f>'Prefill_8K'!$AY$49</f>
-        <v>5086249088.0</v>
+        <f>'Prefill_8K'!$BA$49</f>
+        <v>7451384960</v>
       </c>
       <c r="H20" s="32">
-        <f>'Prefill_8K'!$AY$49</f>
-        <v>5086249088.0</v>
+        <f>'Prefill_8K'!$BA$49</f>
+        <v>7451384960</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B21" s="33" t="str">
-        <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"T",IF(ABS(G21)&gt;=1E9,"G",IF(ABS(G21)&gt;=1E6,"M",IF(ABS(G21)&gt;=1E3,"K",""))))))</f>
-        <v>278.155 G</v>
+        <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>148.351 GB</v>
       </c>
       <c r="C21" s="33" t="str">
-        <f>TEXT(IF(ABS(H21)&gt;=1E12,H21/1E12,IF(ABS(H21)&gt;=1E9,H21/1E9,IF(ABS(H21)&gt;=1E6,H21/1E6,IF(ABS(H21)&gt;=1E3,H21/1E3,H21)))),"#,##0.000")&amp;IF((IF(ABS(H21)&gt;=1E12,"T",IF(ABS(H21)&gt;=1E9,"G",IF(ABS(H21)&gt;=1E6,"M",IF(ABS(H21)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H21)&gt;=1E12,"T",IF(ABS(H21)&gt;=1E9,"G",IF(ABS(H21)&gt;=1E6,"M",IF(ABS(H21)&gt;=1E3,"K",""))))))</f>
-        <v>278.155 G</v>
+        <f>TEXT(IF(ABS(H21)&gt;=1E12,H21/1E12,IF(ABS(H21)&gt;=1E9,H21/1E9,IF(ABS(H21)&gt;=1E6,H21/1E6,IF(ABS(H21)&gt;=1E3,H21/1E3,H21)))),"#,##0.000")&amp;IF((IF(ABS(H21)&gt;=1E12,"TB",IF(ABS(H21)&gt;=1E9,"GB",IF(ABS(H21)&gt;=1E6,"MB",IF(ABS(H21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H21)&gt;=1E12,"TB",IF(ABS(H21)&gt;=1E9,"GB",IF(ABS(H21)&gt;=1E6,"MB",IF(ABS(H21)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>148.351 GB</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="G21" s="32">
-        <f>'Prefill_8K'!$AY$50</f>
-        <v>278154947072.0</v>
+        <f>'Prefill_8K'!$BA$50</f>
+        <v>148351461888.0</v>
       </c>
       <c r="H21" s="32">
-        <f>'Prefill_8K'!$AY$50</f>
-        <v>278154947072.0</v>
+        <f>'Prefill_8K'!$BA$50</f>
+        <v>148351461888.0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B22" s="33" t="str">
-        <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"T",IF(ABS(G22)&gt;=1E9,"G",IF(ABS(G22)&gt;=1E6,"M",IF(ABS(G22)&gt;=1E3,"K",""))))))</f>
-        <v>1.093 G</v>
+        <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>3.314 GB</v>
       </c>
       <c r="C22" s="33" t="str">
-        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"T",IF(ABS(H22)&gt;=1E9,"G",IF(ABS(H22)&gt;=1E6,"M",IF(ABS(H22)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"T",IF(ABS(H22)&gt;=1E9,"G",IF(ABS(H22)&gt;=1E6,"M",IF(ABS(H22)&gt;=1E3,"K",""))))))</f>
-        <v>1.093 G</v>
+        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>3.314 GB</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="G22" s="32">
-        <f>'Prefill_8K'!$AY$51</f>
-        <v>1093371351.0</v>
+        <f>'Prefill_8K'!$BA$51</f>
+        <v>3314423644.0</v>
       </c>
       <c r="H22" s="32">
-        <f>'Prefill_8K'!$AY$51</f>
-        <v>1093371351.0</v>
+        <f>'Prefill_8K'!$BA$51</f>
+        <v>3314423644.0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B23" s="31" t="str">
-        <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"T",IF(ABS(G23)&gt;=1E9,"G",IF(ABS(G23)&gt;=1E6,"M",IF(ABS(G23)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"T",IF(ABS(G23)&gt;=1E9,"G",IF(ABS(G23)&gt;=1E6,"M",IF(ABS(G23)&gt;=1E3,"K",""))))))</f>
-        <v>284.335 G</v>
+        <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>159.117 GB</v>
       </c>
       <c r="C23" s="31" t="str">
-        <f>TEXT(IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,IF(ABS(H23)&gt;=1E3,H23/1E3,H23)))),"#,##0.000")&amp;IF((IF(ABS(H23)&gt;=1E12,"T",IF(ABS(H23)&gt;=1E9,"G",IF(ABS(H23)&gt;=1E6,"M",IF(ABS(H23)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H23)&gt;=1E12,"T",IF(ABS(H23)&gt;=1E9,"G",IF(ABS(H23)&gt;=1E6,"M",IF(ABS(H23)&gt;=1E3,"K",""))))))</f>
-        <v>284.335 G</v>
+        <f>TEXT(IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,IF(ABS(H23)&gt;=1E3,H23/1E3,H23)))),"#,##0.000")&amp;IF((IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>159.117 GB</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="G23" s="32">
-        <f>'Prefill_8K'!$AY$52</f>
-        <v>284334567511.0</v>
+        <f>'Prefill_8K'!$BA$52</f>
+        <v>159117270492.0</v>
       </c>
       <c r="H23" s="32">
-        <f>'Prefill_8K'!$AY$52</f>
-        <v>284334567511.0</v>
+        <f>'Prefill_8K'!$BA$52</f>
+        <v>159117270492.0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B24" s="33" t="str">
         <f>TEXT(IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.451 GB</v>
+        <v>50.987 MB</v>
       </c>
       <c r="C24" s="33" t="str">
         <f>TEXT(IF(ABS(H24)&gt;=1E12,H24/1E12,IF(ABS(H24)&gt;=1E9,H24/1E9,IF(ABS(H24)&gt;=1E6,H24/1E6,IF(ABS(H24)&gt;=1E3,H24/1E3,H24)))),"#,##0.000")&amp;IF((IF(ABS(H24)&gt;=1E12,"TB",IF(ABS(H24)&gt;=1E9,"GB",IF(ABS(H24)&gt;=1E6,"MB",IF(ABS(H24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H24)&gt;=1E12,"TB",IF(ABS(H24)&gt;=1E9,"GB",IF(ABS(H24)&gt;=1E6,"MB",IF(ABS(H24)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>7.451 GB</v>
+        <v>5.811 GB</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="G24" s="32">
-        <f>'Prefill_8K'!$BA$49</f>
-        <v>7451384960</v>
+        <f>'Prefill_8K'!$U$35</f>
+        <v>50987008</v>
       </c>
       <c r="H24" s="32">
-        <f>'Prefill_8K'!$BA$49</f>
-        <v>7451384960</v>
+        <f>'Decode_1M'!$U$35</f>
+        <v>5810552832</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B25" s="33" t="str">
         <f>TEXT(IF(ABS(G25)&gt;=1E12,G25/1E12,IF(ABS(G25)&gt;=1E9,G25/1E9,IF(ABS(G25)&gt;=1E6,G25/1E6,IF(ABS(G25)&gt;=1E3,G25/1E3,G25)))),"#,##0.000")&amp;IF((IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G25)&gt;=1E12,"TB",IF(ABS(G25)&gt;=1E9,"GB",IF(ABS(G25)&gt;=1E6,"MB",IF(ABS(G25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>148.351 GB</v>
+        <v>11.010 MB</v>
       </c>
       <c r="C25" s="33" t="str">
         <f>TEXT(IF(ABS(H25)&gt;=1E12,H25/1E12,IF(ABS(H25)&gt;=1E9,H25/1E9,IF(ABS(H25)&gt;=1E6,H25/1E6,IF(ABS(H25)&gt;=1E3,H25/1E3,H25)))),"#,##0.000")&amp;IF((IF(ABS(H25)&gt;=1E12,"TB",IF(ABS(H25)&gt;=1E9,"GB",IF(ABS(H25)&gt;=1E6,"MB",IF(ABS(H25)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H25)&gt;=1E12,"TB",IF(ABS(H25)&gt;=1E9,"GB",IF(ABS(H25)&gt;=1E6,"MB",IF(ABS(H25)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>148.351 GB</v>
+        <v>1.409 GB</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G25" s="32">
-        <f>'Prefill_8K'!$BA$50</f>
-        <v>148351461888.0</v>
+        <f>'Prefill_8K'!$U$36</f>
+        <v>11010048</v>
       </c>
       <c r="H25" s="32">
-        <f>'Prefill_8K'!$BA$50</f>
-        <v>148351461888.0</v>
+        <f>'Decode_1M'!$U$36</f>
+        <v>1409286144</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B26" s="33" t="str">
         <f>TEXT(IF(ABS(G26)&gt;=1E12,G26/1E12,IF(ABS(G26)&gt;=1E9,G26/1E9,IF(ABS(G26)&gt;=1E6,G26/1E6,IF(ABS(G26)&gt;=1E3,G26/1E3,G26)))),"#,##0.000")&amp;IF((IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G26)&gt;=1E12,"TB",IF(ABS(G26)&gt;=1E9,"GB",IF(ABS(G26)&gt;=1E6,"MB",IF(ABS(G26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>3.314 GB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="C26" s="33" t="str">
         <f>TEXT(IF(ABS(H26)&gt;=1E12,H26/1E12,IF(ABS(H26)&gt;=1E9,H26/1E9,IF(ABS(H26)&gt;=1E6,H26/1E6,IF(ABS(H26)&gt;=1E3,H26/1E3,H26)))),"#,##0.000")&amp;IF((IF(ABS(H26)&gt;=1E12,"TB",IF(ABS(H26)&gt;=1E9,"GB",IF(ABS(H26)&gt;=1E6,"MB",IF(ABS(H26)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H26)&gt;=1E12,"TB",IF(ABS(H26)&gt;=1E9,"GB",IF(ABS(H26)&gt;=1E6,"MB",IF(ABS(H26)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>3.314 GB</v>
+        <v>12.206 MB</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G26" s="32">
-        <f>'Prefill_8K'!$BA$51</f>
-        <v>3314423644.0</v>
-      </c>
-      <c r="H26" s="32">
-        <f>'Prefill_8K'!$BA$51</f>
-        <v>3314423644.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="B27" s="31" t="str">
-        <f>TEXT(IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27)))),"#,##0.000")&amp;IF((IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>159.117 GB</v>
-      </c>
-      <c r="C27" s="31" t="str">
-        <f>TEXT(IF(ABS(H27)&gt;=1E12,H27/1E12,IF(ABS(H27)&gt;=1E9,H27/1E9,IF(ABS(H27)&gt;=1E6,H27/1E6,IF(ABS(H27)&gt;=1E3,H27/1E3,H27)))),"#,##0.000")&amp;IF((IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>159.117 GB</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="G27" s="32">
-        <f>'Prefill_8K'!$BA$52</f>
-        <v>159117270492.0</v>
-      </c>
-      <c r="H27" s="32">
-        <f>'Prefill_8K'!$BA$52</f>
-        <v>159117270492.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="B28" s="33" t="str">
-        <f>TEXT(IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>50.987 MB</v>
-      </c>
-      <c r="C28" s="33" t="str">
-        <f>TEXT(IF(ABS(H28)&gt;=1E12,H28/1E12,IF(ABS(H28)&gt;=1E9,H28/1E9,IF(ABS(H28)&gt;=1E6,H28/1E6,IF(ABS(H28)&gt;=1E3,H28/1E3,H28)))),"#,##0.000")&amp;IF((IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.811 GB</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G28" s="32">
-        <f>'Prefill_8K'!$U$35</f>
-        <v>50987008</v>
-      </c>
-      <c r="H28" s="32">
-        <f>'Decode_1M'!$U$35</f>
-        <v>5810552832</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="B29" s="33" t="str">
-        <f>TEXT(IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,IF(ABS(G29)&gt;=1E3,G29/1E3,G29)))),"#,##0.000")&amp;IF((IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G29)&gt;=1E12,"TB",IF(ABS(G29)&gt;=1E9,"GB",IF(ABS(G29)&gt;=1E6,"MB",IF(ABS(G29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>11.010 MB</v>
-      </c>
-      <c r="C29" s="33" t="str">
-        <f>TEXT(IF(ABS(H29)&gt;=1E12,H29/1E12,IF(ABS(H29)&gt;=1E9,H29/1E9,IF(ABS(H29)&gt;=1E6,H29/1E6,IF(ABS(H29)&gt;=1E3,H29/1E3,H29)))),"#,##0.000")&amp;IF((IF(ABS(H29)&gt;=1E12,"TB",IF(ABS(H29)&gt;=1E9,"GB",IF(ABS(H29)&gt;=1E6,"MB",IF(ABS(H29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H29)&gt;=1E12,"TB",IF(ABS(H29)&gt;=1E9,"GB",IF(ABS(H29)&gt;=1E6,"MB",IF(ABS(H29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.409 GB</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G29" s="32">
-        <f>'Prefill_8K'!$U$36</f>
-        <v>11010048</v>
-      </c>
-      <c r="H29" s="32">
-        <f>'Decode_1M'!$U$36</f>
-        <v>1409286144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B30" s="33" t="str">
-        <f>TEXT(IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,IF(ABS(G30)&gt;=1E3,G30/1E3,G30)))),"#,##0.000")&amp;IF((IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G30)&gt;=1E12,"TB",IF(ABS(G30)&gt;=1E9,"GB",IF(ABS(G30)&gt;=1E6,"MB",IF(ABS(G30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="C30" s="33" t="str">
-        <f>TEXT(IF(ABS(H30)&gt;=1E12,H30/1E12,IF(ABS(H30)&gt;=1E9,H30/1E9,IF(ABS(H30)&gt;=1E6,H30/1E6,IF(ABS(H30)&gt;=1E3,H30/1E3,H30)))),"#,##0.000")&amp;IF((IF(ABS(H30)&gt;=1E12,"TB",IF(ABS(H30)&gt;=1E9,"GB",IF(ABS(H30)&gt;=1E6,"MB",IF(ABS(H30)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H30)&gt;=1E12,"TB",IF(ABS(H30)&gt;=1E9,"GB",IF(ABS(H30)&gt;=1E6,"MB",IF(ABS(H30)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G30" s="32">
         <f>'Prefill_8K'!$U$37</f>
         <v>12206080</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H26" s="32">
         <f>'Decode_1M'!$U$37</f>
         <v>12206080</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="B31" s="33" t="str">
-        <f>TEXT(IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,IF(ABS(G31)&gt;=1E3,G31/1E3,G31)))),"#,##0.000")&amp;IF((IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G31)&gt;=1E12,"TB",IF(ABS(G31)&gt;=1E9,"GB",IF(ABS(G31)&gt;=1E6,"MB",IF(ABS(G31)&gt;=1E3,"KB","bytes"))))))</f>
+    <row r="27" spans="1:8">
+      <c r="A27" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B27" s="33" t="str">
+        <f>TEXT(IF(ABS(G27)&gt;=1E12,G27/1E12,IF(ABS(G27)&gt;=1E9,G27/1E9,IF(ABS(G27)&gt;=1E6,G27/1E6,IF(ABS(G27)&gt;=1E3,G27/1E3,G27)))),"#,##0.000")&amp;IF((IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G27)&gt;=1E12,"TB",IF(ABS(G27)&gt;=1E9,"GB",IF(ABS(G27)&gt;=1E6,"MB",IF(ABS(G27)&gt;=1E3,"KB","bytes"))))))</f>
         <v>7.232 GB</v>
       </c>
-      <c r="C31" s="33" t="str">
-        <f>TEXT(IF(ABS(H31)&gt;=1E12,H31/1E12,IF(ABS(H31)&gt;=1E9,H31/1E9,IF(ABS(H31)&gt;=1E6,H31/1E6,IF(ABS(H31)&gt;=1E3,H31/1E3,H31)))),"#,##0.000")&amp;IF((IF(ABS(H31)&gt;=1E12,"TB",IF(ABS(H31)&gt;=1E9,"GB",IF(ABS(H31)&gt;=1E6,"MB",IF(ABS(H31)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H31)&gt;=1E12,"TB",IF(ABS(H31)&gt;=1E9,"GB",IF(ABS(H31)&gt;=1E6,"MB",IF(ABS(H31)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="C27" s="33" t="str">
+        <f>TEXT(IF(ABS(H27)&gt;=1E12,H27/1E12,IF(ABS(H27)&gt;=1E9,H27/1E9,IF(ABS(H27)&gt;=1E6,H27/1E6,IF(ABS(H27)&gt;=1E3,H27/1E3,H27)))),"#,##0.000")&amp;IF((IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H27)&gt;=1E12,"TB",IF(ABS(H27)&gt;=1E9,"GB",IF(ABS(H27)&gt;=1E6,"MB",IF(ABS(H27)&gt;=1E3,"KB","bytes"))))))</f>
         <v>7.232 GB</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G31" s="32">
+      <c r="D27" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="G27" s="32">
         <f>'Prefill_8K'!$U$38</f>
         <v>7232045056</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H27" s="32">
         <f>'Decode_1M'!$U$38</f>
         <v>7232045056</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="31" t="s">
-        <v>483</v>
-      </c>
-      <c r="B32" s="31" t="str">
-        <f>TEXT(IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,IF(ABS(G32)&gt;=1E3,G32/1E3,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E12,"TB",IF(ABS(G32)&gt;=1E9,"GB",IF(ABS(G32)&gt;=1E6,"MB",IF(ABS(G32)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E12,"TB",IF(ABS(G32)&gt;=1E9,"GB",IF(ABS(G32)&gt;=1E6,"MB",IF(ABS(G32)&gt;=1E3,"KB","bytes"))))))</f>
+    <row r="28" spans="1:8">
+      <c r="A28" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B28" s="31" t="str">
+        <f>TEXT(IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,IF(ABS(G28)&gt;=1E3,G28/1E3,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E12,"TB",IF(ABS(G28)&gt;=1E9,"GB",IF(ABS(G28)&gt;=1E6,"MB",IF(ABS(G28)&gt;=1E3,"KB","bytes"))))))</f>
         <v>166.349 GB</v>
       </c>
-      <c r="C32" s="31" t="str">
-        <f>TEXT(IF(ABS(H32)&gt;=1E12,H32/1E12,IF(ABS(H32)&gt;=1E9,H32/1E9,IF(ABS(H32)&gt;=1E6,H32/1E6,IF(ABS(H32)&gt;=1E3,H32/1E3,H32)))),"#,##0.000")&amp;IF((IF(ABS(H32)&gt;=1E12,"TB",IF(ABS(H32)&gt;=1E9,"GB",IF(ABS(H32)&gt;=1E6,"MB",IF(ABS(H32)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H32)&gt;=1E12,"TB",IF(ABS(H32)&gt;=1E9,"GB",IF(ABS(H32)&gt;=1E6,"MB",IF(ABS(H32)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="C28" s="31" t="str">
+        <f>TEXT(IF(ABS(H28)&gt;=1E12,H28/1E12,IF(ABS(H28)&gt;=1E9,H28/1E9,IF(ABS(H28)&gt;=1E6,H28/1E6,IF(ABS(H28)&gt;=1E3,H28/1E3,H28)))),"#,##0.000")&amp;IF((IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H28)&gt;=1E12,"TB",IF(ABS(H28)&gt;=1E9,"GB",IF(ABS(H28)&gt;=1E6,"MB",IF(ABS(H28)&gt;=1E3,"KB","bytes"))))))</f>
         <v>166.349 GB</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="G32" s="32">
+      <c r="D28" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="G28" s="32">
         <f>'Prefill_8K'!$BA$52+'Prefill_8K'!$U$38</f>
         <v>166349315548.0</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H28" s="32">
         <f>'Prefill_8K'!$BA$52+'Decode_1M'!$U$38</f>
         <v>166349315548.0</v>
       </c>
     </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B32" s="33" t="str">
+        <f>TEXT(IF(ABS(G32)&gt;=1E15,G32/1E15,IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>23.172 TFLOPs</v>
+      </c>
+      <c r="C32" s="33" t="str">
+        <f>TEXT(IF(ABS(H32)&gt;=1E15,H32/1E15,IF(ABS(H32)&gt;=1E12,H32/1E12,IF(ABS(H32)&gt;=1E9,H32/1E9,IF(ABS(H32)&gt;=1E6,H32/1E6,H32)))),"#,##0.000")&amp;IF((IF(ABS(H32)&gt;=1E15,"PFLOPs",IF(ABS(H32)&gt;=1E12,"TFLOPs",IF(ABS(H32)&gt;=1E9,"GFLOPs",IF(ABS(H32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H32)&gt;=1E15,"PFLOPs",IF(ABS(H32)&gt;=1E12,"TFLOPs",IF(ABS(H32)&gt;=1E9,"GFLOPs",IF(ABS(H32)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>19.452 GFLOPs</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G32" s="32">
+        <f>'Prefill_8K'!$AI$14</f>
+        <v>23172382457856.0</v>
+      </c>
+      <c r="H32" s="32">
+        <f>'Decode_1M'!$AI$14</f>
+        <v>19452461056.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" s="33" t="str">
+        <f>TEXT(IF(ABS(G33)&gt;=1E15,G33/1E15,IF(ABS(G33)&gt;=1E12,G33/1E12,IF(ABS(G33)&gt;=1E9,G33/1E9,IF(ABS(G33)&gt;=1E6,G33/1E6,G33)))),"#,##0.000")&amp;IF((IF(ABS(G33)&gt;=1E15,"PFLOPs",IF(ABS(G33)&gt;=1E12,"TFLOPs",IF(ABS(G33)&gt;=1E9,"GFLOPs",IF(ABS(G33)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G33)&gt;=1E15,"PFLOPs",IF(ABS(G33)&gt;=1E12,"TFLOPs",IF(ABS(G33)&gt;=1E9,"GFLOPs",IF(ABS(G33)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>31.766 TFLOPs</v>
+      </c>
+      <c r="C33" s="33" t="str">
+        <f>TEXT(IF(ABS(H33)&gt;=1E15,H33/1E15,IF(ABS(H33)&gt;=1E12,H33/1E12,IF(ABS(H33)&gt;=1E9,H33/1E9,IF(ABS(H33)&gt;=1E6,H33/1E6,H33)))),"#,##0.000")&amp;IF((IF(ABS(H33)&gt;=1E15,"PFLOPs",IF(ABS(H33)&gt;=1E12,"TFLOPs",IF(ABS(H33)&gt;=1E9,"GFLOPs",IF(ABS(H33)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H33)&gt;=1E15,"PFLOPs",IF(ABS(H33)&gt;=1E12,"TFLOPs",IF(ABS(H33)&gt;=1E9,"GFLOPs",IF(ABS(H33)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>3.878 GFLOPs</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G33" s="32">
+        <f>'Prefill_8K'!$AI$15</f>
+        <v>31765578121216.0</v>
+      </c>
+      <c r="H33" s="32">
+        <f>'Decode_1M'!$AI$15</f>
+        <v>3877634048.0</v>
+      </c>
+    </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
+      <c r="A34" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B34" s="33" t="str">
+        <f>TEXT(IF(ABS(G34)&gt;=1E15,G34/1E15,IF(ABS(G34)&gt;=1E12,G34/1E12,IF(ABS(G34)&gt;=1E9,G34/1E9,IF(ABS(G34)&gt;=1E6,G34/1E6,G34)))),"#,##0.000")&amp;IF((IF(ABS(G34)&gt;=1E15,"PFLOPs",IF(ABS(G34)&gt;=1E12,"TFLOPs",IF(ABS(G34)&gt;=1E9,"GFLOPs",IF(ABS(G34)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G34)&gt;=1E15,"PFLOPs",IF(ABS(G34)&gt;=1E12,"TFLOPs",IF(ABS(G34)&gt;=1E9,"GFLOPs",IF(ABS(G34)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>714.608 GFLOPs</v>
+      </c>
+      <c r="C34" s="33" t="str">
+        <f>TEXT(IF(ABS(H34)&gt;=1E15,H34/1E15,IF(ABS(H34)&gt;=1E12,H34/1E12,IF(ABS(H34)&gt;=1E9,H34/1E9,IF(ABS(H34)&gt;=1E6,H34/1E6,H34)))),"#,##0.000")&amp;IF((IF(ABS(H34)&gt;=1E15,"PFLOPs",IF(ABS(H34)&gt;=1E12,"TFLOPs",IF(ABS(H34)&gt;=1E9,"GFLOPs",IF(ABS(H34)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H34)&gt;=1E15,"PFLOPs",IF(ABS(H34)&gt;=1E12,"TFLOPs",IF(ABS(H34)&gt;=1E9,"GFLOPs",IF(ABS(H34)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>219.599 MFLOPs</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G34" s="32">
+        <f>'Prefill_8K'!$AP$48</f>
+        <v>714608328704.0</v>
+      </c>
+      <c r="H34" s="32">
+        <f>'Decode_1M'!$AP$48</f>
+        <v>219599022.0</v>
+      </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>363</v>
+      <c r="A35" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="B35" s="31" t="str">
+        <f>TEXT(IF(ABS(G35)&gt;=1E15,G35/1E15,IF(ABS(G35)&gt;=1E12,G35/1E12,IF(ABS(G35)&gt;=1E9,G35/1E9,IF(ABS(G35)&gt;=1E6,G35/1E6,G35)))),"#,##0.000")&amp;IF((IF(ABS(G35)&gt;=1E15,"PFLOPs",IF(ABS(G35)&gt;=1E12,"TFLOPs",IF(ABS(G35)&gt;=1E9,"GFLOPs",IF(ABS(G35)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G35)&gt;=1E15,"PFLOPs",IF(ABS(G35)&gt;=1E12,"TFLOPs",IF(ABS(G35)&gt;=1E9,"GFLOPs",IF(ABS(G35)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>55.653 TFLOPs</v>
+      </c>
+      <c r="C35" s="31" t="str">
+        <f>TEXT(IF(ABS(H35)&gt;=1E15,H35/1E15,IF(ABS(H35)&gt;=1E12,H35/1E12,IF(ABS(H35)&gt;=1E9,H35/1E9,IF(ABS(H35)&gt;=1E6,H35/1E6,H35)))),"#,##0.000")&amp;IF((IF(ABS(H35)&gt;=1E15,"PFLOPs",IF(ABS(H35)&gt;=1E12,"TFLOPs",IF(ABS(H35)&gt;=1E9,"GFLOPs",IF(ABS(H35)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H35)&gt;=1E15,"PFLOPs",IF(ABS(H35)&gt;=1E12,"TFLOPs",IF(ABS(H35)&gt;=1E9,"GFLOPs",IF(ABS(H35)&gt;=1E6,"MFLOPs","flops"))))))</f>
+        <v>23.550 GFLOPs</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G35" s="32">
+        <f>'Prefill_8K'!$AI$13</f>
+        <v>55652568907776.0</v>
+      </c>
+      <c r="H35" s="32">
+        <f>'Decode_1M'!$AI$13</f>
+        <v>23549694126.0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B36" s="33" t="str">
-        <f>TEXT(IF(ABS(G36)&gt;=1E15,G36/1E15,IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,G36)))),"#,##0.000")&amp;IF((IF(ABS(G36)&gt;=1E15,"PFLOPs",IF(ABS(G36)&gt;=1E12,"TFLOPs",IF(ABS(G36)&gt;=1E9,"GFLOPs",IF(ABS(G36)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G36)&gt;=1E15,"PFLOPs",IF(ABS(G36)&gt;=1E12,"TFLOPs",IF(ABS(G36)&gt;=1E9,"GFLOPs",IF(ABS(G36)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>23.172 TFLOPs</v>
+        <f>TEXT(G36,"#,##0.000")&amp;" GB/s"</f>
+        <v>231.532 GB/s</v>
       </c>
       <c r="C36" s="33" t="str">
-        <f>TEXT(IF(ABS(H36)&gt;=1E15,H36/1E15,IF(ABS(H36)&gt;=1E12,H36/1E12,IF(ABS(H36)&gt;=1E9,H36/1E9,IF(ABS(H36)&gt;=1E6,H36/1E6,H36)))),"#,##0.000")&amp;IF((IF(ABS(H36)&gt;=1E15,"PFLOPs",IF(ABS(H36)&gt;=1E12,"TFLOPs",IF(ABS(H36)&gt;=1E9,"GFLOPs",IF(ABS(H36)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H36)&gt;=1E15,"PFLOPs",IF(ABS(H36)&gt;=1E12,"TFLOPs",IF(ABS(H36)&gt;=1E9,"GFLOPs",IF(ABS(H36)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>19.452 GFLOPs</v>
+        <f>TEXT(H36,"#,##0.000")&amp;" GB/s"</f>
+        <v>403.523 GB/s</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G36" s="32">
-        <f>'Prefill_8K'!$AI$14</f>
-        <v>23172382457856.0</v>
+        <f>'Prefill_8K'!$AJ$14/(PrefillTargetMs/1000)/1E9</f>
+        <v>231.531806144</v>
       </c>
       <c r="H36" s="32">
-        <f>'Decode_1M'!$AI$14</f>
-        <v>19452461056.0</v>
+        <f>'Decode_1M'!$AJ$14/(DecodeTargetMs/1000)/1E9</f>
+        <v>403.5232528</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B37" s="33" t="str">
-        <f>TEXT(IF(ABS(G37)&gt;=1E15,G37/1E15,IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,G37)))),"#,##0.000")&amp;IF((IF(ABS(G37)&gt;=1E15,"PFLOPs",IF(ABS(G37)&gt;=1E12,"TFLOPs",IF(ABS(G37)&gt;=1E9,"GFLOPs",IF(ABS(G37)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G37)&gt;=1E15,"PFLOPs",IF(ABS(G37)&gt;=1E12,"TFLOPs",IF(ABS(G37)&gt;=1E9,"GFLOPs",IF(ABS(G37)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>31.766 TFLOPs</v>
+        <f>TEXT(G37,"#,##0.000")&amp;" GB/s"</f>
+        <v>32.915 GB/s</v>
       </c>
       <c r="C37" s="33" t="str">
-        <f>TEXT(IF(ABS(H37)&gt;=1E15,H37/1E15,IF(ABS(H37)&gt;=1E12,H37/1E12,IF(ABS(H37)&gt;=1E9,H37/1E9,IF(ABS(H37)&gt;=1E6,H37/1E6,H37)))),"#,##0.000")&amp;IF((IF(ABS(H37)&gt;=1E15,"PFLOPs",IF(ABS(H37)&gt;=1E12,"TFLOPs",IF(ABS(H37)&gt;=1E9,"GFLOPs",IF(ABS(H37)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H37)&gt;=1E15,"PFLOPs",IF(ABS(H37)&gt;=1E12,"TFLOPs",IF(ABS(H37)&gt;=1E9,"GFLOPs",IF(ABS(H37)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>3.878 GFLOPs</v>
+        <f>TEXT(H37,"#,##0.000")&amp;" GB/s"</f>
+        <v>160.521 GB/s</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G37" s="32">
-        <f>'Prefill_8K'!$AI$15</f>
-        <v>31765578121216.0</v>
+        <f>'Prefill_8K'!$AJ$15/(PrefillTargetMs/1000)/1E9</f>
+        <v>32.915497472</v>
       </c>
       <c r="H37" s="32">
-        <f>'Decode_1M'!$AI$15</f>
-        <v>3877634048.0</v>
+        <f>'Decode_1M'!$AJ$15/(DecodeTargetMs/1000)/1E9</f>
+        <v>160.5205576</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B38" s="33" t="str">
-        <f>TEXT(IF(ABS(G38)&gt;=1E15,G38/1E15,IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,G38)))),"#,##0.000")&amp;IF((IF(ABS(G38)&gt;=1E15,"PFLOPs",IF(ABS(G38)&gt;=1E12,"TFLOPs",IF(ABS(G38)&gt;=1E9,"GFLOPs",IF(ABS(G38)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G38)&gt;=1E15,"PFLOPs",IF(ABS(G38)&gt;=1E12,"TFLOPs",IF(ABS(G38)&gt;=1E9,"GFLOPs",IF(ABS(G38)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>714.608 GFLOPs</v>
+        <f>TEXT(G38,"#,##0.000")&amp;" GB/s"</f>
+        <v>104.891 GB/s</v>
       </c>
       <c r="C38" s="33" t="str">
-        <f>TEXT(IF(ABS(H38)&gt;=1E15,H38/1E15,IF(ABS(H38)&gt;=1E12,H38/1E12,IF(ABS(H38)&gt;=1E9,H38/1E9,IF(ABS(H38)&gt;=1E6,H38/1E6,H38)))),"#,##0.000")&amp;IF((IF(ABS(H38)&gt;=1E15,"PFLOPs",IF(ABS(H38)&gt;=1E12,"TFLOPs",IF(ABS(H38)&gt;=1E9,"GFLOPs",IF(ABS(H38)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H38)&gt;=1E15,"PFLOPs",IF(ABS(H38)&gt;=1E12,"TFLOPs",IF(ABS(H38)&gt;=1E9,"GFLOPs",IF(ABS(H38)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>219.599 MFLOPs</v>
+        <f>TEXT(H38,"#,##0.000")&amp;" GB/s"</f>
+        <v>41.483 GB/s</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G38" s="32">
-        <f>'Prefill_8K'!$AP$48</f>
-        <v>714608328704.0</v>
+        <f>'Prefill_8K'!$AR$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>104.890576444</v>
       </c>
       <c r="H38" s="32">
-        <f>'Decode_1M'!$AP$48</f>
-        <v>219599022.0</v>
+        <f>'Decode_1M'!$AR$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>41.483014</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="B39" s="31" t="str">
+      <c r="A39" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B39" s="33" t="str">
         <f>TEXT(IF(ABS(G39)&gt;=1E15,G39/1E15,IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,G39)))),"#,##0.000")&amp;IF((IF(ABS(G39)&gt;=1E15,"PFLOPs",IF(ABS(G39)&gt;=1E12,"TFLOPs",IF(ABS(G39)&gt;=1E9,"GFLOPs",IF(ABS(G39)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G39)&gt;=1E15,"PFLOPs",IF(ABS(G39)&gt;=1E12,"TFLOPs",IF(ABS(G39)&gt;=1E9,"GFLOPs",IF(ABS(G39)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>55.653 TFLOPs</v>
       </c>
-      <c r="C39" s="31" t="str">
+      <c r="C39" s="33" t="str">
         <f>TEXT(IF(ABS(H39)&gt;=1E15,H39/1E15,IF(ABS(H39)&gt;=1E12,H39/1E12,IF(ABS(H39)&gt;=1E9,H39/1E9,IF(ABS(H39)&gt;=1E6,H39/1E6,H39)))),"#,##0.000")&amp;IF((IF(ABS(H39)&gt;=1E15,"PFLOPs",IF(ABS(H39)&gt;=1E12,"TFLOPs",IF(ABS(H39)&gt;=1E9,"GFLOPs",IF(ABS(H39)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H39)&gt;=1E15,"PFLOPs",IF(ABS(H39)&gt;=1E12,"TFLOPs",IF(ABS(H39)&gt;=1E9,"GFLOPs",IF(ABS(H39)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>23.550 GFLOPs</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="G39" s="32">
         <f>'Prefill_8K'!$AI$13</f>
@@ -14159,552 +13457,360 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B40" s="33" t="str">
         <f>TEXT(IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40)))),"#,##0.000")&amp;IF((IF(ABS(G40)&gt;=1E12,"TB",IF(ABS(G40)&gt;=1E9,"GB",IF(ABS(G40)&gt;=1E6,"MB",IF(ABS(G40)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G40)&gt;=1E12,"TB",IF(ABS(G40)&gt;=1E9,"GB",IF(ABS(G40)&gt;=1E6,"MB",IF(ABS(G40)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>231.532 GB</v>
+        <v>40.635 GB</v>
       </c>
       <c r="C40" s="33" t="str">
         <f>TEXT(IF(ABS(H40)&gt;=1E12,H40/1E12,IF(ABS(H40)&gt;=1E9,H40/1E9,IF(ABS(H40)&gt;=1E6,H40/1E6,IF(ABS(H40)&gt;=1E3,H40/1E3,H40)))),"#,##0.000")&amp;IF((IF(ABS(H40)&gt;=1E12,"TB",IF(ABS(H40)&gt;=1E9,"GB",IF(ABS(H40)&gt;=1E6,"MB",IF(ABS(H40)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H40)&gt;=1E12,"TB",IF(ABS(H40)&gt;=1E9,"GB",IF(ABS(H40)&gt;=1E6,"MB",IF(ABS(H40)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>4.035 GB</v>
+        <v>5.865 MB</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="G40" s="32">
-        <f>'Prefill_8K'!$AJ$14</f>
-        <v>231531806144.0</v>
+        <f>'Prefill_8K'!$AT$48</f>
+        <v>40635322112.0</v>
       </c>
       <c r="H40" s="32">
-        <f>'Decode_1M'!$AJ$14</f>
-        <v>4035232528.0</v>
+        <f>'Decode_1M'!$AT$48</f>
+        <v>5865216.0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B41" s="33" t="str">
-        <f>TEXT(IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41)))),"#,##0.000")&amp;IF((IF(ABS(G41)&gt;=1E12,"TB",IF(ABS(G41)&gt;=1E9,"GB",IF(ABS(G41)&gt;=1E6,"MB",IF(ABS(G41)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G41)&gt;=1E12,"TB",IF(ABS(G41)&gt;=1E9,"GB",IF(ABS(G41)&gt;=1E6,"MB",IF(ABS(G41)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>32.915 GB</v>
+        <f>TEXT(G41,"#,##0.000")&amp;" GB/s"</f>
+        <v>40.635 GB/s</v>
       </c>
       <c r="C41" s="33" t="str">
-        <f>TEXT(IF(ABS(H41)&gt;=1E12,H41/1E12,IF(ABS(H41)&gt;=1E9,H41/1E9,IF(ABS(H41)&gt;=1E6,H41/1E6,IF(ABS(H41)&gt;=1E3,H41/1E3,H41)))),"#,##0.000")&amp;IF((IF(ABS(H41)&gt;=1E12,"TB",IF(ABS(H41)&gt;=1E9,"GB",IF(ABS(H41)&gt;=1E6,"MB",IF(ABS(H41)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H41)&gt;=1E12,"TB",IF(ABS(H41)&gt;=1E9,"GB",IF(ABS(H41)&gt;=1E6,"MB",IF(ABS(H41)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.605 GB</v>
+        <f>TEXT(H41,"#,##0.000")&amp;" GB/s"</f>
+        <v>0.587 GB/s</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>505</v>
+        <v>457</v>
       </c>
       <c r="G41" s="32">
-        <f>'Prefill_8K'!$AJ$15</f>
-        <v>32915497472.0</v>
+        <f>'Prefill_8K'!$AT$48/(PrefillTargetMs/1000)/1E9</f>
+        <v>40.635322112</v>
       </c>
       <c r="H41" s="32">
-        <f>'Decode_1M'!$AJ$15</f>
-        <v>1605205576.0</v>
+        <f>'Decode_1M'!$AT$48/(DecodeTargetMs/1000)/1E9</f>
+        <v>0.5865216</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B42" s="33" t="str">
-        <f>TEXT(IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42)))),"#,##0.000")&amp;IF((IF(ABS(G42)&gt;=1E12,"TB",IF(ABS(G42)&gt;=1E9,"GB",IF(ABS(G42)&gt;=1E6,"MB",IF(ABS(G42)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G42)&gt;=1E12,"TB",IF(ABS(G42)&gt;=1E9,"GB",IF(ABS(G42)&gt;=1E6,"MB",IF(ABS(G42)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>104.891 GB</v>
+        <f>TEXT(IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42)))),"#,##0.000")&amp;IF((IF(ABS(G42)&gt;=1E12,"T",IF(ABS(G42)&gt;=1E9,"G",IF(ABS(G42)&gt;=1E6,"M",IF(ABS(G42)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G42)&gt;=1E12,"T",IF(ABS(G42)&gt;=1E9,"G",IF(ABS(G42)&gt;=1E6,"M",IF(ABS(G42)&gt;=1E3,"K",""))))))</f>
+        <v>1.140 G</v>
       </c>
       <c r="C42" s="33" t="str">
-        <f>TEXT(IF(ABS(H42)&gt;=1E12,H42/1E12,IF(ABS(H42)&gt;=1E9,H42/1E9,IF(ABS(H42)&gt;=1E6,H42/1E6,IF(ABS(H42)&gt;=1E3,H42/1E3,H42)))),"#,##0.000")&amp;IF((IF(ABS(H42)&gt;=1E12,"TB",IF(ABS(H42)&gt;=1E9,"GB",IF(ABS(H42)&gt;=1E6,"MB",IF(ABS(H42)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H42)&gt;=1E12,"TB",IF(ABS(H42)&gt;=1E9,"GB",IF(ABS(H42)&gt;=1E6,"MB",IF(ABS(H42)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>414.830 MB</v>
+        <f>TEXT(IF(ABS(H42)&gt;=1E12,H42/1E12,IF(ABS(H42)&gt;=1E9,H42/1E9,IF(ABS(H42)&gt;=1E6,H42/1E6,IF(ABS(H42)&gt;=1E3,H42/1E3,H42)))),"#,##0.000")&amp;IF((IF(ABS(H42)&gt;=1E12,"T",IF(ABS(H42)&gt;=1E9,"G",IF(ABS(H42)&gt;=1E6,"M",IF(ABS(H42)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H42)&gt;=1E12,"T",IF(ABS(H42)&gt;=1E9,"G",IF(ABS(H42)&gt;=1E6,"M",IF(ABS(H42)&gt;=1E3,"K",""))))))</f>
+        <v>1.140 G</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G42" s="32">
-        <f>'Prefill_8K'!$AR$48</f>
-        <v>104890576444.0</v>
+        <f>'Prefill_8K'!$AZ$49</f>
+        <v>1139835008.0</v>
       </c>
       <c r="H42" s="32">
-        <f>'Decode_1M'!$AR$48</f>
-        <v>414830140.0</v>
+        <f>'Prefill_8K'!$AZ$49</f>
+        <v>1139835008.0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="B43" s="31" t="str">
-        <f>TEXT(IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43)))),"#,##0.000")&amp;IF((IF(ABS(G43)&gt;=1E12,"TB",IF(ABS(G43)&gt;=1E9,"GB",IF(ABS(G43)&gt;=1E6,"MB",IF(ABS(G43)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G43)&gt;=1E12,"TB",IF(ABS(G43)&gt;=1E9,"GB",IF(ABS(G43)&gt;=1E6,"MB",IF(ABS(G43)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>369.338 GB</v>
-      </c>
-      <c r="C43" s="31" t="str">
-        <f>TEXT(IF(ABS(H43)&gt;=1E12,H43/1E12,IF(ABS(H43)&gt;=1E9,H43/1E9,IF(ABS(H43)&gt;=1E6,H43/1E6,IF(ABS(H43)&gt;=1E3,H43/1E3,H43)))),"#,##0.000")&amp;IF((IF(ABS(H43)&gt;=1E12,"TB",IF(ABS(H43)&gt;=1E9,"GB",IF(ABS(H43)&gt;=1E6,"MB",IF(ABS(H43)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H43)&gt;=1E12,"TB",IF(ABS(H43)&gt;=1E9,"GB",IF(ABS(H43)&gt;=1E6,"MB",IF(ABS(H43)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>6.055 GB</v>
+      <c r="A43" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B43" s="33" t="str">
+        <f>TEXT(IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43)))),"#,##0.000")&amp;IF((IF(ABS(G43)&gt;=1E12,"T",IF(ABS(G43)&gt;=1E9,"G",IF(ABS(G43)&gt;=1E6,"M",IF(ABS(G43)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G43)&gt;=1E12,"T",IF(ABS(G43)&gt;=1E9,"G",IF(ABS(G43)&gt;=1E6,"M",IF(ABS(G43)&gt;=1E3,"K",""))))))</f>
+        <v>35.758 G</v>
+      </c>
+      <c r="C43" s="33" t="str">
+        <f>TEXT(IF(ABS(H43)&gt;=1E12,H43/1E12,IF(ABS(H43)&gt;=1E9,H43/1E9,IF(ABS(H43)&gt;=1E6,H43/1E6,IF(ABS(H43)&gt;=1E3,H43/1E3,H43)))),"#,##0.000")&amp;IF((IF(ABS(H43)&gt;=1E12,"T",IF(ABS(H43)&gt;=1E9,"G",IF(ABS(H43)&gt;=1E6,"M",IF(ABS(H43)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H43)&gt;=1E12,"T",IF(ABS(H43)&gt;=1E9,"G",IF(ABS(H43)&gt;=1E6,"M",IF(ABS(H43)&gt;=1E3,"K",""))))))</f>
+        <v>35.758 G</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="G43" s="32">
-        <f>'Prefill_8K'!$AJ$13</f>
-        <v>369337880060.0</v>
+        <f>'Prefill_8K'!$AZ$50</f>
+        <v>35757730304.0</v>
       </c>
       <c r="H43" s="32">
-        <f>'Decode_1M'!$AJ$13</f>
-        <v>6055268244.0</v>
+        <f>'Prefill_8K'!$AZ$50</f>
+        <v>35757730304.0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B44" s="33" t="str">
-        <f>TEXT(G44,"#,##0.000")&amp;" GB/s"</f>
-        <v>231.532 GB/s</v>
+        <f>TEXT(IF(ABS(G44)&gt;=1E12,G44/1E12,IF(ABS(G44)&gt;=1E9,G44/1E9,IF(ABS(G44)&gt;=1E6,G44/1E6,IF(ABS(G44)&gt;=1E3,G44/1E3,G44)))),"#,##0.000")&amp;IF((IF(ABS(G44)&gt;=1E12,"T",IF(ABS(G44)&gt;=1E9,"G",IF(ABS(G44)&gt;=1E6,"M",IF(ABS(G44)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G44)&gt;=1E12,"T",IF(ABS(G44)&gt;=1E9,"G",IF(ABS(G44)&gt;=1E6,"M",IF(ABS(G44)&gt;=1E3,"K",""))))))</f>
+        <v>166.690 M</v>
       </c>
       <c r="C44" s="33" t="str">
-        <f>TEXT(H44,"#,##0.000")&amp;" GB/s"</f>
-        <v>403.523 GB/s</v>
+        <f>TEXT(IF(ABS(H44)&gt;=1E12,H44/1E12,IF(ABS(H44)&gt;=1E9,H44/1E9,IF(ABS(H44)&gt;=1E6,H44/1E6,IF(ABS(H44)&gt;=1E3,H44/1E3,H44)))),"#,##0.000")&amp;IF((IF(ABS(H44)&gt;=1E12,"T",IF(ABS(H44)&gt;=1E9,"G",IF(ABS(H44)&gt;=1E6,"M",IF(ABS(H44)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H44)&gt;=1E12,"T",IF(ABS(H44)&gt;=1E9,"G",IF(ABS(H44)&gt;=1E6,"M",IF(ABS(H44)&gt;=1E3,"K",""))))))</f>
+        <v>166.690 M</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G44" s="32">
-        <f>'Prefill_8K'!$AJ$14/(PrefillTargetMs/1000)/1E9</f>
-        <v>231.531806144</v>
+        <f>'Prefill_8K'!$AZ$51</f>
+        <v>166689903.0</v>
       </c>
       <c r="H44" s="32">
-        <f>'Decode_1M'!$AJ$14/(DecodeTargetMs/1000)/1E9</f>
-        <v>403.5232528</v>
+        <f>'Prefill_8K'!$AZ$51</f>
+        <v>166689903.0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="B45" s="33" t="str">
-        <f>TEXT(G45,"#,##0.000")&amp;" GB/s"</f>
-        <v>32.915 GB/s</v>
-      </c>
-      <c r="C45" s="33" t="str">
-        <f>TEXT(H45,"#,##0.000")&amp;" GB/s"</f>
-        <v>160.521 GB/s</v>
+      <c r="A45" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B45" s="31" t="str">
+        <f>TEXT(IF(ABS(G45)&gt;=1E12,G45/1E12,IF(ABS(G45)&gt;=1E9,G45/1E9,IF(ABS(G45)&gt;=1E6,G45/1E6,IF(ABS(G45)&gt;=1E3,G45/1E3,G45)))),"#,##0.000")&amp;IF((IF(ABS(G45)&gt;=1E12,"T",IF(ABS(G45)&gt;=1E9,"G",IF(ABS(G45)&gt;=1E6,"M",IF(ABS(G45)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G45)&gt;=1E12,"T",IF(ABS(G45)&gt;=1E9,"G",IF(ABS(G45)&gt;=1E6,"M",IF(ABS(G45)&gt;=1E3,"K",""))))))</f>
+        <v>37.064 G</v>
+      </c>
+      <c r="C45" s="31" t="str">
+        <f>TEXT(IF(ABS(H45)&gt;=1E12,H45/1E12,IF(ABS(H45)&gt;=1E9,H45/1E9,IF(ABS(H45)&gt;=1E6,H45/1E6,IF(ABS(H45)&gt;=1E3,H45/1E3,H45)))),"#,##0.000")&amp;IF((IF(ABS(H45)&gt;=1E12,"T",IF(ABS(H45)&gt;=1E9,"G",IF(ABS(H45)&gt;=1E6,"M",IF(ABS(H45)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H45)&gt;=1E12,"T",IF(ABS(H45)&gt;=1E9,"G",IF(ABS(H45)&gt;=1E6,"M",IF(ABS(H45)&gt;=1E3,"K",""))))))</f>
+        <v>37.064 G</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G45" s="32">
-        <f>'Prefill_8K'!$AJ$15/(PrefillTargetMs/1000)/1E9</f>
-        <v>32.915497472</v>
+        <f>'Prefill_8K'!$AZ$52</f>
+        <v>37064255215.0</v>
       </c>
       <c r="H45" s="32">
-        <f>'Decode_1M'!$AJ$15/(DecodeTargetMs/1000)/1E9</f>
-        <v>160.5205576</v>
+        <f>'Prefill_8K'!$AZ$52</f>
+        <v>37064255215.0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B46" s="33" t="str">
-        <f>TEXT(G46,"#,##0.000")&amp;" GB/s"</f>
-        <v>104.891 GB/s</v>
+        <f>TEXT(IF(ABS(G46)&gt;=1E12,G46/1E12,IF(ABS(G46)&gt;=1E9,G46/1E9,IF(ABS(G46)&gt;=1E6,G46/1E6,IF(ABS(G46)&gt;=1E3,G46/1E3,G46)))),"#,##0.000")&amp;IF((IF(ABS(G46)&gt;=1E12,"TB",IF(ABS(G46)&gt;=1E9,"GB",IF(ABS(G46)&gt;=1E6,"MB",IF(ABS(G46)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G46)&gt;=1E12,"TB",IF(ABS(G46)&gt;=1E9,"GB",IF(ABS(G46)&gt;=1E6,"MB",IF(ABS(G46)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>2.238 GB</v>
       </c>
       <c r="C46" s="33" t="str">
-        <f>TEXT(H46,"#,##0.000")&amp;" GB/s"</f>
-        <v>41.483 GB/s</v>
+        <f>TEXT(IF(ABS(H46)&gt;=1E12,H46/1E12,IF(ABS(H46)&gt;=1E9,H46/1E9,IF(ABS(H46)&gt;=1E6,H46/1E6,IF(ABS(H46)&gt;=1E3,H46/1E3,H46)))),"#,##0.000")&amp;IF((IF(ABS(H46)&gt;=1E12,"TB",IF(ABS(H46)&gt;=1E9,"GB",IF(ABS(H46)&gt;=1E6,"MB",IF(ABS(H46)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H46)&gt;=1E12,"TB",IF(ABS(H46)&gt;=1E9,"GB",IF(ABS(H46)&gt;=1E6,"MB",IF(ABS(H46)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>2.238 GB</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>506</v>
       </c>
       <c r="G46" s="32">
-        <f>'Prefill_8K'!$AR$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>104.890576444</v>
+        <f>'Prefill_8K'!$BB$49</f>
+        <v>2237504960</v>
       </c>
       <c r="H46" s="32">
-        <f>'Decode_1M'!$AR$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>41.483014</v>
+        <f>'Prefill_8K'!$BB$49</f>
+        <v>2237504960</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="B47" s="33" t="str">
-        <f>TEXT(IF(ABS(G47)&gt;=1E15,G47/1E15,IF(ABS(G47)&gt;=1E12,G47/1E12,IF(ABS(G47)&gt;=1E9,G47/1E9,IF(ABS(G47)&gt;=1E6,G47/1E6,G47)))),"#,##0.000")&amp;IF((IF(ABS(G47)&gt;=1E15,"PFLOPs",IF(ABS(G47)&gt;=1E12,"TFLOPs",IF(ABS(G47)&gt;=1E9,"GFLOPs",IF(ABS(G47)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G47)&gt;=1E15,"PFLOPs",IF(ABS(G47)&gt;=1E12,"TFLOPs",IF(ABS(G47)&gt;=1E9,"GFLOPs",IF(ABS(G47)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>55.653 TFLOPs</v>
+        <f>TEXT(IF(ABS(G47)&gt;=1E12,G47/1E12,IF(ABS(G47)&gt;=1E9,G47/1E9,IF(ABS(G47)&gt;=1E6,G47/1E6,IF(ABS(G47)&gt;=1E3,G47/1E3,G47)))),"#,##0.000")&amp;IF((IF(ABS(G47)&gt;=1E12,"TB",IF(ABS(G47)&gt;=1E9,"GB",IF(ABS(G47)&gt;=1E6,"MB",IF(ABS(G47)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G47)&gt;=1E12,"TB",IF(ABS(G47)&gt;=1E9,"GB",IF(ABS(G47)&gt;=1E6,"MB",IF(ABS(G47)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>19.578 GB</v>
       </c>
       <c r="C47" s="33" t="str">
-        <f>TEXT(IF(ABS(H47)&gt;=1E15,H47/1E15,IF(ABS(H47)&gt;=1E12,H47/1E12,IF(ABS(H47)&gt;=1E9,H47/1E9,IF(ABS(H47)&gt;=1E6,H47/1E6,H47)))),"#,##0.000")&amp;IF((IF(ABS(H47)&gt;=1E15,"PFLOPs",IF(ABS(H47)&gt;=1E12,"TFLOPs",IF(ABS(H47)&gt;=1E9,"GFLOPs",IF(ABS(H47)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H47)&gt;=1E15,"PFLOPs",IF(ABS(H47)&gt;=1E12,"TFLOPs",IF(ABS(H47)&gt;=1E9,"GFLOPs",IF(ABS(H47)&gt;=1E6,"MFLOPs","flops"))))))</f>
-        <v>23.550 GFLOPs</v>
+        <f>TEXT(IF(ABS(H47)&gt;=1E12,H47/1E12,IF(ABS(H47)&gt;=1E9,H47/1E9,IF(ABS(H47)&gt;=1E6,H47/1E6,IF(ABS(H47)&gt;=1E3,H47/1E3,H47)))),"#,##0.000")&amp;IF((IF(ABS(H47)&gt;=1E12,"TB",IF(ABS(H47)&gt;=1E9,"GB",IF(ABS(H47)&gt;=1E6,"MB",IF(ABS(H47)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H47)&gt;=1E12,"TB",IF(ABS(H47)&gt;=1E9,"GB",IF(ABS(H47)&gt;=1E6,"MB",IF(ABS(H47)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>19.578 GB</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>507</v>
       </c>
       <c r="G47" s="32">
-        <f>'Prefill_8K'!$AI$13</f>
-        <v>55652568907776.0</v>
+        <f>'Prefill_8K'!$BB$50</f>
+        <v>19577940480.0</v>
       </c>
       <c r="H47" s="32">
-        <f>'Decode_1M'!$AI$13</f>
-        <v>23549694126.0</v>
+        <f>'Prefill_8K'!$BB$50</f>
+        <v>19577940480.0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B48" s="33" t="str">
         <f>TEXT(IF(ABS(G48)&gt;=1E12,G48/1E12,IF(ABS(G48)&gt;=1E9,G48/1E9,IF(ABS(G48)&gt;=1E6,G48/1E6,IF(ABS(G48)&gt;=1E3,G48/1E3,G48)))),"#,##0.000")&amp;IF((IF(ABS(G48)&gt;=1E12,"TB",IF(ABS(G48)&gt;=1E9,"GB",IF(ABS(G48)&gt;=1E6,"MB",IF(ABS(G48)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G48)&gt;=1E12,"TB",IF(ABS(G48)&gt;=1E9,"GB",IF(ABS(G48)&gt;=1E6,"MB",IF(ABS(G48)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>40.635 GB</v>
+        <v>534.377 MB</v>
       </c>
       <c r="C48" s="33" t="str">
         <f>TEXT(IF(ABS(H48)&gt;=1E12,H48/1E12,IF(ABS(H48)&gt;=1E9,H48/1E9,IF(ABS(H48)&gt;=1E6,H48/1E6,IF(ABS(H48)&gt;=1E3,H48/1E3,H48)))),"#,##0.000")&amp;IF((IF(ABS(H48)&gt;=1E12,"TB",IF(ABS(H48)&gt;=1E9,"GB",IF(ABS(H48)&gt;=1E6,"MB",IF(ABS(H48)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H48)&gt;=1E12,"TB",IF(ABS(H48)&gt;=1E9,"GB",IF(ABS(H48)&gt;=1E6,"MB",IF(ABS(H48)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.865 MB</v>
+        <v>534.377 MB</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="G48" s="32">
+        <f>'Prefill_8K'!$BB$51</f>
+        <v>534376892.0</v>
+      </c>
+      <c r="H48" s="32">
+        <f>'Prefill_8K'!$BB$51</f>
+        <v>534376892.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="B49" s="31" t="str">
+        <f>TEXT(IF(ABS(G49)&gt;=1E12,G49/1E12,IF(ABS(G49)&gt;=1E9,G49/1E9,IF(ABS(G49)&gt;=1E6,G49/1E6,IF(ABS(G49)&gt;=1E3,G49/1E3,G49)))),"#,##0.000")&amp;IF((IF(ABS(G49)&gt;=1E12,"TB",IF(ABS(G49)&gt;=1E9,"GB",IF(ABS(G49)&gt;=1E6,"MB",IF(ABS(G49)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G49)&gt;=1E12,"TB",IF(ABS(G49)&gt;=1E9,"GB",IF(ABS(G49)&gt;=1E6,"MB",IF(ABS(G49)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>22.350 GB</v>
+      </c>
+      <c r="C49" s="31" t="str">
+        <f>TEXT(IF(ABS(H49)&gt;=1E12,H49/1E12,IF(ABS(H49)&gt;=1E9,H49/1E9,IF(ABS(H49)&gt;=1E6,H49/1E6,IF(ABS(H49)&gt;=1E3,H49/1E3,H49)))),"#,##0.000")&amp;IF((IF(ABS(H49)&gt;=1E12,"TB",IF(ABS(H49)&gt;=1E9,"GB",IF(ABS(H49)&gt;=1E6,"MB",IF(ABS(H49)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H49)&gt;=1E12,"TB",IF(ABS(H49)&gt;=1E9,"GB",IF(ABS(H49)&gt;=1E6,"MB",IF(ABS(H49)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>22.350 GB</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="G48" s="32">
-        <f>'Prefill_8K'!$AT$48</f>
-        <v>40635322112.0</v>
-      </c>
-      <c r="H48" s="32">
-        <f>'Decode_1M'!$AT$48</f>
-        <v>5865216.0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="B49" s="33" t="str">
-        <f>TEXT(G49,"#,##0.000")&amp;" GB/s"</f>
-        <v>40.635 GB/s</v>
-      </c>
-      <c r="C49" s="33" t="str">
-        <f>TEXT(H49,"#,##0.000")&amp;" GB/s"</f>
-        <v>0.587 GB/s</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>462</v>
-      </c>
       <c r="G49" s="32">
-        <f>'Prefill_8K'!$AT$48/(PrefillTargetMs/1000)/1E9</f>
-        <v>40.635322112</v>
+        <f>'Prefill_8K'!$BB$52</f>
+        <v>22349822332.0</v>
       </c>
       <c r="H49" s="32">
-        <f>'Decode_1M'!$AT$48/(DecodeTargetMs/1000)/1E9</f>
-        <v>0.5865216</v>
+        <f>'Prefill_8K'!$BB$52</f>
+        <v>22349822332.0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B50" s="33" t="str">
-        <f>TEXT(IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50)))),"#,##0.000")&amp;IF((IF(ABS(G50)&gt;=1E12,"T",IF(ABS(G50)&gt;=1E9,"G",IF(ABS(G50)&gt;=1E6,"M",IF(ABS(G50)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G50)&gt;=1E12,"T",IF(ABS(G50)&gt;=1E9,"G",IF(ABS(G50)&gt;=1E6,"M",IF(ABS(G50)&gt;=1E3,"K",""))))))</f>
-        <v>1.140 G</v>
+        <f>TEXT(IF(ABS(G50)&gt;=1E12,G50/1E12,IF(ABS(G50)&gt;=1E9,G50/1E9,IF(ABS(G50)&gt;=1E6,G50/1E6,IF(ABS(G50)&gt;=1E3,G50/1E3,G50)))),"#,##0.000")&amp;IF((IF(ABS(G50)&gt;=1E12,"TB",IF(ABS(G50)&gt;=1E9,"GB",IF(ABS(G50)&gt;=1E6,"MB",IF(ABS(G50)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G50)&gt;=1E12,"TB",IF(ABS(G50)&gt;=1E9,"GB",IF(ABS(G50)&gt;=1E6,"MB",IF(ABS(G50)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>50.987 MB</v>
       </c>
       <c r="C50" s="33" t="str">
-        <f>TEXT(IF(ABS(H50)&gt;=1E12,H50/1E12,IF(ABS(H50)&gt;=1E9,H50/1E9,IF(ABS(H50)&gt;=1E6,H50/1E6,IF(ABS(H50)&gt;=1E3,H50/1E3,H50)))),"#,##0.000")&amp;IF((IF(ABS(H50)&gt;=1E12,"T",IF(ABS(H50)&gt;=1E9,"G",IF(ABS(H50)&gt;=1E6,"M",IF(ABS(H50)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H50)&gt;=1E12,"T",IF(ABS(H50)&gt;=1E9,"G",IF(ABS(H50)&gt;=1E6,"M",IF(ABS(H50)&gt;=1E3,"K",""))))))</f>
-        <v>1.140 G</v>
+        <f>TEXT(IF(ABS(H50)&gt;=1E12,H50/1E12,IF(ABS(H50)&gt;=1E9,H50/1E9,IF(ABS(H50)&gt;=1E6,H50/1E6,IF(ABS(H50)&gt;=1E3,H50/1E3,H50)))),"#,##0.000")&amp;IF((IF(ABS(H50)&gt;=1E12,"TB",IF(ABS(H50)&gt;=1E9,"GB",IF(ABS(H50)&gt;=1E6,"MB",IF(ABS(H50)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H50)&gt;=1E12,"TB",IF(ABS(H50)&gt;=1E9,"GB",IF(ABS(H50)&gt;=1E6,"MB",IF(ABS(H50)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>5.811 GB</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>509</v>
       </c>
       <c r="G50" s="32">
-        <f>'Prefill_8K'!$AZ$49</f>
-        <v>1139835008.0</v>
+        <f>'Prefill_8K'!$X$35</f>
+        <v>50987008</v>
       </c>
       <c r="H50" s="32">
-        <f>'Prefill_8K'!$AZ$49</f>
-        <v>1139835008.0</v>
+        <f>'Decode_1M'!$X$35</f>
+        <v>5810552832</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B51" s="33" t="str">
-        <f>TEXT(IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51)))),"#,##0.000")&amp;IF((IF(ABS(G51)&gt;=1E12,"T",IF(ABS(G51)&gt;=1E9,"G",IF(ABS(G51)&gt;=1E6,"M",IF(ABS(G51)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G51)&gt;=1E12,"T",IF(ABS(G51)&gt;=1E9,"G",IF(ABS(G51)&gt;=1E6,"M",IF(ABS(G51)&gt;=1E3,"K",""))))))</f>
-        <v>35.758 G</v>
+        <f>TEXT(IF(ABS(G51)&gt;=1E12,G51/1E12,IF(ABS(G51)&gt;=1E9,G51/1E9,IF(ABS(G51)&gt;=1E6,G51/1E6,IF(ABS(G51)&gt;=1E3,G51/1E3,G51)))),"#,##0.000")&amp;IF((IF(ABS(G51)&gt;=1E12,"TB",IF(ABS(G51)&gt;=1E9,"GB",IF(ABS(G51)&gt;=1E6,"MB",IF(ABS(G51)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G51)&gt;=1E12,"TB",IF(ABS(G51)&gt;=1E9,"GB",IF(ABS(G51)&gt;=1E6,"MB",IF(ABS(G51)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>11.010 MB</v>
       </c>
       <c r="C51" s="33" t="str">
-        <f>TEXT(IF(ABS(H51)&gt;=1E12,H51/1E12,IF(ABS(H51)&gt;=1E9,H51/1E9,IF(ABS(H51)&gt;=1E6,H51/1E6,IF(ABS(H51)&gt;=1E3,H51/1E3,H51)))),"#,##0.000")&amp;IF((IF(ABS(H51)&gt;=1E12,"T",IF(ABS(H51)&gt;=1E9,"G",IF(ABS(H51)&gt;=1E6,"M",IF(ABS(H51)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H51)&gt;=1E12,"T",IF(ABS(H51)&gt;=1E9,"G",IF(ABS(H51)&gt;=1E6,"M",IF(ABS(H51)&gt;=1E3,"K",""))))))</f>
-        <v>35.758 G</v>
+        <f>TEXT(IF(ABS(H51)&gt;=1E12,H51/1E12,IF(ABS(H51)&gt;=1E9,H51/1E9,IF(ABS(H51)&gt;=1E6,H51/1E6,IF(ABS(H51)&gt;=1E3,H51/1E3,H51)))),"#,##0.000")&amp;IF((IF(ABS(H51)&gt;=1E12,"TB",IF(ABS(H51)&gt;=1E9,"GB",IF(ABS(H51)&gt;=1E6,"MB",IF(ABS(H51)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H51)&gt;=1E12,"TB",IF(ABS(H51)&gt;=1E9,"GB",IF(ABS(H51)&gt;=1E6,"MB",IF(ABS(H51)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>1.409 GB</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="G51" s="32">
-        <f>'Prefill_8K'!$AZ$50</f>
-        <v>35757730304.0</v>
+        <f>'Prefill_8K'!$X$36</f>
+        <v>11010048</v>
       </c>
       <c r="H51" s="32">
-        <f>'Prefill_8K'!$AZ$50</f>
-        <v>35757730304.0</v>
+        <f>'Decode_1M'!$X$36</f>
+        <v>1409286144</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B52" s="33" t="str">
-        <f>TEXT(IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52)))),"#,##0.000")&amp;IF((IF(ABS(G52)&gt;=1E12,"T",IF(ABS(G52)&gt;=1E9,"G",IF(ABS(G52)&gt;=1E6,"M",IF(ABS(G52)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G52)&gt;=1E12,"T",IF(ABS(G52)&gt;=1E9,"G",IF(ABS(G52)&gt;=1E6,"M",IF(ABS(G52)&gt;=1E3,"K",""))))))</f>
-        <v>166.690 M</v>
+        <f>TEXT(IF(ABS(G52)&gt;=1E12,G52/1E12,IF(ABS(G52)&gt;=1E9,G52/1E9,IF(ABS(G52)&gt;=1E6,G52/1E6,IF(ABS(G52)&gt;=1E3,G52/1E3,G52)))),"#,##0.000")&amp;IF((IF(ABS(G52)&gt;=1E12,"TB",IF(ABS(G52)&gt;=1E9,"GB",IF(ABS(G52)&gt;=1E6,"MB",IF(ABS(G52)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G52)&gt;=1E12,"TB",IF(ABS(G52)&gt;=1E9,"GB",IF(ABS(G52)&gt;=1E6,"MB",IF(ABS(G52)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>12.206 MB</v>
       </c>
       <c r="C52" s="33" t="str">
-        <f>TEXT(IF(ABS(H52)&gt;=1E12,H52/1E12,IF(ABS(H52)&gt;=1E9,H52/1E9,IF(ABS(H52)&gt;=1E6,H52/1E6,IF(ABS(H52)&gt;=1E3,H52/1E3,H52)))),"#,##0.000")&amp;IF((IF(ABS(H52)&gt;=1E12,"T",IF(ABS(H52)&gt;=1E9,"G",IF(ABS(H52)&gt;=1E6,"M",IF(ABS(H52)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H52)&gt;=1E12,"T",IF(ABS(H52)&gt;=1E9,"G",IF(ABS(H52)&gt;=1E6,"M",IF(ABS(H52)&gt;=1E3,"K",""))))))</f>
-        <v>166.690 M</v>
+        <f>TEXT(IF(ABS(H52)&gt;=1E12,H52/1E12,IF(ABS(H52)&gt;=1E9,H52/1E9,IF(ABS(H52)&gt;=1E6,H52/1E6,IF(ABS(H52)&gt;=1E3,H52/1E3,H52)))),"#,##0.000")&amp;IF((IF(ABS(H52)&gt;=1E12,"TB",IF(ABS(H52)&gt;=1E9,"GB",IF(ABS(H52)&gt;=1E6,"MB",IF(ABS(H52)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H52)&gt;=1E12,"TB",IF(ABS(H52)&gt;=1E9,"GB",IF(ABS(H52)&gt;=1E6,"MB",IF(ABS(H52)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>12.206 MB</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G52" s="32">
-        <f>'Prefill_8K'!$AZ$51</f>
-        <v>166689903.0</v>
-      </c>
-      <c r="H52" s="32">
-        <f>'Prefill_8K'!$AZ$51</f>
-        <v>166689903.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="B53" s="31" t="str">
-        <f>TEXT(IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53)))),"#,##0.000")&amp;IF((IF(ABS(G53)&gt;=1E12,"T",IF(ABS(G53)&gt;=1E9,"G",IF(ABS(G53)&gt;=1E6,"M",IF(ABS(G53)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G53)&gt;=1E12,"T",IF(ABS(G53)&gt;=1E9,"G",IF(ABS(G53)&gt;=1E6,"M",IF(ABS(G53)&gt;=1E3,"K",""))))))</f>
-        <v>37.064 G</v>
-      </c>
-      <c r="C53" s="31" t="str">
-        <f>TEXT(IF(ABS(H53)&gt;=1E12,H53/1E12,IF(ABS(H53)&gt;=1E9,H53/1E9,IF(ABS(H53)&gt;=1E6,H53/1E6,IF(ABS(H53)&gt;=1E3,H53/1E3,H53)))),"#,##0.000")&amp;IF((IF(ABS(H53)&gt;=1E12,"T",IF(ABS(H53)&gt;=1E9,"G",IF(ABS(H53)&gt;=1E6,"M",IF(ABS(H53)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(H53)&gt;=1E12,"T",IF(ABS(H53)&gt;=1E9,"G",IF(ABS(H53)&gt;=1E6,"M",IF(ABS(H53)&gt;=1E3,"K",""))))))</f>
-        <v>37.064 G</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="G53" s="32">
-        <f>'Prefill_8K'!$AZ$52</f>
-        <v>37064255215.0</v>
-      </c>
-      <c r="H53" s="32">
-        <f>'Prefill_8K'!$AZ$52</f>
-        <v>37064255215.0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="B54" s="33" t="str">
-        <f>TEXT(IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54)))),"#,##0.000")&amp;IF((IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.238 GB</v>
-      </c>
-      <c r="C54" s="33" t="str">
-        <f>TEXT(IF(ABS(H54)&gt;=1E12,H54/1E12,IF(ABS(H54)&gt;=1E9,H54/1E9,IF(ABS(H54)&gt;=1E6,H54/1E6,IF(ABS(H54)&gt;=1E3,H54/1E3,H54)))),"#,##0.000")&amp;IF((IF(ABS(H54)&gt;=1E12,"TB",IF(ABS(H54)&gt;=1E9,"GB",IF(ABS(H54)&gt;=1E6,"MB",IF(ABS(H54)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H54)&gt;=1E12,"TB",IF(ABS(H54)&gt;=1E9,"GB",IF(ABS(H54)&gt;=1E6,"MB",IF(ABS(H54)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>2.238 GB</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="G54" s="32">
-        <f>'Prefill_8K'!$BB$49</f>
-        <v>2237504960</v>
-      </c>
-      <c r="H54" s="32">
-        <f>'Prefill_8K'!$BB$49</f>
-        <v>2237504960</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="B55" s="33" t="str">
-        <f>TEXT(IF(ABS(G55)&gt;=1E12,G55/1E12,IF(ABS(G55)&gt;=1E9,G55/1E9,IF(ABS(G55)&gt;=1E6,G55/1E6,IF(ABS(G55)&gt;=1E3,G55/1E3,G55)))),"#,##0.000")&amp;IF((IF(ABS(G55)&gt;=1E12,"TB",IF(ABS(G55)&gt;=1E9,"GB",IF(ABS(G55)&gt;=1E6,"MB",IF(ABS(G55)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G55)&gt;=1E12,"TB",IF(ABS(G55)&gt;=1E9,"GB",IF(ABS(G55)&gt;=1E6,"MB",IF(ABS(G55)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>19.578 GB</v>
-      </c>
-      <c r="C55" s="33" t="str">
-        <f>TEXT(IF(ABS(H55)&gt;=1E12,H55/1E12,IF(ABS(H55)&gt;=1E9,H55/1E9,IF(ABS(H55)&gt;=1E6,H55/1E6,IF(ABS(H55)&gt;=1E3,H55/1E3,H55)))),"#,##0.000")&amp;IF((IF(ABS(H55)&gt;=1E12,"TB",IF(ABS(H55)&gt;=1E9,"GB",IF(ABS(H55)&gt;=1E6,"MB",IF(ABS(H55)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H55)&gt;=1E12,"TB",IF(ABS(H55)&gt;=1E9,"GB",IF(ABS(H55)&gt;=1E6,"MB",IF(ABS(H55)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>19.578 GB</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="G55" s="32">
-        <f>'Prefill_8K'!$BB$50</f>
-        <v>19577940480.0</v>
-      </c>
-      <c r="H55" s="32">
-        <f>'Prefill_8K'!$BB$50</f>
-        <v>19577940480.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B56" s="33" t="str">
-        <f>TEXT(IF(ABS(G56)&gt;=1E12,G56/1E12,IF(ABS(G56)&gt;=1E9,G56/1E9,IF(ABS(G56)&gt;=1E6,G56/1E6,IF(ABS(G56)&gt;=1E3,G56/1E3,G56)))),"#,##0.000")&amp;IF((IF(ABS(G56)&gt;=1E12,"TB",IF(ABS(G56)&gt;=1E9,"GB",IF(ABS(G56)&gt;=1E6,"MB",IF(ABS(G56)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G56)&gt;=1E12,"TB",IF(ABS(G56)&gt;=1E9,"GB",IF(ABS(G56)&gt;=1E6,"MB",IF(ABS(G56)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>534.377 MB</v>
-      </c>
-      <c r="C56" s="33" t="str">
-        <f>TEXT(IF(ABS(H56)&gt;=1E12,H56/1E12,IF(ABS(H56)&gt;=1E9,H56/1E9,IF(ABS(H56)&gt;=1E6,H56/1E6,IF(ABS(H56)&gt;=1E3,H56/1E3,H56)))),"#,##0.000")&amp;IF((IF(ABS(H56)&gt;=1E12,"TB",IF(ABS(H56)&gt;=1E9,"GB",IF(ABS(H56)&gt;=1E6,"MB",IF(ABS(H56)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H56)&gt;=1E12,"TB",IF(ABS(H56)&gt;=1E9,"GB",IF(ABS(H56)&gt;=1E6,"MB",IF(ABS(H56)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>534.377 MB</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="G56" s="32">
-        <f>'Prefill_8K'!$BB$51</f>
-        <v>534376892.0</v>
-      </c>
-      <c r="H56" s="32">
-        <f>'Prefill_8K'!$BB$51</f>
-        <v>534376892.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="B57" s="31" t="str">
-        <f>TEXT(IF(ABS(G57)&gt;=1E12,G57/1E12,IF(ABS(G57)&gt;=1E9,G57/1E9,IF(ABS(G57)&gt;=1E6,G57/1E6,IF(ABS(G57)&gt;=1E3,G57/1E3,G57)))),"#,##0.000")&amp;IF((IF(ABS(G57)&gt;=1E12,"TB",IF(ABS(G57)&gt;=1E9,"GB",IF(ABS(G57)&gt;=1E6,"MB",IF(ABS(G57)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G57)&gt;=1E12,"TB",IF(ABS(G57)&gt;=1E9,"GB",IF(ABS(G57)&gt;=1E6,"MB",IF(ABS(G57)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>22.350 GB</v>
-      </c>
-      <c r="C57" s="31" t="str">
-        <f>TEXT(IF(ABS(H57)&gt;=1E12,H57/1E12,IF(ABS(H57)&gt;=1E9,H57/1E9,IF(ABS(H57)&gt;=1E6,H57/1E6,IF(ABS(H57)&gt;=1E3,H57/1E3,H57)))),"#,##0.000")&amp;IF((IF(ABS(H57)&gt;=1E12,"TB",IF(ABS(H57)&gt;=1E9,"GB",IF(ABS(H57)&gt;=1E6,"MB",IF(ABS(H57)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H57)&gt;=1E12,"TB",IF(ABS(H57)&gt;=1E9,"GB",IF(ABS(H57)&gt;=1E6,"MB",IF(ABS(H57)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>22.350 GB</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="G57" s="32">
-        <f>'Prefill_8K'!$BB$52</f>
-        <v>22349822332.0</v>
-      </c>
-      <c r="H57" s="32">
-        <f>'Prefill_8K'!$BB$52</f>
-        <v>22349822332.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="B58" s="33" t="str">
-        <f>TEXT(IF(ABS(G58)&gt;=1E12,G58/1E12,IF(ABS(G58)&gt;=1E9,G58/1E9,IF(ABS(G58)&gt;=1E6,G58/1E6,IF(ABS(G58)&gt;=1E3,G58/1E3,G58)))),"#,##0.000")&amp;IF((IF(ABS(G58)&gt;=1E12,"TB",IF(ABS(G58)&gt;=1E9,"GB",IF(ABS(G58)&gt;=1E6,"MB",IF(ABS(G58)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G58)&gt;=1E12,"TB",IF(ABS(G58)&gt;=1E9,"GB",IF(ABS(G58)&gt;=1E6,"MB",IF(ABS(G58)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>50.987 MB</v>
-      </c>
-      <c r="C58" s="33" t="str">
-        <f>TEXT(IF(ABS(H58)&gt;=1E12,H58/1E12,IF(ABS(H58)&gt;=1E9,H58/1E9,IF(ABS(H58)&gt;=1E6,H58/1E6,IF(ABS(H58)&gt;=1E3,H58/1E3,H58)))),"#,##0.000")&amp;IF((IF(ABS(H58)&gt;=1E12,"TB",IF(ABS(H58)&gt;=1E9,"GB",IF(ABS(H58)&gt;=1E6,"MB",IF(ABS(H58)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H58)&gt;=1E12,"TB",IF(ABS(H58)&gt;=1E9,"GB",IF(ABS(H58)&gt;=1E6,"MB",IF(ABS(H58)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>5.811 GB</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G58" s="32">
-        <f>'Prefill_8K'!$X$35</f>
-        <v>50987008</v>
-      </c>
-      <c r="H58" s="32">
-        <f>'Decode_1M'!$X$35</f>
-        <v>5810552832</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="B59" s="33" t="str">
-        <f>TEXT(IF(ABS(G59)&gt;=1E12,G59/1E12,IF(ABS(G59)&gt;=1E9,G59/1E9,IF(ABS(G59)&gt;=1E6,G59/1E6,IF(ABS(G59)&gt;=1E3,G59/1E3,G59)))),"#,##0.000")&amp;IF((IF(ABS(G59)&gt;=1E12,"TB",IF(ABS(G59)&gt;=1E9,"GB",IF(ABS(G59)&gt;=1E6,"MB",IF(ABS(G59)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G59)&gt;=1E12,"TB",IF(ABS(G59)&gt;=1E9,"GB",IF(ABS(G59)&gt;=1E6,"MB",IF(ABS(G59)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>11.010 MB</v>
-      </c>
-      <c r="C59" s="33" t="str">
-        <f>TEXT(IF(ABS(H59)&gt;=1E12,H59/1E12,IF(ABS(H59)&gt;=1E9,H59/1E9,IF(ABS(H59)&gt;=1E6,H59/1E6,IF(ABS(H59)&gt;=1E3,H59/1E3,H59)))),"#,##0.000")&amp;IF((IF(ABS(H59)&gt;=1E12,"TB",IF(ABS(H59)&gt;=1E9,"GB",IF(ABS(H59)&gt;=1E6,"MB",IF(ABS(H59)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H59)&gt;=1E12,"TB",IF(ABS(H59)&gt;=1E9,"GB",IF(ABS(H59)&gt;=1E6,"MB",IF(ABS(H59)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>1.409 GB</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G59" s="32">
-        <f>'Prefill_8K'!$X$36</f>
-        <v>11010048</v>
-      </c>
-      <c r="H59" s="32">
-        <f>'Decode_1M'!$X$36</f>
-        <v>1409286144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B60" s="33" t="str">
-        <f>TEXT(IF(ABS(G60)&gt;=1E12,G60/1E12,IF(ABS(G60)&gt;=1E9,G60/1E9,IF(ABS(G60)&gt;=1E6,G60/1E6,IF(ABS(G60)&gt;=1E3,G60/1E3,G60)))),"#,##0.000")&amp;IF((IF(ABS(G60)&gt;=1E12,"TB",IF(ABS(G60)&gt;=1E9,"GB",IF(ABS(G60)&gt;=1E6,"MB",IF(ABS(G60)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G60)&gt;=1E12,"TB",IF(ABS(G60)&gt;=1E9,"GB",IF(ABS(G60)&gt;=1E6,"MB",IF(ABS(G60)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="C60" s="33" t="str">
-        <f>TEXT(IF(ABS(H60)&gt;=1E12,H60/1E12,IF(ABS(H60)&gt;=1E9,H60/1E9,IF(ABS(H60)&gt;=1E6,H60/1E6,IF(ABS(H60)&gt;=1E3,H60/1E3,H60)))),"#,##0.000")&amp;IF((IF(ABS(H60)&gt;=1E12,"TB",IF(ABS(H60)&gt;=1E9,"GB",IF(ABS(H60)&gt;=1E6,"MB",IF(ABS(H60)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H60)&gt;=1E12,"TB",IF(ABS(H60)&gt;=1E9,"GB",IF(ABS(H60)&gt;=1E6,"MB",IF(ABS(H60)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>12.206 MB</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G60" s="32">
         <f>'Prefill_8K'!$X$37</f>
         <v>12206080</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H52" s="32">
         <f>'Decode_1M'!$X$37</f>
         <v>12206080</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="B61" s="33" t="str">
-        <f>TEXT(IF(ABS(G61)&gt;=1E12,G61/1E12,IF(ABS(G61)&gt;=1E9,G61/1E9,IF(ABS(G61)&gt;=1E6,G61/1E6,IF(ABS(G61)&gt;=1E3,G61/1E3,G61)))),"#,##0.000")&amp;IF((IF(ABS(G61)&gt;=1E12,"TB",IF(ABS(G61)&gt;=1E9,"GB",IF(ABS(G61)&gt;=1E6,"MB",IF(ABS(G61)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G61)&gt;=1E12,"TB",IF(ABS(G61)&gt;=1E9,"GB",IF(ABS(G61)&gt;=1E6,"MB",IF(ABS(G61)&gt;=1E3,"KB","bytes"))))))</f>
+    <row r="53" spans="1:8">
+      <c r="A53" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53" s="33" t="str">
+        <f>TEXT(IF(ABS(G53)&gt;=1E12,G53/1E12,IF(ABS(G53)&gt;=1E9,G53/1E9,IF(ABS(G53)&gt;=1E6,G53/1E6,IF(ABS(G53)&gt;=1E3,G53/1E3,G53)))),"#,##0.000")&amp;IF((IF(ABS(G53)&gt;=1E12,"TB",IF(ABS(G53)&gt;=1E9,"GB",IF(ABS(G53)&gt;=1E6,"MB",IF(ABS(G53)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G53)&gt;=1E12,"TB",IF(ABS(G53)&gt;=1E9,"GB",IF(ABS(G53)&gt;=1E6,"MB",IF(ABS(G53)&gt;=1E3,"KB","bytes"))))))</f>
         <v>7.232 GB</v>
       </c>
-      <c r="C61" s="33" t="str">
-        <f>TEXT(IF(ABS(H61)&gt;=1E12,H61/1E12,IF(ABS(H61)&gt;=1E9,H61/1E9,IF(ABS(H61)&gt;=1E6,H61/1E6,IF(ABS(H61)&gt;=1E3,H61/1E3,H61)))),"#,##0.000")&amp;IF((IF(ABS(H61)&gt;=1E12,"TB",IF(ABS(H61)&gt;=1E9,"GB",IF(ABS(H61)&gt;=1E6,"MB",IF(ABS(H61)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H61)&gt;=1E12,"TB",IF(ABS(H61)&gt;=1E9,"GB",IF(ABS(H61)&gt;=1E6,"MB",IF(ABS(H61)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="C53" s="33" t="str">
+        <f>TEXT(IF(ABS(H53)&gt;=1E12,H53/1E12,IF(ABS(H53)&gt;=1E9,H53/1E9,IF(ABS(H53)&gt;=1E6,H53/1E6,IF(ABS(H53)&gt;=1E3,H53/1E3,H53)))),"#,##0.000")&amp;IF((IF(ABS(H53)&gt;=1E12,"TB",IF(ABS(H53)&gt;=1E9,"GB",IF(ABS(H53)&gt;=1E6,"MB",IF(ABS(H53)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H53)&gt;=1E12,"TB",IF(ABS(H53)&gt;=1E9,"GB",IF(ABS(H53)&gt;=1E6,"MB",IF(ABS(H53)&gt;=1E3,"KB","bytes"))))))</f>
         <v>7.232 GB</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="G61" s="32">
+      <c r="D53" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="G53" s="32">
         <f>'Prefill_8K'!$X$38</f>
         <v>7232045056</v>
       </c>
-      <c r="H61" s="32">
+      <c r="H53" s="32">
         <f>'Decode_1M'!$X$38</f>
         <v>7232045056</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="31" t="s">
-        <v>483</v>
-      </c>
-      <c r="B62" s="31" t="str">
-        <f>TEXT(IF(ABS(G62)&gt;=1E12,G62/1E12,IF(ABS(G62)&gt;=1E9,G62/1E9,IF(ABS(G62)&gt;=1E6,G62/1E6,IF(ABS(G62)&gt;=1E3,G62/1E3,G62)))),"#,##0.000")&amp;IF((IF(ABS(G62)&gt;=1E12,"TB",IF(ABS(G62)&gt;=1E9,"GB",IF(ABS(G62)&gt;=1E6,"MB",IF(ABS(G62)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G62)&gt;=1E12,"TB",IF(ABS(G62)&gt;=1E9,"GB",IF(ABS(G62)&gt;=1E6,"MB",IF(ABS(G62)&gt;=1E3,"KB","bytes"))))))</f>
+    <row r="54" spans="1:8">
+      <c r="A54" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B54" s="31" t="str">
+        <f>TEXT(IF(ABS(G54)&gt;=1E12,G54/1E12,IF(ABS(G54)&gt;=1E9,G54/1E9,IF(ABS(G54)&gt;=1E6,G54/1E6,IF(ABS(G54)&gt;=1E3,G54/1E3,G54)))),"#,##0.000")&amp;IF((IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G54)&gt;=1E12,"TB",IF(ABS(G54)&gt;=1E9,"GB",IF(ABS(G54)&gt;=1E6,"MB",IF(ABS(G54)&gt;=1E3,"KB","bytes"))))))</f>
         <v>29.582 GB</v>
       </c>
-      <c r="C62" s="31" t="str">
-        <f>TEXT(IF(ABS(H62)&gt;=1E12,H62/1E12,IF(ABS(H62)&gt;=1E9,H62/1E9,IF(ABS(H62)&gt;=1E6,H62/1E6,IF(ABS(H62)&gt;=1E3,H62/1E3,H62)))),"#,##0.000")&amp;IF((IF(ABS(H62)&gt;=1E12,"TB",IF(ABS(H62)&gt;=1E9,"GB",IF(ABS(H62)&gt;=1E6,"MB",IF(ABS(H62)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H62)&gt;=1E12,"TB",IF(ABS(H62)&gt;=1E9,"GB",IF(ABS(H62)&gt;=1E6,"MB",IF(ABS(H62)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="C54" s="31" t="str">
+        <f>TEXT(IF(ABS(H54)&gt;=1E12,H54/1E12,IF(ABS(H54)&gt;=1E9,H54/1E9,IF(ABS(H54)&gt;=1E6,H54/1E6,IF(ABS(H54)&gt;=1E3,H54/1E3,H54)))),"#,##0.000")&amp;IF((IF(ABS(H54)&gt;=1E12,"TB",IF(ABS(H54)&gt;=1E9,"GB",IF(ABS(H54)&gt;=1E6,"MB",IF(ABS(H54)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H54)&gt;=1E12,"TB",IF(ABS(H54)&gt;=1E9,"GB",IF(ABS(H54)&gt;=1E6,"MB",IF(ABS(H54)&gt;=1E3,"KB","bytes"))))))</f>
         <v>29.582 GB</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="G62" s="32">
+      <c r="D54" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="G54" s="32">
         <f>'Prefill_8K'!$BB$52+'Prefill_8K'!$X$38</f>
         <v>29581867388.0</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H54" s="32">
         <f>'Prefill_8K'!$BB$52+'Decode_1M'!$X$38</f>
         <v>29581867388.0</v>
       </c>
@@ -14712,7 +13818,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14730,12 +13836,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14743,19 +13849,19 @@
         <v>421</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>423</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -14766,7 +13872,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D4" s="36">
         <f>IF(C4="window",0,IF(C4="short",ShortRatio,LongRatio))</f>
@@ -14777,8 +13883,8 @@
         <v>raw sliding window</v>
       </c>
       <c r="F4" s="4" t="str">
-        <f>IF(B4=0,"inactive",IF(A4&lt;HashLayers,"hash","score"))</f>
-        <v>hash</v>
+        <f>IF(B4=0,"inactive",IF(A4&lt;HashLayers,"Token-ID lookup","score"))</f>
+        <v>Token-ID lookup</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -14789,7 +13895,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D5" s="36">
         <f>IF(C5="window",0,IF(C5="short",ShortRatio,LongRatio))</f>
@@ -14800,8 +13906,8 @@
         <v>raw sliding window</v>
       </c>
       <c r="F5" s="4" t="str">
-        <f>IF(B5=0,"inactive",IF(A5&lt;HashLayers,"hash","score"))</f>
-        <v>hash</v>
+        <f>IF(B5=0,"inactive",IF(A5&lt;HashLayers,"Token-ID lookup","score"))</f>
+        <v>Token-ID lookup</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -14812,7 +13918,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D6" s="36">
         <f>IF(C6="window",0,IF(C6="short",ShortRatio,LongRatio))</f>
@@ -14823,8 +13929,8 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F6" s="4" t="str">
-        <f>IF(B6=0,"inactive",IF(A6&lt;HashLayers,"hash","score"))</f>
-        <v>hash</v>
+        <f>IF(B6=0,"inactive",IF(A6&lt;HashLayers,"Token-ID lookup","score"))</f>
+        <v>Token-ID lookup</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -14835,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D7" s="36">
         <f>IF(C7="window",0,IF(C7="short",ShortRatio,LongRatio))</f>
@@ -14846,7 +13952,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F7" s="4" t="str">
-        <f>IF(B7=0,"inactive",IF(A7&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B7=0,"inactive",IF(A7&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14858,7 +13964,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D8" s="36">
         <f>IF(C8="window",0,IF(C8="short",ShortRatio,LongRatio))</f>
@@ -14869,7 +13975,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F8" s="4" t="str">
-        <f>IF(B8=0,"inactive",IF(A8&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B8=0,"inactive",IF(A8&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14881,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D9" s="36">
         <f>IF(C9="window",0,IF(C9="short",ShortRatio,LongRatio))</f>
@@ -14892,7 +13998,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F9" s="4" t="str">
-        <f>IF(B9=0,"inactive",IF(A9&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B9=0,"inactive",IF(A9&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14904,7 +14010,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D10" s="36">
         <f>IF(C10="window",0,IF(C10="short",ShortRatio,LongRatio))</f>
@@ -14915,7 +14021,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F10" s="4" t="str">
-        <f>IF(B10=0,"inactive",IF(A10&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B10=0,"inactive",IF(A10&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14927,7 +14033,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D11" s="36">
         <f>IF(C11="window",0,IF(C11="short",ShortRatio,LongRatio))</f>
@@ -14938,7 +14044,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F11" s="4" t="str">
-        <f>IF(B11=0,"inactive",IF(A11&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B11=0,"inactive",IF(A11&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14950,7 +14056,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D12" s="36">
         <f>IF(C12="window",0,IF(C12="short",ShortRatio,LongRatio))</f>
@@ -14961,7 +14067,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F12" s="4" t="str">
-        <f>IF(B12=0,"inactive",IF(A12&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B12=0,"inactive",IF(A12&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14973,7 +14079,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D13" s="36">
         <f>IF(C13="window",0,IF(C13="short",ShortRatio,LongRatio))</f>
@@ -14984,7 +14090,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F13" s="4" t="str">
-        <f>IF(B13=0,"inactive",IF(A13&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B13=0,"inactive",IF(A13&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -14996,7 +14102,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D14" s="36">
         <f>IF(C14="window",0,IF(C14="short",ShortRatio,LongRatio))</f>
@@ -15007,7 +14113,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F14" s="4" t="str">
-        <f>IF(B14=0,"inactive",IF(A14&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B14=0,"inactive",IF(A14&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15019,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D15" s="36">
         <f>IF(C15="window",0,IF(C15="short",ShortRatio,LongRatio))</f>
@@ -15030,7 +14136,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F15" s="4" t="str">
-        <f>IF(B15=0,"inactive",IF(A15&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B15=0,"inactive",IF(A15&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15042,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D16" s="36">
         <f>IF(C16="window",0,IF(C16="short",ShortRatio,LongRatio))</f>
@@ -15053,7 +14159,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F16" s="4" t="str">
-        <f>IF(B16=0,"inactive",IF(A16&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B16=0,"inactive",IF(A16&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15065,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D17" s="36">
         <f>IF(C17="window",0,IF(C17="short",ShortRatio,LongRatio))</f>
@@ -15076,7 +14182,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F17" s="4" t="str">
-        <f>IF(B17=0,"inactive",IF(A17&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B17=0,"inactive",IF(A17&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15088,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D18" s="36">
         <f>IF(C18="window",0,IF(C18="short",ShortRatio,LongRatio))</f>
@@ -15099,7 +14205,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F18" s="4" t="str">
-        <f>IF(B18=0,"inactive",IF(A18&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B18=0,"inactive",IF(A18&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15111,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D19" s="36">
         <f>IF(C19="window",0,IF(C19="short",ShortRatio,LongRatio))</f>
@@ -15122,7 +14228,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F19" s="4" t="str">
-        <f>IF(B19=0,"inactive",IF(A19&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B19=0,"inactive",IF(A19&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15134,7 +14240,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D20" s="36">
         <f>IF(C20="window",0,IF(C20="short",ShortRatio,LongRatio))</f>
@@ -15145,7 +14251,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F20" s="4" t="str">
-        <f>IF(B20=0,"inactive",IF(A20&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B20=0,"inactive",IF(A20&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15157,7 +14263,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D21" s="36">
         <f>IF(C21="window",0,IF(C21="short",ShortRatio,LongRatio))</f>
@@ -15168,7 +14274,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F21" s="4" t="str">
-        <f>IF(B21=0,"inactive",IF(A21&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B21=0,"inactive",IF(A21&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15180,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D22" s="36">
         <f>IF(C22="window",0,IF(C22="short",ShortRatio,LongRatio))</f>
@@ -15191,7 +14297,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F22" s="4" t="str">
-        <f>IF(B22=0,"inactive",IF(A22&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B22=0,"inactive",IF(A22&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15203,7 +14309,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D23" s="36">
         <f>IF(C23="window",0,IF(C23="short",ShortRatio,LongRatio))</f>
@@ -15214,7 +14320,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F23" s="4" t="str">
-        <f>IF(B23=0,"inactive",IF(A23&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B23=0,"inactive",IF(A23&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15226,7 +14332,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D24" s="36">
         <f>IF(C24="window",0,IF(C24="short",ShortRatio,LongRatio))</f>
@@ -15237,7 +14343,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F24" s="4" t="str">
-        <f>IF(B24=0,"inactive",IF(A24&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B24=0,"inactive",IF(A24&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15249,7 +14355,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D25" s="36">
         <f>IF(C25="window",0,IF(C25="short",ShortRatio,LongRatio))</f>
@@ -15260,7 +14366,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F25" s="4" t="str">
-        <f>IF(B25=0,"inactive",IF(A25&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B25=0,"inactive",IF(A25&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15272,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D26" s="36">
         <f>IF(C26="window",0,IF(C26="short",ShortRatio,LongRatio))</f>
@@ -15283,7 +14389,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F26" s="4" t="str">
-        <f>IF(B26=0,"inactive",IF(A26&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B26=0,"inactive",IF(A26&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15295,7 +14401,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D27" s="36">
         <f>IF(C27="window",0,IF(C27="short",ShortRatio,LongRatio))</f>
@@ -15306,7 +14412,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F27" s="4" t="str">
-        <f>IF(B27=0,"inactive",IF(A27&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B27=0,"inactive",IF(A27&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15318,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D28" s="36">
         <f>IF(C28="window",0,IF(C28="short",ShortRatio,LongRatio))</f>
@@ -15329,7 +14435,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F28" s="4" t="str">
-        <f>IF(B28=0,"inactive",IF(A28&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B28=0,"inactive",IF(A28&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15341,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D29" s="36">
         <f>IF(C29="window",0,IF(C29="short",ShortRatio,LongRatio))</f>
@@ -15352,7 +14458,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F29" s="4" t="str">
-        <f>IF(B29=0,"inactive",IF(A29&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B29=0,"inactive",IF(A29&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15364,7 +14470,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D30" s="36">
         <f>IF(C30="window",0,IF(C30="short",ShortRatio,LongRatio))</f>
@@ -15375,7 +14481,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F30" s="4" t="str">
-        <f>IF(B30=0,"inactive",IF(A30&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B30=0,"inactive",IF(A30&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15387,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D31" s="36">
         <f>IF(C31="window",0,IF(C31="short",ShortRatio,LongRatio))</f>
@@ -15398,7 +14504,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F31" s="4" t="str">
-        <f>IF(B31=0,"inactive",IF(A31&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B31=0,"inactive",IF(A31&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15410,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D32" s="36">
         <f>IF(C32="window",0,IF(C32="short",ShortRatio,LongRatio))</f>
@@ -15421,7 +14527,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F32" s="4" t="str">
-        <f>IF(B32=0,"inactive",IF(A32&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B32=0,"inactive",IF(A32&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15433,7 +14539,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D33" s="36">
         <f>IF(C33="window",0,IF(C33="short",ShortRatio,LongRatio))</f>
@@ -15444,7 +14550,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F33" s="4" t="str">
-        <f>IF(B33=0,"inactive",IF(A33&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B33=0,"inactive",IF(A33&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15456,7 +14562,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D34" s="36">
         <f>IF(C34="window",0,IF(C34="short",ShortRatio,LongRatio))</f>
@@ -15467,7 +14573,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F34" s="4" t="str">
-        <f>IF(B34=0,"inactive",IF(A34&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B34=0,"inactive",IF(A34&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15479,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D35" s="36">
         <f>IF(C35="window",0,IF(C35="short",ShortRatio,LongRatio))</f>
@@ -15490,7 +14596,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F35" s="4" t="str">
-        <f>IF(B35=0,"inactive",IF(A35&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B35=0,"inactive",IF(A35&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15502,7 +14608,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D36" s="36">
         <f>IF(C36="window",0,IF(C36="short",ShortRatio,LongRatio))</f>
@@ -15513,7 +14619,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F36" s="4" t="str">
-        <f>IF(B36=0,"inactive",IF(A36&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B36=0,"inactive",IF(A36&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15525,7 +14631,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D37" s="36">
         <f>IF(C37="window",0,IF(C37="short",ShortRatio,LongRatio))</f>
@@ -15536,7 +14642,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F37" s="4" t="str">
-        <f>IF(B37=0,"inactive",IF(A37&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B37=0,"inactive",IF(A37&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15548,7 +14654,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D38" s="36">
         <f>IF(C38="window",0,IF(C38="short",ShortRatio,LongRatio))</f>
@@ -15559,7 +14665,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F38" s="4" t="str">
-        <f>IF(B38=0,"inactive",IF(A38&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B38=0,"inactive",IF(A38&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15571,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D39" s="36">
         <f>IF(C39="window",0,IF(C39="short",ShortRatio,LongRatio))</f>
@@ -15582,7 +14688,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F39" s="4" t="str">
-        <f>IF(B39=0,"inactive",IF(A39&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B39=0,"inactive",IF(A39&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15594,7 +14700,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D40" s="36">
         <f>IF(C40="window",0,IF(C40="short",ShortRatio,LongRatio))</f>
@@ -15605,7 +14711,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F40" s="4" t="str">
-        <f>IF(B40=0,"inactive",IF(A40&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B40=0,"inactive",IF(A40&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15617,7 +14723,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D41" s="36">
         <f>IF(C41="window",0,IF(C41="short",ShortRatio,LongRatio))</f>
@@ -15628,7 +14734,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F41" s="4" t="str">
-        <f>IF(B41=0,"inactive",IF(A41&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B41=0,"inactive",IF(A41&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15640,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D42" s="36">
         <f>IF(C42="window",0,IF(C42="short",ShortRatio,LongRatio))</f>
@@ -15651,7 +14757,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F42" s="4" t="str">
-        <f>IF(B42=0,"inactive",IF(A42&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B42=0,"inactive",IF(A42&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15663,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D43" s="36">
         <f>IF(C43="window",0,IF(C43="short",ShortRatio,LongRatio))</f>
@@ -15674,7 +14780,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F43" s="4" t="str">
-        <f>IF(B43=0,"inactive",IF(A43&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B43=0,"inactive",IF(A43&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15686,7 +14792,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D44" s="36">
         <f>IF(C44="window",0,IF(C44="short",ShortRatio,LongRatio))</f>
@@ -15697,7 +14803,7 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F44" s="4" t="str">
-        <f>IF(B44=0,"inactive",IF(A44&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B44=0,"inactive",IF(A44&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15709,7 +14815,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D45" s="36">
         <f>IF(C45="window",0,IF(C45="short",ShortRatio,LongRatio))</f>
@@ -15720,7 +14826,7 @@
         <v>deterministic compressed KV</v>
       </c>
       <c r="F45" s="4" t="str">
-        <f>IF(B45=0,"inactive",IF(A45&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B45=0,"inactive",IF(A45&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
@@ -15732,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D46" s="36">
         <f>IF(C46="window",0,IF(C46="short",ShortRatio,LongRatio))</f>
@@ -15743,11 +14849,11 @@
         <v>compressed KV + Indexer Top-K</v>
       </c>
       <c r="F46" s="4" t="str">
-        <f>IF(B46=0,"inactive",IF(A46&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B46=0,"inactive",IF(A46&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>score</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="34">
         <v>43</v>
       </c>
@@ -15755,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D47" s="36">
         <f>IF(C47="window",0,IF(C47="short",ShortRatio,LongRatio))</f>
@@ -15766,11 +14872,11 @@
         <v>inactive</v>
       </c>
       <c r="F47" s="4" t="str">
-        <f>IF(B47=0,"inactive",IF(A47&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B47=0,"inactive",IF(A47&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="34">
         <v>44</v>
       </c>
@@ -15778,7 +14884,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D48" s="36">
         <f>IF(C48="window",0,IF(C48="short",ShortRatio,LongRatio))</f>
@@ -15789,11 +14895,11 @@
         <v>inactive</v>
       </c>
       <c r="F48" s="4" t="str">
-        <f>IF(B48=0,"inactive",IF(A48&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B48=0,"inactive",IF(A48&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="34">
         <v>45</v>
       </c>
@@ -15801,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D49" s="36">
         <f>IF(C49="window",0,IF(C49="short",ShortRatio,LongRatio))</f>
@@ -15812,11 +14918,11 @@
         <v>inactive</v>
       </c>
       <c r="F49" s="4" t="str">
-        <f>IF(B49=0,"inactive",IF(A49&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B49=0,"inactive",IF(A49&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="34">
         <v>46</v>
       </c>
@@ -15824,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D50" s="36">
         <f>IF(C50="window",0,IF(C50="short",ShortRatio,LongRatio))</f>
@@ -15835,11 +14941,11 @@
         <v>inactive</v>
       </c>
       <c r="F50" s="4" t="str">
-        <f>IF(B50=0,"inactive",IF(A50&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B50=0,"inactive",IF(A50&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="34">
         <v>47</v>
       </c>
@@ -15847,7 +14953,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D51" s="36">
         <f>IF(C51="window",0,IF(C51="short",ShortRatio,LongRatio))</f>
@@ -15858,11 +14964,11 @@
         <v>inactive</v>
       </c>
       <c r="F51" s="4" t="str">
-        <f>IF(B51=0,"inactive",IF(A51&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B51=0,"inactive",IF(A51&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="34">
         <v>48</v>
       </c>
@@ -15870,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D52" s="36">
         <f>IF(C52="window",0,IF(C52="short",ShortRatio,LongRatio))</f>
@@ -15881,11 +14987,11 @@
         <v>inactive</v>
       </c>
       <c r="F52" s="4" t="str">
-        <f>IF(B52=0,"inactive",IF(A52&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B52=0,"inactive",IF(A52&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="34">
         <v>49</v>
       </c>
@@ -15893,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D53" s="36">
         <f>IF(C53="window",0,IF(C53="short",ShortRatio,LongRatio))</f>
@@ -15904,11 +15010,11 @@
         <v>inactive</v>
       </c>
       <c r="F53" s="4" t="str">
-        <f>IF(B53=0,"inactive",IF(A53&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B53=0,"inactive",IF(A53&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="34">
         <v>50</v>
       </c>
@@ -15916,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D54" s="36">
         <f>IF(C54="window",0,IF(C54="short",ShortRatio,LongRatio))</f>
@@ -15927,11 +15033,11 @@
         <v>inactive</v>
       </c>
       <c r="F54" s="4" t="str">
-        <f>IF(B54=0,"inactive",IF(A54&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B54=0,"inactive",IF(A54&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="34">
         <v>51</v>
       </c>
@@ -15939,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D55" s="36">
         <f>IF(C55="window",0,IF(C55="short",ShortRatio,LongRatio))</f>
@@ -15950,11 +15056,11 @@
         <v>inactive</v>
       </c>
       <c r="F55" s="4" t="str">
-        <f>IF(B55=0,"inactive",IF(A55&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B55=0,"inactive",IF(A55&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="34">
         <v>52</v>
       </c>
@@ -15962,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D56" s="36">
         <f>IF(C56="window",0,IF(C56="short",ShortRatio,LongRatio))</f>
@@ -15973,11 +15079,11 @@
         <v>inactive</v>
       </c>
       <c r="F56" s="4" t="str">
-        <f>IF(B56=0,"inactive",IF(A56&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B56=0,"inactive",IF(A56&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" s="34">
         <v>53</v>
       </c>
@@ -15985,7 +15091,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D57" s="36">
         <f>IF(C57="window",0,IF(C57="short",ShortRatio,LongRatio))</f>
@@ -15996,11 +15102,11 @@
         <v>inactive</v>
       </c>
       <c r="F57" s="4" t="str">
-        <f>IF(B57=0,"inactive",IF(A57&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B57=0,"inactive",IF(A57&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" s="34">
         <v>54</v>
       </c>
@@ -16008,7 +15114,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D58" s="36">
         <f>IF(C58="window",0,IF(C58="short",ShortRatio,LongRatio))</f>
@@ -16019,11 +15125,11 @@
         <v>inactive</v>
       </c>
       <c r="F58" s="4" t="str">
-        <f>IF(B58=0,"inactive",IF(A58&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B58=0,"inactive",IF(A58&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="34">
         <v>55</v>
       </c>
@@ -16031,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D59" s="36">
         <f>IF(C59="window",0,IF(C59="short",ShortRatio,LongRatio))</f>
@@ -16042,11 +15148,11 @@
         <v>inactive</v>
       </c>
       <c r="F59" s="4" t="str">
-        <f>IF(B59=0,"inactive",IF(A59&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B59=0,"inactive",IF(A59&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="34">
         <v>56</v>
       </c>
@@ -16054,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D60" s="36">
         <f>IF(C60="window",0,IF(C60="short",ShortRatio,LongRatio))</f>
@@ -16065,11 +15171,11 @@
         <v>inactive</v>
       </c>
       <c r="F60" s="4" t="str">
-        <f>IF(B60=0,"inactive",IF(A60&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B60=0,"inactive",IF(A60&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" s="34">
         <v>57</v>
       </c>
@@ -16077,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D61" s="36">
         <f>IF(C61="window",0,IF(C61="short",ShortRatio,LongRatio))</f>
@@ -16088,11 +15194,11 @@
         <v>inactive</v>
       </c>
       <c r="F61" s="4" t="str">
-        <f>IF(B61=0,"inactive",IF(A61&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B61=0,"inactive",IF(A61&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" s="34">
         <v>58</v>
       </c>
@@ -16100,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D62" s="36">
         <f>IF(C62="window",0,IF(C62="short",ShortRatio,LongRatio))</f>
@@ -16111,11 +15217,11 @@
         <v>inactive</v>
       </c>
       <c r="F62" s="4" t="str">
-        <f>IF(B62=0,"inactive",IF(A62&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B62=0,"inactive",IF(A62&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="34">
         <v>59</v>
       </c>
@@ -16123,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D63" s="36">
         <f>IF(C63="window",0,IF(C63="short",ShortRatio,LongRatio))</f>
@@ -16134,11 +15240,11 @@
         <v>inactive</v>
       </c>
       <c r="F63" s="4" t="str">
-        <f>IF(B63=0,"inactive",IF(A63&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B63=0,"inactive",IF(A63&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="34">
         <v>60</v>
       </c>
@@ -16146,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D64" s="36">
         <f>IF(C64="window",0,IF(C64="short",ShortRatio,LongRatio))</f>
@@ -16157,11 +15263,11 @@
         <v>inactive</v>
       </c>
       <c r="F64" s="4" t="str">
-        <f>IF(B64=0,"inactive",IF(A64&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B64=0,"inactive",IF(A64&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" s="34">
         <v>61</v>
       </c>
@@ -16169,7 +15275,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D65" s="36">
         <f>IF(C65="window",0,IF(C65="short",ShortRatio,LongRatio))</f>
@@ -16180,11 +15286,11 @@
         <v>inactive</v>
       </c>
       <c r="F65" s="4" t="str">
-        <f>IF(B65=0,"inactive",IF(A65&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B65=0,"inactive",IF(A65&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" s="34">
         <v>62</v>
       </c>
@@ -16192,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D66" s="36">
         <f>IF(C66="window",0,IF(C66="short",ShortRatio,LongRatio))</f>
@@ -16203,11 +15309,11 @@
         <v>inactive</v>
       </c>
       <c r="F66" s="4" t="str">
-        <f>IF(B66=0,"inactive",IF(A66&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B66=0,"inactive",IF(A66&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" s="34">
         <v>63</v>
       </c>
@@ -16215,7 +15321,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D67" s="36">
         <f>IF(C67="window",0,IF(C67="short",ShortRatio,LongRatio))</f>
@@ -16226,7 +15332,7 @@
         <v>inactive</v>
       </c>
       <c r="F67" s="4" t="str">
-        <f>IF(B67=0,"inactive",IF(A67&lt;HashLayers,"hash","score"))</f>
+        <f>IF(B67=0,"inactive",IF(A67&lt;HashLayers,"Token-ID lookup","score"))</f>
         <v>inactive</v>
       </c>
     </row>
@@ -16255,15 +15361,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -16271,31 +15377,31 @@
         <v>359</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -16303,39 +15409,39 @@
         <v>59</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -16343,47 +15449,47 @@
         <v>409</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="558">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1534,7 +1534,7 @@
     <t>Preallocated KV + state</t>
   </si>
   <si>
-    <t>Total resident capacity</t>
+    <t>Total capacity per inference / rank</t>
   </si>
   <si>
     <t>参数 + 按 MaxContext 预分配的 KV/状态；不含临时工作区。</t>
@@ -1546,6 +1546,30 @@
     <t>单次推理调用的单 Rank 总 FLOPs；不除以目标时延。</t>
   </si>
   <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>TP8/rank</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Prefill</t>
+  </si>
+  <si>
+    <t>Static parameters + Prefill MaxContext KV/State</t>
+  </si>
+  <si>
+    <t>Decode</t>
+  </si>
+  <si>
+    <t>Static parameters + Decode MaxContext KV/State</t>
+  </si>
+  <si>
     <t>One-inference TFLOPs</t>
   </si>
   <si>
@@ -1576,10 +1600,13 @@
     <t>TP8 GB</t>
   </si>
   <si>
-    <t>Prefill</t>
-  </si>
-  <si>
-    <t>Decode</t>
+    <t>具体内容（Static parameter capacity per rank）：Attention、MoE、Embedding、LM Head、Norm、HC 等静态模型参数及量化 Scale；不含 KV Cache、Compressor State、临时激活和集合通信缓冲区。Prefill/Decode 两图的静态参数数据相同。</t>
+  </si>
+  <si>
+    <t>Capacity GB</t>
+  </si>
+  <si>
+    <t>具体内容（Total capacity per inference / rank）：当前模式单 Rank 的静态参数容量 + 按 MaxContext 预分配的 KV Cache + Compressor State；不含临时激活、residual/HC workspace 和集合通信传输量。</t>
   </si>
   <si>
     <t>Per-Rank Inference Hardware Resource Summary</t>
@@ -1645,9 +1672,6 @@
     <t>Active</t>
   </si>
   <si>
-    <t>Mode</t>
-  </si>
-  <si>
     <t>Attention behavior</t>
   </si>
   <si>
@@ -1667,9 +1691,6 @@
   </si>
   <si>
     <t>Topic</t>
-  </si>
-  <si>
-    <t>Definition</t>
   </si>
   <si>
     <t>仅统计 43 层主推理路径；不含 MTP、反向传播、梯度、优化器状态和训练激活。Layer_Config 最多可维护 64 层。</t>
@@ -2469,7 +2490,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Static parameter capacity per rank</a:t>
+              <a:t>Prefill static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2651,7 +2672,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>TP1 vs TP8: inference resident capacity per rank</a:t>
+              <a:t>Decode static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2675,29 +2696,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$60:$S$61</c:f>
+              <c:f>Comparison!$S$60:$S$62</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Prefill</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Decode</c:v>
+                  <c:v>MoE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$60:$T$61</c:f>
+              <c:f>Comparison!$T$60:$T$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>166.349315548</c:v>
+                  <c:v>7.45138496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>166.349315548</c:v>
+                  <c:v>148.351461888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.314423644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2715,29 +2742,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$60:$S$61</c:f>
+              <c:f>Comparison!$S$60:$S$62</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Prefill</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Decode</c:v>
+                  <c:v>MoE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$60:$U$61</c:f>
+              <c:f>Comparison!$U$60:$U$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>29.581867388</c:v>
+                  <c:v>2.23750496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.581867388</c:v>
+                  <c:v>19.57794048</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.534376892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2805,6 +2838,268 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Prefill total capacity per inference
+/ rank</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Capacity GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$67:$S$68</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>TP1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TP8/rank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$T$67:$T$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>166.349315548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.581867388</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="30"/>
+        <c:axId val="50060001"/>
+        <c:axId val="50060002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50060001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="50060002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50060002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GB</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50060001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Decode total capacity per inference
+/ rank</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Capacity GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$74:$S$75</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>TP1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TP8/rank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$T$74:$T$75</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>166.349315548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.581867388</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="30"/>
+        <c:axId val="50070001"/>
+        <c:axId val="50070002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50070001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="50070002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50070002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GB</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50070001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2841,13 +3136,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2871,13 +3166,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2901,13 +3196,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2931,13 +3226,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2952,6 +3247,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3082,6 +3437,19 @@
     <tableColumn id="4" name="Decode TP1"/>
     <tableColumn id="5" name="Decode TP8/rank"/>
     <tableColumn id="6" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Comparison_Total_Capacity" displayName="Comparison_Total_Capacity" ref="K32:N34" totalsRowShown="0">
+  <autoFilter ref="K32:N34"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Mode"/>
+    <tableColumn id="2" name="TP1"/>
+    <tableColumn id="3" name="TP8/rank"/>
+    <tableColumn id="4" name="Definition"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11406,13 +11774,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="72.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="20.7109375" customWidth="1"/>
+    <col min="15" max="16" width="0" hidden="1" customWidth="1"/>
     <col min="19" max="21" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12407,14 +12777,32 @@
       </c>
     </row>
     <row r="31" spans="1:20">
+      <c r="K31" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
       <c r="S31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="T31" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="K32" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="L32" t="s">
+        <v>483</v>
+      </c>
+      <c r="M32" t="s">
+        <v>484</v>
+      </c>
+      <c r="N32" t="s">
+        <v>485</v>
+      </c>
       <c r="S32" s="4" t="s">
         <v>439</v>
       </c>
@@ -12423,16 +12811,60 @@
         <v>228.39768211456</v>
       </c>
     </row>
-    <row r="33" spans="19:21">
+    <row r="33" spans="11:21">
+      <c r="K33" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="L33" s="33" t="str">
+        <f>TEXT(IF(ABS(O33)&gt;=1E12,O33/1E12,IF(ABS(O33)&gt;=1E9,O33/1E9,IF(ABS(O33)&gt;=1E6,O33/1E6,IF(ABS(O33)&gt;=1E3,O33/1E3,O33)))),"#,##0.000")&amp;IF((IF(ABS(O33)&gt;=1E12,"TB",IF(ABS(O33)&gt;=1E9,"GB",IF(ABS(O33)&gt;=1E6,"MB",IF(ABS(O33)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(O33)&gt;=1E12,"TB",IF(ABS(O33)&gt;=1E9,"GB",IF(ABS(O33)&gt;=1E6,"MB",IF(ABS(O33)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>166.349 GB</v>
+      </c>
+      <c r="M33" s="33" t="str">
+        <f>TEXT(IF(ABS(P33)&gt;=1E12,P33/1E12,IF(ABS(P33)&gt;=1E9,P33/1E9,IF(ABS(P33)&gt;=1E6,P33/1E6,IF(ABS(P33)&gt;=1E3,P33/1E3,P33)))),"#,##0.000")&amp;IF((IF(ABS(P33)&gt;=1E12,"TB",IF(ABS(P33)&gt;=1E9,"GB",IF(ABS(P33)&gt;=1E6,"MB",IF(ABS(P33)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(P33)&gt;=1E12,"TB",IF(ABS(P33)&gt;=1E9,"GB",IF(ABS(P33)&gt;=1E6,"MB",IF(ABS(P33)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>29.582 GB</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="O33" s="32">
+        <f>G27</f>
+        <v>166349315548.0</v>
+      </c>
+      <c r="P33" s="32">
+        <f>H27</f>
+        <v>29581867388.0</v>
+      </c>
       <c r="S33" s="4" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="T33" s="32">
         <f>H28/1e+12</f>
         <v>55.652568907776</v>
       </c>
     </row>
-    <row r="34" spans="19:21">
+    <row r="34" spans="11:21">
+      <c r="K34" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="L34" s="33" t="str">
+        <f>TEXT(IF(ABS(O34)&gt;=1E12,O34/1E12,IF(ABS(O34)&gt;=1E9,O34/1E9,IF(ABS(O34)&gt;=1E6,O34/1E6,IF(ABS(O34)&gt;=1E3,O34/1E3,O34)))),"#,##0.000")&amp;IF((IF(ABS(O34)&gt;=1E12,"TB",IF(ABS(O34)&gt;=1E9,"GB",IF(ABS(O34)&gt;=1E6,"MB",IF(ABS(O34)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(O34)&gt;=1E12,"TB",IF(ABS(O34)&gt;=1E9,"GB",IF(ABS(O34)&gt;=1E6,"MB",IF(ABS(O34)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>166.349 GB</v>
+      </c>
+      <c r="M34" s="33" t="str">
+        <f>TEXT(IF(ABS(P34)&gt;=1E12,P34/1E12,IF(ABS(P34)&gt;=1E9,P34/1E9,IF(ABS(P34)&gt;=1E6,P34/1E6,IF(ABS(P34)&gt;=1E3,P34/1E3,P34)))),"#,##0.000")&amp;IF((IF(ABS(P34)&gt;=1E12,"TB",IF(ABS(P34)&gt;=1E9,"GB",IF(ABS(P34)&gt;=1E6,"MB",IF(ABS(P34)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(P34)&gt;=1E12,"TB",IF(ABS(P34)&gt;=1E9,"GB",IF(ABS(P34)&gt;=1E6,"MB",IF(ABS(P34)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>29.582 GB</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="O34" s="32">
+        <f>I27</f>
+        <v>166349315548.0</v>
+      </c>
+      <c r="P34" s="32">
+        <f>J27</f>
+        <v>29581867388.0</v>
+      </c>
       <c r="S34" s="4" t="s">
         <v>441</v>
       </c>
@@ -12441,27 +12873,27 @@
         <v>0.14035575211</v>
       </c>
     </row>
-    <row r="35" spans="19:21">
+    <row r="35" spans="11:21">
       <c r="S35" s="4" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="T35" s="32">
         <f>J28/1e+12</f>
         <v>0.023549694126</v>
       </c>
     </row>
-    <row r="38" spans="19:21">
+    <row r="38" spans="11:21">
       <c r="S38" s="3" t="s">
         <v>2</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="39" spans="19:21">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="39" spans="11:21">
       <c r="S39" s="4" t="s">
         <v>40</v>
       </c>
@@ -12474,7 +12906,7 @@
         <v>23.172382457856</v>
       </c>
     </row>
-    <row r="40" spans="19:21">
+    <row r="40" spans="11:21">
       <c r="S40" s="4" t="s">
         <v>59</v>
       </c>
@@ -12487,9 +12919,9 @@
         <v>31.765578121216</v>
       </c>
     </row>
-    <row r="41" spans="19:21">
+    <row r="41" spans="11:21">
       <c r="S41" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="T41" s="32">
         <f>G7/1e+12</f>
@@ -12500,18 +12932,18 @@
         <v>0.714608328704</v>
       </c>
     </row>
-    <row r="45" spans="19:21">
+    <row r="45" spans="11:21">
       <c r="S45" s="3" t="s">
         <v>2</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="46" spans="19:21">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="46" spans="11:21">
       <c r="S46" s="4" t="s">
         <v>40</v>
       </c>
@@ -12524,7 +12956,7 @@
         <v>19.452461056</v>
       </c>
     </row>
-    <row r="47" spans="19:21">
+    <row r="47" spans="11:21">
       <c r="S47" s="4" t="s">
         <v>59</v>
       </c>
@@ -12537,9 +12969,9 @@
         <v>3.877634048</v>
       </c>
     </row>
-    <row r="48" spans="19:21">
+    <row r="48" spans="11:21">
       <c r="S48" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="T48" s="32">
         <f>I7/1e+09</f>
@@ -12555,10 +12987,10 @@
         <v>2</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="53" spans="19:21">
@@ -12589,7 +13021,7 @@
     </row>
     <row r="55" spans="19:21">
       <c r="S55" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="T55" s="32">
         <f>G21/1e+09</f>
@@ -12605,43 +13037,140 @@
         <v>2</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="19:21">
       <c r="S60" s="4" t="s">
-        <v>492</v>
+        <v>40</v>
       </c>
       <c r="T60" s="32">
+        <f>I19/1e+09</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="U60" s="32">
+        <f>J19/1e+09</f>
+        <v>2.23750496</v>
+      </c>
+    </row>
+    <row r="61" spans="19:21">
+      <c r="S61" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="T61" s="32">
+        <f>I20/1e+09</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="U61" s="32">
+        <f>J20/1e+09</f>
+        <v>19.57794048</v>
+      </c>
+    </row>
+    <row r="62" spans="19:21">
+      <c r="S62" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="T62" s="32">
+        <f>I21/1e+09</f>
+        <v>3.314423644</v>
+      </c>
+      <c r="U62" s="32">
+        <f>J21/1e+09</f>
+        <v>0.534376892</v>
+      </c>
+    </row>
+    <row r="66" spans="19:20">
+      <c r="S66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="67" spans="19:20">
+      <c r="S67" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="T67" s="32">
         <f>G27/1e+09</f>
         <v>166.349315548</v>
       </c>
-      <c r="U60" s="32">
+    </row>
+    <row r="68" spans="19:20">
+      <c r="S68" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="T68" s="32">
         <f>H27/1e+09</f>
         <v>29.581867388</v>
       </c>
     </row>
-    <row r="61" spans="19:21">
-      <c r="S61" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="T61" s="32">
+    <row r="73" spans="19:20">
+      <c r="S73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="74" spans="19:20">
+      <c r="S74" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="T74" s="32">
         <f>I27/1e+09</f>
         <v>166.349315548</v>
       </c>
-      <c r="U61" s="32">
+    </row>
+    <row r="75" spans="19:20">
+      <c r="S75" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="T75" s="32">
         <f>J27/1e+09</f>
         <v>29.581867388</v>
       </c>
     </row>
+    <row r="97" spans="1:6" ht="36" customHeight="1">
+      <c r="A97" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F97" s="2"/>
+    </row>
+    <row r="121" spans="1:6" ht="36" customHeight="1">
+      <c r="A121" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F121" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="E121:F121"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12659,17 +13188,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="30" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -12680,10 +13209,10 @@
         <v>438</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>363</v>
@@ -12702,7 +13231,7 @@
         <v>123.969 GFLOPs</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G6" s="32">
         <f>'Prefill_8K'!$AF$14</f>
@@ -12726,7 +13255,7 @@
         <v>15.240 GFLOPs</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G7" s="32">
         <f>'Prefill_8K'!$AF$15</f>
@@ -12750,7 +13279,7 @@
         <v>1.146 GFLOPs</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G8" s="32">
         <f>'Prefill_8K'!$AO$48</f>
@@ -12774,7 +13303,7 @@
         <v>140.356 GFLOPs</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G9" s="32">
         <f>'Prefill_8K'!$AF$13</f>
@@ -12798,7 +13327,7 @@
         <v>1,049.223 GB/s</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G10" s="32">
         <f>'Prefill_8K'!$AG$14/(PrefillTargetMs/1000)/1E9</f>
@@ -12822,7 +13351,7 @@
         <v>462.703 GB/s</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G11" s="32">
         <f>'Prefill_8K'!$AG$15/(PrefillTargetMs/1000)/1E9</f>
@@ -12846,7 +13375,7 @@
         <v>226.865 GB/s</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G12" s="32">
         <f>'Prefill_8K'!$AQ$48/(PrefillTargetMs/1000)/1E9</f>
@@ -12870,7 +13399,7 @@
         <v>140.356 GFLOPs</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="G13" s="32">
         <f>'Prefill_8K'!$AF$13</f>
@@ -12894,7 +13423,7 @@
         <v>0.000 B</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="G14" s="32">
         <f>'Prefill_8K'!$AS$48</f>
@@ -12942,7 +13471,7 @@
         <v>5.086 G</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="G16" s="32">
         <f>'Prefill_8K'!$AY$49</f>
@@ -12990,7 +13519,7 @@
         <v>1.093 G</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G18" s="32">
         <f>'Prefill_8K'!$AY$51</f>
@@ -13014,7 +13543,7 @@
         <v>284.335 G</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="G19" s="32">
         <f>'Prefill_8K'!$AY$52</f>
@@ -13038,7 +13567,7 @@
         <v>7.451 GB</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G20" s="32">
         <f>'Prefill_8K'!$BA$49</f>
@@ -13062,7 +13591,7 @@
         <v>148.351 GB</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="G21" s="32">
         <f>'Prefill_8K'!$BA$50</f>
@@ -13086,7 +13615,7 @@
         <v>3.314 GB</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G22" s="32">
         <f>'Prefill_8K'!$BA$51</f>
@@ -13110,7 +13639,7 @@
         <v>159.117 GB</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="G23" s="32">
         <f>'Prefill_8K'!$BA$52</f>
@@ -13134,7 +13663,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G24" s="32">
         <f>'Prefill_8K'!$U$35</f>
@@ -13158,7 +13687,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G25" s="32">
         <f>'Prefill_8K'!$U$36</f>
@@ -13182,7 +13711,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G26" s="32">
         <f>'Prefill_8K'!$U$37</f>
@@ -13206,7 +13735,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G27" s="32">
         <f>'Prefill_8K'!$U$38</f>
@@ -13230,7 +13759,7 @@
         <v>166.349 GB</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="G28" s="32">
         <f>'Prefill_8K'!$BA$52+'Prefill_8K'!$U$38</f>
@@ -13243,7 +13772,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="30" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -13254,10 +13783,10 @@
         <v>438</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>363</v>
@@ -13276,7 +13805,7 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G32" s="32">
         <f>'Prefill_8K'!$AI$14</f>
@@ -13300,7 +13829,7 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G33" s="32">
         <f>'Prefill_8K'!$AI$15</f>
@@ -13324,7 +13853,7 @@
         <v>219.599 MFLOPs</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G34" s="32">
         <f>'Prefill_8K'!$AP$48</f>
@@ -13348,7 +13877,7 @@
         <v>23.550 GFLOPs</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G35" s="32">
         <f>'Prefill_8K'!$AI$13</f>
@@ -13372,7 +13901,7 @@
         <v>403.523 GB/s</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G36" s="32">
         <f>'Prefill_8K'!$AJ$14/(PrefillTargetMs/1000)/1E9</f>
@@ -13396,7 +13925,7 @@
         <v>160.521 GB/s</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G37" s="32">
         <f>'Prefill_8K'!$AJ$15/(PrefillTargetMs/1000)/1E9</f>
@@ -13420,7 +13949,7 @@
         <v>41.483 GB/s</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G38" s="32">
         <f>'Prefill_8K'!$AR$48/(PrefillTargetMs/1000)/1E9</f>
@@ -13444,7 +13973,7 @@
         <v>23.550 GFLOPs</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="G39" s="32">
         <f>'Prefill_8K'!$AI$13</f>
@@ -13468,7 +13997,7 @@
         <v>5.865 MB</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="G40" s="32">
         <f>'Prefill_8K'!$AT$48</f>
@@ -13516,7 +14045,7 @@
         <v>1.140 G</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="G42" s="32">
         <f>'Prefill_8K'!$AZ$49</f>
@@ -13564,7 +14093,7 @@
         <v>166.690 M</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G44" s="32">
         <f>'Prefill_8K'!$AZ$51</f>
@@ -13588,7 +14117,7 @@
         <v>37.064 G</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="G45" s="32">
         <f>'Prefill_8K'!$AZ$52</f>
@@ -13612,7 +14141,7 @@
         <v>2.238 GB</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G46" s="32">
         <f>'Prefill_8K'!$BB$49</f>
@@ -13636,7 +14165,7 @@
         <v>19.578 GB</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="G47" s="32">
         <f>'Prefill_8K'!$BB$50</f>
@@ -13660,7 +14189,7 @@
         <v>534.377 MB</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G48" s="32">
         <f>'Prefill_8K'!$BB$51</f>
@@ -13684,7 +14213,7 @@
         <v>22.350 GB</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="G49" s="32">
         <f>'Prefill_8K'!$BB$52</f>
@@ -13708,7 +14237,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G50" s="32">
         <f>'Prefill_8K'!$X$35</f>
@@ -13732,7 +14261,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G51" s="32">
         <f>'Prefill_8K'!$X$36</f>
@@ -13756,7 +14285,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G52" s="32">
         <f>'Prefill_8K'!$X$37</f>
@@ -13780,7 +14309,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G53" s="32">
         <f>'Prefill_8K'!$X$38</f>
@@ -13804,7 +14333,7 @@
         <v>29.582 GB</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="G54" s="32">
         <f>'Prefill_8K'!$BB$52+'Prefill_8K'!$X$38</f>
@@ -13836,12 +14365,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -13849,19 +14378,19 @@
         <v>421</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>423</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13872,7 +14401,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D4" s="36">
         <f>IF(C4="window",0,IF(C4="short",ShortRatio,LongRatio))</f>
@@ -13895,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D5" s="36">
         <f>IF(C5="window",0,IF(C5="short",ShortRatio,LongRatio))</f>
@@ -13918,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D6" s="36">
         <f>IF(C6="window",0,IF(C6="short",ShortRatio,LongRatio))</f>
@@ -13941,7 +14470,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D7" s="36">
         <f>IF(C7="window",0,IF(C7="short",ShortRatio,LongRatio))</f>
@@ -13964,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D8" s="36">
         <f>IF(C8="window",0,IF(C8="short",ShortRatio,LongRatio))</f>
@@ -13987,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D9" s="36">
         <f>IF(C9="window",0,IF(C9="short",ShortRatio,LongRatio))</f>
@@ -14010,7 +14539,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D10" s="36">
         <f>IF(C10="window",0,IF(C10="short",ShortRatio,LongRatio))</f>
@@ -14033,7 +14562,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D11" s="36">
         <f>IF(C11="window",0,IF(C11="short",ShortRatio,LongRatio))</f>
@@ -14056,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D12" s="36">
         <f>IF(C12="window",0,IF(C12="short",ShortRatio,LongRatio))</f>
@@ -14079,7 +14608,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D13" s="36">
         <f>IF(C13="window",0,IF(C13="short",ShortRatio,LongRatio))</f>
@@ -14102,7 +14631,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D14" s="36">
         <f>IF(C14="window",0,IF(C14="short",ShortRatio,LongRatio))</f>
@@ -14125,7 +14654,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D15" s="36">
         <f>IF(C15="window",0,IF(C15="short",ShortRatio,LongRatio))</f>
@@ -14148,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D16" s="36">
         <f>IF(C16="window",0,IF(C16="short",ShortRatio,LongRatio))</f>
@@ -14171,7 +14700,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D17" s="36">
         <f>IF(C17="window",0,IF(C17="short",ShortRatio,LongRatio))</f>
@@ -14194,7 +14723,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D18" s="36">
         <f>IF(C18="window",0,IF(C18="short",ShortRatio,LongRatio))</f>
@@ -14217,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D19" s="36">
         <f>IF(C19="window",0,IF(C19="short",ShortRatio,LongRatio))</f>
@@ -14240,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D20" s="36">
         <f>IF(C20="window",0,IF(C20="short",ShortRatio,LongRatio))</f>
@@ -14263,7 +14792,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D21" s="36">
         <f>IF(C21="window",0,IF(C21="short",ShortRatio,LongRatio))</f>
@@ -14286,7 +14815,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D22" s="36">
         <f>IF(C22="window",0,IF(C22="short",ShortRatio,LongRatio))</f>
@@ -14309,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D23" s="36">
         <f>IF(C23="window",0,IF(C23="short",ShortRatio,LongRatio))</f>
@@ -14332,7 +14861,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D24" s="36">
         <f>IF(C24="window",0,IF(C24="short",ShortRatio,LongRatio))</f>
@@ -14355,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D25" s="36">
         <f>IF(C25="window",0,IF(C25="short",ShortRatio,LongRatio))</f>
@@ -14378,7 +14907,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D26" s="36">
         <f>IF(C26="window",0,IF(C26="short",ShortRatio,LongRatio))</f>
@@ -14401,7 +14930,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D27" s="36">
         <f>IF(C27="window",0,IF(C27="short",ShortRatio,LongRatio))</f>
@@ -14424,7 +14953,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D28" s="36">
         <f>IF(C28="window",0,IF(C28="short",ShortRatio,LongRatio))</f>
@@ -14447,7 +14976,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D29" s="36">
         <f>IF(C29="window",0,IF(C29="short",ShortRatio,LongRatio))</f>
@@ -14470,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D30" s="36">
         <f>IF(C30="window",0,IF(C30="short",ShortRatio,LongRatio))</f>
@@ -14493,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D31" s="36">
         <f>IF(C31="window",0,IF(C31="short",ShortRatio,LongRatio))</f>
@@ -14516,7 +15045,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D32" s="36">
         <f>IF(C32="window",0,IF(C32="short",ShortRatio,LongRatio))</f>
@@ -14539,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D33" s="36">
         <f>IF(C33="window",0,IF(C33="short",ShortRatio,LongRatio))</f>
@@ -14562,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D34" s="36">
         <f>IF(C34="window",0,IF(C34="short",ShortRatio,LongRatio))</f>
@@ -14585,7 +15114,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D35" s="36">
         <f>IF(C35="window",0,IF(C35="short",ShortRatio,LongRatio))</f>
@@ -14608,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D36" s="36">
         <f>IF(C36="window",0,IF(C36="short",ShortRatio,LongRatio))</f>
@@ -14631,7 +15160,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D37" s="36">
         <f>IF(C37="window",0,IF(C37="short",ShortRatio,LongRatio))</f>
@@ -14654,7 +15183,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D38" s="36">
         <f>IF(C38="window",0,IF(C38="short",ShortRatio,LongRatio))</f>
@@ -14677,7 +15206,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D39" s="36">
         <f>IF(C39="window",0,IF(C39="short",ShortRatio,LongRatio))</f>
@@ -14700,7 +15229,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D40" s="36">
         <f>IF(C40="window",0,IF(C40="short",ShortRatio,LongRatio))</f>
@@ -14723,7 +15252,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D41" s="36">
         <f>IF(C41="window",0,IF(C41="short",ShortRatio,LongRatio))</f>
@@ -14746,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D42" s="36">
         <f>IF(C42="window",0,IF(C42="short",ShortRatio,LongRatio))</f>
@@ -14769,7 +15298,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D43" s="36">
         <f>IF(C43="window",0,IF(C43="short",ShortRatio,LongRatio))</f>
@@ -14792,7 +15321,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D44" s="36">
         <f>IF(C44="window",0,IF(C44="short",ShortRatio,LongRatio))</f>
@@ -14815,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D45" s="36">
         <f>IF(C45="window",0,IF(C45="short",ShortRatio,LongRatio))</f>
@@ -14838,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D46" s="36">
         <f>IF(C46="window",0,IF(C46="short",ShortRatio,LongRatio))</f>
@@ -14861,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D47" s="36">
         <f>IF(C47="window",0,IF(C47="short",ShortRatio,LongRatio))</f>
@@ -14884,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D48" s="36">
         <f>IF(C48="window",0,IF(C48="short",ShortRatio,LongRatio))</f>
@@ -14907,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D49" s="36">
         <f>IF(C49="window",0,IF(C49="short",ShortRatio,LongRatio))</f>
@@ -14930,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D50" s="36">
         <f>IF(C50="window",0,IF(C50="short",ShortRatio,LongRatio))</f>
@@ -14953,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D51" s="36">
         <f>IF(C51="window",0,IF(C51="short",ShortRatio,LongRatio))</f>
@@ -14976,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D52" s="36">
         <f>IF(C52="window",0,IF(C52="short",ShortRatio,LongRatio))</f>
@@ -14999,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D53" s="36">
         <f>IF(C53="window",0,IF(C53="short",ShortRatio,LongRatio))</f>
@@ -15022,7 +15551,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D54" s="36">
         <f>IF(C54="window",0,IF(C54="short",ShortRatio,LongRatio))</f>
@@ -15045,7 +15574,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D55" s="36">
         <f>IF(C55="window",0,IF(C55="short",ShortRatio,LongRatio))</f>
@@ -15068,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D56" s="36">
         <f>IF(C56="window",0,IF(C56="short",ShortRatio,LongRatio))</f>
@@ -15091,7 +15620,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D57" s="36">
         <f>IF(C57="window",0,IF(C57="short",ShortRatio,LongRatio))</f>
@@ -15114,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D58" s="36">
         <f>IF(C58="window",0,IF(C58="short",ShortRatio,LongRatio))</f>
@@ -15137,7 +15666,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D59" s="36">
         <f>IF(C59="window",0,IF(C59="short",ShortRatio,LongRatio))</f>
@@ -15160,7 +15689,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D60" s="36">
         <f>IF(C60="window",0,IF(C60="short",ShortRatio,LongRatio))</f>
@@ -15183,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D61" s="36">
         <f>IF(C61="window",0,IF(C61="short",ShortRatio,LongRatio))</f>
@@ -15206,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D62" s="36">
         <f>IF(C62="window",0,IF(C62="short",ShortRatio,LongRatio))</f>
@@ -15229,7 +15758,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D63" s="36">
         <f>IF(C63="window",0,IF(C63="short",ShortRatio,LongRatio))</f>
@@ -15252,7 +15781,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D64" s="36">
         <f>IF(C64="window",0,IF(C64="short",ShortRatio,LongRatio))</f>
@@ -15275,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D65" s="36">
         <f>IF(C65="window",0,IF(C65="short",ShortRatio,LongRatio))</f>
@@ -15298,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D66" s="36">
         <f>IF(C66="window",0,IF(C66="short",ShortRatio,LongRatio))</f>
@@ -15321,7 +15850,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D67" s="36">
         <f>IF(C67="window",0,IF(C67="short",ShortRatio,LongRatio))</f>
@@ -15361,15 +15890,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>523</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15377,31 +15906,31 @@
         <v>359</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -15409,39 +15938,39 @@
         <v>59</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -15449,47 +15978,47 @@
         <v>409</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/calculate/deepseek_v4_flash_calculator.xlsx
+++ b/calculate/deepseek_v4_flash_calculator.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="541">
   <si>
     <t>DeepSeek V4 Flash - Editable Architecture Parameters</t>
   </si>
@@ -1134,7 +1134,7 @@
     <t>Inference-Path Data Types (dtype) Overview</t>
   </si>
   <si>
-    <t>集中记录各算子模块的参数存储、激活类型和逐层注意力/路由模式。</t>
+    <t>集中记录各算子模块的参数存储、Scale 类型、激活类型和逐层注意力/路由模式。</t>
   </si>
   <si>
     <t>Data types (dtype): module-level storage and compute types</t>
@@ -1146,7 +1146,10 @@
     <t>Module/tensor</t>
   </si>
   <si>
-    <t>Checkpoint/parameter storage</t>
+    <t>Parameter storage / inference dtype</t>
+  </si>
+  <si>
+    <t>Scale type</t>
   </si>
   <si>
     <t>Activation/intermediate computation</t>
@@ -1167,7 +1170,10 @@
     <t>Standard quantized linear layers</t>
   </si>
   <si>
-    <t>FP8 E4M3 + FP8 E8M0 scale factors</t>
+    <t>FP8 E4M3 weights</t>
+  </si>
+  <si>
+    <t>UE8M0 (E8M0), unsigned exponent-only scale</t>
   </si>
   <si>
     <t>Dynamic FP8 activation quantization</t>
@@ -1185,16 +1191,22 @@
     <t>FP8 GEMM; BF16 input dynamically quantized</t>
   </si>
   <si>
-    <t>大多数注意力线性权重。</t>
+    <t>wq_a/wq_b/wkv/wo_b 的权重为 FP8 E4M3；Scale 为无符号 UE8M0/E8M0。</t>
   </si>
   <si>
     <t>Attention output projection wo_a</t>
   </si>
   <si>
+    <t>BF16 inference weights (checkpoint FP8 converted)</t>
+  </si>
+  <si>
+    <t>N/A (BF16 inference weights)</t>
+  </si>
+  <si>
     <t>BF16 tensor product (einsum)</t>
   </si>
   <si>
-    <t>检查点中为 FP8，转换后在推理实现中按 BF16 使用。</t>
+    <t>wo_a 不按 FP8 权重使用；检查点中的 FP8 tensor 在推理实现中转换并按 BF16 使用。</t>
   </si>
   <si>
     <t>RMSNorm weights and normalization</t>
@@ -1209,6 +1221,90 @@
     <t>Norm 计算先转 FP32 以提高稳定性。</t>
   </si>
   <si>
+    <t>Shared experts w1/w2/w3</t>
+  </si>
+  <si>
+    <t>FP8 GEMM; SwiGLU FP32</t>
+  </si>
+  <si>
+    <t>每层 1 个共享专家，跨 TP Rank 复制。</t>
+  </si>
+  <si>
+    <t>Router scores/routing weights</t>
+  </si>
+  <si>
+    <t>FP32 bias; INT32 Token-ID lookup table</t>
+  </si>
+  <si>
+    <t>sqrt(softplus) 评分、Top-K 和归一化在 FP32 中完成；前 3 层使用 Token-ID 查表路由。</t>
+  </si>
+  <si>
+    <t>Routed experts w1/w2/w3</t>
+  </si>
+  <si>
+    <t>FP4 E2M1 packed weights</t>
+  </si>
+  <si>
+    <t>FP4 GEMM; SwiGLU FP32; output cast to BF16</t>
+  </si>
+  <si>
+    <t>专家权重数据类型为 FP4 E2M1；每个令牌激活 6 个路由专家。</t>
+  </si>
+  <si>
+    <t>mHC parameters / attention sinks</t>
+  </si>
+  <si>
+    <t>HC 混合、Sinkhorn 与 Sink 参数使用 FP32。</t>
+  </si>
+  <si>
+    <t>KV cache (main + Indexer)</t>
+  </si>
+  <si>
+    <t>BF16 unquantized</t>
+  </si>
+  <si>
+    <t>N/A (unquantized cache)</t>
+  </si>
+  <si>
+    <t>BF16 cache entries</t>
+  </si>
+  <si>
+    <t>KV cache 类型为未量化 BF16；主 KV 与 Indexer KV 均使用 BF16，局部非 RoPE 维度的 FP8 仅是计算模拟，不改变缓存存储类型。</t>
+  </si>
+  <si>
+    <t>Layers 0-2</t>
+  </si>
+  <si>
+    <t>Token-ID routing table</t>
+  </si>
+  <si>
+    <t>INT32</t>
+  </si>
+  <si>
+    <t>INT32 indexing</t>
+  </si>
+  <si>
+    <t>前 3 层使用令牌编号到专家编号的预计算路由。</t>
+  </si>
+  <si>
+    <t>Ratio-4 layers</t>
+  </si>
+  <si>
+    <t>Indexer projections and scoring</t>
+  </si>
+  <si>
+    <t>wq_b FP8; weights_proj BF16</t>
+  </si>
+  <si>
+    <t>wq_b: UE8M0 (E8M0); weights_proj: N/A</t>
+  </si>
+  <si>
+    <t>QAT/FP4 simulated QKV; FP32 scoring</t>
+  </si>
+  <si>
+    <t>仅 ratio-4 层启用 Indexer。</t>
+  </si>
+  <si>
     <t>Ratio-4 / ratio-128 layers</t>
   </si>
   <si>
@@ -1224,406 +1320,334 @@
     <t>Compressor 参数在推理实现中提升到 FP32。</t>
   </si>
   <si>
-    <t>Ratio-4 layers</t>
-  </si>
-  <si>
-    <t>Indexer projections and scoring</t>
-  </si>
-  <si>
-    <t>wq_b FP8; weights_proj BF16</t>
-  </si>
-  <si>
-    <t>QAT/FP4 simulated QKV; FP32 scoring</t>
-  </si>
-  <si>
-    <t>仅 ratio-4 层启用 Indexer。</t>
-  </si>
-  <si>
-    <t>Routed experts w1/w2/w3</t>
-  </si>
-  <si>
-    <t>FP4 E2M1 packed + FP8 E8M0 scale factors</t>
-  </si>
-  <si>
-    <t>FP4 GEMM; SwiGLU FP32; output cast to BF16</t>
-  </si>
-  <si>
-    <t>专家数据类型为 fp4；每个令牌激活 6 个路由专家。</t>
-  </si>
-  <si>
-    <t>Shared experts w1/w2/w3</t>
-  </si>
-  <si>
-    <t>FP8 GEMM; SwiGLU FP32</t>
-  </si>
-  <si>
-    <t>每层 1 个共享专家，跨 TP Rank 复制。</t>
-  </si>
-  <si>
-    <t>Router scores/routing weights</t>
-  </si>
-  <si>
-    <t>FP32 bias; INT32 Token-ID lookup table</t>
-  </si>
-  <si>
-    <t>sqrt(softplus) 评分、Top-K 和归一化在 FP32 中完成；前 3 层使用 Token-ID 查表路由。</t>
-  </si>
-  <si>
-    <t>Layers 0-2</t>
-  </si>
-  <si>
-    <t>Token-ID routing table</t>
-  </si>
-  <si>
-    <t>INT32</t>
-  </si>
-  <si>
-    <t>INT32 indexing</t>
-  </si>
-  <si>
-    <t>前 3 层使用令牌编号到专家编号的预计算路由。</t>
-  </si>
-  <si>
-    <t>mHC parameters / attention sinks</t>
-  </si>
-  <si>
-    <t>HC 混合、Sinkhorn 与 Sink 参数使用 FP32。</t>
+    <t>Model tail</t>
+  </si>
+  <si>
+    <t>Final normalization / HC head</t>
+  </si>
+  <si>
+    <t>FP32 inference parameters</t>
+  </si>
+  <si>
+    <t>最终 HC 归约与 RMSNorm。</t>
+  </si>
+  <si>
+    <t>LM head / Logits</t>
+  </si>
+  <si>
+    <t>Checkpoint BF16; FP32 implementation parameters</t>
+  </si>
+  <si>
+    <t>FP32 linear layer and Logits</t>
+  </si>
+  <si>
+    <t>词表并行；Logits 以 FP32 计算。</t>
+  </si>
+  <si>
+    <t>43-layer dtype, attention, and routing modes</t>
+  </si>
+  <si>
+    <t>Layer ID</t>
+  </si>
+  <si>
+    <t>Attention mode</t>
+  </si>
+  <si>
+    <t>Compression ratio</t>
+  </si>
+  <si>
+    <t>Routing mode</t>
+  </si>
+  <si>
+    <t>Hidden state / residual</t>
+  </si>
+  <si>
+    <t>Main attention projections</t>
+  </si>
+  <si>
+    <t>Normalization / HC / Router computation</t>
+  </si>
+  <si>
+    <t>Window</t>
+  </si>
+  <si>
+    <t>Token-ID lookup routing (INT32)</t>
+  </si>
+  <si>
+    <t>wq_a/wq_b/wkv/wo_b: FP8 E4M3 weights; wo_a: BF16 inference weights</t>
+  </si>
+  <si>
+    <t>FP4 E2M1</t>
+  </si>
+  <si>
+    <t>FP8 E4M3</t>
+  </si>
+  <si>
+    <t>Short-compression sparse</t>
+  </si>
+  <si>
+    <t>Long-compression</t>
+  </si>
+  <si>
+    <t>Score routing (FP32)</t>
+  </si>
+  <si>
+    <t>TP1 / TP8 Inference Resource Comparison Charts</t>
+  </si>
+  <si>
+    <t>内存容量、参数量、计算量与通信量集中在一张资源表；隐藏列仅保留公式和图表缩放源。</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Prefill TP1</t>
+  </si>
+  <si>
+    <t>Prefill TP8/rank</t>
+  </si>
+  <si>
+    <t>Decode TP1</t>
+  </si>
+  <si>
+    <t>Decode TP8/rank</t>
+  </si>
+  <si>
+    <t>Attention FLOPs</t>
+  </si>
+  <si>
+    <t>单次预填充或解码步骤的每 Rank 逻辑 FLOPs。</t>
+  </si>
+  <si>
+    <t>MoE FLOPs</t>
+  </si>
+  <si>
+    <t>其他推理 FLOPs</t>
+  </si>
+  <si>
+    <t>总推理 FLOPs</t>
+  </si>
+  <si>
+    <t>通信量</t>
+  </si>
+  <si>
+    <t>Ring 集合通信每 Rank 发送加接收；TP1 为 0。</t>
+  </si>
+  <si>
+    <t>注意力逻辑参数量</t>
+  </si>
+  <si>
+    <t>注意力投影、Compressor、Indexer。</t>
+  </si>
+  <si>
+    <t>混合专家逻辑参数量</t>
+  </si>
+  <si>
+    <t>路由/共享专家与 Router。</t>
+  </si>
+  <si>
+    <t>其他逻辑参数量</t>
+  </si>
+  <si>
+    <t>Embedding、LM Head、HC 与 Norm。</t>
+  </si>
+  <si>
+    <t>总逻辑参数量</t>
+  </si>
+  <si>
+    <t>不包含 MTP。</t>
+  </si>
+  <si>
+    <t>注意力参数容量</t>
+  </si>
+  <si>
+    <t>按推理 dtype 与量化 Scale 计算。</t>
+  </si>
+  <si>
+    <t>混合专家参数容量</t>
+  </si>
+  <si>
+    <t>路由专家 FP4、共享专家 FP8、Router 复制。</t>
+  </si>
+  <si>
+    <t>其他参数容量</t>
+  </si>
+  <si>
+    <t>总参数容量</t>
+  </si>
+  <si>
+    <t>每 Rank 静态参数驻留。</t>
+  </si>
+  <si>
+    <t>Effective main KV cache</t>
+  </si>
+  <si>
+    <t>KV 与 Compressor 状态在当前实现中每个 TP Rank 复制。</t>
+  </si>
+  <si>
+    <t>Effective Indexer KV cache</t>
+  </si>
+  <si>
+    <t>Compressor 状态</t>
+  </si>
+  <si>
+    <t>Preallocated KV + state</t>
+  </si>
+  <si>
+    <t>Effective KV cache + state</t>
+  </si>
+  <si>
+    <t>当前场景有效 KV；包含主 KV、Indexer KV 和 Compressor/Indexer State。</t>
+  </si>
+  <si>
+    <t>Total capacity per inference / rank</t>
+  </si>
+  <si>
+    <t>参数 + 按 MaxContext 预分配的 KV/状态；不含临时工作区。</t>
+  </si>
+  <si>
+    <t>一次推理所需计算量</t>
+  </si>
+  <si>
+    <t>单次推理调用的单 Rank 总 FLOPs。</t>
+  </si>
+  <si>
+    <t>One-inference TFLOPs</t>
+  </si>
+  <si>
+    <t>Prefill TP8</t>
+  </si>
+  <si>
+    <t>Decode TP8</t>
+  </si>
+  <si>
+    <t>Capacity GB</t>
+  </si>
+  <si>
+    <t>TP1 TFLOPs</t>
+  </si>
+  <si>
+    <t>TP8 TFLOPs</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>TP1 GFLOPs</t>
+  </si>
+  <si>
+    <t>TP8 GFLOPs</t>
+  </si>
+  <si>
+    <t>TP1 GB</t>
+  </si>
+  <si>
+    <t>TP8 GB</t>
+  </si>
+  <si>
+    <t>具体内容（Static parameter capacity per rank）：Attention、MoE、Embedding、LM Head、Norm、HC 等静态模型参数及量化 Scale；不含 KV Cache、Compressor State、临时激活和集合通信缓冲区。Prefill/Decode 两图的静态参数数据相同。</t>
+  </si>
+  <si>
+    <t>Attention static parameter</t>
+  </si>
+  <si>
+    <t>MoE static parameter</t>
   </si>
   <si>
     <t>KV cache</t>
   </si>
   <si>
-    <t>BF16; partial non-RoPE dimensions simulated with FP8</t>
-  </si>
-  <si>
-    <t>当前推理实现中的 KV 缓存为 BF16。</t>
-  </si>
-  <si>
-    <t>Model tail</t>
-  </si>
-  <si>
-    <t>Final normalization / HC head</t>
-  </si>
-  <si>
-    <t>FP32 inference parameters</t>
-  </si>
-  <si>
-    <t>最终 HC 归约与 RMSNorm。</t>
-  </si>
-  <si>
-    <t>LM head / Logits</t>
-  </si>
-  <si>
-    <t>Checkpoint BF16; FP32 implementation parameters</t>
-  </si>
-  <si>
-    <t>FP32 linear layer and Logits</t>
-  </si>
-  <si>
-    <t>词表并行；Logits 以 FP32 计算。</t>
-  </si>
-  <si>
-    <t>43-layer dtype, attention, and routing modes</t>
-  </si>
-  <si>
-    <t>Layer ID</t>
-  </si>
-  <si>
-    <t>Attention mode</t>
-  </si>
-  <si>
-    <t>Compression ratio</t>
-  </si>
-  <si>
-    <t>Routing mode</t>
-  </si>
-  <si>
-    <t>Hidden state / residual</t>
-  </si>
-  <si>
-    <t>Main attention projections</t>
-  </si>
-  <si>
-    <t>Normalization / HC / Router computation</t>
-  </si>
-  <si>
-    <t>Window</t>
-  </si>
-  <si>
-    <t>Token-ID lookup routing (INT32)</t>
-  </si>
-  <si>
-    <t>FP8 E4M3; wo_a BF16</t>
-  </si>
-  <si>
-    <t>FP4 E2M1</t>
-  </si>
-  <si>
-    <t>FP8 E4M3</t>
-  </si>
-  <si>
-    <t>Short-compression sparse</t>
-  </si>
-  <si>
-    <t>Long-compression</t>
-  </si>
-  <si>
-    <t>Score routing (FP32)</t>
-  </si>
-  <si>
-    <t>TP1 / TP8 Inference Resource Comparison Charts</t>
-  </si>
-  <si>
-    <t>内存容量、参数量、计算量与通信量集中在一张资源表；隐藏列仅保留公式和图表缩放源。</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>Prefill TP1</t>
-  </si>
-  <si>
-    <t>Prefill TP8/rank</t>
-  </si>
-  <si>
-    <t>Decode TP1</t>
-  </si>
-  <si>
-    <t>Decode TP8/rank</t>
-  </si>
-  <si>
-    <t>Attention FLOPs</t>
-  </si>
-  <si>
-    <t>单次预填充或解码步骤的每 Rank 逻辑 FLOPs。</t>
-  </si>
-  <si>
-    <t>MoE FLOPs</t>
-  </si>
-  <si>
-    <t>其他推理 FLOPs</t>
-  </si>
-  <si>
-    <t>总推理 FLOPs</t>
-  </si>
-  <si>
-    <t>通信量</t>
-  </si>
-  <si>
-    <t>Ring 集合通信每 Rank 发送加接收；TP1 为 0。</t>
-  </si>
-  <si>
-    <t>注意力逻辑参数量</t>
-  </si>
-  <si>
-    <t>注意力投影、Compressor、Indexer。</t>
-  </si>
-  <si>
-    <t>混合专家逻辑参数量</t>
-  </si>
-  <si>
-    <t>路由/共享专家与 Router。</t>
-  </si>
-  <si>
-    <t>其他逻辑参数量</t>
-  </si>
-  <si>
-    <t>Embedding、LM Head、HC 与 Norm。</t>
-  </si>
-  <si>
-    <t>总逻辑参数量</t>
-  </si>
-  <si>
-    <t>不包含 MTP。</t>
-  </si>
-  <si>
-    <t>注意力参数容量</t>
-  </si>
-  <si>
-    <t>按推理 dtype 与量化 Scale 计算。</t>
-  </si>
-  <si>
-    <t>混合专家参数容量</t>
-  </si>
-  <si>
-    <t>路由专家 FP4、共享专家 FP8、Router 复制。</t>
-  </si>
-  <si>
-    <t>其他参数容量</t>
-  </si>
-  <si>
-    <t>总参数容量</t>
-  </si>
-  <si>
-    <t>每 Rank 静态参数驻留。</t>
-  </si>
-  <si>
-    <t>Effective main KV cache</t>
-  </si>
-  <si>
-    <t>KV 与 Compressor 状态在当前实现中每个 TP Rank 复制。</t>
-  </si>
-  <si>
-    <t>Effective Indexer KV cache</t>
-  </si>
-  <si>
-    <t>Compressor 状态</t>
-  </si>
-  <si>
-    <t>Preallocated KV + state</t>
-  </si>
-  <si>
-    <t>Total capacity per inference / rank</t>
-  </si>
-  <si>
-    <t>参数 + 按 MaxContext 预分配的 KV/状态；不含临时工作区。</t>
-  </si>
-  <si>
-    <t>一次推理所需计算量</t>
-  </si>
-  <si>
-    <t>单次推理调用的单 Rank 总 FLOPs。</t>
+    <t>具体内容（Prefill capacity components per rank）：横向展示 Attention 静态参数、MoE 静态参数和当前 8K 输入对应的有效 KV cache；KV cache 含 Indexer KV 与 Compressor/Indexer State，Other 静态参数未在图中展示。</t>
+  </si>
+  <si>
+    <t>具体内容（Decode capacity components per rank）：横向展示 Attention 静态参数、MoE 静态参数和 1M 上下文对应的有效 KV cache；KV cache 含 Indexer KV 与 Compressor/Indexer State，Other 静态参数未在图中展示。</t>
+  </si>
+  <si>
+    <t>Communication GB</t>
+  </si>
+  <si>
+    <t>Per-Rank Inference Hardware Resource Summary</t>
+  </si>
+  <si>
+    <t>TP1 与 TP8 分区独立展示；所有值均为单个 Rank，不进行跨 Rank 或跨 TP 求和。</t>
+  </si>
+  <si>
+    <t>TP1 (configured size=1) per-rank resources</t>
+  </si>
+  <si>
+    <t>Prefill/rank</t>
+  </si>
+  <si>
+    <t>Decode/rank</t>
+  </si>
+  <si>
+    <t>单次推理调用的单 Rank 计算量。</t>
+  </si>
+  <si>
+    <t>Ring 集合通信单 Rank 发送加接收；TP1 为 0。</t>
+  </si>
+  <si>
+    <t>投影、Compressor、Indexer。</t>
+  </si>
+  <si>
+    <t>Embedding、LM Head、HC、Norm。</t>
+  </si>
+  <si>
+    <t>不含 MTP。</t>
+  </si>
+  <si>
+    <t>按推理 dtype 与 Scale 计算。</t>
+  </si>
+  <si>
+    <t>路由专家 FP4，共享专家 FP8。</t>
+  </si>
+  <si>
+    <t>单 Rank 静态参数驻留。</t>
+  </si>
+  <si>
+    <t>KV/状态在当前实现中每个 TP Rank 复制。</t>
+  </si>
+  <si>
+    <t>参数 + 预分配 KV/状态；不含临时工作区。</t>
+  </si>
+  <si>
+    <t>TP8 (configured size=8) per-rank resources</t>
+  </si>
+  <si>
+    <t>Per-Layer Attention and Routing Configuration</t>
+  </si>
+  <si>
+    <t>可编辑启用状态和模式；压缩比例与路由行为会自动更新。</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
   <si>
     <t>Mode</t>
   </si>
   <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>TP8/rank</t>
+    <t>Attention behavior</t>
+  </si>
+  <si>
+    <t>Routing behavior</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>Methodology and Limits</t>
+  </si>
+  <si>
+    <t>Topic</t>
   </si>
   <si>
     <t>Definition</t>
-  </si>
-  <si>
-    <t>Prefill</t>
-  </si>
-  <si>
-    <t>Static parameters + Prefill MaxContext KV/State</t>
-  </si>
-  <si>
-    <t>Decode</t>
-  </si>
-  <si>
-    <t>Static parameters + Decode MaxContext KV/State</t>
-  </si>
-  <si>
-    <t>One-inference TFLOPs</t>
-  </si>
-  <si>
-    <t>Prefill TP8</t>
-  </si>
-  <si>
-    <t>Decode TP8</t>
-  </si>
-  <si>
-    <t>TP1 TFLOPs</t>
-  </si>
-  <si>
-    <t>TP8 TFLOPs</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>TP1 GFLOPs</t>
-  </si>
-  <si>
-    <t>TP8 GFLOPs</t>
-  </si>
-  <si>
-    <t>TP1 GB</t>
-  </si>
-  <si>
-    <t>TP8 GB</t>
-  </si>
-  <si>
-    <t>具体内容（Static parameter capacity per rank）：Attention、MoE、Embedding、LM Head、Norm、HC 等静态模型参数及量化 Scale；不含 KV Cache、Compressor State、临时激活和集合通信缓冲区。Prefill/Decode 两图的静态参数数据相同。</t>
-  </si>
-  <si>
-    <t>Capacity GB</t>
-  </si>
-  <si>
-    <t>具体内容（Total capacity per inference / rank）：当前模式单 Rank 的静态参数容量 + 按 MaxContext 预分配的 KV Cache + Compressor State；不含临时激活、residual/HC workspace 和集合通信传输量。</t>
-  </si>
-  <si>
-    <t>Per-Rank Inference Hardware Resource Summary</t>
-  </si>
-  <si>
-    <t>TP1 与 TP8 分区独立展示；所有值均为单个 Rank，不进行跨 Rank 或跨 TP 求和。</t>
-  </si>
-  <si>
-    <t>TP1 (configured size=1) per-rank resources</t>
-  </si>
-  <si>
-    <t>Prefill/rank</t>
-  </si>
-  <si>
-    <t>Decode/rank</t>
-  </si>
-  <si>
-    <t>单次推理调用的单 Rank 计算量。</t>
-  </si>
-  <si>
-    <t>Ring 集合通信单 Rank 发送加接收；TP1 为 0。</t>
-  </si>
-  <si>
-    <t>投影、Compressor、Indexer。</t>
-  </si>
-  <si>
-    <t>Embedding、LM Head、HC、Norm。</t>
-  </si>
-  <si>
-    <t>不含 MTP。</t>
-  </si>
-  <si>
-    <t>按推理 dtype 与 Scale 计算。</t>
-  </si>
-  <si>
-    <t>路由专家 FP4，共享专家 FP8。</t>
-  </si>
-  <si>
-    <t>单 Rank 静态参数驻留。</t>
-  </si>
-  <si>
-    <t>KV/状态在当前实现中每个 TP Rank 复制。</t>
-  </si>
-  <si>
-    <t>参数 + 预分配 KV/状态；不含临时工作区。</t>
-  </si>
-  <si>
-    <t>TP8 (configured size=8) per-rank resources</t>
-  </si>
-  <si>
-    <t>Per-Layer Attention and Routing Configuration</t>
-  </si>
-  <si>
-    <t>可编辑启用状态和模式；压缩比例与路由行为会自动更新。</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Attention behavior</t>
-  </si>
-  <si>
-    <t>Routing behavior</t>
-  </si>
-  <si>
-    <t>window</t>
-  </si>
-  <si>
-    <t>short</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>Methodology and Limits</t>
-  </si>
-  <si>
-    <t>Topic</t>
   </si>
   <si>
     <t>仅统计 43 层主推理路径；不含 MTP、反向传播、梯度、优化器状态和训练激活。Layer_Config 最多可维护 64 层。</t>
@@ -1925,7 +1949,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$27:$S$30</c:f>
+              <c:f>Comparison!$S$28:$S$31</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1945,7 +1969,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$27:$T$30</c:f>
+              <c:f>Comparison!$T$28:$T$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2043,7 +2067,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Prefill compute per rank</a:t>
+              <a:t>Total capacity per inference
+/ rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2059,89 +2084,49 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>TP1 TFLOPs</c:v>
+            <c:v>Capacity GB</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$34:$S$36</c:f>
+              <c:f>Comparison!$S$35:$S$38</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Attention</c:v>
+                  <c:v>Prefill TP1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>MoE</c:v>
+                  <c:v>Prefill TP8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Other</c:v>
+                  <c:v>Decode TP1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Decode TP8</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$34:$T$36</c:f>
+              <c:f>Comparison!$T$35:$T$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>102.836037746688</c:v>
+                  <c:v>166.349315548</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>124.846109360128</c:v>
+                  <c:v>29.581867388</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.715535007744</c:v>
+                  <c:v>166.349315548</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>TP8 TFLOPs</c:v>
-          </c:tx>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
-            <c:showVal val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Comparison!$S$34:$S$36</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Attention</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>MoE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Other</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$U$34:$U$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>23.172382457856</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>31.765578121216</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.714608328704</c:v>
+                <c:pt idx="3">
+                  <c:v>29.581867388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2182,14 +2167,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>TFLOPs</a:t>
+                  <a:t>GB</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -2225,7 +2210,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Decode compute per rank</a:t>
+              <a:t>Prefill compute per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2241,15 +2226,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>TP1 GFLOPs</c:v>
+            <c:v>TP1 TFLOPs</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$41:$S$43</c:f>
+              <c:f>Comparison!$S$42:$S$44</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2266,18 +2251,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$41:$T$43</c:f>
+              <c:f>Comparison!$T$42:$T$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>123.969470464</c:v>
+                  <c:v>102.836037746688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.240003584</c:v>
+                  <c:v>124.846109360128</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.146278062</c:v>
+                  <c:v>0.715535007744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2287,15 +2272,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>TP8 GFLOPs</c:v>
+            <c:v>TP8 TFLOPs</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$41:$S$43</c:f>
+              <c:f>Comparison!$S$42:$S$44</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2312,18 +2297,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$41:$U$43</c:f>
+              <c:f>Comparison!$U$42:$U$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>19.452461056</c:v>
+                  <c:v>23.172382457856</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.877634048</c:v>
+                  <c:v>31.765578121216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.219599022</c:v>
+                  <c:v>0.714608328704</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2364,14 +2349,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>GFLOPs</a:t>
+                  <a:t>TFLOPs</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0&quot; TFLOPs&quot;" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -2407,7 +2392,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Prefill static parameter capacity per rank</a:t>
+              <a:t>Decode compute per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2423,15 +2408,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>TP1 GB</c:v>
+            <c:v>TP1 GFLOPs</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$48:$S$50</c:f>
+              <c:f>Comparison!$S$49:$S$51</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2448,18 +2433,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$48:$T$50</c:f>
+              <c:f>Comparison!$T$49:$T$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>7.45138496</c:v>
+                  <c:v>123.969470464</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>148.351461888</c:v>
+                  <c:v>15.240003584</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.314423644</c:v>
+                  <c:v>1.146278062</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2469,15 +2454,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>TP8 GB</c:v>
+            <c:v>TP8 GFLOPs</c:v>
           </c:tx>
           <c:dLbls>
-            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$48:$S$50</c:f>
+              <c:f>Comparison!$S$49:$S$51</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2494,18 +2479,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$48:$U$50</c:f>
+              <c:f>Comparison!$U$49:$U$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2.23750496</c:v>
+                  <c:v>19.452461056</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.57794048</c:v>
+                  <c:v>3.877634048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.534376892</c:v>
+                  <c:v>0.219599022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2546,14 +2531,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>GB</a:t>
+                  <a:t>GFLOPs</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0&quot; GFLOPs&quot;" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -2589,7 +2574,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Decode static parameter capacity per rank</a:t>
+              <a:t>Prefill static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2613,7 +2598,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$55:$S$57</c:f>
+              <c:f>Comparison!$S$56:$S$58</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2630,7 +2615,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$55:$T$57</c:f>
+              <c:f>Comparison!$T$56:$T$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2659,7 +2644,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$55:$S$57</c:f>
+              <c:f>Comparison!$S$56:$S$58</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2676,7 +2661,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$U$55:$U$57</c:f>
+              <c:f>Comparison!$U$56:$U$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2771,8 +2756,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Prefill total capacity per inference
-/ rank</a:t>
+              <a:t>Decode static parameter capacity per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2788,7 +2772,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Capacity GB</c:v>
+            <c:v>TP1 GB</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
@@ -2796,29 +2780,81 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$62:$S$63</c:f>
+              <c:f>Comparison!$S$63:$S$65</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>TP1</c:v>
+                  <c:v>Attention</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>TP8/rank</c:v>
+                  <c:v>MoE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Other</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$62:$T$63</c:f>
+              <c:f>Comparison!$T$63:$T$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>166.349315548</c:v>
+                  <c:v>7.45138496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.581867388</c:v>
+                  <c:v>148.351461888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.314423644</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TP8 GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$63:$S$65</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Attention</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MoE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Other</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$U$63:$U$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.23750496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.57794048</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.534376892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2902,8 +2938,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Decode total capacity per inference
-/ rank</a:t>
+              <a:t>Prefill capacity components per rank</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2919,7 +2954,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Capacity GB</c:v>
+            <c:v>TP1 GB</c:v>
           </c:tx>
           <c:dLbls>
             <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
@@ -2927,29 +2962,81 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Comparison!$S$69:$S$70</c:f>
+              <c:f>Comparison!$S$70:$S$72</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>TP1</c:v>
+                  <c:v>Attention static parameter</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>TP8/rank</c:v>
+                  <c:v>MoE static parameter</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>KV cache</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$T$69:$T$70</c:f>
+              <c:f>Comparison!$T$70:$T$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>166.349315548</c:v>
+                  <c:v>7.45138496</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.581867388</c:v>
+                  <c:v>148.351461888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.074203136</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TP8 GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$70:$S$72</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Attention static parameter</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MoE static parameter</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>KV cache</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$U$70:$U$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.23750496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.57794048</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.074203136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3017,19 +3104,344 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Decode capacity components per rank</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>TP1 GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$77:$S$79</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Attention static parameter</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MoE static parameter</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>KV cache</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$T$77:$T$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7.45138496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148.351461888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.232045056</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TP8 GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$77:$S$79</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Attention static parameter</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MoE static parameter</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>KV cache</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$U$77:$U$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.23750496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.57794048</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.232045056</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="30"/>
+        <c:axId val="50080001"/>
+        <c:axId val="50080002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50080001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="50080002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50080002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GB</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50080001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Total communication per inference
+/ rank</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Communication GB</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$S$84:$S$87</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Prefill TP1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Prefill TP8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Decode TP1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Decode TP8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$T$84:$T$87</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40.635322112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.005865216</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="30"/>
+        <c:axId val="50090001"/>
+        <c:axId val="50090002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50090001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="50090002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50090002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GB</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0&quot; GB&quot;" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50090001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3051,15 +3463,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3081,15 +3493,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3111,15 +3523,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3141,15 +3553,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3171,15 +3583,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3201,15 +3613,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>4705350</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3224,6 +3636,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4705350</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3313,14 +3785,15 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DType_Module" displayName="DType_Module" ref="A5:E20" totalsRowShown="0">
-  <autoFilter ref="A5:E20"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DType_Module" displayName="DType_Module" ref="A5:F20" totalsRowShown="0">
+  <autoFilter ref="A5:F20"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Scope"/>
     <tableColumn id="2" name="Module/tensor"/>
-    <tableColumn id="3" name="Checkpoint/parameter storage"/>
-    <tableColumn id="4" name="Activation/intermediate computation"/>
-    <tableColumn id="5" name="Notes"/>
+    <tableColumn id="3" name="Parameter storage / inference dtype"/>
+    <tableColumn id="4" name="Scale type"/>
+    <tableColumn id="5" name="Activation/intermediate computation"/>
+    <tableColumn id="6" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3345,8 +3818,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Comparison_Resource_Overview" displayName="Comparison_Resource_Overview" ref="A4:F23" totalsRowShown="0">
-  <autoFilter ref="A4:F23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Comparison_Resource_Overview" displayName="Comparison_Resource_Overview" ref="A4:F24" totalsRowShown="0">
+  <autoFilter ref="A4:F24"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Resource"/>
     <tableColumn id="2" name="Prefill TP1"/>
@@ -3354,19 +3827,6 @@
     <tableColumn id="4" name="Decode TP1"/>
     <tableColumn id="5" name="Decode TP8/rank"/>
     <tableColumn id="6" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Comparison_Total_Capacity" displayName="Comparison_Total_Capacity" ref="K27:N29" totalsRowShown="0">
-  <autoFilter ref="K27:N29"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Mode"/>
-    <tableColumn id="2" name="TP1"/>
-    <tableColumn id="3" name="TP8/rank"/>
-    <tableColumn id="4" name="Definition"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9479,22 +9939,24 @@
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="9" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="66.7109375" customWidth="1"/>
+    <col min="7" max="9" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="28" t="s">
         <v>347</v>
       </c>
@@ -9502,8 +9964,9 @@
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>348</v>
       </c>
@@ -9519,129 +9982,153 @@
       <c r="E5" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>232</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
-        <v>360</v>
-      </c>
       <c r="B9" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>232</v>
+        <v>367</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>369</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>369</v>
+        <v>245</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>373</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>376</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>379</v>
+        <v>245</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>381</v>
@@ -9650,134 +10137,158 @@
         <v>382</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>385</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="E14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>394</v>
+        <v>245</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>395</v>
       </c>
+      <c r="F16" s="4" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>236</v>
+        <v>399</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>236</v>
+        <v>400</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>405</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>399</v>
+        <v>245</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>400</v>
+        <v>406</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>369</v>
+        <v>245</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>404</v>
+        <v>373</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>407</v>
+        <v>245</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>408</v>
+        <v>414</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="28" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
@@ -9790,22 +10301,22 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B23" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C23" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D23" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E23" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="F23" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G23" t="s">
         <v>60</v>
@@ -9814,7 +10325,7 @@
         <v>66</v>
       </c>
       <c r="I23" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -9822,25 +10333,25 @@
         <v>0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C24" s="4">
         <v>0</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>236</v>
@@ -9851,25 +10362,25 @@
         <v>1</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>236</v>
@@ -9880,25 +10391,25 @@
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C26" s="4">
         <v>4</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>236</v>
@@ -9909,25 +10420,25 @@
         <v>3</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C27" s="4">
         <v>128</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>236</v>
@@ -9938,25 +10449,25 @@
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C28" s="4">
         <v>4</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>236</v>
@@ -9967,25 +10478,25 @@
         <v>5</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C29" s="4">
         <v>128</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>236</v>
@@ -9996,25 +10507,25 @@
         <v>6</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>236</v>
@@ -10025,25 +10536,25 @@
         <v>7</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C31" s="4">
         <v>128</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>236</v>
@@ -10054,25 +10565,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C32" s="4">
         <v>4</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>236</v>
@@ -10083,25 +10594,25 @@
         <v>9</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C33" s="4">
         <v>128</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>236</v>
@@ -10112,25 +10623,25 @@
         <v>10</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C34" s="4">
         <v>4</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>236</v>
@@ -10141,25 +10652,25 @@
         <v>11</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C35" s="4">
         <v>128</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>236</v>
@@ -10170,25 +10681,25 @@
         <v>12</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>236</v>
@@ -10199,25 +10710,25 @@
         <v>13</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C37" s="4">
         <v>128</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>236</v>
@@ -10228,25 +10739,25 @@
         <v>14</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C38" s="4">
         <v>4</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>236</v>
@@ -10257,25 +10768,25 @@
         <v>15</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C39" s="4">
         <v>128</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>236</v>
@@ -10286,25 +10797,25 @@
         <v>16</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>236</v>
@@ -10315,25 +10826,25 @@
         <v>17</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C41" s="4">
         <v>128</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>236</v>
@@ -10344,25 +10855,25 @@
         <v>18</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>236</v>
@@ -10373,25 +10884,25 @@
         <v>19</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C43" s="4">
         <v>128</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>236</v>
@@ -10402,25 +10913,25 @@
         <v>20</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C44" s="4">
         <v>4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>236</v>
@@ -10431,25 +10942,25 @@
         <v>21</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C45" s="4">
         <v>128</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>236</v>
@@ -10460,25 +10971,25 @@
         <v>22</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C46" s="4">
         <v>4</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>236</v>
@@ -10489,25 +11000,25 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C47" s="4">
         <v>128</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>236</v>
@@ -10518,25 +11029,25 @@
         <v>24</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C48" s="4">
         <v>4</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>236</v>
@@ -10547,25 +11058,25 @@
         <v>25</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C49" s="4">
         <v>128</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>236</v>
@@ -10576,25 +11087,25 @@
         <v>26</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C50" s="4">
         <v>4</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>236</v>
@@ -10605,25 +11116,25 @@
         <v>27</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C51" s="4">
         <v>128</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>236</v>
@@ -10634,25 +11145,25 @@
         <v>28</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C52" s="4">
         <v>4</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>236</v>
@@ -10663,25 +11174,25 @@
         <v>29</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C53" s="4">
         <v>128</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>236</v>
@@ -10692,25 +11203,25 @@
         <v>30</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C54" s="4">
         <v>4</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>236</v>
@@ -10721,25 +11232,25 @@
         <v>31</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C55" s="4">
         <v>128</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>236</v>
@@ -10750,25 +11261,25 @@
         <v>32</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>236</v>
@@ -10779,25 +11290,25 @@
         <v>33</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C57" s="4">
         <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>236</v>
@@ -10808,25 +11319,25 @@
         <v>34</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>236</v>
@@ -10837,25 +11348,25 @@
         <v>35</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C59" s="4">
         <v>128</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>236</v>
@@ -10866,25 +11377,25 @@
         <v>36</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C60" s="4">
         <v>4</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>236</v>
@@ -10895,25 +11406,25 @@
         <v>37</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C61" s="4">
         <v>128</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>236</v>
@@ -10924,25 +11435,25 @@
         <v>38</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C62" s="4">
         <v>4</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>236</v>
@@ -10953,25 +11464,25 @@
         <v>39</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C63" s="4">
         <v>128</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>236</v>
@@ -10982,25 +11493,25 @@
         <v>40</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C64" s="4">
         <v>4</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>236</v>
@@ -11011,25 +11522,25 @@
         <v>41</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C65" s="4">
         <v>128</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>236</v>
@@ -11040,25 +11551,25 @@
         <v>42</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C66" s="4">
         <v>4</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>232</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>236</v>
@@ -11066,7 +11577,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A22:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11079,51 +11590,49 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U116"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="72.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="14" width="20.7109375" customWidth="1"/>
-    <col min="15" max="16" width="0" hidden="1" customWidth="1"/>
     <col min="19" max="21" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B5" s="31" t="str">
         <f>TEXT(IF(ABS(G5)&gt;=1E15,G5/1E15,IF(ABS(G5)&gt;=1E12,G5/1E12,IF(ABS(G5)&gt;=1E9,G5/1E9,IF(ABS(G5)&gt;=1E6,G5/1E6,G5)))),"#,##0.000")&amp;IF((IF(ABS(G5)&gt;=1E15,"PFLOPs",IF(ABS(G5)&gt;=1E12,"TFLOPs",IF(ABS(G5)&gt;=1E9,"GFLOPs",IF(ABS(G5)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G5)&gt;=1E15,"PFLOPs",IF(ABS(G5)&gt;=1E12,"TFLOPs",IF(ABS(G5)&gt;=1E9,"GFLOPs",IF(ABS(G5)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11142,7 +11651,7 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G5" s="30">
         <f>'Prefill_8K'!$AF$14</f>
@@ -11163,7 +11672,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B6" s="31" t="str">
         <f>TEXT(IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6)))),"#,##0.000")&amp;IF((IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11182,7 +11691,7 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G6" s="30">
         <f>'Prefill_8K'!$AF$15</f>
@@ -11203,7 +11712,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B7" s="31" t="str">
         <f>TEXT(IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7)))),"#,##0.000")&amp;IF((IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11222,7 +11731,7 @@
         <v>219.599 MFLOPs</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G7" s="30">
         <f>'Prefill_8K'!$AO$48</f>
@@ -11243,7 +11752,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="29" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B8" s="29" t="str">
         <f>TEXT(IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8)))),"#,##0.000")&amp;IF((IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -11262,7 +11771,7 @@
         <v>23.550 GFLOPs</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G8" s="30">
         <f>'Prefill_8K'!$AF$13</f>
@@ -11283,7 +11792,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B9" s="31" t="str">
         <f>TEXT(IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,IF(ABS(G9)&gt;=1E3,G9/1E3,G9)))),"#,##0.000")&amp;IF((IF(ABS(G9)&gt;=1E12,"TB",IF(ABS(G9)&gt;=1E9,"GB",IF(ABS(G9)&gt;=1E6,"MB",IF(ABS(G9)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G9)&gt;=1E12,"TB",IF(ABS(G9)&gt;=1E9,"GB",IF(ABS(G9)&gt;=1E6,"MB",IF(ABS(G9)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11302,7 +11811,7 @@
         <v>5.865 MB</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G9" s="30">
         <f>'Prefill_8K'!$AQ$48</f>
@@ -11323,7 +11832,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B10" s="31" t="str">
         <f>TEXT(IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,IF(ABS(G10)&gt;=1E3,G10/1E3,G10)))),"#,##0.000")&amp;IF((IF(ABS(G10)&gt;=1E12,"T",IF(ABS(G10)&gt;=1E9,"G",IF(ABS(G10)&gt;=1E6,"M",IF(ABS(G10)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G10)&gt;=1E12,"T",IF(ABS(G10)&gt;=1E9,"G",IF(ABS(G10)&gt;=1E6,"M",IF(ABS(G10)&gt;=1E3,"K",""))))))</f>
@@ -11342,7 +11851,7 @@
         <v>1.140 G</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G10" s="30">
         <f>'Prefill_8K'!$AY$49</f>
@@ -11363,7 +11872,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B11" s="31" t="str">
         <f>TEXT(IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11)))),"#,##0.000")&amp;IF((IF(ABS(G11)&gt;=1E12,"T",IF(ABS(G11)&gt;=1E9,"G",IF(ABS(G11)&gt;=1E6,"M",IF(ABS(G11)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G11)&gt;=1E12,"T",IF(ABS(G11)&gt;=1E9,"G",IF(ABS(G11)&gt;=1E6,"M",IF(ABS(G11)&gt;=1E3,"K",""))))))</f>
@@ -11382,7 +11891,7 @@
         <v>35.758 G</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G11" s="30">
         <f>'Prefill_8K'!$AY$50</f>
@@ -11403,7 +11912,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B12" s="31" t="str">
         <f>TEXT(IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12)))),"#,##0.000")&amp;IF((IF(ABS(G12)&gt;=1E12,"T",IF(ABS(G12)&gt;=1E9,"G",IF(ABS(G12)&gt;=1E6,"M",IF(ABS(G12)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G12)&gt;=1E12,"T",IF(ABS(G12)&gt;=1E9,"G",IF(ABS(G12)&gt;=1E6,"M",IF(ABS(G12)&gt;=1E3,"K",""))))))</f>
@@ -11422,7 +11931,7 @@
         <v>166.690 M</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G12" s="30">
         <f>'Prefill_8K'!$AY$51</f>
@@ -11443,7 +11952,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="29" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B13" s="29" t="str">
         <f>TEXT(IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13)))),"#,##0.000")&amp;IF((IF(ABS(G13)&gt;=1E12,"T",IF(ABS(G13)&gt;=1E9,"G",IF(ABS(G13)&gt;=1E6,"M",IF(ABS(G13)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G13)&gt;=1E12,"T",IF(ABS(G13)&gt;=1E9,"G",IF(ABS(G13)&gt;=1E6,"M",IF(ABS(G13)&gt;=1E3,"K",""))))))</f>
@@ -11462,7 +11971,7 @@
         <v>37.064 G</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G13" s="30">
         <f>'Prefill_8K'!$AY$52</f>
@@ -11483,7 +11992,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>TEXT(IF(ABS(G14)&gt;=1E12,G14/1E12,IF(ABS(G14)&gt;=1E9,G14/1E9,IF(ABS(G14)&gt;=1E6,G14/1E6,IF(ABS(G14)&gt;=1E3,G14/1E3,G14)))),"#,##0.000")&amp;IF((IF(ABS(G14)&gt;=1E12,"TB",IF(ABS(G14)&gt;=1E9,"GB",IF(ABS(G14)&gt;=1E6,"MB",IF(ABS(G14)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G14)&gt;=1E12,"TB",IF(ABS(G14)&gt;=1E9,"GB",IF(ABS(G14)&gt;=1E6,"MB",IF(ABS(G14)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11502,7 +12011,7 @@
         <v>2.238 GB</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G14" s="30">
         <f>'Prefill_8K'!$BA$49</f>
@@ -11523,7 +12032,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B15" s="31" t="str">
         <f>TEXT(IF(ABS(G15)&gt;=1E12,G15/1E12,IF(ABS(G15)&gt;=1E9,G15/1E9,IF(ABS(G15)&gt;=1E6,G15/1E6,IF(ABS(G15)&gt;=1E3,G15/1E3,G15)))),"#,##0.000")&amp;IF((IF(ABS(G15)&gt;=1E12,"TB",IF(ABS(G15)&gt;=1E9,"GB",IF(ABS(G15)&gt;=1E6,"MB",IF(ABS(G15)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G15)&gt;=1E12,"TB",IF(ABS(G15)&gt;=1E9,"GB",IF(ABS(G15)&gt;=1E6,"MB",IF(ABS(G15)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11542,7 +12051,7 @@
         <v>19.578 GB</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="G15" s="30">
         <f>'Prefill_8K'!$BA$50</f>
@@ -11563,7 +12072,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B16" s="31" t="str">
         <f>TEXT(IF(ABS(G16)&gt;=1E12,G16/1E12,IF(ABS(G16)&gt;=1E9,G16/1E9,IF(ABS(G16)&gt;=1E6,G16/1E6,IF(ABS(G16)&gt;=1E3,G16/1E3,G16)))),"#,##0.000")&amp;IF((IF(ABS(G16)&gt;=1E12,"TB",IF(ABS(G16)&gt;=1E9,"GB",IF(ABS(G16)&gt;=1E6,"MB",IF(ABS(G16)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G16)&gt;=1E12,"TB",IF(ABS(G16)&gt;=1E9,"GB",IF(ABS(G16)&gt;=1E6,"MB",IF(ABS(G16)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11582,7 +12091,7 @@
         <v>534.377 MB</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G16" s="30">
         <f>'Prefill_8K'!$BA$51</f>
@@ -11603,7 +12112,7 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="29" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B17" s="29" t="str">
         <f>TEXT(IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,IF(ABS(G17)&gt;=1E3,G17/1E3,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11622,7 +12131,7 @@
         <v>22.350 GB</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G17" s="30">
         <f>'Prefill_8K'!$BA$52</f>
@@ -11643,7 +12152,7 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B18" s="31" t="str">
         <f>TEXT(IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18)))),"#,##0.000")&amp;IF((IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11662,7 +12171,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G18" s="30">
         <f>'Prefill_8K'!$U$35</f>
@@ -11683,7 +12192,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="4" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B19" s="31" t="str">
         <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11702,7 +12211,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G19" s="30">
         <f>'Prefill_8K'!$U$36</f>
@@ -11723,7 +12232,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B20" s="31" t="str">
         <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11742,7 +12251,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G20" s="30">
         <f>'Prefill_8K'!$U$37</f>
@@ -11763,7 +12272,7 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B21" s="31" t="str">
         <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes"))))))</f>
@@ -11782,7 +12291,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="G21" s="30">
         <f>'Prefill_8K'!$U$38</f>
@@ -11802,480 +12311,592 @@
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="B22" s="29" t="str">
+      <c r="A22" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B22" s="31" t="str">
         <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>74.203 MB</v>
+      </c>
+      <c r="C22" s="31" t="str">
+        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>74.203 MB</v>
+      </c>
+      <c r="D22" s="31" t="str">
+        <f>TEXT(IF(ABS(I22)&gt;=1E12,I22/1E12,IF(ABS(I22)&gt;=1E9,I22/1E9,IF(ABS(I22)&gt;=1E6,I22/1E6,IF(ABS(I22)&gt;=1E3,I22/1E3,I22)))),"#,##0.000")&amp;IF((IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.232 GB</v>
+      </c>
+      <c r="E22" s="31" t="str">
+        <f>TEXT(IF(ABS(J22)&gt;=1E12,J22/1E12,IF(ABS(J22)&gt;=1E9,J22/1E9,IF(ABS(J22)&gt;=1E6,J22/1E6,IF(ABS(J22)&gt;=1E3,J22/1E3,J22)))),"#,##0.000")&amp;IF((IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes"))))))</f>
+        <v>7.232 GB</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="G22" s="30">
+        <f>'Prefill_8K'!$U$35+'Prefill_8K'!$U$36+'Prefill_8K'!$U$37</f>
+        <v>74203136</v>
+      </c>
+      <c r="H22" s="30">
+        <f>'Prefill_8K'!$X$35+'Prefill_8K'!$X$36+'Prefill_8K'!$X$37</f>
+        <v>74203136</v>
+      </c>
+      <c r="I22" s="30">
+        <f>'Decode_1M'!$U$35+'Decode_1M'!$U$36+'Decode_1M'!$U$37</f>
+        <v>7232045056</v>
+      </c>
+      <c r="J22" s="30">
+        <f>'Decode_1M'!$X$35+'Decode_1M'!$X$36+'Decode_1M'!$X$37</f>
+        <v>7232045056</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B23" s="29" t="str">
+        <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes"))))))</f>
         <v>166.349 GB</v>
       </c>
-      <c r="C22" s="29" t="str">
-        <f>TEXT(IF(ABS(H22)&gt;=1E12,H22/1E12,IF(ABS(H22)&gt;=1E9,H22/1E9,IF(ABS(H22)&gt;=1E6,H22/1E6,IF(ABS(H22)&gt;=1E3,H22/1E3,H22)))),"#,##0.000")&amp;IF((IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H22)&gt;=1E12,"TB",IF(ABS(H22)&gt;=1E9,"GB",IF(ABS(H22)&gt;=1E6,"MB",IF(ABS(H22)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="C23" s="29" t="str">
+        <f>TEXT(IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,IF(ABS(H23)&gt;=1E3,H23/1E3,H23)))),"#,##0.000")&amp;IF((IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(H23)&gt;=1E12,"TB",IF(ABS(H23)&gt;=1E9,"GB",IF(ABS(H23)&gt;=1E6,"MB",IF(ABS(H23)&gt;=1E3,"KB","bytes"))))))</f>
         <v>29.582 GB</v>
       </c>
-      <c r="D22" s="29" t="str">
-        <f>TEXT(IF(ABS(I22)&gt;=1E12,I22/1E12,IF(ABS(I22)&gt;=1E9,I22/1E9,IF(ABS(I22)&gt;=1E6,I22/1E6,IF(ABS(I22)&gt;=1E3,I22/1E3,I22)))),"#,##0.000")&amp;IF((IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I22)&gt;=1E12,"TB",IF(ABS(I22)&gt;=1E9,"GB",IF(ABS(I22)&gt;=1E6,"MB",IF(ABS(I22)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="D23" s="29" t="str">
+        <f>TEXT(IF(ABS(I23)&gt;=1E12,I23/1E12,IF(ABS(I23)&gt;=1E9,I23/1E9,IF(ABS(I23)&gt;=1E6,I23/1E6,IF(ABS(I23)&gt;=1E3,I23/1E3,I23)))),"#,##0.000")&amp;IF((IF(ABS(I23)&gt;=1E12,"TB",IF(ABS(I23)&gt;=1E9,"GB",IF(ABS(I23)&gt;=1E6,"MB",IF(ABS(I23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(I23)&gt;=1E12,"TB",IF(ABS(I23)&gt;=1E9,"GB",IF(ABS(I23)&gt;=1E6,"MB",IF(ABS(I23)&gt;=1E3,"KB","bytes"))))))</f>
         <v>166.349 GB</v>
       </c>
-      <c r="E22" s="29" t="str">
-        <f>TEXT(IF(ABS(J22)&gt;=1E12,J22/1E12,IF(ABS(J22)&gt;=1E9,J22/1E9,IF(ABS(J22)&gt;=1E6,J22/1E6,IF(ABS(J22)&gt;=1E3,J22/1E3,J22)))),"#,##0.000")&amp;IF((IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J22)&gt;=1E12,"TB",IF(ABS(J22)&gt;=1E9,"GB",IF(ABS(J22)&gt;=1E6,"MB",IF(ABS(J22)&gt;=1E3,"KB","bytes"))))))</f>
+      <c r="E23" s="29" t="str">
+        <f>TEXT(IF(ABS(J23)&gt;=1E12,J23/1E12,IF(ABS(J23)&gt;=1E9,J23/1E9,IF(ABS(J23)&gt;=1E6,J23/1E6,IF(ABS(J23)&gt;=1E3,J23/1E3,J23)))),"#,##0.000")&amp;IF((IF(ABS(J23)&gt;=1E12,"TB",IF(ABS(J23)&gt;=1E9,"GB",IF(ABS(J23)&gt;=1E6,"MB",IF(ABS(J23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(J23)&gt;=1E12,"TB",IF(ABS(J23)&gt;=1E9,"GB",IF(ABS(J23)&gt;=1E6,"MB",IF(ABS(J23)&gt;=1E3,"KB","bytes"))))))</f>
         <v>29.582 GB</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="G22" s="30">
+      <c r="F23" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G23" s="30">
         <f>'Prefill_8K'!$BA$52+'Prefill_8K'!$U$38</f>
         <v>166349315548.0</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H23" s="30">
         <f>'Prefill_8K'!$BB$52+'Prefill_8K'!$X$38</f>
         <v>29581867388.0</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I23" s="30">
         <f>'Prefill_8K'!$BA$52+'Decode_1M'!$U$38</f>
         <v>166349315548.0</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J23" s="30">
         <f>'Prefill_8K'!$BB$52+'Decode_1M'!$X$38</f>
         <v>29581867388.0</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="B23" s="29" t="str">
-        <f>TEXT(IF(ABS(G23)&gt;=1E15,G23/1E15,IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E15,"PFLOPs",IF(ABS(G23)&gt;=1E12,"TFLOPs",IF(ABS(G23)&gt;=1E9,"GFLOPs",IF(ABS(G23)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E15,"PFLOPs",IF(ABS(G23)&gt;=1E12,"TFLOPs",IF(ABS(G23)&gt;=1E9,"GFLOPs",IF(ABS(G23)&gt;=1E6,"MFLOPs","flops"))))))</f>
+    <row r="24" spans="1:20">
+      <c r="A24" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="B24" s="29" t="str">
+        <f>TEXT(IF(ABS(G24)&gt;=1E15,G24/1E15,IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E15,"PFLOPs",IF(ABS(G24)&gt;=1E12,"TFLOPs",IF(ABS(G24)&gt;=1E9,"GFLOPs",IF(ABS(G24)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E15,"PFLOPs",IF(ABS(G24)&gt;=1E12,"TFLOPs",IF(ABS(G24)&gt;=1E9,"GFLOPs",IF(ABS(G24)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>228.398 TFLOPs</v>
       </c>
-      <c r="C23" s="29" t="str">
-        <f>TEXT(IF(ABS(H23)&gt;=1E15,H23/1E15,IF(ABS(H23)&gt;=1E12,H23/1E12,IF(ABS(H23)&gt;=1E9,H23/1E9,IF(ABS(H23)&gt;=1E6,H23/1E6,H23)))),"#,##0.000")&amp;IF((IF(ABS(H23)&gt;=1E15,"PFLOPs",IF(ABS(H23)&gt;=1E12,"TFLOPs",IF(ABS(H23)&gt;=1E9,"GFLOPs",IF(ABS(H23)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H23)&gt;=1E15,"PFLOPs",IF(ABS(H23)&gt;=1E12,"TFLOPs",IF(ABS(H23)&gt;=1E9,"GFLOPs",IF(ABS(H23)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="C24" s="29" t="str">
+        <f>TEXT(IF(ABS(H24)&gt;=1E15,H24/1E15,IF(ABS(H24)&gt;=1E12,H24/1E12,IF(ABS(H24)&gt;=1E9,H24/1E9,IF(ABS(H24)&gt;=1E6,H24/1E6,H24)))),"#,##0.000")&amp;IF((IF(ABS(H24)&gt;=1E15,"PFLOPs",IF(ABS(H24)&gt;=1E12,"TFLOPs",IF(ABS(H24)&gt;=1E9,"GFLOPs",IF(ABS(H24)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(H24)&gt;=1E15,"PFLOPs",IF(ABS(H24)&gt;=1E12,"TFLOPs",IF(ABS(H24)&gt;=1E9,"GFLOPs",IF(ABS(H24)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>55.653 TFLOPs</v>
       </c>
-      <c r="D23" s="29" t="str">
-        <f>TEXT(IF(ABS(I23)&gt;=1E15,I23/1E15,IF(ABS(I23)&gt;=1E12,I23/1E12,IF(ABS(I23)&gt;=1E9,I23/1E9,IF(ABS(I23)&gt;=1E6,I23/1E6,I23)))),"#,##0.000")&amp;IF((IF(ABS(I23)&gt;=1E15,"PFLOPs",IF(ABS(I23)&gt;=1E12,"TFLOPs",IF(ABS(I23)&gt;=1E9,"GFLOPs",IF(ABS(I23)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(I23)&gt;=1E15,"PFLOPs",IF(ABS(I23)&gt;=1E12,"TFLOPs",IF(ABS(I23)&gt;=1E9,"GFLOPs",IF(ABS(I23)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="D24" s="29" t="str">
+        <f>TEXT(IF(ABS(I24)&gt;=1E15,I24/1E15,IF(ABS(I24)&gt;=1E12,I24/1E12,IF(ABS(I24)&gt;=1E9,I24/1E9,IF(ABS(I24)&gt;=1E6,I24/1E6,I24)))),"#,##0.000")&amp;IF((IF(ABS(I24)&gt;=1E15,"PFLOPs",IF(ABS(I24)&gt;=1E12,"TFLOPs",IF(ABS(I24)&gt;=1E9,"GFLOPs",IF(ABS(I24)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(I24)&gt;=1E15,"PFLOPs",IF(ABS(I24)&gt;=1E12,"TFLOPs",IF(ABS(I24)&gt;=1E9,"GFLOPs",IF(ABS(I24)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>140.356 GFLOPs</v>
       </c>
-      <c r="E23" s="29" t="str">
-        <f>TEXT(IF(ABS(J23)&gt;=1E15,J23/1E15,IF(ABS(J23)&gt;=1E12,J23/1E12,IF(ABS(J23)&gt;=1E9,J23/1E9,IF(ABS(J23)&gt;=1E6,J23/1E6,J23)))),"#,##0.000")&amp;IF((IF(ABS(J23)&gt;=1E15,"PFLOPs",IF(ABS(J23)&gt;=1E12,"TFLOPs",IF(ABS(J23)&gt;=1E9,"GFLOPs",IF(ABS(J23)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(J23)&gt;=1E15,"PFLOPs",IF(ABS(J23)&gt;=1E12,"TFLOPs",IF(ABS(J23)&gt;=1E9,"GFLOPs",IF(ABS(J23)&gt;=1E6,"MFLOPs","flops"))))))</f>
+      <c r="E24" s="29" t="str">
+        <f>TEXT(IF(ABS(J24)&gt;=1E15,J24/1E15,IF(ABS(J24)&gt;=1E12,J24/1E12,IF(ABS(J24)&gt;=1E9,J24/1E9,IF(ABS(J24)&gt;=1E6,J24/1E6,J24)))),"#,##0.000")&amp;IF((IF(ABS(J24)&gt;=1E15,"PFLOPs",IF(ABS(J24)&gt;=1E12,"TFLOPs",IF(ABS(J24)&gt;=1E9,"GFLOPs",IF(ABS(J24)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(J24)&gt;=1E15,"PFLOPs",IF(ABS(J24)&gt;=1E12,"TFLOPs",IF(ABS(J24)&gt;=1E9,"GFLOPs",IF(ABS(J24)&gt;=1E6,"MFLOPs","flops"))))))</f>
         <v>23.550 GFLOPs</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="G23" s="30">
+      <c r="F24" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G24" s="30">
         <f>'Prefill_8K'!$AF$13</f>
         <v>228397682114560.0</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H24" s="30">
         <f>'Prefill_8K'!$AI$13</f>
         <v>55652568907776.0</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I24" s="30">
         <f>'Decode_1M'!$AF$13</f>
         <v>140355752110.0</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J24" s="30">
         <f>'Decode_1M'!$AI$13</f>
         <v>23549694126.0</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
-      <c r="K26" s="28" t="s">
-        <v>459</v>
-      </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="S26" s="3" t="s">
+    <row r="27" spans="1:20">
+      <c r="S27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="K27" t="s">
-        <v>463</v>
-      </c>
-      <c r="L27" t="s">
-        <v>464</v>
-      </c>
-      <c r="M27" t="s">
-        <v>465</v>
-      </c>
-      <c r="N27" t="s">
-        <v>466</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="T27" s="30">
-        <f>G23/1e+12</f>
+      <c r="T27" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="S28" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="T28" s="30">
+        <f>G24/1e+12</f>
         <v>228.39768211456</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
-      <c r="K28" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="L28" s="31" t="str">
-        <f>TEXT(IF(ABS(O28)&gt;=1E12,O28/1E12,IF(ABS(O28)&gt;=1E9,O28/1E9,IF(ABS(O28)&gt;=1E6,O28/1E6,IF(ABS(O28)&gt;=1E3,O28/1E3,O28)))),"#,##0.000")&amp;IF((IF(ABS(O28)&gt;=1E12,"TB",IF(ABS(O28)&gt;=1E9,"GB",IF(ABS(O28)&gt;=1E6,"MB",IF(ABS(O28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(O28)&gt;=1E12,"TB",IF(ABS(O28)&gt;=1E9,"GB",IF(ABS(O28)&gt;=1E6,"MB",IF(ABS(O28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>166.349 GB</v>
-      </c>
-      <c r="M28" s="31" t="str">
-        <f>TEXT(IF(ABS(P28)&gt;=1E12,P28/1E12,IF(ABS(P28)&gt;=1E9,P28/1E9,IF(ABS(P28)&gt;=1E6,P28/1E6,IF(ABS(P28)&gt;=1E3,P28/1E3,P28)))),"#,##0.000")&amp;IF((IF(ABS(P28)&gt;=1E12,"TB",IF(ABS(P28)&gt;=1E9,"GB",IF(ABS(P28)&gt;=1E6,"MB",IF(ABS(P28)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(P28)&gt;=1E12,"TB",IF(ABS(P28)&gt;=1E9,"GB",IF(ABS(P28)&gt;=1E6,"MB",IF(ABS(P28)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>29.582 GB</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="O28" s="30">
-        <f>G22</f>
-        <v>166349315548.0</v>
-      </c>
-      <c r="P28" s="30">
-        <f>H22</f>
-        <v>29581867388.0</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="T28" s="30">
-        <f>H23/1e+12</f>
+    <row r="29" spans="1:20">
+      <c r="S29" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="T29" s="30">
+        <f>H24/1e+12</f>
         <v>55.652568907776</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="K29" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="L29" s="31" t="str">
-        <f>TEXT(IF(ABS(O29)&gt;=1E12,O29/1E12,IF(ABS(O29)&gt;=1E9,O29/1E9,IF(ABS(O29)&gt;=1E6,O29/1E6,IF(ABS(O29)&gt;=1E3,O29/1E3,O29)))),"#,##0.000")&amp;IF((IF(ABS(O29)&gt;=1E12,"TB",IF(ABS(O29)&gt;=1E9,"GB",IF(ABS(O29)&gt;=1E6,"MB",IF(ABS(O29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(O29)&gt;=1E12,"TB",IF(ABS(O29)&gt;=1E9,"GB",IF(ABS(O29)&gt;=1E6,"MB",IF(ABS(O29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>166.349 GB</v>
-      </c>
-      <c r="M29" s="31" t="str">
-        <f>TEXT(IF(ABS(P29)&gt;=1E12,P29/1E12,IF(ABS(P29)&gt;=1E9,P29/1E9,IF(ABS(P29)&gt;=1E6,P29/1E6,IF(ABS(P29)&gt;=1E3,P29/1E3,P29)))),"#,##0.000")&amp;IF((IF(ABS(P29)&gt;=1E12,"TB",IF(ABS(P29)&gt;=1E9,"GB",IF(ABS(P29)&gt;=1E6,"MB",IF(ABS(P29)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(P29)&gt;=1E12,"TB",IF(ABS(P29)&gt;=1E9,"GB",IF(ABS(P29)&gt;=1E6,"MB",IF(ABS(P29)&gt;=1E3,"KB","bytes"))))))</f>
-        <v>29.582 GB</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="O29" s="30">
-        <f>I22</f>
-        <v>166349315548.0</v>
-      </c>
-      <c r="P29" s="30">
-        <f>J22</f>
-        <v>29581867388.0</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="T29" s="30">
-        <f>I23/1e+12</f>
-        <v>0.14035575211</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="S30" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="T30" s="30">
+        <f>I24/1e+12</f>
+        <v>0.14035575211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="S31" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="T31" s="30">
+        <f>J24/1e+12</f>
+        <v>0.023549694126</v>
+      </c>
+    </row>
+    <row r="34" spans="19:21">
+      <c r="S34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="35" spans="19:21">
+      <c r="S35" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="T35" s="30">
+        <f>G23/1e+09</f>
+        <v>166.349315548</v>
+      </c>
+    </row>
+    <row r="36" spans="19:21">
+      <c r="S36" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="T30" s="30">
-        <f>J23/1e+12</f>
-        <v>0.023549694126</v>
-      </c>
-    </row>
-    <row r="33" spans="19:21">
-      <c r="S33" s="3" t="s">
+      <c r="T36" s="30">
+        <f>H23/1e+09</f>
+        <v>29.581867388</v>
+      </c>
+    </row>
+    <row r="37" spans="19:21">
+      <c r="S37" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="T37" s="30">
+        <f>I23/1e+09</f>
+        <v>166.349315548</v>
+      </c>
+    </row>
+    <row r="38" spans="19:21">
+      <c r="S38" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="T38" s="30">
+        <f>J23/1e+09</f>
+        <v>29.581867388</v>
+      </c>
+    </row>
+    <row r="41" spans="19:21">
+      <c r="S41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="34" spans="19:21">
-      <c r="S34" s="4" t="s">
+      <c r="T41" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="42" spans="19:21">
+      <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T34" s="30">
+      <c r="T42" s="30">
         <f>G5/1e+12</f>
         <v>102.836037746688</v>
       </c>
-      <c r="U34" s="30">
+      <c r="U42" s="30">
         <f>H5/1e+12</f>
         <v>23.172382457856</v>
       </c>
     </row>
-    <row r="35" spans="19:21">
-      <c r="S35" s="4" t="s">
+    <row r="43" spans="19:21">
+      <c r="S43" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="30">
+      <c r="T43" s="30">
         <f>G6/1e+12</f>
         <v>124.846109360128</v>
       </c>
-      <c r="U35" s="30">
+      <c r="U43" s="30">
         <f>H6/1e+12</f>
         <v>31.765578121216</v>
       </c>
     </row>
-    <row r="36" spans="19:21">
-      <c r="S36" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="T36" s="30">
+    <row r="44" spans="19:21">
+      <c r="S44" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="T44" s="30">
         <f>G7/1e+12</f>
         <v>0.715535007744</v>
       </c>
-      <c r="U36" s="30">
+      <c r="U44" s="30">
         <f>H7/1e+12</f>
         <v>0.714608328704</v>
       </c>
     </row>
-    <row r="40" spans="19:21">
-      <c r="S40" s="3" t="s">
+    <row r="48" spans="19:21">
+      <c r="S48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T40" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="41" spans="19:21">
-      <c r="S41" s="4" t="s">
+      <c r="T48" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="49" spans="19:21">
+      <c r="S49" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T41" s="30">
+      <c r="T49" s="30">
         <f>I5/1e+09</f>
         <v>123.969470464</v>
       </c>
-      <c r="U41" s="30">
+      <c r="U49" s="30">
         <f>J5/1e+09</f>
         <v>19.452461056</v>
       </c>
     </row>
-    <row r="42" spans="19:21">
-      <c r="S42" s="4" t="s">
+    <row r="50" spans="19:21">
+      <c r="S50" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T42" s="30">
+      <c r="T50" s="30">
         <f>I6/1e+09</f>
         <v>15.240003584</v>
       </c>
-      <c r="U42" s="30">
+      <c r="U50" s="30">
         <f>J6/1e+09</f>
         <v>3.877634048</v>
       </c>
     </row>
-    <row r="43" spans="19:21">
-      <c r="S43" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="T43" s="30">
+    <row r="51" spans="19:21">
+      <c r="S51" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="T51" s="30">
         <f>I7/1e+09</f>
         <v>1.146278062</v>
       </c>
-      <c r="U43" s="30">
+      <c r="U51" s="30">
         <f>J7/1e+09</f>
         <v>0.219599022</v>
       </c>
     </row>
-    <row r="47" spans="19:21">
-      <c r="S47" s="3" t="s">
+    <row r="55" spans="19:21">
+      <c r="S55" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="48" spans="19:21">
-      <c r="S48" s="4" t="s">
+      <c r="T55" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="U55" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="19:21">
+      <c r="S56" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T48" s="30">
+      <c r="T56" s="30">
         <f>G14/1e+09</f>
         <v>7.45138496</v>
       </c>
-      <c r="U48" s="30">
+      <c r="U56" s="30">
         <f>H14/1e+09</f>
         <v>2.23750496</v>
       </c>
     </row>
-    <row r="49" spans="19:21">
-      <c r="S49" s="4" t="s">
+    <row r="57" spans="19:21">
+      <c r="S57" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T49" s="30">
+      <c r="T57" s="30">
         <f>G15/1e+09</f>
         <v>148.351461888</v>
       </c>
-      <c r="U49" s="30">
+      <c r="U57" s="30">
         <f>H15/1e+09</f>
         <v>19.57794048</v>
       </c>
     </row>
-    <row r="50" spans="19:21">
-      <c r="S50" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="T50" s="30">
+    <row r="58" spans="19:21">
+      <c r="S58" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="T58" s="30">
         <f>G16/1e+09</f>
         <v>3.314423644</v>
       </c>
-      <c r="U50" s="30">
+      <c r="U58" s="30">
         <f>H16/1e+09</f>
         <v>0.534376892</v>
       </c>
     </row>
-    <row r="54" spans="19:21">
-      <c r="S54" s="3" t="s">
+    <row r="62" spans="19:21">
+      <c r="S62" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="55" spans="19:21">
-      <c r="S55" s="4" t="s">
+      <c r="T62" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="63" spans="19:21">
+      <c r="S63" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T55" s="30">
+      <c r="T63" s="30">
         <f>I14/1e+09</f>
         <v>7.45138496</v>
       </c>
-      <c r="U55" s="30">
+      <c r="U63" s="30">
         <f>J14/1e+09</f>
         <v>2.23750496</v>
       </c>
     </row>
-    <row r="56" spans="19:21">
-      <c r="S56" s="4" t="s">
+    <row r="64" spans="19:21">
+      <c r="S64" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T56" s="30">
+      <c r="T64" s="30">
         <f>I15/1e+09</f>
         <v>148.351461888</v>
       </c>
-      <c r="U56" s="30">
+      <c r="U64" s="30">
         <f>J15/1e+09</f>
         <v>19.57794048</v>
       </c>
     </row>
-    <row r="57" spans="19:21">
-      <c r="S57" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="T57" s="30">
+    <row r="65" spans="19:21">
+      <c r="S65" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="T65" s="30">
         <f>I16/1e+09</f>
         <v>3.314423644</v>
       </c>
-      <c r="U57" s="30">
+      <c r="U65" s="30">
         <f>J16/1e+09</f>
         <v>0.534376892</v>
       </c>
     </row>
-    <row r="61" spans="19:21">
-      <c r="S61" s="3" t="s">
+    <row r="69" spans="19:21">
+      <c r="S69" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T61" s="3" t="s">
+      <c r="T69" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="62" spans="19:21">
-      <c r="S62" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="T62" s="30">
+    <row r="70" spans="19:21">
+      <c r="S70" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="T70" s="30">
+        <f>G14/1e+09</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="U70" s="30">
+        <f>H14/1e+09</f>
+        <v>2.23750496</v>
+      </c>
+    </row>
+    <row r="71" spans="19:21">
+      <c r="S71" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="T71" s="30">
+        <f>G15/1e+09</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="U71" s="30">
+        <f>H15/1e+09</f>
+        <v>19.57794048</v>
+      </c>
+    </row>
+    <row r="72" spans="19:21">
+      <c r="S72" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="T72" s="30">
         <f>G22/1e+09</f>
-        <v>166.349315548</v>
-      </c>
-    </row>
-    <row r="63" spans="19:21">
-      <c r="S63" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="T63" s="30">
+        <v>0.074203136</v>
+      </c>
+      <c r="U72" s="30">
         <f>H22/1e+09</f>
-        <v>29.581867388</v>
-      </c>
-    </row>
-    <row r="68" spans="19:20">
-      <c r="S68" s="3" t="s">
+        <v>0.074203136</v>
+      </c>
+    </row>
+    <row r="76" spans="19:21">
+      <c r="S76" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T68" s="3" t="s">
+      <c r="T76" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="U76" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="69" spans="19:20">
-      <c r="S69" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="T69" s="30">
+    <row r="77" spans="19:21">
+      <c r="S77" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="T77" s="30">
+        <f>I14/1e+09</f>
+        <v>7.45138496</v>
+      </c>
+      <c r="U77" s="30">
+        <f>J14/1e+09</f>
+        <v>2.23750496</v>
+      </c>
+    </row>
+    <row r="78" spans="19:21">
+      <c r="S78" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="T78" s="30">
+        <f>I15/1e+09</f>
+        <v>148.351461888</v>
+      </c>
+      <c r="U78" s="30">
+        <f>J15/1e+09</f>
+        <v>19.57794048</v>
+      </c>
+    </row>
+    <row r="79" spans="19:21">
+      <c r="S79" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="T79" s="30">
         <f>I22/1e+09</f>
-        <v>166.349315548</v>
-      </c>
-    </row>
-    <row r="70" spans="19:20">
-      <c r="S70" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="T70" s="30">
+        <v>7.232045056</v>
+      </c>
+      <c r="U79" s="30">
         <f>J22/1e+09</f>
-        <v>29.581867388</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="36" customHeight="1">
-      <c r="A92" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F92" s="2"/>
-    </row>
-    <row r="116" spans="1:6" ht="36" customHeight="1">
-      <c r="A116" s="2" t="s">
+        <v>7.232045056</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="S83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
+      <c r="S84" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="T84" s="30">
+        <f>G9/1e+09</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
+      <c r="S85" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="T85" s="30">
+        <f>H9/1e+09</f>
+        <v>40.635322112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
+      <c r="S86" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="T86" s="30">
+        <f>I9/1e+09</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
+      <c r="S87" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="T87" s="30">
+        <f>J9/1e+09</f>
+        <v>0.005865216</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="36" customHeight="1">
+      <c r="A93" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2" t="s">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F116" s="2"/>
+      <c r="F93" s="2"/>
+    </row>
+    <row r="117" spans="1:6" ht="36" customHeight="1">
+      <c r="A117" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F117" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="E116:F116"/>
+  <mergeCells count="4">
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="E117:F117"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12293,17 +12914,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="28" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
@@ -12311,21 +12932,21 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B6" s="31" t="str">
         <f>TEXT(IF(ABS(G6)&gt;=1E15,G6/1E15,IF(ABS(G6)&gt;=1E12,G6/1E12,IF(ABS(G6)&gt;=1E9,G6/1E9,IF(ABS(G6)&gt;=1E6,G6/1E6,G6)))),"#,##0.000")&amp;IF((IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G6)&gt;=1E15,"PFLOPs",IF(ABS(G6)&gt;=1E12,"TFLOPs",IF(ABS(G6)&gt;=1E9,"GFLOPs",IF(ABS(G6)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12336,7 +12957,7 @@
         <v>123.969 GFLOPs</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G6" s="30">
         <f>'Prefill_8K'!$AF$14</f>
@@ -12349,7 +12970,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B7" s="31" t="str">
         <f>TEXT(IF(ABS(G7)&gt;=1E15,G7/1E15,IF(ABS(G7)&gt;=1E12,G7/1E12,IF(ABS(G7)&gt;=1E9,G7/1E9,IF(ABS(G7)&gt;=1E6,G7/1E6,G7)))),"#,##0.000")&amp;IF((IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G7)&gt;=1E15,"PFLOPs",IF(ABS(G7)&gt;=1E12,"TFLOPs",IF(ABS(G7)&gt;=1E9,"GFLOPs",IF(ABS(G7)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12360,7 +12981,7 @@
         <v>15.240 GFLOPs</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G7" s="30">
         <f>'Prefill_8K'!$AF$15</f>
@@ -12373,7 +12994,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B8" s="31" t="str">
         <f>TEXT(IF(ABS(G8)&gt;=1E15,G8/1E15,IF(ABS(G8)&gt;=1E12,G8/1E12,IF(ABS(G8)&gt;=1E9,G8/1E9,IF(ABS(G8)&gt;=1E6,G8/1E6,G8)))),"#,##0.000")&amp;IF((IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G8)&gt;=1E15,"PFLOPs",IF(ABS(G8)&gt;=1E12,"TFLOPs",IF(ABS(G8)&gt;=1E9,"GFLOPs",IF(ABS(G8)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12384,7 +13005,7 @@
         <v>1.146 GFLOPs</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G8" s="30">
         <f>'Prefill_8K'!$AO$48</f>
@@ -12397,7 +13018,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="29" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B9" s="29" t="str">
         <f>TEXT(IF(ABS(G9)&gt;=1E15,G9/1E15,IF(ABS(G9)&gt;=1E12,G9/1E12,IF(ABS(G9)&gt;=1E9,G9/1E9,IF(ABS(G9)&gt;=1E6,G9/1E6,G9)))),"#,##0.000")&amp;IF((IF(ABS(G9)&gt;=1E15,"PFLOPs",IF(ABS(G9)&gt;=1E12,"TFLOPs",IF(ABS(G9)&gt;=1E9,"GFLOPs",IF(ABS(G9)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G9)&gt;=1E15,"PFLOPs",IF(ABS(G9)&gt;=1E12,"TFLOPs",IF(ABS(G9)&gt;=1E9,"GFLOPs",IF(ABS(G9)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12408,7 +13029,7 @@
         <v>140.356 GFLOPs</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G9" s="30">
         <f>'Prefill_8K'!$AF$13</f>
@@ -12421,7 +13042,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B10" s="31" t="str">
         <f>TEXT(IF(ABS(G10)&gt;=1E15,G10/1E15,IF(ABS(G10)&gt;=1E12,G10/1E12,IF(ABS(G10)&gt;=1E9,G10/1E9,IF(ABS(G10)&gt;=1E6,G10/1E6,G10)))),"#,##0.000")&amp;IF((IF(ABS(G10)&gt;=1E15,"PFLOPs",IF(ABS(G10)&gt;=1E12,"TFLOPs",IF(ABS(G10)&gt;=1E9,"GFLOPs",IF(ABS(G10)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G10)&gt;=1E15,"PFLOPs",IF(ABS(G10)&gt;=1E12,"TFLOPs",IF(ABS(G10)&gt;=1E9,"GFLOPs",IF(ABS(G10)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12432,7 +13053,7 @@
         <v>140.356 GFLOPs</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G10" s="30">
         <f>'Prefill_8K'!$AF$13</f>
@@ -12445,7 +13066,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B11" s="31" t="str">
         <f>TEXT(IF(ABS(G11)&gt;=1E12,G11/1E12,IF(ABS(G11)&gt;=1E9,G11/1E9,IF(ABS(G11)&gt;=1E6,G11/1E6,IF(ABS(G11)&gt;=1E3,G11/1E3,G11)))),"#,##0.000")&amp;IF((IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G11)&gt;=1E12,"TB",IF(ABS(G11)&gt;=1E9,"GB",IF(ABS(G11)&gt;=1E6,"MB",IF(ABS(G11)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12456,7 +13077,7 @@
         <v>0.000 B</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G11" s="30">
         <f>'Prefill_8K'!$AQ$48</f>
@@ -12469,7 +13090,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B12" s="31" t="str">
         <f>TEXT(IF(ABS(G12)&gt;=1E12,G12/1E12,IF(ABS(G12)&gt;=1E9,G12/1E9,IF(ABS(G12)&gt;=1E6,G12/1E6,IF(ABS(G12)&gt;=1E3,G12/1E3,G12)))),"#,##0.000")&amp;IF((IF(ABS(G12)&gt;=1E12,"T",IF(ABS(G12)&gt;=1E9,"G",IF(ABS(G12)&gt;=1E6,"M",IF(ABS(G12)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G12)&gt;=1E12,"T",IF(ABS(G12)&gt;=1E9,"G",IF(ABS(G12)&gt;=1E6,"M",IF(ABS(G12)&gt;=1E3,"K",""))))))</f>
@@ -12480,7 +13101,7 @@
         <v>5.086 G</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G12" s="30">
         <f>'Prefill_8K'!$AY$49</f>
@@ -12493,7 +13114,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B13" s="31" t="str">
         <f>TEXT(IF(ABS(G13)&gt;=1E12,G13/1E12,IF(ABS(G13)&gt;=1E9,G13/1E9,IF(ABS(G13)&gt;=1E6,G13/1E6,IF(ABS(G13)&gt;=1E3,G13/1E3,G13)))),"#,##0.000")&amp;IF((IF(ABS(G13)&gt;=1E12,"T",IF(ABS(G13)&gt;=1E9,"G",IF(ABS(G13)&gt;=1E6,"M",IF(ABS(G13)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G13)&gt;=1E12,"T",IF(ABS(G13)&gt;=1E9,"G",IF(ABS(G13)&gt;=1E6,"M",IF(ABS(G13)&gt;=1E3,"K",""))))))</f>
@@ -12504,7 +13125,7 @@
         <v>278.155 G</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G13" s="30">
         <f>'Prefill_8K'!$AY$50</f>
@@ -12517,7 +13138,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>TEXT(IF(ABS(G14)&gt;=1E12,G14/1E12,IF(ABS(G14)&gt;=1E9,G14/1E9,IF(ABS(G14)&gt;=1E6,G14/1E6,IF(ABS(G14)&gt;=1E3,G14/1E3,G14)))),"#,##0.000")&amp;IF((IF(ABS(G14)&gt;=1E12,"T",IF(ABS(G14)&gt;=1E9,"G",IF(ABS(G14)&gt;=1E6,"M",IF(ABS(G14)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G14)&gt;=1E12,"T",IF(ABS(G14)&gt;=1E9,"G",IF(ABS(G14)&gt;=1E6,"M",IF(ABS(G14)&gt;=1E3,"K",""))))))</f>
@@ -12528,7 +13149,7 @@
         <v>1.093 G</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G14" s="30">
         <f>'Prefill_8K'!$AY$51</f>
@@ -12541,7 +13162,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="29" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B15" s="29" t="str">
         <f>TEXT(IF(ABS(G15)&gt;=1E12,G15/1E12,IF(ABS(G15)&gt;=1E9,G15/1E9,IF(ABS(G15)&gt;=1E6,G15/1E6,IF(ABS(G15)&gt;=1E3,G15/1E3,G15)))),"#,##0.000")&amp;IF((IF(ABS(G15)&gt;=1E12,"T",IF(ABS(G15)&gt;=1E9,"G",IF(ABS(G15)&gt;=1E6,"M",IF(ABS(G15)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G15)&gt;=1E12,"T",IF(ABS(G15)&gt;=1E9,"G",IF(ABS(G15)&gt;=1E6,"M",IF(ABS(G15)&gt;=1E3,"K",""))))))</f>
@@ -12552,7 +13173,7 @@
         <v>284.335 G</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G15" s="30">
         <f>'Prefill_8K'!$AY$52</f>
@@ -12565,7 +13186,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B16" s="31" t="str">
         <f>TEXT(IF(ABS(G16)&gt;=1E12,G16/1E12,IF(ABS(G16)&gt;=1E9,G16/1E9,IF(ABS(G16)&gt;=1E6,G16/1E6,IF(ABS(G16)&gt;=1E3,G16/1E3,G16)))),"#,##0.000")&amp;IF((IF(ABS(G16)&gt;=1E12,"TB",IF(ABS(G16)&gt;=1E9,"GB",IF(ABS(G16)&gt;=1E6,"MB",IF(ABS(G16)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G16)&gt;=1E12,"TB",IF(ABS(G16)&gt;=1E9,"GB",IF(ABS(G16)&gt;=1E6,"MB",IF(ABS(G16)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12576,7 +13197,7 @@
         <v>7.451 GB</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G16" s="30">
         <f>'Prefill_8K'!$BA$49</f>
@@ -12589,7 +13210,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B17" s="31" t="str">
         <f>TEXT(IF(ABS(G17)&gt;=1E12,G17/1E12,IF(ABS(G17)&gt;=1E9,G17/1E9,IF(ABS(G17)&gt;=1E6,G17/1E6,IF(ABS(G17)&gt;=1E3,G17/1E3,G17)))),"#,##0.000")&amp;IF((IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G17)&gt;=1E12,"TB",IF(ABS(G17)&gt;=1E9,"GB",IF(ABS(G17)&gt;=1E6,"MB",IF(ABS(G17)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12600,7 +13221,7 @@
         <v>148.351 GB</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="G17" s="30">
         <f>'Prefill_8K'!$BA$50</f>
@@ -12613,7 +13234,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B18" s="31" t="str">
         <f>TEXT(IF(ABS(G18)&gt;=1E12,G18/1E12,IF(ABS(G18)&gt;=1E9,G18/1E9,IF(ABS(G18)&gt;=1E6,G18/1E6,IF(ABS(G18)&gt;=1E3,G18/1E3,G18)))),"#,##0.000")&amp;IF((IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G18)&gt;=1E12,"TB",IF(ABS(G18)&gt;=1E9,"GB",IF(ABS(G18)&gt;=1E6,"MB",IF(ABS(G18)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12624,7 +13245,7 @@
         <v>3.314 GB</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G18" s="30">
         <f>'Prefill_8K'!$BA$51</f>
@@ -12637,7 +13258,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="29" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B19" s="29" t="str">
         <f>TEXT(IF(ABS(G19)&gt;=1E12,G19/1E12,IF(ABS(G19)&gt;=1E9,G19/1E9,IF(ABS(G19)&gt;=1E6,G19/1E6,IF(ABS(G19)&gt;=1E3,G19/1E3,G19)))),"#,##0.000")&amp;IF((IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G19)&gt;=1E12,"TB",IF(ABS(G19)&gt;=1E9,"GB",IF(ABS(G19)&gt;=1E6,"MB",IF(ABS(G19)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12648,7 +13269,7 @@
         <v>159.117 GB</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G19" s="30">
         <f>'Prefill_8K'!$BA$52</f>
@@ -12661,7 +13282,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B20" s="31" t="str">
         <f>TEXT(IF(ABS(G20)&gt;=1E12,G20/1E12,IF(ABS(G20)&gt;=1E9,G20/1E9,IF(ABS(G20)&gt;=1E6,G20/1E6,IF(ABS(G20)&gt;=1E3,G20/1E3,G20)))),"#,##0.000")&amp;IF((IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G20)&gt;=1E12,"TB",IF(ABS(G20)&gt;=1E9,"GB",IF(ABS(G20)&gt;=1E6,"MB",IF(ABS(G20)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12672,7 +13293,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G20" s="30">
         <f>'Prefill_8K'!$U$35</f>
@@ -12685,7 +13306,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B21" s="31" t="str">
         <f>TEXT(IF(ABS(G21)&gt;=1E12,G21/1E12,IF(ABS(G21)&gt;=1E9,G21/1E9,IF(ABS(G21)&gt;=1E6,G21/1E6,IF(ABS(G21)&gt;=1E3,G21/1E3,G21)))),"#,##0.000")&amp;IF((IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G21)&gt;=1E12,"TB",IF(ABS(G21)&gt;=1E9,"GB",IF(ABS(G21)&gt;=1E6,"MB",IF(ABS(G21)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12696,7 +13317,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G21" s="30">
         <f>'Prefill_8K'!$U$36</f>
@@ -12709,7 +13330,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B22" s="31" t="str">
         <f>TEXT(IF(ABS(G22)&gt;=1E12,G22/1E12,IF(ABS(G22)&gt;=1E9,G22/1E9,IF(ABS(G22)&gt;=1E6,G22/1E6,IF(ABS(G22)&gt;=1E3,G22/1E3,G22)))),"#,##0.000")&amp;IF((IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G22)&gt;=1E12,"TB",IF(ABS(G22)&gt;=1E9,"GB",IF(ABS(G22)&gt;=1E6,"MB",IF(ABS(G22)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12720,7 +13341,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G22" s="30">
         <f>'Prefill_8K'!$U$37</f>
@@ -12733,7 +13354,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B23" s="31" t="str">
         <f>TEXT(IF(ABS(G23)&gt;=1E12,G23/1E12,IF(ABS(G23)&gt;=1E9,G23/1E9,IF(ABS(G23)&gt;=1E6,G23/1E6,IF(ABS(G23)&gt;=1E3,G23/1E3,G23)))),"#,##0.000")&amp;IF((IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G23)&gt;=1E12,"TB",IF(ABS(G23)&gt;=1E9,"GB",IF(ABS(G23)&gt;=1E6,"MB",IF(ABS(G23)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12744,7 +13365,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G23" s="30">
         <f>'Prefill_8K'!$U$38</f>
@@ -12757,7 +13378,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="29" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B24" s="29" t="str">
         <f>TEXT(IF(ABS(G24)&gt;=1E12,G24/1E12,IF(ABS(G24)&gt;=1E9,G24/1E9,IF(ABS(G24)&gt;=1E6,G24/1E6,IF(ABS(G24)&gt;=1E3,G24/1E3,G24)))),"#,##0.000")&amp;IF((IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G24)&gt;=1E12,"TB",IF(ABS(G24)&gt;=1E9,"GB",IF(ABS(G24)&gt;=1E6,"MB",IF(ABS(G24)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12768,7 +13389,7 @@
         <v>166.349 GB</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G24" s="30">
         <f>'Prefill_8K'!$BA$52+'Prefill_8K'!$U$38</f>
@@ -12781,7 +13402,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="28" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -12789,21 +13410,21 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B28" s="31" t="str">
         <f>TEXT(IF(ABS(G28)&gt;=1E15,G28/1E15,IF(ABS(G28)&gt;=1E12,G28/1E12,IF(ABS(G28)&gt;=1E9,G28/1E9,IF(ABS(G28)&gt;=1E6,G28/1E6,G28)))),"#,##0.000")&amp;IF((IF(ABS(G28)&gt;=1E15,"PFLOPs",IF(ABS(G28)&gt;=1E12,"TFLOPs",IF(ABS(G28)&gt;=1E9,"GFLOPs",IF(ABS(G28)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G28)&gt;=1E15,"PFLOPs",IF(ABS(G28)&gt;=1E12,"TFLOPs",IF(ABS(G28)&gt;=1E9,"GFLOPs",IF(ABS(G28)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12814,7 +13435,7 @@
         <v>19.452 GFLOPs</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G28" s="30">
         <f>'Prefill_8K'!$AI$14</f>
@@ -12827,7 +13448,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B29" s="31" t="str">
         <f>TEXT(IF(ABS(G29)&gt;=1E15,G29/1E15,IF(ABS(G29)&gt;=1E12,G29/1E12,IF(ABS(G29)&gt;=1E9,G29/1E9,IF(ABS(G29)&gt;=1E6,G29/1E6,G29)))),"#,##0.000")&amp;IF((IF(ABS(G29)&gt;=1E15,"PFLOPs",IF(ABS(G29)&gt;=1E12,"TFLOPs",IF(ABS(G29)&gt;=1E9,"GFLOPs",IF(ABS(G29)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G29)&gt;=1E15,"PFLOPs",IF(ABS(G29)&gt;=1E12,"TFLOPs",IF(ABS(G29)&gt;=1E9,"GFLOPs",IF(ABS(G29)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12838,7 +13459,7 @@
         <v>3.878 GFLOPs</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G29" s="30">
         <f>'Prefill_8K'!$AI$15</f>
@@ -12851,7 +13472,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B30" s="31" t="str">
         <f>TEXT(IF(ABS(G30)&gt;=1E15,G30/1E15,IF(ABS(G30)&gt;=1E12,G30/1E12,IF(ABS(G30)&gt;=1E9,G30/1E9,IF(ABS(G30)&gt;=1E6,G30/1E6,G30)))),"#,##0.000")&amp;IF((IF(ABS(G30)&gt;=1E15,"PFLOPs",IF(ABS(G30)&gt;=1E12,"TFLOPs",IF(ABS(G30)&gt;=1E9,"GFLOPs",IF(ABS(G30)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G30)&gt;=1E15,"PFLOPs",IF(ABS(G30)&gt;=1E12,"TFLOPs",IF(ABS(G30)&gt;=1E9,"GFLOPs",IF(ABS(G30)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12862,7 +13483,7 @@
         <v>219.599 MFLOPs</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G30" s="30">
         <f>'Prefill_8K'!$AP$48</f>
@@ -12875,7 +13496,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="29" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B31" s="29" t="str">
         <f>TEXT(IF(ABS(G31)&gt;=1E15,G31/1E15,IF(ABS(G31)&gt;=1E12,G31/1E12,IF(ABS(G31)&gt;=1E9,G31/1E9,IF(ABS(G31)&gt;=1E6,G31/1E6,G31)))),"#,##0.000")&amp;IF((IF(ABS(G31)&gt;=1E15,"PFLOPs",IF(ABS(G31)&gt;=1E12,"TFLOPs",IF(ABS(G31)&gt;=1E9,"GFLOPs",IF(ABS(G31)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G31)&gt;=1E15,"PFLOPs",IF(ABS(G31)&gt;=1E12,"TFLOPs",IF(ABS(G31)&gt;=1E9,"GFLOPs",IF(ABS(G31)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12886,7 +13507,7 @@
         <v>23.550 GFLOPs</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G31" s="30">
         <f>'Prefill_8K'!$AI$13</f>
@@ -12899,7 +13520,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B32" s="31" t="str">
         <f>TEXT(IF(ABS(G32)&gt;=1E15,G32/1E15,IF(ABS(G32)&gt;=1E12,G32/1E12,IF(ABS(G32)&gt;=1E9,G32/1E9,IF(ABS(G32)&gt;=1E6,G32/1E6,G32)))),"#,##0.000")&amp;IF((IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops")))))="",""," "&amp;(IF(ABS(G32)&gt;=1E15,"PFLOPs",IF(ABS(G32)&gt;=1E12,"TFLOPs",IF(ABS(G32)&gt;=1E9,"GFLOPs",IF(ABS(G32)&gt;=1E6,"MFLOPs","flops"))))))</f>
@@ -12910,7 +13531,7 @@
         <v>23.550 GFLOPs</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G32" s="30">
         <f>'Prefill_8K'!$AI$13</f>
@@ -12923,7 +13544,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B33" s="31" t="str">
         <f>TEXT(IF(ABS(G33)&gt;=1E12,G33/1E12,IF(ABS(G33)&gt;=1E9,G33/1E9,IF(ABS(G33)&gt;=1E6,G33/1E6,IF(ABS(G33)&gt;=1E3,G33/1E3,G33)))),"#,##0.000")&amp;IF((IF(ABS(G33)&gt;=1E12,"TB",IF(ABS(G33)&gt;=1E9,"GB",IF(ABS(G33)&gt;=1E6,"MB",IF(ABS(G33)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G33)&gt;=1E12,"TB",IF(ABS(G33)&gt;=1E9,"GB",IF(ABS(G33)&gt;=1E6,"MB",IF(ABS(G33)&gt;=1E3,"KB","bytes"))))))</f>
@@ -12934,7 +13555,7 @@
         <v>5.865 MB</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G33" s="30">
         <f>'Prefill_8K'!$AR$48</f>
@@ -12947,7 +13568,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B34" s="31" t="str">
         <f>TEXT(IF(ABS(G34)&gt;=1E12,G34/1E12,IF(ABS(G34)&gt;=1E9,G34/1E9,IF(ABS(G34)&gt;=1E6,G34/1E6,IF(ABS(G34)&gt;=1E3,G34/1E3,G34)))),"#,##0.000")&amp;IF((IF(ABS(G34)&gt;=1E12,"T",IF(ABS(G34)&gt;=1E9,"G",IF(ABS(G34)&gt;=1E6,"M",IF(ABS(G34)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G34)&gt;=1E12,"T",IF(ABS(G34)&gt;=1E9,"G",IF(ABS(G34)&gt;=1E6,"M",IF(ABS(G34)&gt;=1E3,"K",""))))))</f>
@@ -12958,7 +13579,7 @@
         <v>1.140 G</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G34" s="30">
         <f>'Prefill_8K'!$AZ$49</f>
@@ -12971,7 +13592,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B35" s="31" t="str">
         <f>TEXT(IF(ABS(G35)&gt;=1E12,G35/1E12,IF(ABS(G35)&gt;=1E9,G35/1E9,IF(ABS(G35)&gt;=1E6,G35/1E6,IF(ABS(G35)&gt;=1E3,G35/1E3,G35)))),"#,##0.000")&amp;IF((IF(ABS(G35)&gt;=1E12,"T",IF(ABS(G35)&gt;=1E9,"G",IF(ABS(G35)&gt;=1E6,"M",IF(ABS(G35)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G35)&gt;=1E12,"T",IF(ABS(G35)&gt;=1E9,"G",IF(ABS(G35)&gt;=1E6,"M",IF(ABS(G35)&gt;=1E3,"K",""))))))</f>
@@ -12982,7 +13603,7 @@
         <v>35.758 G</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G35" s="30">
         <f>'Prefill_8K'!$AZ$50</f>
@@ -12995,7 +13616,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B36" s="31" t="str">
         <f>TEXT(IF(ABS(G36)&gt;=1E12,G36/1E12,IF(ABS(G36)&gt;=1E9,G36/1E9,IF(ABS(G36)&gt;=1E6,G36/1E6,IF(ABS(G36)&gt;=1E3,G36/1E3,G36)))),"#,##0.000")&amp;IF((IF(ABS(G36)&gt;=1E12,"T",IF(ABS(G36)&gt;=1E9,"G",IF(ABS(G36)&gt;=1E6,"M",IF(ABS(G36)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G36)&gt;=1E12,"T",IF(ABS(G36)&gt;=1E9,"G",IF(ABS(G36)&gt;=1E6,"M",IF(ABS(G36)&gt;=1E3,"K",""))))))</f>
@@ -13006,7 +13627,7 @@
         <v>166.690 M</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G36" s="30">
         <f>'Prefill_8K'!$AZ$51</f>
@@ -13019,7 +13640,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="29" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B37" s="29" t="str">
         <f>TEXT(IF(ABS(G37)&gt;=1E12,G37/1E12,IF(ABS(G37)&gt;=1E9,G37/1E9,IF(ABS(G37)&gt;=1E6,G37/1E6,IF(ABS(G37)&gt;=1E3,G37/1E3,G37)))),"#,##0.000")&amp;IF((IF(ABS(G37)&gt;=1E12,"T",IF(ABS(G37)&gt;=1E9,"G",IF(ABS(G37)&gt;=1E6,"M",IF(ABS(G37)&gt;=1E3,"K","")))))="",""," "&amp;(IF(ABS(G37)&gt;=1E12,"T",IF(ABS(G37)&gt;=1E9,"G",IF(ABS(G37)&gt;=1E6,"M",IF(ABS(G37)&gt;=1E3,"K",""))))))</f>
@@ -13030,7 +13651,7 @@
         <v>37.064 G</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G37" s="30">
         <f>'Prefill_8K'!$AZ$52</f>
@@ -13043,7 +13664,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B38" s="31" t="str">
         <f>TEXT(IF(ABS(G38)&gt;=1E12,G38/1E12,IF(ABS(G38)&gt;=1E9,G38/1E9,IF(ABS(G38)&gt;=1E6,G38/1E6,IF(ABS(G38)&gt;=1E3,G38/1E3,G38)))),"#,##0.000")&amp;IF((IF(ABS(G38)&gt;=1E12,"TB",IF(ABS(G38)&gt;=1E9,"GB",IF(ABS(G38)&gt;=1E6,"MB",IF(ABS(G38)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G38)&gt;=1E12,"TB",IF(ABS(G38)&gt;=1E9,"GB",IF(ABS(G38)&gt;=1E6,"MB",IF(ABS(G38)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13054,7 +13675,7 @@
         <v>2.238 GB</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G38" s="30">
         <f>'Prefill_8K'!$BB$49</f>
@@ -13067,7 +13688,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B39" s="31" t="str">
         <f>TEXT(IF(ABS(G39)&gt;=1E12,G39/1E12,IF(ABS(G39)&gt;=1E9,G39/1E9,IF(ABS(G39)&gt;=1E6,G39/1E6,IF(ABS(G39)&gt;=1E3,G39/1E3,G39)))),"#,##0.000")&amp;IF((IF(ABS(G39)&gt;=1E12,"TB",IF(ABS(G39)&gt;=1E9,"GB",IF(ABS(G39)&gt;=1E6,"MB",IF(ABS(G39)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G39)&gt;=1E12,"TB",IF(ABS(G39)&gt;=1E9,"GB",IF(ABS(G39)&gt;=1E6,"MB",IF(ABS(G39)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13078,7 +13699,7 @@
         <v>19.578 GB</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="G39" s="30">
         <f>'Prefill_8K'!$BB$50</f>
@@ -13091,7 +13712,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B40" s="31" t="str">
         <f>TEXT(IF(ABS(G40)&gt;=1E12,G40/1E12,IF(ABS(G40)&gt;=1E9,G40/1E9,IF(ABS(G40)&gt;=1E6,G40/1E6,IF(ABS(G40)&gt;=1E3,G40/1E3,G40)))),"#,##0.000")&amp;IF((IF(ABS(G40)&gt;=1E12,"TB",IF(ABS(G40)&gt;=1E9,"GB",IF(ABS(G40)&gt;=1E6,"MB",IF(ABS(G40)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G40)&gt;=1E12,"TB",IF(ABS(G40)&gt;=1E9,"GB",IF(ABS(G40)&gt;=1E6,"MB",IF(ABS(G40)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13102,7 +13723,7 @@
         <v>534.377 MB</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G40" s="30">
         <f>'Prefill_8K'!$BB$51</f>
@@ -13115,7 +13736,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="29" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B41" s="29" t="str">
         <f>TEXT(IF(ABS(G41)&gt;=1E12,G41/1E12,IF(ABS(G41)&gt;=1E9,G41/1E9,IF(ABS(G41)&gt;=1E6,G41/1E6,IF(ABS(G41)&gt;=1E3,G41/1E3,G41)))),"#,##0.000")&amp;IF((IF(ABS(G41)&gt;=1E12,"TB",IF(ABS(G41)&gt;=1E9,"GB",IF(ABS(G41)&gt;=1E6,"MB",IF(ABS(G41)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G41)&gt;=1E12,"TB",IF(ABS(G41)&gt;=1E9,"GB",IF(ABS(G41)&gt;=1E6,"MB",IF(ABS(G41)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13126,7 +13747,7 @@
         <v>22.350 GB</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G41" s="30">
         <f>'Prefill_8K'!$BB$52</f>
@@ -13139,7 +13760,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B42" s="31" t="str">
         <f>TEXT(IF(ABS(G42)&gt;=1E12,G42/1E12,IF(ABS(G42)&gt;=1E9,G42/1E9,IF(ABS(G42)&gt;=1E6,G42/1E6,IF(ABS(G42)&gt;=1E3,G42/1E3,G42)))),"#,##0.000")&amp;IF((IF(ABS(G42)&gt;=1E12,"TB",IF(ABS(G42)&gt;=1E9,"GB",IF(ABS(G42)&gt;=1E6,"MB",IF(ABS(G42)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G42)&gt;=1E12,"TB",IF(ABS(G42)&gt;=1E9,"GB",IF(ABS(G42)&gt;=1E6,"MB",IF(ABS(G42)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13150,7 +13771,7 @@
         <v>5.811 GB</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G42" s="30">
         <f>'Prefill_8K'!$X$35</f>
@@ -13163,7 +13784,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B43" s="31" t="str">
         <f>TEXT(IF(ABS(G43)&gt;=1E12,G43/1E12,IF(ABS(G43)&gt;=1E9,G43/1E9,IF(ABS(G43)&gt;=1E6,G43/1E6,IF(ABS(G43)&gt;=1E3,G43/1E3,G43)))),"#,##0.000")&amp;IF((IF(ABS(G43)&gt;=1E12,"TB",IF(ABS(G43)&gt;=1E9,"GB",IF(ABS(G43)&gt;=1E6,"MB",IF(ABS(G43)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G43)&gt;=1E12,"TB",IF(ABS(G43)&gt;=1E9,"GB",IF(ABS(G43)&gt;=1E6,"MB",IF(ABS(G43)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13174,7 +13795,7 @@
         <v>1.409 GB</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G43" s="30">
         <f>'Prefill_8K'!$X$36</f>
@@ -13187,7 +13808,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B44" s="31" t="str">
         <f>TEXT(IF(ABS(G44)&gt;=1E12,G44/1E12,IF(ABS(G44)&gt;=1E9,G44/1E9,IF(ABS(G44)&gt;=1E6,G44/1E6,IF(ABS(G44)&gt;=1E3,G44/1E3,G44)))),"#,##0.000")&amp;IF((IF(ABS(G44)&gt;=1E12,"TB",IF(ABS(G44)&gt;=1E9,"GB",IF(ABS(G44)&gt;=1E6,"MB",IF(ABS(G44)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G44)&gt;=1E12,"TB",IF(ABS(G44)&gt;=1E9,"GB",IF(ABS(G44)&gt;=1E6,"MB",IF(ABS(G44)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13198,7 +13819,7 @@
         <v>12.206 MB</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G44" s="30">
         <f>'Prefill_8K'!$X$37</f>
@@ -13211,7 +13832,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B45" s="31" t="str">
         <f>TEXT(IF(ABS(G45)&gt;=1E12,G45/1E12,IF(ABS(G45)&gt;=1E9,G45/1E9,IF(ABS(G45)&gt;=1E6,G45/1E6,IF(ABS(G45)&gt;=1E3,G45/1E3,G45)))),"#,##0.000")&amp;IF((IF(ABS(G45)&gt;=1E12,"TB",IF(ABS(G45)&gt;=1E9,"GB",IF(ABS(G45)&gt;=1E6,"MB",IF(ABS(G45)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G45)&gt;=1E12,"TB",IF(ABS(G45)&gt;=1E9,"GB",IF(ABS(G45)&gt;=1E6,"MB",IF(ABS(G45)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13222,7 +13843,7 @@
         <v>7.232 GB</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G45" s="30">
         <f>'Prefill_8K'!$X$38</f>
@@ -13235,7 +13856,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="29" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B46" s="29" t="str">
         <f>TEXT(IF(ABS(G46)&gt;=1E12,G46/1E12,IF(ABS(G46)&gt;=1E9,G46/1E9,IF(ABS(G46)&gt;=1E6,G46/1E6,IF(ABS(G46)&gt;=1E3,G46/1E3,G46)))),"#,##0.000")&amp;IF((IF(ABS(G46)&gt;=1E12,"TB",IF(ABS(G46)&gt;=1E9,"GB",IF(ABS(G46)&gt;=1E6,"MB",IF(ABS(G46)&gt;=1E3,"KB","bytes")))))="",""," "&amp;(IF(ABS(G46)&gt;=1E12,"TB",IF(ABS(G46)&gt;=1E9,"GB",IF(ABS(G46)&gt;=1E6,"MB",IF(ABS(G46)&gt;=1E3,"KB","bytes"))))))</f>
@@ -13246,7 +13867,7 @@
         <v>29.582 GB</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G46" s="30">
         <f>'Prefill_8K'!$BB$52+'Prefill_8K'!$X$38</f>
@@ -13278,32 +13899,32 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13314,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D4" s="34">
         <f>IF(C4="window",0,IF(C4="short",ShortRatio,LongRatio))</f>
@@ -13337,7 +13958,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D5" s="34">
         <f>IF(C5="window",0,IF(C5="short",ShortRatio,LongRatio))</f>
@@ -13360,7 +13981,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D6" s="34">
         <f>IF(C6="window",0,IF(C6="short",ShortRatio,LongRatio))</f>
@@ -13383,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D7" s="34">
         <f>IF(C7="window",0,IF(C7="short",ShortRatio,LongRatio))</f>
@@ -13406,7 +14027,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D8" s="34">
         <f>IF(C8="window",0,IF(C8="short",ShortRatio,LongRatio))</f>
@@ -13429,7 +14050,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D9" s="34">
         <f>IF(C9="window",0,IF(C9="short",ShortRatio,LongRatio))</f>
@@ -13452,7 +14073,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D10" s="34">
         <f>IF(C10="window",0,IF(C10="short",ShortRatio,LongRatio))</f>
@@ -13475,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D11" s="34">
         <f>IF(C11="window",0,IF(C11="short",ShortRatio,LongRatio))</f>
@@ -13498,7 +14119,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D12" s="34">
         <f>IF(C12="window",0,IF(C12="short",ShortRatio,LongRatio))</f>
@@ -13521,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D13" s="34">
         <f>IF(C13="window",0,IF(C13="short",ShortRatio,LongRatio))</f>
@@ -13544,7 +14165,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D14" s="34">
         <f>IF(C14="window",0,IF(C14="short",ShortRatio,LongRatio))</f>
@@ -13567,7 +14188,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D15" s="34">
         <f>IF(C15="window",0,IF(C15="short",ShortRatio,LongRatio))</f>
@@ -13590,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D16" s="34">
         <f>IF(C16="window",0,IF(C16="short",ShortRatio,LongRatio))</f>
@@ -13613,7 +14234,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D17" s="34">
         <f>IF(C17="window",0,IF(C17="short",ShortRatio,LongRatio))</f>
@@ -13636,7 +14257,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D18" s="34">
         <f>IF(C18="window",0,IF(C18="short",ShortRatio,LongRatio))</f>
@@ -13659,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D19" s="34">
         <f>IF(C19="window",0,IF(C19="short",ShortRatio,LongRatio))</f>
@@ -13682,7 +14303,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D20" s="34">
         <f>IF(C20="window",0,IF(C20="short",ShortRatio,LongRatio))</f>
@@ -13705,7 +14326,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D21" s="34">
         <f>IF(C21="window",0,IF(C21="short",ShortRatio,LongRatio))</f>
@@ -13728,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D22" s="34">
         <f>IF(C22="window",0,IF(C22="short",ShortRatio,LongRatio))</f>
@@ -13751,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D23" s="34">
         <f>IF(C23="window",0,IF(C23="short",ShortRatio,LongRatio))</f>
@@ -13774,7 +14395,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D24" s="34">
         <f>IF(C24="window",0,IF(C24="short",ShortRatio,LongRatio))</f>
@@ -13797,7 +14418,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D25" s="34">
         <f>IF(C25="window",0,IF(C25="short",ShortRatio,LongRatio))</f>
@@ -13820,7 +14441,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D26" s="34">
         <f>IF(C26="window",0,IF(C26="short",ShortRatio,LongRatio))</f>
@@ -13843,7 +14464,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D27" s="34">
         <f>IF(C27="window",0,IF(C27="short",ShortRatio,LongRatio))</f>
@@ -13866,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D28" s="34">
         <f>IF(C28="window",0,IF(C28="short",ShortRatio,LongRatio))</f>
@@ -13889,7 +14510,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D29" s="34">
         <f>IF(C29="window",0,IF(C29="short",ShortRatio,LongRatio))</f>
@@ -13912,7 +14533,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D30" s="34">
         <f>IF(C30="window",0,IF(C30="short",ShortRatio,LongRatio))</f>
@@ -13935,7 +14556,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D31" s="34">
         <f>IF(C31="window",0,IF(C31="short",ShortRatio,LongRatio))</f>
@@ -13958,7 +14579,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D32" s="34">
         <f>IF(C32="window",0,IF(C32="short",ShortRatio,LongRatio))</f>
@@ -13981,7 +14602,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D33" s="34">
         <f>IF(C33="window",0,IF(C33="short",ShortRatio,LongRatio))</f>
@@ -14004,7 +14625,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D34" s="34">
         <f>IF(C34="window",0,IF(C34="short",ShortRatio,LongRatio))</f>
@@ -14027,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D35" s="34">
         <f>IF(C35="window",0,IF(C35="short",ShortRatio,LongRatio))</f>
@@ -14050,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D36" s="34">
         <f>IF(C36="window",0,IF(C36="short",ShortRatio,LongRatio))</f>
@@ -14073,7 +14694,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D37" s="34">
         <f>IF(C37="window",0,IF(C37="short",ShortRatio,LongRatio))</f>
@@ -14096,7 +14717,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D38" s="34">
         <f>IF(C38="window",0,IF(C38="short",ShortRatio,LongRatio))</f>
@@ -14119,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D39" s="34">
         <f>IF(C39="window",0,IF(C39="short",ShortRatio,LongRatio))</f>
@@ -14142,7 +14763,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D40" s="34">
         <f>IF(C40="window",0,IF(C40="short",ShortRatio,LongRatio))</f>
@@ -14165,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D41" s="34">
         <f>IF(C41="window",0,IF(C41="short",ShortRatio,LongRatio))</f>
@@ -14188,7 +14809,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D42" s="34">
         <f>IF(C42="window",0,IF(C42="short",ShortRatio,LongRatio))</f>
@@ -14211,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D43" s="34">
         <f>IF(C43="window",0,IF(C43="short",ShortRatio,LongRatio))</f>
@@ -14234,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D44" s="34">
         <f>IF(C44="window",0,IF(C44="short",ShortRatio,LongRatio))</f>
@@ -14257,7 +14878,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D45" s="34">
         <f>IF(C45="window",0,IF(C45="short",ShortRatio,LongRatio))</f>
@@ -14280,7 +14901,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D46" s="34">
         <f>IF(C46="window",0,IF(C46="short",ShortRatio,LongRatio))</f>
@@ -14303,7 +14924,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D47" s="34">
         <f>IF(C47="window",0,IF(C47="short",ShortRatio,LongRatio))</f>
@@ -14326,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D48" s="34">
         <f>IF(C48="window",0,IF(C48="short",ShortRatio,LongRatio))</f>
@@ -14349,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D49" s="34">
         <f>IF(C49="window",0,IF(C49="short",ShortRatio,LongRatio))</f>
@@ -14372,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D50" s="34">
         <f>IF(C50="window",0,IF(C50="short",ShortRatio,LongRatio))</f>
@@ -14395,7 +15016,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D51" s="34">
         <f>IF(C51="window",0,IF(C51="short",ShortRatio,LongRatio))</f>
@@ -14418,7 +15039,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D52" s="34">
         <f>IF(C52="window",0,IF(C52="short",ShortRatio,LongRatio))</f>
@@ -14441,7 +15062,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D53" s="34">
         <f>IF(C53="window",0,IF(C53="short",ShortRatio,LongRatio))</f>
@@ -14464,7 +15085,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D54" s="34">
         <f>IF(C54="window",0,IF(C54="short",ShortRatio,LongRatio))</f>
@@ -14487,7 +15108,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D55" s="34">
         <f>IF(C55="window",0,IF(C55="short",ShortRatio,LongRatio))</f>
@@ -14510,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D56" s="34">
         <f>IF(C56="window",0,IF(C56="short",ShortRatio,LongRatio))</f>
@@ -14533,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D57" s="34">
         <f>IF(C57="window",0,IF(C57="short",ShortRatio,LongRatio))</f>
@@ -14556,7 +15177,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D58" s="34">
         <f>IF(C58="window",0,IF(C58="short",ShortRatio,LongRatio))</f>
@@ -14579,7 +15200,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D59" s="34">
         <f>IF(C59="window",0,IF(C59="short",ShortRatio,LongRatio))</f>
@@ -14602,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D60" s="34">
         <f>IF(C60="window",0,IF(C60="short",ShortRatio,LongRatio))</f>
@@ -14625,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D61" s="34">
         <f>IF(C61="window",0,IF(C61="short",ShortRatio,LongRatio))</f>
@@ -14648,7 +15269,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D62" s="34">
         <f>IF(C62="window",0,IF(C62="short",ShortRatio,LongRatio))</f>
@@ -14671,7 +15292,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D63" s="34">
         <f>IF(C63="window",0,IF(C63="short",ShortRatio,LongRatio))</f>
@@ -14694,7 +15315,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D64" s="34">
         <f>IF(C64="window",0,IF(C64="short",ShortRatio,LongRatio))</f>
@@ -14717,7 +15338,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D65" s="34">
         <f>IF(C65="window",0,IF(C65="short",ShortRatio,LongRatio))</f>
@@ -14740,7 +15361,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D66" s="34">
         <f>IF(C66="window",0,IF(C66="short",ShortRatio,LongRatio))</f>
@@ -14763,7 +15384,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D67" s="34">
         <f>IF(C67="window",0,IF(C67="short",ShortRatio,LongRatio))</f>
@@ -14803,15 +15424,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>466</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -14819,31 +15440,31 @@
         <v>348</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -14851,71 +15472,71 @@
         <v>59</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>398</v>
+        <v>486</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
